--- a/data/Trump_Second_Term_Weekly_Tracker.xlsx
+++ b/data/Trump_Second_Term_Weekly_Tracker.xlsx
@@ -13,7 +13,7 @@
     <sheet name="Summary" sheetId="3" state="visible" r:id="rId5"/>
   </sheets>
   <definedNames>
-    <definedName function="false" hidden="true" localSheetId="0" name="_xlnm._FilterDatabase" vbProcedure="false">'Weekly Timeline'!$A$2:$F$226</definedName>
+    <definedName function="false" hidden="true" localSheetId="0" name="_xlnm._FilterDatabase" vbProcedure="false">'Weekly Timeline'!$A$2:$F$234</definedName>
   </definedNames>
   <calcPr iterateCount="100" refMode="A1" iterate="false" iterateDelta="0.0001"/>
   <extLst>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1807" uniqueCount="1204">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1864" uniqueCount="1226">
   <si>
     <t xml:space="preserve">Documented actions and policies of the second Trump administration reported as harmful by major news outlets, courts, and government data — Jan 20, 2025 through Jul 8, 2026. One row per event; weeks with multiple events have multiple rows; quiet weeks are skipped. This compiles critical coverage as requested; the administration and its supporters dispute many of these characterizations. See the Sources tab (matching Ref #) and verify details independently before citing.</t>
   </si>
@@ -1692,6 +1692,18 @@
     <t xml:space="preserve">Sep 4</t>
   </si>
   <si>
+    <t xml:space="preserve">Sep 7, 2026</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Sep 10</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Sep 11</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Elections</t>
+  </si>
+  <si>
     <t xml:space="preserve">Ref # matches the Source Ref column on the Weekly Timeline tab. URLs are provided where verified via current web results (mostly 2026 items). For 2025 items, outlet names and dates are given; searching the description text will locate the original coverage. Per your request the mix emphasizes CNN, Politico, MSNBC/MS NOW, NBC and independent outlets, alongside AP, Reuters, Guardian, NPR, CBS, ABC and court documents.</t>
   </si>
   <si>
@@ -3628,6 +3640,60 @@
   </si>
   <si>
     <t xml:space="preserve">https://www.cbsnews.com/news/judge-allows-pentagon-fire-stars-stripes-journalists/</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Jimmy Kimmel says show won’t air James Talarico interview on TV, citing FCC threats</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://www.nbcnews.com/politics/trump-administration/jimmy-kimmel-abc-tv-show-wont-air-james-talarico-interview-fcc-threats-rcna596994</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Sep 10, 2026</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Trump: we will pay every US citizen $5,000 if Republicans win midterms – video</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://www.theguardian.com/us-news/video/2026/sep/10/trump-we-will-pay-every-us-citizen-5000-if-republicans-win-midterms-video</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Appeals court declines to lift block on Postal Service rule for mail ballots</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://www.cbsnews.com/news/appeals-court-trump-usps-mail-ballots-first-circuit/</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Joe diGenova resigns from DOJ after overseeing "grand conspiracy" probe</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://www.cbsnews.com/news/joe-digenova-resigns-doj-grand-conspiracy-investigation-trump-obama-biden/</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Sep 11, 2026</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Under Trump, census eyes sweeping plan to omit immigrants, race data</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://abcnews.com/Politics/wireStory/trump-census-eyes-sweeping-plan-omit-immigrants-race-136353634</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Justice Department directs states to hold on to 2024 election records as it seeks their voter data</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://abcnews.com/Politics/wireStory/justice-department-directs-states-hold-2024-election-records-136350319</t>
+  </si>
+  <si>
+    <t xml:space="preserve">News Wrap: August inflation report shows consumer prices up 3.4%</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://www.pbs.org/newshour/show/news-wrap-august-inflation-report-shows-consumer-prices-up-3-4</t>
+  </si>
+  <si>
+    <t xml:space="preserve">WATCH: Trump leads RNC in pledge to 'cheat like hell' in November elections</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://www.pbs.org/newshour/politics/watch-trump-leads-rnc-in-pledge-to-cheat-like-hell-in-november-elections</t>
   </si>
   <si>
     <t xml:space="preserve">Entries by category (live COUNTIF formulas against the Weekly Timeline tab)</t>
@@ -4109,7 +4175,7 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:F226"/>
+  <dimension ref="A1:F234"/>
   <sheetFormatPr defaultColWidth="8.6875" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="13.01"/>
@@ -8181,7 +8247,7 @@
         <v>220</v>
       </c>
     </row>
-    <row r="223" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="223" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A223" s="4" t="s">
         <v>551</v>
       </c>
@@ -8197,7 +8263,7 @@
         <v>221</v>
       </c>
     </row>
-    <row r="224" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="224" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A224" s="4" t="s">
         <v>551</v>
       </c>
@@ -8213,7 +8279,7 @@
         <v>222</v>
       </c>
     </row>
-    <row r="225" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="225" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A225" s="4" t="s">
         <v>551</v>
       </c>
@@ -8229,7 +8295,7 @@
         <v>223</v>
       </c>
     </row>
-    <row r="226" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="226" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A226" s="4" t="s">
         <v>551</v>
       </c>
@@ -8245,8 +8311,136 @@
         <v>224</v>
       </c>
     </row>
+    <row r="227" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A227" s="5" t="s">
+        <v>555</v>
+      </c>
+      <c r="B227" s="5" t="s">
+        <v>556</v>
+      </c>
+      <c r="C227" s="5" t="s">
+        <v>68</v>
+      </c>
+      <c r="D227" s="5"/>
+      <c r="E227" s="5"/>
+      <c r="F227" s="5" t="n">
+        <v>225</v>
+      </c>
+    </row>
+    <row r="228" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A228" s="5" t="s">
+        <v>555</v>
+      </c>
+      <c r="B228" s="5" t="s">
+        <v>556</v>
+      </c>
+      <c r="C228" s="5" t="s">
+        <v>24</v>
+      </c>
+      <c r="D228" s="5"/>
+      <c r="E228" s="5"/>
+      <c r="F228" s="5" t="n">
+        <v>226</v>
+      </c>
+    </row>
+    <row r="229" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A229" s="5" t="s">
+        <v>555</v>
+      </c>
+      <c r="B229" s="5" t="s">
+        <v>556</v>
+      </c>
+      <c r="C229" s="5" t="s">
+        <v>194</v>
+      </c>
+      <c r="D229" s="5"/>
+      <c r="E229" s="5"/>
+      <c r="F229" s="5" t="n">
+        <v>227</v>
+      </c>
+    </row>
+    <row r="230" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A230" s="5" t="s">
+        <v>555</v>
+      </c>
+      <c r="B230" s="5" t="s">
+        <v>557</v>
+      </c>
+      <c r="C230" s="5" t="s">
+        <v>194</v>
+      </c>
+      <c r="D230" s="5"/>
+      <c r="E230" s="5"/>
+      <c r="F230" s="5" t="n">
+        <v>228</v>
+      </c>
+    </row>
+    <row r="231" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A231" s="5" t="s">
+        <v>555</v>
+      </c>
+      <c r="B231" s="5" t="s">
+        <v>557</v>
+      </c>
+      <c r="C231" s="5" t="s">
+        <v>18</v>
+      </c>
+      <c r="D231" s="5"/>
+      <c r="E231" s="5"/>
+      <c r="F231" s="5" t="n">
+        <v>229</v>
+      </c>
+    </row>
+    <row r="232" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A232" s="5" t="s">
+        <v>555</v>
+      </c>
+      <c r="B232" s="5" t="s">
+        <v>557</v>
+      </c>
+      <c r="C232" s="5" t="s">
+        <v>558</v>
+      </c>
+      <c r="D232" s="5"/>
+      <c r="E232" s="5"/>
+      <c r="F232" s="5" t="n">
+        <v>230</v>
+      </c>
+    </row>
+    <row r="233" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A233" s="5" t="s">
+        <v>555</v>
+      </c>
+      <c r="B233" s="5" t="s">
+        <v>557</v>
+      </c>
+      <c r="C233" s="5" t="s">
+        <v>100</v>
+      </c>
+      <c r="D233" s="5"/>
+      <c r="E233" s="5"/>
+      <c r="F233" s="5" t="n">
+        <v>231</v>
+      </c>
+    </row>
+    <row r="234" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A234" s="5" t="s">
+        <v>555</v>
+      </c>
+      <c r="B234" s="5" t="s">
+        <v>557</v>
+      </c>
+      <c r="C234" s="5" t="s">
+        <v>558</v>
+      </c>
+      <c r="D234" s="5"/>
+      <c r="E234" s="5"/>
+      <c r="F234" s="5" t="n">
+        <v>232</v>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A2:F226"/>
+  <autoFilter ref="A2:F234"/>
   <mergeCells count="1">
     <mergeCell ref="A1:F1"/>
   </mergeCells>
@@ -8266,7 +8460,7 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:E233"/>
+  <dimension ref="A1:E241"/>
   <sheetFormatPr defaultColWidth="8.6875" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="7"/>
@@ -8277,7 +8471,7 @@
   <sheetData>
     <row r="1" customFormat="false" ht="48" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A1" s="2" t="s">
-        <v>555</v>
+        <v>559</v>
       </c>
       <c r="B1" s="2"/>
       <c r="C1" s="2"/>
@@ -8286,19 +8480,19 @@
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A2" s="3" t="s">
-        <v>556</v>
+        <v>560</v>
       </c>
       <c r="B2" s="3" t="s">
-        <v>557</v>
+        <v>561</v>
       </c>
       <c r="C2" s="3" t="s">
-        <v>558</v>
+        <v>562</v>
       </c>
       <c r="D2" s="3" t="s">
-        <v>559</v>
+        <v>563</v>
       </c>
       <c r="E2" s="3" t="s">
-        <v>560</v>
+        <v>564</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -8306,14 +8500,14 @@
         <v>1</v>
       </c>
       <c r="B3" s="5" t="s">
-        <v>561</v>
+        <v>565</v>
       </c>
       <c r="C3" s="5" t="s">
-        <v>562</v>
+        <v>566</v>
       </c>
       <c r="D3" s="5"/>
       <c r="E3" s="5" t="s">
-        <v>563</v>
+        <v>567</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -8321,14 +8515,14 @@
         <v>2</v>
       </c>
       <c r="B4" s="5" t="s">
-        <v>564</v>
+        <v>568</v>
       </c>
       <c r="C4" s="5" t="s">
-        <v>565</v>
+        <v>569</v>
       </c>
       <c r="D4" s="5"/>
       <c r="E4" s="5" t="s">
-        <v>566</v>
+        <v>570</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -8336,14 +8530,14 @@
         <v>3</v>
       </c>
       <c r="B5" s="5" t="s">
-        <v>567</v>
+        <v>571</v>
       </c>
       <c r="C5" s="5" t="s">
-        <v>568</v>
+        <v>572</v>
       </c>
       <c r="D5" s="5"/>
       <c r="E5" s="5" t="s">
-        <v>563</v>
+        <v>567</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -8351,14 +8545,14 @@
         <v>4</v>
       </c>
       <c r="B6" s="5" t="s">
-        <v>569</v>
+        <v>573</v>
       </c>
       <c r="C6" s="5" t="s">
-        <v>570</v>
+        <v>574</v>
       </c>
       <c r="D6" s="5"/>
       <c r="E6" s="5" t="s">
-        <v>571</v>
+        <v>575</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -8366,14 +8560,14 @@
         <v>5</v>
       </c>
       <c r="B7" s="5" t="s">
-        <v>572</v>
+        <v>576</v>
       </c>
       <c r="C7" s="5" t="s">
-        <v>573</v>
+        <v>577</v>
       </c>
       <c r="D7" s="5"/>
       <c r="E7" s="5" t="s">
-        <v>563</v>
+        <v>567</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -8381,14 +8575,14 @@
         <v>6</v>
       </c>
       <c r="B8" s="5" t="s">
-        <v>574</v>
+        <v>578</v>
       </c>
       <c r="C8" s="5" t="s">
-        <v>575</v>
+        <v>579</v>
       </c>
       <c r="D8" s="5"/>
       <c r="E8" s="5" t="s">
-        <v>563</v>
+        <v>567</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -8396,14 +8590,14 @@
         <v>7</v>
       </c>
       <c r="B9" s="5" t="s">
-        <v>576</v>
+        <v>580</v>
       </c>
       <c r="C9" s="5" t="s">
-        <v>577</v>
+        <v>581</v>
       </c>
       <c r="D9" s="5"/>
       <c r="E9" s="5" t="s">
-        <v>578</v>
+        <v>582</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -8411,14 +8605,14 @@
         <v>8</v>
       </c>
       <c r="B10" s="5" t="s">
-        <v>579</v>
+        <v>583</v>
       </c>
       <c r="C10" s="5" t="s">
-        <v>580</v>
+        <v>584</v>
       </c>
       <c r="D10" s="5"/>
       <c r="E10" s="5" t="s">
-        <v>581</v>
+        <v>585</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -8426,14 +8620,14 @@
         <v>9</v>
       </c>
       <c r="B11" s="5" t="s">
-        <v>582</v>
+        <v>586</v>
       </c>
       <c r="C11" s="5" t="s">
-        <v>583</v>
+        <v>587</v>
       </c>
       <c r="D11" s="5"/>
       <c r="E11" s="5" t="s">
-        <v>584</v>
+        <v>588</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -8441,14 +8635,14 @@
         <v>10</v>
       </c>
       <c r="B12" s="5" t="s">
-        <v>585</v>
+        <v>589</v>
       </c>
       <c r="C12" s="5" t="s">
-        <v>586</v>
+        <v>590</v>
       </c>
       <c r="D12" s="5"/>
       <c r="E12" s="5" t="s">
-        <v>587</v>
+        <v>591</v>
       </c>
     </row>
     <row r="13" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -8456,14 +8650,14 @@
         <v>11</v>
       </c>
       <c r="B13" s="5" t="s">
-        <v>588</v>
+        <v>592</v>
       </c>
       <c r="C13" s="5" t="s">
-        <v>589</v>
+        <v>593</v>
       </c>
       <c r="D13" s="5"/>
       <c r="E13" s="5" t="s">
-        <v>590</v>
+        <v>594</v>
       </c>
     </row>
     <row r="14" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -8471,14 +8665,14 @@
         <v>12</v>
       </c>
       <c r="B14" s="5" t="s">
-        <v>591</v>
+        <v>595</v>
       </c>
       <c r="C14" s="5" t="s">
-        <v>592</v>
+        <v>596</v>
       </c>
       <c r="D14" s="5"/>
       <c r="E14" s="5" t="s">
-        <v>593</v>
+        <v>597</v>
       </c>
     </row>
     <row r="15" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -8486,14 +8680,14 @@
         <v>13</v>
       </c>
       <c r="B15" s="5" t="s">
-        <v>594</v>
+        <v>598</v>
       </c>
       <c r="C15" s="5" t="s">
-        <v>595</v>
+        <v>599</v>
       </c>
       <c r="D15" s="5"/>
       <c r="E15" s="5" t="s">
-        <v>596</v>
+        <v>600</v>
       </c>
     </row>
     <row r="16" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -8501,14 +8695,14 @@
         <v>14</v>
       </c>
       <c r="B16" s="5" t="s">
-        <v>597</v>
+        <v>601</v>
       </c>
       <c r="C16" s="5" t="s">
-        <v>598</v>
+        <v>602</v>
       </c>
       <c r="D16" s="5"/>
       <c r="E16" s="5" t="s">
-        <v>599</v>
+        <v>603</v>
       </c>
     </row>
     <row r="17" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -8516,14 +8710,14 @@
         <v>15</v>
       </c>
       <c r="B17" s="5" t="s">
-        <v>600</v>
+        <v>604</v>
       </c>
       <c r="C17" s="5" t="s">
-        <v>601</v>
+        <v>605</v>
       </c>
       <c r="D17" s="5"/>
       <c r="E17" s="5" t="s">
-        <v>602</v>
+        <v>606</v>
       </c>
     </row>
     <row r="18" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -8531,14 +8725,14 @@
         <v>16</v>
       </c>
       <c r="B18" s="5" t="s">
-        <v>603</v>
+        <v>607</v>
       </c>
       <c r="C18" s="5" t="s">
-        <v>604</v>
+        <v>608</v>
       </c>
       <c r="D18" s="5"/>
       <c r="E18" s="5" t="s">
-        <v>605</v>
+        <v>609</v>
       </c>
     </row>
     <row r="19" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -8546,14 +8740,14 @@
         <v>17</v>
       </c>
       <c r="B19" s="5" t="s">
-        <v>606</v>
+        <v>610</v>
       </c>
       <c r="C19" s="5" t="s">
-        <v>607</v>
+        <v>611</v>
       </c>
       <c r="D19" s="5"/>
       <c r="E19" s="5" t="s">
-        <v>608</v>
+        <v>612</v>
       </c>
     </row>
     <row r="20" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -8561,14 +8755,14 @@
         <v>18</v>
       </c>
       <c r="B20" s="5" t="s">
-        <v>609</v>
+        <v>613</v>
       </c>
       <c r="C20" s="5" t="s">
-        <v>610</v>
+        <v>614</v>
       </c>
       <c r="D20" s="5"/>
       <c r="E20" s="5" t="s">
-        <v>611</v>
+        <v>615</v>
       </c>
     </row>
     <row r="21" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -8576,14 +8770,14 @@
         <v>19</v>
       </c>
       <c r="B21" s="5" t="s">
-        <v>612</v>
+        <v>616</v>
       </c>
       <c r="C21" s="5" t="s">
-        <v>613</v>
+        <v>617</v>
       </c>
       <c r="D21" s="5"/>
       <c r="E21" s="5" t="s">
-        <v>614</v>
+        <v>618</v>
       </c>
     </row>
     <row r="22" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -8591,14 +8785,14 @@
         <v>20</v>
       </c>
       <c r="B22" s="5" t="s">
-        <v>615</v>
+        <v>619</v>
       </c>
       <c r="C22" s="5" t="s">
-        <v>616</v>
+        <v>620</v>
       </c>
       <c r="D22" s="5"/>
       <c r="E22" s="5" t="s">
-        <v>617</v>
+        <v>621</v>
       </c>
     </row>
     <row r="23" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -8606,14 +8800,14 @@
         <v>21</v>
       </c>
       <c r="B23" s="5" t="s">
-        <v>618</v>
+        <v>622</v>
       </c>
       <c r="C23" s="5" t="s">
-        <v>619</v>
+        <v>623</v>
       </c>
       <c r="D23" s="5"/>
       <c r="E23" s="5" t="s">
-        <v>620</v>
+        <v>624</v>
       </c>
     </row>
     <row r="24" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -8621,14 +8815,14 @@
         <v>22</v>
       </c>
       <c r="B24" s="5" t="s">
-        <v>621</v>
+        <v>625</v>
       </c>
       <c r="C24" s="5" t="s">
-        <v>622</v>
+        <v>626</v>
       </c>
       <c r="D24" s="5"/>
       <c r="E24" s="5" t="s">
-        <v>623</v>
+        <v>627</v>
       </c>
     </row>
     <row r="25" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -8636,14 +8830,14 @@
         <v>23</v>
       </c>
       <c r="B25" s="5" t="s">
-        <v>624</v>
+        <v>628</v>
       </c>
       <c r="C25" s="5" t="s">
-        <v>625</v>
+        <v>629</v>
       </c>
       <c r="D25" s="5"/>
       <c r="E25" s="5" t="s">
-        <v>626</v>
+        <v>630</v>
       </c>
     </row>
     <row r="26" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -8651,14 +8845,14 @@
         <v>24</v>
       </c>
       <c r="B26" s="5" t="s">
-        <v>627</v>
+        <v>631</v>
       </c>
       <c r="C26" s="5" t="s">
-        <v>628</v>
+        <v>632</v>
       </c>
       <c r="D26" s="5"/>
       <c r="E26" s="5" t="s">
-        <v>629</v>
+        <v>633</v>
       </c>
     </row>
     <row r="27" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -8666,14 +8860,14 @@
         <v>25</v>
       </c>
       <c r="B27" s="5" t="s">
-        <v>630</v>
+        <v>634</v>
       </c>
       <c r="C27" s="5" t="s">
-        <v>631</v>
+        <v>635</v>
       </c>
       <c r="D27" s="5"/>
       <c r="E27" s="5" t="s">
-        <v>632</v>
+        <v>636</v>
       </c>
     </row>
     <row r="28" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -8681,14 +8875,14 @@
         <v>26</v>
       </c>
       <c r="B28" s="5" t="s">
-        <v>633</v>
+        <v>637</v>
       </c>
       <c r="C28" s="5" t="s">
-        <v>634</v>
+        <v>638</v>
       </c>
       <c r="D28" s="5"/>
       <c r="E28" s="5" t="s">
-        <v>635</v>
+        <v>639</v>
       </c>
     </row>
     <row r="29" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -8696,14 +8890,14 @@
         <v>27</v>
       </c>
       <c r="B29" s="5" t="s">
-        <v>636</v>
+        <v>640</v>
       </c>
       <c r="C29" s="5" t="s">
-        <v>637</v>
+        <v>641</v>
       </c>
       <c r="D29" s="5"/>
       <c r="E29" s="5" t="s">
-        <v>638</v>
+        <v>642</v>
       </c>
     </row>
     <row r="30" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -8711,14 +8905,14 @@
         <v>28</v>
       </c>
       <c r="B30" s="5" t="s">
-        <v>639</v>
+        <v>643</v>
       </c>
       <c r="C30" s="5" t="s">
-        <v>640</v>
+        <v>644</v>
       </c>
       <c r="D30" s="5"/>
       <c r="E30" s="5" t="s">
-        <v>641</v>
+        <v>645</v>
       </c>
     </row>
     <row r="31" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -8726,14 +8920,14 @@
         <v>29</v>
       </c>
       <c r="B31" s="5" t="s">
-        <v>642</v>
+        <v>646</v>
       </c>
       <c r="C31" s="5" t="s">
-        <v>643</v>
+        <v>647</v>
       </c>
       <c r="D31" s="5"/>
       <c r="E31" s="5" t="s">
-        <v>644</v>
+        <v>648</v>
       </c>
     </row>
     <row r="32" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -8741,14 +8935,14 @@
         <v>30</v>
       </c>
       <c r="B32" s="5" t="s">
-        <v>588</v>
+        <v>592</v>
       </c>
       <c r="C32" s="5" t="s">
-        <v>645</v>
+        <v>649</v>
       </c>
       <c r="D32" s="5"/>
       <c r="E32" s="5" t="s">
-        <v>646</v>
+        <v>650</v>
       </c>
     </row>
     <row r="33" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -8756,14 +8950,14 @@
         <v>31</v>
       </c>
       <c r="B33" s="5" t="s">
-        <v>647</v>
+        <v>651</v>
       </c>
       <c r="C33" s="5" t="s">
-        <v>648</v>
+        <v>652</v>
       </c>
       <c r="D33" s="5"/>
       <c r="E33" s="5" t="s">
-        <v>649</v>
+        <v>653</v>
       </c>
     </row>
     <row r="34" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -8771,14 +8965,14 @@
         <v>32</v>
       </c>
       <c r="B34" s="5" t="s">
-        <v>606</v>
+        <v>610</v>
       </c>
       <c r="C34" s="5" t="s">
-        <v>650</v>
+        <v>654</v>
       </c>
       <c r="D34" s="5"/>
       <c r="E34" s="5" t="s">
-        <v>651</v>
+        <v>655</v>
       </c>
     </row>
     <row r="35" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -8786,14 +8980,14 @@
         <v>33</v>
       </c>
       <c r="B35" s="5" t="s">
-        <v>652</v>
+        <v>656</v>
       </c>
       <c r="C35" s="5" t="s">
-        <v>653</v>
+        <v>657</v>
       </c>
       <c r="D35" s="5"/>
       <c r="E35" s="5" t="s">
-        <v>654</v>
+        <v>658</v>
       </c>
     </row>
     <row r="36" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -8801,14 +8995,14 @@
         <v>34</v>
       </c>
       <c r="B36" s="5" t="s">
-        <v>655</v>
+        <v>659</v>
       </c>
       <c r="C36" s="5" t="s">
-        <v>656</v>
+        <v>660</v>
       </c>
       <c r="D36" s="5"/>
       <c r="E36" s="5" t="s">
-        <v>657</v>
+        <v>661</v>
       </c>
     </row>
     <row r="37" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -8816,14 +9010,14 @@
         <v>35</v>
       </c>
       <c r="B37" s="5" t="s">
-        <v>658</v>
+        <v>662</v>
       </c>
       <c r="C37" s="5" t="s">
-        <v>659</v>
+        <v>663</v>
       </c>
       <c r="D37" s="5"/>
       <c r="E37" s="5" t="s">
-        <v>660</v>
+        <v>664</v>
       </c>
     </row>
     <row r="38" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -8831,14 +9025,14 @@
         <v>36</v>
       </c>
       <c r="B38" s="5" t="s">
-        <v>606</v>
+        <v>610</v>
       </c>
       <c r="C38" s="5" t="s">
-        <v>661</v>
+        <v>665</v>
       </c>
       <c r="D38" s="5"/>
       <c r="E38" s="5" t="s">
-        <v>662</v>
+        <v>666</v>
       </c>
     </row>
     <row r="39" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -8846,14 +9040,14 @@
         <v>37</v>
       </c>
       <c r="B39" s="5" t="s">
-        <v>663</v>
+        <v>667</v>
       </c>
       <c r="C39" s="5" t="s">
-        <v>664</v>
+        <v>668</v>
       </c>
       <c r="D39" s="5"/>
       <c r="E39" s="5" t="s">
-        <v>665</v>
+        <v>669</v>
       </c>
     </row>
     <row r="40" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -8861,14 +9055,14 @@
         <v>38</v>
       </c>
       <c r="B40" s="5" t="s">
-        <v>666</v>
+        <v>670</v>
       </c>
       <c r="C40" s="5" t="s">
-        <v>667</v>
+        <v>671</v>
       </c>
       <c r="D40" s="5"/>
       <c r="E40" s="5" t="s">
-        <v>668</v>
+        <v>672</v>
       </c>
     </row>
     <row r="41" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -8876,10 +9070,10 @@
         <v>39</v>
       </c>
       <c r="B41" s="5" t="s">
-        <v>669</v>
+        <v>673</v>
       </c>
       <c r="C41" s="5" t="s">
-        <v>670</v>
+        <v>674</v>
       </c>
       <c r="D41" s="5"/>
       <c r="E41" s="5" t="s">
@@ -8891,14 +9085,14 @@
         <v>40</v>
       </c>
       <c r="B42" s="5" t="s">
-        <v>671</v>
+        <v>675</v>
       </c>
       <c r="C42" s="5" t="s">
-        <v>672</v>
+        <v>676</v>
       </c>
       <c r="D42" s="5"/>
       <c r="E42" s="5" t="s">
-        <v>673</v>
+        <v>677</v>
       </c>
     </row>
     <row r="43" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -8906,14 +9100,14 @@
         <v>41</v>
       </c>
       <c r="B43" s="5" t="s">
-        <v>674</v>
+        <v>678</v>
       </c>
       <c r="C43" s="5" t="s">
-        <v>675</v>
+        <v>679</v>
       </c>
       <c r="D43" s="5"/>
       <c r="E43" s="5" t="s">
-        <v>676</v>
+        <v>680</v>
       </c>
     </row>
     <row r="44" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -8921,14 +9115,14 @@
         <v>42</v>
       </c>
       <c r="B44" s="5" t="s">
-        <v>677</v>
+        <v>681</v>
       </c>
       <c r="C44" s="5" t="s">
-        <v>678</v>
+        <v>682</v>
       </c>
       <c r="D44" s="5"/>
       <c r="E44" s="5" t="s">
-        <v>679</v>
+        <v>683</v>
       </c>
     </row>
     <row r="45" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -8936,14 +9130,14 @@
         <v>43</v>
       </c>
       <c r="B45" s="5" t="s">
-        <v>680</v>
+        <v>684</v>
       </c>
       <c r="C45" s="5" t="s">
-        <v>681</v>
+        <v>685</v>
       </c>
       <c r="D45" s="5"/>
       <c r="E45" s="5" t="s">
-        <v>682</v>
+        <v>686</v>
       </c>
     </row>
     <row r="46" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -8951,14 +9145,14 @@
         <v>44</v>
       </c>
       <c r="B46" s="5" t="s">
-        <v>683</v>
+        <v>687</v>
       </c>
       <c r="C46" s="5" t="s">
-        <v>684</v>
+        <v>688</v>
       </c>
       <c r="D46" s="5"/>
       <c r="E46" s="5" t="s">
-        <v>685</v>
+        <v>689</v>
       </c>
     </row>
     <row r="47" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -8966,14 +9160,14 @@
         <v>45</v>
       </c>
       <c r="B47" s="5" t="s">
-        <v>686</v>
+        <v>690</v>
       </c>
       <c r="C47" s="5" t="s">
-        <v>687</v>
+        <v>691</v>
       </c>
       <c r="D47" s="5"/>
       <c r="E47" s="5" t="s">
-        <v>688</v>
+        <v>692</v>
       </c>
     </row>
     <row r="48" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -8981,14 +9175,14 @@
         <v>46</v>
       </c>
       <c r="B48" s="5" t="s">
-        <v>689</v>
+        <v>693</v>
       </c>
       <c r="C48" s="5" t="s">
-        <v>690</v>
+        <v>694</v>
       </c>
       <c r="D48" s="5"/>
       <c r="E48" s="5" t="s">
-        <v>691</v>
+        <v>695</v>
       </c>
     </row>
     <row r="49" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -8996,14 +9190,14 @@
         <v>47</v>
       </c>
       <c r="B49" s="5" t="s">
-        <v>692</v>
+        <v>696</v>
       </c>
       <c r="C49" s="5" t="s">
-        <v>693</v>
+        <v>697</v>
       </c>
       <c r="D49" s="5"/>
       <c r="E49" s="5" t="s">
-        <v>694</v>
+        <v>698</v>
       </c>
     </row>
     <row r="50" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -9011,14 +9205,14 @@
         <v>48</v>
       </c>
       <c r="B50" s="5" t="s">
-        <v>695</v>
+        <v>699</v>
       </c>
       <c r="C50" s="5" t="s">
-        <v>696</v>
+        <v>700</v>
       </c>
       <c r="D50" s="5"/>
       <c r="E50" s="5" t="s">
-        <v>697</v>
+        <v>701</v>
       </c>
     </row>
     <row r="51" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -9026,14 +9220,14 @@
         <v>49</v>
       </c>
       <c r="B51" s="5" t="s">
-        <v>698</v>
+        <v>702</v>
       </c>
       <c r="C51" s="5" t="s">
-        <v>699</v>
+        <v>703</v>
       </c>
       <c r="D51" s="5"/>
       <c r="E51" s="5" t="s">
-        <v>700</v>
+        <v>704</v>
       </c>
     </row>
     <row r="52" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -9041,14 +9235,14 @@
         <v>50</v>
       </c>
       <c r="B52" s="5" t="s">
-        <v>701</v>
+        <v>705</v>
       </c>
       <c r="C52" s="5" t="s">
-        <v>702</v>
+        <v>706</v>
       </c>
       <c r="D52" s="5"/>
       <c r="E52" s="5" t="s">
-        <v>703</v>
+        <v>707</v>
       </c>
     </row>
     <row r="53" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -9056,14 +9250,14 @@
         <v>51</v>
       </c>
       <c r="B53" s="5" t="s">
-        <v>704</v>
+        <v>708</v>
       </c>
       <c r="C53" s="5" t="s">
-        <v>705</v>
+        <v>709</v>
       </c>
       <c r="D53" s="5"/>
       <c r="E53" s="5" t="s">
-        <v>706</v>
+        <v>710</v>
       </c>
     </row>
     <row r="54" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -9071,14 +9265,14 @@
         <v>52</v>
       </c>
       <c r="B54" s="5" t="s">
-        <v>606</v>
+        <v>610</v>
       </c>
       <c r="C54" s="5" t="s">
-        <v>707</v>
+        <v>711</v>
       </c>
       <c r="D54" s="5"/>
       <c r="E54" s="5" t="s">
-        <v>708</v>
+        <v>712</v>
       </c>
     </row>
     <row r="55" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -9086,14 +9280,14 @@
         <v>53</v>
       </c>
       <c r="B55" s="5" t="s">
-        <v>709</v>
+        <v>713</v>
       </c>
       <c r="C55" s="5" t="s">
-        <v>710</v>
+        <v>714</v>
       </c>
       <c r="D55" s="5"/>
       <c r="E55" s="5" t="s">
-        <v>711</v>
+        <v>715</v>
       </c>
     </row>
     <row r="56" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -9101,14 +9295,14 @@
         <v>54</v>
       </c>
       <c r="B56" s="5" t="s">
-        <v>712</v>
+        <v>716</v>
       </c>
       <c r="C56" s="5" t="s">
-        <v>713</v>
+        <v>717</v>
       </c>
       <c r="D56" s="5"/>
       <c r="E56" s="5" t="s">
-        <v>714</v>
+        <v>718</v>
       </c>
     </row>
     <row r="57" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -9116,14 +9310,14 @@
         <v>55</v>
       </c>
       <c r="B57" s="5" t="s">
-        <v>715</v>
+        <v>719</v>
       </c>
       <c r="C57" s="5" t="s">
-        <v>716</v>
+        <v>720</v>
       </c>
       <c r="D57" s="5"/>
       <c r="E57" s="5" t="s">
-        <v>717</v>
+        <v>721</v>
       </c>
     </row>
     <row r="58" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -9131,14 +9325,14 @@
         <v>56</v>
       </c>
       <c r="B58" s="5" t="s">
-        <v>718</v>
+        <v>722</v>
       </c>
       <c r="C58" s="5" t="s">
-        <v>719</v>
+        <v>723</v>
       </c>
       <c r="D58" s="5"/>
       <c r="E58" s="5" t="s">
-        <v>720</v>
+        <v>724</v>
       </c>
     </row>
     <row r="59" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -9146,14 +9340,14 @@
         <v>57</v>
       </c>
       <c r="B59" s="5" t="s">
-        <v>721</v>
+        <v>725</v>
       </c>
       <c r="C59" s="5" t="s">
-        <v>722</v>
+        <v>726</v>
       </c>
       <c r="D59" s="5"/>
       <c r="E59" s="5" t="s">
-        <v>723</v>
+        <v>727</v>
       </c>
     </row>
     <row r="60" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -9161,14 +9355,14 @@
         <v>58</v>
       </c>
       <c r="B60" s="5" t="s">
-        <v>724</v>
+        <v>728</v>
       </c>
       <c r="C60" s="5" t="s">
-        <v>725</v>
+        <v>729</v>
       </c>
       <c r="D60" s="5"/>
       <c r="E60" s="5" t="s">
-        <v>726</v>
+        <v>730</v>
       </c>
     </row>
     <row r="61" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -9176,14 +9370,14 @@
         <v>59</v>
       </c>
       <c r="B61" s="5" t="s">
-        <v>727</v>
+        <v>731</v>
       </c>
       <c r="C61" s="5" t="s">
-        <v>728</v>
+        <v>732</v>
       </c>
       <c r="D61" s="5"/>
       <c r="E61" s="5" t="s">
-        <v>729</v>
+        <v>733</v>
       </c>
     </row>
     <row r="62" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -9191,14 +9385,14 @@
         <v>60</v>
       </c>
       <c r="B62" s="5" t="s">
-        <v>730</v>
+        <v>734</v>
       </c>
       <c r="C62" s="5" t="s">
-        <v>731</v>
+        <v>735</v>
       </c>
       <c r="D62" s="5"/>
       <c r="E62" s="5" t="s">
-        <v>732</v>
+        <v>736</v>
       </c>
     </row>
     <row r="63" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -9206,14 +9400,14 @@
         <v>61</v>
       </c>
       <c r="B63" s="5" t="s">
-        <v>733</v>
+        <v>737</v>
       </c>
       <c r="C63" s="5" t="s">
-        <v>734</v>
+        <v>738</v>
       </c>
       <c r="D63" s="5"/>
       <c r="E63" s="5" t="s">
-        <v>735</v>
+        <v>739</v>
       </c>
     </row>
     <row r="64" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -9221,14 +9415,14 @@
         <v>62</v>
       </c>
       <c r="B64" s="5" t="s">
-        <v>736</v>
+        <v>740</v>
       </c>
       <c r="C64" s="5" t="s">
-        <v>737</v>
+        <v>741</v>
       </c>
       <c r="D64" s="5"/>
       <c r="E64" s="5" t="s">
-        <v>738</v>
+        <v>742</v>
       </c>
     </row>
     <row r="65" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -9236,14 +9430,14 @@
         <v>63</v>
       </c>
       <c r="B65" s="5" t="s">
-        <v>739</v>
+        <v>743</v>
       </c>
       <c r="C65" s="5" t="s">
-        <v>740</v>
+        <v>744</v>
       </c>
       <c r="D65" s="5"/>
       <c r="E65" s="5" t="s">
-        <v>741</v>
+        <v>745</v>
       </c>
     </row>
     <row r="66" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -9251,14 +9445,14 @@
         <v>64</v>
       </c>
       <c r="B66" s="5" t="s">
-        <v>742</v>
+        <v>746</v>
       </c>
       <c r="C66" s="5" t="s">
-        <v>743</v>
+        <v>747</v>
       </c>
       <c r="D66" s="5"/>
       <c r="E66" s="5" t="s">
-        <v>744</v>
+        <v>748</v>
       </c>
     </row>
     <row r="67" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -9266,14 +9460,14 @@
         <v>65</v>
       </c>
       <c r="B67" s="5" t="s">
-        <v>745</v>
+        <v>749</v>
       </c>
       <c r="C67" s="5" t="s">
-        <v>746</v>
+        <v>750</v>
       </c>
       <c r="D67" s="5"/>
       <c r="E67" s="5" t="s">
-        <v>747</v>
+        <v>751</v>
       </c>
     </row>
     <row r="68" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -9281,14 +9475,14 @@
         <v>66</v>
       </c>
       <c r="B68" s="5" t="s">
-        <v>748</v>
+        <v>752</v>
       </c>
       <c r="C68" s="5" t="s">
-        <v>749</v>
+        <v>753</v>
       </c>
       <c r="D68" s="5"/>
       <c r="E68" s="5" t="s">
-        <v>750</v>
+        <v>754</v>
       </c>
     </row>
     <row r="69" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -9296,14 +9490,14 @@
         <v>67</v>
       </c>
       <c r="B69" s="5" t="s">
-        <v>751</v>
+        <v>755</v>
       </c>
       <c r="C69" s="5" t="s">
-        <v>752</v>
+        <v>756</v>
       </c>
       <c r="D69" s="5"/>
       <c r="E69" s="5" t="s">
-        <v>753</v>
+        <v>757</v>
       </c>
     </row>
     <row r="70" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -9311,14 +9505,14 @@
         <v>68</v>
       </c>
       <c r="B70" s="5" t="s">
-        <v>754</v>
+        <v>758</v>
       </c>
       <c r="C70" s="5" t="s">
-        <v>755</v>
+        <v>759</v>
       </c>
       <c r="D70" s="5"/>
       <c r="E70" s="5" t="s">
-        <v>756</v>
+        <v>760</v>
       </c>
     </row>
     <row r="71" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -9326,14 +9520,14 @@
         <v>69</v>
       </c>
       <c r="B71" s="5" t="s">
-        <v>757</v>
+        <v>761</v>
       </c>
       <c r="C71" s="5" t="s">
-        <v>758</v>
+        <v>762</v>
       </c>
       <c r="D71" s="5"/>
       <c r="E71" s="5" t="s">
-        <v>759</v>
+        <v>763</v>
       </c>
     </row>
     <row r="72" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -9341,14 +9535,14 @@
         <v>70</v>
       </c>
       <c r="B72" s="5" t="s">
-        <v>760</v>
+        <v>764</v>
       </c>
       <c r="C72" s="5" t="s">
-        <v>761</v>
+        <v>765</v>
       </c>
       <c r="D72" s="5"/>
       <c r="E72" s="5" t="s">
-        <v>762</v>
+        <v>766</v>
       </c>
     </row>
     <row r="73" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -9356,14 +9550,14 @@
         <v>71</v>
       </c>
       <c r="B73" s="5" t="s">
-        <v>763</v>
+        <v>767</v>
       </c>
       <c r="C73" s="5" t="s">
-        <v>764</v>
+        <v>768</v>
       </c>
       <c r="D73" s="5"/>
       <c r="E73" s="5" t="s">
-        <v>765</v>
+        <v>769</v>
       </c>
     </row>
     <row r="74" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -9371,14 +9565,14 @@
         <v>72</v>
       </c>
       <c r="B74" s="5" t="s">
-        <v>766</v>
+        <v>770</v>
       </c>
       <c r="C74" s="5" t="s">
-        <v>767</v>
+        <v>771</v>
       </c>
       <c r="D74" s="5"/>
       <c r="E74" s="5" t="s">
-        <v>768</v>
+        <v>772</v>
       </c>
     </row>
     <row r="75" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -9386,14 +9580,14 @@
         <v>73</v>
       </c>
       <c r="B75" s="5" t="s">
-        <v>606</v>
+        <v>610</v>
       </c>
       <c r="C75" s="5" t="s">
-        <v>769</v>
+        <v>773</v>
       </c>
       <c r="D75" s="5"/>
       <c r="E75" s="5" t="s">
-        <v>770</v>
+        <v>774</v>
       </c>
     </row>
     <row r="76" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -9401,14 +9595,14 @@
         <v>74</v>
       </c>
       <c r="B76" s="5" t="s">
-        <v>771</v>
+        <v>775</v>
       </c>
       <c r="C76" s="5" t="s">
-        <v>772</v>
+        <v>776</v>
       </c>
       <c r="D76" s="5"/>
       <c r="E76" s="5" t="s">
-        <v>773</v>
+        <v>777</v>
       </c>
     </row>
     <row r="77" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -9416,14 +9610,14 @@
         <v>75</v>
       </c>
       <c r="B77" s="5" t="s">
-        <v>606</v>
+        <v>610</v>
       </c>
       <c r="C77" s="5" t="s">
-        <v>774</v>
+        <v>778</v>
       </c>
       <c r="D77" s="5"/>
       <c r="E77" s="5" t="s">
-        <v>775</v>
+        <v>779</v>
       </c>
     </row>
     <row r="78" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -9431,14 +9625,14 @@
         <v>76</v>
       </c>
       <c r="B78" s="5" t="s">
-        <v>776</v>
+        <v>780</v>
       </c>
       <c r="C78" s="5" t="s">
-        <v>777</v>
+        <v>781</v>
       </c>
       <c r="D78" s="5"/>
       <c r="E78" s="5" t="s">
-        <v>778</v>
+        <v>782</v>
       </c>
     </row>
     <row r="79" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -9446,14 +9640,14 @@
         <v>77</v>
       </c>
       <c r="B79" s="5" t="s">
-        <v>779</v>
+        <v>783</v>
       </c>
       <c r="C79" s="5" t="s">
-        <v>780</v>
+        <v>784</v>
       </c>
       <c r="D79" s="5"/>
       <c r="E79" s="5" t="s">
-        <v>781</v>
+        <v>785</v>
       </c>
     </row>
     <row r="80" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -9461,14 +9655,14 @@
         <v>78</v>
       </c>
       <c r="B80" s="5" t="s">
-        <v>704</v>
+        <v>708</v>
       </c>
       <c r="C80" s="5" t="s">
-        <v>782</v>
+        <v>786</v>
       </c>
       <c r="D80" s="5"/>
       <c r="E80" s="5" t="s">
-        <v>783</v>
+        <v>787</v>
       </c>
     </row>
     <row r="81" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -9476,14 +9670,14 @@
         <v>79</v>
       </c>
       <c r="B81" s="5" t="s">
-        <v>576</v>
+        <v>580</v>
       </c>
       <c r="C81" s="5" t="s">
-        <v>784</v>
+        <v>788</v>
       </c>
       <c r="D81" s="5"/>
       <c r="E81" s="5" t="s">
-        <v>785</v>
+        <v>789</v>
       </c>
     </row>
     <row r="82" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -9491,16 +9685,16 @@
         <v>80</v>
       </c>
       <c r="B82" s="5" t="s">
-        <v>786</v>
+        <v>790</v>
       </c>
       <c r="C82" s="5" t="s">
-        <v>787</v>
+        <v>791</v>
       </c>
       <c r="D82" s="6" t="s">
-        <v>788</v>
+        <v>792</v>
       </c>
       <c r="E82" s="5" t="s">
-        <v>789</v>
+        <v>793</v>
       </c>
     </row>
     <row r="83" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -9508,16 +9702,16 @@
         <v>81</v>
       </c>
       <c r="B83" s="5" t="s">
-        <v>790</v>
+        <v>794</v>
       </c>
       <c r="C83" s="5" t="s">
-        <v>791</v>
+        <v>795</v>
       </c>
       <c r="D83" s="6" t="s">
-        <v>792</v>
+        <v>796</v>
       </c>
       <c r="E83" s="5" t="s">
-        <v>793</v>
+        <v>797</v>
       </c>
     </row>
     <row r="84" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -9525,13 +9719,13 @@
         <v>82</v>
       </c>
       <c r="B84" s="5" t="s">
-        <v>794</v>
+        <v>798</v>
       </c>
       <c r="C84" s="5" t="s">
-        <v>795</v>
+        <v>799</v>
       </c>
       <c r="D84" s="6" t="s">
-        <v>796</v>
+        <v>800</v>
       </c>
       <c r="E84" s="5" t="s">
         <v>297</v>
@@ -9542,13 +9736,13 @@
         <v>83</v>
       </c>
       <c r="B85" s="5" t="s">
-        <v>797</v>
+        <v>801</v>
       </c>
       <c r="C85" s="5" t="s">
-        <v>798</v>
+        <v>802</v>
       </c>
       <c r="D85" s="6" t="s">
-        <v>799</v>
+        <v>803</v>
       </c>
       <c r="E85" s="5" t="s">
         <v>300</v>
@@ -9559,16 +9753,16 @@
         <v>84</v>
       </c>
       <c r="B86" s="5" t="s">
-        <v>800</v>
+        <v>804</v>
       </c>
       <c r="C86" s="5" t="s">
-        <v>801</v>
+        <v>805</v>
       </c>
       <c r="D86" s="6" t="s">
-        <v>802</v>
+        <v>806</v>
       </c>
       <c r="E86" s="5" t="s">
-        <v>803</v>
+        <v>807</v>
       </c>
     </row>
     <row r="87" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -9576,16 +9770,16 @@
         <v>85</v>
       </c>
       <c r="B87" s="5" t="s">
-        <v>804</v>
+        <v>808</v>
       </c>
       <c r="C87" s="5" t="s">
-        <v>805</v>
+        <v>809</v>
       </c>
       <c r="D87" s="6" t="s">
-        <v>806</v>
+        <v>810</v>
       </c>
       <c r="E87" s="5" t="s">
-        <v>807</v>
+        <v>811</v>
       </c>
     </row>
     <row r="88" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -9593,16 +9787,16 @@
         <v>86</v>
       </c>
       <c r="B88" s="5" t="s">
-        <v>808</v>
+        <v>812</v>
       </c>
       <c r="C88" s="5" t="s">
-        <v>809</v>
+        <v>813</v>
       </c>
       <c r="D88" s="6" t="s">
-        <v>810</v>
+        <v>814</v>
       </c>
       <c r="E88" s="5" t="s">
-        <v>807</v>
+        <v>811</v>
       </c>
     </row>
     <row r="89" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -9610,16 +9804,16 @@
         <v>87</v>
       </c>
       <c r="B89" s="5" t="s">
+        <v>815</v>
+      </c>
+      <c r="C89" s="5" t="s">
+        <v>816</v>
+      </c>
+      <c r="D89" s="6" t="s">
+        <v>817</v>
+      </c>
+      <c r="E89" s="5" t="s">
         <v>811</v>
-      </c>
-      <c r="C89" s="5" t="s">
-        <v>812</v>
-      </c>
-      <c r="D89" s="6" t="s">
-        <v>813</v>
-      </c>
-      <c r="E89" s="5" t="s">
-        <v>807</v>
       </c>
     </row>
     <row r="90" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -9627,16 +9821,16 @@
         <v>88</v>
       </c>
       <c r="B90" s="5" t="s">
-        <v>814</v>
+        <v>818</v>
       </c>
       <c r="C90" s="5" t="s">
-        <v>815</v>
+        <v>819</v>
       </c>
       <c r="D90" s="6" t="s">
-        <v>816</v>
+        <v>820</v>
       </c>
       <c r="E90" s="5" t="s">
-        <v>817</v>
+        <v>821</v>
       </c>
     </row>
     <row r="91" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -9644,16 +9838,16 @@
         <v>89</v>
       </c>
       <c r="B91" s="5" t="s">
-        <v>818</v>
+        <v>822</v>
       </c>
       <c r="C91" s="5" t="s">
-        <v>819</v>
+        <v>823</v>
       </c>
       <c r="D91" s="6" t="s">
-        <v>820</v>
+        <v>824</v>
       </c>
       <c r="E91" s="5" t="s">
-        <v>817</v>
+        <v>821</v>
       </c>
     </row>
     <row r="92" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -9661,16 +9855,16 @@
         <v>90</v>
       </c>
       <c r="B92" s="5" t="s">
-        <v>808</v>
+        <v>812</v>
       </c>
       <c r="C92" s="5" t="s">
-        <v>821</v>
+        <v>825</v>
       </c>
       <c r="D92" s="6" t="s">
-        <v>822</v>
+        <v>826</v>
       </c>
       <c r="E92" s="5" t="s">
-        <v>823</v>
+        <v>827</v>
       </c>
     </row>
     <row r="93" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -9678,16 +9872,16 @@
         <v>91</v>
       </c>
       <c r="B93" s="5" t="s">
-        <v>824</v>
+        <v>828</v>
       </c>
       <c r="C93" s="5" t="s">
-        <v>825</v>
+        <v>829</v>
       </c>
       <c r="D93" s="6" t="s">
-        <v>826</v>
+        <v>830</v>
       </c>
       <c r="E93" s="5" t="s">
-        <v>823</v>
+        <v>827</v>
       </c>
     </row>
     <row r="94" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -9695,16 +9889,16 @@
         <v>92</v>
       </c>
       <c r="B94" s="5" t="s">
-        <v>827</v>
+        <v>831</v>
       </c>
       <c r="C94" s="5" t="s">
-        <v>828</v>
+        <v>832</v>
       </c>
       <c r="D94" s="6" t="s">
-        <v>829</v>
+        <v>833</v>
       </c>
       <c r="E94" s="5" t="s">
-        <v>830</v>
+        <v>834</v>
       </c>
     </row>
     <row r="95" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -9712,16 +9906,16 @@
         <v>93</v>
       </c>
       <c r="B95" s="5" t="s">
-        <v>669</v>
+        <v>673</v>
       </c>
       <c r="C95" s="5" t="s">
-        <v>831</v>
+        <v>835</v>
       </c>
       <c r="D95" s="6" t="s">
-        <v>832</v>
+        <v>836</v>
       </c>
       <c r="E95" s="5" t="s">
-        <v>833</v>
+        <v>837</v>
       </c>
     </row>
     <row r="96" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -9729,16 +9923,16 @@
         <v>94</v>
       </c>
       <c r="B96" s="5" t="s">
-        <v>814</v>
+        <v>818</v>
       </c>
       <c r="C96" s="5" t="s">
-        <v>834</v>
+        <v>838</v>
       </c>
       <c r="D96" s="6" t="s">
-        <v>835</v>
+        <v>839</v>
       </c>
       <c r="E96" s="5" t="s">
-        <v>833</v>
+        <v>837</v>
       </c>
     </row>
     <row r="97" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -9746,16 +9940,16 @@
         <v>95</v>
       </c>
       <c r="B97" s="5" t="s">
-        <v>836</v>
+        <v>840</v>
       </c>
       <c r="C97" s="5" t="s">
+        <v>841</v>
+      </c>
+      <c r="D97" s="6" t="s">
+        <v>842</v>
+      </c>
+      <c r="E97" s="5" t="s">
         <v>837</v>
-      </c>
-      <c r="D97" s="6" t="s">
-        <v>838</v>
-      </c>
-      <c r="E97" s="5" t="s">
-        <v>833</v>
       </c>
     </row>
     <row r="98" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -9763,16 +9957,16 @@
         <v>96</v>
       </c>
       <c r="B98" s="5" t="s">
-        <v>794</v>
+        <v>798</v>
       </c>
       <c r="C98" s="5" t="s">
-        <v>839</v>
+        <v>843</v>
       </c>
       <c r="D98" s="6" t="s">
-        <v>840</v>
+        <v>844</v>
       </c>
       <c r="E98" s="5" t="s">
-        <v>823</v>
+        <v>827</v>
       </c>
     </row>
     <row r="99" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -9780,16 +9974,16 @@
         <v>97</v>
       </c>
       <c r="B99" s="5" t="s">
-        <v>841</v>
+        <v>845</v>
       </c>
       <c r="C99" s="5" t="s">
-        <v>842</v>
+        <v>846</v>
       </c>
       <c r="D99" s="6" t="s">
-        <v>843</v>
+        <v>847</v>
       </c>
       <c r="E99" s="5" t="s">
-        <v>844</v>
+        <v>848</v>
       </c>
     </row>
     <row r="100" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -9797,16 +9991,16 @@
         <v>98</v>
       </c>
       <c r="B100" s="5" t="s">
-        <v>808</v>
+        <v>812</v>
       </c>
       <c r="C100" s="5" t="s">
-        <v>845</v>
+        <v>849</v>
       </c>
       <c r="D100" s="6" t="s">
-        <v>846</v>
+        <v>850</v>
       </c>
       <c r="E100" s="5" t="s">
-        <v>847</v>
+        <v>851</v>
       </c>
     </row>
     <row r="101" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -9814,16 +10008,16 @@
         <v>99</v>
       </c>
       <c r="B101" s="5" t="s">
-        <v>814</v>
+        <v>818</v>
       </c>
       <c r="C101" s="5" t="s">
-        <v>848</v>
+        <v>852</v>
       </c>
       <c r="D101" s="6" t="s">
-        <v>849</v>
+        <v>853</v>
       </c>
       <c r="E101" s="5" t="s">
-        <v>850</v>
+        <v>854</v>
       </c>
     </row>
     <row r="102" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -9831,16 +10025,16 @@
         <v>100</v>
       </c>
       <c r="B102" s="5" t="s">
-        <v>851</v>
+        <v>855</v>
       </c>
       <c r="C102" s="5" t="s">
-        <v>852</v>
+        <v>856</v>
       </c>
       <c r="D102" s="6" t="s">
-        <v>853</v>
+        <v>857</v>
       </c>
       <c r="E102" s="5" t="s">
-        <v>854</v>
+        <v>858</v>
       </c>
     </row>
     <row r="103" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -9848,16 +10042,16 @@
         <v>101</v>
       </c>
       <c r="B103" s="5" t="s">
-        <v>794</v>
+        <v>798</v>
       </c>
       <c r="C103" s="5" t="s">
-        <v>855</v>
+        <v>859</v>
       </c>
       <c r="D103" s="6" t="s">
-        <v>856</v>
+        <v>860</v>
       </c>
       <c r="E103" s="5" t="s">
-        <v>857</v>
+        <v>861</v>
       </c>
     </row>
     <row r="104" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -9865,13 +10059,13 @@
         <v>102</v>
       </c>
       <c r="B104" s="5" t="s">
-        <v>669</v>
+        <v>673</v>
       </c>
       <c r="C104" s="5" t="s">
-        <v>858</v>
+        <v>862</v>
       </c>
       <c r="D104" s="6" t="s">
-        <v>859</v>
+        <v>863</v>
       </c>
       <c r="E104" s="5" t="s">
         <v>352</v>
@@ -9882,16 +10076,16 @@
         <v>103</v>
       </c>
       <c r="B105" s="5" t="s">
-        <v>860</v>
+        <v>864</v>
       </c>
       <c r="C105" s="5" t="s">
-        <v>861</v>
+        <v>865</v>
       </c>
       <c r="D105" s="6" t="s">
-        <v>862</v>
+        <v>866</v>
       </c>
       <c r="E105" s="5" t="s">
-        <v>863</v>
+        <v>867</v>
       </c>
     </row>
     <row r="106" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -9899,16 +10093,16 @@
         <v>104</v>
       </c>
       <c r="B106" s="5" t="s">
-        <v>864</v>
+        <v>868</v>
       </c>
       <c r="C106" s="5" t="s">
-        <v>865</v>
+        <v>869</v>
       </c>
       <c r="D106" s="6" t="s">
-        <v>866</v>
+        <v>870</v>
       </c>
       <c r="E106" s="5" t="s">
-        <v>867</v>
+        <v>871</v>
       </c>
     </row>
     <row r="107" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -9916,16 +10110,16 @@
         <v>105</v>
       </c>
       <c r="B107" s="5" t="s">
-        <v>868</v>
+        <v>872</v>
       </c>
       <c r="C107" s="5" t="s">
-        <v>869</v>
+        <v>873</v>
       </c>
       <c r="D107" s="6" t="s">
-        <v>870</v>
+        <v>874</v>
       </c>
       <c r="E107" s="5" t="s">
-        <v>871</v>
+        <v>875</v>
       </c>
     </row>
     <row r="108" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -9933,16 +10127,16 @@
         <v>106</v>
       </c>
       <c r="B108" s="5" t="s">
-        <v>864</v>
+        <v>868</v>
       </c>
       <c r="C108" s="5" t="s">
-        <v>872</v>
+        <v>876</v>
       </c>
       <c r="D108" s="6" t="s">
-        <v>873</v>
+        <v>877</v>
       </c>
       <c r="E108" s="5" t="s">
-        <v>874</v>
+        <v>878</v>
       </c>
     </row>
     <row r="109" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -9950,13 +10144,13 @@
         <v>107</v>
       </c>
       <c r="B109" s="5" t="s">
-        <v>875</v>
+        <v>879</v>
       </c>
       <c r="C109" s="5" t="s">
-        <v>876</v>
+        <v>880</v>
       </c>
       <c r="D109" s="6" t="s">
-        <v>877</v>
+        <v>881</v>
       </c>
       <c r="E109" s="5" t="s">
         <v>368</v>
@@ -9967,13 +10161,13 @@
         <v>108</v>
       </c>
       <c r="B110" s="5" t="s">
-        <v>669</v>
+        <v>673</v>
       </c>
       <c r="C110" s="5" t="s">
-        <v>878</v>
+        <v>882</v>
       </c>
       <c r="D110" s="6" t="s">
-        <v>879</v>
+        <v>883</v>
       </c>
       <c r="E110" s="5" t="s">
         <v>368</v>
@@ -9984,16 +10178,16 @@
         <v>109</v>
       </c>
       <c r="B111" s="5" t="s">
-        <v>868</v>
+        <v>872</v>
       </c>
       <c r="C111" s="5" t="s">
-        <v>880</v>
+        <v>884</v>
       </c>
       <c r="D111" s="6" t="s">
-        <v>881</v>
+        <v>885</v>
       </c>
       <c r="E111" s="5" t="s">
-        <v>882</v>
+        <v>886</v>
       </c>
     </row>
     <row r="112" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -10001,16 +10195,16 @@
         <v>110</v>
       </c>
       <c r="B112" s="5" t="s">
-        <v>808</v>
+        <v>812</v>
       </c>
       <c r="C112" s="5" t="s">
-        <v>883</v>
+        <v>887</v>
       </c>
       <c r="D112" s="6" t="s">
-        <v>884</v>
+        <v>888</v>
       </c>
       <c r="E112" s="5" t="s">
-        <v>885</v>
+        <v>889</v>
       </c>
     </row>
     <row r="113" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -10018,13 +10212,13 @@
         <v>111</v>
       </c>
       <c r="B113" s="5" t="s">
-        <v>800</v>
+        <v>804</v>
       </c>
       <c r="C113" s="5" t="s">
-        <v>886</v>
+        <v>890</v>
       </c>
       <c r="D113" s="6" t="s">
-        <v>887</v>
+        <v>891</v>
       </c>
       <c r="E113" s="5" t="s">
         <v>382</v>
@@ -10035,16 +10229,16 @@
         <v>112</v>
       </c>
       <c r="B114" s="5" t="s">
-        <v>808</v>
+        <v>812</v>
       </c>
       <c r="C114" s="5" t="s">
-        <v>888</v>
+        <v>892</v>
       </c>
       <c r="D114" s="6" t="s">
-        <v>889</v>
+        <v>893</v>
       </c>
       <c r="E114" s="5" t="s">
-        <v>890</v>
+        <v>894</v>
       </c>
     </row>
     <row r="115" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -10052,16 +10246,16 @@
         <v>113</v>
       </c>
       <c r="B115" s="5" t="s">
-        <v>891</v>
+        <v>895</v>
       </c>
       <c r="C115" s="5" t="s">
-        <v>892</v>
+        <v>896</v>
       </c>
       <c r="D115" s="6" t="s">
-        <v>893</v>
+        <v>897</v>
       </c>
       <c r="E115" s="5" t="s">
-        <v>894</v>
+        <v>898</v>
       </c>
     </row>
     <row r="116" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -10069,16 +10263,16 @@
         <v>114</v>
       </c>
       <c r="B116" s="5" t="s">
-        <v>814</v>
+        <v>818</v>
       </c>
       <c r="C116" s="5" t="s">
-        <v>895</v>
+        <v>899</v>
       </c>
       <c r="D116" s="6" t="s">
-        <v>896</v>
+        <v>900</v>
       </c>
       <c r="E116" s="5" t="s">
-        <v>894</v>
+        <v>898</v>
       </c>
     </row>
     <row r="117" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -10086,16 +10280,16 @@
         <v>115</v>
       </c>
       <c r="B117" s="5" t="s">
-        <v>897</v>
+        <v>901</v>
       </c>
       <c r="C117" s="5" t="s">
-        <v>898</v>
+        <v>902</v>
       </c>
       <c r="D117" s="6" t="s">
-        <v>899</v>
+        <v>903</v>
       </c>
       <c r="E117" s="5" t="s">
-        <v>900</v>
+        <v>904</v>
       </c>
     </row>
     <row r="118" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -10103,13 +10297,13 @@
         <v>116</v>
       </c>
       <c r="B118" s="5" t="s">
-        <v>814</v>
+        <v>818</v>
       </c>
       <c r="C118" s="5" t="s">
-        <v>901</v>
+        <v>905</v>
       </c>
       <c r="D118" s="6" t="s">
-        <v>902</v>
+        <v>906</v>
       </c>
       <c r="E118" s="5" t="s">
         <v>396</v>
@@ -10120,16 +10314,16 @@
         <v>117</v>
       </c>
       <c r="B119" s="5" t="s">
-        <v>903</v>
+        <v>907</v>
       </c>
       <c r="C119" s="5" t="s">
-        <v>904</v>
+        <v>908</v>
       </c>
       <c r="D119" s="6" t="s">
-        <v>905</v>
+        <v>909</v>
       </c>
       <c r="E119" s="5" t="s">
-        <v>906</v>
+        <v>910</v>
       </c>
     </row>
     <row r="120" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -10137,16 +10331,16 @@
         <v>118</v>
       </c>
       <c r="B120" s="5" t="s">
-        <v>891</v>
+        <v>895</v>
       </c>
       <c r="C120" s="5" t="s">
-        <v>907</v>
+        <v>911</v>
       </c>
       <c r="D120" s="6" t="s">
-        <v>908</v>
+        <v>912</v>
       </c>
       <c r="E120" s="5" t="s">
-        <v>909</v>
+        <v>913</v>
       </c>
     </row>
     <row r="121" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -10154,16 +10348,16 @@
         <v>119</v>
       </c>
       <c r="B121" s="5" t="s">
+        <v>914</v>
+      </c>
+      <c r="C121" s="5" t="s">
+        <v>915</v>
+      </c>
+      <c r="D121" s="6" t="s">
+        <v>916</v>
+      </c>
+      <c r="E121" s="5" t="s">
         <v>910</v>
-      </c>
-      <c r="C121" s="5" t="s">
-        <v>911</v>
-      </c>
-      <c r="D121" s="6" t="s">
-        <v>912</v>
-      </c>
-      <c r="E121" s="5" t="s">
-        <v>906</v>
       </c>
     </row>
     <row r="122" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -10171,16 +10365,16 @@
         <v>120</v>
       </c>
       <c r="B122" s="5" t="s">
-        <v>913</v>
+        <v>917</v>
       </c>
       <c r="C122" s="5" t="s">
-        <v>914</v>
+        <v>918</v>
       </c>
       <c r="D122" s="6" t="s">
-        <v>915</v>
+        <v>919</v>
       </c>
       <c r="E122" s="5" t="s">
-        <v>916</v>
+        <v>920</v>
       </c>
     </row>
     <row r="123" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -10188,13 +10382,13 @@
         <v>121</v>
       </c>
       <c r="B123" s="5" t="s">
-        <v>814</v>
+        <v>818</v>
       </c>
       <c r="C123" s="5" t="s">
-        <v>917</v>
+        <v>921</v>
       </c>
       <c r="D123" s="6" t="s">
-        <v>918</v>
+        <v>922</v>
       </c>
       <c r="E123" s="5" t="s">
         <v>409</v>
@@ -10205,13 +10399,13 @@
         <v>122</v>
       </c>
       <c r="B124" s="5" t="s">
-        <v>875</v>
+        <v>879</v>
       </c>
       <c r="C124" s="5" t="s">
-        <v>919</v>
+        <v>923</v>
       </c>
       <c r="D124" s="6" t="s">
-        <v>920</v>
+        <v>924</v>
       </c>
       <c r="E124" s="5" t="s">
         <v>409</v>
@@ -10222,16 +10416,16 @@
         <v>123</v>
       </c>
       <c r="B125" s="5" t="s">
-        <v>841</v>
+        <v>845</v>
       </c>
       <c r="C125" s="5" t="s">
-        <v>921</v>
+        <v>925</v>
       </c>
       <c r="D125" s="6" t="s">
-        <v>922</v>
+        <v>926</v>
       </c>
       <c r="E125" s="5" t="s">
-        <v>923</v>
+        <v>927</v>
       </c>
     </row>
     <row r="126" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -10239,16 +10433,16 @@
         <v>124</v>
       </c>
       <c r="B126" s="5" t="s">
-        <v>924</v>
+        <v>928</v>
       </c>
       <c r="C126" s="5" t="s">
-        <v>925</v>
+        <v>929</v>
       </c>
       <c r="D126" s="6" t="s">
-        <v>926</v>
+        <v>930</v>
       </c>
       <c r="E126" s="5" t="s">
-        <v>923</v>
+        <v>927</v>
       </c>
     </row>
     <row r="127" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -10256,16 +10450,16 @@
         <v>125</v>
       </c>
       <c r="B127" s="5" t="s">
-        <v>860</v>
+        <v>864</v>
       </c>
       <c r="C127" s="5" t="s">
-        <v>927</v>
+        <v>931</v>
       </c>
       <c r="D127" s="6" t="s">
-        <v>928</v>
+        <v>932</v>
       </c>
       <c r="E127" s="5" t="s">
-        <v>929</v>
+        <v>933</v>
       </c>
     </row>
     <row r="128" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -10273,16 +10467,16 @@
         <v>126</v>
       </c>
       <c r="B128" s="5" t="s">
-        <v>930</v>
+        <v>934</v>
       </c>
       <c r="C128" s="5" t="s">
-        <v>931</v>
+        <v>935</v>
       </c>
       <c r="D128" s="6" t="s">
-        <v>932</v>
+        <v>936</v>
       </c>
       <c r="E128" s="5" t="s">
-        <v>933</v>
+        <v>937</v>
       </c>
     </row>
     <row r="129" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -10290,16 +10484,16 @@
         <v>127</v>
       </c>
       <c r="B129" s="5" t="s">
-        <v>934</v>
+        <v>938</v>
       </c>
       <c r="C129" s="5" t="s">
-        <v>935</v>
+        <v>939</v>
       </c>
       <c r="D129" s="6" t="s">
-        <v>936</v>
+        <v>940</v>
       </c>
       <c r="E129" s="5" t="s">
-        <v>937</v>
+        <v>941</v>
       </c>
     </row>
     <row r="130" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -10307,16 +10501,16 @@
         <v>128</v>
       </c>
       <c r="B130" s="5" t="s">
-        <v>938</v>
+        <v>942</v>
       </c>
       <c r="C130" s="5" t="s">
-        <v>939</v>
+        <v>943</v>
       </c>
       <c r="D130" s="6" t="s">
-        <v>936</v>
+        <v>940</v>
       </c>
       <c r="E130" s="5" t="s">
-        <v>940</v>
+        <v>944</v>
       </c>
     </row>
     <row r="131" customFormat="false" ht="34.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -10324,13 +10518,13 @@
         <v>129</v>
       </c>
       <c r="B131" s="5" t="s">
-        <v>941</v>
+        <v>945</v>
       </c>
       <c r="C131" s="5" t="s">
-        <v>942</v>
+        <v>946</v>
       </c>
       <c r="D131" s="6" t="s">
-        <v>936</v>
+        <v>940</v>
       </c>
       <c r="E131" s="5" t="s">
         <v>434</v>
@@ -10341,16 +10535,16 @@
         <v>130</v>
       </c>
       <c r="B132" s="5" t="s">
-        <v>943</v>
+        <v>947</v>
       </c>
       <c r="C132" s="5" t="s">
-        <v>944</v>
+        <v>948</v>
       </c>
       <c r="D132" s="6" t="s">
-        <v>945</v>
+        <v>949</v>
       </c>
       <c r="E132" s="5" t="s">
-        <v>946</v>
+        <v>950</v>
       </c>
     </row>
     <row r="133" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -10358,16 +10552,16 @@
         <v>131</v>
       </c>
       <c r="B133" s="5" t="s">
-        <v>947</v>
+        <v>951</v>
       </c>
       <c r="C133" s="5" t="s">
-        <v>948</v>
+        <v>952</v>
       </c>
       <c r="D133" s="6" t="s">
-        <v>949</v>
+        <v>953</v>
       </c>
       <c r="E133" s="5" t="s">
-        <v>946</v>
+        <v>950</v>
       </c>
     </row>
     <row r="134" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -10375,16 +10569,16 @@
         <v>132</v>
       </c>
       <c r="B134" s="5" t="s">
-        <v>950</v>
+        <v>954</v>
       </c>
       <c r="C134" s="5" t="s">
-        <v>951</v>
+        <v>955</v>
       </c>
       <c r="D134" s="6" t="s">
-        <v>952</v>
+        <v>956</v>
       </c>
       <c r="E134" s="5" t="s">
-        <v>953</v>
+        <v>957</v>
       </c>
     </row>
     <row r="135" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -10392,16 +10586,16 @@
         <v>133</v>
       </c>
       <c r="B135" s="5" t="s">
-        <v>954</v>
+        <v>958</v>
       </c>
       <c r="C135" s="5" t="s">
-        <v>955</v>
+        <v>959</v>
       </c>
       <c r="D135" s="6" t="s">
-        <v>956</v>
+        <v>960</v>
       </c>
       <c r="E135" s="5" t="s">
-        <v>957</v>
+        <v>961</v>
       </c>
     </row>
     <row r="136" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -10409,13 +10603,13 @@
         <v>134</v>
       </c>
       <c r="B136" s="5" t="s">
-        <v>669</v>
+        <v>673</v>
       </c>
       <c r="C136" s="5" t="s">
-        <v>958</v>
+        <v>962</v>
       </c>
       <c r="D136" s="6" t="s">
-        <v>959</v>
+        <v>963</v>
       </c>
       <c r="E136" s="5" t="s">
         <v>451</v>
@@ -10426,13 +10620,13 @@
         <v>135</v>
       </c>
       <c r="B137" s="5" t="s">
-        <v>960</v>
+        <v>964</v>
       </c>
       <c r="C137" s="5" t="s">
-        <v>961</v>
+        <v>965</v>
       </c>
       <c r="D137" s="6" t="s">
-        <v>962</v>
+        <v>966</v>
       </c>
       <c r="E137" s="5" t="s">
         <v>451</v>
@@ -10443,16 +10637,16 @@
         <v>136</v>
       </c>
       <c r="B138" s="5" t="s">
-        <v>963</v>
+        <v>967</v>
       </c>
       <c r="C138" s="5" t="s">
-        <v>964</v>
+        <v>968</v>
       </c>
       <c r="D138" s="6" t="s">
-        <v>965</v>
+        <v>969</v>
       </c>
       <c r="E138" s="5" t="s">
-        <v>966</v>
+        <v>970</v>
       </c>
     </row>
     <row r="139" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -10460,16 +10654,16 @@
         <v>137</v>
       </c>
       <c r="B139" s="5" t="s">
-        <v>967</v>
+        <v>971</v>
       </c>
       <c r="C139" s="5" t="s">
-        <v>968</v>
+        <v>972</v>
       </c>
       <c r="D139" s="6" t="s">
-        <v>969</v>
+        <v>973</v>
       </c>
       <c r="E139" s="5" t="s">
-        <v>970</v>
+        <v>974</v>
       </c>
     </row>
     <row r="140" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -10477,13 +10671,13 @@
         <v>138</v>
       </c>
       <c r="B140" s="5" t="s">
-        <v>836</v>
+        <v>840</v>
       </c>
       <c r="C140" s="5" t="s">
-        <v>971</v>
+        <v>975</v>
       </c>
       <c r="D140" s="6" t="s">
-        <v>972</v>
+        <v>976</v>
       </c>
       <c r="E140" s="5" t="s">
         <v>463</v>
@@ -10494,16 +10688,16 @@
         <v>139</v>
       </c>
       <c r="B141" s="5" t="s">
-        <v>841</v>
+        <v>845</v>
       </c>
       <c r="C141" s="5" t="s">
-        <v>973</v>
+        <v>977</v>
       </c>
       <c r="D141" s="6" t="s">
-        <v>974</v>
+        <v>978</v>
       </c>
       <c r="E141" s="5" t="s">
-        <v>975</v>
+        <v>979</v>
       </c>
     </row>
     <row r="142" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -10511,16 +10705,16 @@
         <v>140</v>
       </c>
       <c r="B142" s="5" t="s">
-        <v>976</v>
+        <v>980</v>
       </c>
       <c r="C142" s="5" t="s">
-        <v>977</v>
+        <v>981</v>
       </c>
       <c r="D142" s="6" t="s">
-        <v>978</v>
+        <v>982</v>
       </c>
       <c r="E142" s="5" t="s">
-        <v>979</v>
+        <v>983</v>
       </c>
     </row>
     <row r="143" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -10528,13 +10722,13 @@
         <v>141</v>
       </c>
       <c r="B143" s="5" t="s">
-        <v>808</v>
+        <v>812</v>
       </c>
       <c r="C143" s="5" t="s">
-        <v>980</v>
+        <v>984</v>
       </c>
       <c r="D143" s="6" t="s">
-        <v>981</v>
+        <v>985</v>
       </c>
       <c r="E143" s="5" t="s">
         <v>472</v>
@@ -10545,16 +10739,16 @@
         <v>142</v>
       </c>
       <c r="B144" s="5" t="s">
-        <v>982</v>
+        <v>986</v>
       </c>
       <c r="C144" s="5" t="s">
-        <v>983</v>
+        <v>987</v>
       </c>
       <c r="D144" s="6" t="s">
-        <v>984</v>
+        <v>988</v>
       </c>
       <c r="E144" s="5" t="s">
-        <v>985</v>
+        <v>989</v>
       </c>
     </row>
     <row r="145" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -10562,13 +10756,13 @@
         <v>143</v>
       </c>
       <c r="B145" s="5" t="s">
-        <v>868</v>
+        <v>872</v>
       </c>
       <c r="C145" s="5" t="s">
-        <v>986</v>
+        <v>990</v>
       </c>
       <c r="D145" s="6" t="s">
-        <v>987</v>
+        <v>991</v>
       </c>
       <c r="E145" s="5" t="s">
         <v>479</v>
@@ -10579,16 +10773,16 @@
         <v>144</v>
       </c>
       <c r="B146" s="5" t="s">
-        <v>808</v>
+        <v>812</v>
       </c>
       <c r="C146" s="5" t="s">
-        <v>988</v>
+        <v>992</v>
       </c>
       <c r="D146" s="6" t="s">
-        <v>989</v>
+        <v>993</v>
       </c>
       <c r="E146" s="5" t="s">
-        <v>990</v>
+        <v>994</v>
       </c>
     </row>
     <row r="147" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -10596,16 +10790,16 @@
         <v>145</v>
       </c>
       <c r="B147" s="5" t="s">
-        <v>991</v>
+        <v>995</v>
       </c>
       <c r="C147" s="5" t="s">
-        <v>992</v>
+        <v>996</v>
       </c>
       <c r="D147" s="6" t="s">
-        <v>993</v>
+        <v>997</v>
       </c>
       <c r="E147" s="5" t="s">
-        <v>994</v>
+        <v>998</v>
       </c>
     </row>
     <row r="148" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -10613,16 +10807,16 @@
         <v>146</v>
       </c>
       <c r="B148" s="5" t="s">
-        <v>995</v>
+        <v>999</v>
       </c>
       <c r="C148" s="5" t="s">
-        <v>996</v>
+        <v>1000</v>
       </c>
       <c r="D148" s="6" t="s">
-        <v>997</v>
+        <v>1001</v>
       </c>
       <c r="E148" s="5" t="s">
-        <v>998</v>
+        <v>1002</v>
       </c>
     </row>
     <row r="149" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -10630,13 +10824,13 @@
         <v>147</v>
       </c>
       <c r="B149" s="5" t="s">
-        <v>999</v>
+        <v>1003</v>
       </c>
       <c r="C149" s="5" t="s">
-        <v>1000</v>
+        <v>1004</v>
       </c>
       <c r="D149" s="6" t="s">
-        <v>932</v>
+        <v>936</v>
       </c>
       <c r="E149" s="5" t="s">
         <v>492</v>
@@ -10647,13 +10841,13 @@
         <v>148</v>
       </c>
       <c r="B150" s="5" t="s">
-        <v>1001</v>
+        <v>1005</v>
       </c>
       <c r="C150" s="5" t="s">
-        <v>1002</v>
+        <v>1006</v>
       </c>
       <c r="D150" s="6" t="s">
-        <v>936</v>
+        <v>940</v>
       </c>
       <c r="E150" s="5" t="s">
         <v>492</v>
@@ -10664,16 +10858,16 @@
         <v>149</v>
       </c>
       <c r="B151" s="5" t="s">
-        <v>1003</v>
+        <v>1007</v>
       </c>
       <c r="C151" s="5" t="s">
-        <v>1004</v>
+        <v>1008</v>
       </c>
       <c r="D151" s="6" t="s">
-        <v>1005</v>
+        <v>1009</v>
       </c>
       <c r="E151" s="5" t="s">
-        <v>1006</v>
+        <v>1010</v>
       </c>
     </row>
     <row r="152" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -10681,16 +10875,16 @@
         <v>150</v>
       </c>
       <c r="B152" s="5" t="s">
-        <v>1003</v>
+        <v>1007</v>
       </c>
       <c r="C152" s="5" t="s">
-        <v>1007</v>
+        <v>1011</v>
       </c>
       <c r="D152" s="6" t="s">
-        <v>1005</v>
+        <v>1009</v>
       </c>
       <c r="E152" s="5" t="s">
-        <v>1006</v>
+        <v>1010</v>
       </c>
     </row>
     <row r="153" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -10698,16 +10892,16 @@
         <v>151</v>
       </c>
       <c r="B153" s="5" t="s">
-        <v>1008</v>
+        <v>1012</v>
       </c>
       <c r="C153" s="5" t="s">
-        <v>1009</v>
+        <v>1013</v>
       </c>
       <c r="D153" s="6" t="s">
-        <v>1010</v>
+        <v>1014</v>
       </c>
       <c r="E153" s="5" t="s">
-        <v>1011</v>
+        <v>1015</v>
       </c>
     </row>
     <row r="154" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -10715,16 +10909,16 @@
         <v>152</v>
       </c>
       <c r="B154" s="5" t="s">
-        <v>1008</v>
+        <v>1012</v>
       </c>
       <c r="C154" s="5" t="s">
-        <v>1012</v>
+        <v>1016</v>
       </c>
       <c r="D154" s="6" t="s">
-        <v>1010</v>
+        <v>1014</v>
       </c>
       <c r="E154" s="5" t="s">
-        <v>1011</v>
+        <v>1015</v>
       </c>
     </row>
     <row r="155" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -10732,16 +10926,16 @@
         <v>153</v>
       </c>
       <c r="B155" s="5" t="s">
-        <v>1013</v>
+        <v>1017</v>
       </c>
       <c r="C155" s="5" t="s">
-        <v>1014</v>
+        <v>1018</v>
       </c>
       <c r="D155" s="6" t="s">
-        <v>1015</v>
+        <v>1019</v>
       </c>
       <c r="E155" s="5" t="s">
-        <v>1016</v>
+        <v>1020</v>
       </c>
     </row>
     <row r="156" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -10749,16 +10943,16 @@
         <v>154</v>
       </c>
       <c r="B156" s="5" t="s">
-        <v>841</v>
+        <v>845</v>
       </c>
       <c r="C156" s="5" t="s">
-        <v>1017</v>
+        <v>1021</v>
       </c>
       <c r="D156" s="6" t="s">
-        <v>1018</v>
+        <v>1022</v>
       </c>
       <c r="E156" s="5" t="s">
-        <v>1016</v>
+        <v>1020</v>
       </c>
     </row>
     <row r="157" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -10766,14 +10960,14 @@
         <v>155</v>
       </c>
       <c r="B157" s="5" t="s">
-        <v>1019</v>
+        <v>1023</v>
       </c>
       <c r="C157" s="5" t="s">
-        <v>1020</v>
+        <v>1024</v>
       </c>
       <c r="D157" s="5"/>
       <c r="E157" s="5" t="s">
-        <v>1021</v>
+        <v>1025</v>
       </c>
     </row>
     <row r="158" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -10781,16 +10975,16 @@
         <v>156</v>
       </c>
       <c r="B158" s="5" t="s">
-        <v>1022</v>
+        <v>1026</v>
       </c>
       <c r="C158" s="5" t="s">
-        <v>1023</v>
+        <v>1027</v>
       </c>
       <c r="D158" s="6" t="s">
-        <v>1024</v>
+        <v>1028</v>
       </c>
       <c r="E158" s="5" t="s">
-        <v>1021</v>
+        <v>1025</v>
       </c>
     </row>
     <row r="159" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -10798,16 +10992,16 @@
         <v>157</v>
       </c>
       <c r="B159" s="5" t="s">
-        <v>669</v>
+        <v>673</v>
       </c>
       <c r="C159" s="5" t="s">
-        <v>1025</v>
+        <v>1029</v>
       </c>
       <c r="D159" s="6" t="s">
-        <v>1026</v>
+        <v>1030</v>
       </c>
       <c r="E159" s="5" t="s">
-        <v>1027</v>
+        <v>1031</v>
       </c>
     </row>
     <row r="160" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -10815,16 +11009,16 @@
         <v>158</v>
       </c>
       <c r="B160" s="5" t="s">
-        <v>808</v>
+        <v>812</v>
       </c>
       <c r="C160" s="5" t="s">
-        <v>1028</v>
+        <v>1032</v>
       </c>
       <c r="D160" s="6" t="s">
-        <v>1029</v>
+        <v>1033</v>
       </c>
       <c r="E160" s="5" t="s">
-        <v>1027</v>
+        <v>1031</v>
       </c>
     </row>
     <row r="161" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -10832,16 +11026,16 @@
         <v>159</v>
       </c>
       <c r="B161" s="5" t="s">
-        <v>864</v>
+        <v>868</v>
       </c>
       <c r="C161" s="5" t="s">
-        <v>1030</v>
+        <v>1034</v>
       </c>
       <c r="D161" s="6" t="s">
+        <v>1035</v>
+      </c>
+      <c r="E161" s="5" t="s">
         <v>1031</v>
-      </c>
-      <c r="E161" s="5" t="s">
-        <v>1027</v>
       </c>
     </row>
     <row r="162" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -10849,16 +11043,16 @@
         <v>160</v>
       </c>
       <c r="B162" s="5" t="s">
-        <v>1032</v>
+        <v>1036</v>
       </c>
       <c r="C162" s="5" t="s">
-        <v>1033</v>
+        <v>1037</v>
       </c>
       <c r="D162" s="6" t="s">
-        <v>1034</v>
+        <v>1038</v>
       </c>
       <c r="E162" s="5" t="s">
-        <v>1027</v>
+        <v>1031</v>
       </c>
     </row>
     <row r="163" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -10866,16 +11060,16 @@
         <v>161</v>
       </c>
       <c r="B163" s="5" t="s">
-        <v>1032</v>
+        <v>1036</v>
       </c>
       <c r="C163" s="5" t="s">
-        <v>1035</v>
+        <v>1039</v>
       </c>
       <c r="D163" s="6" t="s">
-        <v>1036</v>
+        <v>1040</v>
       </c>
       <c r="E163" s="5" t="s">
-        <v>1027</v>
+        <v>1031</v>
       </c>
     </row>
     <row r="164" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -10883,16 +11077,16 @@
         <v>162</v>
       </c>
       <c r="B164" s="5" t="s">
-        <v>875</v>
+        <v>879</v>
       </c>
       <c r="C164" s="5" t="s">
-        <v>1037</v>
+        <v>1041</v>
       </c>
       <c r="D164" s="6" t="s">
-        <v>1038</v>
+        <v>1042</v>
       </c>
       <c r="E164" s="5" t="s">
-        <v>1039</v>
+        <v>1043</v>
       </c>
     </row>
     <row r="165" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -10900,16 +11094,16 @@
         <v>163</v>
       </c>
       <c r="B165" s="5" t="s">
-        <v>669</v>
+        <v>673</v>
       </c>
       <c r="C165" s="5" t="s">
-        <v>1040</v>
+        <v>1044</v>
       </c>
       <c r="D165" s="6" t="s">
-        <v>1041</v>
+        <v>1045</v>
       </c>
       <c r="E165" s="5" t="s">
-        <v>1039</v>
+        <v>1043</v>
       </c>
     </row>
     <row r="166" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -10917,13 +11111,13 @@
         <v>157</v>
       </c>
       <c r="B166" s="5" t="s">
-        <v>1032</v>
+        <v>1036</v>
       </c>
       <c r="C166" s="5" t="s">
-        <v>1042</v>
+        <v>1046</v>
       </c>
       <c r="D166" s="6" t="s">
-        <v>1043</v>
+        <v>1047</v>
       </c>
       <c r="E166" s="5" t="s">
         <v>521</v>
@@ -10934,16 +11128,16 @@
         <v>158</v>
       </c>
       <c r="B167" s="5" t="s">
-        <v>891</v>
+        <v>895</v>
       </c>
       <c r="C167" s="5" t="s">
-        <v>1044</v>
+        <v>1048</v>
       </c>
       <c r="D167" s="6" t="s">
-        <v>1045</v>
+        <v>1049</v>
       </c>
       <c r="E167" s="5" t="s">
-        <v>1046</v>
+        <v>1050</v>
       </c>
     </row>
     <row r="168" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -10951,13 +11145,13 @@
         <v>159</v>
       </c>
       <c r="B168" s="5" t="s">
-        <v>669</v>
+        <v>673</v>
       </c>
       <c r="C168" s="5" t="s">
-        <v>1047</v>
+        <v>1051</v>
       </c>
       <c r="D168" s="6" t="s">
-        <v>1048</v>
+        <v>1052</v>
       </c>
       <c r="E168" s="5" t="s">
         <v>524</v>
@@ -10968,16 +11162,16 @@
         <v>160</v>
       </c>
       <c r="B169" s="5" t="s">
-        <v>864</v>
+        <v>868</v>
       </c>
       <c r="C169" s="5" t="s">
-        <v>1049</v>
+        <v>1053</v>
       </c>
       <c r="D169" s="6" t="s">
-        <v>1050</v>
+        <v>1054</v>
       </c>
       <c r="E169" s="5" t="s">
-        <v>1051</v>
+        <v>1055</v>
       </c>
     </row>
     <row r="170" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -10985,16 +11179,16 @@
         <v>161</v>
       </c>
       <c r="B170" s="5" t="s">
-        <v>864</v>
+        <v>868</v>
       </c>
       <c r="C170" s="5" t="s">
-        <v>1052</v>
+        <v>1056</v>
       </c>
       <c r="D170" s="6" t="s">
-        <v>1053</v>
+        <v>1057</v>
       </c>
       <c r="E170" s="5" t="s">
-        <v>1051</v>
+        <v>1055</v>
       </c>
     </row>
     <row r="171" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -11002,16 +11196,16 @@
         <v>162</v>
       </c>
       <c r="B171" s="5" t="s">
-        <v>864</v>
+        <v>868</v>
       </c>
       <c r="C171" s="5" t="s">
-        <v>1054</v>
+        <v>1058</v>
       </c>
       <c r="D171" s="6" t="s">
+        <v>1059</v>
+      </c>
+      <c r="E171" s="5" t="s">
         <v>1055</v>
-      </c>
-      <c r="E171" s="5" t="s">
-        <v>1051</v>
       </c>
     </row>
     <row r="172" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -11019,16 +11213,16 @@
         <v>163</v>
       </c>
       <c r="B172" s="5" t="s">
-        <v>814</v>
+        <v>818</v>
       </c>
       <c r="C172" s="5" t="s">
-        <v>1056</v>
+        <v>1060</v>
       </c>
       <c r="D172" s="6" t="s">
-        <v>1057</v>
+        <v>1061</v>
       </c>
       <c r="E172" s="5" t="s">
-        <v>1058</v>
+        <v>1062</v>
       </c>
     </row>
     <row r="173" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -11036,16 +11230,16 @@
         <v>164</v>
       </c>
       <c r="B173" s="5" t="s">
-        <v>808</v>
+        <v>812</v>
       </c>
       <c r="C173" s="5" t="s">
-        <v>1059</v>
+        <v>1063</v>
       </c>
       <c r="D173" s="6" t="s">
-        <v>1060</v>
+        <v>1064</v>
       </c>
       <c r="E173" s="5" t="s">
-        <v>1061</v>
+        <v>1065</v>
       </c>
     </row>
     <row r="174" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -11053,16 +11247,16 @@
         <v>165</v>
       </c>
       <c r="B174" s="5" t="s">
-        <v>808</v>
+        <v>812</v>
       </c>
       <c r="C174" s="5" t="s">
-        <v>1062</v>
+        <v>1066</v>
       </c>
       <c r="D174" s="6" t="s">
-        <v>1063</v>
+        <v>1067</v>
       </c>
       <c r="E174" s="5" t="s">
-        <v>1061</v>
+        <v>1065</v>
       </c>
     </row>
     <row r="175" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -11070,16 +11264,16 @@
         <v>166</v>
       </c>
       <c r="B175" s="5" t="s">
-        <v>808</v>
+        <v>812</v>
       </c>
       <c r="C175" s="5" t="s">
-        <v>1064</v>
+        <v>1068</v>
       </c>
       <c r="D175" s="6" t="s">
+        <v>1069</v>
+      </c>
+      <c r="E175" s="5" t="s">
         <v>1065</v>
-      </c>
-      <c r="E175" s="5" t="s">
-        <v>1061</v>
       </c>
     </row>
     <row r="176" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -11087,16 +11281,16 @@
         <v>167</v>
       </c>
       <c r="B176" s="5" t="s">
-        <v>875</v>
+        <v>879</v>
       </c>
       <c r="C176" s="5" t="s">
-        <v>1066</v>
+        <v>1070</v>
       </c>
       <c r="D176" s="6" t="s">
-        <v>1067</v>
+        <v>1071</v>
       </c>
       <c r="E176" s="5" t="s">
-        <v>1068</v>
+        <v>1072</v>
       </c>
     </row>
     <row r="177" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -11104,16 +11298,16 @@
         <v>168</v>
       </c>
       <c r="B177" s="5" t="s">
-        <v>669</v>
+        <v>673</v>
       </c>
       <c r="C177" s="5" t="s">
-        <v>1069</v>
+        <v>1073</v>
       </c>
       <c r="D177" s="6" t="s">
-        <v>1070</v>
+        <v>1074</v>
       </c>
       <c r="E177" s="5" t="s">
-        <v>1068</v>
+        <v>1072</v>
       </c>
     </row>
     <row r="178" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -11121,16 +11315,16 @@
         <v>169</v>
       </c>
       <c r="B178" s="5" t="s">
-        <v>669</v>
+        <v>673</v>
       </c>
       <c r="C178" s="5" t="s">
-        <v>1071</v>
+        <v>1075</v>
       </c>
       <c r="D178" s="6" t="s">
+        <v>1076</v>
+      </c>
+      <c r="E178" s="5" t="s">
         <v>1072</v>
-      </c>
-      <c r="E178" s="5" t="s">
-        <v>1068</v>
       </c>
     </row>
     <row r="179" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -11138,16 +11332,16 @@
         <v>170</v>
       </c>
       <c r="B179" s="5" t="s">
-        <v>891</v>
+        <v>895</v>
       </c>
       <c r="C179" s="5" t="s">
-        <v>1073</v>
+        <v>1077</v>
       </c>
       <c r="D179" s="6" t="s">
-        <v>1074</v>
+        <v>1078</v>
       </c>
       <c r="E179" s="5" t="s">
-        <v>1068</v>
+        <v>1072</v>
       </c>
     </row>
     <row r="180" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -11155,16 +11349,16 @@
         <v>171</v>
       </c>
       <c r="B180" s="5" t="s">
-        <v>891</v>
+        <v>895</v>
       </c>
       <c r="C180" s="5" t="s">
-        <v>1075</v>
+        <v>1079</v>
       </c>
       <c r="D180" s="6" t="s">
-        <v>1076</v>
+        <v>1080</v>
       </c>
       <c r="E180" s="5" t="s">
-        <v>1068</v>
+        <v>1072</v>
       </c>
     </row>
     <row r="181" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -11172,16 +11366,16 @@
         <v>172</v>
       </c>
       <c r="B181" s="5" t="s">
-        <v>864</v>
+        <v>868</v>
       </c>
       <c r="C181" s="5" t="s">
-        <v>1077</v>
+        <v>1081</v>
       </c>
       <c r="D181" s="6" t="s">
-        <v>1078</v>
+        <v>1082</v>
       </c>
       <c r="E181" s="5" t="s">
-        <v>1079</v>
+        <v>1083</v>
       </c>
     </row>
     <row r="182" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -11189,16 +11383,16 @@
         <v>173</v>
       </c>
       <c r="B182" s="5" t="s">
-        <v>669</v>
+        <v>673</v>
       </c>
       <c r="C182" s="5" t="s">
-        <v>1080</v>
+        <v>1084</v>
       </c>
       <c r="D182" s="6" t="s">
-        <v>1081</v>
+        <v>1085</v>
       </c>
       <c r="E182" s="5" t="s">
-        <v>1082</v>
+        <v>1086</v>
       </c>
     </row>
     <row r="183" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -11206,16 +11400,16 @@
         <v>174</v>
       </c>
       <c r="B183" s="5" t="s">
-        <v>669</v>
+        <v>673</v>
       </c>
       <c r="C183" s="5" t="s">
-        <v>1083</v>
+        <v>1087</v>
       </c>
       <c r="D183" s="6" t="s">
-        <v>1084</v>
+        <v>1088</v>
       </c>
       <c r="E183" s="5" t="s">
-        <v>1082</v>
+        <v>1086</v>
       </c>
     </row>
     <row r="184" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -11223,16 +11417,16 @@
         <v>175</v>
       </c>
       <c r="B184" s="5" t="s">
-        <v>669</v>
+        <v>673</v>
       </c>
       <c r="C184" s="5" t="s">
-        <v>1085</v>
+        <v>1089</v>
       </c>
       <c r="D184" s="6" t="s">
+        <v>1090</v>
+      </c>
+      <c r="E184" s="5" t="s">
         <v>1086</v>
-      </c>
-      <c r="E184" s="5" t="s">
-        <v>1082</v>
       </c>
     </row>
     <row r="185" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -11240,16 +11434,16 @@
         <v>176</v>
       </c>
       <c r="B185" s="5" t="s">
-        <v>1032</v>
+        <v>1036</v>
       </c>
       <c r="C185" s="5" t="s">
-        <v>1087</v>
+        <v>1091</v>
       </c>
       <c r="D185" s="6" t="s">
-        <v>1088</v>
+        <v>1092</v>
       </c>
       <c r="E185" s="5" t="s">
-        <v>1082</v>
+        <v>1086</v>
       </c>
     </row>
     <row r="186" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -11257,16 +11451,16 @@
         <v>177</v>
       </c>
       <c r="B186" s="5" t="s">
-        <v>1032</v>
+        <v>1036</v>
       </c>
       <c r="C186" s="5" t="s">
-        <v>1089</v>
+        <v>1093</v>
       </c>
       <c r="D186" s="6" t="s">
-        <v>1090</v>
+        <v>1094</v>
       </c>
       <c r="E186" s="5" t="s">
-        <v>1082</v>
+        <v>1086</v>
       </c>
     </row>
     <row r="187" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -11274,16 +11468,16 @@
         <v>178</v>
       </c>
       <c r="B187" s="5" t="s">
-        <v>1032</v>
+        <v>1036</v>
       </c>
       <c r="C187" s="5" t="s">
-        <v>1091</v>
+        <v>1095</v>
       </c>
       <c r="D187" s="6" t="s">
-        <v>1092</v>
+        <v>1096</v>
       </c>
       <c r="E187" s="5" t="s">
-        <v>1082</v>
+        <v>1086</v>
       </c>
     </row>
     <row r="188" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -11291,16 +11485,16 @@
         <v>179</v>
       </c>
       <c r="B188" s="5" t="s">
-        <v>669</v>
+        <v>673</v>
       </c>
       <c r="C188" s="5" t="s">
-        <v>1093</v>
+        <v>1097</v>
       </c>
       <c r="D188" s="6" t="s">
-        <v>1094</v>
+        <v>1098</v>
       </c>
       <c r="E188" s="5" t="s">
-        <v>1095</v>
+        <v>1099</v>
       </c>
     </row>
     <row r="189" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -11308,16 +11502,16 @@
         <v>180</v>
       </c>
       <c r="B189" s="5" t="s">
-        <v>669</v>
+        <v>673</v>
       </c>
       <c r="C189" s="5" t="s">
-        <v>1096</v>
+        <v>1100</v>
       </c>
       <c r="D189" s="6" t="s">
-        <v>1097</v>
+        <v>1101</v>
       </c>
       <c r="E189" s="5" t="s">
-        <v>1095</v>
+        <v>1099</v>
       </c>
     </row>
     <row r="190" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -11325,16 +11519,16 @@
         <v>181</v>
       </c>
       <c r="B190" s="5" t="s">
-        <v>864</v>
+        <v>868</v>
       </c>
       <c r="C190" s="5" t="s">
-        <v>1098</v>
+        <v>1102</v>
       </c>
       <c r="D190" s="6" t="s">
+        <v>1103</v>
+      </c>
+      <c r="E190" s="5" t="s">
         <v>1099</v>
-      </c>
-      <c r="E190" s="5" t="s">
-        <v>1095</v>
       </c>
     </row>
     <row r="191" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -11342,16 +11536,16 @@
         <v>182</v>
       </c>
       <c r="B191" s="5" t="s">
-        <v>1032</v>
+        <v>1036</v>
       </c>
       <c r="C191" s="5" t="s">
-        <v>1100</v>
+        <v>1104</v>
       </c>
       <c r="D191" s="6" t="s">
-        <v>1101</v>
+        <v>1105</v>
       </c>
       <c r="E191" s="5" t="s">
-        <v>1095</v>
+        <v>1099</v>
       </c>
     </row>
     <row r="192" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -11359,16 +11553,16 @@
         <v>183</v>
       </c>
       <c r="B192" s="5" t="s">
-        <v>1032</v>
+        <v>1036</v>
       </c>
       <c r="C192" s="5" t="s">
-        <v>1102</v>
+        <v>1106</v>
       </c>
       <c r="D192" s="6" t="s">
-        <v>1103</v>
+        <v>1107</v>
       </c>
       <c r="E192" s="5" t="s">
-        <v>1095</v>
+        <v>1099</v>
       </c>
     </row>
     <row r="193" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -11376,13 +11570,13 @@
         <v>184</v>
       </c>
       <c r="B193" s="5" t="s">
-        <v>864</v>
+        <v>868</v>
       </c>
       <c r="C193" s="5" t="s">
-        <v>1104</v>
+        <v>1108</v>
       </c>
       <c r="D193" s="6" t="s">
-        <v>1105</v>
+        <v>1109</v>
       </c>
       <c r="E193" s="5" t="s">
         <v>533</v>
@@ -11393,16 +11587,16 @@
         <v>185</v>
       </c>
       <c r="B194" s="5" t="s">
-        <v>864</v>
+        <v>868</v>
       </c>
       <c r="C194" s="5" t="s">
-        <v>1106</v>
+        <v>1110</v>
       </c>
       <c r="D194" s="6" t="s">
-        <v>1107</v>
+        <v>1111</v>
       </c>
       <c r="E194" s="5" t="s">
-        <v>1108</v>
+        <v>1112</v>
       </c>
     </row>
     <row r="195" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -11410,16 +11604,16 @@
         <v>186</v>
       </c>
       <c r="B195" s="5" t="s">
-        <v>669</v>
+        <v>673</v>
       </c>
       <c r="C195" s="5" t="s">
-        <v>1109</v>
+        <v>1113</v>
       </c>
       <c r="D195" s="6" t="s">
-        <v>1110</v>
+        <v>1114</v>
       </c>
       <c r="E195" s="5" t="s">
-        <v>1111</v>
+        <v>1115</v>
       </c>
     </row>
     <row r="196" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -11427,16 +11621,16 @@
         <v>187</v>
       </c>
       <c r="B196" s="5" t="s">
-        <v>808</v>
+        <v>812</v>
       </c>
       <c r="C196" s="5" t="s">
-        <v>1112</v>
+        <v>1116</v>
       </c>
       <c r="D196" s="6" t="s">
-        <v>1113</v>
+        <v>1117</v>
       </c>
       <c r="E196" s="5" t="s">
-        <v>1111</v>
+        <v>1115</v>
       </c>
     </row>
     <row r="197" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -11444,16 +11638,16 @@
         <v>188</v>
       </c>
       <c r="B197" s="5" t="s">
-        <v>1032</v>
+        <v>1036</v>
       </c>
       <c r="C197" s="5" t="s">
-        <v>1114</v>
+        <v>1118</v>
       </c>
       <c r="D197" s="6" t="s">
+        <v>1119</v>
+      </c>
+      <c r="E197" s="5" t="s">
         <v>1115</v>
-      </c>
-      <c r="E197" s="5" t="s">
-        <v>1111</v>
       </c>
     </row>
     <row r="198" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -11461,16 +11655,16 @@
         <v>189</v>
       </c>
       <c r="B198" s="5" t="s">
-        <v>1032</v>
+        <v>1036</v>
       </c>
       <c r="C198" s="5" t="s">
-        <v>1116</v>
+        <v>1120</v>
       </c>
       <c r="D198" s="6" t="s">
-        <v>1117</v>
+        <v>1121</v>
       </c>
       <c r="E198" s="5" t="s">
-        <v>1111</v>
+        <v>1115</v>
       </c>
     </row>
     <row r="199" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -11478,16 +11672,16 @@
         <v>190</v>
       </c>
       <c r="B199" s="5" t="s">
-        <v>875</v>
+        <v>879</v>
       </c>
       <c r="C199" s="5" t="s">
-        <v>1118</v>
+        <v>1122</v>
       </c>
       <c r="D199" s="6" t="s">
-        <v>1119</v>
+        <v>1123</v>
       </c>
       <c r="E199" s="5" t="s">
-        <v>1120</v>
+        <v>1124</v>
       </c>
     </row>
     <row r="200" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -11495,16 +11689,16 @@
         <v>191</v>
       </c>
       <c r="B200" s="5" t="s">
-        <v>875</v>
+        <v>879</v>
       </c>
       <c r="C200" s="5" t="s">
-        <v>1121</v>
+        <v>1125</v>
       </c>
       <c r="D200" s="6" t="s">
-        <v>1122</v>
+        <v>1126</v>
       </c>
       <c r="E200" s="5" t="s">
-        <v>1120</v>
+        <v>1124</v>
       </c>
     </row>
     <row r="201" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -11512,16 +11706,16 @@
         <v>192</v>
       </c>
       <c r="B201" s="5" t="s">
-        <v>669</v>
+        <v>673</v>
       </c>
       <c r="C201" s="5" t="s">
-        <v>1123</v>
+        <v>1127</v>
       </c>
       <c r="D201" s="6" t="s">
+        <v>1128</v>
+      </c>
+      <c r="E201" s="5" t="s">
         <v>1124</v>
-      </c>
-      <c r="E201" s="5" t="s">
-        <v>1120</v>
       </c>
     </row>
     <row r="202" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -11529,16 +11723,16 @@
         <v>193</v>
       </c>
       <c r="B202" s="5" t="s">
-        <v>669</v>
+        <v>673</v>
       </c>
       <c r="C202" s="5" t="s">
-        <v>1125</v>
+        <v>1129</v>
       </c>
       <c r="D202" s="6" t="s">
-        <v>1126</v>
+        <v>1130</v>
       </c>
       <c r="E202" s="5" t="s">
-        <v>1127</v>
+        <v>1131</v>
       </c>
     </row>
     <row r="203" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -11546,16 +11740,16 @@
         <v>194</v>
       </c>
       <c r="B203" s="5" t="s">
-        <v>669</v>
+        <v>673</v>
       </c>
       <c r="C203" s="5" t="s">
-        <v>1128</v>
+        <v>1132</v>
       </c>
       <c r="D203" s="6" t="s">
-        <v>1129</v>
+        <v>1133</v>
       </c>
       <c r="E203" s="5" t="s">
-        <v>1127</v>
+        <v>1131</v>
       </c>
     </row>
     <row r="204" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -11563,16 +11757,16 @@
         <v>195</v>
       </c>
       <c r="B204" s="5" t="s">
-        <v>669</v>
+        <v>673</v>
       </c>
       <c r="C204" s="5" t="s">
-        <v>1130</v>
+        <v>1134</v>
       </c>
       <c r="D204" s="6" t="s">
-        <v>1131</v>
+        <v>1135</v>
       </c>
       <c r="E204" s="5" t="s">
-        <v>1132</v>
+        <v>1136</v>
       </c>
     </row>
     <row r="205" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -11580,13 +11774,13 @@
         <v>196</v>
       </c>
       <c r="B205" s="5" t="s">
-        <v>864</v>
+        <v>868</v>
       </c>
       <c r="C205" s="5" t="s">
-        <v>1133</v>
+        <v>1137</v>
       </c>
       <c r="D205" s="6" t="s">
-        <v>1134</v>
+        <v>1138</v>
       </c>
       <c r="E205" s="5" t="s">
         <v>540</v>
@@ -11597,16 +11791,16 @@
         <v>197</v>
       </c>
       <c r="B206" s="5" t="s">
-        <v>669</v>
+        <v>673</v>
       </c>
       <c r="C206" s="5" t="s">
-        <v>1135</v>
+        <v>1139</v>
       </c>
       <c r="D206" s="6" t="s">
-        <v>1136</v>
+        <v>1140</v>
       </c>
       <c r="E206" s="5" t="s">
-        <v>1137</v>
+        <v>1141</v>
       </c>
     </row>
     <row r="207" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -11614,16 +11808,16 @@
         <v>198</v>
       </c>
       <c r="B207" s="5" t="s">
-        <v>891</v>
+        <v>895</v>
       </c>
       <c r="C207" s="5" t="s">
-        <v>1138</v>
+        <v>1142</v>
       </c>
       <c r="D207" s="6" t="s">
-        <v>1139</v>
+        <v>1143</v>
       </c>
       <c r="E207" s="5" t="s">
-        <v>1137</v>
+        <v>1141</v>
       </c>
     </row>
     <row r="208" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -11631,16 +11825,16 @@
         <v>199</v>
       </c>
       <c r="B208" s="5" t="s">
-        <v>1032</v>
+        <v>1036</v>
       </c>
       <c r="C208" s="5" t="s">
-        <v>1140</v>
+        <v>1144</v>
       </c>
       <c r="D208" s="6" t="s">
+        <v>1145</v>
+      </c>
+      <c r="E208" s="5" t="s">
         <v>1141</v>
-      </c>
-      <c r="E208" s="5" t="s">
-        <v>1137</v>
       </c>
     </row>
     <row r="209" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -11648,16 +11842,16 @@
         <v>200</v>
       </c>
       <c r="B209" s="5" t="s">
-        <v>1032</v>
+        <v>1036</v>
       </c>
       <c r="C209" s="5" t="s">
-        <v>1142</v>
+        <v>1146</v>
       </c>
       <c r="D209" s="6" t="s">
-        <v>1143</v>
+        <v>1147</v>
       </c>
       <c r="E209" s="5" t="s">
-        <v>1137</v>
+        <v>1141</v>
       </c>
     </row>
     <row r="210" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -11665,16 +11859,16 @@
         <v>201</v>
       </c>
       <c r="B210" s="5" t="s">
-        <v>808</v>
+        <v>812</v>
       </c>
       <c r="C210" s="5" t="s">
-        <v>1144</v>
+        <v>1148</v>
       </c>
       <c r="D210" s="6" t="s">
-        <v>1145</v>
+        <v>1149</v>
       </c>
       <c r="E210" s="5" t="s">
-        <v>1146</v>
+        <v>1150</v>
       </c>
     </row>
     <row r="211" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -11682,16 +11876,16 @@
         <v>202</v>
       </c>
       <c r="B211" s="5" t="s">
-        <v>891</v>
+        <v>895</v>
       </c>
       <c r="C211" s="5" t="s">
-        <v>1147</v>
+        <v>1151</v>
       </c>
       <c r="D211" s="6" t="s">
-        <v>1148</v>
+        <v>1152</v>
       </c>
       <c r="E211" s="5" t="s">
-        <v>1146</v>
+        <v>1150</v>
       </c>
     </row>
     <row r="212" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -11699,16 +11893,16 @@
         <v>203</v>
       </c>
       <c r="B212" s="5" t="s">
-        <v>891</v>
+        <v>895</v>
       </c>
       <c r="C212" s="5" t="s">
-        <v>1149</v>
+        <v>1153</v>
       </c>
       <c r="D212" s="6" t="s">
+        <v>1154</v>
+      </c>
+      <c r="E212" s="5" t="s">
         <v>1150</v>
-      </c>
-      <c r="E212" s="5" t="s">
-        <v>1146</v>
       </c>
     </row>
     <row r="213" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -11716,16 +11910,16 @@
         <v>204</v>
       </c>
       <c r="B213" s="5" t="s">
-        <v>864</v>
+        <v>868</v>
       </c>
       <c r="C213" s="5" t="s">
-        <v>1151</v>
+        <v>1155</v>
       </c>
       <c r="D213" s="6" t="s">
-        <v>1152</v>
+        <v>1156</v>
       </c>
       <c r="E213" s="5" t="s">
-        <v>1046</v>
+        <v>1050</v>
       </c>
     </row>
     <row r="214" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -11733,16 +11927,16 @@
         <v>205</v>
       </c>
       <c r="B214" s="5" t="s">
-        <v>669</v>
+        <v>673</v>
       </c>
       <c r="C214" s="5" t="s">
-        <v>1153</v>
+        <v>1157</v>
       </c>
       <c r="D214" s="6" t="s">
-        <v>1154</v>
+        <v>1158</v>
       </c>
       <c r="E214" s="5" t="s">
-        <v>1155</v>
+        <v>1159</v>
       </c>
     </row>
     <row r="215" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -11750,16 +11944,16 @@
         <v>206</v>
       </c>
       <c r="B215" s="5" t="s">
-        <v>808</v>
+        <v>812</v>
       </c>
       <c r="C215" s="5" t="s">
-        <v>1156</v>
+        <v>1160</v>
       </c>
       <c r="D215" s="6" t="s">
-        <v>1157</v>
+        <v>1161</v>
       </c>
       <c r="E215" s="5" t="s">
-        <v>1158</v>
+        <v>1162</v>
       </c>
     </row>
     <row r="216" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -11767,16 +11961,16 @@
         <v>207</v>
       </c>
       <c r="B216" s="5" t="s">
-        <v>891</v>
+        <v>895</v>
       </c>
       <c r="C216" s="5" t="s">
-        <v>1159</v>
+        <v>1163</v>
       </c>
       <c r="D216" s="6" t="s">
-        <v>1160</v>
+        <v>1164</v>
       </c>
       <c r="E216" s="5" t="s">
-        <v>1158</v>
+        <v>1162</v>
       </c>
     </row>
     <row r="217" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -11784,16 +11978,16 @@
         <v>208</v>
       </c>
       <c r="B217" s="5" t="s">
-        <v>669</v>
+        <v>673</v>
       </c>
       <c r="C217" s="5" t="s">
-        <v>1161</v>
+        <v>1165</v>
       </c>
       <c r="D217" s="6" t="s">
-        <v>1162</v>
+        <v>1166</v>
       </c>
       <c r="E217" s="5" t="s">
-        <v>1163</v>
+        <v>1167</v>
       </c>
     </row>
     <row r="218" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -11801,16 +11995,16 @@
         <v>209</v>
       </c>
       <c r="B218" s="5" t="s">
-        <v>808</v>
+        <v>812</v>
       </c>
       <c r="C218" s="5" t="s">
-        <v>1164</v>
+        <v>1168</v>
       </c>
       <c r="D218" s="6" t="s">
-        <v>1165</v>
+        <v>1169</v>
       </c>
       <c r="E218" s="5" t="s">
-        <v>1163</v>
+        <v>1167</v>
       </c>
     </row>
     <row r="219" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -11818,16 +12012,16 @@
         <v>210</v>
       </c>
       <c r="B219" s="5" t="s">
-        <v>891</v>
+        <v>895</v>
       </c>
       <c r="C219" s="5" t="s">
-        <v>1166</v>
+        <v>1170</v>
       </c>
       <c r="D219" s="6" t="s">
+        <v>1171</v>
+      </c>
+      <c r="E219" s="5" t="s">
         <v>1167</v>
-      </c>
-      <c r="E219" s="5" t="s">
-        <v>1163</v>
       </c>
     </row>
     <row r="220" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -11835,16 +12029,16 @@
         <v>211</v>
       </c>
       <c r="B220" s="5" t="s">
-        <v>1032</v>
+        <v>1036</v>
       </c>
       <c r="C220" s="5" t="s">
-        <v>1168</v>
+        <v>1172</v>
       </c>
       <c r="D220" s="6" t="s">
-        <v>1169</v>
+        <v>1173</v>
       </c>
       <c r="E220" s="5" t="s">
-        <v>1163</v>
+        <v>1167</v>
       </c>
     </row>
     <row r="221" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -11852,16 +12046,16 @@
         <v>212</v>
       </c>
       <c r="B221" s="5" t="s">
-        <v>864</v>
+        <v>868</v>
       </c>
       <c r="C221" s="5" t="s">
-        <v>1170</v>
+        <v>1174</v>
       </c>
       <c r="D221" s="6" t="s">
-        <v>1171</v>
+        <v>1175</v>
       </c>
       <c r="E221" s="5" t="s">
-        <v>1172</v>
+        <v>1176</v>
       </c>
     </row>
     <row r="222" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -11869,16 +12063,16 @@
         <v>213</v>
       </c>
       <c r="B222" s="5" t="s">
-        <v>669</v>
+        <v>673</v>
       </c>
       <c r="C222" s="5" t="s">
-        <v>1173</v>
+        <v>1177</v>
       </c>
       <c r="D222" s="6" t="s">
-        <v>1174</v>
+        <v>1178</v>
       </c>
       <c r="E222" s="5" t="s">
-        <v>1175</v>
+        <v>1179</v>
       </c>
     </row>
     <row r="223" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -11886,16 +12080,16 @@
         <v>214</v>
       </c>
       <c r="B223" s="5" t="s">
-        <v>864</v>
+        <v>868</v>
       </c>
       <c r="C223" s="5" t="s">
-        <v>1176</v>
+        <v>1180</v>
       </c>
       <c r="D223" s="6" t="s">
-        <v>1177</v>
+        <v>1181</v>
       </c>
       <c r="E223" s="5" t="s">
-        <v>1175</v>
+        <v>1179</v>
       </c>
     </row>
     <row r="224" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -11903,16 +12097,16 @@
         <v>215</v>
       </c>
       <c r="B224" s="5" t="s">
-        <v>864</v>
+        <v>868</v>
       </c>
       <c r="C224" s="5" t="s">
-        <v>1178</v>
+        <v>1182</v>
       </c>
       <c r="D224" s="6" t="s">
+        <v>1183</v>
+      </c>
+      <c r="E224" s="5" t="s">
         <v>1179</v>
-      </c>
-      <c r="E224" s="5" t="s">
-        <v>1175</v>
       </c>
     </row>
     <row r="225" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -11920,16 +12114,16 @@
         <v>216</v>
       </c>
       <c r="B225" s="5" t="s">
-        <v>1032</v>
+        <v>1036</v>
       </c>
       <c r="C225" s="5" t="s">
-        <v>1180</v>
+        <v>1184</v>
       </c>
       <c r="D225" s="6" t="s">
-        <v>1181</v>
+        <v>1185</v>
       </c>
       <c r="E225" s="5" t="s">
-        <v>1175</v>
+        <v>1179</v>
       </c>
     </row>
     <row r="226" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -11937,16 +12131,16 @@
         <v>217</v>
       </c>
       <c r="B226" s="5" t="s">
-        <v>875</v>
+        <v>879</v>
       </c>
       <c r="C226" s="5" t="s">
-        <v>1182</v>
+        <v>1186</v>
       </c>
       <c r="D226" s="6" t="s">
-        <v>1183</v>
+        <v>1187</v>
       </c>
       <c r="E226" s="5" t="s">
-        <v>1184</v>
+        <v>1188</v>
       </c>
     </row>
     <row r="227" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -11954,16 +12148,16 @@
         <v>218</v>
       </c>
       <c r="B227" s="5" t="s">
-        <v>669</v>
+        <v>673</v>
       </c>
       <c r="C227" s="5" t="s">
-        <v>1185</v>
+        <v>1189</v>
       </c>
       <c r="D227" s="6" t="s">
-        <v>1186</v>
+        <v>1190</v>
       </c>
       <c r="E227" s="5" t="s">
-        <v>1184</v>
+        <v>1188</v>
       </c>
     </row>
     <row r="228" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -11971,16 +12165,16 @@
         <v>219</v>
       </c>
       <c r="B228" s="5" t="s">
-        <v>808</v>
+        <v>812</v>
       </c>
       <c r="C228" s="5" t="s">
-        <v>1187</v>
+        <v>1191</v>
       </c>
       <c r="D228" s="6" t="s">
+        <v>1192</v>
+      </c>
+      <c r="E228" s="5" t="s">
         <v>1188</v>
-      </c>
-      <c r="E228" s="5" t="s">
-        <v>1184</v>
       </c>
     </row>
     <row r="229" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -11988,84 +12182,220 @@
         <v>220</v>
       </c>
       <c r="B229" s="5" t="s">
-        <v>1032</v>
+        <v>1036</v>
       </c>
       <c r="C229" s="5" t="s">
-        <v>1189</v>
+        <v>1193</v>
       </c>
       <c r="D229" s="6" t="s">
-        <v>1190</v>
+        <v>1194</v>
       </c>
       <c r="E229" s="5" t="s">
-        <v>1184</v>
-      </c>
-    </row>
-    <row r="230" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+        <v>1188</v>
+      </c>
+    </row>
+    <row r="230" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A230" s="5" t="n">
         <v>221</v>
       </c>
       <c r="B230" s="5" t="s">
-        <v>669</v>
+        <v>673</v>
       </c>
       <c r="C230" s="5" t="s">
-        <v>1191</v>
+        <v>1195</v>
       </c>
       <c r="D230" s="6" t="s">
-        <v>1192</v>
+        <v>1196</v>
       </c>
       <c r="E230" s="5" t="s">
-        <v>1193</v>
-      </c>
-    </row>
-    <row r="231" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+        <v>1197</v>
+      </c>
+    </row>
+    <row r="231" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A231" s="5" t="n">
         <v>222</v>
       </c>
       <c r="B231" s="5" t="s">
-        <v>864</v>
+        <v>868</v>
       </c>
       <c r="C231" s="5" t="s">
-        <v>1194</v>
+        <v>1198</v>
       </c>
       <c r="D231" s="6" t="s">
-        <v>1195</v>
+        <v>1199</v>
       </c>
       <c r="E231" s="5" t="s">
-        <v>1193</v>
-      </c>
-    </row>
-    <row r="232" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+        <v>1197</v>
+      </c>
+    </row>
+    <row r="232" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A232" s="5" t="n">
         <v>223</v>
       </c>
       <c r="B232" s="5" t="s">
-        <v>669</v>
+        <v>673</v>
       </c>
       <c r="C232" s="5" t="s">
-        <v>1196</v>
+        <v>1200</v>
       </c>
       <c r="D232" s="6" t="s">
-        <v>1197</v>
+        <v>1201</v>
       </c>
       <c r="E232" s="5" t="s">
-        <v>1198</v>
-      </c>
-    </row>
-    <row r="233" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+        <v>1202</v>
+      </c>
+    </row>
+    <row r="233" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A233" s="5" t="n">
         <v>224</v>
       </c>
       <c r="B233" s="5" t="s">
-        <v>891</v>
+        <v>895</v>
       </c>
       <c r="C233" s="5" t="s">
-        <v>1199</v>
+        <v>1203</v>
       </c>
       <c r="D233" s="6" t="s">
-        <v>1200</v>
+        <v>1204</v>
       </c>
       <c r="E233" s="5" t="s">
-        <v>1198</v>
+        <v>1202</v>
+      </c>
+    </row>
+    <row r="234" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A234" s="5" t="n">
+        <v>225</v>
+      </c>
+      <c r="B234" s="5" t="s">
+        <v>673</v>
+      </c>
+      <c r="C234" s="5" t="s">
+        <v>1205</v>
+      </c>
+      <c r="D234" s="6" t="s">
+        <v>1206</v>
+      </c>
+      <c r="E234" s="5" t="s">
+        <v>1207</v>
+      </c>
+    </row>
+    <row r="235" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A235" s="5" t="n">
+        <v>226</v>
+      </c>
+      <c r="B235" s="5" t="s">
+        <v>812</v>
+      </c>
+      <c r="C235" s="5" t="s">
+        <v>1208</v>
+      </c>
+      <c r="D235" s="6" t="s">
+        <v>1209</v>
+      </c>
+      <c r="E235" s="5" t="s">
+        <v>1207</v>
+      </c>
+    </row>
+    <row r="236" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A236" s="5" t="n">
+        <v>227</v>
+      </c>
+      <c r="B236" s="5" t="s">
+        <v>895</v>
+      </c>
+      <c r="C236" s="5" t="s">
+        <v>1210</v>
+      </c>
+      <c r="D236" s="6" t="s">
+        <v>1211</v>
+      </c>
+      <c r="E236" s="5" t="s">
+        <v>1207</v>
+      </c>
+    </row>
+    <row r="237" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A237" s="5" t="n">
+        <v>228</v>
+      </c>
+      <c r="B237" s="5" t="s">
+        <v>895</v>
+      </c>
+      <c r="C237" s="5" t="s">
+        <v>1212</v>
+      </c>
+      <c r="D237" s="6" t="s">
+        <v>1213</v>
+      </c>
+      <c r="E237" s="5" t="s">
+        <v>1214</v>
+      </c>
+    </row>
+    <row r="238" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A238" s="5" t="n">
+        <v>229</v>
+      </c>
+      <c r="B238" s="5" t="s">
+        <v>868</v>
+      </c>
+      <c r="C238" s="5" t="s">
+        <v>1215</v>
+      </c>
+      <c r="D238" s="6" t="s">
+        <v>1216</v>
+      </c>
+      <c r="E238" s="5" t="s">
+        <v>1214</v>
+      </c>
+    </row>
+    <row r="239" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A239" s="5" t="n">
+        <v>230</v>
+      </c>
+      <c r="B239" s="5" t="s">
+        <v>868</v>
+      </c>
+      <c r="C239" s="5" t="s">
+        <v>1217</v>
+      </c>
+      <c r="D239" s="6" t="s">
+        <v>1218</v>
+      </c>
+      <c r="E239" s="5" t="s">
+        <v>1214</v>
+      </c>
+    </row>
+    <row r="240" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A240" s="5" t="n">
+        <v>231</v>
+      </c>
+      <c r="B240" s="5" t="s">
+        <v>1036</v>
+      </c>
+      <c r="C240" s="5" t="s">
+        <v>1219</v>
+      </c>
+      <c r="D240" s="6" t="s">
+        <v>1220</v>
+      </c>
+      <c r="E240" s="5" t="s">
+        <v>1214</v>
+      </c>
+    </row>
+    <row r="241" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A241" s="5" t="n">
+        <v>232</v>
+      </c>
+      <c r="B241" s="5" t="s">
+        <v>1036</v>
+      </c>
+      <c r="C241" s="5" t="s">
+        <v>1221</v>
+      </c>
+      <c r="D241" s="6" t="s">
+        <v>1222</v>
+      </c>
+      <c r="E241" s="5" t="s">
+        <v>1214</v>
       </c>
     </row>
   </sheetData>
@@ -12224,6 +12554,14 @@
     <hyperlink ref="D231" r:id="rId149" display="https://abcnews.com/Politics/wireStory/excavation-work-trumps-arch-washington-begin-2-weeks-136185425"/>
     <hyperlink ref="D232" r:id="rId150" display="https://www.nbcnews.com/politics/justice-department/trump-administration-rolls-5-voter-fraud-prosecutions-ahead-midterms-rcna596089"/>
     <hyperlink ref="D233" r:id="rId151" display="https://www.cbsnews.com/news/judge-allows-pentagon-fire-stars-stripes-journalists/"/>
+    <hyperlink ref="D234" r:id="rId152" display="https://www.nbcnews.com/politics/trump-administration/jimmy-kimmel-abc-tv-show-wont-air-james-talarico-interview-fcc-threats-rcna596994"/>
+    <hyperlink ref="D235" r:id="rId153" display="https://www.theguardian.com/us-news/video/2026/sep/10/trump-we-will-pay-every-us-citizen-5000-if-republicans-win-midterms-video"/>
+    <hyperlink ref="D236" r:id="rId154" display="https://www.cbsnews.com/news/appeals-court-trump-usps-mail-ballots-first-circuit/"/>
+    <hyperlink ref="D237" r:id="rId155" display="https://www.cbsnews.com/news/joe-digenova-resigns-doj-grand-conspiracy-investigation-trump-obama-biden/"/>
+    <hyperlink ref="D238" r:id="rId156" display="https://abcnews.com/Politics/wireStory/trump-census-eyes-sweeping-plan-omit-immigrants-race-136353634"/>
+    <hyperlink ref="D239" r:id="rId157" display="https://abcnews.com/Politics/wireStory/justice-department-directs-states-hold-2024-election-records-136350319"/>
+    <hyperlink ref="D240" r:id="rId158" display="https://www.pbs.org/newshour/show/news-wrap-august-inflation-report-shows-consumer-prices-up-3-4"/>
+    <hyperlink ref="D241" r:id="rId159" display="https://www.pbs.org/newshour/politics/watch-trump-leads-rnc-in-pledge-to-cheat-like-hell-in-november-elections"/>
   </hyperlinks>
   <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.511811023622047" footer="0.511811023622047"/>
@@ -12240,7 +12578,7 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:B21"/>
+  <dimension ref="A1:B22"/>
   <sheetFormatPr defaultColWidth="8.6875" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="30.01"/>
@@ -12249,7 +12587,7 @@
   <sheetData>
     <row r="1" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A1" s="7" t="s">
-        <v>1201</v>
+        <v>1223</v>
       </c>
       <c r="B1" s="7"/>
     </row>
@@ -12258,7 +12596,7 @@
         <v>3</v>
       </c>
       <c r="B2" s="8" t="s">
-        <v>1202</v>
+        <v>1224</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -12276,7 +12614,7 @@
       </c>
       <c r="B4" s="9" t="n">
         <f aca="false">COUNTIF('Weekly Timeline'!C:C,A4)</f>
-        <v>12</v>
+        <v>13</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -12285,7 +12623,7 @@
       </c>
       <c r="B5" s="9" t="n">
         <f aca="false">COUNTIF('Weekly Timeline'!C:C,A5)</f>
-        <v>6</v>
+        <v>8</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -12303,7 +12641,7 @@
       </c>
       <c r="B7" s="9" t="n">
         <f aca="false">COUNTIF('Weekly Timeline'!C:C,A7)</f>
-        <v>13</v>
+        <v>14</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -12317,70 +12655,70 @@
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A9" s="9" t="s">
-        <v>21</v>
+        <v>558</v>
       </c>
       <c r="B9" s="9" t="n">
         <f aca="false">COUNTIF('Weekly Timeline'!C:C,A9)</f>
-        <v>4</v>
+        <v>2</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A10" s="9" t="s">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="B10" s="9" t="n">
         <f aca="false">COUNTIF('Weekly Timeline'!C:C,A10)</f>
-        <v>29</v>
+        <v>4</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A11" s="9" t="s">
-        <v>38</v>
+        <v>24</v>
       </c>
       <c r="B11" s="9" t="n">
         <f aca="false">COUNTIF('Weekly Timeline'!C:C,A11)</f>
-        <v>3</v>
+        <v>30</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A12" s="9" t="s">
-        <v>48</v>
+        <v>38</v>
       </c>
       <c r="B12" s="9" t="n">
         <f aca="false">COUNTIF('Weekly Timeline'!C:C,A12)</f>
-        <v>14</v>
+        <v>3</v>
       </c>
     </row>
     <row r="13" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A13" s="9" t="s">
-        <v>171</v>
+        <v>48</v>
       </c>
       <c r="B13" s="9" t="n">
         <f aca="false">COUNTIF('Weekly Timeline'!C:C,A13)</f>
-        <v>4</v>
+        <v>14</v>
       </c>
     </row>
     <row r="14" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A14" s="9" t="s">
-        <v>12</v>
+        <v>171</v>
       </c>
       <c r="B14" s="9" t="n">
         <f aca="false">COUNTIF('Weekly Timeline'!C:C,A14)</f>
-        <v>19</v>
+        <v>4</v>
       </c>
     </row>
     <row r="15" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A15" s="9" t="s">
-        <v>112</v>
+        <v>12</v>
       </c>
       <c r="B15" s="9" t="n">
         <f aca="false">COUNTIF('Weekly Timeline'!C:C,A15)</f>
-        <v>1</v>
+        <v>19</v>
       </c>
     </row>
     <row r="16" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A16" s="9" t="s">
-        <v>553</v>
+        <v>112</v>
       </c>
       <c r="B16" s="9" t="n">
         <f aca="false">COUNTIF('Weekly Timeline'!C:C,A16)</f>
@@ -12389,47 +12727,56 @@
     </row>
     <row r="17" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A17" s="9" t="s">
-        <v>15</v>
+        <v>553</v>
       </c>
       <c r="B17" s="9" t="n">
         <f aca="false">COUNTIF('Weekly Timeline'!C:C,A17)</f>
-        <v>4</v>
+        <v>1</v>
       </c>
     </row>
     <row r="18" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A18" s="9" t="s">
-        <v>68</v>
+        <v>15</v>
       </c>
       <c r="B18" s="9" t="n">
         <f aca="false">COUNTIF('Weekly Timeline'!C:C,A18)</f>
-        <v>9</v>
+        <v>4</v>
       </c>
     </row>
     <row r="19" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A19" s="9" t="s">
-        <v>72</v>
+        <v>68</v>
       </c>
       <c r="B19" s="9" t="n">
         <f aca="false">COUNTIF('Weekly Timeline'!C:C,A19)</f>
-        <v>4</v>
+        <v>10</v>
       </c>
     </row>
     <row r="20" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A20" s="9" t="s">
-        <v>346</v>
+        <v>72</v>
       </c>
       <c r="B20" s="9" t="n">
         <f aca="false">COUNTIF('Weekly Timeline'!C:C,A20)</f>
+        <v>4</v>
+      </c>
+    </row>
+    <row r="21" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A21" s="9" t="s">
+        <v>346</v>
+      </c>
+      <c r="B21" s="9" t="n">
+        <f aca="false">COUNTIF('Weekly Timeline'!C:C,A21)</f>
         <v>1</v>
       </c>
     </row>
-    <row r="21" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A21" s="10" t="s">
-        <v>1203</v>
-      </c>
-      <c r="B21" s="10" t="n">
-        <f aca="false">SUM(B3:B20)</f>
-        <v>168</v>
+    <row r="22" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A22" s="10" t="s">
+        <v>1225</v>
+      </c>
+      <c r="B22" s="10" t="n">
+        <f aca="false">SUM(B3:B21)</f>
+        <v>176</v>
       </c>
     </row>
   </sheetData>

--- a/data/Trump_Second_Term_Weekly_Tracker.xlsx
+++ b/data/Trump_Second_Term_Weekly_Tracker.xlsx
@@ -13,7 +13,7 @@
     <sheet name="Summary" sheetId="3" state="visible" r:id="rId5"/>
   </sheets>
   <definedNames>
-    <definedName function="false" hidden="true" localSheetId="0" name="_xlnm._FilterDatabase" vbProcedure="false">'Weekly Timeline'!$A$2:$F$234</definedName>
+    <definedName function="false" hidden="true" localSheetId="0" name="_xlnm._FilterDatabase" vbProcedure="false">'Weekly Timeline'!$A$2:$F$239</definedName>
   </definedNames>
   <calcPr iterateCount="100" refMode="A1" iterate="false" iterateDelta="0.0001"/>
   <extLst>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1864" uniqueCount="1226">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1894" uniqueCount="1240">
   <si>
     <t xml:space="preserve">Documented actions and policies of the second Trump administration reported as harmful by major news outlets, courts, and government data — Jan 20, 2025 through Jul 8, 2026. One row per event; weeks with multiple events have multiple rows; quiet weeks are skipped. This compiles critical coverage as requested; the administration and its supporters dispute many of these characterizations. See the Sources tab (matching Ref #) and verify details independently before citing.</t>
   </si>
@@ -1704,6 +1704,15 @@
     <t xml:space="preserve">Elections</t>
   </si>
   <si>
+    <t xml:space="preserve">Sep 14, 2026</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Sep 14</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Sep 18</t>
+  </si>
+  <si>
     <t xml:space="preserve">Ref # matches the Source Ref column on the Weekly Timeline tab. URLs are provided where verified via current web results (mostly 2026 items). For 2025 items, outlet names and dates are given; searching the description text will locate the original coverage. Per your request the mix emphasizes CNN, Politico, MSNBC/MS NOW, NBC and independent outlets, alongside AP, Reuters, Guardian, NPR, CBS, ABC and court documents.</t>
   </si>
   <si>
@@ -3694,6 +3703,39 @@
   </si>
   <si>
     <t xml:space="preserve">https://www.pbs.org/newshour/politics/watch-trump-leads-rnc-in-pledge-to-cheat-like-hell-in-november-elections</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Second federal judge freezes Trump mail ballot order with US Supreme Court poised to weigh in</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://abcnews.com/Politics/wireStory/federal-judge-freezes-trump-mail-ballot-order-us-136415151</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Trump says he is banning CNN, MS NOW and Politico from the White House</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://www.npr.org/2026/09/18/g-s1-144112/trump-ban-cnn-msnow-politico-white-house-media</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Sep 18, 2026</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Trump announces agreement with Denmark to secure ‘permanent’ control over Greenland’s security</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://www.nbcnews.com/politics/trump-administration/trump-announces-agreement-denmark-secure-permanent-control-greenlands-rcna598641</t>
+  </si>
+  <si>
+    <t xml:space="preserve">U.S. clears potential $24.3B F-35 sale to Saudi Arabia despite security concerns</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://www.nbcnews.com/politics/national-security/state-department-approves-243b-f-35-fighter-jet-sale-saudi-arabia-chin-rcna598487</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Judge rules EPA illegally terminated $7 billion solar program intended to help poorer Americans</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://abcnews.com/Politics/wireStory/judge-rules-epa-illegally-terminated-7-billion-solar-136569326</t>
   </si>
   <si>
     <t xml:space="preserve">Entries by category (live COUNTIF formulas against the Weekly Timeline tab)</t>
@@ -3882,7 +3924,7 @@
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="164" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -4175,7 +4217,7 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:F234"/>
+  <dimension ref="A1:F239"/>
   <sheetFormatPr defaultColWidth="8.6875" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="13.01"/>
@@ -8311,7 +8353,7 @@
         <v>224</v>
       </c>
     </row>
-    <row r="227" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="227" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A227" s="5" t="s">
         <v>555</v>
       </c>
@@ -8327,7 +8369,7 @@
         <v>225</v>
       </c>
     </row>
-    <row r="228" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="228" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A228" s="5" t="s">
         <v>555</v>
       </c>
@@ -8343,7 +8385,7 @@
         <v>226</v>
       </c>
     </row>
-    <row r="229" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="229" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A229" s="5" t="s">
         <v>555</v>
       </c>
@@ -8359,7 +8401,7 @@
         <v>227</v>
       </c>
     </row>
-    <row r="230" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="230" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A230" s="5" t="s">
         <v>555</v>
       </c>
@@ -8375,7 +8417,7 @@
         <v>228</v>
       </c>
     </row>
-    <row r="231" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="231" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A231" s="5" t="s">
         <v>555</v>
       </c>
@@ -8391,7 +8433,7 @@
         <v>229</v>
       </c>
     </row>
-    <row r="232" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="232" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A232" s="5" t="s">
         <v>555</v>
       </c>
@@ -8407,7 +8449,7 @@
         <v>230</v>
       </c>
     </row>
-    <row r="233" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="233" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A233" s="5" t="s">
         <v>555</v>
       </c>
@@ -8423,7 +8465,7 @@
         <v>231</v>
       </c>
     </row>
-    <row r="234" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="234" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A234" s="5" t="s">
         <v>555</v>
       </c>
@@ -8439,8 +8481,78 @@
         <v>232</v>
       </c>
     </row>
+    <row r="235" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A235" s="4" t="s">
+        <v>559</v>
+      </c>
+      <c r="B235" s="4" t="s">
+        <v>560</v>
+      </c>
+      <c r="C235" s="4"/>
+      <c r="D235" s="4"/>
+      <c r="E235" s="4"/>
+      <c r="F235" s="4" t="n">
+        <v>233</v>
+      </c>
+    </row>
+    <row r="236" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A236" s="4" t="s">
+        <v>559</v>
+      </c>
+      <c r="B236" s="4" t="s">
+        <v>561</v>
+      </c>
+      <c r="C236" s="4"/>
+      <c r="D236" s="4"/>
+      <c r="E236" s="4"/>
+      <c r="F236" s="4" t="n">
+        <v>234</v>
+      </c>
+    </row>
+    <row r="237" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A237" s="4" t="s">
+        <v>559</v>
+      </c>
+      <c r="B237" s="4" t="s">
+        <v>561</v>
+      </c>
+      <c r="C237" s="4"/>
+      <c r="D237" s="4"/>
+      <c r="E237" s="4"/>
+      <c r="F237" s="4" t="n">
+        <v>235</v>
+      </c>
+    </row>
+    <row r="238" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A238" s="4" t="s">
+        <v>559</v>
+      </c>
+      <c r="B238" s="4" t="s">
+        <v>561</v>
+      </c>
+      <c r="C238" s="4"/>
+      <c r="D238" s="4"/>
+      <c r="E238" s="4"/>
+      <c r="F238" s="4" t="n">
+        <v>236</v>
+      </c>
+    </row>
+    <row r="239" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A239" s="4" t="s">
+        <v>559</v>
+      </c>
+      <c r="B239" s="4" t="s">
+        <v>561</v>
+      </c>
+      <c r="C239" s="4"/>
+      <c r="D239" s="4"/>
+      <c r="E239" s="4"/>
+      <c r="F239" s="4" t="n">
+        <v>237</v>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A2:F234"/>
+  <autoFilter ref="A2:F239"/>
   <mergeCells count="1">
     <mergeCell ref="A1:F1"/>
   </mergeCells>
@@ -8460,7 +8572,7 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:E241"/>
+  <dimension ref="A1:E246"/>
   <sheetFormatPr defaultColWidth="8.6875" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="7"/>
@@ -8471,7 +8583,7 @@
   <sheetData>
     <row r="1" customFormat="false" ht="48" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A1" s="2" t="s">
-        <v>559</v>
+        <v>562</v>
       </c>
       <c r="B1" s="2"/>
       <c r="C1" s="2"/>
@@ -8480,19 +8592,19 @@
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A2" s="3" t="s">
-        <v>560</v>
+        <v>563</v>
       </c>
       <c r="B2" s="3" t="s">
-        <v>561</v>
+        <v>564</v>
       </c>
       <c r="C2" s="3" t="s">
-        <v>562</v>
+        <v>565</v>
       </c>
       <c r="D2" s="3" t="s">
-        <v>563</v>
+        <v>566</v>
       </c>
       <c r="E2" s="3" t="s">
-        <v>564</v>
+        <v>567</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -8500,14 +8612,14 @@
         <v>1</v>
       </c>
       <c r="B3" s="5" t="s">
-        <v>565</v>
+        <v>568</v>
       </c>
       <c r="C3" s="5" t="s">
-        <v>566</v>
+        <v>569</v>
       </c>
       <c r="D3" s="5"/>
       <c r="E3" s="5" t="s">
-        <v>567</v>
+        <v>570</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -8515,14 +8627,14 @@
         <v>2</v>
       </c>
       <c r="B4" s="5" t="s">
-        <v>568</v>
+        <v>571</v>
       </c>
       <c r="C4" s="5" t="s">
-        <v>569</v>
+        <v>572</v>
       </c>
       <c r="D4" s="5"/>
       <c r="E4" s="5" t="s">
-        <v>570</v>
+        <v>573</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -8530,14 +8642,14 @@
         <v>3</v>
       </c>
       <c r="B5" s="5" t="s">
-        <v>571</v>
+        <v>574</v>
       </c>
       <c r="C5" s="5" t="s">
-        <v>572</v>
+        <v>575</v>
       </c>
       <c r="D5" s="5"/>
       <c r="E5" s="5" t="s">
-        <v>567</v>
+        <v>570</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -8545,14 +8657,14 @@
         <v>4</v>
       </c>
       <c r="B6" s="5" t="s">
-        <v>573</v>
+        <v>576</v>
       </c>
       <c r="C6" s="5" t="s">
-        <v>574</v>
+        <v>577</v>
       </c>
       <c r="D6" s="5"/>
       <c r="E6" s="5" t="s">
-        <v>575</v>
+        <v>578</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -8560,14 +8672,14 @@
         <v>5</v>
       </c>
       <c r="B7" s="5" t="s">
-        <v>576</v>
+        <v>579</v>
       </c>
       <c r="C7" s="5" t="s">
-        <v>577</v>
+        <v>580</v>
       </c>
       <c r="D7" s="5"/>
       <c r="E7" s="5" t="s">
-        <v>567</v>
+        <v>570</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -8575,14 +8687,14 @@
         <v>6</v>
       </c>
       <c r="B8" s="5" t="s">
-        <v>578</v>
+        <v>581</v>
       </c>
       <c r="C8" s="5" t="s">
-        <v>579</v>
+        <v>582</v>
       </c>
       <c r="D8" s="5"/>
       <c r="E8" s="5" t="s">
-        <v>567</v>
+        <v>570</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -8590,14 +8702,14 @@
         <v>7</v>
       </c>
       <c r="B9" s="5" t="s">
-        <v>580</v>
+        <v>583</v>
       </c>
       <c r="C9" s="5" t="s">
-        <v>581</v>
+        <v>584</v>
       </c>
       <c r="D9" s="5"/>
       <c r="E9" s="5" t="s">
-        <v>582</v>
+        <v>585</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -8605,14 +8717,14 @@
         <v>8</v>
       </c>
       <c r="B10" s="5" t="s">
-        <v>583</v>
+        <v>586</v>
       </c>
       <c r="C10" s="5" t="s">
-        <v>584</v>
+        <v>587</v>
       </c>
       <c r="D10" s="5"/>
       <c r="E10" s="5" t="s">
-        <v>585</v>
+        <v>588</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -8620,14 +8732,14 @@
         <v>9</v>
       </c>
       <c r="B11" s="5" t="s">
-        <v>586</v>
+        <v>589</v>
       </c>
       <c r="C11" s="5" t="s">
-        <v>587</v>
+        <v>590</v>
       </c>
       <c r="D11" s="5"/>
       <c r="E11" s="5" t="s">
-        <v>588</v>
+        <v>591</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -8635,14 +8747,14 @@
         <v>10</v>
       </c>
       <c r="B12" s="5" t="s">
-        <v>589</v>
+        <v>592</v>
       </c>
       <c r="C12" s="5" t="s">
-        <v>590</v>
+        <v>593</v>
       </c>
       <c r="D12" s="5"/>
       <c r="E12" s="5" t="s">
-        <v>591</v>
+        <v>594</v>
       </c>
     </row>
     <row r="13" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -8650,14 +8762,14 @@
         <v>11</v>
       </c>
       <c r="B13" s="5" t="s">
-        <v>592</v>
+        <v>595</v>
       </c>
       <c r="C13" s="5" t="s">
-        <v>593</v>
+        <v>596</v>
       </c>
       <c r="D13" s="5"/>
       <c r="E13" s="5" t="s">
-        <v>594</v>
+        <v>597</v>
       </c>
     </row>
     <row r="14" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -8665,14 +8777,14 @@
         <v>12</v>
       </c>
       <c r="B14" s="5" t="s">
-        <v>595</v>
+        <v>598</v>
       </c>
       <c r="C14" s="5" t="s">
-        <v>596</v>
+        <v>599</v>
       </c>
       <c r="D14" s="5"/>
       <c r="E14" s="5" t="s">
-        <v>597</v>
+        <v>600</v>
       </c>
     </row>
     <row r="15" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -8680,14 +8792,14 @@
         <v>13</v>
       </c>
       <c r="B15" s="5" t="s">
-        <v>598</v>
+        <v>601</v>
       </c>
       <c r="C15" s="5" t="s">
-        <v>599</v>
+        <v>602</v>
       </c>
       <c r="D15" s="5"/>
       <c r="E15" s="5" t="s">
-        <v>600</v>
+        <v>603</v>
       </c>
     </row>
     <row r="16" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -8695,14 +8807,14 @@
         <v>14</v>
       </c>
       <c r="B16" s="5" t="s">
-        <v>601</v>
+        <v>604</v>
       </c>
       <c r="C16" s="5" t="s">
-        <v>602</v>
+        <v>605</v>
       </c>
       <c r="D16" s="5"/>
       <c r="E16" s="5" t="s">
-        <v>603</v>
+        <v>606</v>
       </c>
     </row>
     <row r="17" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -8710,14 +8822,14 @@
         <v>15</v>
       </c>
       <c r="B17" s="5" t="s">
-        <v>604</v>
+        <v>607</v>
       </c>
       <c r="C17" s="5" t="s">
-        <v>605</v>
+        <v>608</v>
       </c>
       <c r="D17" s="5"/>
       <c r="E17" s="5" t="s">
-        <v>606</v>
+        <v>609</v>
       </c>
     </row>
     <row r="18" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -8725,14 +8837,14 @@
         <v>16</v>
       </c>
       <c r="B18" s="5" t="s">
-        <v>607</v>
+        <v>610</v>
       </c>
       <c r="C18" s="5" t="s">
-        <v>608</v>
+        <v>611</v>
       </c>
       <c r="D18" s="5"/>
       <c r="E18" s="5" t="s">
-        <v>609</v>
+        <v>612</v>
       </c>
     </row>
     <row r="19" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -8740,14 +8852,14 @@
         <v>17</v>
       </c>
       <c r="B19" s="5" t="s">
-        <v>610</v>
+        <v>613</v>
       </c>
       <c r="C19" s="5" t="s">
-        <v>611</v>
+        <v>614</v>
       </c>
       <c r="D19" s="5"/>
       <c r="E19" s="5" t="s">
-        <v>612</v>
+        <v>615</v>
       </c>
     </row>
     <row r="20" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -8755,14 +8867,14 @@
         <v>18</v>
       </c>
       <c r="B20" s="5" t="s">
-        <v>613</v>
+        <v>616</v>
       </c>
       <c r="C20" s="5" t="s">
-        <v>614</v>
+        <v>617</v>
       </c>
       <c r="D20" s="5"/>
       <c r="E20" s="5" t="s">
-        <v>615</v>
+        <v>618</v>
       </c>
     </row>
     <row r="21" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -8770,14 +8882,14 @@
         <v>19</v>
       </c>
       <c r="B21" s="5" t="s">
-        <v>616</v>
+        <v>619</v>
       </c>
       <c r="C21" s="5" t="s">
-        <v>617</v>
+        <v>620</v>
       </c>
       <c r="D21" s="5"/>
       <c r="E21" s="5" t="s">
-        <v>618</v>
+        <v>621</v>
       </c>
     </row>
     <row r="22" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -8785,14 +8897,14 @@
         <v>20</v>
       </c>
       <c r="B22" s="5" t="s">
-        <v>619</v>
+        <v>622</v>
       </c>
       <c r="C22" s="5" t="s">
-        <v>620</v>
+        <v>623</v>
       </c>
       <c r="D22" s="5"/>
       <c r="E22" s="5" t="s">
-        <v>621</v>
+        <v>624</v>
       </c>
     </row>
     <row r="23" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -8800,14 +8912,14 @@
         <v>21</v>
       </c>
       <c r="B23" s="5" t="s">
-        <v>622</v>
+        <v>625</v>
       </c>
       <c r="C23" s="5" t="s">
-        <v>623</v>
+        <v>626</v>
       </c>
       <c r="D23" s="5"/>
       <c r="E23" s="5" t="s">
-        <v>624</v>
+        <v>627</v>
       </c>
     </row>
     <row r="24" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -8815,14 +8927,14 @@
         <v>22</v>
       </c>
       <c r="B24" s="5" t="s">
-        <v>625</v>
+        <v>628</v>
       </c>
       <c r="C24" s="5" t="s">
-        <v>626</v>
+        <v>629</v>
       </c>
       <c r="D24" s="5"/>
       <c r="E24" s="5" t="s">
-        <v>627</v>
+        <v>630</v>
       </c>
     </row>
     <row r="25" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -8830,14 +8942,14 @@
         <v>23</v>
       </c>
       <c r="B25" s="5" t="s">
-        <v>628</v>
+        <v>631</v>
       </c>
       <c r="C25" s="5" t="s">
-        <v>629</v>
+        <v>632</v>
       </c>
       <c r="D25" s="5"/>
       <c r="E25" s="5" t="s">
-        <v>630</v>
+        <v>633</v>
       </c>
     </row>
     <row r="26" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -8845,14 +8957,14 @@
         <v>24</v>
       </c>
       <c r="B26" s="5" t="s">
-        <v>631</v>
+        <v>634</v>
       </c>
       <c r="C26" s="5" t="s">
-        <v>632</v>
+        <v>635</v>
       </c>
       <c r="D26" s="5"/>
       <c r="E26" s="5" t="s">
-        <v>633</v>
+        <v>636</v>
       </c>
     </row>
     <row r="27" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -8860,14 +8972,14 @@
         <v>25</v>
       </c>
       <c r="B27" s="5" t="s">
-        <v>634</v>
+        <v>637</v>
       </c>
       <c r="C27" s="5" t="s">
-        <v>635</v>
+        <v>638</v>
       </c>
       <c r="D27" s="5"/>
       <c r="E27" s="5" t="s">
-        <v>636</v>
+        <v>639</v>
       </c>
     </row>
     <row r="28" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -8875,14 +8987,14 @@
         <v>26</v>
       </c>
       <c r="B28" s="5" t="s">
-        <v>637</v>
+        <v>640</v>
       </c>
       <c r="C28" s="5" t="s">
-        <v>638</v>
+        <v>641</v>
       </c>
       <c r="D28" s="5"/>
       <c r="E28" s="5" t="s">
-        <v>639</v>
+        <v>642</v>
       </c>
     </row>
     <row r="29" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -8890,14 +9002,14 @@
         <v>27</v>
       </c>
       <c r="B29" s="5" t="s">
-        <v>640</v>
+        <v>643</v>
       </c>
       <c r="C29" s="5" t="s">
-        <v>641</v>
+        <v>644</v>
       </c>
       <c r="D29" s="5"/>
       <c r="E29" s="5" t="s">
-        <v>642</v>
+        <v>645</v>
       </c>
     </row>
     <row r="30" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -8905,14 +9017,14 @@
         <v>28</v>
       </c>
       <c r="B30" s="5" t="s">
-        <v>643</v>
+        <v>646</v>
       </c>
       <c r="C30" s="5" t="s">
-        <v>644</v>
+        <v>647</v>
       </c>
       <c r="D30" s="5"/>
       <c r="E30" s="5" t="s">
-        <v>645</v>
+        <v>648</v>
       </c>
     </row>
     <row r="31" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -8920,14 +9032,14 @@
         <v>29</v>
       </c>
       <c r="B31" s="5" t="s">
-        <v>646</v>
+        <v>649</v>
       </c>
       <c r="C31" s="5" t="s">
-        <v>647</v>
+        <v>650</v>
       </c>
       <c r="D31" s="5"/>
       <c r="E31" s="5" t="s">
-        <v>648</v>
+        <v>651</v>
       </c>
     </row>
     <row r="32" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -8935,14 +9047,14 @@
         <v>30</v>
       </c>
       <c r="B32" s="5" t="s">
-        <v>592</v>
+        <v>595</v>
       </c>
       <c r="C32" s="5" t="s">
-        <v>649</v>
+        <v>652</v>
       </c>
       <c r="D32" s="5"/>
       <c r="E32" s="5" t="s">
-        <v>650</v>
+        <v>653</v>
       </c>
     </row>
     <row r="33" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -8950,14 +9062,14 @@
         <v>31</v>
       </c>
       <c r="B33" s="5" t="s">
-        <v>651</v>
+        <v>654</v>
       </c>
       <c r="C33" s="5" t="s">
-        <v>652</v>
+        <v>655</v>
       </c>
       <c r="D33" s="5"/>
       <c r="E33" s="5" t="s">
-        <v>653</v>
+        <v>656</v>
       </c>
     </row>
     <row r="34" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -8965,14 +9077,14 @@
         <v>32</v>
       </c>
       <c r="B34" s="5" t="s">
-        <v>610</v>
+        <v>613</v>
       </c>
       <c r="C34" s="5" t="s">
-        <v>654</v>
+        <v>657</v>
       </c>
       <c r="D34" s="5"/>
       <c r="E34" s="5" t="s">
-        <v>655</v>
+        <v>658</v>
       </c>
     </row>
     <row r="35" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -8980,14 +9092,14 @@
         <v>33</v>
       </c>
       <c r="B35" s="5" t="s">
-        <v>656</v>
+        <v>659</v>
       </c>
       <c r="C35" s="5" t="s">
-        <v>657</v>
+        <v>660</v>
       </c>
       <c r="D35" s="5"/>
       <c r="E35" s="5" t="s">
-        <v>658</v>
+        <v>661</v>
       </c>
     </row>
     <row r="36" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -8995,14 +9107,14 @@
         <v>34</v>
       </c>
       <c r="B36" s="5" t="s">
-        <v>659</v>
+        <v>662</v>
       </c>
       <c r="C36" s="5" t="s">
-        <v>660</v>
+        <v>663</v>
       </c>
       <c r="D36" s="5"/>
       <c r="E36" s="5" t="s">
-        <v>661</v>
+        <v>664</v>
       </c>
     </row>
     <row r="37" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -9010,14 +9122,14 @@
         <v>35</v>
       </c>
       <c r="B37" s="5" t="s">
-        <v>662</v>
+        <v>665</v>
       </c>
       <c r="C37" s="5" t="s">
-        <v>663</v>
+        <v>666</v>
       </c>
       <c r="D37" s="5"/>
       <c r="E37" s="5" t="s">
-        <v>664</v>
+        <v>667</v>
       </c>
     </row>
     <row r="38" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -9025,14 +9137,14 @@
         <v>36</v>
       </c>
       <c r="B38" s="5" t="s">
-        <v>610</v>
+        <v>613</v>
       </c>
       <c r="C38" s="5" t="s">
-        <v>665</v>
+        <v>668</v>
       </c>
       <c r="D38" s="5"/>
       <c r="E38" s="5" t="s">
-        <v>666</v>
+        <v>669</v>
       </c>
     </row>
     <row r="39" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -9040,14 +9152,14 @@
         <v>37</v>
       </c>
       <c r="B39" s="5" t="s">
-        <v>667</v>
+        <v>670</v>
       </c>
       <c r="C39" s="5" t="s">
-        <v>668</v>
+        <v>671</v>
       </c>
       <c r="D39" s="5"/>
       <c r="E39" s="5" t="s">
-        <v>669</v>
+        <v>672</v>
       </c>
     </row>
     <row r="40" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -9055,14 +9167,14 @@
         <v>38</v>
       </c>
       <c r="B40" s="5" t="s">
-        <v>670</v>
+        <v>673</v>
       </c>
       <c r="C40" s="5" t="s">
-        <v>671</v>
+        <v>674</v>
       </c>
       <c r="D40" s="5"/>
       <c r="E40" s="5" t="s">
-        <v>672</v>
+        <v>675</v>
       </c>
     </row>
     <row r="41" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -9070,10 +9182,10 @@
         <v>39</v>
       </c>
       <c r="B41" s="5" t="s">
-        <v>673</v>
+        <v>676</v>
       </c>
       <c r="C41" s="5" t="s">
-        <v>674</v>
+        <v>677</v>
       </c>
       <c r="D41" s="5"/>
       <c r="E41" s="5" t="s">
@@ -9085,14 +9197,14 @@
         <v>40</v>
       </c>
       <c r="B42" s="5" t="s">
-        <v>675</v>
+        <v>678</v>
       </c>
       <c r="C42" s="5" t="s">
-        <v>676</v>
+        <v>679</v>
       </c>
       <c r="D42" s="5"/>
       <c r="E42" s="5" t="s">
-        <v>677</v>
+        <v>680</v>
       </c>
     </row>
     <row r="43" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -9100,14 +9212,14 @@
         <v>41</v>
       </c>
       <c r="B43" s="5" t="s">
-        <v>678</v>
+        <v>681</v>
       </c>
       <c r="C43" s="5" t="s">
-        <v>679</v>
+        <v>682</v>
       </c>
       <c r="D43" s="5"/>
       <c r="E43" s="5" t="s">
-        <v>680</v>
+        <v>683</v>
       </c>
     </row>
     <row r="44" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -9115,14 +9227,14 @@
         <v>42</v>
       </c>
       <c r="B44" s="5" t="s">
-        <v>681</v>
+        <v>684</v>
       </c>
       <c r="C44" s="5" t="s">
-        <v>682</v>
+        <v>685</v>
       </c>
       <c r="D44" s="5"/>
       <c r="E44" s="5" t="s">
-        <v>683</v>
+        <v>686</v>
       </c>
     </row>
     <row r="45" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -9130,14 +9242,14 @@
         <v>43</v>
       </c>
       <c r="B45" s="5" t="s">
-        <v>684</v>
+        <v>687</v>
       </c>
       <c r="C45" s="5" t="s">
-        <v>685</v>
+        <v>688</v>
       </c>
       <c r="D45" s="5"/>
       <c r="E45" s="5" t="s">
-        <v>686</v>
+        <v>689</v>
       </c>
     </row>
     <row r="46" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -9145,14 +9257,14 @@
         <v>44</v>
       </c>
       <c r="B46" s="5" t="s">
-        <v>687</v>
+        <v>690</v>
       </c>
       <c r="C46" s="5" t="s">
-        <v>688</v>
+        <v>691</v>
       </c>
       <c r="D46" s="5"/>
       <c r="E46" s="5" t="s">
-        <v>689</v>
+        <v>692</v>
       </c>
     </row>
     <row r="47" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -9160,14 +9272,14 @@
         <v>45</v>
       </c>
       <c r="B47" s="5" t="s">
-        <v>690</v>
+        <v>693</v>
       </c>
       <c r="C47" s="5" t="s">
-        <v>691</v>
+        <v>694</v>
       </c>
       <c r="D47" s="5"/>
       <c r="E47" s="5" t="s">
-        <v>692</v>
+        <v>695</v>
       </c>
     </row>
     <row r="48" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -9175,14 +9287,14 @@
         <v>46</v>
       </c>
       <c r="B48" s="5" t="s">
-        <v>693</v>
+        <v>696</v>
       </c>
       <c r="C48" s="5" t="s">
-        <v>694</v>
+        <v>697</v>
       </c>
       <c r="D48" s="5"/>
       <c r="E48" s="5" t="s">
-        <v>695</v>
+        <v>698</v>
       </c>
     </row>
     <row r="49" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -9190,14 +9302,14 @@
         <v>47</v>
       </c>
       <c r="B49" s="5" t="s">
-        <v>696</v>
+        <v>699</v>
       </c>
       <c r="C49" s="5" t="s">
-        <v>697</v>
+        <v>700</v>
       </c>
       <c r="D49" s="5"/>
       <c r="E49" s="5" t="s">
-        <v>698</v>
+        <v>701</v>
       </c>
     </row>
     <row r="50" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -9205,14 +9317,14 @@
         <v>48</v>
       </c>
       <c r="B50" s="5" t="s">
-        <v>699</v>
+        <v>702</v>
       </c>
       <c r="C50" s="5" t="s">
-        <v>700</v>
+        <v>703</v>
       </c>
       <c r="D50" s="5"/>
       <c r="E50" s="5" t="s">
-        <v>701</v>
+        <v>704</v>
       </c>
     </row>
     <row r="51" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -9220,14 +9332,14 @@
         <v>49</v>
       </c>
       <c r="B51" s="5" t="s">
-        <v>702</v>
+        <v>705</v>
       </c>
       <c r="C51" s="5" t="s">
-        <v>703</v>
+        <v>706</v>
       </c>
       <c r="D51" s="5"/>
       <c r="E51" s="5" t="s">
-        <v>704</v>
+        <v>707</v>
       </c>
     </row>
     <row r="52" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -9235,14 +9347,14 @@
         <v>50</v>
       </c>
       <c r="B52" s="5" t="s">
-        <v>705</v>
+        <v>708</v>
       </c>
       <c r="C52" s="5" t="s">
-        <v>706</v>
+        <v>709</v>
       </c>
       <c r="D52" s="5"/>
       <c r="E52" s="5" t="s">
-        <v>707</v>
+        <v>710</v>
       </c>
     </row>
     <row r="53" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -9250,14 +9362,14 @@
         <v>51</v>
       </c>
       <c r="B53" s="5" t="s">
-        <v>708</v>
+        <v>711</v>
       </c>
       <c r="C53" s="5" t="s">
-        <v>709</v>
+        <v>712</v>
       </c>
       <c r="D53" s="5"/>
       <c r="E53" s="5" t="s">
-        <v>710</v>
+        <v>713</v>
       </c>
     </row>
     <row r="54" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -9265,14 +9377,14 @@
         <v>52</v>
       </c>
       <c r="B54" s="5" t="s">
-        <v>610</v>
+        <v>613</v>
       </c>
       <c r="C54" s="5" t="s">
-        <v>711</v>
+        <v>714</v>
       </c>
       <c r="D54" s="5"/>
       <c r="E54" s="5" t="s">
-        <v>712</v>
+        <v>715</v>
       </c>
     </row>
     <row r="55" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -9280,14 +9392,14 @@
         <v>53</v>
       </c>
       <c r="B55" s="5" t="s">
-        <v>713</v>
+        <v>716</v>
       </c>
       <c r="C55" s="5" t="s">
-        <v>714</v>
+        <v>717</v>
       </c>
       <c r="D55" s="5"/>
       <c r="E55" s="5" t="s">
-        <v>715</v>
+        <v>718</v>
       </c>
     </row>
     <row r="56" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -9295,14 +9407,14 @@
         <v>54</v>
       </c>
       <c r="B56" s="5" t="s">
-        <v>716</v>
+        <v>719</v>
       </c>
       <c r="C56" s="5" t="s">
-        <v>717</v>
+        <v>720</v>
       </c>
       <c r="D56" s="5"/>
       <c r="E56" s="5" t="s">
-        <v>718</v>
+        <v>721</v>
       </c>
     </row>
     <row r="57" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -9310,14 +9422,14 @@
         <v>55</v>
       </c>
       <c r="B57" s="5" t="s">
-        <v>719</v>
+        <v>722</v>
       </c>
       <c r="C57" s="5" t="s">
-        <v>720</v>
+        <v>723</v>
       </c>
       <c r="D57" s="5"/>
       <c r="E57" s="5" t="s">
-        <v>721</v>
+        <v>724</v>
       </c>
     </row>
     <row r="58" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -9325,14 +9437,14 @@
         <v>56</v>
       </c>
       <c r="B58" s="5" t="s">
-        <v>722</v>
+        <v>725</v>
       </c>
       <c r="C58" s="5" t="s">
-        <v>723</v>
+        <v>726</v>
       </c>
       <c r="D58" s="5"/>
       <c r="E58" s="5" t="s">
-        <v>724</v>
+        <v>727</v>
       </c>
     </row>
     <row r="59" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -9340,14 +9452,14 @@
         <v>57</v>
       </c>
       <c r="B59" s="5" t="s">
-        <v>725</v>
+        <v>728</v>
       </c>
       <c r="C59" s="5" t="s">
-        <v>726</v>
+        <v>729</v>
       </c>
       <c r="D59" s="5"/>
       <c r="E59" s="5" t="s">
-        <v>727</v>
+        <v>730</v>
       </c>
     </row>
     <row r="60" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -9355,14 +9467,14 @@
         <v>58</v>
       </c>
       <c r="B60" s="5" t="s">
-        <v>728</v>
+        <v>731</v>
       </c>
       <c r="C60" s="5" t="s">
-        <v>729</v>
+        <v>732</v>
       </c>
       <c r="D60" s="5"/>
       <c r="E60" s="5" t="s">
-        <v>730</v>
+        <v>733</v>
       </c>
     </row>
     <row r="61" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -9370,14 +9482,14 @@
         <v>59</v>
       </c>
       <c r="B61" s="5" t="s">
-        <v>731</v>
+        <v>734</v>
       </c>
       <c r="C61" s="5" t="s">
-        <v>732</v>
+        <v>735</v>
       </c>
       <c r="D61" s="5"/>
       <c r="E61" s="5" t="s">
-        <v>733</v>
+        <v>736</v>
       </c>
     </row>
     <row r="62" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -9385,14 +9497,14 @@
         <v>60</v>
       </c>
       <c r="B62" s="5" t="s">
-        <v>734</v>
+        <v>737</v>
       </c>
       <c r="C62" s="5" t="s">
-        <v>735</v>
+        <v>738</v>
       </c>
       <c r="D62" s="5"/>
       <c r="E62" s="5" t="s">
-        <v>736</v>
+        <v>739</v>
       </c>
     </row>
     <row r="63" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -9400,14 +9512,14 @@
         <v>61</v>
       </c>
       <c r="B63" s="5" t="s">
-        <v>737</v>
+        <v>740</v>
       </c>
       <c r="C63" s="5" t="s">
-        <v>738</v>
+        <v>741</v>
       </c>
       <c r="D63" s="5"/>
       <c r="E63" s="5" t="s">
-        <v>739</v>
+        <v>742</v>
       </c>
     </row>
     <row r="64" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -9415,14 +9527,14 @@
         <v>62</v>
       </c>
       <c r="B64" s="5" t="s">
-        <v>740</v>
+        <v>743</v>
       </c>
       <c r="C64" s="5" t="s">
-        <v>741</v>
+        <v>744</v>
       </c>
       <c r="D64" s="5"/>
       <c r="E64" s="5" t="s">
-        <v>742</v>
+        <v>745</v>
       </c>
     </row>
     <row r="65" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -9430,14 +9542,14 @@
         <v>63</v>
       </c>
       <c r="B65" s="5" t="s">
-        <v>743</v>
+        <v>746</v>
       </c>
       <c r="C65" s="5" t="s">
-        <v>744</v>
+        <v>747</v>
       </c>
       <c r="D65" s="5"/>
       <c r="E65" s="5" t="s">
-        <v>745</v>
+        <v>748</v>
       </c>
     </row>
     <row r="66" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -9445,14 +9557,14 @@
         <v>64</v>
       </c>
       <c r="B66" s="5" t="s">
-        <v>746</v>
+        <v>749</v>
       </c>
       <c r="C66" s="5" t="s">
-        <v>747</v>
+        <v>750</v>
       </c>
       <c r="D66" s="5"/>
       <c r="E66" s="5" t="s">
-        <v>748</v>
+        <v>751</v>
       </c>
     </row>
     <row r="67" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -9460,14 +9572,14 @@
         <v>65</v>
       </c>
       <c r="B67" s="5" t="s">
-        <v>749</v>
+        <v>752</v>
       </c>
       <c r="C67" s="5" t="s">
-        <v>750</v>
+        <v>753</v>
       </c>
       <c r="D67" s="5"/>
       <c r="E67" s="5" t="s">
-        <v>751</v>
+        <v>754</v>
       </c>
     </row>
     <row r="68" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -9475,14 +9587,14 @@
         <v>66</v>
       </c>
       <c r="B68" s="5" t="s">
-        <v>752</v>
+        <v>755</v>
       </c>
       <c r="C68" s="5" t="s">
-        <v>753</v>
+        <v>756</v>
       </c>
       <c r="D68" s="5"/>
       <c r="E68" s="5" t="s">
-        <v>754</v>
+        <v>757</v>
       </c>
     </row>
     <row r="69" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -9490,14 +9602,14 @@
         <v>67</v>
       </c>
       <c r="B69" s="5" t="s">
-        <v>755</v>
+        <v>758</v>
       </c>
       <c r="C69" s="5" t="s">
-        <v>756</v>
+        <v>759</v>
       </c>
       <c r="D69" s="5"/>
       <c r="E69" s="5" t="s">
-        <v>757</v>
+        <v>760</v>
       </c>
     </row>
     <row r="70" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -9505,14 +9617,14 @@
         <v>68</v>
       </c>
       <c r="B70" s="5" t="s">
-        <v>758</v>
+        <v>761</v>
       </c>
       <c r="C70" s="5" t="s">
-        <v>759</v>
+        <v>762</v>
       </c>
       <c r="D70" s="5"/>
       <c r="E70" s="5" t="s">
-        <v>760</v>
+        <v>763</v>
       </c>
     </row>
     <row r="71" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -9520,14 +9632,14 @@
         <v>69</v>
       </c>
       <c r="B71" s="5" t="s">
-        <v>761</v>
+        <v>764</v>
       </c>
       <c r="C71" s="5" t="s">
-        <v>762</v>
+        <v>765</v>
       </c>
       <c r="D71" s="5"/>
       <c r="E71" s="5" t="s">
-        <v>763</v>
+        <v>766</v>
       </c>
     </row>
     <row r="72" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -9535,14 +9647,14 @@
         <v>70</v>
       </c>
       <c r="B72" s="5" t="s">
-        <v>764</v>
+        <v>767</v>
       </c>
       <c r="C72" s="5" t="s">
-        <v>765</v>
+        <v>768</v>
       </c>
       <c r="D72" s="5"/>
       <c r="E72" s="5" t="s">
-        <v>766</v>
+        <v>769</v>
       </c>
     </row>
     <row r="73" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -9550,14 +9662,14 @@
         <v>71</v>
       </c>
       <c r="B73" s="5" t="s">
-        <v>767</v>
+        <v>770</v>
       </c>
       <c r="C73" s="5" t="s">
-        <v>768</v>
+        <v>771</v>
       </c>
       <c r="D73" s="5"/>
       <c r="E73" s="5" t="s">
-        <v>769</v>
+        <v>772</v>
       </c>
     </row>
     <row r="74" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -9565,14 +9677,14 @@
         <v>72</v>
       </c>
       <c r="B74" s="5" t="s">
-        <v>770</v>
+        <v>773</v>
       </c>
       <c r="C74" s="5" t="s">
-        <v>771</v>
+        <v>774</v>
       </c>
       <c r="D74" s="5"/>
       <c r="E74" s="5" t="s">
-        <v>772</v>
+        <v>775</v>
       </c>
     </row>
     <row r="75" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -9580,14 +9692,14 @@
         <v>73</v>
       </c>
       <c r="B75" s="5" t="s">
-        <v>610</v>
+        <v>613</v>
       </c>
       <c r="C75" s="5" t="s">
-        <v>773</v>
+        <v>776</v>
       </c>
       <c r="D75" s="5"/>
       <c r="E75" s="5" t="s">
-        <v>774</v>
+        <v>777</v>
       </c>
     </row>
     <row r="76" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -9595,14 +9707,14 @@
         <v>74</v>
       </c>
       <c r="B76" s="5" t="s">
-        <v>775</v>
+        <v>778</v>
       </c>
       <c r="C76" s="5" t="s">
-        <v>776</v>
+        <v>779</v>
       </c>
       <c r="D76" s="5"/>
       <c r="E76" s="5" t="s">
-        <v>777</v>
+        <v>780</v>
       </c>
     </row>
     <row r="77" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -9610,14 +9722,14 @@
         <v>75</v>
       </c>
       <c r="B77" s="5" t="s">
-        <v>610</v>
+        <v>613</v>
       </c>
       <c r="C77" s="5" t="s">
-        <v>778</v>
+        <v>781</v>
       </c>
       <c r="D77" s="5"/>
       <c r="E77" s="5" t="s">
-        <v>779</v>
+        <v>782</v>
       </c>
     </row>
     <row r="78" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -9625,14 +9737,14 @@
         <v>76</v>
       </c>
       <c r="B78" s="5" t="s">
-        <v>780</v>
+        <v>783</v>
       </c>
       <c r="C78" s="5" t="s">
-        <v>781</v>
+        <v>784</v>
       </c>
       <c r="D78" s="5"/>
       <c r="E78" s="5" t="s">
-        <v>782</v>
+        <v>785</v>
       </c>
     </row>
     <row r="79" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -9640,14 +9752,14 @@
         <v>77</v>
       </c>
       <c r="B79" s="5" t="s">
-        <v>783</v>
+        <v>786</v>
       </c>
       <c r="C79" s="5" t="s">
-        <v>784</v>
+        <v>787</v>
       </c>
       <c r="D79" s="5"/>
       <c r="E79" s="5" t="s">
-        <v>785</v>
+        <v>788</v>
       </c>
     </row>
     <row r="80" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -9655,14 +9767,14 @@
         <v>78</v>
       </c>
       <c r="B80" s="5" t="s">
-        <v>708</v>
+        <v>711</v>
       </c>
       <c r="C80" s="5" t="s">
-        <v>786</v>
+        <v>789</v>
       </c>
       <c r="D80" s="5"/>
       <c r="E80" s="5" t="s">
-        <v>787</v>
+        <v>790</v>
       </c>
     </row>
     <row r="81" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -9670,14 +9782,14 @@
         <v>79</v>
       </c>
       <c r="B81" s="5" t="s">
-        <v>580</v>
+        <v>583</v>
       </c>
       <c r="C81" s="5" t="s">
-        <v>788</v>
+        <v>791</v>
       </c>
       <c r="D81" s="5"/>
       <c r="E81" s="5" t="s">
-        <v>789</v>
+        <v>792</v>
       </c>
     </row>
     <row r="82" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -9685,16 +9797,16 @@
         <v>80</v>
       </c>
       <c r="B82" s="5" t="s">
-        <v>790</v>
+        <v>793</v>
       </c>
       <c r="C82" s="5" t="s">
-        <v>791</v>
+        <v>794</v>
       </c>
       <c r="D82" s="6" t="s">
-        <v>792</v>
+        <v>795</v>
       </c>
       <c r="E82" s="5" t="s">
-        <v>793</v>
+        <v>796</v>
       </c>
     </row>
     <row r="83" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -9702,16 +9814,16 @@
         <v>81</v>
       </c>
       <c r="B83" s="5" t="s">
-        <v>794</v>
+        <v>797</v>
       </c>
       <c r="C83" s="5" t="s">
-        <v>795</v>
+        <v>798</v>
       </c>
       <c r="D83" s="6" t="s">
-        <v>796</v>
+        <v>799</v>
       </c>
       <c r="E83" s="5" t="s">
-        <v>797</v>
+        <v>800</v>
       </c>
     </row>
     <row r="84" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -9719,13 +9831,13 @@
         <v>82</v>
       </c>
       <c r="B84" s="5" t="s">
-        <v>798</v>
+        <v>801</v>
       </c>
       <c r="C84" s="5" t="s">
-        <v>799</v>
+        <v>802</v>
       </c>
       <c r="D84" s="6" t="s">
-        <v>800</v>
+        <v>803</v>
       </c>
       <c r="E84" s="5" t="s">
         <v>297</v>
@@ -9736,13 +9848,13 @@
         <v>83</v>
       </c>
       <c r="B85" s="5" t="s">
-        <v>801</v>
+        <v>804</v>
       </c>
       <c r="C85" s="5" t="s">
-        <v>802</v>
+        <v>805</v>
       </c>
       <c r="D85" s="6" t="s">
-        <v>803</v>
+        <v>806</v>
       </c>
       <c r="E85" s="5" t="s">
         <v>300</v>
@@ -9753,16 +9865,16 @@
         <v>84</v>
       </c>
       <c r="B86" s="5" t="s">
-        <v>804</v>
+        <v>807</v>
       </c>
       <c r="C86" s="5" t="s">
-        <v>805</v>
+        <v>808</v>
       </c>
       <c r="D86" s="6" t="s">
-        <v>806</v>
+        <v>809</v>
       </c>
       <c r="E86" s="5" t="s">
-        <v>807</v>
+        <v>810</v>
       </c>
     </row>
     <row r="87" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -9770,16 +9882,16 @@
         <v>85</v>
       </c>
       <c r="B87" s="5" t="s">
-        <v>808</v>
+        <v>811</v>
       </c>
       <c r="C87" s="5" t="s">
-        <v>809</v>
+        <v>812</v>
       </c>
       <c r="D87" s="6" t="s">
-        <v>810</v>
+        <v>813</v>
       </c>
       <c r="E87" s="5" t="s">
-        <v>811</v>
+        <v>814</v>
       </c>
     </row>
     <row r="88" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -9787,16 +9899,16 @@
         <v>86</v>
       </c>
       <c r="B88" s="5" t="s">
-        <v>812</v>
+        <v>815</v>
       </c>
       <c r="C88" s="5" t="s">
-        <v>813</v>
+        <v>816</v>
       </c>
       <c r="D88" s="6" t="s">
+        <v>817</v>
+      </c>
+      <c r="E88" s="5" t="s">
         <v>814</v>
-      </c>
-      <c r="E88" s="5" t="s">
-        <v>811</v>
       </c>
     </row>
     <row r="89" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -9804,16 +9916,16 @@
         <v>87</v>
       </c>
       <c r="B89" s="5" t="s">
-        <v>815</v>
+        <v>818</v>
       </c>
       <c r="C89" s="5" t="s">
-        <v>816</v>
+        <v>819</v>
       </c>
       <c r="D89" s="6" t="s">
-        <v>817</v>
+        <v>820</v>
       </c>
       <c r="E89" s="5" t="s">
-        <v>811</v>
+        <v>814</v>
       </c>
     </row>
     <row r="90" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -9821,16 +9933,16 @@
         <v>88</v>
       </c>
       <c r="B90" s="5" t="s">
-        <v>818</v>
+        <v>821</v>
       </c>
       <c r="C90" s="5" t="s">
-        <v>819</v>
+        <v>822</v>
       </c>
       <c r="D90" s="6" t="s">
-        <v>820</v>
+        <v>823</v>
       </c>
       <c r="E90" s="5" t="s">
-        <v>821</v>
+        <v>824</v>
       </c>
     </row>
     <row r="91" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -9838,16 +9950,16 @@
         <v>89</v>
       </c>
       <c r="B91" s="5" t="s">
-        <v>822</v>
+        <v>825</v>
       </c>
       <c r="C91" s="5" t="s">
-        <v>823</v>
+        <v>826</v>
       </c>
       <c r="D91" s="6" t="s">
+        <v>827</v>
+      </c>
+      <c r="E91" s="5" t="s">
         <v>824</v>
-      </c>
-      <c r="E91" s="5" t="s">
-        <v>821</v>
       </c>
     </row>
     <row r="92" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -9855,16 +9967,16 @@
         <v>90</v>
       </c>
       <c r="B92" s="5" t="s">
-        <v>812</v>
+        <v>815</v>
       </c>
       <c r="C92" s="5" t="s">
-        <v>825</v>
+        <v>828</v>
       </c>
       <c r="D92" s="6" t="s">
-        <v>826</v>
+        <v>829</v>
       </c>
       <c r="E92" s="5" t="s">
-        <v>827</v>
+        <v>830</v>
       </c>
     </row>
     <row r="93" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -9872,16 +9984,16 @@
         <v>91</v>
       </c>
       <c r="B93" s="5" t="s">
-        <v>828</v>
+        <v>831</v>
       </c>
       <c r="C93" s="5" t="s">
-        <v>829</v>
+        <v>832</v>
       </c>
       <c r="D93" s="6" t="s">
+        <v>833</v>
+      </c>
+      <c r="E93" s="5" t="s">
         <v>830</v>
-      </c>
-      <c r="E93" s="5" t="s">
-        <v>827</v>
       </c>
     </row>
     <row r="94" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -9889,16 +10001,16 @@
         <v>92</v>
       </c>
       <c r="B94" s="5" t="s">
-        <v>831</v>
+        <v>834</v>
       </c>
       <c r="C94" s="5" t="s">
-        <v>832</v>
+        <v>835</v>
       </c>
       <c r="D94" s="6" t="s">
-        <v>833</v>
+        <v>836</v>
       </c>
       <c r="E94" s="5" t="s">
-        <v>834</v>
+        <v>837</v>
       </c>
     </row>
     <row r="95" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -9906,16 +10018,16 @@
         <v>93</v>
       </c>
       <c r="B95" s="5" t="s">
-        <v>673</v>
+        <v>676</v>
       </c>
       <c r="C95" s="5" t="s">
-        <v>835</v>
+        <v>838</v>
       </c>
       <c r="D95" s="6" t="s">
-        <v>836</v>
+        <v>839</v>
       </c>
       <c r="E95" s="5" t="s">
-        <v>837</v>
+        <v>840</v>
       </c>
     </row>
     <row r="96" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -9923,16 +10035,16 @@
         <v>94</v>
       </c>
       <c r="B96" s="5" t="s">
-        <v>818</v>
+        <v>821</v>
       </c>
       <c r="C96" s="5" t="s">
-        <v>838</v>
+        <v>841</v>
       </c>
       <c r="D96" s="6" t="s">
-        <v>839</v>
+        <v>842</v>
       </c>
       <c r="E96" s="5" t="s">
-        <v>837</v>
+        <v>840</v>
       </c>
     </row>
     <row r="97" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -9940,16 +10052,16 @@
         <v>95</v>
       </c>
       <c r="B97" s="5" t="s">
+        <v>843</v>
+      </c>
+      <c r="C97" s="5" t="s">
+        <v>844</v>
+      </c>
+      <c r="D97" s="6" t="s">
+        <v>845</v>
+      </c>
+      <c r="E97" s="5" t="s">
         <v>840</v>
-      </c>
-      <c r="C97" s="5" t="s">
-        <v>841</v>
-      </c>
-      <c r="D97" s="6" t="s">
-        <v>842</v>
-      </c>
-      <c r="E97" s="5" t="s">
-        <v>837</v>
       </c>
     </row>
     <row r="98" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -9957,16 +10069,16 @@
         <v>96</v>
       </c>
       <c r="B98" s="5" t="s">
-        <v>798</v>
+        <v>801</v>
       </c>
       <c r="C98" s="5" t="s">
-        <v>843</v>
+        <v>846</v>
       </c>
       <c r="D98" s="6" t="s">
-        <v>844</v>
+        <v>847</v>
       </c>
       <c r="E98" s="5" t="s">
-        <v>827</v>
+        <v>830</v>
       </c>
     </row>
     <row r="99" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -9974,16 +10086,16 @@
         <v>97</v>
       </c>
       <c r="B99" s="5" t="s">
-        <v>845</v>
+        <v>848</v>
       </c>
       <c r="C99" s="5" t="s">
-        <v>846</v>
+        <v>849</v>
       </c>
       <c r="D99" s="6" t="s">
-        <v>847</v>
+        <v>850</v>
       </c>
       <c r="E99" s="5" t="s">
-        <v>848</v>
+        <v>851</v>
       </c>
     </row>
     <row r="100" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -9991,16 +10103,16 @@
         <v>98</v>
       </c>
       <c r="B100" s="5" t="s">
-        <v>812</v>
+        <v>815</v>
       </c>
       <c r="C100" s="5" t="s">
-        <v>849</v>
+        <v>852</v>
       </c>
       <c r="D100" s="6" t="s">
-        <v>850</v>
+        <v>853</v>
       </c>
       <c r="E100" s="5" t="s">
-        <v>851</v>
+        <v>854</v>
       </c>
     </row>
     <row r="101" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -10008,16 +10120,16 @@
         <v>99</v>
       </c>
       <c r="B101" s="5" t="s">
-        <v>818</v>
+        <v>821</v>
       </c>
       <c r="C101" s="5" t="s">
-        <v>852</v>
+        <v>855</v>
       </c>
       <c r="D101" s="6" t="s">
-        <v>853</v>
+        <v>856</v>
       </c>
       <c r="E101" s="5" t="s">
-        <v>854</v>
+        <v>857</v>
       </c>
     </row>
     <row r="102" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -10025,16 +10137,16 @@
         <v>100</v>
       </c>
       <c r="B102" s="5" t="s">
-        <v>855</v>
+        <v>858</v>
       </c>
       <c r="C102" s="5" t="s">
-        <v>856</v>
+        <v>859</v>
       </c>
       <c r="D102" s="6" t="s">
-        <v>857</v>
+        <v>860</v>
       </c>
       <c r="E102" s="5" t="s">
-        <v>858</v>
+        <v>861</v>
       </c>
     </row>
     <row r="103" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -10042,16 +10154,16 @@
         <v>101</v>
       </c>
       <c r="B103" s="5" t="s">
-        <v>798</v>
+        <v>801</v>
       </c>
       <c r="C103" s="5" t="s">
-        <v>859</v>
+        <v>862</v>
       </c>
       <c r="D103" s="6" t="s">
-        <v>860</v>
+        <v>863</v>
       </c>
       <c r="E103" s="5" t="s">
-        <v>861</v>
+        <v>864</v>
       </c>
     </row>
     <row r="104" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -10059,13 +10171,13 @@
         <v>102</v>
       </c>
       <c r="B104" s="5" t="s">
-        <v>673</v>
+        <v>676</v>
       </c>
       <c r="C104" s="5" t="s">
-        <v>862</v>
+        <v>865</v>
       </c>
       <c r="D104" s="6" t="s">
-        <v>863</v>
+        <v>866</v>
       </c>
       <c r="E104" s="5" t="s">
         <v>352</v>
@@ -10076,16 +10188,16 @@
         <v>103</v>
       </c>
       <c r="B105" s="5" t="s">
-        <v>864</v>
+        <v>867</v>
       </c>
       <c r="C105" s="5" t="s">
-        <v>865</v>
+        <v>868</v>
       </c>
       <c r="D105" s="6" t="s">
-        <v>866</v>
+        <v>869</v>
       </c>
       <c r="E105" s="5" t="s">
-        <v>867</v>
+        <v>870</v>
       </c>
     </row>
     <row r="106" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -10093,16 +10205,16 @@
         <v>104</v>
       </c>
       <c r="B106" s="5" t="s">
-        <v>868</v>
+        <v>871</v>
       </c>
       <c r="C106" s="5" t="s">
-        <v>869</v>
+        <v>872</v>
       </c>
       <c r="D106" s="6" t="s">
-        <v>870</v>
+        <v>873</v>
       </c>
       <c r="E106" s="5" t="s">
-        <v>871</v>
+        <v>874</v>
       </c>
     </row>
     <row r="107" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -10110,16 +10222,16 @@
         <v>105</v>
       </c>
       <c r="B107" s="5" t="s">
-        <v>872</v>
+        <v>875</v>
       </c>
       <c r="C107" s="5" t="s">
-        <v>873</v>
+        <v>876</v>
       </c>
       <c r="D107" s="6" t="s">
-        <v>874</v>
+        <v>877</v>
       </c>
       <c r="E107" s="5" t="s">
-        <v>875</v>
+        <v>878</v>
       </c>
     </row>
     <row r="108" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -10127,16 +10239,16 @@
         <v>106</v>
       </c>
       <c r="B108" s="5" t="s">
-        <v>868</v>
+        <v>871</v>
       </c>
       <c r="C108" s="5" t="s">
-        <v>876</v>
+        <v>879</v>
       </c>
       <c r="D108" s="6" t="s">
-        <v>877</v>
+        <v>880</v>
       </c>
       <c r="E108" s="5" t="s">
-        <v>878</v>
+        <v>881</v>
       </c>
     </row>
     <row r="109" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -10144,13 +10256,13 @@
         <v>107</v>
       </c>
       <c r="B109" s="5" t="s">
-        <v>879</v>
+        <v>882</v>
       </c>
       <c r="C109" s="5" t="s">
-        <v>880</v>
+        <v>883</v>
       </c>
       <c r="D109" s="6" t="s">
-        <v>881</v>
+        <v>884</v>
       </c>
       <c r="E109" s="5" t="s">
         <v>368</v>
@@ -10161,13 +10273,13 @@
         <v>108</v>
       </c>
       <c r="B110" s="5" t="s">
-        <v>673</v>
+        <v>676</v>
       </c>
       <c r="C110" s="5" t="s">
-        <v>882</v>
+        <v>885</v>
       </c>
       <c r="D110" s="6" t="s">
-        <v>883</v>
+        <v>886</v>
       </c>
       <c r="E110" s="5" t="s">
         <v>368</v>
@@ -10178,16 +10290,16 @@
         <v>109</v>
       </c>
       <c r="B111" s="5" t="s">
-        <v>872</v>
+        <v>875</v>
       </c>
       <c r="C111" s="5" t="s">
-        <v>884</v>
+        <v>887</v>
       </c>
       <c r="D111" s="6" t="s">
-        <v>885</v>
+        <v>888</v>
       </c>
       <c r="E111" s="5" t="s">
-        <v>886</v>
+        <v>889</v>
       </c>
     </row>
     <row r="112" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -10195,16 +10307,16 @@
         <v>110</v>
       </c>
       <c r="B112" s="5" t="s">
-        <v>812</v>
+        <v>815</v>
       </c>
       <c r="C112" s="5" t="s">
-        <v>887</v>
+        <v>890</v>
       </c>
       <c r="D112" s="6" t="s">
-        <v>888</v>
+        <v>891</v>
       </c>
       <c r="E112" s="5" t="s">
-        <v>889</v>
+        <v>892</v>
       </c>
     </row>
     <row r="113" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -10212,13 +10324,13 @@
         <v>111</v>
       </c>
       <c r="B113" s="5" t="s">
-        <v>804</v>
+        <v>807</v>
       </c>
       <c r="C113" s="5" t="s">
-        <v>890</v>
+        <v>893</v>
       </c>
       <c r="D113" s="6" t="s">
-        <v>891</v>
+        <v>894</v>
       </c>
       <c r="E113" s="5" t="s">
         <v>382</v>
@@ -10229,16 +10341,16 @@
         <v>112</v>
       </c>
       <c r="B114" s="5" t="s">
-        <v>812</v>
+        <v>815</v>
       </c>
       <c r="C114" s="5" t="s">
-        <v>892</v>
+        <v>895</v>
       </c>
       <c r="D114" s="6" t="s">
-        <v>893</v>
+        <v>896</v>
       </c>
       <c r="E114" s="5" t="s">
-        <v>894</v>
+        <v>897</v>
       </c>
     </row>
     <row r="115" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -10246,16 +10358,16 @@
         <v>113</v>
       </c>
       <c r="B115" s="5" t="s">
-        <v>895</v>
+        <v>898</v>
       </c>
       <c r="C115" s="5" t="s">
-        <v>896</v>
+        <v>899</v>
       </c>
       <c r="D115" s="6" t="s">
-        <v>897</v>
+        <v>900</v>
       </c>
       <c r="E115" s="5" t="s">
-        <v>898</v>
+        <v>901</v>
       </c>
     </row>
     <row r="116" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -10263,16 +10375,16 @@
         <v>114</v>
       </c>
       <c r="B116" s="5" t="s">
-        <v>818</v>
+        <v>821</v>
       </c>
       <c r="C116" s="5" t="s">
-        <v>899</v>
+        <v>902</v>
       </c>
       <c r="D116" s="6" t="s">
-        <v>900</v>
+        <v>903</v>
       </c>
       <c r="E116" s="5" t="s">
-        <v>898</v>
+        <v>901</v>
       </c>
     </row>
     <row r="117" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -10280,16 +10392,16 @@
         <v>115</v>
       </c>
       <c r="B117" s="5" t="s">
-        <v>901</v>
+        <v>904</v>
       </c>
       <c r="C117" s="5" t="s">
-        <v>902</v>
+        <v>905</v>
       </c>
       <c r="D117" s="6" t="s">
-        <v>903</v>
+        <v>906</v>
       </c>
       <c r="E117" s="5" t="s">
-        <v>904</v>
+        <v>907</v>
       </c>
     </row>
     <row r="118" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -10297,13 +10409,13 @@
         <v>116</v>
       </c>
       <c r="B118" s="5" t="s">
-        <v>818</v>
+        <v>821</v>
       </c>
       <c r="C118" s="5" t="s">
-        <v>905</v>
+        <v>908</v>
       </c>
       <c r="D118" s="6" t="s">
-        <v>906</v>
+        <v>909</v>
       </c>
       <c r="E118" s="5" t="s">
         <v>396</v>
@@ -10314,16 +10426,16 @@
         <v>117</v>
       </c>
       <c r="B119" s="5" t="s">
-        <v>907</v>
+        <v>910</v>
       </c>
       <c r="C119" s="5" t="s">
-        <v>908</v>
+        <v>911</v>
       </c>
       <c r="D119" s="6" t="s">
-        <v>909</v>
+        <v>912</v>
       </c>
       <c r="E119" s="5" t="s">
-        <v>910</v>
+        <v>913</v>
       </c>
     </row>
     <row r="120" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -10331,16 +10443,16 @@
         <v>118</v>
       </c>
       <c r="B120" s="5" t="s">
-        <v>895</v>
+        <v>898</v>
       </c>
       <c r="C120" s="5" t="s">
-        <v>911</v>
+        <v>914</v>
       </c>
       <c r="D120" s="6" t="s">
-        <v>912</v>
+        <v>915</v>
       </c>
       <c r="E120" s="5" t="s">
-        <v>913</v>
+        <v>916</v>
       </c>
     </row>
     <row r="121" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -10348,16 +10460,16 @@
         <v>119</v>
       </c>
       <c r="B121" s="5" t="s">
-        <v>914</v>
+        <v>917</v>
       </c>
       <c r="C121" s="5" t="s">
-        <v>915</v>
+        <v>918</v>
       </c>
       <c r="D121" s="6" t="s">
-        <v>916</v>
+        <v>919</v>
       </c>
       <c r="E121" s="5" t="s">
-        <v>910</v>
+        <v>913</v>
       </c>
     </row>
     <row r="122" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -10365,16 +10477,16 @@
         <v>120</v>
       </c>
       <c r="B122" s="5" t="s">
-        <v>917</v>
+        <v>920</v>
       </c>
       <c r="C122" s="5" t="s">
-        <v>918</v>
+        <v>921</v>
       </c>
       <c r="D122" s="6" t="s">
-        <v>919</v>
+        <v>922</v>
       </c>
       <c r="E122" s="5" t="s">
-        <v>920</v>
+        <v>923</v>
       </c>
     </row>
     <row r="123" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -10382,13 +10494,13 @@
         <v>121</v>
       </c>
       <c r="B123" s="5" t="s">
-        <v>818</v>
+        <v>821</v>
       </c>
       <c r="C123" s="5" t="s">
-        <v>921</v>
+        <v>924</v>
       </c>
       <c r="D123" s="6" t="s">
-        <v>922</v>
+        <v>925</v>
       </c>
       <c r="E123" s="5" t="s">
         <v>409</v>
@@ -10399,13 +10511,13 @@
         <v>122</v>
       </c>
       <c r="B124" s="5" t="s">
-        <v>879</v>
+        <v>882</v>
       </c>
       <c r="C124" s="5" t="s">
-        <v>923</v>
+        <v>926</v>
       </c>
       <c r="D124" s="6" t="s">
-        <v>924</v>
+        <v>927</v>
       </c>
       <c r="E124" s="5" t="s">
         <v>409</v>
@@ -10416,16 +10528,16 @@
         <v>123</v>
       </c>
       <c r="B125" s="5" t="s">
-        <v>845</v>
+        <v>848</v>
       </c>
       <c r="C125" s="5" t="s">
-        <v>925</v>
+        <v>928</v>
       </c>
       <c r="D125" s="6" t="s">
-        <v>926</v>
+        <v>929</v>
       </c>
       <c r="E125" s="5" t="s">
-        <v>927</v>
+        <v>930</v>
       </c>
     </row>
     <row r="126" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -10433,16 +10545,16 @@
         <v>124</v>
       </c>
       <c r="B126" s="5" t="s">
-        <v>928</v>
+        <v>931</v>
       </c>
       <c r="C126" s="5" t="s">
-        <v>929</v>
+        <v>932</v>
       </c>
       <c r="D126" s="6" t="s">
+        <v>933</v>
+      </c>
+      <c r="E126" s="5" t="s">
         <v>930</v>
-      </c>
-      <c r="E126" s="5" t="s">
-        <v>927</v>
       </c>
     </row>
     <row r="127" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -10450,16 +10562,16 @@
         <v>125</v>
       </c>
       <c r="B127" s="5" t="s">
-        <v>864</v>
+        <v>867</v>
       </c>
       <c r="C127" s="5" t="s">
-        <v>931</v>
+        <v>934</v>
       </c>
       <c r="D127" s="6" t="s">
-        <v>932</v>
+        <v>935</v>
       </c>
       <c r="E127" s="5" t="s">
-        <v>933</v>
+        <v>936</v>
       </c>
     </row>
     <row r="128" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -10467,16 +10579,16 @@
         <v>126</v>
       </c>
       <c r="B128" s="5" t="s">
-        <v>934</v>
+        <v>937</v>
       </c>
       <c r="C128" s="5" t="s">
-        <v>935</v>
+        <v>938</v>
       </c>
       <c r="D128" s="6" t="s">
-        <v>936</v>
+        <v>939</v>
       </c>
       <c r="E128" s="5" t="s">
-        <v>937</v>
+        <v>940</v>
       </c>
     </row>
     <row r="129" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -10484,16 +10596,16 @@
         <v>127</v>
       </c>
       <c r="B129" s="5" t="s">
-        <v>938</v>
+        <v>941</v>
       </c>
       <c r="C129" s="5" t="s">
-        <v>939</v>
+        <v>942</v>
       </c>
       <c r="D129" s="6" t="s">
-        <v>940</v>
+        <v>943</v>
       </c>
       <c r="E129" s="5" t="s">
-        <v>941</v>
+        <v>944</v>
       </c>
     </row>
     <row r="130" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -10501,16 +10613,16 @@
         <v>128</v>
       </c>
       <c r="B130" s="5" t="s">
-        <v>942</v>
+        <v>945</v>
       </c>
       <c r="C130" s="5" t="s">
+        <v>946</v>
+      </c>
+      <c r="D130" s="6" t="s">
         <v>943</v>
       </c>
-      <c r="D130" s="6" t="s">
-        <v>940</v>
-      </c>
       <c r="E130" s="5" t="s">
-        <v>944</v>
+        <v>947</v>
       </c>
     </row>
     <row r="131" customFormat="false" ht="34.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -10518,13 +10630,13 @@
         <v>129</v>
       </c>
       <c r="B131" s="5" t="s">
-        <v>945</v>
+        <v>948</v>
       </c>
       <c r="C131" s="5" t="s">
-        <v>946</v>
+        <v>949</v>
       </c>
       <c r="D131" s="6" t="s">
-        <v>940</v>
+        <v>943</v>
       </c>
       <c r="E131" s="5" t="s">
         <v>434</v>
@@ -10535,16 +10647,16 @@
         <v>130</v>
       </c>
       <c r="B132" s="5" t="s">
-        <v>947</v>
+        <v>950</v>
       </c>
       <c r="C132" s="5" t="s">
-        <v>948</v>
+        <v>951</v>
       </c>
       <c r="D132" s="6" t="s">
-        <v>949</v>
+        <v>952</v>
       </c>
       <c r="E132" s="5" t="s">
-        <v>950</v>
+        <v>953</v>
       </c>
     </row>
     <row r="133" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -10552,16 +10664,16 @@
         <v>131</v>
       </c>
       <c r="B133" s="5" t="s">
-        <v>951</v>
+        <v>954</v>
       </c>
       <c r="C133" s="5" t="s">
-        <v>952</v>
+        <v>955</v>
       </c>
       <c r="D133" s="6" t="s">
+        <v>956</v>
+      </c>
+      <c r="E133" s="5" t="s">
         <v>953</v>
-      </c>
-      <c r="E133" s="5" t="s">
-        <v>950</v>
       </c>
     </row>
     <row r="134" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -10569,16 +10681,16 @@
         <v>132</v>
       </c>
       <c r="B134" s="5" t="s">
-        <v>954</v>
+        <v>957</v>
       </c>
       <c r="C134" s="5" t="s">
-        <v>955</v>
+        <v>958</v>
       </c>
       <c r="D134" s="6" t="s">
-        <v>956</v>
+        <v>959</v>
       </c>
       <c r="E134" s="5" t="s">
-        <v>957</v>
+        <v>960</v>
       </c>
     </row>
     <row r="135" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -10586,16 +10698,16 @@
         <v>133</v>
       </c>
       <c r="B135" s="5" t="s">
-        <v>958</v>
+        <v>961</v>
       </c>
       <c r="C135" s="5" t="s">
-        <v>959</v>
+        <v>962</v>
       </c>
       <c r="D135" s="6" t="s">
-        <v>960</v>
+        <v>963</v>
       </c>
       <c r="E135" s="5" t="s">
-        <v>961</v>
+        <v>964</v>
       </c>
     </row>
     <row r="136" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -10603,13 +10715,13 @@
         <v>134</v>
       </c>
       <c r="B136" s="5" t="s">
-        <v>673</v>
+        <v>676</v>
       </c>
       <c r="C136" s="5" t="s">
-        <v>962</v>
+        <v>965</v>
       </c>
       <c r="D136" s="6" t="s">
-        <v>963</v>
+        <v>966</v>
       </c>
       <c r="E136" s="5" t="s">
         <v>451</v>
@@ -10620,13 +10732,13 @@
         <v>135</v>
       </c>
       <c r="B137" s="5" t="s">
-        <v>964</v>
+        <v>967</v>
       </c>
       <c r="C137" s="5" t="s">
-        <v>965</v>
+        <v>968</v>
       </c>
       <c r="D137" s="6" t="s">
-        <v>966</v>
+        <v>969</v>
       </c>
       <c r="E137" s="5" t="s">
         <v>451</v>
@@ -10637,16 +10749,16 @@
         <v>136</v>
       </c>
       <c r="B138" s="5" t="s">
-        <v>967</v>
+        <v>970</v>
       </c>
       <c r="C138" s="5" t="s">
-        <v>968</v>
+        <v>971</v>
       </c>
       <c r="D138" s="6" t="s">
-        <v>969</v>
+        <v>972</v>
       </c>
       <c r="E138" s="5" t="s">
-        <v>970</v>
+        <v>973</v>
       </c>
     </row>
     <row r="139" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -10654,16 +10766,16 @@
         <v>137</v>
       </c>
       <c r="B139" s="5" t="s">
-        <v>971</v>
+        <v>974</v>
       </c>
       <c r="C139" s="5" t="s">
-        <v>972</v>
+        <v>975</v>
       </c>
       <c r="D139" s="6" t="s">
-        <v>973</v>
+        <v>976</v>
       </c>
       <c r="E139" s="5" t="s">
-        <v>974</v>
+        <v>977</v>
       </c>
     </row>
     <row r="140" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -10671,13 +10783,13 @@
         <v>138</v>
       </c>
       <c r="B140" s="5" t="s">
-        <v>840</v>
+        <v>843</v>
       </c>
       <c r="C140" s="5" t="s">
-        <v>975</v>
+        <v>978</v>
       </c>
       <c r="D140" s="6" t="s">
-        <v>976</v>
+        <v>979</v>
       </c>
       <c r="E140" s="5" t="s">
         <v>463</v>
@@ -10688,16 +10800,16 @@
         <v>139</v>
       </c>
       <c r="B141" s="5" t="s">
-        <v>845</v>
+        <v>848</v>
       </c>
       <c r="C141" s="5" t="s">
-        <v>977</v>
+        <v>980</v>
       </c>
       <c r="D141" s="6" t="s">
-        <v>978</v>
+        <v>981</v>
       </c>
       <c r="E141" s="5" t="s">
-        <v>979</v>
+        <v>982</v>
       </c>
     </row>
     <row r="142" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -10705,16 +10817,16 @@
         <v>140</v>
       </c>
       <c r="B142" s="5" t="s">
-        <v>980</v>
+        <v>983</v>
       </c>
       <c r="C142" s="5" t="s">
-        <v>981</v>
+        <v>984</v>
       </c>
       <c r="D142" s="6" t="s">
-        <v>982</v>
+        <v>985</v>
       </c>
       <c r="E142" s="5" t="s">
-        <v>983</v>
+        <v>986</v>
       </c>
     </row>
     <row r="143" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -10722,13 +10834,13 @@
         <v>141</v>
       </c>
       <c r="B143" s="5" t="s">
-        <v>812</v>
+        <v>815</v>
       </c>
       <c r="C143" s="5" t="s">
-        <v>984</v>
+        <v>987</v>
       </c>
       <c r="D143" s="6" t="s">
-        <v>985</v>
+        <v>988</v>
       </c>
       <c r="E143" s="5" t="s">
         <v>472</v>
@@ -10739,16 +10851,16 @@
         <v>142</v>
       </c>
       <c r="B144" s="5" t="s">
-        <v>986</v>
+        <v>989</v>
       </c>
       <c r="C144" s="5" t="s">
-        <v>987</v>
+        <v>990</v>
       </c>
       <c r="D144" s="6" t="s">
-        <v>988</v>
+        <v>991</v>
       </c>
       <c r="E144" s="5" t="s">
-        <v>989</v>
+        <v>992</v>
       </c>
     </row>
     <row r="145" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -10756,13 +10868,13 @@
         <v>143</v>
       </c>
       <c r="B145" s="5" t="s">
-        <v>872</v>
+        <v>875</v>
       </c>
       <c r="C145" s="5" t="s">
-        <v>990</v>
+        <v>993</v>
       </c>
       <c r="D145" s="6" t="s">
-        <v>991</v>
+        <v>994</v>
       </c>
       <c r="E145" s="5" t="s">
         <v>479</v>
@@ -10773,16 +10885,16 @@
         <v>144</v>
       </c>
       <c r="B146" s="5" t="s">
-        <v>812</v>
+        <v>815</v>
       </c>
       <c r="C146" s="5" t="s">
-        <v>992</v>
+        <v>995</v>
       </c>
       <c r="D146" s="6" t="s">
-        <v>993</v>
+        <v>996</v>
       </c>
       <c r="E146" s="5" t="s">
-        <v>994</v>
+        <v>997</v>
       </c>
     </row>
     <row r="147" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -10790,16 +10902,16 @@
         <v>145</v>
       </c>
       <c r="B147" s="5" t="s">
-        <v>995</v>
+        <v>998</v>
       </c>
       <c r="C147" s="5" t="s">
-        <v>996</v>
+        <v>999</v>
       </c>
       <c r="D147" s="6" t="s">
-        <v>997</v>
+        <v>1000</v>
       </c>
       <c r="E147" s="5" t="s">
-        <v>998</v>
+        <v>1001</v>
       </c>
     </row>
     <row r="148" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -10807,16 +10919,16 @@
         <v>146</v>
       </c>
       <c r="B148" s="5" t="s">
-        <v>999</v>
+        <v>1002</v>
       </c>
       <c r="C148" s="5" t="s">
-        <v>1000</v>
+        <v>1003</v>
       </c>
       <c r="D148" s="6" t="s">
-        <v>1001</v>
+        <v>1004</v>
       </c>
       <c r="E148" s="5" t="s">
-        <v>1002</v>
+        <v>1005</v>
       </c>
     </row>
     <row r="149" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -10824,13 +10936,13 @@
         <v>147</v>
       </c>
       <c r="B149" s="5" t="s">
-        <v>1003</v>
+        <v>1006</v>
       </c>
       <c r="C149" s="5" t="s">
-        <v>1004</v>
+        <v>1007</v>
       </c>
       <c r="D149" s="6" t="s">
-        <v>936</v>
+        <v>939</v>
       </c>
       <c r="E149" s="5" t="s">
         <v>492</v>
@@ -10841,13 +10953,13 @@
         <v>148</v>
       </c>
       <c r="B150" s="5" t="s">
-        <v>1005</v>
+        <v>1008</v>
       </c>
       <c r="C150" s="5" t="s">
-        <v>1006</v>
+        <v>1009</v>
       </c>
       <c r="D150" s="6" t="s">
-        <v>940</v>
+        <v>943</v>
       </c>
       <c r="E150" s="5" t="s">
         <v>492</v>
@@ -10858,16 +10970,16 @@
         <v>149</v>
       </c>
       <c r="B151" s="5" t="s">
-        <v>1007</v>
+        <v>1010</v>
       </c>
       <c r="C151" s="5" t="s">
-        <v>1008</v>
+        <v>1011</v>
       </c>
       <c r="D151" s="6" t="s">
-        <v>1009</v>
+        <v>1012</v>
       </c>
       <c r="E151" s="5" t="s">
-        <v>1010</v>
+        <v>1013</v>
       </c>
     </row>
     <row r="152" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -10875,16 +10987,16 @@
         <v>150</v>
       </c>
       <c r="B152" s="5" t="s">
-        <v>1007</v>
+        <v>1010</v>
       </c>
       <c r="C152" s="5" t="s">
-        <v>1011</v>
+        <v>1014</v>
       </c>
       <c r="D152" s="6" t="s">
-        <v>1009</v>
+        <v>1012</v>
       </c>
       <c r="E152" s="5" t="s">
-        <v>1010</v>
+        <v>1013</v>
       </c>
     </row>
     <row r="153" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -10892,16 +11004,16 @@
         <v>151</v>
       </c>
       <c r="B153" s="5" t="s">
-        <v>1012</v>
+        <v>1015</v>
       </c>
       <c r="C153" s="5" t="s">
-        <v>1013</v>
+        <v>1016</v>
       </c>
       <c r="D153" s="6" t="s">
-        <v>1014</v>
+        <v>1017</v>
       </c>
       <c r="E153" s="5" t="s">
-        <v>1015</v>
+        <v>1018</v>
       </c>
     </row>
     <row r="154" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -10909,16 +11021,16 @@
         <v>152</v>
       </c>
       <c r="B154" s="5" t="s">
-        <v>1012</v>
+        <v>1015</v>
       </c>
       <c r="C154" s="5" t="s">
-        <v>1016</v>
+        <v>1019</v>
       </c>
       <c r="D154" s="6" t="s">
-        <v>1014</v>
+        <v>1017</v>
       </c>
       <c r="E154" s="5" t="s">
-        <v>1015</v>
+        <v>1018</v>
       </c>
     </row>
     <row r="155" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -10926,16 +11038,16 @@
         <v>153</v>
       </c>
       <c r="B155" s="5" t="s">
-        <v>1017</v>
+        <v>1020</v>
       </c>
       <c r="C155" s="5" t="s">
-        <v>1018</v>
+        <v>1021</v>
       </c>
       <c r="D155" s="6" t="s">
-        <v>1019</v>
+        <v>1022</v>
       </c>
       <c r="E155" s="5" t="s">
-        <v>1020</v>
+        <v>1023</v>
       </c>
     </row>
     <row r="156" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -10943,16 +11055,16 @@
         <v>154</v>
       </c>
       <c r="B156" s="5" t="s">
-        <v>845</v>
+        <v>848</v>
       </c>
       <c r="C156" s="5" t="s">
-        <v>1021</v>
+        <v>1024</v>
       </c>
       <c r="D156" s="6" t="s">
-        <v>1022</v>
+        <v>1025</v>
       </c>
       <c r="E156" s="5" t="s">
-        <v>1020</v>
+        <v>1023</v>
       </c>
     </row>
     <row r="157" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -10960,14 +11072,14 @@
         <v>155</v>
       </c>
       <c r="B157" s="5" t="s">
-        <v>1023</v>
+        <v>1026</v>
       </c>
       <c r="C157" s="5" t="s">
-        <v>1024</v>
+        <v>1027</v>
       </c>
       <c r="D157" s="5"/>
       <c r="E157" s="5" t="s">
-        <v>1025</v>
+        <v>1028</v>
       </c>
     </row>
     <row r="158" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -10975,16 +11087,16 @@
         <v>156</v>
       </c>
       <c r="B158" s="5" t="s">
-        <v>1026</v>
+        <v>1029</v>
       </c>
       <c r="C158" s="5" t="s">
-        <v>1027</v>
+        <v>1030</v>
       </c>
       <c r="D158" s="6" t="s">
+        <v>1031</v>
+      </c>
+      <c r="E158" s="5" t="s">
         <v>1028</v>
-      </c>
-      <c r="E158" s="5" t="s">
-        <v>1025</v>
       </c>
     </row>
     <row r="159" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -10992,16 +11104,16 @@
         <v>157</v>
       </c>
       <c r="B159" s="5" t="s">
-        <v>673</v>
+        <v>676</v>
       </c>
       <c r="C159" s="5" t="s">
-        <v>1029</v>
+        <v>1032</v>
       </c>
       <c r="D159" s="6" t="s">
-        <v>1030</v>
+        <v>1033</v>
       </c>
       <c r="E159" s="5" t="s">
-        <v>1031</v>
+        <v>1034</v>
       </c>
     </row>
     <row r="160" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -11009,16 +11121,16 @@
         <v>158</v>
       </c>
       <c r="B160" s="5" t="s">
-        <v>812</v>
+        <v>815</v>
       </c>
       <c r="C160" s="5" t="s">
-        <v>1032</v>
+        <v>1035</v>
       </c>
       <c r="D160" s="6" t="s">
-        <v>1033</v>
+        <v>1036</v>
       </c>
       <c r="E160" s="5" t="s">
-        <v>1031</v>
+        <v>1034</v>
       </c>
     </row>
     <row r="161" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -11026,16 +11138,16 @@
         <v>159</v>
       </c>
       <c r="B161" s="5" t="s">
-        <v>868</v>
+        <v>871</v>
       </c>
       <c r="C161" s="5" t="s">
+        <v>1037</v>
+      </c>
+      <c r="D161" s="6" t="s">
+        <v>1038</v>
+      </c>
+      <c r="E161" s="5" t="s">
         <v>1034</v>
-      </c>
-      <c r="D161" s="6" t="s">
-        <v>1035</v>
-      </c>
-      <c r="E161" s="5" t="s">
-        <v>1031</v>
       </c>
     </row>
     <row r="162" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -11043,16 +11155,16 @@
         <v>160</v>
       </c>
       <c r="B162" s="5" t="s">
-        <v>1036</v>
+        <v>1039</v>
       </c>
       <c r="C162" s="5" t="s">
-        <v>1037</v>
+        <v>1040</v>
       </c>
       <c r="D162" s="6" t="s">
-        <v>1038</v>
+        <v>1041</v>
       </c>
       <c r="E162" s="5" t="s">
-        <v>1031</v>
+        <v>1034</v>
       </c>
     </row>
     <row r="163" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -11060,16 +11172,16 @@
         <v>161</v>
       </c>
       <c r="B163" s="5" t="s">
-        <v>1036</v>
+        <v>1039</v>
       </c>
       <c r="C163" s="5" t="s">
-        <v>1039</v>
+        <v>1042</v>
       </c>
       <c r="D163" s="6" t="s">
-        <v>1040</v>
+        <v>1043</v>
       </c>
       <c r="E163" s="5" t="s">
-        <v>1031</v>
+        <v>1034</v>
       </c>
     </row>
     <row r="164" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -11077,16 +11189,16 @@
         <v>162</v>
       </c>
       <c r="B164" s="5" t="s">
-        <v>879</v>
+        <v>882</v>
       </c>
       <c r="C164" s="5" t="s">
-        <v>1041</v>
+        <v>1044</v>
       </c>
       <c r="D164" s="6" t="s">
-        <v>1042</v>
+        <v>1045</v>
       </c>
       <c r="E164" s="5" t="s">
-        <v>1043</v>
+        <v>1046</v>
       </c>
     </row>
     <row r="165" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -11094,16 +11206,16 @@
         <v>163</v>
       </c>
       <c r="B165" s="5" t="s">
-        <v>673</v>
+        <v>676</v>
       </c>
       <c r="C165" s="5" t="s">
-        <v>1044</v>
+        <v>1047</v>
       </c>
       <c r="D165" s="6" t="s">
-        <v>1045</v>
+        <v>1048</v>
       </c>
       <c r="E165" s="5" t="s">
-        <v>1043</v>
+        <v>1046</v>
       </c>
     </row>
     <row r="166" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -11111,13 +11223,13 @@
         <v>157</v>
       </c>
       <c r="B166" s="5" t="s">
-        <v>1036</v>
+        <v>1039</v>
       </c>
       <c r="C166" s="5" t="s">
-        <v>1046</v>
+        <v>1049</v>
       </c>
       <c r="D166" s="6" t="s">
-        <v>1047</v>
+        <v>1050</v>
       </c>
       <c r="E166" s="5" t="s">
         <v>521</v>
@@ -11128,16 +11240,16 @@
         <v>158</v>
       </c>
       <c r="B167" s="5" t="s">
-        <v>895</v>
+        <v>898</v>
       </c>
       <c r="C167" s="5" t="s">
-        <v>1048</v>
+        <v>1051</v>
       </c>
       <c r="D167" s="6" t="s">
-        <v>1049</v>
+        <v>1052</v>
       </c>
       <c r="E167" s="5" t="s">
-        <v>1050</v>
+        <v>1053</v>
       </c>
     </row>
     <row r="168" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -11145,13 +11257,13 @@
         <v>159</v>
       </c>
       <c r="B168" s="5" t="s">
-        <v>673</v>
+        <v>676</v>
       </c>
       <c r="C168" s="5" t="s">
-        <v>1051</v>
+        <v>1054</v>
       </c>
       <c r="D168" s="6" t="s">
-        <v>1052</v>
+        <v>1055</v>
       </c>
       <c r="E168" s="5" t="s">
         <v>524</v>
@@ -11162,16 +11274,16 @@
         <v>160</v>
       </c>
       <c r="B169" s="5" t="s">
-        <v>868</v>
+        <v>871</v>
       </c>
       <c r="C169" s="5" t="s">
-        <v>1053</v>
+        <v>1056</v>
       </c>
       <c r="D169" s="6" t="s">
-        <v>1054</v>
+        <v>1057</v>
       </c>
       <c r="E169" s="5" t="s">
-        <v>1055</v>
+        <v>1058</v>
       </c>
     </row>
     <row r="170" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -11179,16 +11291,16 @@
         <v>161</v>
       </c>
       <c r="B170" s="5" t="s">
-        <v>868</v>
+        <v>871</v>
       </c>
       <c r="C170" s="5" t="s">
-        <v>1056</v>
+        <v>1059</v>
       </c>
       <c r="D170" s="6" t="s">
-        <v>1057</v>
+        <v>1060</v>
       </c>
       <c r="E170" s="5" t="s">
-        <v>1055</v>
+        <v>1058</v>
       </c>
     </row>
     <row r="171" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -11196,16 +11308,16 @@
         <v>162</v>
       </c>
       <c r="B171" s="5" t="s">
-        <v>868</v>
+        <v>871</v>
       </c>
       <c r="C171" s="5" t="s">
+        <v>1061</v>
+      </c>
+      <c r="D171" s="6" t="s">
+        <v>1062</v>
+      </c>
+      <c r="E171" s="5" t="s">
         <v>1058</v>
-      </c>
-      <c r="D171" s="6" t="s">
-        <v>1059</v>
-      </c>
-      <c r="E171" s="5" t="s">
-        <v>1055</v>
       </c>
     </row>
     <row r="172" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -11213,16 +11325,16 @@
         <v>163</v>
       </c>
       <c r="B172" s="5" t="s">
-        <v>818</v>
+        <v>821</v>
       </c>
       <c r="C172" s="5" t="s">
-        <v>1060</v>
+        <v>1063</v>
       </c>
       <c r="D172" s="6" t="s">
-        <v>1061</v>
+        <v>1064</v>
       </c>
       <c r="E172" s="5" t="s">
-        <v>1062</v>
+        <v>1065</v>
       </c>
     </row>
     <row r="173" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -11230,16 +11342,16 @@
         <v>164</v>
       </c>
       <c r="B173" s="5" t="s">
-        <v>812</v>
+        <v>815</v>
       </c>
       <c r="C173" s="5" t="s">
-        <v>1063</v>
+        <v>1066</v>
       </c>
       <c r="D173" s="6" t="s">
-        <v>1064</v>
+        <v>1067</v>
       </c>
       <c r="E173" s="5" t="s">
-        <v>1065</v>
+        <v>1068</v>
       </c>
     </row>
     <row r="174" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -11247,16 +11359,16 @@
         <v>165</v>
       </c>
       <c r="B174" s="5" t="s">
-        <v>812</v>
+        <v>815</v>
       </c>
       <c r="C174" s="5" t="s">
-        <v>1066</v>
+        <v>1069</v>
       </c>
       <c r="D174" s="6" t="s">
-        <v>1067</v>
+        <v>1070</v>
       </c>
       <c r="E174" s="5" t="s">
-        <v>1065</v>
+        <v>1068</v>
       </c>
     </row>
     <row r="175" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -11264,16 +11376,16 @@
         <v>166</v>
       </c>
       <c r="B175" s="5" t="s">
-        <v>812</v>
+        <v>815</v>
       </c>
       <c r="C175" s="5" t="s">
+        <v>1071</v>
+      </c>
+      <c r="D175" s="6" t="s">
+        <v>1072</v>
+      </c>
+      <c r="E175" s="5" t="s">
         <v>1068</v>
-      </c>
-      <c r="D175" s="6" t="s">
-        <v>1069</v>
-      </c>
-      <c r="E175" s="5" t="s">
-        <v>1065</v>
       </c>
     </row>
     <row r="176" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -11281,16 +11393,16 @@
         <v>167</v>
       </c>
       <c r="B176" s="5" t="s">
-        <v>879</v>
+        <v>882</v>
       </c>
       <c r="C176" s="5" t="s">
-        <v>1070</v>
+        <v>1073</v>
       </c>
       <c r="D176" s="6" t="s">
-        <v>1071</v>
+        <v>1074</v>
       </c>
       <c r="E176" s="5" t="s">
-        <v>1072</v>
+        <v>1075</v>
       </c>
     </row>
     <row r="177" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -11298,16 +11410,16 @@
         <v>168</v>
       </c>
       <c r="B177" s="5" t="s">
-        <v>673</v>
+        <v>676</v>
       </c>
       <c r="C177" s="5" t="s">
-        <v>1073</v>
+        <v>1076</v>
       </c>
       <c r="D177" s="6" t="s">
-        <v>1074</v>
+        <v>1077</v>
       </c>
       <c r="E177" s="5" t="s">
-        <v>1072</v>
+        <v>1075</v>
       </c>
     </row>
     <row r="178" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -11315,16 +11427,16 @@
         <v>169</v>
       </c>
       <c r="B178" s="5" t="s">
-        <v>673</v>
+        <v>676</v>
       </c>
       <c r="C178" s="5" t="s">
+        <v>1078</v>
+      </c>
+      <c r="D178" s="6" t="s">
+        <v>1079</v>
+      </c>
+      <c r="E178" s="5" t="s">
         <v>1075</v>
-      </c>
-      <c r="D178" s="6" t="s">
-        <v>1076</v>
-      </c>
-      <c r="E178" s="5" t="s">
-        <v>1072</v>
       </c>
     </row>
     <row r="179" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -11332,16 +11444,16 @@
         <v>170</v>
       </c>
       <c r="B179" s="5" t="s">
-        <v>895</v>
+        <v>898</v>
       </c>
       <c r="C179" s="5" t="s">
-        <v>1077</v>
+        <v>1080</v>
       </c>
       <c r="D179" s="6" t="s">
-        <v>1078</v>
+        <v>1081</v>
       </c>
       <c r="E179" s="5" t="s">
-        <v>1072</v>
+        <v>1075</v>
       </c>
     </row>
     <row r="180" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -11349,16 +11461,16 @@
         <v>171</v>
       </c>
       <c r="B180" s="5" t="s">
-        <v>895</v>
+        <v>898</v>
       </c>
       <c r="C180" s="5" t="s">
-        <v>1079</v>
+        <v>1082</v>
       </c>
       <c r="D180" s="6" t="s">
-        <v>1080</v>
+        <v>1083</v>
       </c>
       <c r="E180" s="5" t="s">
-        <v>1072</v>
+        <v>1075</v>
       </c>
     </row>
     <row r="181" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -11366,16 +11478,16 @@
         <v>172</v>
       </c>
       <c r="B181" s="5" t="s">
-        <v>868</v>
+        <v>871</v>
       </c>
       <c r="C181" s="5" t="s">
-        <v>1081</v>
+        <v>1084</v>
       </c>
       <c r="D181" s="6" t="s">
-        <v>1082</v>
+        <v>1085</v>
       </c>
       <c r="E181" s="5" t="s">
-        <v>1083</v>
+        <v>1086</v>
       </c>
     </row>
     <row r="182" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -11383,16 +11495,16 @@
         <v>173</v>
       </c>
       <c r="B182" s="5" t="s">
-        <v>673</v>
+        <v>676</v>
       </c>
       <c r="C182" s="5" t="s">
-        <v>1084</v>
+        <v>1087</v>
       </c>
       <c r="D182" s="6" t="s">
-        <v>1085</v>
+        <v>1088</v>
       </c>
       <c r="E182" s="5" t="s">
-        <v>1086</v>
+        <v>1089</v>
       </c>
     </row>
     <row r="183" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -11400,16 +11512,16 @@
         <v>174</v>
       </c>
       <c r="B183" s="5" t="s">
-        <v>673</v>
+        <v>676</v>
       </c>
       <c r="C183" s="5" t="s">
-        <v>1087</v>
+        <v>1090</v>
       </c>
       <c r="D183" s="6" t="s">
-        <v>1088</v>
+        <v>1091</v>
       </c>
       <c r="E183" s="5" t="s">
-        <v>1086</v>
+        <v>1089</v>
       </c>
     </row>
     <row r="184" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -11417,16 +11529,16 @@
         <v>175</v>
       </c>
       <c r="B184" s="5" t="s">
-        <v>673</v>
+        <v>676</v>
       </c>
       <c r="C184" s="5" t="s">
+        <v>1092</v>
+      </c>
+      <c r="D184" s="6" t="s">
+        <v>1093</v>
+      </c>
+      <c r="E184" s="5" t="s">
         <v>1089</v>
-      </c>
-      <c r="D184" s="6" t="s">
-        <v>1090</v>
-      </c>
-      <c r="E184" s="5" t="s">
-        <v>1086</v>
       </c>
     </row>
     <row r="185" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -11434,16 +11546,16 @@
         <v>176</v>
       </c>
       <c r="B185" s="5" t="s">
-        <v>1036</v>
+        <v>1039</v>
       </c>
       <c r="C185" s="5" t="s">
-        <v>1091</v>
+        <v>1094</v>
       </c>
       <c r="D185" s="6" t="s">
-        <v>1092</v>
+        <v>1095</v>
       </c>
       <c r="E185" s="5" t="s">
-        <v>1086</v>
+        <v>1089</v>
       </c>
     </row>
     <row r="186" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -11451,16 +11563,16 @@
         <v>177</v>
       </c>
       <c r="B186" s="5" t="s">
-        <v>1036</v>
+        <v>1039</v>
       </c>
       <c r="C186" s="5" t="s">
-        <v>1093</v>
+        <v>1096</v>
       </c>
       <c r="D186" s="6" t="s">
-        <v>1094</v>
+        <v>1097</v>
       </c>
       <c r="E186" s="5" t="s">
-        <v>1086</v>
+        <v>1089</v>
       </c>
     </row>
     <row r="187" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -11468,16 +11580,16 @@
         <v>178</v>
       </c>
       <c r="B187" s="5" t="s">
-        <v>1036</v>
+        <v>1039</v>
       </c>
       <c r="C187" s="5" t="s">
-        <v>1095</v>
+        <v>1098</v>
       </c>
       <c r="D187" s="6" t="s">
-        <v>1096</v>
+        <v>1099</v>
       </c>
       <c r="E187" s="5" t="s">
-        <v>1086</v>
+        <v>1089</v>
       </c>
     </row>
     <row r="188" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -11485,16 +11597,16 @@
         <v>179</v>
       </c>
       <c r="B188" s="5" t="s">
-        <v>673</v>
+        <v>676</v>
       </c>
       <c r="C188" s="5" t="s">
-        <v>1097</v>
+        <v>1100</v>
       </c>
       <c r="D188" s="6" t="s">
-        <v>1098</v>
+        <v>1101</v>
       </c>
       <c r="E188" s="5" t="s">
-        <v>1099</v>
+        <v>1102</v>
       </c>
     </row>
     <row r="189" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -11502,16 +11614,16 @@
         <v>180</v>
       </c>
       <c r="B189" s="5" t="s">
-        <v>673</v>
+        <v>676</v>
       </c>
       <c r="C189" s="5" t="s">
-        <v>1100</v>
+        <v>1103</v>
       </c>
       <c r="D189" s="6" t="s">
-        <v>1101</v>
+        <v>1104</v>
       </c>
       <c r="E189" s="5" t="s">
-        <v>1099</v>
+        <v>1102</v>
       </c>
     </row>
     <row r="190" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -11519,16 +11631,16 @@
         <v>181</v>
       </c>
       <c r="B190" s="5" t="s">
-        <v>868</v>
+        <v>871</v>
       </c>
       <c r="C190" s="5" t="s">
+        <v>1105</v>
+      </c>
+      <c r="D190" s="6" t="s">
+        <v>1106</v>
+      </c>
+      <c r="E190" s="5" t="s">
         <v>1102</v>
-      </c>
-      <c r="D190" s="6" t="s">
-        <v>1103</v>
-      </c>
-      <c r="E190" s="5" t="s">
-        <v>1099</v>
       </c>
     </row>
     <row r="191" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -11536,16 +11648,16 @@
         <v>182</v>
       </c>
       <c r="B191" s="5" t="s">
-        <v>1036</v>
+        <v>1039</v>
       </c>
       <c r="C191" s="5" t="s">
-        <v>1104</v>
+        <v>1107</v>
       </c>
       <c r="D191" s="6" t="s">
-        <v>1105</v>
+        <v>1108</v>
       </c>
       <c r="E191" s="5" t="s">
-        <v>1099</v>
+        <v>1102</v>
       </c>
     </row>
     <row r="192" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -11553,16 +11665,16 @@
         <v>183</v>
       </c>
       <c r="B192" s="5" t="s">
-        <v>1036</v>
+        <v>1039</v>
       </c>
       <c r="C192" s="5" t="s">
-        <v>1106</v>
+        <v>1109</v>
       </c>
       <c r="D192" s="6" t="s">
-        <v>1107</v>
+        <v>1110</v>
       </c>
       <c r="E192" s="5" t="s">
-        <v>1099</v>
+        <v>1102</v>
       </c>
     </row>
     <row r="193" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -11570,13 +11682,13 @@
         <v>184</v>
       </c>
       <c r="B193" s="5" t="s">
-        <v>868</v>
+        <v>871</v>
       </c>
       <c r="C193" s="5" t="s">
-        <v>1108</v>
+        <v>1111</v>
       </c>
       <c r="D193" s="6" t="s">
-        <v>1109</v>
+        <v>1112</v>
       </c>
       <c r="E193" s="5" t="s">
         <v>533</v>
@@ -11587,16 +11699,16 @@
         <v>185</v>
       </c>
       <c r="B194" s="5" t="s">
-        <v>868</v>
+        <v>871</v>
       </c>
       <c r="C194" s="5" t="s">
-        <v>1110</v>
+        <v>1113</v>
       </c>
       <c r="D194" s="6" t="s">
-        <v>1111</v>
+        <v>1114</v>
       </c>
       <c r="E194" s="5" t="s">
-        <v>1112</v>
+        <v>1115</v>
       </c>
     </row>
     <row r="195" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -11604,16 +11716,16 @@
         <v>186</v>
       </c>
       <c r="B195" s="5" t="s">
-        <v>673</v>
+        <v>676</v>
       </c>
       <c r="C195" s="5" t="s">
-        <v>1113</v>
+        <v>1116</v>
       </c>
       <c r="D195" s="6" t="s">
-        <v>1114</v>
+        <v>1117</v>
       </c>
       <c r="E195" s="5" t="s">
-        <v>1115</v>
+        <v>1118</v>
       </c>
     </row>
     <row r="196" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -11621,16 +11733,16 @@
         <v>187</v>
       </c>
       <c r="B196" s="5" t="s">
-        <v>812</v>
+        <v>815</v>
       </c>
       <c r="C196" s="5" t="s">
-        <v>1116</v>
+        <v>1119</v>
       </c>
       <c r="D196" s="6" t="s">
-        <v>1117</v>
+        <v>1120</v>
       </c>
       <c r="E196" s="5" t="s">
-        <v>1115</v>
+        <v>1118</v>
       </c>
     </row>
     <row r="197" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -11638,16 +11750,16 @@
         <v>188</v>
       </c>
       <c r="B197" s="5" t="s">
-        <v>1036</v>
+        <v>1039</v>
       </c>
       <c r="C197" s="5" t="s">
+        <v>1121</v>
+      </c>
+      <c r="D197" s="6" t="s">
+        <v>1122</v>
+      </c>
+      <c r="E197" s="5" t="s">
         <v>1118</v>
-      </c>
-      <c r="D197" s="6" t="s">
-        <v>1119</v>
-      </c>
-      <c r="E197" s="5" t="s">
-        <v>1115</v>
       </c>
     </row>
     <row r="198" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -11655,16 +11767,16 @@
         <v>189</v>
       </c>
       <c r="B198" s="5" t="s">
-        <v>1036</v>
+        <v>1039</v>
       </c>
       <c r="C198" s="5" t="s">
-        <v>1120</v>
+        <v>1123</v>
       </c>
       <c r="D198" s="6" t="s">
-        <v>1121</v>
+        <v>1124</v>
       </c>
       <c r="E198" s="5" t="s">
-        <v>1115</v>
+        <v>1118</v>
       </c>
     </row>
     <row r="199" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -11672,16 +11784,16 @@
         <v>190</v>
       </c>
       <c r="B199" s="5" t="s">
-        <v>879</v>
+        <v>882</v>
       </c>
       <c r="C199" s="5" t="s">
-        <v>1122</v>
+        <v>1125</v>
       </c>
       <c r="D199" s="6" t="s">
-        <v>1123</v>
+        <v>1126</v>
       </c>
       <c r="E199" s="5" t="s">
-        <v>1124</v>
+        <v>1127</v>
       </c>
     </row>
     <row r="200" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -11689,16 +11801,16 @@
         <v>191</v>
       </c>
       <c r="B200" s="5" t="s">
-        <v>879</v>
+        <v>882</v>
       </c>
       <c r="C200" s="5" t="s">
-        <v>1125</v>
+        <v>1128</v>
       </c>
       <c r="D200" s="6" t="s">
-        <v>1126</v>
+        <v>1129</v>
       </c>
       <c r="E200" s="5" t="s">
-        <v>1124</v>
+        <v>1127</v>
       </c>
     </row>
     <row r="201" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -11706,16 +11818,16 @@
         <v>192</v>
       </c>
       <c r="B201" s="5" t="s">
-        <v>673</v>
+        <v>676</v>
       </c>
       <c r="C201" s="5" t="s">
+        <v>1130</v>
+      </c>
+      <c r="D201" s="6" t="s">
+        <v>1131</v>
+      </c>
+      <c r="E201" s="5" t="s">
         <v>1127</v>
-      </c>
-      <c r="D201" s="6" t="s">
-        <v>1128</v>
-      </c>
-      <c r="E201" s="5" t="s">
-        <v>1124</v>
       </c>
     </row>
     <row r="202" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -11723,16 +11835,16 @@
         <v>193</v>
       </c>
       <c r="B202" s="5" t="s">
-        <v>673</v>
+        <v>676</v>
       </c>
       <c r="C202" s="5" t="s">
-        <v>1129</v>
+        <v>1132</v>
       </c>
       <c r="D202" s="6" t="s">
-        <v>1130</v>
+        <v>1133</v>
       </c>
       <c r="E202" s="5" t="s">
-        <v>1131</v>
+        <v>1134</v>
       </c>
     </row>
     <row r="203" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -11740,16 +11852,16 @@
         <v>194</v>
       </c>
       <c r="B203" s="5" t="s">
-        <v>673</v>
+        <v>676</v>
       </c>
       <c r="C203" s="5" t="s">
-        <v>1132</v>
+        <v>1135</v>
       </c>
       <c r="D203" s="6" t="s">
-        <v>1133</v>
+        <v>1136</v>
       </c>
       <c r="E203" s="5" t="s">
-        <v>1131</v>
+        <v>1134</v>
       </c>
     </row>
     <row r="204" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -11757,16 +11869,16 @@
         <v>195</v>
       </c>
       <c r="B204" s="5" t="s">
-        <v>673</v>
+        <v>676</v>
       </c>
       <c r="C204" s="5" t="s">
-        <v>1134</v>
+        <v>1137</v>
       </c>
       <c r="D204" s="6" t="s">
-        <v>1135</v>
+        <v>1138</v>
       </c>
       <c r="E204" s="5" t="s">
-        <v>1136</v>
+        <v>1139</v>
       </c>
     </row>
     <row r="205" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -11774,13 +11886,13 @@
         <v>196</v>
       </c>
       <c r="B205" s="5" t="s">
-        <v>868</v>
+        <v>871</v>
       </c>
       <c r="C205" s="5" t="s">
-        <v>1137</v>
+        <v>1140</v>
       </c>
       <c r="D205" s="6" t="s">
-        <v>1138</v>
+        <v>1141</v>
       </c>
       <c r="E205" s="5" t="s">
         <v>540</v>
@@ -11791,16 +11903,16 @@
         <v>197</v>
       </c>
       <c r="B206" s="5" t="s">
-        <v>673</v>
+        <v>676</v>
       </c>
       <c r="C206" s="5" t="s">
-        <v>1139</v>
+        <v>1142</v>
       </c>
       <c r="D206" s="6" t="s">
-        <v>1140</v>
+        <v>1143</v>
       </c>
       <c r="E206" s="5" t="s">
-        <v>1141</v>
+        <v>1144</v>
       </c>
     </row>
     <row r="207" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -11808,16 +11920,16 @@
         <v>198</v>
       </c>
       <c r="B207" s="5" t="s">
-        <v>895</v>
+        <v>898</v>
       </c>
       <c r="C207" s="5" t="s">
-        <v>1142</v>
+        <v>1145</v>
       </c>
       <c r="D207" s="6" t="s">
-        <v>1143</v>
+        <v>1146</v>
       </c>
       <c r="E207" s="5" t="s">
-        <v>1141</v>
+        <v>1144</v>
       </c>
     </row>
     <row r="208" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -11825,16 +11937,16 @@
         <v>199</v>
       </c>
       <c r="B208" s="5" t="s">
-        <v>1036</v>
+        <v>1039</v>
       </c>
       <c r="C208" s="5" t="s">
+        <v>1147</v>
+      </c>
+      <c r="D208" s="6" t="s">
+        <v>1148</v>
+      </c>
+      <c r="E208" s="5" t="s">
         <v>1144</v>
-      </c>
-      <c r="D208" s="6" t="s">
-        <v>1145</v>
-      </c>
-      <c r="E208" s="5" t="s">
-        <v>1141</v>
       </c>
     </row>
     <row r="209" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -11842,16 +11954,16 @@
         <v>200</v>
       </c>
       <c r="B209" s="5" t="s">
-        <v>1036</v>
+        <v>1039</v>
       </c>
       <c r="C209" s="5" t="s">
-        <v>1146</v>
+        <v>1149</v>
       </c>
       <c r="D209" s="6" t="s">
-        <v>1147</v>
+        <v>1150</v>
       </c>
       <c r="E209" s="5" t="s">
-        <v>1141</v>
+        <v>1144</v>
       </c>
     </row>
     <row r="210" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -11859,16 +11971,16 @@
         <v>201</v>
       </c>
       <c r="B210" s="5" t="s">
-        <v>812</v>
+        <v>815</v>
       </c>
       <c r="C210" s="5" t="s">
-        <v>1148</v>
+        <v>1151</v>
       </c>
       <c r="D210" s="6" t="s">
-        <v>1149</v>
+        <v>1152</v>
       </c>
       <c r="E210" s="5" t="s">
-        <v>1150</v>
+        <v>1153</v>
       </c>
     </row>
     <row r="211" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -11876,16 +11988,16 @@
         <v>202</v>
       </c>
       <c r="B211" s="5" t="s">
-        <v>895</v>
+        <v>898</v>
       </c>
       <c r="C211" s="5" t="s">
-        <v>1151</v>
+        <v>1154</v>
       </c>
       <c r="D211" s="6" t="s">
-        <v>1152</v>
+        <v>1155</v>
       </c>
       <c r="E211" s="5" t="s">
-        <v>1150</v>
+        <v>1153</v>
       </c>
     </row>
     <row r="212" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -11893,16 +12005,16 @@
         <v>203</v>
       </c>
       <c r="B212" s="5" t="s">
-        <v>895</v>
+        <v>898</v>
       </c>
       <c r="C212" s="5" t="s">
+        <v>1156</v>
+      </c>
+      <c r="D212" s="6" t="s">
+        <v>1157</v>
+      </c>
+      <c r="E212" s="5" t="s">
         <v>1153</v>
-      </c>
-      <c r="D212" s="6" t="s">
-        <v>1154</v>
-      </c>
-      <c r="E212" s="5" t="s">
-        <v>1150</v>
       </c>
     </row>
     <row r="213" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -11910,16 +12022,16 @@
         <v>204</v>
       </c>
       <c r="B213" s="5" t="s">
-        <v>868</v>
+        <v>871</v>
       </c>
       <c r="C213" s="5" t="s">
-        <v>1155</v>
+        <v>1158</v>
       </c>
       <c r="D213" s="6" t="s">
-        <v>1156</v>
+        <v>1159</v>
       </c>
       <c r="E213" s="5" t="s">
-        <v>1050</v>
+        <v>1053</v>
       </c>
     </row>
     <row r="214" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -11927,16 +12039,16 @@
         <v>205</v>
       </c>
       <c r="B214" s="5" t="s">
-        <v>673</v>
+        <v>676</v>
       </c>
       <c r="C214" s="5" t="s">
-        <v>1157</v>
+        <v>1160</v>
       </c>
       <c r="D214" s="6" t="s">
-        <v>1158</v>
+        <v>1161</v>
       </c>
       <c r="E214" s="5" t="s">
-        <v>1159</v>
+        <v>1162</v>
       </c>
     </row>
     <row r="215" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -11944,16 +12056,16 @@
         <v>206</v>
       </c>
       <c r="B215" s="5" t="s">
-        <v>812</v>
+        <v>815</v>
       </c>
       <c r="C215" s="5" t="s">
-        <v>1160</v>
+        <v>1163</v>
       </c>
       <c r="D215" s="6" t="s">
-        <v>1161</v>
+        <v>1164</v>
       </c>
       <c r="E215" s="5" t="s">
-        <v>1162</v>
+        <v>1165</v>
       </c>
     </row>
     <row r="216" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -11961,16 +12073,16 @@
         <v>207</v>
       </c>
       <c r="B216" s="5" t="s">
-        <v>895</v>
+        <v>898</v>
       </c>
       <c r="C216" s="5" t="s">
-        <v>1163</v>
+        <v>1166</v>
       </c>
       <c r="D216" s="6" t="s">
-        <v>1164</v>
+        <v>1167</v>
       </c>
       <c r="E216" s="5" t="s">
-        <v>1162</v>
+        <v>1165</v>
       </c>
     </row>
     <row r="217" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -11978,16 +12090,16 @@
         <v>208</v>
       </c>
       <c r="B217" s="5" t="s">
-        <v>673</v>
+        <v>676</v>
       </c>
       <c r="C217" s="5" t="s">
-        <v>1165</v>
+        <v>1168</v>
       </c>
       <c r="D217" s="6" t="s">
-        <v>1166</v>
+        <v>1169</v>
       </c>
       <c r="E217" s="5" t="s">
-        <v>1167</v>
+        <v>1170</v>
       </c>
     </row>
     <row r="218" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -11995,16 +12107,16 @@
         <v>209</v>
       </c>
       <c r="B218" s="5" t="s">
-        <v>812</v>
+        <v>815</v>
       </c>
       <c r="C218" s="5" t="s">
-        <v>1168</v>
+        <v>1171</v>
       </c>
       <c r="D218" s="6" t="s">
-        <v>1169</v>
+        <v>1172</v>
       </c>
       <c r="E218" s="5" t="s">
-        <v>1167</v>
+        <v>1170</v>
       </c>
     </row>
     <row r="219" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -12012,16 +12124,16 @@
         <v>210</v>
       </c>
       <c r="B219" s="5" t="s">
-        <v>895</v>
+        <v>898</v>
       </c>
       <c r="C219" s="5" t="s">
+        <v>1173</v>
+      </c>
+      <c r="D219" s="6" t="s">
+        <v>1174</v>
+      </c>
+      <c r="E219" s="5" t="s">
         <v>1170</v>
-      </c>
-      <c r="D219" s="6" t="s">
-        <v>1171</v>
-      </c>
-      <c r="E219" s="5" t="s">
-        <v>1167</v>
       </c>
     </row>
     <row r="220" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -12029,16 +12141,16 @@
         <v>211</v>
       </c>
       <c r="B220" s="5" t="s">
-        <v>1036</v>
+        <v>1039</v>
       </c>
       <c r="C220" s="5" t="s">
-        <v>1172</v>
+        <v>1175</v>
       </c>
       <c r="D220" s="6" t="s">
-        <v>1173</v>
+        <v>1176</v>
       </c>
       <c r="E220" s="5" t="s">
-        <v>1167</v>
+        <v>1170</v>
       </c>
     </row>
     <row r="221" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -12046,16 +12158,16 @@
         <v>212</v>
       </c>
       <c r="B221" s="5" t="s">
-        <v>868</v>
+        <v>871</v>
       </c>
       <c r="C221" s="5" t="s">
-        <v>1174</v>
+        <v>1177</v>
       </c>
       <c r="D221" s="6" t="s">
-        <v>1175</v>
+        <v>1178</v>
       </c>
       <c r="E221" s="5" t="s">
-        <v>1176</v>
+        <v>1179</v>
       </c>
     </row>
     <row r="222" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -12063,16 +12175,16 @@
         <v>213</v>
       </c>
       <c r="B222" s="5" t="s">
-        <v>673</v>
+        <v>676</v>
       </c>
       <c r="C222" s="5" t="s">
-        <v>1177</v>
+        <v>1180</v>
       </c>
       <c r="D222" s="6" t="s">
-        <v>1178</v>
+        <v>1181</v>
       </c>
       <c r="E222" s="5" t="s">
-        <v>1179</v>
+        <v>1182</v>
       </c>
     </row>
     <row r="223" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -12080,16 +12192,16 @@
         <v>214</v>
       </c>
       <c r="B223" s="5" t="s">
-        <v>868</v>
+        <v>871</v>
       </c>
       <c r="C223" s="5" t="s">
-        <v>1180</v>
+        <v>1183</v>
       </c>
       <c r="D223" s="6" t="s">
-        <v>1181</v>
+        <v>1184</v>
       </c>
       <c r="E223" s="5" t="s">
-        <v>1179</v>
+        <v>1182</v>
       </c>
     </row>
     <row r="224" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -12097,16 +12209,16 @@
         <v>215</v>
       </c>
       <c r="B224" s="5" t="s">
-        <v>868</v>
+        <v>871</v>
       </c>
       <c r="C224" s="5" t="s">
+        <v>1185</v>
+      </c>
+      <c r="D224" s="6" t="s">
+        <v>1186</v>
+      </c>
+      <c r="E224" s="5" t="s">
         <v>1182</v>
-      </c>
-      <c r="D224" s="6" t="s">
-        <v>1183</v>
-      </c>
-      <c r="E224" s="5" t="s">
-        <v>1179</v>
       </c>
     </row>
     <row r="225" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -12114,16 +12226,16 @@
         <v>216</v>
       </c>
       <c r="B225" s="5" t="s">
-        <v>1036</v>
+        <v>1039</v>
       </c>
       <c r="C225" s="5" t="s">
-        <v>1184</v>
+        <v>1187</v>
       </c>
       <c r="D225" s="6" t="s">
-        <v>1185</v>
+        <v>1188</v>
       </c>
       <c r="E225" s="5" t="s">
-        <v>1179</v>
+        <v>1182</v>
       </c>
     </row>
     <row r="226" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -12131,16 +12243,16 @@
         <v>217</v>
       </c>
       <c r="B226" s="5" t="s">
-        <v>879</v>
+        <v>882</v>
       </c>
       <c r="C226" s="5" t="s">
-        <v>1186</v>
+        <v>1189</v>
       </c>
       <c r="D226" s="6" t="s">
-        <v>1187</v>
+        <v>1190</v>
       </c>
       <c r="E226" s="5" t="s">
-        <v>1188</v>
+        <v>1191</v>
       </c>
     </row>
     <row r="227" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -12148,16 +12260,16 @@
         <v>218</v>
       </c>
       <c r="B227" s="5" t="s">
-        <v>673</v>
+        <v>676</v>
       </c>
       <c r="C227" s="5" t="s">
-        <v>1189</v>
+        <v>1192</v>
       </c>
       <c r="D227" s="6" t="s">
-        <v>1190</v>
+        <v>1193</v>
       </c>
       <c r="E227" s="5" t="s">
-        <v>1188</v>
+        <v>1191</v>
       </c>
     </row>
     <row r="228" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -12165,16 +12277,16 @@
         <v>219</v>
       </c>
       <c r="B228" s="5" t="s">
-        <v>812</v>
+        <v>815</v>
       </c>
       <c r="C228" s="5" t="s">
+        <v>1194</v>
+      </c>
+      <c r="D228" s="6" t="s">
+        <v>1195</v>
+      </c>
+      <c r="E228" s="5" t="s">
         <v>1191</v>
-      </c>
-      <c r="D228" s="6" t="s">
-        <v>1192</v>
-      </c>
-      <c r="E228" s="5" t="s">
-        <v>1188</v>
       </c>
     </row>
     <row r="229" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -12182,16 +12294,16 @@
         <v>220</v>
       </c>
       <c r="B229" s="5" t="s">
-        <v>1036</v>
+        <v>1039</v>
       </c>
       <c r="C229" s="5" t="s">
-        <v>1193</v>
+        <v>1196</v>
       </c>
       <c r="D229" s="6" t="s">
-        <v>1194</v>
+        <v>1197</v>
       </c>
       <c r="E229" s="5" t="s">
-        <v>1188</v>
+        <v>1191</v>
       </c>
     </row>
     <row r="230" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -12199,16 +12311,16 @@
         <v>221</v>
       </c>
       <c r="B230" s="5" t="s">
-        <v>673</v>
+        <v>676</v>
       </c>
       <c r="C230" s="5" t="s">
-        <v>1195</v>
+        <v>1198</v>
       </c>
       <c r="D230" s="6" t="s">
-        <v>1196</v>
+        <v>1199</v>
       </c>
       <c r="E230" s="5" t="s">
-        <v>1197</v>
+        <v>1200</v>
       </c>
     </row>
     <row r="231" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -12216,16 +12328,16 @@
         <v>222</v>
       </c>
       <c r="B231" s="5" t="s">
-        <v>868</v>
+        <v>871</v>
       </c>
       <c r="C231" s="5" t="s">
-        <v>1198</v>
+        <v>1201</v>
       </c>
       <c r="D231" s="6" t="s">
-        <v>1199</v>
+        <v>1202</v>
       </c>
       <c r="E231" s="5" t="s">
-        <v>1197</v>
+        <v>1200</v>
       </c>
     </row>
     <row r="232" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -12233,16 +12345,16 @@
         <v>223</v>
       </c>
       <c r="B232" s="5" t="s">
-        <v>673</v>
+        <v>676</v>
       </c>
       <c r="C232" s="5" t="s">
-        <v>1200</v>
+        <v>1203</v>
       </c>
       <c r="D232" s="6" t="s">
-        <v>1201</v>
+        <v>1204</v>
       </c>
       <c r="E232" s="5" t="s">
-        <v>1202</v>
+        <v>1205</v>
       </c>
     </row>
     <row r="233" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -12250,152 +12362,237 @@
         <v>224</v>
       </c>
       <c r="B233" s="5" t="s">
-        <v>895</v>
+        <v>898</v>
       </c>
       <c r="C233" s="5" t="s">
-        <v>1203</v>
+        <v>1206</v>
       </c>
       <c r="D233" s="6" t="s">
-        <v>1204</v>
+        <v>1207</v>
       </c>
       <c r="E233" s="5" t="s">
-        <v>1202</v>
-      </c>
-    </row>
-    <row r="234" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+        <v>1205</v>
+      </c>
+    </row>
+    <row r="234" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A234" s="5" t="n">
         <v>225</v>
       </c>
       <c r="B234" s="5" t="s">
-        <v>673</v>
+        <v>676</v>
       </c>
       <c r="C234" s="5" t="s">
-        <v>1205</v>
+        <v>1208</v>
       </c>
       <c r="D234" s="6" t="s">
-        <v>1206</v>
+        <v>1209</v>
       </c>
       <c r="E234" s="5" t="s">
-        <v>1207</v>
-      </c>
-    </row>
-    <row r="235" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+        <v>1210</v>
+      </c>
+    </row>
+    <row r="235" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A235" s="5" t="n">
         <v>226</v>
       </c>
       <c r="B235" s="5" t="s">
-        <v>812</v>
+        <v>815</v>
       </c>
       <c r="C235" s="5" t="s">
-        <v>1208</v>
+        <v>1211</v>
       </c>
       <c r="D235" s="6" t="s">
-        <v>1209</v>
+        <v>1212</v>
       </c>
       <c r="E235" s="5" t="s">
-        <v>1207</v>
-      </c>
-    </row>
-    <row r="236" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+        <v>1210</v>
+      </c>
+    </row>
+    <row r="236" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A236" s="5" t="n">
         <v>227</v>
       </c>
       <c r="B236" s="5" t="s">
-        <v>895</v>
+        <v>898</v>
       </c>
       <c r="C236" s="5" t="s">
+        <v>1213</v>
+      </c>
+      <c r="D236" s="6" t="s">
+        <v>1214</v>
+      </c>
+      <c r="E236" s="5" t="s">
         <v>1210</v>
       </c>
-      <c r="D236" s="6" t="s">
-        <v>1211</v>
-      </c>
-      <c r="E236" s="5" t="s">
-        <v>1207</v>
-      </c>
-    </row>
-    <row r="237" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    </row>
+    <row r="237" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A237" s="5" t="n">
         <v>228</v>
       </c>
       <c r="B237" s="5" t="s">
-        <v>895</v>
+        <v>898</v>
       </c>
       <c r="C237" s="5" t="s">
-        <v>1212</v>
+        <v>1215</v>
       </c>
       <c r="D237" s="6" t="s">
-        <v>1213</v>
+        <v>1216</v>
       </c>
       <c r="E237" s="5" t="s">
-        <v>1214</v>
-      </c>
-    </row>
-    <row r="238" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+        <v>1217</v>
+      </c>
+    </row>
+    <row r="238" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A238" s="5" t="n">
         <v>229</v>
       </c>
       <c r="B238" s="5" t="s">
-        <v>868</v>
+        <v>871</v>
       </c>
       <c r="C238" s="5" t="s">
-        <v>1215</v>
+        <v>1218</v>
       </c>
       <c r="D238" s="6" t="s">
-        <v>1216</v>
+        <v>1219</v>
       </c>
       <c r="E238" s="5" t="s">
-        <v>1214</v>
-      </c>
-    </row>
-    <row r="239" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+        <v>1217</v>
+      </c>
+    </row>
+    <row r="239" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A239" s="5" t="n">
         <v>230</v>
       </c>
       <c r="B239" s="5" t="s">
-        <v>868</v>
+        <v>871</v>
       </c>
       <c r="C239" s="5" t="s">
+        <v>1220</v>
+      </c>
+      <c r="D239" s="6" t="s">
+        <v>1221</v>
+      </c>
+      <c r="E239" s="5" t="s">
         <v>1217</v>
       </c>
-      <c r="D239" s="6" t="s">
-        <v>1218</v>
-      </c>
-      <c r="E239" s="5" t="s">
-        <v>1214</v>
-      </c>
-    </row>
-    <row r="240" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    </row>
+    <row r="240" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A240" s="5" t="n">
         <v>231</v>
       </c>
       <c r="B240" s="5" t="s">
-        <v>1036</v>
+        <v>1039</v>
       </c>
       <c r="C240" s="5" t="s">
-        <v>1219</v>
+        <v>1222</v>
       </c>
       <c r="D240" s="6" t="s">
-        <v>1220</v>
+        <v>1223</v>
       </c>
       <c r="E240" s="5" t="s">
-        <v>1214</v>
-      </c>
-    </row>
-    <row r="241" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+        <v>1217</v>
+      </c>
+    </row>
+    <row r="241" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A241" s="5" t="n">
         <v>232</v>
       </c>
       <c r="B241" s="5" t="s">
-        <v>1036</v>
+        <v>1039</v>
       </c>
       <c r="C241" s="5" t="s">
-        <v>1221</v>
+        <v>1224</v>
       </c>
       <c r="D241" s="6" t="s">
-        <v>1222</v>
+        <v>1225</v>
       </c>
       <c r="E241" s="5" t="s">
-        <v>1214</v>
+        <v>1217</v>
+      </c>
+    </row>
+    <row r="242" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A242" s="5" t="n">
+        <v>233</v>
+      </c>
+      <c r="B242" s="5" t="s">
+        <v>871</v>
+      </c>
+      <c r="C242" s="5" t="s">
+        <v>1226</v>
+      </c>
+      <c r="D242" s="6" t="s">
+        <v>1227</v>
+      </c>
+      <c r="E242" s="5" t="s">
+        <v>559</v>
+      </c>
+    </row>
+    <row r="243" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A243" s="5" t="n">
+        <v>234</v>
+      </c>
+      <c r="B243" s="5" t="s">
+        <v>882</v>
+      </c>
+      <c r="C243" s="5" t="s">
+        <v>1228</v>
+      </c>
+      <c r="D243" s="6" t="s">
+        <v>1229</v>
+      </c>
+      <c r="E243" s="5" t="s">
+        <v>1230</v>
+      </c>
+    </row>
+    <row r="244" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A244" s="5" t="n">
+        <v>235</v>
+      </c>
+      <c r="B244" s="5" t="s">
+        <v>676</v>
+      </c>
+      <c r="C244" s="5" t="s">
+        <v>1231</v>
+      </c>
+      <c r="D244" s="6" t="s">
+        <v>1232</v>
+      </c>
+      <c r="E244" s="5" t="s">
+        <v>1230</v>
+      </c>
+    </row>
+    <row r="245" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A245" s="5" t="n">
+        <v>236</v>
+      </c>
+      <c r="B245" s="5" t="s">
+        <v>676</v>
+      </c>
+      <c r="C245" s="5" t="s">
+        <v>1233</v>
+      </c>
+      <c r="D245" s="6" t="s">
+        <v>1234</v>
+      </c>
+      <c r="E245" s="5" t="s">
+        <v>1230</v>
+      </c>
+    </row>
+    <row r="246" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A246" s="5" t="n">
+        <v>237</v>
+      </c>
+      <c r="B246" s="5" t="s">
+        <v>871</v>
+      </c>
+      <c r="C246" s="5" t="s">
+        <v>1235</v>
+      </c>
+      <c r="D246" s="6" t="s">
+        <v>1236</v>
+      </c>
+      <c r="E246" s="5" t="s">
+        <v>1230</v>
       </c>
     </row>
   </sheetData>
@@ -12562,6 +12759,11 @@
     <hyperlink ref="D239" r:id="rId157" display="https://abcnews.com/Politics/wireStory/justice-department-directs-states-hold-2024-election-records-136350319"/>
     <hyperlink ref="D240" r:id="rId158" display="https://www.pbs.org/newshour/show/news-wrap-august-inflation-report-shows-consumer-prices-up-3-4"/>
     <hyperlink ref="D241" r:id="rId159" display="https://www.pbs.org/newshour/politics/watch-trump-leads-rnc-in-pledge-to-cheat-like-hell-in-november-elections"/>
+    <hyperlink ref="D242" r:id="rId160" display="https://abcnews.com/Politics/wireStory/federal-judge-freezes-trump-mail-ballot-order-us-136415151"/>
+    <hyperlink ref="D243" r:id="rId161" display="https://www.npr.org/2026/09/18/g-s1-144112/trump-ban-cnn-msnow-politico-white-house-media"/>
+    <hyperlink ref="D244" r:id="rId162" display="https://www.nbcnews.com/politics/trump-administration/trump-announces-agreement-denmark-secure-permanent-control-greenlands-rcna598641"/>
+    <hyperlink ref="D245" r:id="rId163" display="https://www.nbcnews.com/politics/national-security/state-department-approves-243b-f-35-fighter-jet-sale-saudi-arabia-chin-rcna598487"/>
+    <hyperlink ref="D246" r:id="rId164" display="https://abcnews.com/Politics/wireStory/judge-rules-epa-illegally-terminated-7-billion-solar-136569326"/>
   </hyperlinks>
   <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.511811023622047" footer="0.511811023622047"/>
@@ -12587,7 +12789,7 @@
   <sheetData>
     <row r="1" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A1" s="7" t="s">
-        <v>1223</v>
+        <v>1237</v>
       </c>
       <c r="B1" s="7"/>
     </row>
@@ -12596,7 +12798,7 @@
         <v>3</v>
       </c>
       <c r="B2" s="8" t="s">
-        <v>1224</v>
+        <v>1238</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -12770,9 +12972,9 @@
         <v>1</v>
       </c>
     </row>
-    <row r="22" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="22" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A22" s="10" t="s">
-        <v>1225</v>
+        <v>1239</v>
       </c>
       <c r="B22" s="10" t="n">
         <f aca="false">SUM(B3:B21)</f>

--- a/data/Trump_Second_Term_Weekly_Tracker.xlsx
+++ b/data/Trump_Second_Term_Weekly_Tracker.xlsx
@@ -8481,7 +8481,7 @@
         <v>232</v>
       </c>
     </row>
-    <row r="235" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="235" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A235" s="4" t="s">
         <v>559</v>
       </c>
@@ -8495,7 +8495,7 @@
         <v>233</v>
       </c>
     </row>
-    <row r="236" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="236" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A236" s="4" t="s">
         <v>559</v>
       </c>
@@ -8509,7 +8509,7 @@
         <v>234</v>
       </c>
     </row>
-    <row r="237" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="237" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A237" s="4" t="s">
         <v>559</v>
       </c>
@@ -8523,7 +8523,7 @@
         <v>235</v>
       </c>
     </row>
-    <row r="238" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="238" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A238" s="4" t="s">
         <v>559</v>
       </c>
@@ -8537,7 +8537,7 @@
         <v>236</v>
       </c>
     </row>
-    <row r="239" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="239" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A239" s="4" t="s">
         <v>559</v>
       </c>
@@ -12510,7 +12510,7 @@
         <v>1217</v>
       </c>
     </row>
-    <row r="242" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="242" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A242" s="5" t="n">
         <v>233</v>
       </c>
@@ -12527,7 +12527,7 @@
         <v>559</v>
       </c>
     </row>
-    <row r="243" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="243" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A243" s="5" t="n">
         <v>234</v>
       </c>
@@ -12544,7 +12544,7 @@
         <v>1230</v>
       </c>
     </row>
-    <row r="244" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="244" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A244" s="5" t="n">
         <v>235</v>
       </c>
@@ -12561,7 +12561,7 @@
         <v>1230</v>
       </c>
     </row>
-    <row r="245" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="245" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A245" s="5" t="n">
         <v>236</v>
       </c>
@@ -12578,7 +12578,7 @@
         <v>1230</v>
       </c>
     </row>
-    <row r="246" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="246" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A246" s="5" t="n">
         <v>237</v>
       </c>

--- a/data/Trump_Second_Term_Weekly_Tracker.xlsx
+++ b/data/Trump_Second_Term_Weekly_Tracker.xlsx
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1894" uniqueCount="1240">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1899" uniqueCount="1240">
   <si>
     <t xml:space="preserve">Documented actions and policies of the second Trump administration reported as harmful by major news outlets, courts, and government data — Jan 20, 2025 through Jul 8, 2026. One row per event; weeks with multiple events have multiple rows; quiet weeks are skipped. This compiles critical coverage as requested; the administration and its supporters dispute many of these characterizations. See the Sources tab (matching Ref #) and verify details independently before citing.</t>
   </si>
@@ -8488,7 +8488,9 @@
       <c r="B235" s="4" t="s">
         <v>560</v>
       </c>
-      <c r="C235" s="4"/>
+      <c r="C235" s="4" t="s">
+        <v>558</v>
+      </c>
       <c r="D235" s="4"/>
       <c r="E235" s="4"/>
       <c r="F235" s="4" t="n">
@@ -8502,7 +8504,9 @@
       <c r="B236" s="4" t="s">
         <v>561</v>
       </c>
-      <c r="C236" s="4"/>
+      <c r="C236" s="4" t="s">
+        <v>68</v>
+      </c>
       <c r="D236" s="4"/>
       <c r="E236" s="4"/>
       <c r="F236" s="4" t="n">
@@ -8516,7 +8520,9 @@
       <c r="B237" s="4" t="s">
         <v>561</v>
       </c>
-      <c r="C237" s="4"/>
+      <c r="C237" s="4" t="s">
+        <v>48</v>
+      </c>
       <c r="D237" s="4"/>
       <c r="E237" s="4"/>
       <c r="F237" s="4" t="n">
@@ -8530,7 +8536,9 @@
       <c r="B238" s="4" t="s">
         <v>561</v>
       </c>
-      <c r="C238" s="4"/>
+      <c r="C238" s="4" t="s">
+        <v>48</v>
+      </c>
       <c r="D238" s="4"/>
       <c r="E238" s="4"/>
       <c r="F238" s="4" t="n">
@@ -8544,7 +8552,9 @@
       <c r="B239" s="4" t="s">
         <v>561</v>
       </c>
-      <c r="C239" s="4"/>
+      <c r="C239" s="4" t="s">
+        <v>18</v>
+      </c>
       <c r="D239" s="4"/>
       <c r="E239" s="4"/>
       <c r="F239" s="4" t="n">
@@ -12816,7 +12826,7 @@
       </c>
       <c r="B4" s="9" t="n">
         <f aca="false">COUNTIF('Weekly Timeline'!C:C,A4)</f>
-        <v>13</v>
+        <v>14</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -12861,7 +12871,7 @@
       </c>
       <c r="B9" s="9" t="n">
         <f aca="false">COUNTIF('Weekly Timeline'!C:C,A9)</f>
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -12897,7 +12907,7 @@
       </c>
       <c r="B13" s="9" t="n">
         <f aca="false">COUNTIF('Weekly Timeline'!C:C,A13)</f>
-        <v>14</v>
+        <v>16</v>
       </c>
     </row>
     <row r="14" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -12951,7 +12961,7 @@
       </c>
       <c r="B19" s="9" t="n">
         <f aca="false">COUNTIF('Weekly Timeline'!C:C,A19)</f>
-        <v>10</v>
+        <v>11</v>
       </c>
     </row>
     <row r="20" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -12978,7 +12988,7 @@
       </c>
       <c r="B22" s="10" t="n">
         <f aca="false">SUM(B3:B21)</f>
-        <v>176</v>
+        <v>181</v>
       </c>
     </row>
   </sheetData>

--- a/data/Trump_Second_Term_Weekly_Tracker.xlsx
+++ b/data/Trump_Second_Term_Weekly_Tracker.xlsx
@@ -13,7 +13,7 @@
     <sheet name="Summary" sheetId="3" state="visible" r:id="rId5"/>
   </sheets>
   <definedNames>
-    <definedName function="false" hidden="true" localSheetId="0" name="_xlnm._FilterDatabase" vbProcedure="false">'Weekly Timeline'!$A$2:$F$239</definedName>
+    <definedName function="false" hidden="true" localSheetId="0" name="_xlnm._FilterDatabase" vbProcedure="false">'Weekly Timeline'!$A$2:$F$243</definedName>
   </definedNames>
   <calcPr iterateCount="100" refMode="A1" iterate="false" iterateDelta="0.0001"/>
   <extLst>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1899" uniqueCount="1240">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1927" uniqueCount="1253">
   <si>
     <t xml:space="preserve">Documented actions and policies of the second Trump administration reported as harmful by major news outlets, courts, and government data — Jan 20, 2025 through Jul 8, 2026. One row per event; weeks with multiple events have multiple rows; quiet weeks are skipped. This compiles critical coverage as requested; the administration and its supporters dispute many of these characterizations. See the Sources tab (matching Ref #) and verify details independently before citing.</t>
   </si>
@@ -1713,6 +1713,15 @@
     <t xml:space="preserve">Sep 18</t>
   </si>
   <si>
+    <t xml:space="preserve">Sep 21, 2026</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Sep 21</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Sep 20</t>
+  </si>
+  <si>
     <t xml:space="preserve">Ref # matches the Source Ref column on the Weekly Timeline tab. URLs are provided where verified via current web results (mostly 2026 items). For 2025 items, outlet names and dates are given; searching the description text will locate the original coverage. Per your request the mix emphasizes CNN, Politico, MSNBC/MS NOW, NBC and independent outlets, alongside AP, Reuters, Guardian, NPR, CBS, ABC and court documents.</t>
   </si>
   <si>
@@ -3736,6 +3745,36 @@
   </si>
   <si>
     <t xml:space="preserve">https://abcnews.com/Politics/wireStory/judge-rules-epa-illegally-terminated-7-billion-solar-136569326</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ICE agent shoots and wounds man in Austin</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://www.theguardian.com/us-news/video/2026/sep/21/austin-texas-ice-shooting-protests</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Supreme Court allows Trump administration to use expanded database for potential voter purges</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://www.nbcnews.com/politics/supreme-court/supreme-court-allows-trump-administration-use-expanded-database-potent-rcna596611</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Sep 25, 2026</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Trump administration guts data collection on US education as math and reading scores plummet</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://www.theguardian.com/us-news/ng-interactive/2026/sep/25/student-math-reading-test-scores</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Texas ICE shooting leaves Venezuelan DoorDash driver with bullet in his back, says lawyer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://www.bbc.com/news/articles/c3y0z25v0zjwo</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Sep 20, 2026</t>
   </si>
   <si>
     <t xml:space="preserve">Entries by category (live COUNTIF formulas against the Weekly Timeline tab)</t>
@@ -4217,7 +4256,7 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:F239"/>
+  <dimension ref="A1:F243"/>
   <sheetFormatPr defaultColWidth="8.6875" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="13.01"/>
@@ -8561,8 +8600,72 @@
         <v>237</v>
       </c>
     </row>
+    <row r="240" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A240" s="5" t="s">
+        <v>562</v>
+      </c>
+      <c r="B240" s="5" t="s">
+        <v>563</v>
+      </c>
+      <c r="C240" s="5" t="s">
+        <v>18</v>
+      </c>
+      <c r="D240" s="5"/>
+      <c r="E240" s="5"/>
+      <c r="F240" s="5" t="n">
+        <v>238</v>
+      </c>
+    </row>
+    <row r="241" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A241" s="5" t="s">
+        <v>562</v>
+      </c>
+      <c r="B241" s="5" t="s">
+        <v>246</v>
+      </c>
+      <c r="C241" s="5" t="s">
+        <v>558</v>
+      </c>
+      <c r="D241" s="5"/>
+      <c r="E241" s="5"/>
+      <c r="F241" s="5" t="n">
+        <v>239</v>
+      </c>
+    </row>
+    <row r="242" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A242" s="5" t="s">
+        <v>562</v>
+      </c>
+      <c r="B242" s="5" t="s">
+        <v>246</v>
+      </c>
+      <c r="C242" s="5" t="s">
+        <v>107</v>
+      </c>
+      <c r="D242" s="5"/>
+      <c r="E242" s="5"/>
+      <c r="F242" s="5" t="n">
+        <v>240</v>
+      </c>
+    </row>
+    <row r="243" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A243" s="4" t="s">
+        <v>559</v>
+      </c>
+      <c r="B243" s="4" t="s">
+        <v>564</v>
+      </c>
+      <c r="C243" s="4" t="s">
+        <v>18</v>
+      </c>
+      <c r="D243" s="4"/>
+      <c r="E243" s="4"/>
+      <c r="F243" s="4" t="n">
+        <v>241</v>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A2:F239"/>
+  <autoFilter ref="A2:F243"/>
   <mergeCells count="1">
     <mergeCell ref="A1:F1"/>
   </mergeCells>
@@ -8582,7 +8685,7 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:E246"/>
+  <dimension ref="A1:E250"/>
   <sheetFormatPr defaultColWidth="8.6875" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="7"/>
@@ -8593,7 +8696,7 @@
   <sheetData>
     <row r="1" customFormat="false" ht="48" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A1" s="2" t="s">
-        <v>562</v>
+        <v>565</v>
       </c>
       <c r="B1" s="2"/>
       <c r="C1" s="2"/>
@@ -8602,19 +8705,19 @@
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A2" s="3" t="s">
-        <v>563</v>
+        <v>566</v>
       </c>
       <c r="B2" s="3" t="s">
-        <v>564</v>
+        <v>567</v>
       </c>
       <c r="C2" s="3" t="s">
-        <v>565</v>
+        <v>568</v>
       </c>
       <c r="D2" s="3" t="s">
-        <v>566</v>
+        <v>569</v>
       </c>
       <c r="E2" s="3" t="s">
-        <v>567</v>
+        <v>570</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -8622,14 +8725,14 @@
         <v>1</v>
       </c>
       <c r="B3" s="5" t="s">
-        <v>568</v>
+        <v>571</v>
       </c>
       <c r="C3" s="5" t="s">
-        <v>569</v>
+        <v>572</v>
       </c>
       <c r="D3" s="5"/>
       <c r="E3" s="5" t="s">
-        <v>570</v>
+        <v>573</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -8637,14 +8740,14 @@
         <v>2</v>
       </c>
       <c r="B4" s="5" t="s">
-        <v>571</v>
+        <v>574</v>
       </c>
       <c r="C4" s="5" t="s">
-        <v>572</v>
+        <v>575</v>
       </c>
       <c r="D4" s="5"/>
       <c r="E4" s="5" t="s">
-        <v>573</v>
+        <v>576</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -8652,14 +8755,14 @@
         <v>3</v>
       </c>
       <c r="B5" s="5" t="s">
-        <v>574</v>
+        <v>577</v>
       </c>
       <c r="C5" s="5" t="s">
-        <v>575</v>
+        <v>578</v>
       </c>
       <c r="D5" s="5"/>
       <c r="E5" s="5" t="s">
-        <v>570</v>
+        <v>573</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -8667,14 +8770,14 @@
         <v>4</v>
       </c>
       <c r="B6" s="5" t="s">
-        <v>576</v>
+        <v>579</v>
       </c>
       <c r="C6" s="5" t="s">
-        <v>577</v>
+        <v>580</v>
       </c>
       <c r="D6" s="5"/>
       <c r="E6" s="5" t="s">
-        <v>578</v>
+        <v>581</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -8682,14 +8785,14 @@
         <v>5</v>
       </c>
       <c r="B7" s="5" t="s">
-        <v>579</v>
+        <v>582</v>
       </c>
       <c r="C7" s="5" t="s">
-        <v>580</v>
+        <v>583</v>
       </c>
       <c r="D7" s="5"/>
       <c r="E7" s="5" t="s">
-        <v>570</v>
+        <v>573</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -8697,14 +8800,14 @@
         <v>6</v>
       </c>
       <c r="B8" s="5" t="s">
-        <v>581</v>
+        <v>584</v>
       </c>
       <c r="C8" s="5" t="s">
-        <v>582</v>
+        <v>585</v>
       </c>
       <c r="D8" s="5"/>
       <c r="E8" s="5" t="s">
-        <v>570</v>
+        <v>573</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -8712,14 +8815,14 @@
         <v>7</v>
       </c>
       <c r="B9" s="5" t="s">
-        <v>583</v>
+        <v>586</v>
       </c>
       <c r="C9" s="5" t="s">
-        <v>584</v>
+        <v>587</v>
       </c>
       <c r="D9" s="5"/>
       <c r="E9" s="5" t="s">
-        <v>585</v>
+        <v>588</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -8727,14 +8830,14 @@
         <v>8</v>
       </c>
       <c r="B10" s="5" t="s">
-        <v>586</v>
+        <v>589</v>
       </c>
       <c r="C10" s="5" t="s">
-        <v>587</v>
+        <v>590</v>
       </c>
       <c r="D10" s="5"/>
       <c r="E10" s="5" t="s">
-        <v>588</v>
+        <v>591</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -8742,14 +8845,14 @@
         <v>9</v>
       </c>
       <c r="B11" s="5" t="s">
-        <v>589</v>
+        <v>592</v>
       </c>
       <c r="C11" s="5" t="s">
-        <v>590</v>
+        <v>593</v>
       </c>
       <c r="D11" s="5"/>
       <c r="E11" s="5" t="s">
-        <v>591</v>
+        <v>594</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -8757,14 +8860,14 @@
         <v>10</v>
       </c>
       <c r="B12" s="5" t="s">
-        <v>592</v>
+        <v>595</v>
       </c>
       <c r="C12" s="5" t="s">
-        <v>593</v>
+        <v>596</v>
       </c>
       <c r="D12" s="5"/>
       <c r="E12" s="5" t="s">
-        <v>594</v>
+        <v>597</v>
       </c>
     </row>
     <row r="13" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -8772,14 +8875,14 @@
         <v>11</v>
       </c>
       <c r="B13" s="5" t="s">
-        <v>595</v>
+        <v>598</v>
       </c>
       <c r="C13" s="5" t="s">
-        <v>596</v>
+        <v>599</v>
       </c>
       <c r="D13" s="5"/>
       <c r="E13" s="5" t="s">
-        <v>597</v>
+        <v>600</v>
       </c>
     </row>
     <row r="14" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -8787,14 +8890,14 @@
         <v>12</v>
       </c>
       <c r="B14" s="5" t="s">
-        <v>598</v>
+        <v>601</v>
       </c>
       <c r="C14" s="5" t="s">
-        <v>599</v>
+        <v>602</v>
       </c>
       <c r="D14" s="5"/>
       <c r="E14" s="5" t="s">
-        <v>600</v>
+        <v>603</v>
       </c>
     </row>
     <row r="15" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -8802,14 +8905,14 @@
         <v>13</v>
       </c>
       <c r="B15" s="5" t="s">
-        <v>601</v>
+        <v>604</v>
       </c>
       <c r="C15" s="5" t="s">
-        <v>602</v>
+        <v>605</v>
       </c>
       <c r="D15" s="5"/>
       <c r="E15" s="5" t="s">
-        <v>603</v>
+        <v>606</v>
       </c>
     </row>
     <row r="16" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -8817,14 +8920,14 @@
         <v>14</v>
       </c>
       <c r="B16" s="5" t="s">
-        <v>604</v>
+        <v>607</v>
       </c>
       <c r="C16" s="5" t="s">
-        <v>605</v>
+        <v>608</v>
       </c>
       <c r="D16" s="5"/>
       <c r="E16" s="5" t="s">
-        <v>606</v>
+        <v>609</v>
       </c>
     </row>
     <row r="17" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -8832,14 +8935,14 @@
         <v>15</v>
       </c>
       <c r="B17" s="5" t="s">
-        <v>607</v>
+        <v>610</v>
       </c>
       <c r="C17" s="5" t="s">
-        <v>608</v>
+        <v>611</v>
       </c>
       <c r="D17" s="5"/>
       <c r="E17" s="5" t="s">
-        <v>609</v>
+        <v>612</v>
       </c>
     </row>
     <row r="18" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -8847,14 +8950,14 @@
         <v>16</v>
       </c>
       <c r="B18" s="5" t="s">
-        <v>610</v>
+        <v>613</v>
       </c>
       <c r="C18" s="5" t="s">
-        <v>611</v>
+        <v>614</v>
       </c>
       <c r="D18" s="5"/>
       <c r="E18" s="5" t="s">
-        <v>612</v>
+        <v>615</v>
       </c>
     </row>
     <row r="19" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -8862,14 +8965,14 @@
         <v>17</v>
       </c>
       <c r="B19" s="5" t="s">
-        <v>613</v>
+        <v>616</v>
       </c>
       <c r="C19" s="5" t="s">
-        <v>614</v>
+        <v>617</v>
       </c>
       <c r="D19" s="5"/>
       <c r="E19" s="5" t="s">
-        <v>615</v>
+        <v>618</v>
       </c>
     </row>
     <row r="20" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -8877,14 +8980,14 @@
         <v>18</v>
       </c>
       <c r="B20" s="5" t="s">
-        <v>616</v>
+        <v>619</v>
       </c>
       <c r="C20" s="5" t="s">
-        <v>617</v>
+        <v>620</v>
       </c>
       <c r="D20" s="5"/>
       <c r="E20" s="5" t="s">
-        <v>618</v>
+        <v>621</v>
       </c>
     </row>
     <row r="21" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -8892,14 +8995,14 @@
         <v>19</v>
       </c>
       <c r="B21" s="5" t="s">
-        <v>619</v>
+        <v>622</v>
       </c>
       <c r="C21" s="5" t="s">
-        <v>620</v>
+        <v>623</v>
       </c>
       <c r="D21" s="5"/>
       <c r="E21" s="5" t="s">
-        <v>621</v>
+        <v>624</v>
       </c>
     </row>
     <row r="22" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -8907,14 +9010,14 @@
         <v>20</v>
       </c>
       <c r="B22" s="5" t="s">
-        <v>622</v>
+        <v>625</v>
       </c>
       <c r="C22" s="5" t="s">
-        <v>623</v>
+        <v>626</v>
       </c>
       <c r="D22" s="5"/>
       <c r="E22" s="5" t="s">
-        <v>624</v>
+        <v>627</v>
       </c>
     </row>
     <row r="23" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -8922,14 +9025,14 @@
         <v>21</v>
       </c>
       <c r="B23" s="5" t="s">
-        <v>625</v>
+        <v>628</v>
       </c>
       <c r="C23" s="5" t="s">
-        <v>626</v>
+        <v>629</v>
       </c>
       <c r="D23" s="5"/>
       <c r="E23" s="5" t="s">
-        <v>627</v>
+        <v>630</v>
       </c>
     </row>
     <row r="24" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -8937,14 +9040,14 @@
         <v>22</v>
       </c>
       <c r="B24" s="5" t="s">
-        <v>628</v>
+        <v>631</v>
       </c>
       <c r="C24" s="5" t="s">
-        <v>629</v>
+        <v>632</v>
       </c>
       <c r="D24" s="5"/>
       <c r="E24" s="5" t="s">
-        <v>630</v>
+        <v>633</v>
       </c>
     </row>
     <row r="25" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -8952,14 +9055,14 @@
         <v>23</v>
       </c>
       <c r="B25" s="5" t="s">
-        <v>631</v>
+        <v>634</v>
       </c>
       <c r="C25" s="5" t="s">
-        <v>632</v>
+        <v>635</v>
       </c>
       <c r="D25" s="5"/>
       <c r="E25" s="5" t="s">
-        <v>633</v>
+        <v>636</v>
       </c>
     </row>
     <row r="26" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -8967,14 +9070,14 @@
         <v>24</v>
       </c>
       <c r="B26" s="5" t="s">
-        <v>634</v>
+        <v>637</v>
       </c>
       <c r="C26" s="5" t="s">
-        <v>635</v>
+        <v>638</v>
       </c>
       <c r="D26" s="5"/>
       <c r="E26" s="5" t="s">
-        <v>636</v>
+        <v>639</v>
       </c>
     </row>
     <row r="27" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -8982,14 +9085,14 @@
         <v>25</v>
       </c>
       <c r="B27" s="5" t="s">
-        <v>637</v>
+        <v>640</v>
       </c>
       <c r="C27" s="5" t="s">
-        <v>638</v>
+        <v>641</v>
       </c>
       <c r="D27" s="5"/>
       <c r="E27" s="5" t="s">
-        <v>639</v>
+        <v>642</v>
       </c>
     </row>
     <row r="28" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -8997,14 +9100,14 @@
         <v>26</v>
       </c>
       <c r="B28" s="5" t="s">
-        <v>640</v>
+        <v>643</v>
       </c>
       <c r="C28" s="5" t="s">
-        <v>641</v>
+        <v>644</v>
       </c>
       <c r="D28" s="5"/>
       <c r="E28" s="5" t="s">
-        <v>642</v>
+        <v>645</v>
       </c>
     </row>
     <row r="29" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -9012,14 +9115,14 @@
         <v>27</v>
       </c>
       <c r="B29" s="5" t="s">
-        <v>643</v>
+        <v>646</v>
       </c>
       <c r="C29" s="5" t="s">
-        <v>644</v>
+        <v>647</v>
       </c>
       <c r="D29" s="5"/>
       <c r="E29" s="5" t="s">
-        <v>645</v>
+        <v>648</v>
       </c>
     </row>
     <row r="30" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -9027,14 +9130,14 @@
         <v>28</v>
       </c>
       <c r="B30" s="5" t="s">
-        <v>646</v>
+        <v>649</v>
       </c>
       <c r="C30" s="5" t="s">
-        <v>647</v>
+        <v>650</v>
       </c>
       <c r="D30" s="5"/>
       <c r="E30" s="5" t="s">
-        <v>648</v>
+        <v>651</v>
       </c>
     </row>
     <row r="31" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -9042,14 +9145,14 @@
         <v>29</v>
       </c>
       <c r="B31" s="5" t="s">
-        <v>649</v>
+        <v>652</v>
       </c>
       <c r="C31" s="5" t="s">
-        <v>650</v>
+        <v>653</v>
       </c>
       <c r="D31" s="5"/>
       <c r="E31" s="5" t="s">
-        <v>651</v>
+        <v>654</v>
       </c>
     </row>
     <row r="32" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -9057,14 +9160,14 @@
         <v>30</v>
       </c>
       <c r="B32" s="5" t="s">
-        <v>595</v>
+        <v>598</v>
       </c>
       <c r="C32" s="5" t="s">
-        <v>652</v>
+        <v>655</v>
       </c>
       <c r="D32" s="5"/>
       <c r="E32" s="5" t="s">
-        <v>653</v>
+        <v>656</v>
       </c>
     </row>
     <row r="33" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -9072,14 +9175,14 @@
         <v>31</v>
       </c>
       <c r="B33" s="5" t="s">
-        <v>654</v>
+        <v>657</v>
       </c>
       <c r="C33" s="5" t="s">
-        <v>655</v>
+        <v>658</v>
       </c>
       <c r="D33" s="5"/>
       <c r="E33" s="5" t="s">
-        <v>656</v>
+        <v>659</v>
       </c>
     </row>
     <row r="34" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -9087,14 +9190,14 @@
         <v>32</v>
       </c>
       <c r="B34" s="5" t="s">
-        <v>613</v>
+        <v>616</v>
       </c>
       <c r="C34" s="5" t="s">
-        <v>657</v>
+        <v>660</v>
       </c>
       <c r="D34" s="5"/>
       <c r="E34" s="5" t="s">
-        <v>658</v>
+        <v>661</v>
       </c>
     </row>
     <row r="35" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -9102,14 +9205,14 @@
         <v>33</v>
       </c>
       <c r="B35" s="5" t="s">
-        <v>659</v>
+        <v>662</v>
       </c>
       <c r="C35" s="5" t="s">
-        <v>660</v>
+        <v>663</v>
       </c>
       <c r="D35" s="5"/>
       <c r="E35" s="5" t="s">
-        <v>661</v>
+        <v>664</v>
       </c>
     </row>
     <row r="36" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -9117,14 +9220,14 @@
         <v>34</v>
       </c>
       <c r="B36" s="5" t="s">
-        <v>662</v>
+        <v>665</v>
       </c>
       <c r="C36" s="5" t="s">
-        <v>663</v>
+        <v>666</v>
       </c>
       <c r="D36" s="5"/>
       <c r="E36" s="5" t="s">
-        <v>664</v>
+        <v>667</v>
       </c>
     </row>
     <row r="37" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -9132,14 +9235,14 @@
         <v>35</v>
       </c>
       <c r="B37" s="5" t="s">
-        <v>665</v>
+        <v>668</v>
       </c>
       <c r="C37" s="5" t="s">
-        <v>666</v>
+        <v>669</v>
       </c>
       <c r="D37" s="5"/>
       <c r="E37" s="5" t="s">
-        <v>667</v>
+        <v>670</v>
       </c>
     </row>
     <row r="38" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -9147,14 +9250,14 @@
         <v>36</v>
       </c>
       <c r="B38" s="5" t="s">
-        <v>613</v>
+        <v>616</v>
       </c>
       <c r="C38" s="5" t="s">
-        <v>668</v>
+        <v>671</v>
       </c>
       <c r="D38" s="5"/>
       <c r="E38" s="5" t="s">
-        <v>669</v>
+        <v>672</v>
       </c>
     </row>
     <row r="39" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -9162,14 +9265,14 @@
         <v>37</v>
       </c>
       <c r="B39" s="5" t="s">
-        <v>670</v>
+        <v>673</v>
       </c>
       <c r="C39" s="5" t="s">
-        <v>671</v>
+        <v>674</v>
       </c>
       <c r="D39" s="5"/>
       <c r="E39" s="5" t="s">
-        <v>672</v>
+        <v>675</v>
       </c>
     </row>
     <row r="40" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -9177,14 +9280,14 @@
         <v>38</v>
       </c>
       <c r="B40" s="5" t="s">
-        <v>673</v>
+        <v>676</v>
       </c>
       <c r="C40" s="5" t="s">
-        <v>674</v>
+        <v>677</v>
       </c>
       <c r="D40" s="5"/>
       <c r="E40" s="5" t="s">
-        <v>675</v>
+        <v>678</v>
       </c>
     </row>
     <row r="41" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -9192,10 +9295,10 @@
         <v>39</v>
       </c>
       <c r="B41" s="5" t="s">
-        <v>676</v>
+        <v>679</v>
       </c>
       <c r="C41" s="5" t="s">
-        <v>677</v>
+        <v>680</v>
       </c>
       <c r="D41" s="5"/>
       <c r="E41" s="5" t="s">
@@ -9207,14 +9310,14 @@
         <v>40</v>
       </c>
       <c r="B42" s="5" t="s">
-        <v>678</v>
+        <v>681</v>
       </c>
       <c r="C42" s="5" t="s">
-        <v>679</v>
+        <v>682</v>
       </c>
       <c r="D42" s="5"/>
       <c r="E42" s="5" t="s">
-        <v>680</v>
+        <v>683</v>
       </c>
     </row>
     <row r="43" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -9222,14 +9325,14 @@
         <v>41</v>
       </c>
       <c r="B43" s="5" t="s">
-        <v>681</v>
+        <v>684</v>
       </c>
       <c r="C43" s="5" t="s">
-        <v>682</v>
+        <v>685</v>
       </c>
       <c r="D43" s="5"/>
       <c r="E43" s="5" t="s">
-        <v>683</v>
+        <v>686</v>
       </c>
     </row>
     <row r="44" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -9237,14 +9340,14 @@
         <v>42</v>
       </c>
       <c r="B44" s="5" t="s">
-        <v>684</v>
+        <v>687</v>
       </c>
       <c r="C44" s="5" t="s">
-        <v>685</v>
+        <v>688</v>
       </c>
       <c r="D44" s="5"/>
       <c r="E44" s="5" t="s">
-        <v>686</v>
+        <v>689</v>
       </c>
     </row>
     <row r="45" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -9252,14 +9355,14 @@
         <v>43</v>
       </c>
       <c r="B45" s="5" t="s">
-        <v>687</v>
+        <v>690</v>
       </c>
       <c r="C45" s="5" t="s">
-        <v>688</v>
+        <v>691</v>
       </c>
       <c r="D45" s="5"/>
       <c r="E45" s="5" t="s">
-        <v>689</v>
+        <v>692</v>
       </c>
     </row>
     <row r="46" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -9267,14 +9370,14 @@
         <v>44</v>
       </c>
       <c r="B46" s="5" t="s">
-        <v>690</v>
+        <v>693</v>
       </c>
       <c r="C46" s="5" t="s">
-        <v>691</v>
+        <v>694</v>
       </c>
       <c r="D46" s="5"/>
       <c r="E46" s="5" t="s">
-        <v>692</v>
+        <v>695</v>
       </c>
     </row>
     <row r="47" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -9282,14 +9385,14 @@
         <v>45</v>
       </c>
       <c r="B47" s="5" t="s">
-        <v>693</v>
+        <v>696</v>
       </c>
       <c r="C47" s="5" t="s">
-        <v>694</v>
+        <v>697</v>
       </c>
       <c r="D47" s="5"/>
       <c r="E47" s="5" t="s">
-        <v>695</v>
+        <v>698</v>
       </c>
     </row>
     <row r="48" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -9297,14 +9400,14 @@
         <v>46</v>
       </c>
       <c r="B48" s="5" t="s">
-        <v>696</v>
+        <v>699</v>
       </c>
       <c r="C48" s="5" t="s">
-        <v>697</v>
+        <v>700</v>
       </c>
       <c r="D48" s="5"/>
       <c r="E48" s="5" t="s">
-        <v>698</v>
+        <v>701</v>
       </c>
     </row>
     <row r="49" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -9312,14 +9415,14 @@
         <v>47</v>
       </c>
       <c r="B49" s="5" t="s">
-        <v>699</v>
+        <v>702</v>
       </c>
       <c r="C49" s="5" t="s">
-        <v>700</v>
+        <v>703</v>
       </c>
       <c r="D49" s="5"/>
       <c r="E49" s="5" t="s">
-        <v>701</v>
+        <v>704</v>
       </c>
     </row>
     <row r="50" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -9327,14 +9430,14 @@
         <v>48</v>
       </c>
       <c r="B50" s="5" t="s">
-        <v>702</v>
+        <v>705</v>
       </c>
       <c r="C50" s="5" t="s">
-        <v>703</v>
+        <v>706</v>
       </c>
       <c r="D50" s="5"/>
       <c r="E50" s="5" t="s">
-        <v>704</v>
+        <v>707</v>
       </c>
     </row>
     <row r="51" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -9342,14 +9445,14 @@
         <v>49</v>
       </c>
       <c r="B51" s="5" t="s">
-        <v>705</v>
+        <v>708</v>
       </c>
       <c r="C51" s="5" t="s">
-        <v>706</v>
+        <v>709</v>
       </c>
       <c r="D51" s="5"/>
       <c r="E51" s="5" t="s">
-        <v>707</v>
+        <v>710</v>
       </c>
     </row>
     <row r="52" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -9357,14 +9460,14 @@
         <v>50</v>
       </c>
       <c r="B52" s="5" t="s">
-        <v>708</v>
+        <v>711</v>
       </c>
       <c r="C52" s="5" t="s">
-        <v>709</v>
+        <v>712</v>
       </c>
       <c r="D52" s="5"/>
       <c r="E52" s="5" t="s">
-        <v>710</v>
+        <v>713</v>
       </c>
     </row>
     <row r="53" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -9372,14 +9475,14 @@
         <v>51</v>
       </c>
       <c r="B53" s="5" t="s">
-        <v>711</v>
+        <v>714</v>
       </c>
       <c r="C53" s="5" t="s">
-        <v>712</v>
+        <v>715</v>
       </c>
       <c r="D53" s="5"/>
       <c r="E53" s="5" t="s">
-        <v>713</v>
+        <v>716</v>
       </c>
     </row>
     <row r="54" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -9387,14 +9490,14 @@
         <v>52</v>
       </c>
       <c r="B54" s="5" t="s">
-        <v>613</v>
+        <v>616</v>
       </c>
       <c r="C54" s="5" t="s">
-        <v>714</v>
+        <v>717</v>
       </c>
       <c r="D54" s="5"/>
       <c r="E54" s="5" t="s">
-        <v>715</v>
+        <v>718</v>
       </c>
     </row>
     <row r="55" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -9402,14 +9505,14 @@
         <v>53</v>
       </c>
       <c r="B55" s="5" t="s">
-        <v>716</v>
+        <v>719</v>
       </c>
       <c r="C55" s="5" t="s">
-        <v>717</v>
+        <v>720</v>
       </c>
       <c r="D55" s="5"/>
       <c r="E55" s="5" t="s">
-        <v>718</v>
+        <v>721</v>
       </c>
     </row>
     <row r="56" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -9417,14 +9520,14 @@
         <v>54</v>
       </c>
       <c r="B56" s="5" t="s">
-        <v>719</v>
+        <v>722</v>
       </c>
       <c r="C56" s="5" t="s">
-        <v>720</v>
+        <v>723</v>
       </c>
       <c r="D56" s="5"/>
       <c r="E56" s="5" t="s">
-        <v>721</v>
+        <v>724</v>
       </c>
     </row>
     <row r="57" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -9432,14 +9535,14 @@
         <v>55</v>
       </c>
       <c r="B57" s="5" t="s">
-        <v>722</v>
+        <v>725</v>
       </c>
       <c r="C57" s="5" t="s">
-        <v>723</v>
+        <v>726</v>
       </c>
       <c r="D57" s="5"/>
       <c r="E57" s="5" t="s">
-        <v>724</v>
+        <v>727</v>
       </c>
     </row>
     <row r="58" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -9447,14 +9550,14 @@
         <v>56</v>
       </c>
       <c r="B58" s="5" t="s">
-        <v>725</v>
+        <v>728</v>
       </c>
       <c r="C58" s="5" t="s">
-        <v>726</v>
+        <v>729</v>
       </c>
       <c r="D58" s="5"/>
       <c r="E58" s="5" t="s">
-        <v>727</v>
+        <v>730</v>
       </c>
     </row>
     <row r="59" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -9462,14 +9565,14 @@
         <v>57</v>
       </c>
       <c r="B59" s="5" t="s">
-        <v>728</v>
+        <v>731</v>
       </c>
       <c r="C59" s="5" t="s">
-        <v>729</v>
+        <v>732</v>
       </c>
       <c r="D59" s="5"/>
       <c r="E59" s="5" t="s">
-        <v>730</v>
+        <v>733</v>
       </c>
     </row>
     <row r="60" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -9477,14 +9580,14 @@
         <v>58</v>
       </c>
       <c r="B60" s="5" t="s">
-        <v>731</v>
+        <v>734</v>
       </c>
       <c r="C60" s="5" t="s">
-        <v>732</v>
+        <v>735</v>
       </c>
       <c r="D60" s="5"/>
       <c r="E60" s="5" t="s">
-        <v>733</v>
+        <v>736</v>
       </c>
     </row>
     <row r="61" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -9492,14 +9595,14 @@
         <v>59</v>
       </c>
       <c r="B61" s="5" t="s">
-        <v>734</v>
+        <v>737</v>
       </c>
       <c r="C61" s="5" t="s">
-        <v>735</v>
+        <v>738</v>
       </c>
       <c r="D61" s="5"/>
       <c r="E61" s="5" t="s">
-        <v>736</v>
+        <v>739</v>
       </c>
     </row>
     <row r="62" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -9507,14 +9610,14 @@
         <v>60</v>
       </c>
       <c r="B62" s="5" t="s">
-        <v>737</v>
+        <v>740</v>
       </c>
       <c r="C62" s="5" t="s">
-        <v>738</v>
+        <v>741</v>
       </c>
       <c r="D62" s="5"/>
       <c r="E62" s="5" t="s">
-        <v>739</v>
+        <v>742</v>
       </c>
     </row>
     <row r="63" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -9522,14 +9625,14 @@
         <v>61</v>
       </c>
       <c r="B63" s="5" t="s">
-        <v>740</v>
+        <v>743</v>
       </c>
       <c r="C63" s="5" t="s">
-        <v>741</v>
+        <v>744</v>
       </c>
       <c r="D63" s="5"/>
       <c r="E63" s="5" t="s">
-        <v>742</v>
+        <v>745</v>
       </c>
     </row>
     <row r="64" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -9537,14 +9640,14 @@
         <v>62</v>
       </c>
       <c r="B64" s="5" t="s">
-        <v>743</v>
+        <v>746</v>
       </c>
       <c r="C64" s="5" t="s">
-        <v>744</v>
+        <v>747</v>
       </c>
       <c r="D64" s="5"/>
       <c r="E64" s="5" t="s">
-        <v>745</v>
+        <v>748</v>
       </c>
     </row>
     <row r="65" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -9552,14 +9655,14 @@
         <v>63</v>
       </c>
       <c r="B65" s="5" t="s">
-        <v>746</v>
+        <v>749</v>
       </c>
       <c r="C65" s="5" t="s">
-        <v>747</v>
+        <v>750</v>
       </c>
       <c r="D65" s="5"/>
       <c r="E65" s="5" t="s">
-        <v>748</v>
+        <v>751</v>
       </c>
     </row>
     <row r="66" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -9567,14 +9670,14 @@
         <v>64</v>
       </c>
       <c r="B66" s="5" t="s">
-        <v>749</v>
+        <v>752</v>
       </c>
       <c r="C66" s="5" t="s">
-        <v>750</v>
+        <v>753</v>
       </c>
       <c r="D66" s="5"/>
       <c r="E66" s="5" t="s">
-        <v>751</v>
+        <v>754</v>
       </c>
     </row>
     <row r="67" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -9582,14 +9685,14 @@
         <v>65</v>
       </c>
       <c r="B67" s="5" t="s">
-        <v>752</v>
+        <v>755</v>
       </c>
       <c r="C67" s="5" t="s">
-        <v>753</v>
+        <v>756</v>
       </c>
       <c r="D67" s="5"/>
       <c r="E67" s="5" t="s">
-        <v>754</v>
+        <v>757</v>
       </c>
     </row>
     <row r="68" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -9597,14 +9700,14 @@
         <v>66</v>
       </c>
       <c r="B68" s="5" t="s">
-        <v>755</v>
+        <v>758</v>
       </c>
       <c r="C68" s="5" t="s">
-        <v>756</v>
+        <v>759</v>
       </c>
       <c r="D68" s="5"/>
       <c r="E68" s="5" t="s">
-        <v>757</v>
+        <v>760</v>
       </c>
     </row>
     <row r="69" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -9612,14 +9715,14 @@
         <v>67</v>
       </c>
       <c r="B69" s="5" t="s">
-        <v>758</v>
+        <v>761</v>
       </c>
       <c r="C69" s="5" t="s">
-        <v>759</v>
+        <v>762</v>
       </c>
       <c r="D69" s="5"/>
       <c r="E69" s="5" t="s">
-        <v>760</v>
+        <v>763</v>
       </c>
     </row>
     <row r="70" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -9627,14 +9730,14 @@
         <v>68</v>
       </c>
       <c r="B70" s="5" t="s">
-        <v>761</v>
+        <v>764</v>
       </c>
       <c r="C70" s="5" t="s">
-        <v>762</v>
+        <v>765</v>
       </c>
       <c r="D70" s="5"/>
       <c r="E70" s="5" t="s">
-        <v>763</v>
+        <v>766</v>
       </c>
     </row>
     <row r="71" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -9642,14 +9745,14 @@
         <v>69</v>
       </c>
       <c r="B71" s="5" t="s">
-        <v>764</v>
+        <v>767</v>
       </c>
       <c r="C71" s="5" t="s">
-        <v>765</v>
+        <v>768</v>
       </c>
       <c r="D71" s="5"/>
       <c r="E71" s="5" t="s">
-        <v>766</v>
+        <v>769</v>
       </c>
     </row>
     <row r="72" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -9657,14 +9760,14 @@
         <v>70</v>
       </c>
       <c r="B72" s="5" t="s">
-        <v>767</v>
+        <v>770</v>
       </c>
       <c r="C72" s="5" t="s">
-        <v>768</v>
+        <v>771</v>
       </c>
       <c r="D72" s="5"/>
       <c r="E72" s="5" t="s">
-        <v>769</v>
+        <v>772</v>
       </c>
     </row>
     <row r="73" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -9672,14 +9775,14 @@
         <v>71</v>
       </c>
       <c r="B73" s="5" t="s">
-        <v>770</v>
+        <v>773</v>
       </c>
       <c r="C73" s="5" t="s">
-        <v>771</v>
+        <v>774</v>
       </c>
       <c r="D73" s="5"/>
       <c r="E73" s="5" t="s">
-        <v>772</v>
+        <v>775</v>
       </c>
     </row>
     <row r="74" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -9687,14 +9790,14 @@
         <v>72</v>
       </c>
       <c r="B74" s="5" t="s">
-        <v>773</v>
+        <v>776</v>
       </c>
       <c r="C74" s="5" t="s">
-        <v>774</v>
+        <v>777</v>
       </c>
       <c r="D74" s="5"/>
       <c r="E74" s="5" t="s">
-        <v>775</v>
+        <v>778</v>
       </c>
     </row>
     <row r="75" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -9702,14 +9805,14 @@
         <v>73</v>
       </c>
       <c r="B75" s="5" t="s">
-        <v>613</v>
+        <v>616</v>
       </c>
       <c r="C75" s="5" t="s">
-        <v>776</v>
+        <v>779</v>
       </c>
       <c r="D75" s="5"/>
       <c r="E75" s="5" t="s">
-        <v>777</v>
+        <v>780</v>
       </c>
     </row>
     <row r="76" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -9717,14 +9820,14 @@
         <v>74</v>
       </c>
       <c r="B76" s="5" t="s">
-        <v>778</v>
+        <v>781</v>
       </c>
       <c r="C76" s="5" t="s">
-        <v>779</v>
+        <v>782</v>
       </c>
       <c r="D76" s="5"/>
       <c r="E76" s="5" t="s">
-        <v>780</v>
+        <v>783</v>
       </c>
     </row>
     <row r="77" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -9732,14 +9835,14 @@
         <v>75</v>
       </c>
       <c r="B77" s="5" t="s">
-        <v>613</v>
+        <v>616</v>
       </c>
       <c r="C77" s="5" t="s">
-        <v>781</v>
+        <v>784</v>
       </c>
       <c r="D77" s="5"/>
       <c r="E77" s="5" t="s">
-        <v>782</v>
+        <v>785</v>
       </c>
     </row>
     <row r="78" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -9747,14 +9850,14 @@
         <v>76</v>
       </c>
       <c r="B78" s="5" t="s">
-        <v>783</v>
+        <v>786</v>
       </c>
       <c r="C78" s="5" t="s">
-        <v>784</v>
+        <v>787</v>
       </c>
       <c r="D78" s="5"/>
       <c r="E78" s="5" t="s">
-        <v>785</v>
+        <v>788</v>
       </c>
     </row>
     <row r="79" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -9762,14 +9865,14 @@
         <v>77</v>
       </c>
       <c r="B79" s="5" t="s">
-        <v>786</v>
+        <v>789</v>
       </c>
       <c r="C79" s="5" t="s">
-        <v>787</v>
+        <v>790</v>
       </c>
       <c r="D79" s="5"/>
       <c r="E79" s="5" t="s">
-        <v>788</v>
+        <v>791</v>
       </c>
     </row>
     <row r="80" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -9777,14 +9880,14 @@
         <v>78</v>
       </c>
       <c r="B80" s="5" t="s">
-        <v>711</v>
+        <v>714</v>
       </c>
       <c r="C80" s="5" t="s">
-        <v>789</v>
+        <v>792</v>
       </c>
       <c r="D80" s="5"/>
       <c r="E80" s="5" t="s">
-        <v>790</v>
+        <v>793</v>
       </c>
     </row>
     <row r="81" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -9792,14 +9895,14 @@
         <v>79</v>
       </c>
       <c r="B81" s="5" t="s">
-        <v>583</v>
+        <v>586</v>
       </c>
       <c r="C81" s="5" t="s">
-        <v>791</v>
+        <v>794</v>
       </c>
       <c r="D81" s="5"/>
       <c r="E81" s="5" t="s">
-        <v>792</v>
+        <v>795</v>
       </c>
     </row>
     <row r="82" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -9807,16 +9910,16 @@
         <v>80</v>
       </c>
       <c r="B82" s="5" t="s">
-        <v>793</v>
+        <v>796</v>
       </c>
       <c r="C82" s="5" t="s">
-        <v>794</v>
+        <v>797</v>
       </c>
       <c r="D82" s="6" t="s">
-        <v>795</v>
+        <v>798</v>
       </c>
       <c r="E82" s="5" t="s">
-        <v>796</v>
+        <v>799</v>
       </c>
     </row>
     <row r="83" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -9824,16 +9927,16 @@
         <v>81</v>
       </c>
       <c r="B83" s="5" t="s">
-        <v>797</v>
+        <v>800</v>
       </c>
       <c r="C83" s="5" t="s">
-        <v>798</v>
+        <v>801</v>
       </c>
       <c r="D83" s="6" t="s">
-        <v>799</v>
+        <v>802</v>
       </c>
       <c r="E83" s="5" t="s">
-        <v>800</v>
+        <v>803</v>
       </c>
     </row>
     <row r="84" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -9841,13 +9944,13 @@
         <v>82</v>
       </c>
       <c r="B84" s="5" t="s">
-        <v>801</v>
+        <v>804</v>
       </c>
       <c r="C84" s="5" t="s">
-        <v>802</v>
+        <v>805</v>
       </c>
       <c r="D84" s="6" t="s">
-        <v>803</v>
+        <v>806</v>
       </c>
       <c r="E84" s="5" t="s">
         <v>297</v>
@@ -9858,13 +9961,13 @@
         <v>83</v>
       </c>
       <c r="B85" s="5" t="s">
-        <v>804</v>
+        <v>807</v>
       </c>
       <c r="C85" s="5" t="s">
-        <v>805</v>
+        <v>808</v>
       </c>
       <c r="D85" s="6" t="s">
-        <v>806</v>
+        <v>809</v>
       </c>
       <c r="E85" s="5" t="s">
         <v>300</v>
@@ -9875,16 +9978,16 @@
         <v>84</v>
       </c>
       <c r="B86" s="5" t="s">
-        <v>807</v>
+        <v>810</v>
       </c>
       <c r="C86" s="5" t="s">
-        <v>808</v>
+        <v>811</v>
       </c>
       <c r="D86" s="6" t="s">
-        <v>809</v>
+        <v>812</v>
       </c>
       <c r="E86" s="5" t="s">
-        <v>810</v>
+        <v>813</v>
       </c>
     </row>
     <row r="87" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -9892,16 +9995,16 @@
         <v>85</v>
       </c>
       <c r="B87" s="5" t="s">
-        <v>811</v>
+        <v>814</v>
       </c>
       <c r="C87" s="5" t="s">
-        <v>812</v>
+        <v>815</v>
       </c>
       <c r="D87" s="6" t="s">
-        <v>813</v>
+        <v>816</v>
       </c>
       <c r="E87" s="5" t="s">
-        <v>814</v>
+        <v>817</v>
       </c>
     </row>
     <row r="88" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -9909,16 +10012,16 @@
         <v>86</v>
       </c>
       <c r="B88" s="5" t="s">
-        <v>815</v>
+        <v>818</v>
       </c>
       <c r="C88" s="5" t="s">
-        <v>816</v>
+        <v>819</v>
       </c>
       <c r="D88" s="6" t="s">
+        <v>820</v>
+      </c>
+      <c r="E88" s="5" t="s">
         <v>817</v>
-      </c>
-      <c r="E88" s="5" t="s">
-        <v>814</v>
       </c>
     </row>
     <row r="89" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -9926,16 +10029,16 @@
         <v>87</v>
       </c>
       <c r="B89" s="5" t="s">
-        <v>818</v>
+        <v>821</v>
       </c>
       <c r="C89" s="5" t="s">
-        <v>819</v>
+        <v>822</v>
       </c>
       <c r="D89" s="6" t="s">
-        <v>820</v>
+        <v>823</v>
       </c>
       <c r="E89" s="5" t="s">
-        <v>814</v>
+        <v>817</v>
       </c>
     </row>
     <row r="90" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -9943,16 +10046,16 @@
         <v>88</v>
       </c>
       <c r="B90" s="5" t="s">
-        <v>821</v>
+        <v>824</v>
       </c>
       <c r="C90" s="5" t="s">
-        <v>822</v>
+        <v>825</v>
       </c>
       <c r="D90" s="6" t="s">
-        <v>823</v>
+        <v>826</v>
       </c>
       <c r="E90" s="5" t="s">
-        <v>824</v>
+        <v>827</v>
       </c>
     </row>
     <row r="91" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -9960,16 +10063,16 @@
         <v>89</v>
       </c>
       <c r="B91" s="5" t="s">
-        <v>825</v>
+        <v>828</v>
       </c>
       <c r="C91" s="5" t="s">
-        <v>826</v>
+        <v>829</v>
       </c>
       <c r="D91" s="6" t="s">
+        <v>830</v>
+      </c>
+      <c r="E91" s="5" t="s">
         <v>827</v>
-      </c>
-      <c r="E91" s="5" t="s">
-        <v>824</v>
       </c>
     </row>
     <row r="92" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -9977,16 +10080,16 @@
         <v>90</v>
       </c>
       <c r="B92" s="5" t="s">
-        <v>815</v>
+        <v>818</v>
       </c>
       <c r="C92" s="5" t="s">
-        <v>828</v>
+        <v>831</v>
       </c>
       <c r="D92" s="6" t="s">
-        <v>829</v>
+        <v>832</v>
       </c>
       <c r="E92" s="5" t="s">
-        <v>830</v>
+        <v>833</v>
       </c>
     </row>
     <row r="93" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -9994,16 +10097,16 @@
         <v>91</v>
       </c>
       <c r="B93" s="5" t="s">
-        <v>831</v>
+        <v>834</v>
       </c>
       <c r="C93" s="5" t="s">
-        <v>832</v>
+        <v>835</v>
       </c>
       <c r="D93" s="6" t="s">
+        <v>836</v>
+      </c>
+      <c r="E93" s="5" t="s">
         <v>833</v>
-      </c>
-      <c r="E93" s="5" t="s">
-        <v>830</v>
       </c>
     </row>
     <row r="94" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -10011,16 +10114,16 @@
         <v>92</v>
       </c>
       <c r="B94" s="5" t="s">
-        <v>834</v>
+        <v>837</v>
       </c>
       <c r="C94" s="5" t="s">
-        <v>835</v>
+        <v>838</v>
       </c>
       <c r="D94" s="6" t="s">
-        <v>836</v>
+        <v>839</v>
       </c>
       <c r="E94" s="5" t="s">
-        <v>837</v>
+        <v>840</v>
       </c>
     </row>
     <row r="95" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -10028,16 +10131,16 @@
         <v>93</v>
       </c>
       <c r="B95" s="5" t="s">
-        <v>676</v>
+        <v>679</v>
       </c>
       <c r="C95" s="5" t="s">
-        <v>838</v>
+        <v>841</v>
       </c>
       <c r="D95" s="6" t="s">
-        <v>839</v>
+        <v>842</v>
       </c>
       <c r="E95" s="5" t="s">
-        <v>840</v>
+        <v>843</v>
       </c>
     </row>
     <row r="96" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -10045,16 +10148,16 @@
         <v>94</v>
       </c>
       <c r="B96" s="5" t="s">
-        <v>821</v>
+        <v>824</v>
       </c>
       <c r="C96" s="5" t="s">
-        <v>841</v>
+        <v>844</v>
       </c>
       <c r="D96" s="6" t="s">
-        <v>842</v>
+        <v>845</v>
       </c>
       <c r="E96" s="5" t="s">
-        <v>840</v>
+        <v>843</v>
       </c>
     </row>
     <row r="97" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -10062,16 +10165,16 @@
         <v>95</v>
       </c>
       <c r="B97" s="5" t="s">
+        <v>846</v>
+      </c>
+      <c r="C97" s="5" t="s">
+        <v>847</v>
+      </c>
+      <c r="D97" s="6" t="s">
+        <v>848</v>
+      </c>
+      <c r="E97" s="5" t="s">
         <v>843</v>
-      </c>
-      <c r="C97" s="5" t="s">
-        <v>844</v>
-      </c>
-      <c r="D97" s="6" t="s">
-        <v>845</v>
-      </c>
-      <c r="E97" s="5" t="s">
-        <v>840</v>
       </c>
     </row>
     <row r="98" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -10079,16 +10182,16 @@
         <v>96</v>
       </c>
       <c r="B98" s="5" t="s">
-        <v>801</v>
+        <v>804</v>
       </c>
       <c r="C98" s="5" t="s">
-        <v>846</v>
+        <v>849</v>
       </c>
       <c r="D98" s="6" t="s">
-        <v>847</v>
+        <v>850</v>
       </c>
       <c r="E98" s="5" t="s">
-        <v>830</v>
+        <v>833</v>
       </c>
     </row>
     <row r="99" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -10096,16 +10199,16 @@
         <v>97</v>
       </c>
       <c r="B99" s="5" t="s">
-        <v>848</v>
+        <v>851</v>
       </c>
       <c r="C99" s="5" t="s">
-        <v>849</v>
+        <v>852</v>
       </c>
       <c r="D99" s="6" t="s">
-        <v>850</v>
+        <v>853</v>
       </c>
       <c r="E99" s="5" t="s">
-        <v>851</v>
+        <v>854</v>
       </c>
     </row>
     <row r="100" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -10113,16 +10216,16 @@
         <v>98</v>
       </c>
       <c r="B100" s="5" t="s">
-        <v>815</v>
+        <v>818</v>
       </c>
       <c r="C100" s="5" t="s">
-        <v>852</v>
+        <v>855</v>
       </c>
       <c r="D100" s="6" t="s">
-        <v>853</v>
+        <v>856</v>
       </c>
       <c r="E100" s="5" t="s">
-        <v>854</v>
+        <v>857</v>
       </c>
     </row>
     <row r="101" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -10130,16 +10233,16 @@
         <v>99</v>
       </c>
       <c r="B101" s="5" t="s">
-        <v>821</v>
+        <v>824</v>
       </c>
       <c r="C101" s="5" t="s">
-        <v>855</v>
+        <v>858</v>
       </c>
       <c r="D101" s="6" t="s">
-        <v>856</v>
+        <v>859</v>
       </c>
       <c r="E101" s="5" t="s">
-        <v>857</v>
+        <v>860</v>
       </c>
     </row>
     <row r="102" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -10147,16 +10250,16 @@
         <v>100</v>
       </c>
       <c r="B102" s="5" t="s">
-        <v>858</v>
+        <v>861</v>
       </c>
       <c r="C102" s="5" t="s">
-        <v>859</v>
+        <v>862</v>
       </c>
       <c r="D102" s="6" t="s">
-        <v>860</v>
+        <v>863</v>
       </c>
       <c r="E102" s="5" t="s">
-        <v>861</v>
+        <v>864</v>
       </c>
     </row>
     <row r="103" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -10164,16 +10267,16 @@
         <v>101</v>
       </c>
       <c r="B103" s="5" t="s">
-        <v>801</v>
+        <v>804</v>
       </c>
       <c r="C103" s="5" t="s">
-        <v>862</v>
+        <v>865</v>
       </c>
       <c r="D103" s="6" t="s">
-        <v>863</v>
+        <v>866</v>
       </c>
       <c r="E103" s="5" t="s">
-        <v>864</v>
+        <v>867</v>
       </c>
     </row>
     <row r="104" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -10181,13 +10284,13 @@
         <v>102</v>
       </c>
       <c r="B104" s="5" t="s">
-        <v>676</v>
+        <v>679</v>
       </c>
       <c r="C104" s="5" t="s">
-        <v>865</v>
+        <v>868</v>
       </c>
       <c r="D104" s="6" t="s">
-        <v>866</v>
+        <v>869</v>
       </c>
       <c r="E104" s="5" t="s">
         <v>352</v>
@@ -10198,16 +10301,16 @@
         <v>103</v>
       </c>
       <c r="B105" s="5" t="s">
-        <v>867</v>
+        <v>870</v>
       </c>
       <c r="C105" s="5" t="s">
-        <v>868</v>
+        <v>871</v>
       </c>
       <c r="D105" s="6" t="s">
-        <v>869</v>
+        <v>872</v>
       </c>
       <c r="E105" s="5" t="s">
-        <v>870</v>
+        <v>873</v>
       </c>
     </row>
     <row r="106" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -10215,16 +10318,16 @@
         <v>104</v>
       </c>
       <c r="B106" s="5" t="s">
-        <v>871</v>
+        <v>874</v>
       </c>
       <c r="C106" s="5" t="s">
-        <v>872</v>
+        <v>875</v>
       </c>
       <c r="D106" s="6" t="s">
-        <v>873</v>
+        <v>876</v>
       </c>
       <c r="E106" s="5" t="s">
-        <v>874</v>
+        <v>877</v>
       </c>
     </row>
     <row r="107" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -10232,16 +10335,16 @@
         <v>105</v>
       </c>
       <c r="B107" s="5" t="s">
-        <v>875</v>
+        <v>878</v>
       </c>
       <c r="C107" s="5" t="s">
-        <v>876</v>
+        <v>879</v>
       </c>
       <c r="D107" s="6" t="s">
-        <v>877</v>
+        <v>880</v>
       </c>
       <c r="E107" s="5" t="s">
-        <v>878</v>
+        <v>881</v>
       </c>
     </row>
     <row r="108" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -10249,16 +10352,16 @@
         <v>106</v>
       </c>
       <c r="B108" s="5" t="s">
-        <v>871</v>
+        <v>874</v>
       </c>
       <c r="C108" s="5" t="s">
-        <v>879</v>
+        <v>882</v>
       </c>
       <c r="D108" s="6" t="s">
-        <v>880</v>
+        <v>883</v>
       </c>
       <c r="E108" s="5" t="s">
-        <v>881</v>
+        <v>884</v>
       </c>
     </row>
     <row r="109" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -10266,13 +10369,13 @@
         <v>107</v>
       </c>
       <c r="B109" s="5" t="s">
-        <v>882</v>
+        <v>885</v>
       </c>
       <c r="C109" s="5" t="s">
-        <v>883</v>
+        <v>886</v>
       </c>
       <c r="D109" s="6" t="s">
-        <v>884</v>
+        <v>887</v>
       </c>
       <c r="E109" s="5" t="s">
         <v>368</v>
@@ -10283,13 +10386,13 @@
         <v>108</v>
       </c>
       <c r="B110" s="5" t="s">
-        <v>676</v>
+        <v>679</v>
       </c>
       <c r="C110" s="5" t="s">
-        <v>885</v>
+        <v>888</v>
       </c>
       <c r="D110" s="6" t="s">
-        <v>886</v>
+        <v>889</v>
       </c>
       <c r="E110" s="5" t="s">
         <v>368</v>
@@ -10300,16 +10403,16 @@
         <v>109</v>
       </c>
       <c r="B111" s="5" t="s">
-        <v>875</v>
+        <v>878</v>
       </c>
       <c r="C111" s="5" t="s">
-        <v>887</v>
+        <v>890</v>
       </c>
       <c r="D111" s="6" t="s">
-        <v>888</v>
+        <v>891</v>
       </c>
       <c r="E111" s="5" t="s">
-        <v>889</v>
+        <v>892</v>
       </c>
     </row>
     <row r="112" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -10317,16 +10420,16 @@
         <v>110</v>
       </c>
       <c r="B112" s="5" t="s">
-        <v>815</v>
+        <v>818</v>
       </c>
       <c r="C112" s="5" t="s">
-        <v>890</v>
+        <v>893</v>
       </c>
       <c r="D112" s="6" t="s">
-        <v>891</v>
+        <v>894</v>
       </c>
       <c r="E112" s="5" t="s">
-        <v>892</v>
+        <v>895</v>
       </c>
     </row>
     <row r="113" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -10334,13 +10437,13 @@
         <v>111</v>
       </c>
       <c r="B113" s="5" t="s">
-        <v>807</v>
+        <v>810</v>
       </c>
       <c r="C113" s="5" t="s">
-        <v>893</v>
+        <v>896</v>
       </c>
       <c r="D113" s="6" t="s">
-        <v>894</v>
+        <v>897</v>
       </c>
       <c r="E113" s="5" t="s">
         <v>382</v>
@@ -10351,16 +10454,16 @@
         <v>112</v>
       </c>
       <c r="B114" s="5" t="s">
-        <v>815</v>
+        <v>818</v>
       </c>
       <c r="C114" s="5" t="s">
-        <v>895</v>
+        <v>898</v>
       </c>
       <c r="D114" s="6" t="s">
-        <v>896</v>
+        <v>899</v>
       </c>
       <c r="E114" s="5" t="s">
-        <v>897</v>
+        <v>900</v>
       </c>
     </row>
     <row r="115" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -10368,16 +10471,16 @@
         <v>113</v>
       </c>
       <c r="B115" s="5" t="s">
-        <v>898</v>
+        <v>901</v>
       </c>
       <c r="C115" s="5" t="s">
-        <v>899</v>
+        <v>902</v>
       </c>
       <c r="D115" s="6" t="s">
-        <v>900</v>
+        <v>903</v>
       </c>
       <c r="E115" s="5" t="s">
-        <v>901</v>
+        <v>904</v>
       </c>
     </row>
     <row r="116" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -10385,16 +10488,16 @@
         <v>114</v>
       </c>
       <c r="B116" s="5" t="s">
-        <v>821</v>
+        <v>824</v>
       </c>
       <c r="C116" s="5" t="s">
-        <v>902</v>
+        <v>905</v>
       </c>
       <c r="D116" s="6" t="s">
-        <v>903</v>
+        <v>906</v>
       </c>
       <c r="E116" s="5" t="s">
-        <v>901</v>
+        <v>904</v>
       </c>
     </row>
     <row r="117" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -10402,16 +10505,16 @@
         <v>115</v>
       </c>
       <c r="B117" s="5" t="s">
-        <v>904</v>
+        <v>907</v>
       </c>
       <c r="C117" s="5" t="s">
-        <v>905</v>
+        <v>908</v>
       </c>
       <c r="D117" s="6" t="s">
-        <v>906</v>
+        <v>909</v>
       </c>
       <c r="E117" s="5" t="s">
-        <v>907</v>
+        <v>910</v>
       </c>
     </row>
     <row r="118" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -10419,13 +10522,13 @@
         <v>116</v>
       </c>
       <c r="B118" s="5" t="s">
-        <v>821</v>
+        <v>824</v>
       </c>
       <c r="C118" s="5" t="s">
-        <v>908</v>
+        <v>911</v>
       </c>
       <c r="D118" s="6" t="s">
-        <v>909</v>
+        <v>912</v>
       </c>
       <c r="E118" s="5" t="s">
         <v>396</v>
@@ -10436,16 +10539,16 @@
         <v>117</v>
       </c>
       <c r="B119" s="5" t="s">
-        <v>910</v>
+        <v>913</v>
       </c>
       <c r="C119" s="5" t="s">
-        <v>911</v>
+        <v>914</v>
       </c>
       <c r="D119" s="6" t="s">
-        <v>912</v>
+        <v>915</v>
       </c>
       <c r="E119" s="5" t="s">
-        <v>913</v>
+        <v>916</v>
       </c>
     </row>
     <row r="120" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -10453,16 +10556,16 @@
         <v>118</v>
       </c>
       <c r="B120" s="5" t="s">
-        <v>898</v>
+        <v>901</v>
       </c>
       <c r="C120" s="5" t="s">
-        <v>914</v>
+        <v>917</v>
       </c>
       <c r="D120" s="6" t="s">
-        <v>915</v>
+        <v>918</v>
       </c>
       <c r="E120" s="5" t="s">
-        <v>916</v>
+        <v>919</v>
       </c>
     </row>
     <row r="121" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -10470,16 +10573,16 @@
         <v>119</v>
       </c>
       <c r="B121" s="5" t="s">
-        <v>917</v>
+        <v>920</v>
       </c>
       <c r="C121" s="5" t="s">
-        <v>918</v>
+        <v>921</v>
       </c>
       <c r="D121" s="6" t="s">
-        <v>919</v>
+        <v>922</v>
       </c>
       <c r="E121" s="5" t="s">
-        <v>913</v>
+        <v>916</v>
       </c>
     </row>
     <row r="122" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -10487,16 +10590,16 @@
         <v>120</v>
       </c>
       <c r="B122" s="5" t="s">
-        <v>920</v>
+        <v>923</v>
       </c>
       <c r="C122" s="5" t="s">
-        <v>921</v>
+        <v>924</v>
       </c>
       <c r="D122" s="6" t="s">
-        <v>922</v>
+        <v>925</v>
       </c>
       <c r="E122" s="5" t="s">
-        <v>923</v>
+        <v>926</v>
       </c>
     </row>
     <row r="123" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -10504,13 +10607,13 @@
         <v>121</v>
       </c>
       <c r="B123" s="5" t="s">
-        <v>821</v>
+        <v>824</v>
       </c>
       <c r="C123" s="5" t="s">
-        <v>924</v>
+        <v>927</v>
       </c>
       <c r="D123" s="6" t="s">
-        <v>925</v>
+        <v>928</v>
       </c>
       <c r="E123" s="5" t="s">
         <v>409</v>
@@ -10521,13 +10624,13 @@
         <v>122</v>
       </c>
       <c r="B124" s="5" t="s">
-        <v>882</v>
+        <v>885</v>
       </c>
       <c r="C124" s="5" t="s">
-        <v>926</v>
+        <v>929</v>
       </c>
       <c r="D124" s="6" t="s">
-        <v>927</v>
+        <v>930</v>
       </c>
       <c r="E124" s="5" t="s">
         <v>409</v>
@@ -10538,16 +10641,16 @@
         <v>123</v>
       </c>
       <c r="B125" s="5" t="s">
-        <v>848</v>
+        <v>851</v>
       </c>
       <c r="C125" s="5" t="s">
-        <v>928</v>
+        <v>931</v>
       </c>
       <c r="D125" s="6" t="s">
-        <v>929</v>
+        <v>932</v>
       </c>
       <c r="E125" s="5" t="s">
-        <v>930</v>
+        <v>933</v>
       </c>
     </row>
     <row r="126" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -10555,16 +10658,16 @@
         <v>124</v>
       </c>
       <c r="B126" s="5" t="s">
-        <v>931</v>
+        <v>934</v>
       </c>
       <c r="C126" s="5" t="s">
-        <v>932</v>
+        <v>935</v>
       </c>
       <c r="D126" s="6" t="s">
+        <v>936</v>
+      </c>
+      <c r="E126" s="5" t="s">
         <v>933</v>
-      </c>
-      <c r="E126" s="5" t="s">
-        <v>930</v>
       </c>
     </row>
     <row r="127" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -10572,16 +10675,16 @@
         <v>125</v>
       </c>
       <c r="B127" s="5" t="s">
-        <v>867</v>
+        <v>870</v>
       </c>
       <c r="C127" s="5" t="s">
-        <v>934</v>
+        <v>937</v>
       </c>
       <c r="D127" s="6" t="s">
-        <v>935</v>
+        <v>938</v>
       </c>
       <c r="E127" s="5" t="s">
-        <v>936</v>
+        <v>939</v>
       </c>
     </row>
     <row r="128" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -10589,16 +10692,16 @@
         <v>126</v>
       </c>
       <c r="B128" s="5" t="s">
-        <v>937</v>
+        <v>940</v>
       </c>
       <c r="C128" s="5" t="s">
-        <v>938</v>
+        <v>941</v>
       </c>
       <c r="D128" s="6" t="s">
-        <v>939</v>
+        <v>942</v>
       </c>
       <c r="E128" s="5" t="s">
-        <v>940</v>
+        <v>943</v>
       </c>
     </row>
     <row r="129" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -10606,16 +10709,16 @@
         <v>127</v>
       </c>
       <c r="B129" s="5" t="s">
-        <v>941</v>
+        <v>944</v>
       </c>
       <c r="C129" s="5" t="s">
-        <v>942</v>
+        <v>945</v>
       </c>
       <c r="D129" s="6" t="s">
-        <v>943</v>
+        <v>946</v>
       </c>
       <c r="E129" s="5" t="s">
-        <v>944</v>
+        <v>947</v>
       </c>
     </row>
     <row r="130" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -10623,16 +10726,16 @@
         <v>128</v>
       </c>
       <c r="B130" s="5" t="s">
-        <v>945</v>
+        <v>948</v>
       </c>
       <c r="C130" s="5" t="s">
+        <v>949</v>
+      </c>
+      <c r="D130" s="6" t="s">
         <v>946</v>
       </c>
-      <c r="D130" s="6" t="s">
-        <v>943</v>
-      </c>
       <c r="E130" s="5" t="s">
-        <v>947</v>
+        <v>950</v>
       </c>
     </row>
     <row r="131" customFormat="false" ht="34.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -10640,13 +10743,13 @@
         <v>129</v>
       </c>
       <c r="B131" s="5" t="s">
-        <v>948</v>
+        <v>951</v>
       </c>
       <c r="C131" s="5" t="s">
-        <v>949</v>
+        <v>952</v>
       </c>
       <c r="D131" s="6" t="s">
-        <v>943</v>
+        <v>946</v>
       </c>
       <c r="E131" s="5" t="s">
         <v>434</v>
@@ -10657,16 +10760,16 @@
         <v>130</v>
       </c>
       <c r="B132" s="5" t="s">
-        <v>950</v>
+        <v>953</v>
       </c>
       <c r="C132" s="5" t="s">
-        <v>951</v>
+        <v>954</v>
       </c>
       <c r="D132" s="6" t="s">
-        <v>952</v>
+        <v>955</v>
       </c>
       <c r="E132" s="5" t="s">
-        <v>953</v>
+        <v>956</v>
       </c>
     </row>
     <row r="133" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -10674,16 +10777,16 @@
         <v>131</v>
       </c>
       <c r="B133" s="5" t="s">
-        <v>954</v>
+        <v>957</v>
       </c>
       <c r="C133" s="5" t="s">
-        <v>955</v>
+        <v>958</v>
       </c>
       <c r="D133" s="6" t="s">
+        <v>959</v>
+      </c>
+      <c r="E133" s="5" t="s">
         <v>956</v>
-      </c>
-      <c r="E133" s="5" t="s">
-        <v>953</v>
       </c>
     </row>
     <row r="134" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -10691,16 +10794,16 @@
         <v>132</v>
       </c>
       <c r="B134" s="5" t="s">
-        <v>957</v>
+        <v>960</v>
       </c>
       <c r="C134" s="5" t="s">
-        <v>958</v>
+        <v>961</v>
       </c>
       <c r="D134" s="6" t="s">
-        <v>959</v>
+        <v>962</v>
       </c>
       <c r="E134" s="5" t="s">
-        <v>960</v>
+        <v>963</v>
       </c>
     </row>
     <row r="135" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -10708,16 +10811,16 @@
         <v>133</v>
       </c>
       <c r="B135" s="5" t="s">
-        <v>961</v>
+        <v>964</v>
       </c>
       <c r="C135" s="5" t="s">
-        <v>962</v>
+        <v>965</v>
       </c>
       <c r="D135" s="6" t="s">
-        <v>963</v>
+        <v>966</v>
       </c>
       <c r="E135" s="5" t="s">
-        <v>964</v>
+        <v>967</v>
       </c>
     </row>
     <row r="136" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -10725,13 +10828,13 @@
         <v>134</v>
       </c>
       <c r="B136" s="5" t="s">
-        <v>676</v>
+        <v>679</v>
       </c>
       <c r="C136" s="5" t="s">
-        <v>965</v>
+        <v>968</v>
       </c>
       <c r="D136" s="6" t="s">
-        <v>966</v>
+        <v>969</v>
       </c>
       <c r="E136" s="5" t="s">
         <v>451</v>
@@ -10742,13 +10845,13 @@
         <v>135</v>
       </c>
       <c r="B137" s="5" t="s">
-        <v>967</v>
+        <v>970</v>
       </c>
       <c r="C137" s="5" t="s">
-        <v>968</v>
+        <v>971</v>
       </c>
       <c r="D137" s="6" t="s">
-        <v>969</v>
+        <v>972</v>
       </c>
       <c r="E137" s="5" t="s">
         <v>451</v>
@@ -10759,16 +10862,16 @@
         <v>136</v>
       </c>
       <c r="B138" s="5" t="s">
-        <v>970</v>
+        <v>973</v>
       </c>
       <c r="C138" s="5" t="s">
-        <v>971</v>
+        <v>974</v>
       </c>
       <c r="D138" s="6" t="s">
-        <v>972</v>
+        <v>975</v>
       </c>
       <c r="E138" s="5" t="s">
-        <v>973</v>
+        <v>976</v>
       </c>
     </row>
     <row r="139" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -10776,16 +10879,16 @@
         <v>137</v>
       </c>
       <c r="B139" s="5" t="s">
-        <v>974</v>
+        <v>977</v>
       </c>
       <c r="C139" s="5" t="s">
-        <v>975</v>
+        <v>978</v>
       </c>
       <c r="D139" s="6" t="s">
-        <v>976</v>
+        <v>979</v>
       </c>
       <c r="E139" s="5" t="s">
-        <v>977</v>
+        <v>980</v>
       </c>
     </row>
     <row r="140" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -10793,13 +10896,13 @@
         <v>138</v>
       </c>
       <c r="B140" s="5" t="s">
-        <v>843</v>
+        <v>846</v>
       </c>
       <c r="C140" s="5" t="s">
-        <v>978</v>
+        <v>981</v>
       </c>
       <c r="D140" s="6" t="s">
-        <v>979</v>
+        <v>982</v>
       </c>
       <c r="E140" s="5" t="s">
         <v>463</v>
@@ -10810,16 +10913,16 @@
         <v>139</v>
       </c>
       <c r="B141" s="5" t="s">
-        <v>848</v>
+        <v>851</v>
       </c>
       <c r="C141" s="5" t="s">
-        <v>980</v>
+        <v>983</v>
       </c>
       <c r="D141" s="6" t="s">
-        <v>981</v>
+        <v>984</v>
       </c>
       <c r="E141" s="5" t="s">
-        <v>982</v>
+        <v>985</v>
       </c>
     </row>
     <row r="142" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -10827,16 +10930,16 @@
         <v>140</v>
       </c>
       <c r="B142" s="5" t="s">
-        <v>983</v>
+        <v>986</v>
       </c>
       <c r="C142" s="5" t="s">
-        <v>984</v>
+        <v>987</v>
       </c>
       <c r="D142" s="6" t="s">
-        <v>985</v>
+        <v>988</v>
       </c>
       <c r="E142" s="5" t="s">
-        <v>986</v>
+        <v>989</v>
       </c>
     </row>
     <row r="143" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -10844,13 +10947,13 @@
         <v>141</v>
       </c>
       <c r="B143" s="5" t="s">
-        <v>815</v>
+        <v>818</v>
       </c>
       <c r="C143" s="5" t="s">
-        <v>987</v>
+        <v>990</v>
       </c>
       <c r="D143" s="6" t="s">
-        <v>988</v>
+        <v>991</v>
       </c>
       <c r="E143" s="5" t="s">
         <v>472</v>
@@ -10861,16 +10964,16 @@
         <v>142</v>
       </c>
       <c r="B144" s="5" t="s">
-        <v>989</v>
+        <v>992</v>
       </c>
       <c r="C144" s="5" t="s">
-        <v>990</v>
+        <v>993</v>
       </c>
       <c r="D144" s="6" t="s">
-        <v>991</v>
+        <v>994</v>
       </c>
       <c r="E144" s="5" t="s">
-        <v>992</v>
+        <v>995</v>
       </c>
     </row>
     <row r="145" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -10878,13 +10981,13 @@
         <v>143</v>
       </c>
       <c r="B145" s="5" t="s">
-        <v>875</v>
+        <v>878</v>
       </c>
       <c r="C145" s="5" t="s">
-        <v>993</v>
+        <v>996</v>
       </c>
       <c r="D145" s="6" t="s">
-        <v>994</v>
+        <v>997</v>
       </c>
       <c r="E145" s="5" t="s">
         <v>479</v>
@@ -10895,16 +10998,16 @@
         <v>144</v>
       </c>
       <c r="B146" s="5" t="s">
-        <v>815</v>
+        <v>818</v>
       </c>
       <c r="C146" s="5" t="s">
-        <v>995</v>
+        <v>998</v>
       </c>
       <c r="D146" s="6" t="s">
-        <v>996</v>
+        <v>999</v>
       </c>
       <c r="E146" s="5" t="s">
-        <v>997</v>
+        <v>1000</v>
       </c>
     </row>
     <row r="147" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -10912,16 +11015,16 @@
         <v>145</v>
       </c>
       <c r="B147" s="5" t="s">
-        <v>998</v>
+        <v>1001</v>
       </c>
       <c r="C147" s="5" t="s">
-        <v>999</v>
+        <v>1002</v>
       </c>
       <c r="D147" s="6" t="s">
-        <v>1000</v>
+        <v>1003</v>
       </c>
       <c r="E147" s="5" t="s">
-        <v>1001</v>
+        <v>1004</v>
       </c>
     </row>
     <row r="148" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -10929,16 +11032,16 @@
         <v>146</v>
       </c>
       <c r="B148" s="5" t="s">
-        <v>1002</v>
+        <v>1005</v>
       </c>
       <c r="C148" s="5" t="s">
-        <v>1003</v>
+        <v>1006</v>
       </c>
       <c r="D148" s="6" t="s">
-        <v>1004</v>
+        <v>1007</v>
       </c>
       <c r="E148" s="5" t="s">
-        <v>1005</v>
+        <v>1008</v>
       </c>
     </row>
     <row r="149" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -10946,13 +11049,13 @@
         <v>147</v>
       </c>
       <c r="B149" s="5" t="s">
-        <v>1006</v>
+        <v>1009</v>
       </c>
       <c r="C149" s="5" t="s">
-        <v>1007</v>
+        <v>1010</v>
       </c>
       <c r="D149" s="6" t="s">
-        <v>939</v>
+        <v>942</v>
       </c>
       <c r="E149" s="5" t="s">
         <v>492</v>
@@ -10963,13 +11066,13 @@
         <v>148</v>
       </c>
       <c r="B150" s="5" t="s">
-        <v>1008</v>
+        <v>1011</v>
       </c>
       <c r="C150" s="5" t="s">
-        <v>1009</v>
+        <v>1012</v>
       </c>
       <c r="D150" s="6" t="s">
-        <v>943</v>
+        <v>946</v>
       </c>
       <c r="E150" s="5" t="s">
         <v>492</v>
@@ -10980,16 +11083,16 @@
         <v>149</v>
       </c>
       <c r="B151" s="5" t="s">
-        <v>1010</v>
+        <v>1013</v>
       </c>
       <c r="C151" s="5" t="s">
-        <v>1011</v>
+        <v>1014</v>
       </c>
       <c r="D151" s="6" t="s">
-        <v>1012</v>
+        <v>1015</v>
       </c>
       <c r="E151" s="5" t="s">
-        <v>1013</v>
+        <v>1016</v>
       </c>
     </row>
     <row r="152" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -10997,16 +11100,16 @@
         <v>150</v>
       </c>
       <c r="B152" s="5" t="s">
-        <v>1010</v>
+        <v>1013</v>
       </c>
       <c r="C152" s="5" t="s">
-        <v>1014</v>
+        <v>1017</v>
       </c>
       <c r="D152" s="6" t="s">
-        <v>1012</v>
+        <v>1015</v>
       </c>
       <c r="E152" s="5" t="s">
-        <v>1013</v>
+        <v>1016</v>
       </c>
     </row>
     <row r="153" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -11014,16 +11117,16 @@
         <v>151</v>
       </c>
       <c r="B153" s="5" t="s">
-        <v>1015</v>
+        <v>1018</v>
       </c>
       <c r="C153" s="5" t="s">
-        <v>1016</v>
+        <v>1019</v>
       </c>
       <c r="D153" s="6" t="s">
-        <v>1017</v>
+        <v>1020</v>
       </c>
       <c r="E153" s="5" t="s">
-        <v>1018</v>
+        <v>1021</v>
       </c>
     </row>
     <row r="154" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -11031,16 +11134,16 @@
         <v>152</v>
       </c>
       <c r="B154" s="5" t="s">
-        <v>1015</v>
+        <v>1018</v>
       </c>
       <c r="C154" s="5" t="s">
-        <v>1019</v>
+        <v>1022</v>
       </c>
       <c r="D154" s="6" t="s">
-        <v>1017</v>
+        <v>1020</v>
       </c>
       <c r="E154" s="5" t="s">
-        <v>1018</v>
+        <v>1021</v>
       </c>
     </row>
     <row r="155" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -11048,16 +11151,16 @@
         <v>153</v>
       </c>
       <c r="B155" s="5" t="s">
-        <v>1020</v>
+        <v>1023</v>
       </c>
       <c r="C155" s="5" t="s">
-        <v>1021</v>
+        <v>1024</v>
       </c>
       <c r="D155" s="6" t="s">
-        <v>1022</v>
+        <v>1025</v>
       </c>
       <c r="E155" s="5" t="s">
-        <v>1023</v>
+        <v>1026</v>
       </c>
     </row>
     <row r="156" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -11065,16 +11168,16 @@
         <v>154</v>
       </c>
       <c r="B156" s="5" t="s">
-        <v>848</v>
+        <v>851</v>
       </c>
       <c r="C156" s="5" t="s">
-        <v>1024</v>
+        <v>1027</v>
       </c>
       <c r="D156" s="6" t="s">
-        <v>1025</v>
+        <v>1028</v>
       </c>
       <c r="E156" s="5" t="s">
-        <v>1023</v>
+        <v>1026</v>
       </c>
     </row>
     <row r="157" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -11082,14 +11185,14 @@
         <v>155</v>
       </c>
       <c r="B157" s="5" t="s">
-        <v>1026</v>
+        <v>1029</v>
       </c>
       <c r="C157" s="5" t="s">
-        <v>1027</v>
+        <v>1030</v>
       </c>
       <c r="D157" s="5"/>
       <c r="E157" s="5" t="s">
-        <v>1028</v>
+        <v>1031</v>
       </c>
     </row>
     <row r="158" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -11097,16 +11200,16 @@
         <v>156</v>
       </c>
       <c r="B158" s="5" t="s">
-        <v>1029</v>
+        <v>1032</v>
       </c>
       <c r="C158" s="5" t="s">
-        <v>1030</v>
+        <v>1033</v>
       </c>
       <c r="D158" s="6" t="s">
+        <v>1034</v>
+      </c>
+      <c r="E158" s="5" t="s">
         <v>1031</v>
-      </c>
-      <c r="E158" s="5" t="s">
-        <v>1028</v>
       </c>
     </row>
     <row r="159" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -11114,16 +11217,16 @@
         <v>157</v>
       </c>
       <c r="B159" s="5" t="s">
-        <v>676</v>
+        <v>679</v>
       </c>
       <c r="C159" s="5" t="s">
-        <v>1032</v>
+        <v>1035</v>
       </c>
       <c r="D159" s="6" t="s">
-        <v>1033</v>
+        <v>1036</v>
       </c>
       <c r="E159" s="5" t="s">
-        <v>1034</v>
+        <v>1037</v>
       </c>
     </row>
     <row r="160" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -11131,16 +11234,16 @@
         <v>158</v>
       </c>
       <c r="B160" s="5" t="s">
-        <v>815</v>
+        <v>818</v>
       </c>
       <c r="C160" s="5" t="s">
-        <v>1035</v>
+        <v>1038</v>
       </c>
       <c r="D160" s="6" t="s">
-        <v>1036</v>
+        <v>1039</v>
       </c>
       <c r="E160" s="5" t="s">
-        <v>1034</v>
+        <v>1037</v>
       </c>
     </row>
     <row r="161" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -11148,16 +11251,16 @@
         <v>159</v>
       </c>
       <c r="B161" s="5" t="s">
-        <v>871</v>
+        <v>874</v>
       </c>
       <c r="C161" s="5" t="s">
+        <v>1040</v>
+      </c>
+      <c r="D161" s="6" t="s">
+        <v>1041</v>
+      </c>
+      <c r="E161" s="5" t="s">
         <v>1037</v>
-      </c>
-      <c r="D161" s="6" t="s">
-        <v>1038</v>
-      </c>
-      <c r="E161" s="5" t="s">
-        <v>1034</v>
       </c>
     </row>
     <row r="162" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -11165,16 +11268,16 @@
         <v>160</v>
       </c>
       <c r="B162" s="5" t="s">
-        <v>1039</v>
+        <v>1042</v>
       </c>
       <c r="C162" s="5" t="s">
-        <v>1040</v>
+        <v>1043</v>
       </c>
       <c r="D162" s="6" t="s">
-        <v>1041</v>
+        <v>1044</v>
       </c>
       <c r="E162" s="5" t="s">
-        <v>1034</v>
+        <v>1037</v>
       </c>
     </row>
     <row r="163" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -11182,16 +11285,16 @@
         <v>161</v>
       </c>
       <c r="B163" s="5" t="s">
-        <v>1039</v>
+        <v>1042</v>
       </c>
       <c r="C163" s="5" t="s">
-        <v>1042</v>
+        <v>1045</v>
       </c>
       <c r="D163" s="6" t="s">
-        <v>1043</v>
+        <v>1046</v>
       </c>
       <c r="E163" s="5" t="s">
-        <v>1034</v>
+        <v>1037</v>
       </c>
     </row>
     <row r="164" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -11199,16 +11302,16 @@
         <v>162</v>
       </c>
       <c r="B164" s="5" t="s">
-        <v>882</v>
+        <v>885</v>
       </c>
       <c r="C164" s="5" t="s">
-        <v>1044</v>
+        <v>1047</v>
       </c>
       <c r="D164" s="6" t="s">
-        <v>1045</v>
+        <v>1048</v>
       </c>
       <c r="E164" s="5" t="s">
-        <v>1046</v>
+        <v>1049</v>
       </c>
     </row>
     <row r="165" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -11216,16 +11319,16 @@
         <v>163</v>
       </c>
       <c r="B165" s="5" t="s">
-        <v>676</v>
+        <v>679</v>
       </c>
       <c r="C165" s="5" t="s">
-        <v>1047</v>
+        <v>1050</v>
       </c>
       <c r="D165" s="6" t="s">
-        <v>1048</v>
+        <v>1051</v>
       </c>
       <c r="E165" s="5" t="s">
-        <v>1046</v>
+        <v>1049</v>
       </c>
     </row>
     <row r="166" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -11233,13 +11336,13 @@
         <v>157</v>
       </c>
       <c r="B166" s="5" t="s">
-        <v>1039</v>
+        <v>1042</v>
       </c>
       <c r="C166" s="5" t="s">
-        <v>1049</v>
+        <v>1052</v>
       </c>
       <c r="D166" s="6" t="s">
-        <v>1050</v>
+        <v>1053</v>
       </c>
       <c r="E166" s="5" t="s">
         <v>521</v>
@@ -11250,16 +11353,16 @@
         <v>158</v>
       </c>
       <c r="B167" s="5" t="s">
-        <v>898</v>
+        <v>901</v>
       </c>
       <c r="C167" s="5" t="s">
-        <v>1051</v>
+        <v>1054</v>
       </c>
       <c r="D167" s="6" t="s">
-        <v>1052</v>
+        <v>1055</v>
       </c>
       <c r="E167" s="5" t="s">
-        <v>1053</v>
+        <v>1056</v>
       </c>
     </row>
     <row r="168" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -11267,13 +11370,13 @@
         <v>159</v>
       </c>
       <c r="B168" s="5" t="s">
-        <v>676</v>
+        <v>679</v>
       </c>
       <c r="C168" s="5" t="s">
-        <v>1054</v>
+        <v>1057</v>
       </c>
       <c r="D168" s="6" t="s">
-        <v>1055</v>
+        <v>1058</v>
       </c>
       <c r="E168" s="5" t="s">
         <v>524</v>
@@ -11284,16 +11387,16 @@
         <v>160</v>
       </c>
       <c r="B169" s="5" t="s">
-        <v>871</v>
+        <v>874</v>
       </c>
       <c r="C169" s="5" t="s">
-        <v>1056</v>
+        <v>1059</v>
       </c>
       <c r="D169" s="6" t="s">
-        <v>1057</v>
+        <v>1060</v>
       </c>
       <c r="E169" s="5" t="s">
-        <v>1058</v>
+        <v>1061</v>
       </c>
     </row>
     <row r="170" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -11301,16 +11404,16 @@
         <v>161</v>
       </c>
       <c r="B170" s="5" t="s">
-        <v>871</v>
+        <v>874</v>
       </c>
       <c r="C170" s="5" t="s">
-        <v>1059</v>
+        <v>1062</v>
       </c>
       <c r="D170" s="6" t="s">
-        <v>1060</v>
+        <v>1063</v>
       </c>
       <c r="E170" s="5" t="s">
-        <v>1058</v>
+        <v>1061</v>
       </c>
     </row>
     <row r="171" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -11318,16 +11421,16 @@
         <v>162</v>
       </c>
       <c r="B171" s="5" t="s">
-        <v>871</v>
+        <v>874</v>
       </c>
       <c r="C171" s="5" t="s">
+        <v>1064</v>
+      </c>
+      <c r="D171" s="6" t="s">
+        <v>1065</v>
+      </c>
+      <c r="E171" s="5" t="s">
         <v>1061</v>
-      </c>
-      <c r="D171" s="6" t="s">
-        <v>1062</v>
-      </c>
-      <c r="E171" s="5" t="s">
-        <v>1058</v>
       </c>
     </row>
     <row r="172" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -11335,16 +11438,16 @@
         <v>163</v>
       </c>
       <c r="B172" s="5" t="s">
-        <v>821</v>
+        <v>824</v>
       </c>
       <c r="C172" s="5" t="s">
-        <v>1063</v>
+        <v>1066</v>
       </c>
       <c r="D172" s="6" t="s">
-        <v>1064</v>
+        <v>1067</v>
       </c>
       <c r="E172" s="5" t="s">
-        <v>1065</v>
+        <v>1068</v>
       </c>
     </row>
     <row r="173" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -11352,16 +11455,16 @@
         <v>164</v>
       </c>
       <c r="B173" s="5" t="s">
-        <v>815</v>
+        <v>818</v>
       </c>
       <c r="C173" s="5" t="s">
-        <v>1066</v>
+        <v>1069</v>
       </c>
       <c r="D173" s="6" t="s">
-        <v>1067</v>
+        <v>1070</v>
       </c>
       <c r="E173" s="5" t="s">
-        <v>1068</v>
+        <v>1071</v>
       </c>
     </row>
     <row r="174" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -11369,16 +11472,16 @@
         <v>165</v>
       </c>
       <c r="B174" s="5" t="s">
-        <v>815</v>
+        <v>818</v>
       </c>
       <c r="C174" s="5" t="s">
-        <v>1069</v>
+        <v>1072</v>
       </c>
       <c r="D174" s="6" t="s">
-        <v>1070</v>
+        <v>1073</v>
       </c>
       <c r="E174" s="5" t="s">
-        <v>1068</v>
+        <v>1071</v>
       </c>
     </row>
     <row r="175" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -11386,16 +11489,16 @@
         <v>166</v>
       </c>
       <c r="B175" s="5" t="s">
-        <v>815</v>
+        <v>818</v>
       </c>
       <c r="C175" s="5" t="s">
+        <v>1074</v>
+      </c>
+      <c r="D175" s="6" t="s">
+        <v>1075</v>
+      </c>
+      <c r="E175" s="5" t="s">
         <v>1071</v>
-      </c>
-      <c r="D175" s="6" t="s">
-        <v>1072</v>
-      </c>
-      <c r="E175" s="5" t="s">
-        <v>1068</v>
       </c>
     </row>
     <row r="176" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -11403,16 +11506,16 @@
         <v>167</v>
       </c>
       <c r="B176" s="5" t="s">
-        <v>882</v>
+        <v>885</v>
       </c>
       <c r="C176" s="5" t="s">
-        <v>1073</v>
+        <v>1076</v>
       </c>
       <c r="D176" s="6" t="s">
-        <v>1074</v>
+        <v>1077</v>
       </c>
       <c r="E176" s="5" t="s">
-        <v>1075</v>
+        <v>1078</v>
       </c>
     </row>
     <row r="177" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -11420,16 +11523,16 @@
         <v>168</v>
       </c>
       <c r="B177" s="5" t="s">
-        <v>676</v>
+        <v>679</v>
       </c>
       <c r="C177" s="5" t="s">
-        <v>1076</v>
+        <v>1079</v>
       </c>
       <c r="D177" s="6" t="s">
-        <v>1077</v>
+        <v>1080</v>
       </c>
       <c r="E177" s="5" t="s">
-        <v>1075</v>
+        <v>1078</v>
       </c>
     </row>
     <row r="178" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -11437,16 +11540,16 @@
         <v>169</v>
       </c>
       <c r="B178" s="5" t="s">
-        <v>676</v>
+        <v>679</v>
       </c>
       <c r="C178" s="5" t="s">
+        <v>1081</v>
+      </c>
+      <c r="D178" s="6" t="s">
+        <v>1082</v>
+      </c>
+      <c r="E178" s="5" t="s">
         <v>1078</v>
-      </c>
-      <c r="D178" s="6" t="s">
-        <v>1079</v>
-      </c>
-      <c r="E178" s="5" t="s">
-        <v>1075</v>
       </c>
     </row>
     <row r="179" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -11454,16 +11557,16 @@
         <v>170</v>
       </c>
       <c r="B179" s="5" t="s">
-        <v>898</v>
+        <v>901</v>
       </c>
       <c r="C179" s="5" t="s">
-        <v>1080</v>
+        <v>1083</v>
       </c>
       <c r="D179" s="6" t="s">
-        <v>1081</v>
+        <v>1084</v>
       </c>
       <c r="E179" s="5" t="s">
-        <v>1075</v>
+        <v>1078</v>
       </c>
     </row>
     <row r="180" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -11471,16 +11574,16 @@
         <v>171</v>
       </c>
       <c r="B180" s="5" t="s">
-        <v>898</v>
+        <v>901</v>
       </c>
       <c r="C180" s="5" t="s">
-        <v>1082</v>
+        <v>1085</v>
       </c>
       <c r="D180" s="6" t="s">
-        <v>1083</v>
+        <v>1086</v>
       </c>
       <c r="E180" s="5" t="s">
-        <v>1075</v>
+        <v>1078</v>
       </c>
     </row>
     <row r="181" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -11488,16 +11591,16 @@
         <v>172</v>
       </c>
       <c r="B181" s="5" t="s">
-        <v>871</v>
+        <v>874</v>
       </c>
       <c r="C181" s="5" t="s">
-        <v>1084</v>
+        <v>1087</v>
       </c>
       <c r="D181" s="6" t="s">
-        <v>1085</v>
+        <v>1088</v>
       </c>
       <c r="E181" s="5" t="s">
-        <v>1086</v>
+        <v>1089</v>
       </c>
     </row>
     <row r="182" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -11505,16 +11608,16 @@
         <v>173</v>
       </c>
       <c r="B182" s="5" t="s">
-        <v>676</v>
+        <v>679</v>
       </c>
       <c r="C182" s="5" t="s">
-        <v>1087</v>
+        <v>1090</v>
       </c>
       <c r="D182" s="6" t="s">
-        <v>1088</v>
+        <v>1091</v>
       </c>
       <c r="E182" s="5" t="s">
-        <v>1089</v>
+        <v>1092</v>
       </c>
     </row>
     <row r="183" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -11522,16 +11625,16 @@
         <v>174</v>
       </c>
       <c r="B183" s="5" t="s">
-        <v>676</v>
+        <v>679</v>
       </c>
       <c r="C183" s="5" t="s">
-        <v>1090</v>
+        <v>1093</v>
       </c>
       <c r="D183" s="6" t="s">
-        <v>1091</v>
+        <v>1094</v>
       </c>
       <c r="E183" s="5" t="s">
-        <v>1089</v>
+        <v>1092</v>
       </c>
     </row>
     <row r="184" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -11539,16 +11642,16 @@
         <v>175</v>
       </c>
       <c r="B184" s="5" t="s">
-        <v>676</v>
+        <v>679</v>
       </c>
       <c r="C184" s="5" t="s">
+        <v>1095</v>
+      </c>
+      <c r="D184" s="6" t="s">
+        <v>1096</v>
+      </c>
+      <c r="E184" s="5" t="s">
         <v>1092</v>
-      </c>
-      <c r="D184" s="6" t="s">
-        <v>1093</v>
-      </c>
-      <c r="E184" s="5" t="s">
-        <v>1089</v>
       </c>
     </row>
     <row r="185" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -11556,16 +11659,16 @@
         <v>176</v>
       </c>
       <c r="B185" s="5" t="s">
-        <v>1039</v>
+        <v>1042</v>
       </c>
       <c r="C185" s="5" t="s">
-        <v>1094</v>
+        <v>1097</v>
       </c>
       <c r="D185" s="6" t="s">
-        <v>1095</v>
+        <v>1098</v>
       </c>
       <c r="E185" s="5" t="s">
-        <v>1089</v>
+        <v>1092</v>
       </c>
     </row>
     <row r="186" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -11573,16 +11676,16 @@
         <v>177</v>
       </c>
       <c r="B186" s="5" t="s">
-        <v>1039</v>
+        <v>1042</v>
       </c>
       <c r="C186" s="5" t="s">
-        <v>1096</v>
+        <v>1099</v>
       </c>
       <c r="D186" s="6" t="s">
-        <v>1097</v>
+        <v>1100</v>
       </c>
       <c r="E186" s="5" t="s">
-        <v>1089</v>
+        <v>1092</v>
       </c>
     </row>
     <row r="187" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -11590,16 +11693,16 @@
         <v>178</v>
       </c>
       <c r="B187" s="5" t="s">
-        <v>1039</v>
+        <v>1042</v>
       </c>
       <c r="C187" s="5" t="s">
-        <v>1098</v>
+        <v>1101</v>
       </c>
       <c r="D187" s="6" t="s">
-        <v>1099</v>
+        <v>1102</v>
       </c>
       <c r="E187" s="5" t="s">
-        <v>1089</v>
+        <v>1092</v>
       </c>
     </row>
     <row r="188" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -11607,16 +11710,16 @@
         <v>179</v>
       </c>
       <c r="B188" s="5" t="s">
-        <v>676</v>
+        <v>679</v>
       </c>
       <c r="C188" s="5" t="s">
-        <v>1100</v>
+        <v>1103</v>
       </c>
       <c r="D188" s="6" t="s">
-        <v>1101</v>
+        <v>1104</v>
       </c>
       <c r="E188" s="5" t="s">
-        <v>1102</v>
+        <v>1105</v>
       </c>
     </row>
     <row r="189" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -11624,16 +11727,16 @@
         <v>180</v>
       </c>
       <c r="B189" s="5" t="s">
-        <v>676</v>
+        <v>679</v>
       </c>
       <c r="C189" s="5" t="s">
-        <v>1103</v>
+        <v>1106</v>
       </c>
       <c r="D189" s="6" t="s">
-        <v>1104</v>
+        <v>1107</v>
       </c>
       <c r="E189" s="5" t="s">
-        <v>1102</v>
+        <v>1105</v>
       </c>
     </row>
     <row r="190" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -11641,16 +11744,16 @@
         <v>181</v>
       </c>
       <c r="B190" s="5" t="s">
-        <v>871</v>
+        <v>874</v>
       </c>
       <c r="C190" s="5" t="s">
+        <v>1108</v>
+      </c>
+      <c r="D190" s="6" t="s">
+        <v>1109</v>
+      </c>
+      <c r="E190" s="5" t="s">
         <v>1105</v>
-      </c>
-      <c r="D190" s="6" t="s">
-        <v>1106</v>
-      </c>
-      <c r="E190" s="5" t="s">
-        <v>1102</v>
       </c>
     </row>
     <row r="191" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -11658,16 +11761,16 @@
         <v>182</v>
       </c>
       <c r="B191" s="5" t="s">
-        <v>1039</v>
+        <v>1042</v>
       </c>
       <c r="C191" s="5" t="s">
-        <v>1107</v>
+        <v>1110</v>
       </c>
       <c r="D191" s="6" t="s">
-        <v>1108</v>
+        <v>1111</v>
       </c>
       <c r="E191" s="5" t="s">
-        <v>1102</v>
+        <v>1105</v>
       </c>
     </row>
     <row r="192" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -11675,16 +11778,16 @@
         <v>183</v>
       </c>
       <c r="B192" s="5" t="s">
-        <v>1039</v>
+        <v>1042</v>
       </c>
       <c r="C192" s="5" t="s">
-        <v>1109</v>
+        <v>1112</v>
       </c>
       <c r="D192" s="6" t="s">
-        <v>1110</v>
+        <v>1113</v>
       </c>
       <c r="E192" s="5" t="s">
-        <v>1102</v>
+        <v>1105</v>
       </c>
     </row>
     <row r="193" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -11692,13 +11795,13 @@
         <v>184</v>
       </c>
       <c r="B193" s="5" t="s">
-        <v>871</v>
+        <v>874</v>
       </c>
       <c r="C193" s="5" t="s">
-        <v>1111</v>
+        <v>1114</v>
       </c>
       <c r="D193" s="6" t="s">
-        <v>1112</v>
+        <v>1115</v>
       </c>
       <c r="E193" s="5" t="s">
         <v>533</v>
@@ -11709,16 +11812,16 @@
         <v>185</v>
       </c>
       <c r="B194" s="5" t="s">
-        <v>871</v>
+        <v>874</v>
       </c>
       <c r="C194" s="5" t="s">
-        <v>1113</v>
+        <v>1116</v>
       </c>
       <c r="D194" s="6" t="s">
-        <v>1114</v>
+        <v>1117</v>
       </c>
       <c r="E194" s="5" t="s">
-        <v>1115</v>
+        <v>1118</v>
       </c>
     </row>
     <row r="195" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -11726,16 +11829,16 @@
         <v>186</v>
       </c>
       <c r="B195" s="5" t="s">
-        <v>676</v>
+        <v>679</v>
       </c>
       <c r="C195" s="5" t="s">
-        <v>1116</v>
+        <v>1119</v>
       </c>
       <c r="D195" s="6" t="s">
-        <v>1117</v>
+        <v>1120</v>
       </c>
       <c r="E195" s="5" t="s">
-        <v>1118</v>
+        <v>1121</v>
       </c>
     </row>
     <row r="196" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -11743,16 +11846,16 @@
         <v>187</v>
       </c>
       <c r="B196" s="5" t="s">
-        <v>815</v>
+        <v>818</v>
       </c>
       <c r="C196" s="5" t="s">
-        <v>1119</v>
+        <v>1122</v>
       </c>
       <c r="D196" s="6" t="s">
-        <v>1120</v>
+        <v>1123</v>
       </c>
       <c r="E196" s="5" t="s">
-        <v>1118</v>
+        <v>1121</v>
       </c>
     </row>
     <row r="197" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -11760,16 +11863,16 @@
         <v>188</v>
       </c>
       <c r="B197" s="5" t="s">
-        <v>1039</v>
+        <v>1042</v>
       </c>
       <c r="C197" s="5" t="s">
+        <v>1124</v>
+      </c>
+      <c r="D197" s="6" t="s">
+        <v>1125</v>
+      </c>
+      <c r="E197" s="5" t="s">
         <v>1121</v>
-      </c>
-      <c r="D197" s="6" t="s">
-        <v>1122</v>
-      </c>
-      <c r="E197" s="5" t="s">
-        <v>1118</v>
       </c>
     </row>
     <row r="198" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -11777,16 +11880,16 @@
         <v>189</v>
       </c>
       <c r="B198" s="5" t="s">
-        <v>1039</v>
+        <v>1042</v>
       </c>
       <c r="C198" s="5" t="s">
-        <v>1123</v>
+        <v>1126</v>
       </c>
       <c r="D198" s="6" t="s">
-        <v>1124</v>
+        <v>1127</v>
       </c>
       <c r="E198" s="5" t="s">
-        <v>1118</v>
+        <v>1121</v>
       </c>
     </row>
     <row r="199" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -11794,16 +11897,16 @@
         <v>190</v>
       </c>
       <c r="B199" s="5" t="s">
-        <v>882</v>
+        <v>885</v>
       </c>
       <c r="C199" s="5" t="s">
-        <v>1125</v>
+        <v>1128</v>
       </c>
       <c r="D199" s="6" t="s">
-        <v>1126</v>
+        <v>1129</v>
       </c>
       <c r="E199" s="5" t="s">
-        <v>1127</v>
+        <v>1130</v>
       </c>
     </row>
     <row r="200" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -11811,16 +11914,16 @@
         <v>191</v>
       </c>
       <c r="B200" s="5" t="s">
-        <v>882</v>
+        <v>885</v>
       </c>
       <c r="C200" s="5" t="s">
-        <v>1128</v>
+        <v>1131</v>
       </c>
       <c r="D200" s="6" t="s">
-        <v>1129</v>
+        <v>1132</v>
       </c>
       <c r="E200" s="5" t="s">
-        <v>1127</v>
+        <v>1130</v>
       </c>
     </row>
     <row r="201" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -11828,16 +11931,16 @@
         <v>192</v>
       </c>
       <c r="B201" s="5" t="s">
-        <v>676</v>
+        <v>679</v>
       </c>
       <c r="C201" s="5" t="s">
+        <v>1133</v>
+      </c>
+      <c r="D201" s="6" t="s">
+        <v>1134</v>
+      </c>
+      <c r="E201" s="5" t="s">
         <v>1130</v>
-      </c>
-      <c r="D201" s="6" t="s">
-        <v>1131</v>
-      </c>
-      <c r="E201" s="5" t="s">
-        <v>1127</v>
       </c>
     </row>
     <row r="202" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -11845,16 +11948,16 @@
         <v>193</v>
       </c>
       <c r="B202" s="5" t="s">
-        <v>676</v>
+        <v>679</v>
       </c>
       <c r="C202" s="5" t="s">
-        <v>1132</v>
+        <v>1135</v>
       </c>
       <c r="D202" s="6" t="s">
-        <v>1133</v>
+        <v>1136</v>
       </c>
       <c r="E202" s="5" t="s">
-        <v>1134</v>
+        <v>1137</v>
       </c>
     </row>
     <row r="203" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -11862,16 +11965,16 @@
         <v>194</v>
       </c>
       <c r="B203" s="5" t="s">
-        <v>676</v>
+        <v>679</v>
       </c>
       <c r="C203" s="5" t="s">
-        <v>1135</v>
+        <v>1138</v>
       </c>
       <c r="D203" s="6" t="s">
-        <v>1136</v>
+        <v>1139</v>
       </c>
       <c r="E203" s="5" t="s">
-        <v>1134</v>
+        <v>1137</v>
       </c>
     </row>
     <row r="204" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -11879,16 +11982,16 @@
         <v>195</v>
       </c>
       <c r="B204" s="5" t="s">
-        <v>676</v>
+        <v>679</v>
       </c>
       <c r="C204" s="5" t="s">
-        <v>1137</v>
+        <v>1140</v>
       </c>
       <c r="D204" s="6" t="s">
-        <v>1138</v>
+        <v>1141</v>
       </c>
       <c r="E204" s="5" t="s">
-        <v>1139</v>
+        <v>1142</v>
       </c>
     </row>
     <row r="205" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -11896,13 +11999,13 @@
         <v>196</v>
       </c>
       <c r="B205" s="5" t="s">
-        <v>871</v>
+        <v>874</v>
       </c>
       <c r="C205" s="5" t="s">
-        <v>1140</v>
+        <v>1143</v>
       </c>
       <c r="D205" s="6" t="s">
-        <v>1141</v>
+        <v>1144</v>
       </c>
       <c r="E205" s="5" t="s">
         <v>540</v>
@@ -11913,16 +12016,16 @@
         <v>197</v>
       </c>
       <c r="B206" s="5" t="s">
-        <v>676</v>
+        <v>679</v>
       </c>
       <c r="C206" s="5" t="s">
-        <v>1142</v>
+        <v>1145</v>
       </c>
       <c r="D206" s="6" t="s">
-        <v>1143</v>
+        <v>1146</v>
       </c>
       <c r="E206" s="5" t="s">
-        <v>1144</v>
+        <v>1147</v>
       </c>
     </row>
     <row r="207" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -11930,16 +12033,16 @@
         <v>198</v>
       </c>
       <c r="B207" s="5" t="s">
-        <v>898</v>
+        <v>901</v>
       </c>
       <c r="C207" s="5" t="s">
-        <v>1145</v>
+        <v>1148</v>
       </c>
       <c r="D207" s="6" t="s">
-        <v>1146</v>
+        <v>1149</v>
       </c>
       <c r="E207" s="5" t="s">
-        <v>1144</v>
+        <v>1147</v>
       </c>
     </row>
     <row r="208" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -11947,16 +12050,16 @@
         <v>199</v>
       </c>
       <c r="B208" s="5" t="s">
-        <v>1039</v>
+        <v>1042</v>
       </c>
       <c r="C208" s="5" t="s">
+        <v>1150</v>
+      </c>
+      <c r="D208" s="6" t="s">
+        <v>1151</v>
+      </c>
+      <c r="E208" s="5" t="s">
         <v>1147</v>
-      </c>
-      <c r="D208" s="6" t="s">
-        <v>1148</v>
-      </c>
-      <c r="E208" s="5" t="s">
-        <v>1144</v>
       </c>
     </row>
     <row r="209" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -11964,16 +12067,16 @@
         <v>200</v>
       </c>
       <c r="B209" s="5" t="s">
-        <v>1039</v>
+        <v>1042</v>
       </c>
       <c r="C209" s="5" t="s">
-        <v>1149</v>
+        <v>1152</v>
       </c>
       <c r="D209" s="6" t="s">
-        <v>1150</v>
+        <v>1153</v>
       </c>
       <c r="E209" s="5" t="s">
-        <v>1144</v>
+        <v>1147</v>
       </c>
     </row>
     <row r="210" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -11981,16 +12084,16 @@
         <v>201</v>
       </c>
       <c r="B210" s="5" t="s">
-        <v>815</v>
+        <v>818</v>
       </c>
       <c r="C210" s="5" t="s">
-        <v>1151</v>
+        <v>1154</v>
       </c>
       <c r="D210" s="6" t="s">
-        <v>1152</v>
+        <v>1155</v>
       </c>
       <c r="E210" s="5" t="s">
-        <v>1153</v>
+        <v>1156</v>
       </c>
     </row>
     <row r="211" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -11998,16 +12101,16 @@
         <v>202</v>
       </c>
       <c r="B211" s="5" t="s">
-        <v>898</v>
+        <v>901</v>
       </c>
       <c r="C211" s="5" t="s">
-        <v>1154</v>
+        <v>1157</v>
       </c>
       <c r="D211" s="6" t="s">
-        <v>1155</v>
+        <v>1158</v>
       </c>
       <c r="E211" s="5" t="s">
-        <v>1153</v>
+        <v>1156</v>
       </c>
     </row>
     <row r="212" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -12015,16 +12118,16 @@
         <v>203</v>
       </c>
       <c r="B212" s="5" t="s">
-        <v>898</v>
+        <v>901</v>
       </c>
       <c r="C212" s="5" t="s">
+        <v>1159</v>
+      </c>
+      <c r="D212" s="6" t="s">
+        <v>1160</v>
+      </c>
+      <c r="E212" s="5" t="s">
         <v>1156</v>
-      </c>
-      <c r="D212" s="6" t="s">
-        <v>1157</v>
-      </c>
-      <c r="E212" s="5" t="s">
-        <v>1153</v>
       </c>
     </row>
     <row r="213" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -12032,16 +12135,16 @@
         <v>204</v>
       </c>
       <c r="B213" s="5" t="s">
-        <v>871</v>
+        <v>874</v>
       </c>
       <c r="C213" s="5" t="s">
-        <v>1158</v>
+        <v>1161</v>
       </c>
       <c r="D213" s="6" t="s">
-        <v>1159</v>
+        <v>1162</v>
       </c>
       <c r="E213" s="5" t="s">
-        <v>1053</v>
+        <v>1056</v>
       </c>
     </row>
     <row r="214" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -12049,16 +12152,16 @@
         <v>205</v>
       </c>
       <c r="B214" s="5" t="s">
-        <v>676</v>
+        <v>679</v>
       </c>
       <c r="C214" s="5" t="s">
-        <v>1160</v>
+        <v>1163</v>
       </c>
       <c r="D214" s="6" t="s">
-        <v>1161</v>
+        <v>1164</v>
       </c>
       <c r="E214" s="5" t="s">
-        <v>1162</v>
+        <v>1165</v>
       </c>
     </row>
     <row r="215" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -12066,16 +12169,16 @@
         <v>206</v>
       </c>
       <c r="B215" s="5" t="s">
-        <v>815</v>
+        <v>818</v>
       </c>
       <c r="C215" s="5" t="s">
-        <v>1163</v>
+        <v>1166</v>
       </c>
       <c r="D215" s="6" t="s">
-        <v>1164</v>
+        <v>1167</v>
       </c>
       <c r="E215" s="5" t="s">
-        <v>1165</v>
+        <v>1168</v>
       </c>
     </row>
     <row r="216" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -12083,16 +12186,16 @@
         <v>207</v>
       </c>
       <c r="B216" s="5" t="s">
-        <v>898</v>
+        <v>901</v>
       </c>
       <c r="C216" s="5" t="s">
-        <v>1166</v>
+        <v>1169</v>
       </c>
       <c r="D216" s="6" t="s">
-        <v>1167</v>
+        <v>1170</v>
       </c>
       <c r="E216" s="5" t="s">
-        <v>1165</v>
+        <v>1168</v>
       </c>
     </row>
     <row r="217" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -12100,16 +12203,16 @@
         <v>208</v>
       </c>
       <c r="B217" s="5" t="s">
-        <v>676</v>
+        <v>679</v>
       </c>
       <c r="C217" s="5" t="s">
-        <v>1168</v>
+        <v>1171</v>
       </c>
       <c r="D217" s="6" t="s">
-        <v>1169</v>
+        <v>1172</v>
       </c>
       <c r="E217" s="5" t="s">
-        <v>1170</v>
+        <v>1173</v>
       </c>
     </row>
     <row r="218" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -12117,16 +12220,16 @@
         <v>209</v>
       </c>
       <c r="B218" s="5" t="s">
-        <v>815</v>
+        <v>818</v>
       </c>
       <c r="C218" s="5" t="s">
-        <v>1171</v>
+        <v>1174</v>
       </c>
       <c r="D218" s="6" t="s">
-        <v>1172</v>
+        <v>1175</v>
       </c>
       <c r="E218" s="5" t="s">
-        <v>1170</v>
+        <v>1173</v>
       </c>
     </row>
     <row r="219" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -12134,16 +12237,16 @@
         <v>210</v>
       </c>
       <c r="B219" s="5" t="s">
-        <v>898</v>
+        <v>901</v>
       </c>
       <c r="C219" s="5" t="s">
+        <v>1176</v>
+      </c>
+      <c r="D219" s="6" t="s">
+        <v>1177</v>
+      </c>
+      <c r="E219" s="5" t="s">
         <v>1173</v>
-      </c>
-      <c r="D219" s="6" t="s">
-        <v>1174</v>
-      </c>
-      <c r="E219" s="5" t="s">
-        <v>1170</v>
       </c>
     </row>
     <row r="220" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -12151,16 +12254,16 @@
         <v>211</v>
       </c>
       <c r="B220" s="5" t="s">
-        <v>1039</v>
+        <v>1042</v>
       </c>
       <c r="C220" s="5" t="s">
-        <v>1175</v>
+        <v>1178</v>
       </c>
       <c r="D220" s="6" t="s">
-        <v>1176</v>
+        <v>1179</v>
       </c>
       <c r="E220" s="5" t="s">
-        <v>1170</v>
+        <v>1173</v>
       </c>
     </row>
     <row r="221" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -12168,16 +12271,16 @@
         <v>212</v>
       </c>
       <c r="B221" s="5" t="s">
-        <v>871</v>
+        <v>874</v>
       </c>
       <c r="C221" s="5" t="s">
-        <v>1177</v>
+        <v>1180</v>
       </c>
       <c r="D221" s="6" t="s">
-        <v>1178</v>
+        <v>1181</v>
       </c>
       <c r="E221" s="5" t="s">
-        <v>1179</v>
+        <v>1182</v>
       </c>
     </row>
     <row r="222" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -12185,16 +12288,16 @@
         <v>213</v>
       </c>
       <c r="B222" s="5" t="s">
-        <v>676</v>
+        <v>679</v>
       </c>
       <c r="C222" s="5" t="s">
-        <v>1180</v>
+        <v>1183</v>
       </c>
       <c r="D222" s="6" t="s">
-        <v>1181</v>
+        <v>1184</v>
       </c>
       <c r="E222" s="5" t="s">
-        <v>1182</v>
+        <v>1185</v>
       </c>
     </row>
     <row r="223" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -12202,16 +12305,16 @@
         <v>214</v>
       </c>
       <c r="B223" s="5" t="s">
-        <v>871</v>
+        <v>874</v>
       </c>
       <c r="C223" s="5" t="s">
-        <v>1183</v>
+        <v>1186</v>
       </c>
       <c r="D223" s="6" t="s">
-        <v>1184</v>
+        <v>1187</v>
       </c>
       <c r="E223" s="5" t="s">
-        <v>1182</v>
+        <v>1185</v>
       </c>
     </row>
     <row r="224" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -12219,16 +12322,16 @@
         <v>215</v>
       </c>
       <c r="B224" s="5" t="s">
-        <v>871</v>
+        <v>874</v>
       </c>
       <c r="C224" s="5" t="s">
+        <v>1188</v>
+      </c>
+      <c r="D224" s="6" t="s">
+        <v>1189</v>
+      </c>
+      <c r="E224" s="5" t="s">
         <v>1185</v>
-      </c>
-      <c r="D224" s="6" t="s">
-        <v>1186</v>
-      </c>
-      <c r="E224" s="5" t="s">
-        <v>1182</v>
       </c>
     </row>
     <row r="225" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -12236,16 +12339,16 @@
         <v>216</v>
       </c>
       <c r="B225" s="5" t="s">
-        <v>1039</v>
+        <v>1042</v>
       </c>
       <c r="C225" s="5" t="s">
-        <v>1187</v>
+        <v>1190</v>
       </c>
       <c r="D225" s="6" t="s">
-        <v>1188</v>
+        <v>1191</v>
       </c>
       <c r="E225" s="5" t="s">
-        <v>1182</v>
+        <v>1185</v>
       </c>
     </row>
     <row r="226" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -12253,16 +12356,16 @@
         <v>217</v>
       </c>
       <c r="B226" s="5" t="s">
-        <v>882</v>
+        <v>885</v>
       </c>
       <c r="C226" s="5" t="s">
-        <v>1189</v>
+        <v>1192</v>
       </c>
       <c r="D226" s="6" t="s">
-        <v>1190</v>
+        <v>1193</v>
       </c>
       <c r="E226" s="5" t="s">
-        <v>1191</v>
+        <v>1194</v>
       </c>
     </row>
     <row r="227" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -12270,16 +12373,16 @@
         <v>218</v>
       </c>
       <c r="B227" s="5" t="s">
-        <v>676</v>
+        <v>679</v>
       </c>
       <c r="C227" s="5" t="s">
-        <v>1192</v>
+        <v>1195</v>
       </c>
       <c r="D227" s="6" t="s">
-        <v>1193</v>
+        <v>1196</v>
       </c>
       <c r="E227" s="5" t="s">
-        <v>1191</v>
+        <v>1194</v>
       </c>
     </row>
     <row r="228" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -12287,16 +12390,16 @@
         <v>219</v>
       </c>
       <c r="B228" s="5" t="s">
-        <v>815</v>
+        <v>818</v>
       </c>
       <c r="C228" s="5" t="s">
+        <v>1197</v>
+      </c>
+      <c r="D228" s="6" t="s">
+        <v>1198</v>
+      </c>
+      <c r="E228" s="5" t="s">
         <v>1194</v>
-      </c>
-      <c r="D228" s="6" t="s">
-        <v>1195</v>
-      </c>
-      <c r="E228" s="5" t="s">
-        <v>1191</v>
       </c>
     </row>
     <row r="229" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -12304,16 +12407,16 @@
         <v>220</v>
       </c>
       <c r="B229" s="5" t="s">
-        <v>1039</v>
+        <v>1042</v>
       </c>
       <c r="C229" s="5" t="s">
-        <v>1196</v>
+        <v>1199</v>
       </c>
       <c r="D229" s="6" t="s">
-        <v>1197</v>
+        <v>1200</v>
       </c>
       <c r="E229" s="5" t="s">
-        <v>1191</v>
+        <v>1194</v>
       </c>
     </row>
     <row r="230" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -12321,16 +12424,16 @@
         <v>221</v>
       </c>
       <c r="B230" s="5" t="s">
-        <v>676</v>
+        <v>679</v>
       </c>
       <c r="C230" s="5" t="s">
-        <v>1198</v>
+        <v>1201</v>
       </c>
       <c r="D230" s="6" t="s">
-        <v>1199</v>
+        <v>1202</v>
       </c>
       <c r="E230" s="5" t="s">
-        <v>1200</v>
+        <v>1203</v>
       </c>
     </row>
     <row r="231" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -12338,16 +12441,16 @@
         <v>222</v>
       </c>
       <c r="B231" s="5" t="s">
-        <v>871</v>
+        <v>874</v>
       </c>
       <c r="C231" s="5" t="s">
-        <v>1201</v>
+        <v>1204</v>
       </c>
       <c r="D231" s="6" t="s">
-        <v>1202</v>
+        <v>1205</v>
       </c>
       <c r="E231" s="5" t="s">
-        <v>1200</v>
+        <v>1203</v>
       </c>
     </row>
     <row r="232" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -12355,16 +12458,16 @@
         <v>223</v>
       </c>
       <c r="B232" s="5" t="s">
-        <v>676</v>
+        <v>679</v>
       </c>
       <c r="C232" s="5" t="s">
-        <v>1203</v>
+        <v>1206</v>
       </c>
       <c r="D232" s="6" t="s">
-        <v>1204</v>
+        <v>1207</v>
       </c>
       <c r="E232" s="5" t="s">
-        <v>1205</v>
+        <v>1208</v>
       </c>
     </row>
     <row r="233" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -12372,16 +12475,16 @@
         <v>224</v>
       </c>
       <c r="B233" s="5" t="s">
-        <v>898</v>
+        <v>901</v>
       </c>
       <c r="C233" s="5" t="s">
-        <v>1206</v>
+        <v>1209</v>
       </c>
       <c r="D233" s="6" t="s">
-        <v>1207</v>
+        <v>1210</v>
       </c>
       <c r="E233" s="5" t="s">
-        <v>1205</v>
+        <v>1208</v>
       </c>
     </row>
     <row r="234" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -12389,16 +12492,16 @@
         <v>225</v>
       </c>
       <c r="B234" s="5" t="s">
-        <v>676</v>
+        <v>679</v>
       </c>
       <c r="C234" s="5" t="s">
-        <v>1208</v>
+        <v>1211</v>
       </c>
       <c r="D234" s="6" t="s">
-        <v>1209</v>
+        <v>1212</v>
       </c>
       <c r="E234" s="5" t="s">
-        <v>1210</v>
+        <v>1213</v>
       </c>
     </row>
     <row r="235" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -12406,16 +12509,16 @@
         <v>226</v>
       </c>
       <c r="B235" s="5" t="s">
-        <v>815</v>
+        <v>818</v>
       </c>
       <c r="C235" s="5" t="s">
-        <v>1211</v>
+        <v>1214</v>
       </c>
       <c r="D235" s="6" t="s">
-        <v>1212</v>
+        <v>1215</v>
       </c>
       <c r="E235" s="5" t="s">
-        <v>1210</v>
+        <v>1213</v>
       </c>
     </row>
     <row r="236" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -12423,16 +12526,16 @@
         <v>227</v>
       </c>
       <c r="B236" s="5" t="s">
-        <v>898</v>
+        <v>901</v>
       </c>
       <c r="C236" s="5" t="s">
+        <v>1216</v>
+      </c>
+      <c r="D236" s="6" t="s">
+        <v>1217</v>
+      </c>
+      <c r="E236" s="5" t="s">
         <v>1213</v>
-      </c>
-      <c r="D236" s="6" t="s">
-        <v>1214</v>
-      </c>
-      <c r="E236" s="5" t="s">
-        <v>1210</v>
       </c>
     </row>
     <row r="237" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -12440,16 +12543,16 @@
         <v>228</v>
       </c>
       <c r="B237" s="5" t="s">
-        <v>898</v>
+        <v>901</v>
       </c>
       <c r="C237" s="5" t="s">
-        <v>1215</v>
+        <v>1218</v>
       </c>
       <c r="D237" s="6" t="s">
-        <v>1216</v>
+        <v>1219</v>
       </c>
       <c r="E237" s="5" t="s">
-        <v>1217</v>
+        <v>1220</v>
       </c>
     </row>
     <row r="238" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -12457,16 +12560,16 @@
         <v>229</v>
       </c>
       <c r="B238" s="5" t="s">
-        <v>871</v>
+        <v>874</v>
       </c>
       <c r="C238" s="5" t="s">
-        <v>1218</v>
+        <v>1221</v>
       </c>
       <c r="D238" s="6" t="s">
-        <v>1219</v>
+        <v>1222</v>
       </c>
       <c r="E238" s="5" t="s">
-        <v>1217</v>
+        <v>1220</v>
       </c>
     </row>
     <row r="239" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -12474,16 +12577,16 @@
         <v>230</v>
       </c>
       <c r="B239" s="5" t="s">
-        <v>871</v>
+        <v>874</v>
       </c>
       <c r="C239" s="5" t="s">
+        <v>1223</v>
+      </c>
+      <c r="D239" s="6" t="s">
+        <v>1224</v>
+      </c>
+      <c r="E239" s="5" t="s">
         <v>1220</v>
-      </c>
-      <c r="D239" s="6" t="s">
-        <v>1221</v>
-      </c>
-      <c r="E239" s="5" t="s">
-        <v>1217</v>
       </c>
     </row>
     <row r="240" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -12491,16 +12594,16 @@
         <v>231</v>
       </c>
       <c r="B240" s="5" t="s">
-        <v>1039</v>
+        <v>1042</v>
       </c>
       <c r="C240" s="5" t="s">
-        <v>1222</v>
+        <v>1225</v>
       </c>
       <c r="D240" s="6" t="s">
-        <v>1223</v>
+        <v>1226</v>
       </c>
       <c r="E240" s="5" t="s">
-        <v>1217</v>
+        <v>1220</v>
       </c>
     </row>
     <row r="241" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -12508,16 +12611,16 @@
         <v>232</v>
       </c>
       <c r="B241" s="5" t="s">
-        <v>1039</v>
+        <v>1042</v>
       </c>
       <c r="C241" s="5" t="s">
-        <v>1224</v>
+        <v>1227</v>
       </c>
       <c r="D241" s="6" t="s">
-        <v>1225</v>
+        <v>1228</v>
       </c>
       <c r="E241" s="5" t="s">
-        <v>1217</v>
+        <v>1220</v>
       </c>
     </row>
     <row r="242" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -12525,13 +12628,13 @@
         <v>233</v>
       </c>
       <c r="B242" s="5" t="s">
-        <v>871</v>
+        <v>874</v>
       </c>
       <c r="C242" s="5" t="s">
-        <v>1226</v>
+        <v>1229</v>
       </c>
       <c r="D242" s="6" t="s">
-        <v>1227</v>
+        <v>1230</v>
       </c>
       <c r="E242" s="5" t="s">
         <v>559</v>
@@ -12542,16 +12645,16 @@
         <v>234</v>
       </c>
       <c r="B243" s="5" t="s">
-        <v>882</v>
+        <v>885</v>
       </c>
       <c r="C243" s="5" t="s">
-        <v>1228</v>
+        <v>1231</v>
       </c>
       <c r="D243" s="6" t="s">
-        <v>1229</v>
+        <v>1232</v>
       </c>
       <c r="E243" s="5" t="s">
-        <v>1230</v>
+        <v>1233</v>
       </c>
     </row>
     <row r="244" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -12559,16 +12662,16 @@
         <v>235</v>
       </c>
       <c r="B244" s="5" t="s">
-        <v>676</v>
+        <v>679</v>
       </c>
       <c r="C244" s="5" t="s">
-        <v>1231</v>
+        <v>1234</v>
       </c>
       <c r="D244" s="6" t="s">
-        <v>1232</v>
+        <v>1235</v>
       </c>
       <c r="E244" s="5" t="s">
-        <v>1230</v>
+        <v>1233</v>
       </c>
     </row>
     <row r="245" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -12576,16 +12679,16 @@
         <v>236</v>
       </c>
       <c r="B245" s="5" t="s">
-        <v>676</v>
+        <v>679</v>
       </c>
       <c r="C245" s="5" t="s">
+        <v>1236</v>
+      </c>
+      <c r="D245" s="6" t="s">
+        <v>1237</v>
+      </c>
+      <c r="E245" s="5" t="s">
         <v>1233</v>
-      </c>
-      <c r="D245" s="6" t="s">
-        <v>1234</v>
-      </c>
-      <c r="E245" s="5" t="s">
-        <v>1230</v>
       </c>
     </row>
     <row r="246" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -12593,16 +12696,84 @@
         <v>237</v>
       </c>
       <c r="B246" s="5" t="s">
-        <v>871</v>
+        <v>874</v>
       </c>
       <c r="C246" s="5" t="s">
-        <v>1235</v>
+        <v>1238</v>
       </c>
       <c r="D246" s="6" t="s">
-        <v>1236</v>
+        <v>1239</v>
       </c>
       <c r="E246" s="5" t="s">
-        <v>1230</v>
+        <v>1233</v>
+      </c>
+    </row>
+    <row r="247" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A247" s="5" t="n">
+        <v>238</v>
+      </c>
+      <c r="B247" s="5" t="s">
+        <v>818</v>
+      </c>
+      <c r="C247" s="5" t="s">
+        <v>1240</v>
+      </c>
+      <c r="D247" s="6" t="s">
+        <v>1241</v>
+      </c>
+      <c r="E247" s="5" t="s">
+        <v>562</v>
+      </c>
+    </row>
+    <row r="248" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A248" s="5" t="n">
+        <v>239</v>
+      </c>
+      <c r="B248" s="5" t="s">
+        <v>679</v>
+      </c>
+      <c r="C248" s="5" t="s">
+        <v>1242</v>
+      </c>
+      <c r="D248" s="6" t="s">
+        <v>1243</v>
+      </c>
+      <c r="E248" s="5" t="s">
+        <v>1244</v>
+      </c>
+    </row>
+    <row r="249" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A249" s="5" t="n">
+        <v>240</v>
+      </c>
+      <c r="B249" s="5" t="s">
+        <v>818</v>
+      </c>
+      <c r="C249" s="5" t="s">
+        <v>1245</v>
+      </c>
+      <c r="D249" s="6" t="s">
+        <v>1246</v>
+      </c>
+      <c r="E249" s="5" t="s">
+        <v>1244</v>
+      </c>
+    </row>
+    <row r="250" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A250" s="5" t="n">
+        <v>241</v>
+      </c>
+      <c r="B250" s="5" t="s">
+        <v>804</v>
+      </c>
+      <c r="C250" s="5" t="s">
+        <v>1247</v>
+      </c>
+      <c r="D250" s="6" t="s">
+        <v>1248</v>
+      </c>
+      <c r="E250" s="5" t="s">
+        <v>1249</v>
       </c>
     </row>
   </sheetData>
@@ -12774,6 +12945,10 @@
     <hyperlink ref="D244" r:id="rId162" display="https://www.nbcnews.com/politics/trump-administration/trump-announces-agreement-denmark-secure-permanent-control-greenlands-rcna598641"/>
     <hyperlink ref="D245" r:id="rId163" display="https://www.nbcnews.com/politics/national-security/state-department-approves-243b-f-35-fighter-jet-sale-saudi-arabia-chin-rcna598487"/>
     <hyperlink ref="D246" r:id="rId164" display="https://abcnews.com/Politics/wireStory/judge-rules-epa-illegally-terminated-7-billion-solar-136569326"/>
+    <hyperlink ref="D247" r:id="rId165" display="https://www.theguardian.com/us-news/video/2026/sep/21/austin-texas-ice-shooting-protests"/>
+    <hyperlink ref="D248" r:id="rId166" display="https://www.nbcnews.com/politics/supreme-court/supreme-court-allows-trump-administration-use-expanded-database-potent-rcna596611"/>
+    <hyperlink ref="D249" r:id="rId167" display="https://www.theguardian.com/us-news/ng-interactive/2026/sep/25/student-math-reading-test-scores"/>
+    <hyperlink ref="D250" r:id="rId168" display="https://www.bbc.com/news/articles/c3y0z25v0zjwo"/>
   </hyperlinks>
   <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.511811023622047" footer="0.511811023622047"/>
@@ -12799,7 +12974,7 @@
   <sheetData>
     <row r="1" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A1" s="7" t="s">
-        <v>1237</v>
+        <v>1250</v>
       </c>
       <c r="B1" s="7"/>
     </row>
@@ -12808,7 +12983,7 @@
         <v>3</v>
       </c>
       <c r="B2" s="8" t="s">
-        <v>1238</v>
+        <v>1251</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -12826,7 +13001,7 @@
       </c>
       <c r="B4" s="9" t="n">
         <f aca="false">COUNTIF('Weekly Timeline'!C:C,A4)</f>
-        <v>14</v>
+        <v>16</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -12862,7 +13037,7 @@
       </c>
       <c r="B8" s="9" t="n">
         <f aca="false">COUNTIF('Weekly Timeline'!C:C,A8)</f>
-        <v>4</v>
+        <v>5</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -12871,7 +13046,7 @@
       </c>
       <c r="B9" s="9" t="n">
         <f aca="false">COUNTIF('Weekly Timeline'!C:C,A9)</f>
-        <v>3</v>
+        <v>4</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -12984,11 +13159,11 @@
     </row>
     <row r="22" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A22" s="10" t="s">
-        <v>1239</v>
+        <v>1252</v>
       </c>
       <c r="B22" s="10" t="n">
         <f aca="false">SUM(B3:B21)</f>
-        <v>181</v>
+        <v>185</v>
       </c>
     </row>
   </sheetData>

--- a/data/Trump_Second_Term_Weekly_Tracker.xlsx
+++ b/data/Trump_Second_Term_Weekly_Tracker.xlsx
@@ -13,7 +13,7 @@
     <sheet name="Summary" sheetId="3" state="visible" r:id="rId5"/>
   </sheets>
   <definedNames>
-    <definedName function="false" hidden="true" localSheetId="0" name="_xlnm._FilterDatabase" vbProcedure="false">'Weekly Timeline'!$A$2:$F$243</definedName>
+    <definedName function="false" hidden="true" localSheetId="0" name="_xlnm._FilterDatabase" vbProcedure="false">'Weekly Timeline'!$A$2:$F$252</definedName>
   </definedNames>
   <calcPr iterateCount="100" refMode="A1" iterate="false" iterateDelta="0.0001"/>
   <extLst>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1927" uniqueCount="1253">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1991" uniqueCount="1279">
   <si>
     <t xml:space="preserve">Documented actions and policies of the second Trump administration reported as harmful by major news outlets, courts, and government data — Jan 20, 2025 through Jul 8, 2026. One row per event; weeks with multiple events have multiple rows; quiet weeks are skipped. This compiles critical coverage as requested; the administration and its supporters dispute many of these characterizations. See the Sources tab (matching Ref #) and verify details independently before citing.</t>
   </si>
@@ -1722,6 +1722,15 @@
     <t xml:space="preserve">Sep 20</t>
   </si>
   <si>
+    <t xml:space="preserve">Sep 26</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Law Enforcement</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Sep 22</t>
+  </si>
+  <si>
     <t xml:space="preserve">Ref # matches the Source Ref column on the Weekly Timeline tab. URLs are provided where verified via current web results (mostly 2026 items). For 2025 items, outlet names and dates are given; searching the description text will locate the original coverage. Per your request the mix emphasizes CNN, Politico, MSNBC/MS NOW, NBC and independent outlets, alongside AP, Reuters, Guardian, NPR, CBS, ABC and court documents.</t>
   </si>
   <si>
@@ -3775,6 +3784,75 @@
   </si>
   <si>
     <t xml:space="preserve">Sep 20, 2026</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ICE has abducted a college athlete. What are the NCAA and universities going to do about it?</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://www.theguardian.com/sport/2026/sep/26/aminata-seck-ice-international-college-athletes</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Sep 26, 2026</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Axios</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Trump TV is live. Here's what it's actually showing</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://www.axios.com/2026/09/22/trump-trumptv-white-house-live-news-network</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Sep 22, 2026</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Los Angeles Times</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Supreme Court upholds Trump's expanded citizenship data checks, stoking fears of voter purges</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://www.latimes.com/politics/story/2026-09-25/justices-uphold-trumps-expanded-data-checks-to-spot-non-citizens-who-registered-to-vote</t>
+  </si>
+  <si>
+    <t xml:space="preserve">White House blocks CNN from Air Force One in latest escalation with news media</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://www.theguardian.com/us-news/2026/sep/25/white-house-cnn-air-force-one</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Trump's proposed Washington arch to become sniper, drone facility</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://www.axios.com/2026/09/20/trump-arch-washington-snipers-drones</t>
+  </si>
+  <si>
+    <t xml:space="preserve">The New York Times</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Trump Proposes $810 Million in Education and Health Cuts, Defying Congress</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://www.nytimes.com/2026/09/25/us/politics/white-house-rescissions-education-and-health-funds.html</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Trump cancels nearly $1bn in funding approved by Congress</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://www.theguardian.com/us-news/2026/sep/25/trump-cancels-congress-funding</t>
+  </si>
+  <si>
+    <t xml:space="preserve">CNN is getting new owners with close ties to Trump</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://www.npr.org/2026/09/26/nx-s1-5981103/cnn-is-getting-new-owners-with-close-ties-to-trump</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Trump, addressing U.N., threatens to 'annihilate' Iran if war continues</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://www.latimes.com/politics/story/2026-09-22/trump-threatens-to-send-iran-into-hell-if-war-carries-on</t>
   </si>
   <si>
     <t xml:space="preserve">Entries by category (live COUNTIF formulas against the Weekly Timeline tab)</t>
@@ -3963,7 +4041,7 @@
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -4256,7 +4334,7 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:F243"/>
+  <dimension ref="A1:F252"/>
   <sheetFormatPr defaultColWidth="8.6875" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="13.01"/>
@@ -8600,7 +8678,7 @@
         <v>237</v>
       </c>
     </row>
-    <row r="240" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="240" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A240" s="5" t="s">
         <v>562</v>
       </c>
@@ -8616,7 +8694,7 @@
         <v>238</v>
       </c>
     </row>
-    <row r="241" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="241" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A241" s="5" t="s">
         <v>562</v>
       </c>
@@ -8632,7 +8710,7 @@
         <v>239</v>
       </c>
     </row>
-    <row r="242" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="242" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A242" s="5" t="s">
         <v>562</v>
       </c>
@@ -8648,7 +8726,7 @@
         <v>240</v>
       </c>
     </row>
-    <row r="243" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="243" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A243" s="4" t="s">
         <v>559</v>
       </c>
@@ -8664,8 +8742,152 @@
         <v>241</v>
       </c>
     </row>
+    <row r="244" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A244" s="5" t="s">
+        <v>562</v>
+      </c>
+      <c r="B244" s="5" t="s">
+        <v>565</v>
+      </c>
+      <c r="C244" s="5" t="s">
+        <v>566</v>
+      </c>
+      <c r="D244" s="5"/>
+      <c r="E244" s="5"/>
+      <c r="F244" s="5" t="n">
+        <v>242</v>
+      </c>
+    </row>
+    <row r="245" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A245" s="5" t="s">
+        <v>562</v>
+      </c>
+      <c r="B245" s="5" t="s">
+        <v>567</v>
+      </c>
+      <c r="C245" s="5" t="s">
+        <v>24</v>
+      </c>
+      <c r="D245" s="5"/>
+      <c r="E245" s="5"/>
+      <c r="F245" s="5" t="n">
+        <v>243</v>
+      </c>
+    </row>
+    <row r="246" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A246" s="5" t="s">
+        <v>562</v>
+      </c>
+      <c r="B246" s="5" t="s">
+        <v>246</v>
+      </c>
+      <c r="C246" s="5" t="s">
+        <v>194</v>
+      </c>
+      <c r="D246" s="5"/>
+      <c r="E246" s="5"/>
+      <c r="F246" s="5" t="n">
+        <v>244</v>
+      </c>
+    </row>
+    <row r="247" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A247" s="5" t="s">
+        <v>562</v>
+      </c>
+      <c r="B247" s="5" t="s">
+        <v>565</v>
+      </c>
+      <c r="C247" s="5" t="s">
+        <v>68</v>
+      </c>
+      <c r="D247" s="5"/>
+      <c r="E247" s="5"/>
+      <c r="F247" s="5" t="n">
+        <v>245</v>
+      </c>
+    </row>
+    <row r="248" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A248" s="4" t="s">
+        <v>559</v>
+      </c>
+      <c r="B248" s="4" t="s">
+        <v>564</v>
+      </c>
+      <c r="C248" s="4" t="s">
+        <v>553</v>
+      </c>
+      <c r="D248" s="4"/>
+      <c r="E248" s="4"/>
+      <c r="F248" s="4" t="n">
+        <v>246</v>
+      </c>
+    </row>
+    <row r="249" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A249" s="5" t="s">
+        <v>562</v>
+      </c>
+      <c r="B249" s="5" t="s">
+        <v>565</v>
+      </c>
+      <c r="C249" s="5" t="s">
+        <v>24</v>
+      </c>
+      <c r="D249" s="5"/>
+      <c r="E249" s="5"/>
+      <c r="F249" s="5" t="n">
+        <v>247</v>
+      </c>
+    </row>
+    <row r="250" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A250" s="5" t="s">
+        <v>562</v>
+      </c>
+      <c r="B250" s="5" t="s">
+        <v>565</v>
+      </c>
+      <c r="C250" s="5" t="s">
+        <v>24</v>
+      </c>
+      <c r="D250" s="5"/>
+      <c r="E250" s="5"/>
+      <c r="F250" s="5" t="n">
+        <v>248</v>
+      </c>
+    </row>
+    <row r="251" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A251" s="5" t="s">
+        <v>562</v>
+      </c>
+      <c r="B251" s="5" t="s">
+        <v>565</v>
+      </c>
+      <c r="C251" s="5" t="s">
+        <v>68</v>
+      </c>
+      <c r="D251" s="5"/>
+      <c r="E251" s="5"/>
+      <c r="F251" s="5" t="n">
+        <v>249</v>
+      </c>
+    </row>
+    <row r="252" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A252" s="5" t="s">
+        <v>562</v>
+      </c>
+      <c r="B252" s="5" t="s">
+        <v>567</v>
+      </c>
+      <c r="C252" s="5" t="s">
+        <v>48</v>
+      </c>
+      <c r="D252" s="5"/>
+      <c r="E252" s="5"/>
+      <c r="F252" s="5" t="n">
+        <v>250</v>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A2:F243"/>
+  <autoFilter ref="A2:F252"/>
   <mergeCells count="1">
     <mergeCell ref="A1:F1"/>
   </mergeCells>
@@ -8685,7 +8907,7 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:E250"/>
+  <dimension ref="A1:E259"/>
   <sheetFormatPr defaultColWidth="8.6875" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="7"/>
@@ -8696,7 +8918,7 @@
   <sheetData>
     <row r="1" customFormat="false" ht="48" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A1" s="2" t="s">
-        <v>565</v>
+        <v>568</v>
       </c>
       <c r="B1" s="2"/>
       <c r="C1" s="2"/>
@@ -8705,19 +8927,19 @@
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A2" s="3" t="s">
-        <v>566</v>
+        <v>569</v>
       </c>
       <c r="B2" s="3" t="s">
-        <v>567</v>
+        <v>570</v>
       </c>
       <c r="C2" s="3" t="s">
-        <v>568</v>
+        <v>571</v>
       </c>
       <c r="D2" s="3" t="s">
-        <v>569</v>
+        <v>572</v>
       </c>
       <c r="E2" s="3" t="s">
-        <v>570</v>
+        <v>573</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -8725,14 +8947,14 @@
         <v>1</v>
       </c>
       <c r="B3" s="5" t="s">
-        <v>571</v>
+        <v>574</v>
       </c>
       <c r="C3" s="5" t="s">
-        <v>572</v>
+        <v>575</v>
       </c>
       <c r="D3" s="5"/>
       <c r="E3" s="5" t="s">
-        <v>573</v>
+        <v>576</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -8740,14 +8962,14 @@
         <v>2</v>
       </c>
       <c r="B4" s="5" t="s">
-        <v>574</v>
+        <v>577</v>
       </c>
       <c r="C4" s="5" t="s">
-        <v>575</v>
+        <v>578</v>
       </c>
       <c r="D4" s="5"/>
       <c r="E4" s="5" t="s">
-        <v>576</v>
+        <v>579</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -8755,14 +8977,14 @@
         <v>3</v>
       </c>
       <c r="B5" s="5" t="s">
-        <v>577</v>
+        <v>580</v>
       </c>
       <c r="C5" s="5" t="s">
-        <v>578</v>
+        <v>581</v>
       </c>
       <c r="D5" s="5"/>
       <c r="E5" s="5" t="s">
-        <v>573</v>
+        <v>576</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -8770,14 +8992,14 @@
         <v>4</v>
       </c>
       <c r="B6" s="5" t="s">
-        <v>579</v>
+        <v>582</v>
       </c>
       <c r="C6" s="5" t="s">
-        <v>580</v>
+        <v>583</v>
       </c>
       <c r="D6" s="5"/>
       <c r="E6" s="5" t="s">
-        <v>581</v>
+        <v>584</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -8785,14 +9007,14 @@
         <v>5</v>
       </c>
       <c r="B7" s="5" t="s">
-        <v>582</v>
+        <v>585</v>
       </c>
       <c r="C7" s="5" t="s">
-        <v>583</v>
+        <v>586</v>
       </c>
       <c r="D7" s="5"/>
       <c r="E7" s="5" t="s">
-        <v>573</v>
+        <v>576</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -8800,14 +9022,14 @@
         <v>6</v>
       </c>
       <c r="B8" s="5" t="s">
-        <v>584</v>
+        <v>587</v>
       </c>
       <c r="C8" s="5" t="s">
-        <v>585</v>
+        <v>588</v>
       </c>
       <c r="D8" s="5"/>
       <c r="E8" s="5" t="s">
-        <v>573</v>
+        <v>576</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -8815,14 +9037,14 @@
         <v>7</v>
       </c>
       <c r="B9" s="5" t="s">
-        <v>586</v>
+        <v>589</v>
       </c>
       <c r="C9" s="5" t="s">
-        <v>587</v>
+        <v>590</v>
       </c>
       <c r="D9" s="5"/>
       <c r="E9" s="5" t="s">
-        <v>588</v>
+        <v>591</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -8830,14 +9052,14 @@
         <v>8</v>
       </c>
       <c r="B10" s="5" t="s">
-        <v>589</v>
+        <v>592</v>
       </c>
       <c r="C10" s="5" t="s">
-        <v>590</v>
+        <v>593</v>
       </c>
       <c r="D10" s="5"/>
       <c r="E10" s="5" t="s">
-        <v>591</v>
+        <v>594</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -8845,14 +9067,14 @@
         <v>9</v>
       </c>
       <c r="B11" s="5" t="s">
-        <v>592</v>
+        <v>595</v>
       </c>
       <c r="C11" s="5" t="s">
-        <v>593</v>
+        <v>596</v>
       </c>
       <c r="D11" s="5"/>
       <c r="E11" s="5" t="s">
-        <v>594</v>
+        <v>597</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -8860,14 +9082,14 @@
         <v>10</v>
       </c>
       <c r="B12" s="5" t="s">
-        <v>595</v>
+        <v>598</v>
       </c>
       <c r="C12" s="5" t="s">
-        <v>596</v>
+        <v>599</v>
       </c>
       <c r="D12" s="5"/>
       <c r="E12" s="5" t="s">
-        <v>597</v>
+        <v>600</v>
       </c>
     </row>
     <row r="13" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -8875,14 +9097,14 @@
         <v>11</v>
       </c>
       <c r="B13" s="5" t="s">
-        <v>598</v>
+        <v>601</v>
       </c>
       <c r="C13" s="5" t="s">
-        <v>599</v>
+        <v>602</v>
       </c>
       <c r="D13" s="5"/>
       <c r="E13" s="5" t="s">
-        <v>600</v>
+        <v>603</v>
       </c>
     </row>
     <row r="14" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -8890,14 +9112,14 @@
         <v>12</v>
       </c>
       <c r="B14" s="5" t="s">
-        <v>601</v>
+        <v>604</v>
       </c>
       <c r="C14" s="5" t="s">
-        <v>602</v>
+        <v>605</v>
       </c>
       <c r="D14" s="5"/>
       <c r="E14" s="5" t="s">
-        <v>603</v>
+        <v>606</v>
       </c>
     </row>
     <row r="15" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -8905,14 +9127,14 @@
         <v>13</v>
       </c>
       <c r="B15" s="5" t="s">
-        <v>604</v>
+        <v>607</v>
       </c>
       <c r="C15" s="5" t="s">
-        <v>605</v>
+        <v>608</v>
       </c>
       <c r="D15" s="5"/>
       <c r="E15" s="5" t="s">
-        <v>606</v>
+        <v>609</v>
       </c>
     </row>
     <row r="16" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -8920,14 +9142,14 @@
         <v>14</v>
       </c>
       <c r="B16" s="5" t="s">
-        <v>607</v>
+        <v>610</v>
       </c>
       <c r="C16" s="5" t="s">
-        <v>608</v>
+        <v>611</v>
       </c>
       <c r="D16" s="5"/>
       <c r="E16" s="5" t="s">
-        <v>609</v>
+        <v>612</v>
       </c>
     </row>
     <row r="17" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -8935,14 +9157,14 @@
         <v>15</v>
       </c>
       <c r="B17" s="5" t="s">
-        <v>610</v>
+        <v>613</v>
       </c>
       <c r="C17" s="5" t="s">
-        <v>611</v>
+        <v>614</v>
       </c>
       <c r="D17" s="5"/>
       <c r="E17" s="5" t="s">
-        <v>612</v>
+        <v>615</v>
       </c>
     </row>
     <row r="18" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -8950,14 +9172,14 @@
         <v>16</v>
       </c>
       <c r="B18" s="5" t="s">
-        <v>613</v>
+        <v>616</v>
       </c>
       <c r="C18" s="5" t="s">
-        <v>614</v>
+        <v>617</v>
       </c>
       <c r="D18" s="5"/>
       <c r="E18" s="5" t="s">
-        <v>615</v>
+        <v>618</v>
       </c>
     </row>
     <row r="19" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -8965,14 +9187,14 @@
         <v>17</v>
       </c>
       <c r="B19" s="5" t="s">
-        <v>616</v>
+        <v>619</v>
       </c>
       <c r="C19" s="5" t="s">
-        <v>617</v>
+        <v>620</v>
       </c>
       <c r="D19" s="5"/>
       <c r="E19" s="5" t="s">
-        <v>618</v>
+        <v>621</v>
       </c>
     </row>
     <row r="20" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -8980,14 +9202,14 @@
         <v>18</v>
       </c>
       <c r="B20" s="5" t="s">
-        <v>619</v>
+        <v>622</v>
       </c>
       <c r="C20" s="5" t="s">
-        <v>620</v>
+        <v>623</v>
       </c>
       <c r="D20" s="5"/>
       <c r="E20" s="5" t="s">
-        <v>621</v>
+        <v>624</v>
       </c>
     </row>
     <row r="21" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -8995,14 +9217,14 @@
         <v>19</v>
       </c>
       <c r="B21" s="5" t="s">
-        <v>622</v>
+        <v>625</v>
       </c>
       <c r="C21" s="5" t="s">
-        <v>623</v>
+        <v>626</v>
       </c>
       <c r="D21" s="5"/>
       <c r="E21" s="5" t="s">
-        <v>624</v>
+        <v>627</v>
       </c>
     </row>
     <row r="22" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -9010,14 +9232,14 @@
         <v>20</v>
       </c>
       <c r="B22" s="5" t="s">
-        <v>625</v>
+        <v>628</v>
       </c>
       <c r="C22" s="5" t="s">
-        <v>626</v>
+        <v>629</v>
       </c>
       <c r="D22" s="5"/>
       <c r="E22" s="5" t="s">
-        <v>627</v>
+        <v>630</v>
       </c>
     </row>
     <row r="23" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -9025,14 +9247,14 @@
         <v>21</v>
       </c>
       <c r="B23" s="5" t="s">
-        <v>628</v>
+        <v>631</v>
       </c>
       <c r="C23" s="5" t="s">
-        <v>629</v>
+        <v>632</v>
       </c>
       <c r="D23" s="5"/>
       <c r="E23" s="5" t="s">
-        <v>630</v>
+        <v>633</v>
       </c>
     </row>
     <row r="24" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -9040,14 +9262,14 @@
         <v>22</v>
       </c>
       <c r="B24" s="5" t="s">
-        <v>631</v>
+        <v>634</v>
       </c>
       <c r="C24" s="5" t="s">
-        <v>632</v>
+        <v>635</v>
       </c>
       <c r="D24" s="5"/>
       <c r="E24" s="5" t="s">
-        <v>633</v>
+        <v>636</v>
       </c>
     </row>
     <row r="25" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -9055,14 +9277,14 @@
         <v>23</v>
       </c>
       <c r="B25" s="5" t="s">
-        <v>634</v>
+        <v>637</v>
       </c>
       <c r="C25" s="5" t="s">
-        <v>635</v>
+        <v>638</v>
       </c>
       <c r="D25" s="5"/>
       <c r="E25" s="5" t="s">
-        <v>636</v>
+        <v>639</v>
       </c>
     </row>
     <row r="26" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -9070,14 +9292,14 @@
         <v>24</v>
       </c>
       <c r="B26" s="5" t="s">
-        <v>637</v>
+        <v>640</v>
       </c>
       <c r="C26" s="5" t="s">
-        <v>638</v>
+        <v>641</v>
       </c>
       <c r="D26" s="5"/>
       <c r="E26" s="5" t="s">
-        <v>639</v>
+        <v>642</v>
       </c>
     </row>
     <row r="27" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -9085,14 +9307,14 @@
         <v>25</v>
       </c>
       <c r="B27" s="5" t="s">
-        <v>640</v>
+        <v>643</v>
       </c>
       <c r="C27" s="5" t="s">
-        <v>641</v>
+        <v>644</v>
       </c>
       <c r="D27" s="5"/>
       <c r="E27" s="5" t="s">
-        <v>642</v>
+        <v>645</v>
       </c>
     </row>
     <row r="28" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -9100,14 +9322,14 @@
         <v>26</v>
       </c>
       <c r="B28" s="5" t="s">
-        <v>643</v>
+        <v>646</v>
       </c>
       <c r="C28" s="5" t="s">
-        <v>644</v>
+        <v>647</v>
       </c>
       <c r="D28" s="5"/>
       <c r="E28" s="5" t="s">
-        <v>645</v>
+        <v>648</v>
       </c>
     </row>
     <row r="29" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -9115,14 +9337,14 @@
         <v>27</v>
       </c>
       <c r="B29" s="5" t="s">
-        <v>646</v>
+        <v>649</v>
       </c>
       <c r="C29" s="5" t="s">
-        <v>647</v>
+        <v>650</v>
       </c>
       <c r="D29" s="5"/>
       <c r="E29" s="5" t="s">
-        <v>648</v>
+        <v>651</v>
       </c>
     </row>
     <row r="30" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -9130,14 +9352,14 @@
         <v>28</v>
       </c>
       <c r="B30" s="5" t="s">
-        <v>649</v>
+        <v>652</v>
       </c>
       <c r="C30" s="5" t="s">
-        <v>650</v>
+        <v>653</v>
       </c>
       <c r="D30" s="5"/>
       <c r="E30" s="5" t="s">
-        <v>651</v>
+        <v>654</v>
       </c>
     </row>
     <row r="31" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -9145,14 +9367,14 @@
         <v>29</v>
       </c>
       <c r="B31" s="5" t="s">
-        <v>652</v>
+        <v>655</v>
       </c>
       <c r="C31" s="5" t="s">
-        <v>653</v>
+        <v>656</v>
       </c>
       <c r="D31" s="5"/>
       <c r="E31" s="5" t="s">
-        <v>654</v>
+        <v>657</v>
       </c>
     </row>
     <row r="32" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -9160,14 +9382,14 @@
         <v>30</v>
       </c>
       <c r="B32" s="5" t="s">
-        <v>598</v>
+        <v>601</v>
       </c>
       <c r="C32" s="5" t="s">
-        <v>655</v>
+        <v>658</v>
       </c>
       <c r="D32" s="5"/>
       <c r="E32" s="5" t="s">
-        <v>656</v>
+        <v>659</v>
       </c>
     </row>
     <row r="33" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -9175,14 +9397,14 @@
         <v>31</v>
       </c>
       <c r="B33" s="5" t="s">
-        <v>657</v>
+        <v>660</v>
       </c>
       <c r="C33" s="5" t="s">
-        <v>658</v>
+        <v>661</v>
       </c>
       <c r="D33" s="5"/>
       <c r="E33" s="5" t="s">
-        <v>659</v>
+        <v>662</v>
       </c>
     </row>
     <row r="34" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -9190,14 +9412,14 @@
         <v>32</v>
       </c>
       <c r="B34" s="5" t="s">
-        <v>616</v>
+        <v>619</v>
       </c>
       <c r="C34" s="5" t="s">
-        <v>660</v>
+        <v>663</v>
       </c>
       <c r="D34" s="5"/>
       <c r="E34" s="5" t="s">
-        <v>661</v>
+        <v>664</v>
       </c>
     </row>
     <row r="35" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -9205,14 +9427,14 @@
         <v>33</v>
       </c>
       <c r="B35" s="5" t="s">
-        <v>662</v>
+        <v>665</v>
       </c>
       <c r="C35" s="5" t="s">
-        <v>663</v>
+        <v>666</v>
       </c>
       <c r="D35" s="5"/>
       <c r="E35" s="5" t="s">
-        <v>664</v>
+        <v>667</v>
       </c>
     </row>
     <row r="36" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -9220,14 +9442,14 @@
         <v>34</v>
       </c>
       <c r="B36" s="5" t="s">
-        <v>665</v>
+        <v>668</v>
       </c>
       <c r="C36" s="5" t="s">
-        <v>666</v>
+        <v>669</v>
       </c>
       <c r="D36" s="5"/>
       <c r="E36" s="5" t="s">
-        <v>667</v>
+        <v>670</v>
       </c>
     </row>
     <row r="37" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -9235,14 +9457,14 @@
         <v>35</v>
       </c>
       <c r="B37" s="5" t="s">
-        <v>668</v>
+        <v>671</v>
       </c>
       <c r="C37" s="5" t="s">
-        <v>669</v>
+        <v>672</v>
       </c>
       <c r="D37" s="5"/>
       <c r="E37" s="5" t="s">
-        <v>670</v>
+        <v>673</v>
       </c>
     </row>
     <row r="38" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -9250,14 +9472,14 @@
         <v>36</v>
       </c>
       <c r="B38" s="5" t="s">
-        <v>616</v>
+        <v>619</v>
       </c>
       <c r="C38" s="5" t="s">
-        <v>671</v>
+        <v>674</v>
       </c>
       <c r="D38" s="5"/>
       <c r="E38" s="5" t="s">
-        <v>672</v>
+        <v>675</v>
       </c>
     </row>
     <row r="39" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -9265,14 +9487,14 @@
         <v>37</v>
       </c>
       <c r="B39" s="5" t="s">
-        <v>673</v>
+        <v>676</v>
       </c>
       <c r="C39" s="5" t="s">
-        <v>674</v>
+        <v>677</v>
       </c>
       <c r="D39" s="5"/>
       <c r="E39" s="5" t="s">
-        <v>675</v>
+        <v>678</v>
       </c>
     </row>
     <row r="40" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -9280,14 +9502,14 @@
         <v>38</v>
       </c>
       <c r="B40" s="5" t="s">
-        <v>676</v>
+        <v>679</v>
       </c>
       <c r="C40" s="5" t="s">
-        <v>677</v>
+        <v>680</v>
       </c>
       <c r="D40" s="5"/>
       <c r="E40" s="5" t="s">
-        <v>678</v>
+        <v>681</v>
       </c>
     </row>
     <row r="41" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -9295,10 +9517,10 @@
         <v>39</v>
       </c>
       <c r="B41" s="5" t="s">
-        <v>679</v>
+        <v>682</v>
       </c>
       <c r="C41" s="5" t="s">
-        <v>680</v>
+        <v>683</v>
       </c>
       <c r="D41" s="5"/>
       <c r="E41" s="5" t="s">
@@ -9310,14 +9532,14 @@
         <v>40</v>
       </c>
       <c r="B42" s="5" t="s">
-        <v>681</v>
+        <v>684</v>
       </c>
       <c r="C42" s="5" t="s">
-        <v>682</v>
+        <v>685</v>
       </c>
       <c r="D42" s="5"/>
       <c r="E42" s="5" t="s">
-        <v>683</v>
+        <v>686</v>
       </c>
     </row>
     <row r="43" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -9325,14 +9547,14 @@
         <v>41</v>
       </c>
       <c r="B43" s="5" t="s">
-        <v>684</v>
+        <v>687</v>
       </c>
       <c r="C43" s="5" t="s">
-        <v>685</v>
+        <v>688</v>
       </c>
       <c r="D43" s="5"/>
       <c r="E43" s="5" t="s">
-        <v>686</v>
+        <v>689</v>
       </c>
     </row>
     <row r="44" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -9340,14 +9562,14 @@
         <v>42</v>
       </c>
       <c r="B44" s="5" t="s">
-        <v>687</v>
+        <v>690</v>
       </c>
       <c r="C44" s="5" t="s">
-        <v>688</v>
+        <v>691</v>
       </c>
       <c r="D44" s="5"/>
       <c r="E44" s="5" t="s">
-        <v>689</v>
+        <v>692</v>
       </c>
     </row>
     <row r="45" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -9355,14 +9577,14 @@
         <v>43</v>
       </c>
       <c r="B45" s="5" t="s">
-        <v>690</v>
+        <v>693</v>
       </c>
       <c r="C45" s="5" t="s">
-        <v>691</v>
+        <v>694</v>
       </c>
       <c r="D45" s="5"/>
       <c r="E45" s="5" t="s">
-        <v>692</v>
+        <v>695</v>
       </c>
     </row>
     <row r="46" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -9370,14 +9592,14 @@
         <v>44</v>
       </c>
       <c r="B46" s="5" t="s">
-        <v>693</v>
+        <v>696</v>
       </c>
       <c r="C46" s="5" t="s">
-        <v>694</v>
+        <v>697</v>
       </c>
       <c r="D46" s="5"/>
       <c r="E46" s="5" t="s">
-        <v>695</v>
+        <v>698</v>
       </c>
     </row>
     <row r="47" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -9385,14 +9607,14 @@
         <v>45</v>
       </c>
       <c r="B47" s="5" t="s">
-        <v>696</v>
+        <v>699</v>
       </c>
       <c r="C47" s="5" t="s">
-        <v>697</v>
+        <v>700</v>
       </c>
       <c r="D47" s="5"/>
       <c r="E47" s="5" t="s">
-        <v>698</v>
+        <v>701</v>
       </c>
     </row>
     <row r="48" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -9400,14 +9622,14 @@
         <v>46</v>
       </c>
       <c r="B48" s="5" t="s">
-        <v>699</v>
+        <v>702</v>
       </c>
       <c r="C48" s="5" t="s">
-        <v>700</v>
+        <v>703</v>
       </c>
       <c r="D48" s="5"/>
       <c r="E48" s="5" t="s">
-        <v>701</v>
+        <v>704</v>
       </c>
     </row>
     <row r="49" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -9415,14 +9637,14 @@
         <v>47</v>
       </c>
       <c r="B49" s="5" t="s">
-        <v>702</v>
+        <v>705</v>
       </c>
       <c r="C49" s="5" t="s">
-        <v>703</v>
+        <v>706</v>
       </c>
       <c r="D49" s="5"/>
       <c r="E49" s="5" t="s">
-        <v>704</v>
+        <v>707</v>
       </c>
     </row>
     <row r="50" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -9430,14 +9652,14 @@
         <v>48</v>
       </c>
       <c r="B50" s="5" t="s">
-        <v>705</v>
+        <v>708</v>
       </c>
       <c r="C50" s="5" t="s">
-        <v>706</v>
+        <v>709</v>
       </c>
       <c r="D50" s="5"/>
       <c r="E50" s="5" t="s">
-        <v>707</v>
+        <v>710</v>
       </c>
     </row>
     <row r="51" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -9445,14 +9667,14 @@
         <v>49</v>
       </c>
       <c r="B51" s="5" t="s">
-        <v>708</v>
+        <v>711</v>
       </c>
       <c r="C51" s="5" t="s">
-        <v>709</v>
+        <v>712</v>
       </c>
       <c r="D51" s="5"/>
       <c r="E51" s="5" t="s">
-        <v>710</v>
+        <v>713</v>
       </c>
     </row>
     <row r="52" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -9460,14 +9682,14 @@
         <v>50</v>
       </c>
       <c r="B52" s="5" t="s">
-        <v>711</v>
+        <v>714</v>
       </c>
       <c r="C52" s="5" t="s">
-        <v>712</v>
+        <v>715</v>
       </c>
       <c r="D52" s="5"/>
       <c r="E52" s="5" t="s">
-        <v>713</v>
+        <v>716</v>
       </c>
     </row>
     <row r="53" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -9475,14 +9697,14 @@
         <v>51</v>
       </c>
       <c r="B53" s="5" t="s">
-        <v>714</v>
+        <v>717</v>
       </c>
       <c r="C53" s="5" t="s">
-        <v>715</v>
+        <v>718</v>
       </c>
       <c r="D53" s="5"/>
       <c r="E53" s="5" t="s">
-        <v>716</v>
+        <v>719</v>
       </c>
     </row>
     <row r="54" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -9490,14 +9712,14 @@
         <v>52</v>
       </c>
       <c r="B54" s="5" t="s">
-        <v>616</v>
+        <v>619</v>
       </c>
       <c r="C54" s="5" t="s">
-        <v>717</v>
+        <v>720</v>
       </c>
       <c r="D54" s="5"/>
       <c r="E54" s="5" t="s">
-        <v>718</v>
+        <v>721</v>
       </c>
     </row>
     <row r="55" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -9505,14 +9727,14 @@
         <v>53</v>
       </c>
       <c r="B55" s="5" t="s">
-        <v>719</v>
+        <v>722</v>
       </c>
       <c r="C55" s="5" t="s">
-        <v>720</v>
+        <v>723</v>
       </c>
       <c r="D55" s="5"/>
       <c r="E55" s="5" t="s">
-        <v>721</v>
+        <v>724</v>
       </c>
     </row>
     <row r="56" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -9520,14 +9742,14 @@
         <v>54</v>
       </c>
       <c r="B56" s="5" t="s">
-        <v>722</v>
+        <v>725</v>
       </c>
       <c r="C56" s="5" t="s">
-        <v>723</v>
+        <v>726</v>
       </c>
       <c r="D56" s="5"/>
       <c r="E56" s="5" t="s">
-        <v>724</v>
+        <v>727</v>
       </c>
     </row>
     <row r="57" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -9535,14 +9757,14 @@
         <v>55</v>
       </c>
       <c r="B57" s="5" t="s">
-        <v>725</v>
+        <v>728</v>
       </c>
       <c r="C57" s="5" t="s">
-        <v>726</v>
+        <v>729</v>
       </c>
       <c r="D57" s="5"/>
       <c r="E57" s="5" t="s">
-        <v>727</v>
+        <v>730</v>
       </c>
     </row>
     <row r="58" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -9550,14 +9772,14 @@
         <v>56</v>
       </c>
       <c r="B58" s="5" t="s">
-        <v>728</v>
+        <v>731</v>
       </c>
       <c r="C58" s="5" t="s">
-        <v>729</v>
+        <v>732</v>
       </c>
       <c r="D58" s="5"/>
       <c r="E58" s="5" t="s">
-        <v>730</v>
+        <v>733</v>
       </c>
     </row>
     <row r="59" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -9565,14 +9787,14 @@
         <v>57</v>
       </c>
       <c r="B59" s="5" t="s">
-        <v>731</v>
+        <v>734</v>
       </c>
       <c r="C59" s="5" t="s">
-        <v>732</v>
+        <v>735</v>
       </c>
       <c r="D59" s="5"/>
       <c r="E59" s="5" t="s">
-        <v>733</v>
+        <v>736</v>
       </c>
     </row>
     <row r="60" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -9580,14 +9802,14 @@
         <v>58</v>
       </c>
       <c r="B60" s="5" t="s">
-        <v>734</v>
+        <v>737</v>
       </c>
       <c r="C60" s="5" t="s">
-        <v>735</v>
+        <v>738</v>
       </c>
       <c r="D60" s="5"/>
       <c r="E60" s="5" t="s">
-        <v>736</v>
+        <v>739</v>
       </c>
     </row>
     <row r="61" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -9595,14 +9817,14 @@
         <v>59</v>
       </c>
       <c r="B61" s="5" t="s">
-        <v>737</v>
+        <v>740</v>
       </c>
       <c r="C61" s="5" t="s">
-        <v>738</v>
+        <v>741</v>
       </c>
       <c r="D61" s="5"/>
       <c r="E61" s="5" t="s">
-        <v>739</v>
+        <v>742</v>
       </c>
     </row>
     <row r="62" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -9610,14 +9832,14 @@
         <v>60</v>
       </c>
       <c r="B62" s="5" t="s">
-        <v>740</v>
+        <v>743</v>
       </c>
       <c r="C62" s="5" t="s">
-        <v>741</v>
+        <v>744</v>
       </c>
       <c r="D62" s="5"/>
       <c r="E62" s="5" t="s">
-        <v>742</v>
+        <v>745</v>
       </c>
     </row>
     <row r="63" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -9625,14 +9847,14 @@
         <v>61</v>
       </c>
       <c r="B63" s="5" t="s">
-        <v>743</v>
+        <v>746</v>
       </c>
       <c r="C63" s="5" t="s">
-        <v>744</v>
+        <v>747</v>
       </c>
       <c r="D63" s="5"/>
       <c r="E63" s="5" t="s">
-        <v>745</v>
+        <v>748</v>
       </c>
     </row>
     <row r="64" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -9640,14 +9862,14 @@
         <v>62</v>
       </c>
       <c r="B64" s="5" t="s">
-        <v>746</v>
+        <v>749</v>
       </c>
       <c r="C64" s="5" t="s">
-        <v>747</v>
+        <v>750</v>
       </c>
       <c r="D64" s="5"/>
       <c r="E64" s="5" t="s">
-        <v>748</v>
+        <v>751</v>
       </c>
     </row>
     <row r="65" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -9655,14 +9877,14 @@
         <v>63</v>
       </c>
       <c r="B65" s="5" t="s">
-        <v>749</v>
+        <v>752</v>
       </c>
       <c r="C65" s="5" t="s">
-        <v>750</v>
+        <v>753</v>
       </c>
       <c r="D65" s="5"/>
       <c r="E65" s="5" t="s">
-        <v>751</v>
+        <v>754</v>
       </c>
     </row>
     <row r="66" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -9670,14 +9892,14 @@
         <v>64</v>
       </c>
       <c r="B66" s="5" t="s">
-        <v>752</v>
+        <v>755</v>
       </c>
       <c r="C66" s="5" t="s">
-        <v>753</v>
+        <v>756</v>
       </c>
       <c r="D66" s="5"/>
       <c r="E66" s="5" t="s">
-        <v>754</v>
+        <v>757</v>
       </c>
     </row>
     <row r="67" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -9685,14 +9907,14 @@
         <v>65</v>
       </c>
       <c r="B67" s="5" t="s">
-        <v>755</v>
+        <v>758</v>
       </c>
       <c r="C67" s="5" t="s">
-        <v>756</v>
+        <v>759</v>
       </c>
       <c r="D67" s="5"/>
       <c r="E67" s="5" t="s">
-        <v>757</v>
+        <v>760</v>
       </c>
     </row>
     <row r="68" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -9700,14 +9922,14 @@
         <v>66</v>
       </c>
       <c r="B68" s="5" t="s">
-        <v>758</v>
+        <v>761</v>
       </c>
       <c r="C68" s="5" t="s">
-        <v>759</v>
+        <v>762</v>
       </c>
       <c r="D68" s="5"/>
       <c r="E68" s="5" t="s">
-        <v>760</v>
+        <v>763</v>
       </c>
     </row>
     <row r="69" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -9715,14 +9937,14 @@
         <v>67</v>
       </c>
       <c r="B69" s="5" t="s">
-        <v>761</v>
+        <v>764</v>
       </c>
       <c r="C69" s="5" t="s">
-        <v>762</v>
+        <v>765</v>
       </c>
       <c r="D69" s="5"/>
       <c r="E69" s="5" t="s">
-        <v>763</v>
+        <v>766</v>
       </c>
     </row>
     <row r="70" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -9730,14 +9952,14 @@
         <v>68</v>
       </c>
       <c r="B70" s="5" t="s">
-        <v>764</v>
+        <v>767</v>
       </c>
       <c r="C70" s="5" t="s">
-        <v>765</v>
+        <v>768</v>
       </c>
       <c r="D70" s="5"/>
       <c r="E70" s="5" t="s">
-        <v>766</v>
+        <v>769</v>
       </c>
     </row>
     <row r="71" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -9745,14 +9967,14 @@
         <v>69</v>
       </c>
       <c r="B71" s="5" t="s">
-        <v>767</v>
+        <v>770</v>
       </c>
       <c r="C71" s="5" t="s">
-        <v>768</v>
+        <v>771</v>
       </c>
       <c r="D71" s="5"/>
       <c r="E71" s="5" t="s">
-        <v>769</v>
+        <v>772</v>
       </c>
     </row>
     <row r="72" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -9760,14 +9982,14 @@
         <v>70</v>
       </c>
       <c r="B72" s="5" t="s">
-        <v>770</v>
+        <v>773</v>
       </c>
       <c r="C72" s="5" t="s">
-        <v>771</v>
+        <v>774</v>
       </c>
       <c r="D72" s="5"/>
       <c r="E72" s="5" t="s">
-        <v>772</v>
+        <v>775</v>
       </c>
     </row>
     <row r="73" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -9775,14 +9997,14 @@
         <v>71</v>
       </c>
       <c r="B73" s="5" t="s">
-        <v>773</v>
+        <v>776</v>
       </c>
       <c r="C73" s="5" t="s">
-        <v>774</v>
+        <v>777</v>
       </c>
       <c r="D73" s="5"/>
       <c r="E73" s="5" t="s">
-        <v>775</v>
+        <v>778</v>
       </c>
     </row>
     <row r="74" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -9790,14 +10012,14 @@
         <v>72</v>
       </c>
       <c r="B74" s="5" t="s">
-        <v>776</v>
+        <v>779</v>
       </c>
       <c r="C74" s="5" t="s">
-        <v>777</v>
+        <v>780</v>
       </c>
       <c r="D74" s="5"/>
       <c r="E74" s="5" t="s">
-        <v>778</v>
+        <v>781</v>
       </c>
     </row>
     <row r="75" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -9805,14 +10027,14 @@
         <v>73</v>
       </c>
       <c r="B75" s="5" t="s">
-        <v>616</v>
+        <v>619</v>
       </c>
       <c r="C75" s="5" t="s">
-        <v>779</v>
+        <v>782</v>
       </c>
       <c r="D75" s="5"/>
       <c r="E75" s="5" t="s">
-        <v>780</v>
+        <v>783</v>
       </c>
     </row>
     <row r="76" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -9820,14 +10042,14 @@
         <v>74</v>
       </c>
       <c r="B76" s="5" t="s">
-        <v>781</v>
+        <v>784</v>
       </c>
       <c r="C76" s="5" t="s">
-        <v>782</v>
+        <v>785</v>
       </c>
       <c r="D76" s="5"/>
       <c r="E76" s="5" t="s">
-        <v>783</v>
+        <v>786</v>
       </c>
     </row>
     <row r="77" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -9835,14 +10057,14 @@
         <v>75</v>
       </c>
       <c r="B77" s="5" t="s">
-        <v>616</v>
+        <v>619</v>
       </c>
       <c r="C77" s="5" t="s">
-        <v>784</v>
+        <v>787</v>
       </c>
       <c r="D77" s="5"/>
       <c r="E77" s="5" t="s">
-        <v>785</v>
+        <v>788</v>
       </c>
     </row>
     <row r="78" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -9850,14 +10072,14 @@
         <v>76</v>
       </c>
       <c r="B78" s="5" t="s">
-        <v>786</v>
+        <v>789</v>
       </c>
       <c r="C78" s="5" t="s">
-        <v>787</v>
+        <v>790</v>
       </c>
       <c r="D78" s="5"/>
       <c r="E78" s="5" t="s">
-        <v>788</v>
+        <v>791</v>
       </c>
     </row>
     <row r="79" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -9865,14 +10087,14 @@
         <v>77</v>
       </c>
       <c r="B79" s="5" t="s">
-        <v>789</v>
+        <v>792</v>
       </c>
       <c r="C79" s="5" t="s">
-        <v>790</v>
+        <v>793</v>
       </c>
       <c r="D79" s="5"/>
       <c r="E79" s="5" t="s">
-        <v>791</v>
+        <v>794</v>
       </c>
     </row>
     <row r="80" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -9880,14 +10102,14 @@
         <v>78</v>
       </c>
       <c r="B80" s="5" t="s">
-        <v>714</v>
+        <v>717</v>
       </c>
       <c r="C80" s="5" t="s">
-        <v>792</v>
+        <v>795</v>
       </c>
       <c r="D80" s="5"/>
       <c r="E80" s="5" t="s">
-        <v>793</v>
+        <v>796</v>
       </c>
     </row>
     <row r="81" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -9895,14 +10117,14 @@
         <v>79</v>
       </c>
       <c r="B81" s="5" t="s">
-        <v>586</v>
+        <v>589</v>
       </c>
       <c r="C81" s="5" t="s">
-        <v>794</v>
+        <v>797</v>
       </c>
       <c r="D81" s="5"/>
       <c r="E81" s="5" t="s">
-        <v>795</v>
+        <v>798</v>
       </c>
     </row>
     <row r="82" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -9910,16 +10132,16 @@
         <v>80</v>
       </c>
       <c r="B82" s="5" t="s">
-        <v>796</v>
+        <v>799</v>
       </c>
       <c r="C82" s="5" t="s">
-        <v>797</v>
+        <v>800</v>
       </c>
       <c r="D82" s="6" t="s">
-        <v>798</v>
+        <v>801</v>
       </c>
       <c r="E82" s="5" t="s">
-        <v>799</v>
+        <v>802</v>
       </c>
     </row>
     <row r="83" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -9927,16 +10149,16 @@
         <v>81</v>
       </c>
       <c r="B83" s="5" t="s">
-        <v>800</v>
+        <v>803</v>
       </c>
       <c r="C83" s="5" t="s">
-        <v>801</v>
+        <v>804</v>
       </c>
       <c r="D83" s="6" t="s">
-        <v>802</v>
+        <v>805</v>
       </c>
       <c r="E83" s="5" t="s">
-        <v>803</v>
+        <v>806</v>
       </c>
     </row>
     <row r="84" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -9944,13 +10166,13 @@
         <v>82</v>
       </c>
       <c r="B84" s="5" t="s">
-        <v>804</v>
+        <v>807</v>
       </c>
       <c r="C84" s="5" t="s">
-        <v>805</v>
+        <v>808</v>
       </c>
       <c r="D84" s="6" t="s">
-        <v>806</v>
+        <v>809</v>
       </c>
       <c r="E84" s="5" t="s">
         <v>297</v>
@@ -9961,13 +10183,13 @@
         <v>83</v>
       </c>
       <c r="B85" s="5" t="s">
-        <v>807</v>
+        <v>810</v>
       </c>
       <c r="C85" s="5" t="s">
-        <v>808</v>
+        <v>811</v>
       </c>
       <c r="D85" s="6" t="s">
-        <v>809</v>
+        <v>812</v>
       </c>
       <c r="E85" s="5" t="s">
         <v>300</v>
@@ -9978,16 +10200,16 @@
         <v>84</v>
       </c>
       <c r="B86" s="5" t="s">
-        <v>810</v>
+        <v>813</v>
       </c>
       <c r="C86" s="5" t="s">
-        <v>811</v>
+        <v>814</v>
       </c>
       <c r="D86" s="6" t="s">
-        <v>812</v>
+        <v>815</v>
       </c>
       <c r="E86" s="5" t="s">
-        <v>813</v>
+        <v>816</v>
       </c>
     </row>
     <row r="87" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -9995,16 +10217,16 @@
         <v>85</v>
       </c>
       <c r="B87" s="5" t="s">
-        <v>814</v>
+        <v>817</v>
       </c>
       <c r="C87" s="5" t="s">
-        <v>815</v>
+        <v>818</v>
       </c>
       <c r="D87" s="6" t="s">
-        <v>816</v>
+        <v>819</v>
       </c>
       <c r="E87" s="5" t="s">
-        <v>817</v>
+        <v>820</v>
       </c>
     </row>
     <row r="88" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -10012,16 +10234,16 @@
         <v>86</v>
       </c>
       <c r="B88" s="5" t="s">
-        <v>818</v>
+        <v>821</v>
       </c>
       <c r="C88" s="5" t="s">
-        <v>819</v>
+        <v>822</v>
       </c>
       <c r="D88" s="6" t="s">
+        <v>823</v>
+      </c>
+      <c r="E88" s="5" t="s">
         <v>820</v>
-      </c>
-      <c r="E88" s="5" t="s">
-        <v>817</v>
       </c>
     </row>
     <row r="89" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -10029,16 +10251,16 @@
         <v>87</v>
       </c>
       <c r="B89" s="5" t="s">
-        <v>821</v>
+        <v>824</v>
       </c>
       <c r="C89" s="5" t="s">
-        <v>822</v>
+        <v>825</v>
       </c>
       <c r="D89" s="6" t="s">
-        <v>823</v>
+        <v>826</v>
       </c>
       <c r="E89" s="5" t="s">
-        <v>817</v>
+        <v>820</v>
       </c>
     </row>
     <row r="90" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -10046,16 +10268,16 @@
         <v>88</v>
       </c>
       <c r="B90" s="5" t="s">
-        <v>824</v>
+        <v>827</v>
       </c>
       <c r="C90" s="5" t="s">
-        <v>825</v>
+        <v>828</v>
       </c>
       <c r="D90" s="6" t="s">
-        <v>826</v>
+        <v>829</v>
       </c>
       <c r="E90" s="5" t="s">
-        <v>827</v>
+        <v>830</v>
       </c>
     </row>
     <row r="91" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -10063,16 +10285,16 @@
         <v>89</v>
       </c>
       <c r="B91" s="5" t="s">
-        <v>828</v>
+        <v>831</v>
       </c>
       <c r="C91" s="5" t="s">
-        <v>829</v>
+        <v>832</v>
       </c>
       <c r="D91" s="6" t="s">
+        <v>833</v>
+      </c>
+      <c r="E91" s="5" t="s">
         <v>830</v>
-      </c>
-      <c r="E91" s="5" t="s">
-        <v>827</v>
       </c>
     </row>
     <row r="92" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -10080,16 +10302,16 @@
         <v>90</v>
       </c>
       <c r="B92" s="5" t="s">
-        <v>818</v>
+        <v>821</v>
       </c>
       <c r="C92" s="5" t="s">
-        <v>831</v>
+        <v>834</v>
       </c>
       <c r="D92" s="6" t="s">
-        <v>832</v>
+        <v>835</v>
       </c>
       <c r="E92" s="5" t="s">
-        <v>833</v>
+        <v>836</v>
       </c>
     </row>
     <row r="93" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -10097,16 +10319,16 @@
         <v>91</v>
       </c>
       <c r="B93" s="5" t="s">
-        <v>834</v>
+        <v>837</v>
       </c>
       <c r="C93" s="5" t="s">
-        <v>835</v>
+        <v>838</v>
       </c>
       <c r="D93" s="6" t="s">
+        <v>839</v>
+      </c>
+      <c r="E93" s="5" t="s">
         <v>836</v>
-      </c>
-      <c r="E93" s="5" t="s">
-        <v>833</v>
       </c>
     </row>
     <row r="94" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -10114,16 +10336,16 @@
         <v>92</v>
       </c>
       <c r="B94" s="5" t="s">
-        <v>837</v>
+        <v>840</v>
       </c>
       <c r="C94" s="5" t="s">
-        <v>838</v>
+        <v>841</v>
       </c>
       <c r="D94" s="6" t="s">
-        <v>839</v>
+        <v>842</v>
       </c>
       <c r="E94" s="5" t="s">
-        <v>840</v>
+        <v>843</v>
       </c>
     </row>
     <row r="95" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -10131,16 +10353,16 @@
         <v>93</v>
       </c>
       <c r="B95" s="5" t="s">
-        <v>679</v>
+        <v>682</v>
       </c>
       <c r="C95" s="5" t="s">
-        <v>841</v>
+        <v>844</v>
       </c>
       <c r="D95" s="6" t="s">
-        <v>842</v>
+        <v>845</v>
       </c>
       <c r="E95" s="5" t="s">
-        <v>843</v>
+        <v>846</v>
       </c>
     </row>
     <row r="96" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -10148,16 +10370,16 @@
         <v>94</v>
       </c>
       <c r="B96" s="5" t="s">
-        <v>824</v>
+        <v>827</v>
       </c>
       <c r="C96" s="5" t="s">
-        <v>844</v>
+        <v>847</v>
       </c>
       <c r="D96" s="6" t="s">
-        <v>845</v>
+        <v>848</v>
       </c>
       <c r="E96" s="5" t="s">
-        <v>843</v>
+        <v>846</v>
       </c>
     </row>
     <row r="97" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -10165,16 +10387,16 @@
         <v>95</v>
       </c>
       <c r="B97" s="5" t="s">
+        <v>849</v>
+      </c>
+      <c r="C97" s="5" t="s">
+        <v>850</v>
+      </c>
+      <c r="D97" s="6" t="s">
+        <v>851</v>
+      </c>
+      <c r="E97" s="5" t="s">
         <v>846</v>
-      </c>
-      <c r="C97" s="5" t="s">
-        <v>847</v>
-      </c>
-      <c r="D97" s="6" t="s">
-        <v>848</v>
-      </c>
-      <c r="E97" s="5" t="s">
-        <v>843</v>
       </c>
     </row>
     <row r="98" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -10182,16 +10404,16 @@
         <v>96</v>
       </c>
       <c r="B98" s="5" t="s">
-        <v>804</v>
+        <v>807</v>
       </c>
       <c r="C98" s="5" t="s">
-        <v>849</v>
+        <v>852</v>
       </c>
       <c r="D98" s="6" t="s">
-        <v>850</v>
+        <v>853</v>
       </c>
       <c r="E98" s="5" t="s">
-        <v>833</v>
+        <v>836</v>
       </c>
     </row>
     <row r="99" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -10199,16 +10421,16 @@
         <v>97</v>
       </c>
       <c r="B99" s="5" t="s">
-        <v>851</v>
+        <v>854</v>
       </c>
       <c r="C99" s="5" t="s">
-        <v>852</v>
+        <v>855</v>
       </c>
       <c r="D99" s="6" t="s">
-        <v>853</v>
+        <v>856</v>
       </c>
       <c r="E99" s="5" t="s">
-        <v>854</v>
+        <v>857</v>
       </c>
     </row>
     <row r="100" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -10216,16 +10438,16 @@
         <v>98</v>
       </c>
       <c r="B100" s="5" t="s">
-        <v>818</v>
+        <v>821</v>
       </c>
       <c r="C100" s="5" t="s">
-        <v>855</v>
+        <v>858</v>
       </c>
       <c r="D100" s="6" t="s">
-        <v>856</v>
+        <v>859</v>
       </c>
       <c r="E100" s="5" t="s">
-        <v>857</v>
+        <v>860</v>
       </c>
     </row>
     <row r="101" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -10233,16 +10455,16 @@
         <v>99</v>
       </c>
       <c r="B101" s="5" t="s">
-        <v>824</v>
+        <v>827</v>
       </c>
       <c r="C101" s="5" t="s">
-        <v>858</v>
+        <v>861</v>
       </c>
       <c r="D101" s="6" t="s">
-        <v>859</v>
+        <v>862</v>
       </c>
       <c r="E101" s="5" t="s">
-        <v>860</v>
+        <v>863</v>
       </c>
     </row>
     <row r="102" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -10250,16 +10472,16 @@
         <v>100</v>
       </c>
       <c r="B102" s="5" t="s">
-        <v>861</v>
+        <v>864</v>
       </c>
       <c r="C102" s="5" t="s">
-        <v>862</v>
+        <v>865</v>
       </c>
       <c r="D102" s="6" t="s">
-        <v>863</v>
+        <v>866</v>
       </c>
       <c r="E102" s="5" t="s">
-        <v>864</v>
+        <v>867</v>
       </c>
     </row>
     <row r="103" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -10267,16 +10489,16 @@
         <v>101</v>
       </c>
       <c r="B103" s="5" t="s">
-        <v>804</v>
+        <v>807</v>
       </c>
       <c r="C103" s="5" t="s">
-        <v>865</v>
+        <v>868</v>
       </c>
       <c r="D103" s="6" t="s">
-        <v>866</v>
+        <v>869</v>
       </c>
       <c r="E103" s="5" t="s">
-        <v>867</v>
+        <v>870</v>
       </c>
     </row>
     <row r="104" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -10284,13 +10506,13 @@
         <v>102</v>
       </c>
       <c r="B104" s="5" t="s">
-        <v>679</v>
+        <v>682</v>
       </c>
       <c r="C104" s="5" t="s">
-        <v>868</v>
+        <v>871</v>
       </c>
       <c r="D104" s="6" t="s">
-        <v>869</v>
+        <v>872</v>
       </c>
       <c r="E104" s="5" t="s">
         <v>352</v>
@@ -10301,16 +10523,16 @@
         <v>103</v>
       </c>
       <c r="B105" s="5" t="s">
-        <v>870</v>
+        <v>873</v>
       </c>
       <c r="C105" s="5" t="s">
-        <v>871</v>
+        <v>874</v>
       </c>
       <c r="D105" s="6" t="s">
-        <v>872</v>
+        <v>875</v>
       </c>
       <c r="E105" s="5" t="s">
-        <v>873</v>
+        <v>876</v>
       </c>
     </row>
     <row r="106" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -10318,16 +10540,16 @@
         <v>104</v>
       </c>
       <c r="B106" s="5" t="s">
-        <v>874</v>
+        <v>877</v>
       </c>
       <c r="C106" s="5" t="s">
-        <v>875</v>
+        <v>878</v>
       </c>
       <c r="D106" s="6" t="s">
-        <v>876</v>
+        <v>879</v>
       </c>
       <c r="E106" s="5" t="s">
-        <v>877</v>
+        <v>880</v>
       </c>
     </row>
     <row r="107" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -10335,16 +10557,16 @@
         <v>105</v>
       </c>
       <c r="B107" s="5" t="s">
-        <v>878</v>
+        <v>881</v>
       </c>
       <c r="C107" s="5" t="s">
-        <v>879</v>
+        <v>882</v>
       </c>
       <c r="D107" s="6" t="s">
-        <v>880</v>
+        <v>883</v>
       </c>
       <c r="E107" s="5" t="s">
-        <v>881</v>
+        <v>884</v>
       </c>
     </row>
     <row r="108" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -10352,16 +10574,16 @@
         <v>106</v>
       </c>
       <c r="B108" s="5" t="s">
-        <v>874</v>
+        <v>877</v>
       </c>
       <c r="C108" s="5" t="s">
-        <v>882</v>
+        <v>885</v>
       </c>
       <c r="D108" s="6" t="s">
-        <v>883</v>
+        <v>886</v>
       </c>
       <c r="E108" s="5" t="s">
-        <v>884</v>
+        <v>887</v>
       </c>
     </row>
     <row r="109" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -10369,13 +10591,13 @@
         <v>107</v>
       </c>
       <c r="B109" s="5" t="s">
-        <v>885</v>
+        <v>888</v>
       </c>
       <c r="C109" s="5" t="s">
-        <v>886</v>
+        <v>889</v>
       </c>
       <c r="D109" s="6" t="s">
-        <v>887</v>
+        <v>890</v>
       </c>
       <c r="E109" s="5" t="s">
         <v>368</v>
@@ -10386,13 +10608,13 @@
         <v>108</v>
       </c>
       <c r="B110" s="5" t="s">
-        <v>679</v>
+        <v>682</v>
       </c>
       <c r="C110" s="5" t="s">
-        <v>888</v>
+        <v>891</v>
       </c>
       <c r="D110" s="6" t="s">
-        <v>889</v>
+        <v>892</v>
       </c>
       <c r="E110" s="5" t="s">
         <v>368</v>
@@ -10403,16 +10625,16 @@
         <v>109</v>
       </c>
       <c r="B111" s="5" t="s">
-        <v>878</v>
+        <v>881</v>
       </c>
       <c r="C111" s="5" t="s">
-        <v>890</v>
+        <v>893</v>
       </c>
       <c r="D111" s="6" t="s">
-        <v>891</v>
+        <v>894</v>
       </c>
       <c r="E111" s="5" t="s">
-        <v>892</v>
+        <v>895</v>
       </c>
     </row>
     <row r="112" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -10420,16 +10642,16 @@
         <v>110</v>
       </c>
       <c r="B112" s="5" t="s">
-        <v>818</v>
+        <v>821</v>
       </c>
       <c r="C112" s="5" t="s">
-        <v>893</v>
+        <v>896</v>
       </c>
       <c r="D112" s="6" t="s">
-        <v>894</v>
+        <v>897</v>
       </c>
       <c r="E112" s="5" t="s">
-        <v>895</v>
+        <v>898</v>
       </c>
     </row>
     <row r="113" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -10437,13 +10659,13 @@
         <v>111</v>
       </c>
       <c r="B113" s="5" t="s">
-        <v>810</v>
+        <v>813</v>
       </c>
       <c r="C113" s="5" t="s">
-        <v>896</v>
+        <v>899</v>
       </c>
       <c r="D113" s="6" t="s">
-        <v>897</v>
+        <v>900</v>
       </c>
       <c r="E113" s="5" t="s">
         <v>382</v>
@@ -10454,16 +10676,16 @@
         <v>112</v>
       </c>
       <c r="B114" s="5" t="s">
-        <v>818</v>
+        <v>821</v>
       </c>
       <c r="C114" s="5" t="s">
-        <v>898</v>
+        <v>901</v>
       </c>
       <c r="D114" s="6" t="s">
-        <v>899</v>
+        <v>902</v>
       </c>
       <c r="E114" s="5" t="s">
-        <v>900</v>
+        <v>903</v>
       </c>
     </row>
     <row r="115" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -10471,16 +10693,16 @@
         <v>113</v>
       </c>
       <c r="B115" s="5" t="s">
-        <v>901</v>
+        <v>904</v>
       </c>
       <c r="C115" s="5" t="s">
-        <v>902</v>
+        <v>905</v>
       </c>
       <c r="D115" s="6" t="s">
-        <v>903</v>
+        <v>906</v>
       </c>
       <c r="E115" s="5" t="s">
-        <v>904</v>
+        <v>907</v>
       </c>
     </row>
     <row r="116" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -10488,16 +10710,16 @@
         <v>114</v>
       </c>
       <c r="B116" s="5" t="s">
-        <v>824</v>
+        <v>827</v>
       </c>
       <c r="C116" s="5" t="s">
-        <v>905</v>
+        <v>908</v>
       </c>
       <c r="D116" s="6" t="s">
-        <v>906</v>
+        <v>909</v>
       </c>
       <c r="E116" s="5" t="s">
-        <v>904</v>
+        <v>907</v>
       </c>
     </row>
     <row r="117" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -10505,16 +10727,16 @@
         <v>115</v>
       </c>
       <c r="B117" s="5" t="s">
-        <v>907</v>
+        <v>910</v>
       </c>
       <c r="C117" s="5" t="s">
-        <v>908</v>
+        <v>911</v>
       </c>
       <c r="D117" s="6" t="s">
-        <v>909</v>
+        <v>912</v>
       </c>
       <c r="E117" s="5" t="s">
-        <v>910</v>
+        <v>913</v>
       </c>
     </row>
     <row r="118" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -10522,13 +10744,13 @@
         <v>116</v>
       </c>
       <c r="B118" s="5" t="s">
-        <v>824</v>
+        <v>827</v>
       </c>
       <c r="C118" s="5" t="s">
-        <v>911</v>
+        <v>914</v>
       </c>
       <c r="D118" s="6" t="s">
-        <v>912</v>
+        <v>915</v>
       </c>
       <c r="E118" s="5" t="s">
         <v>396</v>
@@ -10539,16 +10761,16 @@
         <v>117</v>
       </c>
       <c r="B119" s="5" t="s">
-        <v>913</v>
+        <v>916</v>
       </c>
       <c r="C119" s="5" t="s">
-        <v>914</v>
+        <v>917</v>
       </c>
       <c r="D119" s="6" t="s">
-        <v>915</v>
+        <v>918</v>
       </c>
       <c r="E119" s="5" t="s">
-        <v>916</v>
+        <v>919</v>
       </c>
     </row>
     <row r="120" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -10556,16 +10778,16 @@
         <v>118</v>
       </c>
       <c r="B120" s="5" t="s">
-        <v>901</v>
+        <v>904</v>
       </c>
       <c r="C120" s="5" t="s">
-        <v>917</v>
+        <v>920</v>
       </c>
       <c r="D120" s="6" t="s">
-        <v>918</v>
+        <v>921</v>
       </c>
       <c r="E120" s="5" t="s">
-        <v>919</v>
+        <v>922</v>
       </c>
     </row>
     <row r="121" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -10573,16 +10795,16 @@
         <v>119</v>
       </c>
       <c r="B121" s="5" t="s">
-        <v>920</v>
+        <v>923</v>
       </c>
       <c r="C121" s="5" t="s">
-        <v>921</v>
+        <v>924</v>
       </c>
       <c r="D121" s="6" t="s">
-        <v>922</v>
+        <v>925</v>
       </c>
       <c r="E121" s="5" t="s">
-        <v>916</v>
+        <v>919</v>
       </c>
     </row>
     <row r="122" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -10590,16 +10812,16 @@
         <v>120</v>
       </c>
       <c r="B122" s="5" t="s">
-        <v>923</v>
+        <v>926</v>
       </c>
       <c r="C122" s="5" t="s">
-        <v>924</v>
+        <v>927</v>
       </c>
       <c r="D122" s="6" t="s">
-        <v>925</v>
+        <v>928</v>
       </c>
       <c r="E122" s="5" t="s">
-        <v>926</v>
+        <v>929</v>
       </c>
     </row>
     <row r="123" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -10607,13 +10829,13 @@
         <v>121</v>
       </c>
       <c r="B123" s="5" t="s">
-        <v>824</v>
+        <v>827</v>
       </c>
       <c r="C123" s="5" t="s">
-        <v>927</v>
+        <v>930</v>
       </c>
       <c r="D123" s="6" t="s">
-        <v>928</v>
+        <v>931</v>
       </c>
       <c r="E123" s="5" t="s">
         <v>409</v>
@@ -10624,13 +10846,13 @@
         <v>122</v>
       </c>
       <c r="B124" s="5" t="s">
-        <v>885</v>
+        <v>888</v>
       </c>
       <c r="C124" s="5" t="s">
-        <v>929</v>
+        <v>932</v>
       </c>
       <c r="D124" s="6" t="s">
-        <v>930</v>
+        <v>933</v>
       </c>
       <c r="E124" s="5" t="s">
         <v>409</v>
@@ -10641,16 +10863,16 @@
         <v>123</v>
       </c>
       <c r="B125" s="5" t="s">
-        <v>851</v>
+        <v>854</v>
       </c>
       <c r="C125" s="5" t="s">
-        <v>931</v>
+        <v>934</v>
       </c>
       <c r="D125" s="6" t="s">
-        <v>932</v>
+        <v>935</v>
       </c>
       <c r="E125" s="5" t="s">
-        <v>933</v>
+        <v>936</v>
       </c>
     </row>
     <row r="126" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -10658,16 +10880,16 @@
         <v>124</v>
       </c>
       <c r="B126" s="5" t="s">
-        <v>934</v>
+        <v>937</v>
       </c>
       <c r="C126" s="5" t="s">
-        <v>935</v>
+        <v>938</v>
       </c>
       <c r="D126" s="6" t="s">
+        <v>939</v>
+      </c>
+      <c r="E126" s="5" t="s">
         <v>936</v>
-      </c>
-      <c r="E126" s="5" t="s">
-        <v>933</v>
       </c>
     </row>
     <row r="127" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -10675,16 +10897,16 @@
         <v>125</v>
       </c>
       <c r="B127" s="5" t="s">
-        <v>870</v>
+        <v>873</v>
       </c>
       <c r="C127" s="5" t="s">
-        <v>937</v>
+        <v>940</v>
       </c>
       <c r="D127" s="6" t="s">
-        <v>938</v>
+        <v>941</v>
       </c>
       <c r="E127" s="5" t="s">
-        <v>939</v>
+        <v>942</v>
       </c>
     </row>
     <row r="128" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -10692,16 +10914,16 @@
         <v>126</v>
       </c>
       <c r="B128" s="5" t="s">
-        <v>940</v>
+        <v>943</v>
       </c>
       <c r="C128" s="5" t="s">
-        <v>941</v>
+        <v>944</v>
       </c>
       <c r="D128" s="6" t="s">
-        <v>942</v>
+        <v>945</v>
       </c>
       <c r="E128" s="5" t="s">
-        <v>943</v>
+        <v>946</v>
       </c>
     </row>
     <row r="129" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -10709,16 +10931,16 @@
         <v>127</v>
       </c>
       <c r="B129" s="5" t="s">
-        <v>944</v>
+        <v>947</v>
       </c>
       <c r="C129" s="5" t="s">
-        <v>945</v>
+        <v>948</v>
       </c>
       <c r="D129" s="6" t="s">
-        <v>946</v>
+        <v>949</v>
       </c>
       <c r="E129" s="5" t="s">
-        <v>947</v>
+        <v>950</v>
       </c>
     </row>
     <row r="130" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -10726,16 +10948,16 @@
         <v>128</v>
       </c>
       <c r="B130" s="5" t="s">
-        <v>948</v>
+        <v>951</v>
       </c>
       <c r="C130" s="5" t="s">
+        <v>952</v>
+      </c>
+      <c r="D130" s="6" t="s">
         <v>949</v>
       </c>
-      <c r="D130" s="6" t="s">
-        <v>946</v>
-      </c>
       <c r="E130" s="5" t="s">
-        <v>950</v>
+        <v>953</v>
       </c>
     </row>
     <row r="131" customFormat="false" ht="34.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -10743,13 +10965,13 @@
         <v>129</v>
       </c>
       <c r="B131" s="5" t="s">
-        <v>951</v>
+        <v>954</v>
       </c>
       <c r="C131" s="5" t="s">
-        <v>952</v>
+        <v>955</v>
       </c>
       <c r="D131" s="6" t="s">
-        <v>946</v>
+        <v>949</v>
       </c>
       <c r="E131" s="5" t="s">
         <v>434</v>
@@ -10760,16 +10982,16 @@
         <v>130</v>
       </c>
       <c r="B132" s="5" t="s">
-        <v>953</v>
+        <v>956</v>
       </c>
       <c r="C132" s="5" t="s">
-        <v>954</v>
+        <v>957</v>
       </c>
       <c r="D132" s="6" t="s">
-        <v>955</v>
+        <v>958</v>
       </c>
       <c r="E132" s="5" t="s">
-        <v>956</v>
+        <v>959</v>
       </c>
     </row>
     <row r="133" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -10777,16 +10999,16 @@
         <v>131</v>
       </c>
       <c r="B133" s="5" t="s">
-        <v>957</v>
+        <v>960</v>
       </c>
       <c r="C133" s="5" t="s">
-        <v>958</v>
+        <v>961</v>
       </c>
       <c r="D133" s="6" t="s">
+        <v>962</v>
+      </c>
+      <c r="E133" s="5" t="s">
         <v>959</v>
-      </c>
-      <c r="E133" s="5" t="s">
-        <v>956</v>
       </c>
     </row>
     <row r="134" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -10794,16 +11016,16 @@
         <v>132</v>
       </c>
       <c r="B134" s="5" t="s">
-        <v>960</v>
+        <v>963</v>
       </c>
       <c r="C134" s="5" t="s">
-        <v>961</v>
+        <v>964</v>
       </c>
       <c r="D134" s="6" t="s">
-        <v>962</v>
+        <v>965</v>
       </c>
       <c r="E134" s="5" t="s">
-        <v>963</v>
+        <v>966</v>
       </c>
     </row>
     <row r="135" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -10811,16 +11033,16 @@
         <v>133</v>
       </c>
       <c r="B135" s="5" t="s">
-        <v>964</v>
+        <v>967</v>
       </c>
       <c r="C135" s="5" t="s">
-        <v>965</v>
+        <v>968</v>
       </c>
       <c r="D135" s="6" t="s">
-        <v>966</v>
+        <v>969</v>
       </c>
       <c r="E135" s="5" t="s">
-        <v>967</v>
+        <v>970</v>
       </c>
     </row>
     <row r="136" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -10828,13 +11050,13 @@
         <v>134</v>
       </c>
       <c r="B136" s="5" t="s">
-        <v>679</v>
+        <v>682</v>
       </c>
       <c r="C136" s="5" t="s">
-        <v>968</v>
+        <v>971</v>
       </c>
       <c r="D136" s="6" t="s">
-        <v>969</v>
+        <v>972</v>
       </c>
       <c r="E136" s="5" t="s">
         <v>451</v>
@@ -10845,13 +11067,13 @@
         <v>135</v>
       </c>
       <c r="B137" s="5" t="s">
-        <v>970</v>
+        <v>973</v>
       </c>
       <c r="C137" s="5" t="s">
-        <v>971</v>
+        <v>974</v>
       </c>
       <c r="D137" s="6" t="s">
-        <v>972</v>
+        <v>975</v>
       </c>
       <c r="E137" s="5" t="s">
         <v>451</v>
@@ -10862,16 +11084,16 @@
         <v>136</v>
       </c>
       <c r="B138" s="5" t="s">
-        <v>973</v>
+        <v>976</v>
       </c>
       <c r="C138" s="5" t="s">
-        <v>974</v>
+        <v>977</v>
       </c>
       <c r="D138" s="6" t="s">
-        <v>975</v>
+        <v>978</v>
       </c>
       <c r="E138" s="5" t="s">
-        <v>976</v>
+        <v>979</v>
       </c>
     </row>
     <row r="139" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -10879,16 +11101,16 @@
         <v>137</v>
       </c>
       <c r="B139" s="5" t="s">
-        <v>977</v>
+        <v>980</v>
       </c>
       <c r="C139" s="5" t="s">
-        <v>978</v>
+        <v>981</v>
       </c>
       <c r="D139" s="6" t="s">
-        <v>979</v>
+        <v>982</v>
       </c>
       <c r="E139" s="5" t="s">
-        <v>980</v>
+        <v>983</v>
       </c>
     </row>
     <row r="140" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -10896,13 +11118,13 @@
         <v>138</v>
       </c>
       <c r="B140" s="5" t="s">
-        <v>846</v>
+        <v>849</v>
       </c>
       <c r="C140" s="5" t="s">
-        <v>981</v>
+        <v>984</v>
       </c>
       <c r="D140" s="6" t="s">
-        <v>982</v>
+        <v>985</v>
       </c>
       <c r="E140" s="5" t="s">
         <v>463</v>
@@ -10913,16 +11135,16 @@
         <v>139</v>
       </c>
       <c r="B141" s="5" t="s">
-        <v>851</v>
+        <v>854</v>
       </c>
       <c r="C141" s="5" t="s">
-        <v>983</v>
+        <v>986</v>
       </c>
       <c r="D141" s="6" t="s">
-        <v>984</v>
+        <v>987</v>
       </c>
       <c r="E141" s="5" t="s">
-        <v>985</v>
+        <v>988</v>
       </c>
     </row>
     <row r="142" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -10930,16 +11152,16 @@
         <v>140</v>
       </c>
       <c r="B142" s="5" t="s">
-        <v>986</v>
+        <v>989</v>
       </c>
       <c r="C142" s="5" t="s">
-        <v>987</v>
+        <v>990</v>
       </c>
       <c r="D142" s="6" t="s">
-        <v>988</v>
+        <v>991</v>
       </c>
       <c r="E142" s="5" t="s">
-        <v>989</v>
+        <v>992</v>
       </c>
     </row>
     <row r="143" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -10947,13 +11169,13 @@
         <v>141</v>
       </c>
       <c r="B143" s="5" t="s">
-        <v>818</v>
+        <v>821</v>
       </c>
       <c r="C143" s="5" t="s">
-        <v>990</v>
+        <v>993</v>
       </c>
       <c r="D143" s="6" t="s">
-        <v>991</v>
+        <v>994</v>
       </c>
       <c r="E143" s="5" t="s">
         <v>472</v>
@@ -10964,16 +11186,16 @@
         <v>142</v>
       </c>
       <c r="B144" s="5" t="s">
-        <v>992</v>
+        <v>995</v>
       </c>
       <c r="C144" s="5" t="s">
-        <v>993</v>
+        <v>996</v>
       </c>
       <c r="D144" s="6" t="s">
-        <v>994</v>
+        <v>997</v>
       </c>
       <c r="E144" s="5" t="s">
-        <v>995</v>
+        <v>998</v>
       </c>
     </row>
     <row r="145" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -10981,13 +11203,13 @@
         <v>143</v>
       </c>
       <c r="B145" s="5" t="s">
-        <v>878</v>
+        <v>881</v>
       </c>
       <c r="C145" s="5" t="s">
-        <v>996</v>
+        <v>999</v>
       </c>
       <c r="D145" s="6" t="s">
-        <v>997</v>
+        <v>1000</v>
       </c>
       <c r="E145" s="5" t="s">
         <v>479</v>
@@ -10998,16 +11220,16 @@
         <v>144</v>
       </c>
       <c r="B146" s="5" t="s">
-        <v>818</v>
+        <v>821</v>
       </c>
       <c r="C146" s="5" t="s">
-        <v>998</v>
+        <v>1001</v>
       </c>
       <c r="D146" s="6" t="s">
-        <v>999</v>
+        <v>1002</v>
       </c>
       <c r="E146" s="5" t="s">
-        <v>1000</v>
+        <v>1003</v>
       </c>
     </row>
     <row r="147" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -11015,16 +11237,16 @@
         <v>145</v>
       </c>
       <c r="B147" s="5" t="s">
-        <v>1001</v>
+        <v>1004</v>
       </c>
       <c r="C147" s="5" t="s">
-        <v>1002</v>
+        <v>1005</v>
       </c>
       <c r="D147" s="6" t="s">
-        <v>1003</v>
+        <v>1006</v>
       </c>
       <c r="E147" s="5" t="s">
-        <v>1004</v>
+        <v>1007</v>
       </c>
     </row>
     <row r="148" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -11032,16 +11254,16 @@
         <v>146</v>
       </c>
       <c r="B148" s="5" t="s">
-        <v>1005</v>
+        <v>1008</v>
       </c>
       <c r="C148" s="5" t="s">
-        <v>1006</v>
+        <v>1009</v>
       </c>
       <c r="D148" s="6" t="s">
-        <v>1007</v>
+        <v>1010</v>
       </c>
       <c r="E148" s="5" t="s">
-        <v>1008</v>
+        <v>1011</v>
       </c>
     </row>
     <row r="149" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -11049,13 +11271,13 @@
         <v>147</v>
       </c>
       <c r="B149" s="5" t="s">
-        <v>1009</v>
+        <v>1012</v>
       </c>
       <c r="C149" s="5" t="s">
-        <v>1010</v>
+        <v>1013</v>
       </c>
       <c r="D149" s="6" t="s">
-        <v>942</v>
+        <v>945</v>
       </c>
       <c r="E149" s="5" t="s">
         <v>492</v>
@@ -11066,13 +11288,13 @@
         <v>148</v>
       </c>
       <c r="B150" s="5" t="s">
-        <v>1011</v>
+        <v>1014</v>
       </c>
       <c r="C150" s="5" t="s">
-        <v>1012</v>
+        <v>1015</v>
       </c>
       <c r="D150" s="6" t="s">
-        <v>946</v>
+        <v>949</v>
       </c>
       <c r="E150" s="5" t="s">
         <v>492</v>
@@ -11083,16 +11305,16 @@
         <v>149</v>
       </c>
       <c r="B151" s="5" t="s">
-        <v>1013</v>
+        <v>1016</v>
       </c>
       <c r="C151" s="5" t="s">
-        <v>1014</v>
+        <v>1017</v>
       </c>
       <c r="D151" s="6" t="s">
-        <v>1015</v>
+        <v>1018</v>
       </c>
       <c r="E151" s="5" t="s">
-        <v>1016</v>
+        <v>1019</v>
       </c>
     </row>
     <row r="152" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -11100,16 +11322,16 @@
         <v>150</v>
       </c>
       <c r="B152" s="5" t="s">
-        <v>1013</v>
+        <v>1016</v>
       </c>
       <c r="C152" s="5" t="s">
-        <v>1017</v>
+        <v>1020</v>
       </c>
       <c r="D152" s="6" t="s">
-        <v>1015</v>
+        <v>1018</v>
       </c>
       <c r="E152" s="5" t="s">
-        <v>1016</v>
+        <v>1019</v>
       </c>
     </row>
     <row r="153" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -11117,16 +11339,16 @@
         <v>151</v>
       </c>
       <c r="B153" s="5" t="s">
-        <v>1018</v>
+        <v>1021</v>
       </c>
       <c r="C153" s="5" t="s">
-        <v>1019</v>
+        <v>1022</v>
       </c>
       <c r="D153" s="6" t="s">
-        <v>1020</v>
+        <v>1023</v>
       </c>
       <c r="E153" s="5" t="s">
-        <v>1021</v>
+        <v>1024</v>
       </c>
     </row>
     <row r="154" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -11134,16 +11356,16 @@
         <v>152</v>
       </c>
       <c r="B154" s="5" t="s">
-        <v>1018</v>
+        <v>1021</v>
       </c>
       <c r="C154" s="5" t="s">
-        <v>1022</v>
+        <v>1025</v>
       </c>
       <c r="D154" s="6" t="s">
-        <v>1020</v>
+        <v>1023</v>
       </c>
       <c r="E154" s="5" t="s">
-        <v>1021</v>
+        <v>1024</v>
       </c>
     </row>
     <row r="155" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -11151,16 +11373,16 @@
         <v>153</v>
       </c>
       <c r="B155" s="5" t="s">
-        <v>1023</v>
+        <v>1026</v>
       </c>
       <c r="C155" s="5" t="s">
-        <v>1024</v>
+        <v>1027</v>
       </c>
       <c r="D155" s="6" t="s">
-        <v>1025</v>
+        <v>1028</v>
       </c>
       <c r="E155" s="5" t="s">
-        <v>1026</v>
+        <v>1029</v>
       </c>
     </row>
     <row r="156" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -11168,16 +11390,16 @@
         <v>154</v>
       </c>
       <c r="B156" s="5" t="s">
-        <v>851</v>
+        <v>854</v>
       </c>
       <c r="C156" s="5" t="s">
-        <v>1027</v>
+        <v>1030</v>
       </c>
       <c r="D156" s="6" t="s">
-        <v>1028</v>
+        <v>1031</v>
       </c>
       <c r="E156" s="5" t="s">
-        <v>1026</v>
+        <v>1029</v>
       </c>
     </row>
     <row r="157" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -11185,14 +11407,14 @@
         <v>155</v>
       </c>
       <c r="B157" s="5" t="s">
-        <v>1029</v>
+        <v>1032</v>
       </c>
       <c r="C157" s="5" t="s">
-        <v>1030</v>
+        <v>1033</v>
       </c>
       <c r="D157" s="5"/>
       <c r="E157" s="5" t="s">
-        <v>1031</v>
+        <v>1034</v>
       </c>
     </row>
     <row r="158" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -11200,16 +11422,16 @@
         <v>156</v>
       </c>
       <c r="B158" s="5" t="s">
-        <v>1032</v>
+        <v>1035</v>
       </c>
       <c r="C158" s="5" t="s">
-        <v>1033</v>
+        <v>1036</v>
       </c>
       <c r="D158" s="6" t="s">
+        <v>1037</v>
+      </c>
+      <c r="E158" s="5" t="s">
         <v>1034</v>
-      </c>
-      <c r="E158" s="5" t="s">
-        <v>1031</v>
       </c>
     </row>
     <row r="159" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -11217,16 +11439,16 @@
         <v>157</v>
       </c>
       <c r="B159" s="5" t="s">
-        <v>679</v>
+        <v>682</v>
       </c>
       <c r="C159" s="5" t="s">
-        <v>1035</v>
+        <v>1038</v>
       </c>
       <c r="D159" s="6" t="s">
-        <v>1036</v>
+        <v>1039</v>
       </c>
       <c r="E159" s="5" t="s">
-        <v>1037</v>
+        <v>1040</v>
       </c>
     </row>
     <row r="160" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -11234,16 +11456,16 @@
         <v>158</v>
       </c>
       <c r="B160" s="5" t="s">
-        <v>818</v>
+        <v>821</v>
       </c>
       <c r="C160" s="5" t="s">
-        <v>1038</v>
+        <v>1041</v>
       </c>
       <c r="D160" s="6" t="s">
-        <v>1039</v>
+        <v>1042</v>
       </c>
       <c r="E160" s="5" t="s">
-        <v>1037</v>
+        <v>1040</v>
       </c>
     </row>
     <row r="161" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -11251,16 +11473,16 @@
         <v>159</v>
       </c>
       <c r="B161" s="5" t="s">
-        <v>874</v>
+        <v>877</v>
       </c>
       <c r="C161" s="5" t="s">
+        <v>1043</v>
+      </c>
+      <c r="D161" s="6" t="s">
+        <v>1044</v>
+      </c>
+      <c r="E161" s="5" t="s">
         <v>1040</v>
-      </c>
-      <c r="D161" s="6" t="s">
-        <v>1041</v>
-      </c>
-      <c r="E161" s="5" t="s">
-        <v>1037</v>
       </c>
     </row>
     <row r="162" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -11268,16 +11490,16 @@
         <v>160</v>
       </c>
       <c r="B162" s="5" t="s">
-        <v>1042</v>
+        <v>1045</v>
       </c>
       <c r="C162" s="5" t="s">
-        <v>1043</v>
+        <v>1046</v>
       </c>
       <c r="D162" s="6" t="s">
-        <v>1044</v>
+        <v>1047</v>
       </c>
       <c r="E162" s="5" t="s">
-        <v>1037</v>
+        <v>1040</v>
       </c>
     </row>
     <row r="163" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -11285,16 +11507,16 @@
         <v>161</v>
       </c>
       <c r="B163" s="5" t="s">
-        <v>1042</v>
+        <v>1045</v>
       </c>
       <c r="C163" s="5" t="s">
-        <v>1045</v>
+        <v>1048</v>
       </c>
       <c r="D163" s="6" t="s">
-        <v>1046</v>
+        <v>1049</v>
       </c>
       <c r="E163" s="5" t="s">
-        <v>1037</v>
+        <v>1040</v>
       </c>
     </row>
     <row r="164" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -11302,16 +11524,16 @@
         <v>162</v>
       </c>
       <c r="B164" s="5" t="s">
-        <v>885</v>
+        <v>888</v>
       </c>
       <c r="C164" s="5" t="s">
-        <v>1047</v>
+        <v>1050</v>
       </c>
       <c r="D164" s="6" t="s">
-        <v>1048</v>
+        <v>1051</v>
       </c>
       <c r="E164" s="5" t="s">
-        <v>1049</v>
+        <v>1052</v>
       </c>
     </row>
     <row r="165" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -11319,16 +11541,16 @@
         <v>163</v>
       </c>
       <c r="B165" s="5" t="s">
-        <v>679</v>
+        <v>682</v>
       </c>
       <c r="C165" s="5" t="s">
-        <v>1050</v>
+        <v>1053</v>
       </c>
       <c r="D165" s="6" t="s">
-        <v>1051</v>
+        <v>1054</v>
       </c>
       <c r="E165" s="5" t="s">
-        <v>1049</v>
+        <v>1052</v>
       </c>
     </row>
     <row r="166" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -11336,13 +11558,13 @@
         <v>157</v>
       </c>
       <c r="B166" s="5" t="s">
-        <v>1042</v>
+        <v>1045</v>
       </c>
       <c r="C166" s="5" t="s">
-        <v>1052</v>
+        <v>1055</v>
       </c>
       <c r="D166" s="6" t="s">
-        <v>1053</v>
+        <v>1056</v>
       </c>
       <c r="E166" s="5" t="s">
         <v>521</v>
@@ -11353,16 +11575,16 @@
         <v>158</v>
       </c>
       <c r="B167" s="5" t="s">
-        <v>901</v>
+        <v>904</v>
       </c>
       <c r="C167" s="5" t="s">
-        <v>1054</v>
+        <v>1057</v>
       </c>
       <c r="D167" s="6" t="s">
-        <v>1055</v>
+        <v>1058</v>
       </c>
       <c r="E167" s="5" t="s">
-        <v>1056</v>
+        <v>1059</v>
       </c>
     </row>
     <row r="168" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -11370,13 +11592,13 @@
         <v>159</v>
       </c>
       <c r="B168" s="5" t="s">
-        <v>679</v>
+        <v>682</v>
       </c>
       <c r="C168" s="5" t="s">
-        <v>1057</v>
+        <v>1060</v>
       </c>
       <c r="D168" s="6" t="s">
-        <v>1058</v>
+        <v>1061</v>
       </c>
       <c r="E168" s="5" t="s">
         <v>524</v>
@@ -11387,16 +11609,16 @@
         <v>160</v>
       </c>
       <c r="B169" s="5" t="s">
-        <v>874</v>
+        <v>877</v>
       </c>
       <c r="C169" s="5" t="s">
-        <v>1059</v>
+        <v>1062</v>
       </c>
       <c r="D169" s="6" t="s">
-        <v>1060</v>
+        <v>1063</v>
       </c>
       <c r="E169" s="5" t="s">
-        <v>1061</v>
+        <v>1064</v>
       </c>
     </row>
     <row r="170" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -11404,16 +11626,16 @@
         <v>161</v>
       </c>
       <c r="B170" s="5" t="s">
-        <v>874</v>
+        <v>877</v>
       </c>
       <c r="C170" s="5" t="s">
-        <v>1062</v>
+        <v>1065</v>
       </c>
       <c r="D170" s="6" t="s">
-        <v>1063</v>
+        <v>1066</v>
       </c>
       <c r="E170" s="5" t="s">
-        <v>1061</v>
+        <v>1064</v>
       </c>
     </row>
     <row r="171" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -11421,16 +11643,16 @@
         <v>162</v>
       </c>
       <c r="B171" s="5" t="s">
-        <v>874</v>
+        <v>877</v>
       </c>
       <c r="C171" s="5" t="s">
+        <v>1067</v>
+      </c>
+      <c r="D171" s="6" t="s">
+        <v>1068</v>
+      </c>
+      <c r="E171" s="5" t="s">
         <v>1064</v>
-      </c>
-      <c r="D171" s="6" t="s">
-        <v>1065</v>
-      </c>
-      <c r="E171" s="5" t="s">
-        <v>1061</v>
       </c>
     </row>
     <row r="172" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -11438,16 +11660,16 @@
         <v>163</v>
       </c>
       <c r="B172" s="5" t="s">
-        <v>824</v>
+        <v>827</v>
       </c>
       <c r="C172" s="5" t="s">
-        <v>1066</v>
+        <v>1069</v>
       </c>
       <c r="D172" s="6" t="s">
-        <v>1067</v>
+        <v>1070</v>
       </c>
       <c r="E172" s="5" t="s">
-        <v>1068</v>
+        <v>1071</v>
       </c>
     </row>
     <row r="173" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -11455,16 +11677,16 @@
         <v>164</v>
       </c>
       <c r="B173" s="5" t="s">
-        <v>818</v>
+        <v>821</v>
       </c>
       <c r="C173" s="5" t="s">
-        <v>1069</v>
+        <v>1072</v>
       </c>
       <c r="D173" s="6" t="s">
-        <v>1070</v>
+        <v>1073</v>
       </c>
       <c r="E173" s="5" t="s">
-        <v>1071</v>
+        <v>1074</v>
       </c>
     </row>
     <row r="174" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -11472,16 +11694,16 @@
         <v>165</v>
       </c>
       <c r="B174" s="5" t="s">
-        <v>818</v>
+        <v>821</v>
       </c>
       <c r="C174" s="5" t="s">
-        <v>1072</v>
+        <v>1075</v>
       </c>
       <c r="D174" s="6" t="s">
-        <v>1073</v>
+        <v>1076</v>
       </c>
       <c r="E174" s="5" t="s">
-        <v>1071</v>
+        <v>1074</v>
       </c>
     </row>
     <row r="175" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -11489,16 +11711,16 @@
         <v>166</v>
       </c>
       <c r="B175" s="5" t="s">
-        <v>818</v>
+        <v>821</v>
       </c>
       <c r="C175" s="5" t="s">
+        <v>1077</v>
+      </c>
+      <c r="D175" s="6" t="s">
+        <v>1078</v>
+      </c>
+      <c r="E175" s="5" t="s">
         <v>1074</v>
-      </c>
-      <c r="D175" s="6" t="s">
-        <v>1075</v>
-      </c>
-      <c r="E175" s="5" t="s">
-        <v>1071</v>
       </c>
     </row>
     <row r="176" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -11506,16 +11728,16 @@
         <v>167</v>
       </c>
       <c r="B176" s="5" t="s">
-        <v>885</v>
+        <v>888</v>
       </c>
       <c r="C176" s="5" t="s">
-        <v>1076</v>
+        <v>1079</v>
       </c>
       <c r="D176" s="6" t="s">
-        <v>1077</v>
+        <v>1080</v>
       </c>
       <c r="E176" s="5" t="s">
-        <v>1078</v>
+        <v>1081</v>
       </c>
     </row>
     <row r="177" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -11523,16 +11745,16 @@
         <v>168</v>
       </c>
       <c r="B177" s="5" t="s">
-        <v>679</v>
+        <v>682</v>
       </c>
       <c r="C177" s="5" t="s">
-        <v>1079</v>
+        <v>1082</v>
       </c>
       <c r="D177" s="6" t="s">
-        <v>1080</v>
+        <v>1083</v>
       </c>
       <c r="E177" s="5" t="s">
-        <v>1078</v>
+        <v>1081</v>
       </c>
     </row>
     <row r="178" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -11540,16 +11762,16 @@
         <v>169</v>
       </c>
       <c r="B178" s="5" t="s">
-        <v>679</v>
+        <v>682</v>
       </c>
       <c r="C178" s="5" t="s">
+        <v>1084</v>
+      </c>
+      <c r="D178" s="6" t="s">
+        <v>1085</v>
+      </c>
+      <c r="E178" s="5" t="s">
         <v>1081</v>
-      </c>
-      <c r="D178" s="6" t="s">
-        <v>1082</v>
-      </c>
-      <c r="E178" s="5" t="s">
-        <v>1078</v>
       </c>
     </row>
     <row r="179" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -11557,16 +11779,16 @@
         <v>170</v>
       </c>
       <c r="B179" s="5" t="s">
-        <v>901</v>
+        <v>904</v>
       </c>
       <c r="C179" s="5" t="s">
-        <v>1083</v>
+        <v>1086</v>
       </c>
       <c r="D179" s="6" t="s">
-        <v>1084</v>
+        <v>1087</v>
       </c>
       <c r="E179" s="5" t="s">
-        <v>1078</v>
+        <v>1081</v>
       </c>
     </row>
     <row r="180" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -11574,16 +11796,16 @@
         <v>171</v>
       </c>
       <c r="B180" s="5" t="s">
-        <v>901</v>
+        <v>904</v>
       </c>
       <c r="C180" s="5" t="s">
-        <v>1085</v>
+        <v>1088</v>
       </c>
       <c r="D180" s="6" t="s">
-        <v>1086</v>
+        <v>1089</v>
       </c>
       <c r="E180" s="5" t="s">
-        <v>1078</v>
+        <v>1081</v>
       </c>
     </row>
     <row r="181" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -11591,16 +11813,16 @@
         <v>172</v>
       </c>
       <c r="B181" s="5" t="s">
-        <v>874</v>
+        <v>877</v>
       </c>
       <c r="C181" s="5" t="s">
-        <v>1087</v>
+        <v>1090</v>
       </c>
       <c r="D181" s="6" t="s">
-        <v>1088</v>
+        <v>1091</v>
       </c>
       <c r="E181" s="5" t="s">
-        <v>1089</v>
+        <v>1092</v>
       </c>
     </row>
     <row r="182" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -11608,16 +11830,16 @@
         <v>173</v>
       </c>
       <c r="B182" s="5" t="s">
-        <v>679</v>
+        <v>682</v>
       </c>
       <c r="C182" s="5" t="s">
-        <v>1090</v>
+        <v>1093</v>
       </c>
       <c r="D182" s="6" t="s">
-        <v>1091</v>
+        <v>1094</v>
       </c>
       <c r="E182" s="5" t="s">
-        <v>1092</v>
+        <v>1095</v>
       </c>
     </row>
     <row r="183" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -11625,16 +11847,16 @@
         <v>174</v>
       </c>
       <c r="B183" s="5" t="s">
-        <v>679</v>
+        <v>682</v>
       </c>
       <c r="C183" s="5" t="s">
-        <v>1093</v>
+        <v>1096</v>
       </c>
       <c r="D183" s="6" t="s">
-        <v>1094</v>
+        <v>1097</v>
       </c>
       <c r="E183" s="5" t="s">
-        <v>1092</v>
+        <v>1095</v>
       </c>
     </row>
     <row r="184" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -11642,16 +11864,16 @@
         <v>175</v>
       </c>
       <c r="B184" s="5" t="s">
-        <v>679</v>
+        <v>682</v>
       </c>
       <c r="C184" s="5" t="s">
+        <v>1098</v>
+      </c>
+      <c r="D184" s="6" t="s">
+        <v>1099</v>
+      </c>
+      <c r="E184" s="5" t="s">
         <v>1095</v>
-      </c>
-      <c r="D184" s="6" t="s">
-        <v>1096</v>
-      </c>
-      <c r="E184" s="5" t="s">
-        <v>1092</v>
       </c>
     </row>
     <row r="185" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -11659,16 +11881,16 @@
         <v>176</v>
       </c>
       <c r="B185" s="5" t="s">
-        <v>1042</v>
+        <v>1045</v>
       </c>
       <c r="C185" s="5" t="s">
-        <v>1097</v>
+        <v>1100</v>
       </c>
       <c r="D185" s="6" t="s">
-        <v>1098</v>
+        <v>1101</v>
       </c>
       <c r="E185" s="5" t="s">
-        <v>1092</v>
+        <v>1095</v>
       </c>
     </row>
     <row r="186" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -11676,16 +11898,16 @@
         <v>177</v>
       </c>
       <c r="B186" s="5" t="s">
-        <v>1042</v>
+        <v>1045</v>
       </c>
       <c r="C186" s="5" t="s">
-        <v>1099</v>
+        <v>1102</v>
       </c>
       <c r="D186" s="6" t="s">
-        <v>1100</v>
+        <v>1103</v>
       </c>
       <c r="E186" s="5" t="s">
-        <v>1092</v>
+        <v>1095</v>
       </c>
     </row>
     <row r="187" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -11693,16 +11915,16 @@
         <v>178</v>
       </c>
       <c r="B187" s="5" t="s">
-        <v>1042</v>
+        <v>1045</v>
       </c>
       <c r="C187" s="5" t="s">
-        <v>1101</v>
+        <v>1104</v>
       </c>
       <c r="D187" s="6" t="s">
-        <v>1102</v>
+        <v>1105</v>
       </c>
       <c r="E187" s="5" t="s">
-        <v>1092</v>
+        <v>1095</v>
       </c>
     </row>
     <row r="188" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -11710,16 +11932,16 @@
         <v>179</v>
       </c>
       <c r="B188" s="5" t="s">
-        <v>679</v>
+        <v>682</v>
       </c>
       <c r="C188" s="5" t="s">
-        <v>1103</v>
+        <v>1106</v>
       </c>
       <c r="D188" s="6" t="s">
-        <v>1104</v>
+        <v>1107</v>
       </c>
       <c r="E188" s="5" t="s">
-        <v>1105</v>
+        <v>1108</v>
       </c>
     </row>
     <row r="189" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -11727,16 +11949,16 @@
         <v>180</v>
       </c>
       <c r="B189" s="5" t="s">
-        <v>679</v>
+        <v>682</v>
       </c>
       <c r="C189" s="5" t="s">
-        <v>1106</v>
+        <v>1109</v>
       </c>
       <c r="D189" s="6" t="s">
-        <v>1107</v>
+        <v>1110</v>
       </c>
       <c r="E189" s="5" t="s">
-        <v>1105</v>
+        <v>1108</v>
       </c>
     </row>
     <row r="190" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -11744,16 +11966,16 @@
         <v>181</v>
       </c>
       <c r="B190" s="5" t="s">
-        <v>874</v>
+        <v>877</v>
       </c>
       <c r="C190" s="5" t="s">
+        <v>1111</v>
+      </c>
+      <c r="D190" s="6" t="s">
+        <v>1112</v>
+      </c>
+      <c r="E190" s="5" t="s">
         <v>1108</v>
-      </c>
-      <c r="D190" s="6" t="s">
-        <v>1109</v>
-      </c>
-      <c r="E190" s="5" t="s">
-        <v>1105</v>
       </c>
     </row>
     <row r="191" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -11761,16 +11983,16 @@
         <v>182</v>
       </c>
       <c r="B191" s="5" t="s">
-        <v>1042</v>
+        <v>1045</v>
       </c>
       <c r="C191" s="5" t="s">
-        <v>1110</v>
+        <v>1113</v>
       </c>
       <c r="D191" s="6" t="s">
-        <v>1111</v>
+        <v>1114</v>
       </c>
       <c r="E191" s="5" t="s">
-        <v>1105</v>
+        <v>1108</v>
       </c>
     </row>
     <row r="192" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -11778,16 +12000,16 @@
         <v>183</v>
       </c>
       <c r="B192" s="5" t="s">
-        <v>1042</v>
+        <v>1045</v>
       </c>
       <c r="C192" s="5" t="s">
-        <v>1112</v>
+        <v>1115</v>
       </c>
       <c r="D192" s="6" t="s">
-        <v>1113</v>
+        <v>1116</v>
       </c>
       <c r="E192" s="5" t="s">
-        <v>1105</v>
+        <v>1108</v>
       </c>
     </row>
     <row r="193" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -11795,13 +12017,13 @@
         <v>184</v>
       </c>
       <c r="B193" s="5" t="s">
-        <v>874</v>
+        <v>877</v>
       </c>
       <c r="C193" s="5" t="s">
-        <v>1114</v>
+        <v>1117</v>
       </c>
       <c r="D193" s="6" t="s">
-        <v>1115</v>
+        <v>1118</v>
       </c>
       <c r="E193" s="5" t="s">
         <v>533</v>
@@ -11812,16 +12034,16 @@
         <v>185</v>
       </c>
       <c r="B194" s="5" t="s">
-        <v>874</v>
+        <v>877</v>
       </c>
       <c r="C194" s="5" t="s">
-        <v>1116</v>
+        <v>1119</v>
       </c>
       <c r="D194" s="6" t="s">
-        <v>1117</v>
+        <v>1120</v>
       </c>
       <c r="E194" s="5" t="s">
-        <v>1118</v>
+        <v>1121</v>
       </c>
     </row>
     <row r="195" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -11829,16 +12051,16 @@
         <v>186</v>
       </c>
       <c r="B195" s="5" t="s">
-        <v>679</v>
+        <v>682</v>
       </c>
       <c r="C195" s="5" t="s">
-        <v>1119</v>
+        <v>1122</v>
       </c>
       <c r="D195" s="6" t="s">
-        <v>1120</v>
+        <v>1123</v>
       </c>
       <c r="E195" s="5" t="s">
-        <v>1121</v>
+        <v>1124</v>
       </c>
     </row>
     <row r="196" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -11846,16 +12068,16 @@
         <v>187</v>
       </c>
       <c r="B196" s="5" t="s">
-        <v>818</v>
+        <v>821</v>
       </c>
       <c r="C196" s="5" t="s">
-        <v>1122</v>
+        <v>1125</v>
       </c>
       <c r="D196" s="6" t="s">
-        <v>1123</v>
+        <v>1126</v>
       </c>
       <c r="E196" s="5" t="s">
-        <v>1121</v>
+        <v>1124</v>
       </c>
     </row>
     <row r="197" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -11863,16 +12085,16 @@
         <v>188</v>
       </c>
       <c r="B197" s="5" t="s">
-        <v>1042</v>
+        <v>1045</v>
       </c>
       <c r="C197" s="5" t="s">
+        <v>1127</v>
+      </c>
+      <c r="D197" s="6" t="s">
+        <v>1128</v>
+      </c>
+      <c r="E197" s="5" t="s">
         <v>1124</v>
-      </c>
-      <c r="D197" s="6" t="s">
-        <v>1125</v>
-      </c>
-      <c r="E197" s="5" t="s">
-        <v>1121</v>
       </c>
     </row>
     <row r="198" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -11880,16 +12102,16 @@
         <v>189</v>
       </c>
       <c r="B198" s="5" t="s">
-        <v>1042</v>
+        <v>1045</v>
       </c>
       <c r="C198" s="5" t="s">
-        <v>1126</v>
+        <v>1129</v>
       </c>
       <c r="D198" s="6" t="s">
-        <v>1127</v>
+        <v>1130</v>
       </c>
       <c r="E198" s="5" t="s">
-        <v>1121</v>
+        <v>1124</v>
       </c>
     </row>
     <row r="199" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -11897,16 +12119,16 @@
         <v>190</v>
       </c>
       <c r="B199" s="5" t="s">
-        <v>885</v>
+        <v>888</v>
       </c>
       <c r="C199" s="5" t="s">
-        <v>1128</v>
+        <v>1131</v>
       </c>
       <c r="D199" s="6" t="s">
-        <v>1129</v>
+        <v>1132</v>
       </c>
       <c r="E199" s="5" t="s">
-        <v>1130</v>
+        <v>1133</v>
       </c>
     </row>
     <row r="200" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -11914,16 +12136,16 @@
         <v>191</v>
       </c>
       <c r="B200" s="5" t="s">
-        <v>885</v>
+        <v>888</v>
       </c>
       <c r="C200" s="5" t="s">
-        <v>1131</v>
+        <v>1134</v>
       </c>
       <c r="D200" s="6" t="s">
-        <v>1132</v>
+        <v>1135</v>
       </c>
       <c r="E200" s="5" t="s">
-        <v>1130</v>
+        <v>1133</v>
       </c>
     </row>
     <row r="201" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -11931,16 +12153,16 @@
         <v>192</v>
       </c>
       <c r="B201" s="5" t="s">
-        <v>679</v>
+        <v>682</v>
       </c>
       <c r="C201" s="5" t="s">
+        <v>1136</v>
+      </c>
+      <c r="D201" s="6" t="s">
+        <v>1137</v>
+      </c>
+      <c r="E201" s="5" t="s">
         <v>1133</v>
-      </c>
-      <c r="D201" s="6" t="s">
-        <v>1134</v>
-      </c>
-      <c r="E201" s="5" t="s">
-        <v>1130</v>
       </c>
     </row>
     <row r="202" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -11948,16 +12170,16 @@
         <v>193</v>
       </c>
       <c r="B202" s="5" t="s">
-        <v>679</v>
+        <v>682</v>
       </c>
       <c r="C202" s="5" t="s">
-        <v>1135</v>
+        <v>1138</v>
       </c>
       <c r="D202" s="6" t="s">
-        <v>1136</v>
+        <v>1139</v>
       </c>
       <c r="E202" s="5" t="s">
-        <v>1137</v>
+        <v>1140</v>
       </c>
     </row>
     <row r="203" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -11965,16 +12187,16 @@
         <v>194</v>
       </c>
       <c r="B203" s="5" t="s">
-        <v>679</v>
+        <v>682</v>
       </c>
       <c r="C203" s="5" t="s">
-        <v>1138</v>
+        <v>1141</v>
       </c>
       <c r="D203" s="6" t="s">
-        <v>1139</v>
+        <v>1142</v>
       </c>
       <c r="E203" s="5" t="s">
-        <v>1137</v>
+        <v>1140</v>
       </c>
     </row>
     <row r="204" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -11982,16 +12204,16 @@
         <v>195</v>
       </c>
       <c r="B204" s="5" t="s">
-        <v>679</v>
+        <v>682</v>
       </c>
       <c r="C204" s="5" t="s">
-        <v>1140</v>
+        <v>1143</v>
       </c>
       <c r="D204" s="6" t="s">
-        <v>1141</v>
+        <v>1144</v>
       </c>
       <c r="E204" s="5" t="s">
-        <v>1142</v>
+        <v>1145</v>
       </c>
     </row>
     <row r="205" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -11999,13 +12221,13 @@
         <v>196</v>
       </c>
       <c r="B205" s="5" t="s">
-        <v>874</v>
+        <v>877</v>
       </c>
       <c r="C205" s="5" t="s">
-        <v>1143</v>
+        <v>1146</v>
       </c>
       <c r="D205" s="6" t="s">
-        <v>1144</v>
+        <v>1147</v>
       </c>
       <c r="E205" s="5" t="s">
         <v>540</v>
@@ -12016,16 +12238,16 @@
         <v>197</v>
       </c>
       <c r="B206" s="5" t="s">
-        <v>679</v>
+        <v>682</v>
       </c>
       <c r="C206" s="5" t="s">
-        <v>1145</v>
+        <v>1148</v>
       </c>
       <c r="D206" s="6" t="s">
-        <v>1146</v>
+        <v>1149</v>
       </c>
       <c r="E206" s="5" t="s">
-        <v>1147</v>
+        <v>1150</v>
       </c>
     </row>
     <row r="207" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -12033,16 +12255,16 @@
         <v>198</v>
       </c>
       <c r="B207" s="5" t="s">
-        <v>901</v>
+        <v>904</v>
       </c>
       <c r="C207" s="5" t="s">
-        <v>1148</v>
+        <v>1151</v>
       </c>
       <c r="D207" s="6" t="s">
-        <v>1149</v>
+        <v>1152</v>
       </c>
       <c r="E207" s="5" t="s">
-        <v>1147</v>
+        <v>1150</v>
       </c>
     </row>
     <row r="208" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -12050,16 +12272,16 @@
         <v>199</v>
       </c>
       <c r="B208" s="5" t="s">
-        <v>1042</v>
+        <v>1045</v>
       </c>
       <c r="C208" s="5" t="s">
+        <v>1153</v>
+      </c>
+      <c r="D208" s="6" t="s">
+        <v>1154</v>
+      </c>
+      <c r="E208" s="5" t="s">
         <v>1150</v>
-      </c>
-      <c r="D208" s="6" t="s">
-        <v>1151</v>
-      </c>
-      <c r="E208" s="5" t="s">
-        <v>1147</v>
       </c>
     </row>
     <row r="209" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -12067,16 +12289,16 @@
         <v>200</v>
       </c>
       <c r="B209" s="5" t="s">
-        <v>1042</v>
+        <v>1045</v>
       </c>
       <c r="C209" s="5" t="s">
-        <v>1152</v>
+        <v>1155</v>
       </c>
       <c r="D209" s="6" t="s">
-        <v>1153</v>
+        <v>1156</v>
       </c>
       <c r="E209" s="5" t="s">
-        <v>1147</v>
+        <v>1150</v>
       </c>
     </row>
     <row r="210" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -12084,16 +12306,16 @@
         <v>201</v>
       </c>
       <c r="B210" s="5" t="s">
-        <v>818</v>
+        <v>821</v>
       </c>
       <c r="C210" s="5" t="s">
-        <v>1154</v>
+        <v>1157</v>
       </c>
       <c r="D210" s="6" t="s">
-        <v>1155</v>
+        <v>1158</v>
       </c>
       <c r="E210" s="5" t="s">
-        <v>1156</v>
+        <v>1159</v>
       </c>
     </row>
     <row r="211" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -12101,16 +12323,16 @@
         <v>202</v>
       </c>
       <c r="B211" s="5" t="s">
-        <v>901</v>
+        <v>904</v>
       </c>
       <c r="C211" s="5" t="s">
-        <v>1157</v>
+        <v>1160</v>
       </c>
       <c r="D211" s="6" t="s">
-        <v>1158</v>
+        <v>1161</v>
       </c>
       <c r="E211" s="5" t="s">
-        <v>1156</v>
+        <v>1159</v>
       </c>
     </row>
     <row r="212" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -12118,16 +12340,16 @@
         <v>203</v>
       </c>
       <c r="B212" s="5" t="s">
-        <v>901</v>
+        <v>904</v>
       </c>
       <c r="C212" s="5" t="s">
+        <v>1162</v>
+      </c>
+      <c r="D212" s="6" t="s">
+        <v>1163</v>
+      </c>
+      <c r="E212" s="5" t="s">
         <v>1159</v>
-      </c>
-      <c r="D212" s="6" t="s">
-        <v>1160</v>
-      </c>
-      <c r="E212" s="5" t="s">
-        <v>1156</v>
       </c>
     </row>
     <row r="213" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -12135,16 +12357,16 @@
         <v>204</v>
       </c>
       <c r="B213" s="5" t="s">
-        <v>874</v>
+        <v>877</v>
       </c>
       <c r="C213" s="5" t="s">
-        <v>1161</v>
+        <v>1164</v>
       </c>
       <c r="D213" s="6" t="s">
-        <v>1162</v>
+        <v>1165</v>
       </c>
       <c r="E213" s="5" t="s">
-        <v>1056</v>
+        <v>1059</v>
       </c>
     </row>
     <row r="214" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -12152,16 +12374,16 @@
         <v>205</v>
       </c>
       <c r="B214" s="5" t="s">
-        <v>679</v>
+        <v>682</v>
       </c>
       <c r="C214" s="5" t="s">
-        <v>1163</v>
+        <v>1166</v>
       </c>
       <c r="D214" s="6" t="s">
-        <v>1164</v>
+        <v>1167</v>
       </c>
       <c r="E214" s="5" t="s">
-        <v>1165</v>
+        <v>1168</v>
       </c>
     </row>
     <row r="215" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -12169,16 +12391,16 @@
         <v>206</v>
       </c>
       <c r="B215" s="5" t="s">
-        <v>818</v>
+        <v>821</v>
       </c>
       <c r="C215" s="5" t="s">
-        <v>1166</v>
+        <v>1169</v>
       </c>
       <c r="D215" s="6" t="s">
-        <v>1167</v>
+        <v>1170</v>
       </c>
       <c r="E215" s="5" t="s">
-        <v>1168</v>
+        <v>1171</v>
       </c>
     </row>
     <row r="216" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -12186,16 +12408,16 @@
         <v>207</v>
       </c>
       <c r="B216" s="5" t="s">
-        <v>901</v>
+        <v>904</v>
       </c>
       <c r="C216" s="5" t="s">
-        <v>1169</v>
+        <v>1172</v>
       </c>
       <c r="D216" s="6" t="s">
-        <v>1170</v>
+        <v>1173</v>
       </c>
       <c r="E216" s="5" t="s">
-        <v>1168</v>
+        <v>1171</v>
       </c>
     </row>
     <row r="217" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -12203,16 +12425,16 @@
         <v>208</v>
       </c>
       <c r="B217" s="5" t="s">
-        <v>679</v>
+        <v>682</v>
       </c>
       <c r="C217" s="5" t="s">
-        <v>1171</v>
+        <v>1174</v>
       </c>
       <c r="D217" s="6" t="s">
-        <v>1172</v>
+        <v>1175</v>
       </c>
       <c r="E217" s="5" t="s">
-        <v>1173</v>
+        <v>1176</v>
       </c>
     </row>
     <row r="218" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -12220,16 +12442,16 @@
         <v>209</v>
       </c>
       <c r="B218" s="5" t="s">
-        <v>818</v>
+        <v>821</v>
       </c>
       <c r="C218" s="5" t="s">
-        <v>1174</v>
+        <v>1177</v>
       </c>
       <c r="D218" s="6" t="s">
-        <v>1175</v>
+        <v>1178</v>
       </c>
       <c r="E218" s="5" t="s">
-        <v>1173</v>
+        <v>1176</v>
       </c>
     </row>
     <row r="219" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -12237,16 +12459,16 @@
         <v>210</v>
       </c>
       <c r="B219" s="5" t="s">
-        <v>901</v>
+        <v>904</v>
       </c>
       <c r="C219" s="5" t="s">
+        <v>1179</v>
+      </c>
+      <c r="D219" s="6" t="s">
+        <v>1180</v>
+      </c>
+      <c r="E219" s="5" t="s">
         <v>1176</v>
-      </c>
-      <c r="D219" s="6" t="s">
-        <v>1177</v>
-      </c>
-      <c r="E219" s="5" t="s">
-        <v>1173</v>
       </c>
     </row>
     <row r="220" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -12254,16 +12476,16 @@
         <v>211</v>
       </c>
       <c r="B220" s="5" t="s">
-        <v>1042</v>
+        <v>1045</v>
       </c>
       <c r="C220" s="5" t="s">
-        <v>1178</v>
+        <v>1181</v>
       </c>
       <c r="D220" s="6" t="s">
-        <v>1179</v>
+        <v>1182</v>
       </c>
       <c r="E220" s="5" t="s">
-        <v>1173</v>
+        <v>1176</v>
       </c>
     </row>
     <row r="221" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -12271,16 +12493,16 @@
         <v>212</v>
       </c>
       <c r="B221" s="5" t="s">
-        <v>874</v>
+        <v>877</v>
       </c>
       <c r="C221" s="5" t="s">
-        <v>1180</v>
+        <v>1183</v>
       </c>
       <c r="D221" s="6" t="s">
-        <v>1181</v>
+        <v>1184</v>
       </c>
       <c r="E221" s="5" t="s">
-        <v>1182</v>
+        <v>1185</v>
       </c>
     </row>
     <row r="222" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -12288,16 +12510,16 @@
         <v>213</v>
       </c>
       <c r="B222" s="5" t="s">
-        <v>679</v>
+        <v>682</v>
       </c>
       <c r="C222" s="5" t="s">
-        <v>1183</v>
+        <v>1186</v>
       </c>
       <c r="D222" s="6" t="s">
-        <v>1184</v>
+        <v>1187</v>
       </c>
       <c r="E222" s="5" t="s">
-        <v>1185</v>
+        <v>1188</v>
       </c>
     </row>
     <row r="223" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -12305,16 +12527,16 @@
         <v>214</v>
       </c>
       <c r="B223" s="5" t="s">
-        <v>874</v>
+        <v>877</v>
       </c>
       <c r="C223" s="5" t="s">
-        <v>1186</v>
+        <v>1189</v>
       </c>
       <c r="D223" s="6" t="s">
-        <v>1187</v>
+        <v>1190</v>
       </c>
       <c r="E223" s="5" t="s">
-        <v>1185</v>
+        <v>1188</v>
       </c>
     </row>
     <row r="224" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -12322,16 +12544,16 @@
         <v>215</v>
       </c>
       <c r="B224" s="5" t="s">
-        <v>874</v>
+        <v>877</v>
       </c>
       <c r="C224" s="5" t="s">
+        <v>1191</v>
+      </c>
+      <c r="D224" s="6" t="s">
+        <v>1192</v>
+      </c>
+      <c r="E224" s="5" t="s">
         <v>1188</v>
-      </c>
-      <c r="D224" s="6" t="s">
-        <v>1189</v>
-      </c>
-      <c r="E224" s="5" t="s">
-        <v>1185</v>
       </c>
     </row>
     <row r="225" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -12339,16 +12561,16 @@
         <v>216</v>
       </c>
       <c r="B225" s="5" t="s">
-        <v>1042</v>
+        <v>1045</v>
       </c>
       <c r="C225" s="5" t="s">
-        <v>1190</v>
+        <v>1193</v>
       </c>
       <c r="D225" s="6" t="s">
-        <v>1191</v>
+        <v>1194</v>
       </c>
       <c r="E225" s="5" t="s">
-        <v>1185</v>
+        <v>1188</v>
       </c>
     </row>
     <row r="226" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -12356,16 +12578,16 @@
         <v>217</v>
       </c>
       <c r="B226" s="5" t="s">
-        <v>885</v>
+        <v>888</v>
       </c>
       <c r="C226" s="5" t="s">
-        <v>1192</v>
+        <v>1195</v>
       </c>
       <c r="D226" s="6" t="s">
-        <v>1193</v>
+        <v>1196</v>
       </c>
       <c r="E226" s="5" t="s">
-        <v>1194</v>
+        <v>1197</v>
       </c>
     </row>
     <row r="227" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -12373,16 +12595,16 @@
         <v>218</v>
       </c>
       <c r="B227" s="5" t="s">
-        <v>679</v>
+        <v>682</v>
       </c>
       <c r="C227" s="5" t="s">
-        <v>1195</v>
+        <v>1198</v>
       </c>
       <c r="D227" s="6" t="s">
-        <v>1196</v>
+        <v>1199</v>
       </c>
       <c r="E227" s="5" t="s">
-        <v>1194</v>
+        <v>1197</v>
       </c>
     </row>
     <row r="228" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -12390,16 +12612,16 @@
         <v>219</v>
       </c>
       <c r="B228" s="5" t="s">
-        <v>818</v>
+        <v>821</v>
       </c>
       <c r="C228" s="5" t="s">
+        <v>1200</v>
+      </c>
+      <c r="D228" s="6" t="s">
+        <v>1201</v>
+      </c>
+      <c r="E228" s="5" t="s">
         <v>1197</v>
-      </c>
-      <c r="D228" s="6" t="s">
-        <v>1198</v>
-      </c>
-      <c r="E228" s="5" t="s">
-        <v>1194</v>
       </c>
     </row>
     <row r="229" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -12407,16 +12629,16 @@
         <v>220</v>
       </c>
       <c r="B229" s="5" t="s">
-        <v>1042</v>
+        <v>1045</v>
       </c>
       <c r="C229" s="5" t="s">
-        <v>1199</v>
+        <v>1202</v>
       </c>
       <c r="D229" s="6" t="s">
-        <v>1200</v>
+        <v>1203</v>
       </c>
       <c r="E229" s="5" t="s">
-        <v>1194</v>
+        <v>1197</v>
       </c>
     </row>
     <row r="230" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -12424,16 +12646,16 @@
         <v>221</v>
       </c>
       <c r="B230" s="5" t="s">
-        <v>679</v>
+        <v>682</v>
       </c>
       <c r="C230" s="5" t="s">
-        <v>1201</v>
+        <v>1204</v>
       </c>
       <c r="D230" s="6" t="s">
-        <v>1202</v>
+        <v>1205</v>
       </c>
       <c r="E230" s="5" t="s">
-        <v>1203</v>
+        <v>1206</v>
       </c>
     </row>
     <row r="231" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -12441,16 +12663,16 @@
         <v>222</v>
       </c>
       <c r="B231" s="5" t="s">
-        <v>874</v>
+        <v>877</v>
       </c>
       <c r="C231" s="5" t="s">
-        <v>1204</v>
+        <v>1207</v>
       </c>
       <c r="D231" s="6" t="s">
-        <v>1205</v>
+        <v>1208</v>
       </c>
       <c r="E231" s="5" t="s">
-        <v>1203</v>
+        <v>1206</v>
       </c>
     </row>
     <row r="232" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -12458,16 +12680,16 @@
         <v>223</v>
       </c>
       <c r="B232" s="5" t="s">
-        <v>679</v>
+        <v>682</v>
       </c>
       <c r="C232" s="5" t="s">
-        <v>1206</v>
+        <v>1209</v>
       </c>
       <c r="D232" s="6" t="s">
-        <v>1207</v>
+        <v>1210</v>
       </c>
       <c r="E232" s="5" t="s">
-        <v>1208</v>
+        <v>1211</v>
       </c>
     </row>
     <row r="233" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -12475,16 +12697,16 @@
         <v>224</v>
       </c>
       <c r="B233" s="5" t="s">
-        <v>901</v>
+        <v>904</v>
       </c>
       <c r="C233" s="5" t="s">
-        <v>1209</v>
+        <v>1212</v>
       </c>
       <c r="D233" s="6" t="s">
-        <v>1210</v>
+        <v>1213</v>
       </c>
       <c r="E233" s="5" t="s">
-        <v>1208</v>
+        <v>1211</v>
       </c>
     </row>
     <row r="234" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -12492,16 +12714,16 @@
         <v>225</v>
       </c>
       <c r="B234" s="5" t="s">
-        <v>679</v>
+        <v>682</v>
       </c>
       <c r="C234" s="5" t="s">
-        <v>1211</v>
+        <v>1214</v>
       </c>
       <c r="D234" s="6" t="s">
-        <v>1212</v>
+        <v>1215</v>
       </c>
       <c r="E234" s="5" t="s">
-        <v>1213</v>
+        <v>1216</v>
       </c>
     </row>
     <row r="235" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -12509,16 +12731,16 @@
         <v>226</v>
       </c>
       <c r="B235" s="5" t="s">
-        <v>818</v>
+        <v>821</v>
       </c>
       <c r="C235" s="5" t="s">
-        <v>1214</v>
+        <v>1217</v>
       </c>
       <c r="D235" s="6" t="s">
-        <v>1215</v>
+        <v>1218</v>
       </c>
       <c r="E235" s="5" t="s">
-        <v>1213</v>
+        <v>1216</v>
       </c>
     </row>
     <row r="236" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -12526,16 +12748,16 @@
         <v>227</v>
       </c>
       <c r="B236" s="5" t="s">
-        <v>901</v>
+        <v>904</v>
       </c>
       <c r="C236" s="5" t="s">
+        <v>1219</v>
+      </c>
+      <c r="D236" s="6" t="s">
+        <v>1220</v>
+      </c>
+      <c r="E236" s="5" t="s">
         <v>1216</v>
-      </c>
-      <c r="D236" s="6" t="s">
-        <v>1217</v>
-      </c>
-      <c r="E236" s="5" t="s">
-        <v>1213</v>
       </c>
     </row>
     <row r="237" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -12543,16 +12765,16 @@
         <v>228</v>
       </c>
       <c r="B237" s="5" t="s">
-        <v>901</v>
+        <v>904</v>
       </c>
       <c r="C237" s="5" t="s">
-        <v>1218</v>
+        <v>1221</v>
       </c>
       <c r="D237" s="6" t="s">
-        <v>1219</v>
+        <v>1222</v>
       </c>
       <c r="E237" s="5" t="s">
-        <v>1220</v>
+        <v>1223</v>
       </c>
     </row>
     <row r="238" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -12560,16 +12782,16 @@
         <v>229</v>
       </c>
       <c r="B238" s="5" t="s">
-        <v>874</v>
+        <v>877</v>
       </c>
       <c r="C238" s="5" t="s">
-        <v>1221</v>
+        <v>1224</v>
       </c>
       <c r="D238" s="6" t="s">
-        <v>1222</v>
+        <v>1225</v>
       </c>
       <c r="E238" s="5" t="s">
-        <v>1220</v>
+        <v>1223</v>
       </c>
     </row>
     <row r="239" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -12577,16 +12799,16 @@
         <v>230</v>
       </c>
       <c r="B239" s="5" t="s">
-        <v>874</v>
+        <v>877</v>
       </c>
       <c r="C239" s="5" t="s">
+        <v>1226</v>
+      </c>
+      <c r="D239" s="6" t="s">
+        <v>1227</v>
+      </c>
+      <c r="E239" s="5" t="s">
         <v>1223</v>
-      </c>
-      <c r="D239" s="6" t="s">
-        <v>1224</v>
-      </c>
-      <c r="E239" s="5" t="s">
-        <v>1220</v>
       </c>
     </row>
     <row r="240" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -12594,16 +12816,16 @@
         <v>231</v>
       </c>
       <c r="B240" s="5" t="s">
-        <v>1042</v>
+        <v>1045</v>
       </c>
       <c r="C240" s="5" t="s">
-        <v>1225</v>
+        <v>1228</v>
       </c>
       <c r="D240" s="6" t="s">
-        <v>1226</v>
+        <v>1229</v>
       </c>
       <c r="E240" s="5" t="s">
-        <v>1220</v>
+        <v>1223</v>
       </c>
     </row>
     <row r="241" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -12611,16 +12833,16 @@
         <v>232</v>
       </c>
       <c r="B241" s="5" t="s">
-        <v>1042</v>
+        <v>1045</v>
       </c>
       <c r="C241" s="5" t="s">
-        <v>1227</v>
+        <v>1230</v>
       </c>
       <c r="D241" s="6" t="s">
-        <v>1228</v>
+        <v>1231</v>
       </c>
       <c r="E241" s="5" t="s">
-        <v>1220</v>
+        <v>1223</v>
       </c>
     </row>
     <row r="242" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -12628,13 +12850,13 @@
         <v>233</v>
       </c>
       <c r="B242" s="5" t="s">
-        <v>874</v>
+        <v>877</v>
       </c>
       <c r="C242" s="5" t="s">
-        <v>1229</v>
+        <v>1232</v>
       </c>
       <c r="D242" s="6" t="s">
-        <v>1230</v>
+        <v>1233</v>
       </c>
       <c r="E242" s="5" t="s">
         <v>559</v>
@@ -12645,16 +12867,16 @@
         <v>234</v>
       </c>
       <c r="B243" s="5" t="s">
-        <v>885</v>
+        <v>888</v>
       </c>
       <c r="C243" s="5" t="s">
-        <v>1231</v>
+        <v>1234</v>
       </c>
       <c r="D243" s="6" t="s">
-        <v>1232</v>
+        <v>1235</v>
       </c>
       <c r="E243" s="5" t="s">
-        <v>1233</v>
+        <v>1236</v>
       </c>
     </row>
     <row r="244" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -12662,16 +12884,16 @@
         <v>235</v>
       </c>
       <c r="B244" s="5" t="s">
-        <v>679</v>
+        <v>682</v>
       </c>
       <c r="C244" s="5" t="s">
-        <v>1234</v>
+        <v>1237</v>
       </c>
       <c r="D244" s="6" t="s">
-        <v>1235</v>
+        <v>1238</v>
       </c>
       <c r="E244" s="5" t="s">
-        <v>1233</v>
+        <v>1236</v>
       </c>
     </row>
     <row r="245" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -12679,16 +12901,16 @@
         <v>236</v>
       </c>
       <c r="B245" s="5" t="s">
-        <v>679</v>
+        <v>682</v>
       </c>
       <c r="C245" s="5" t="s">
+        <v>1239</v>
+      </c>
+      <c r="D245" s="6" t="s">
+        <v>1240</v>
+      </c>
+      <c r="E245" s="5" t="s">
         <v>1236</v>
-      </c>
-      <c r="D245" s="6" t="s">
-        <v>1237</v>
-      </c>
-      <c r="E245" s="5" t="s">
-        <v>1233</v>
       </c>
     </row>
     <row r="246" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -12696,84 +12918,237 @@
         <v>237</v>
       </c>
       <c r="B246" s="5" t="s">
-        <v>874</v>
+        <v>877</v>
       </c>
       <c r="C246" s="5" t="s">
-        <v>1238</v>
+        <v>1241</v>
       </c>
       <c r="D246" s="6" t="s">
-        <v>1239</v>
+        <v>1242</v>
       </c>
       <c r="E246" s="5" t="s">
-        <v>1233</v>
-      </c>
-    </row>
-    <row r="247" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+        <v>1236</v>
+      </c>
+    </row>
+    <row r="247" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A247" s="5" t="n">
         <v>238</v>
       </c>
       <c r="B247" s="5" t="s">
-        <v>818</v>
+        <v>821</v>
       </c>
       <c r="C247" s="5" t="s">
-        <v>1240</v>
+        <v>1243</v>
       </c>
       <c r="D247" s="6" t="s">
-        <v>1241</v>
+        <v>1244</v>
       </c>
       <c r="E247" s="5" t="s">
         <v>562</v>
       </c>
     </row>
-    <row r="248" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="248" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A248" s="5" t="n">
         <v>239</v>
       </c>
       <c r="B248" s="5" t="s">
-        <v>679</v>
+        <v>682</v>
       </c>
       <c r="C248" s="5" t="s">
-        <v>1242</v>
+        <v>1245</v>
       </c>
       <c r="D248" s="6" t="s">
-        <v>1243</v>
+        <v>1246</v>
       </c>
       <c r="E248" s="5" t="s">
-        <v>1244</v>
-      </c>
-    </row>
-    <row r="249" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+        <v>1247</v>
+      </c>
+    </row>
+    <row r="249" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A249" s="5" t="n">
         <v>240</v>
       </c>
       <c r="B249" s="5" t="s">
-        <v>818</v>
+        <v>821</v>
       </c>
       <c r="C249" s="5" t="s">
-        <v>1245</v>
+        <v>1248</v>
       </c>
       <c r="D249" s="6" t="s">
-        <v>1246</v>
+        <v>1249</v>
       </c>
       <c r="E249" s="5" t="s">
-        <v>1244</v>
-      </c>
-    </row>
-    <row r="250" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+        <v>1247</v>
+      </c>
+    </row>
+    <row r="250" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A250" s="5" t="n">
         <v>241</v>
       </c>
       <c r="B250" s="5" t="s">
-        <v>804</v>
+        <v>807</v>
       </c>
       <c r="C250" s="5" t="s">
+        <v>1250</v>
+      </c>
+      <c r="D250" s="6" t="s">
+        <v>1251</v>
+      </c>
+      <c r="E250" s="5" t="s">
+        <v>1252</v>
+      </c>
+    </row>
+    <row r="251" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A251" s="5" t="n">
+        <v>242</v>
+      </c>
+      <c r="B251" s="5" t="s">
+        <v>821</v>
+      </c>
+      <c r="C251" s="5" t="s">
+        <v>1253</v>
+      </c>
+      <c r="D251" s="6" t="s">
+        <v>1254</v>
+      </c>
+      <c r="E251" s="5" t="s">
+        <v>1255</v>
+      </c>
+    </row>
+    <row r="252" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A252" s="5" t="n">
+        <v>243</v>
+      </c>
+      <c r="B252" s="5" t="s">
+        <v>1256</v>
+      </c>
+      <c r="C252" s="5" t="s">
+        <v>1257</v>
+      </c>
+      <c r="D252" s="6" t="s">
+        <v>1258</v>
+      </c>
+      <c r="E252" s="5" t="s">
+        <v>1259</v>
+      </c>
+    </row>
+    <row r="253" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A253" s="5" t="n">
+        <v>244</v>
+      </c>
+      <c r="B253" s="5" t="s">
+        <v>1260</v>
+      </c>
+      <c r="C253" s="5" t="s">
+        <v>1261</v>
+      </c>
+      <c r="D253" s="6" t="s">
+        <v>1262</v>
+      </c>
+      <c r="E253" s="5" t="s">
         <v>1247</v>
       </c>
-      <c r="D250" s="6" t="s">
-        <v>1248</v>
-      </c>
-      <c r="E250" s="5" t="s">
-        <v>1249</v>
+    </row>
+    <row r="254" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A254" s="5" t="n">
+        <v>245</v>
+      </c>
+      <c r="B254" s="5" t="s">
+        <v>821</v>
+      </c>
+      <c r="C254" s="5" t="s">
+        <v>1263</v>
+      </c>
+      <c r="D254" s="6" t="s">
+        <v>1264</v>
+      </c>
+      <c r="E254" s="5" t="s">
+        <v>1255</v>
+      </c>
+    </row>
+    <row r="255" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A255" s="5" t="n">
+        <v>246</v>
+      </c>
+      <c r="B255" s="5" t="s">
+        <v>1256</v>
+      </c>
+      <c r="C255" s="5" t="s">
+        <v>1265</v>
+      </c>
+      <c r="D255" s="6" t="s">
+        <v>1266</v>
+      </c>
+      <c r="E255" s="5" t="s">
+        <v>1252</v>
+      </c>
+    </row>
+    <row r="256" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A256" s="5" t="n">
+        <v>247</v>
+      </c>
+      <c r="B256" s="5" t="s">
+        <v>1267</v>
+      </c>
+      <c r="C256" s="5" t="s">
+        <v>1268</v>
+      </c>
+      <c r="D256" s="6" t="s">
+        <v>1269</v>
+      </c>
+      <c r="E256" s="5" t="s">
+        <v>1255</v>
+      </c>
+    </row>
+    <row r="257" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A257" s="5" t="n">
+        <v>248</v>
+      </c>
+      <c r="B257" s="5" t="s">
+        <v>821</v>
+      </c>
+      <c r="C257" s="5" t="s">
+        <v>1270</v>
+      </c>
+      <c r="D257" s="6" t="s">
+        <v>1271</v>
+      </c>
+      <c r="E257" s="5" t="s">
+        <v>1255</v>
+      </c>
+    </row>
+    <row r="258" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A258" s="5" t="n">
+        <v>249</v>
+      </c>
+      <c r="B258" s="5" t="s">
+        <v>888</v>
+      </c>
+      <c r="C258" s="5" t="s">
+        <v>1272</v>
+      </c>
+      <c r="D258" s="6" t="s">
+        <v>1273</v>
+      </c>
+      <c r="E258" s="5" t="s">
+        <v>1255</v>
+      </c>
+    </row>
+    <row r="259" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A259" s="5" t="n">
+        <v>250</v>
+      </c>
+      <c r="B259" s="5" t="s">
+        <v>1260</v>
+      </c>
+      <c r="C259" s="5" t="s">
+        <v>1274</v>
+      </c>
+      <c r="D259" s="6" t="s">
+        <v>1275</v>
+      </c>
+      <c r="E259" s="5" t="s">
+        <v>1259</v>
       </c>
     </row>
   </sheetData>
@@ -12949,6 +13324,15 @@
     <hyperlink ref="D248" r:id="rId166" display="https://www.nbcnews.com/politics/supreme-court/supreme-court-allows-trump-administration-use-expanded-database-potent-rcna596611"/>
     <hyperlink ref="D249" r:id="rId167" display="https://www.theguardian.com/us-news/ng-interactive/2026/sep/25/student-math-reading-test-scores"/>
     <hyperlink ref="D250" r:id="rId168" display="https://www.bbc.com/news/articles/c3y0z25v0zjwo"/>
+    <hyperlink ref="D251" r:id="rId169" display="https://www.theguardian.com/sport/2026/sep/26/aminata-seck-ice-international-college-athletes"/>
+    <hyperlink ref="D252" r:id="rId170" display="https://www.axios.com/2026/09/22/trump-trumptv-white-house-live-news-network"/>
+    <hyperlink ref="D253" r:id="rId171" display="https://www.latimes.com/politics/story/2026-09-25/justices-uphold-trumps-expanded-data-checks-to-spot-non-citizens-who-registered-to-vote"/>
+    <hyperlink ref="D254" r:id="rId172" display="https://www.theguardian.com/us-news/2026/sep/25/white-house-cnn-air-force-one"/>
+    <hyperlink ref="D255" r:id="rId173" display="https://www.axios.com/2026/09/20/trump-arch-washington-snipers-drones"/>
+    <hyperlink ref="D256" r:id="rId174" display="https://www.nytimes.com/2026/09/25/us/politics/white-house-rescissions-education-and-health-funds.html"/>
+    <hyperlink ref="D257" r:id="rId175" display="https://www.theguardian.com/us-news/2026/sep/25/trump-cancels-congress-funding"/>
+    <hyperlink ref="D258" r:id="rId176" display="https://www.npr.org/2026/09/26/nx-s1-5981103/cnn-is-getting-new-owners-with-close-ties-to-trump"/>
+    <hyperlink ref="D259" r:id="rId177" display="https://www.latimes.com/politics/story/2026-09-22/trump-threatens-to-send-iran-into-hell-if-war-carries-on"/>
   </hyperlinks>
   <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.511811023622047" footer="0.511811023622047"/>
@@ -12965,7 +13349,7 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:B22"/>
+  <dimension ref="A1:B23"/>
   <sheetFormatPr defaultColWidth="8.6875" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="30.01"/>
@@ -12974,7 +13358,7 @@
   <sheetData>
     <row r="1" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A1" s="7" t="s">
-        <v>1250</v>
+        <v>1276</v>
       </c>
       <c r="B1" s="7"/>
     </row>
@@ -12983,7 +13367,7 @@
         <v>3</v>
       </c>
       <c r="B2" s="8" t="s">
-        <v>1251</v>
+        <v>1277</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -13010,7 +13394,7 @@
       </c>
       <c r="B5" s="9" t="n">
         <f aca="false">COUNTIF('Weekly Timeline'!C:C,A5)</f>
-        <v>8</v>
+        <v>9</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -13064,7 +13448,7 @@
       </c>
       <c r="B11" s="9" t="n">
         <f aca="false">COUNTIF('Weekly Timeline'!C:C,A11)</f>
-        <v>30</v>
+        <v>33</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -13082,7 +13466,7 @@
       </c>
       <c r="B13" s="9" t="n">
         <f aca="false">COUNTIF('Weekly Timeline'!C:C,A13)</f>
-        <v>16</v>
+        <v>17</v>
       </c>
     </row>
     <row r="14" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -13118,7 +13502,7 @@
       </c>
       <c r="B17" s="9" t="n">
         <f aca="false">COUNTIF('Weekly Timeline'!C:C,A17)</f>
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="18" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -13132,38 +13516,47 @@
     </row>
     <row r="19" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A19" s="9" t="s">
-        <v>68</v>
+        <v>566</v>
       </c>
       <c r="B19" s="9" t="n">
         <f aca="false">COUNTIF('Weekly Timeline'!C:C,A19)</f>
-        <v>11</v>
+        <v>1</v>
       </c>
     </row>
     <row r="20" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A20" s="9" t="s">
-        <v>72</v>
+        <v>68</v>
       </c>
       <c r="B20" s="9" t="n">
         <f aca="false">COUNTIF('Weekly Timeline'!C:C,A20)</f>
-        <v>4</v>
+        <v>13</v>
       </c>
     </row>
     <row r="21" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A21" s="9" t="s">
-        <v>346</v>
+        <v>72</v>
       </c>
       <c r="B21" s="9" t="n">
         <f aca="false">COUNTIF('Weekly Timeline'!C:C,A21)</f>
+        <v>4</v>
+      </c>
+    </row>
+    <row r="22" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A22" s="9" t="s">
+        <v>346</v>
+      </c>
+      <c r="B22" s="9" t="n">
+        <f aca="false">COUNTIF('Weekly Timeline'!C:C,A22)</f>
         <v>1</v>
       </c>
     </row>
-    <row r="22" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A22" s="10" t="s">
-        <v>1252</v>
-      </c>
-      <c r="B22" s="10" t="n">
-        <f aca="false">SUM(B3:B21)</f>
-        <v>185</v>
+    <row r="23" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A23" s="10" t="s">
+        <v>1278</v>
+      </c>
+      <c r="B23" s="10" t="n">
+        <f aca="false">SUM(B3:B22)</f>
+        <v>194</v>
       </c>
     </row>
   </sheetData>

--- a/data/Trump_Second_Term_Weekly_Tracker.xlsx
+++ b/data/Trump_Second_Term_Weekly_Tracker.xlsx
@@ -13,7 +13,7 @@
     <sheet name="Summary" sheetId="3" state="visible" r:id="rId5"/>
   </sheets>
   <definedNames>
-    <definedName function="false" hidden="true" localSheetId="0" name="_xlnm._FilterDatabase" vbProcedure="false">'Weekly Timeline'!$A$2:$F$252</definedName>
+    <definedName function="false" hidden="true" localSheetId="0" name="_xlnm._FilterDatabase" vbProcedure="false">'Weekly Timeline'!$A$2:$F$260</definedName>
   </definedNames>
   <calcPr iterateCount="100" refMode="A1" iterate="false" iterateDelta="0.0001"/>
   <extLst>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1991" uniqueCount="1279">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2047" uniqueCount="1301">
   <si>
     <t xml:space="preserve">Documented actions and policies of the second Trump administration reported as harmful by major news outlets, courts, and government data — Jan 20, 2025 through Jul 8, 2026. One row per event; weeks with multiple events have multiple rows; quiet weeks are skipped. This compiles critical coverage as requested; the administration and its supporters dispute many of these characterizations. See the Sources tab (matching Ref #) and verify details independently before citing.</t>
   </si>
@@ -1731,6 +1731,12 @@
     <t xml:space="preserve">Sep 22</t>
   </si>
   <si>
+    <t xml:space="preserve">Sep 28, 2026</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Sep 29</t>
+  </si>
+  <si>
     <t xml:space="preserve">Ref # matches the Source Ref column on the Weekly Timeline tab. URLs are provided where verified via current web results (mostly 2026 items). For 2025 items, outlet names and dates are given; searching the description text will locate the original coverage. Per your request the mix emphasizes CNN, Politico, MSNBC/MS NOW, NBC and independent outlets, alongside AP, Reuters, Guardian, NPR, CBS, ABC and court documents.</t>
   </si>
   <si>
@@ -3853,6 +3859,66 @@
   </si>
   <si>
     <t xml:space="preserve">https://www.latimes.com/politics/story/2026-09-22/trump-threatens-to-send-iran-into-hell-if-war-carries-on</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Supreme Court green-lights Trump's third-country deportations</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://www.axios.com/2026/09/29/supreme-court-trump-third-country-deportations</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Sep 29, 2026</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Trump leans on SCOTUS shadow docket more than Biden, Obama and Bush combined</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://www.axios.com/2026/09/29/trump-supreme-court-shadow-docket-41-applications</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Venezuelan man shot and wounded by ICE agent in Texas is charged with assaulting an officer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://www.nbcnews.com/news/us-news/venezuelan-man-shot-wounded-ice-agent-texas-charged-assaulting-officer-rcna600533</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Trump campaign ads paid with public money violate federal law, critics say</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://www.theguardian.com/us-news/2026/sep/30/trump-campaign-ads-violate-federal-law</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Sep 30, 2026</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Trump says he’d consider issuing pardons to administration officials before he leaves office</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://www.nbcnews.com/politics/trump-administration/trump-considering-preemptive-pardons-administration-officials-rcna600905</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Oct 1, 2026</t>
+  </si>
+  <si>
+    <t xml:space="preserve">White House blocks CNN from pool duty despite judge’s order</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://thehill.com/homenews/6122096-white-house-blocks-cnn-pool-trump/</t>
+  </si>
+  <si>
+    <t xml:space="preserve">The Washington Post</t>
+  </si>
+  <si>
+    <t xml:space="preserve">GOP senator blocks bill to stop Trump from demolishing Kennedy Center</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://www.washingtonpost.com/politics/2026/09/29/gop-senator-blocks-bill-stop-trump-demolishing-kennedy-center/</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Trump administration says it's scaling back fuel efficiency standards for new cars</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://www.npr.org/2026/09/29/nx-s1-5983673/trump-administration-says-its-scaling-back-fuel-efficiency-standards-for-new-cars</t>
   </si>
   <si>
     <t xml:space="preserve">Entries by category (live COUNTIF formulas against the Weekly Timeline tab)</t>
@@ -4041,7 +4107,7 @@
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="164" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -4334,7 +4400,7 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:F252"/>
+  <dimension ref="A1:F260"/>
   <sheetFormatPr defaultColWidth="8.6875" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="13.01"/>
@@ -8742,7 +8808,7 @@
         <v>241</v>
       </c>
     </row>
-    <row r="244" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="244" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A244" s="5" t="s">
         <v>562</v>
       </c>
@@ -8758,7 +8824,7 @@
         <v>242</v>
       </c>
     </row>
-    <row r="245" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="245" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A245" s="5" t="s">
         <v>562</v>
       </c>
@@ -8774,7 +8840,7 @@
         <v>243</v>
       </c>
     </row>
-    <row r="246" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="246" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A246" s="5" t="s">
         <v>562</v>
       </c>
@@ -8790,7 +8856,7 @@
         <v>244</v>
       </c>
     </row>
-    <row r="247" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="247" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A247" s="5" t="s">
         <v>562</v>
       </c>
@@ -8806,7 +8872,7 @@
         <v>245</v>
       </c>
     </row>
-    <row r="248" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="248" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A248" s="4" t="s">
         <v>559</v>
       </c>
@@ -8822,7 +8888,7 @@
         <v>246</v>
       </c>
     </row>
-    <row r="249" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="249" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A249" s="5" t="s">
         <v>562</v>
       </c>
@@ -8838,7 +8904,7 @@
         <v>247</v>
       </c>
     </row>
-    <row r="250" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="250" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A250" s="5" t="s">
         <v>562</v>
       </c>
@@ -8854,7 +8920,7 @@
         <v>248</v>
       </c>
     </row>
-    <row r="251" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="251" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A251" s="5" t="s">
         <v>562</v>
       </c>
@@ -8870,7 +8936,7 @@
         <v>249</v>
       </c>
     </row>
-    <row r="252" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="252" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A252" s="5" t="s">
         <v>562</v>
       </c>
@@ -8886,8 +8952,136 @@
         <v>250</v>
       </c>
     </row>
+    <row r="253" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A253" s="4" t="s">
+        <v>568</v>
+      </c>
+      <c r="B253" s="4" t="s">
+        <v>569</v>
+      </c>
+      <c r="C253" s="4" t="s">
+        <v>194</v>
+      </c>
+      <c r="D253" s="4"/>
+      <c r="E253" s="4"/>
+      <c r="F253" s="4" t="n">
+        <v>251</v>
+      </c>
+    </row>
+    <row r="254" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A254" s="4" t="s">
+        <v>568</v>
+      </c>
+      <c r="B254" s="4" t="s">
+        <v>569</v>
+      </c>
+      <c r="C254" s="4" t="s">
+        <v>194</v>
+      </c>
+      <c r="D254" s="4"/>
+      <c r="E254" s="4"/>
+      <c r="F254" s="4" t="n">
+        <v>252</v>
+      </c>
+    </row>
+    <row r="255" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A255" s="4" t="s">
+        <v>568</v>
+      </c>
+      <c r="B255" s="4" t="s">
+        <v>569</v>
+      </c>
+      <c r="C255" s="4" t="s">
+        <v>566</v>
+      </c>
+      <c r="D255" s="4"/>
+      <c r="E255" s="4"/>
+      <c r="F255" s="4" t="n">
+        <v>253</v>
+      </c>
+    </row>
+    <row r="256" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A256" s="4" t="s">
+        <v>568</v>
+      </c>
+      <c r="B256" s="4" t="s">
+        <v>252</v>
+      </c>
+      <c r="C256" s="4" t="s">
+        <v>24</v>
+      </c>
+      <c r="D256" s="4"/>
+      <c r="E256" s="4"/>
+      <c r="F256" s="4" t="n">
+        <v>254</v>
+      </c>
+    </row>
+    <row r="257" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A257" s="4" t="s">
+        <v>568</v>
+      </c>
+      <c r="B257" s="4" t="s">
+        <v>255</v>
+      </c>
+      <c r="C257" s="4" t="s">
+        <v>24</v>
+      </c>
+      <c r="D257" s="4"/>
+      <c r="E257" s="4"/>
+      <c r="F257" s="4" t="n">
+        <v>255</v>
+      </c>
+    </row>
+    <row r="258" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A258" s="4" t="s">
+        <v>568</v>
+      </c>
+      <c r="B258" s="4" t="s">
+        <v>255</v>
+      </c>
+      <c r="C258" s="4" t="s">
+        <v>68</v>
+      </c>
+      <c r="D258" s="4"/>
+      <c r="E258" s="4"/>
+      <c r="F258" s="4" t="n">
+        <v>256</v>
+      </c>
+    </row>
+    <row r="259" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A259" s="4" t="s">
+        <v>568</v>
+      </c>
+      <c r="B259" s="4" t="s">
+        <v>569</v>
+      </c>
+      <c r="C259" s="4" t="s">
+        <v>24</v>
+      </c>
+      <c r="D259" s="4"/>
+      <c r="E259" s="4"/>
+      <c r="F259" s="4" t="n">
+        <v>257</v>
+      </c>
+    </row>
+    <row r="260" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A260" s="4" t="s">
+        <v>568</v>
+      </c>
+      <c r="B260" s="4" t="s">
+        <v>569</v>
+      </c>
+      <c r="C260" s="4" t="s">
+        <v>21</v>
+      </c>
+      <c r="D260" s="4"/>
+      <c r="E260" s="4"/>
+      <c r="F260" s="4" t="n">
+        <v>258</v>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A2:F252"/>
+  <autoFilter ref="A2:F260"/>
   <mergeCells count="1">
     <mergeCell ref="A1:F1"/>
   </mergeCells>
@@ -8907,7 +9101,7 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:E259"/>
+  <dimension ref="A1:E267"/>
   <sheetFormatPr defaultColWidth="8.6875" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="7"/>
@@ -8918,7 +9112,7 @@
   <sheetData>
     <row r="1" customFormat="false" ht="48" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A1" s="2" t="s">
-        <v>568</v>
+        <v>570</v>
       </c>
       <c r="B1" s="2"/>
       <c r="C1" s="2"/>
@@ -8927,19 +9121,19 @@
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A2" s="3" t="s">
-        <v>569</v>
+        <v>571</v>
       </c>
       <c r="B2" s="3" t="s">
-        <v>570</v>
+        <v>572</v>
       </c>
       <c r="C2" s="3" t="s">
-        <v>571</v>
+        <v>573</v>
       </c>
       <c r="D2" s="3" t="s">
-        <v>572</v>
+        <v>574</v>
       </c>
       <c r="E2" s="3" t="s">
-        <v>573</v>
+        <v>575</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -8947,14 +9141,14 @@
         <v>1</v>
       </c>
       <c r="B3" s="5" t="s">
-        <v>574</v>
+        <v>576</v>
       </c>
       <c r="C3" s="5" t="s">
-        <v>575</v>
+        <v>577</v>
       </c>
       <c r="D3" s="5"/>
       <c r="E3" s="5" t="s">
-        <v>576</v>
+        <v>578</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -8962,14 +9156,14 @@
         <v>2</v>
       </c>
       <c r="B4" s="5" t="s">
-        <v>577</v>
+        <v>579</v>
       </c>
       <c r="C4" s="5" t="s">
-        <v>578</v>
+        <v>580</v>
       </c>
       <c r="D4" s="5"/>
       <c r="E4" s="5" t="s">
-        <v>579</v>
+        <v>581</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -8977,14 +9171,14 @@
         <v>3</v>
       </c>
       <c r="B5" s="5" t="s">
-        <v>580</v>
+        <v>582</v>
       </c>
       <c r="C5" s="5" t="s">
-        <v>581</v>
+        <v>583</v>
       </c>
       <c r="D5" s="5"/>
       <c r="E5" s="5" t="s">
-        <v>576</v>
+        <v>578</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -8992,14 +9186,14 @@
         <v>4</v>
       </c>
       <c r="B6" s="5" t="s">
-        <v>582</v>
+        <v>584</v>
       </c>
       <c r="C6" s="5" t="s">
-        <v>583</v>
+        <v>585</v>
       </c>
       <c r="D6" s="5"/>
       <c r="E6" s="5" t="s">
-        <v>584</v>
+        <v>586</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -9007,14 +9201,14 @@
         <v>5</v>
       </c>
       <c r="B7" s="5" t="s">
-        <v>585</v>
+        <v>587</v>
       </c>
       <c r="C7" s="5" t="s">
-        <v>586</v>
+        <v>588</v>
       </c>
       <c r="D7" s="5"/>
       <c r="E7" s="5" t="s">
-        <v>576</v>
+        <v>578</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -9022,14 +9216,14 @@
         <v>6</v>
       </c>
       <c r="B8" s="5" t="s">
-        <v>587</v>
+        <v>589</v>
       </c>
       <c r="C8" s="5" t="s">
-        <v>588</v>
+        <v>590</v>
       </c>
       <c r="D8" s="5"/>
       <c r="E8" s="5" t="s">
-        <v>576</v>
+        <v>578</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -9037,14 +9231,14 @@
         <v>7</v>
       </c>
       <c r="B9" s="5" t="s">
-        <v>589</v>
+        <v>591</v>
       </c>
       <c r="C9" s="5" t="s">
-        <v>590</v>
+        <v>592</v>
       </c>
       <c r="D9" s="5"/>
       <c r="E9" s="5" t="s">
-        <v>591</v>
+        <v>593</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -9052,14 +9246,14 @@
         <v>8</v>
       </c>
       <c r="B10" s="5" t="s">
-        <v>592</v>
+        <v>594</v>
       </c>
       <c r="C10" s="5" t="s">
-        <v>593</v>
+        <v>595</v>
       </c>
       <c r="D10" s="5"/>
       <c r="E10" s="5" t="s">
-        <v>594</v>
+        <v>596</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -9067,14 +9261,14 @@
         <v>9</v>
       </c>
       <c r="B11" s="5" t="s">
-        <v>595</v>
+        <v>597</v>
       </c>
       <c r="C11" s="5" t="s">
-        <v>596</v>
+        <v>598</v>
       </c>
       <c r="D11" s="5"/>
       <c r="E11" s="5" t="s">
-        <v>597</v>
+        <v>599</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -9082,14 +9276,14 @@
         <v>10</v>
       </c>
       <c r="B12" s="5" t="s">
-        <v>598</v>
+        <v>600</v>
       </c>
       <c r="C12" s="5" t="s">
-        <v>599</v>
+        <v>601</v>
       </c>
       <c r="D12" s="5"/>
       <c r="E12" s="5" t="s">
-        <v>600</v>
+        <v>602</v>
       </c>
     </row>
     <row r="13" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -9097,14 +9291,14 @@
         <v>11</v>
       </c>
       <c r="B13" s="5" t="s">
-        <v>601</v>
+        <v>603</v>
       </c>
       <c r="C13" s="5" t="s">
-        <v>602</v>
+        <v>604</v>
       </c>
       <c r="D13" s="5"/>
       <c r="E13" s="5" t="s">
-        <v>603</v>
+        <v>605</v>
       </c>
     </row>
     <row r="14" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -9112,14 +9306,14 @@
         <v>12</v>
       </c>
       <c r="B14" s="5" t="s">
-        <v>604</v>
+        <v>606</v>
       </c>
       <c r="C14" s="5" t="s">
-        <v>605</v>
+        <v>607</v>
       </c>
       <c r="D14" s="5"/>
       <c r="E14" s="5" t="s">
-        <v>606</v>
+        <v>608</v>
       </c>
     </row>
     <row r="15" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -9127,14 +9321,14 @@
         <v>13</v>
       </c>
       <c r="B15" s="5" t="s">
-        <v>607</v>
+        <v>609</v>
       </c>
       <c r="C15" s="5" t="s">
-        <v>608</v>
+        <v>610</v>
       </c>
       <c r="D15" s="5"/>
       <c r="E15" s="5" t="s">
-        <v>609</v>
+        <v>611</v>
       </c>
     </row>
     <row r="16" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -9142,14 +9336,14 @@
         <v>14</v>
       </c>
       <c r="B16" s="5" t="s">
-        <v>610</v>
+        <v>612</v>
       </c>
       <c r="C16" s="5" t="s">
-        <v>611</v>
+        <v>613</v>
       </c>
       <c r="D16" s="5"/>
       <c r="E16" s="5" t="s">
-        <v>612</v>
+        <v>614</v>
       </c>
     </row>
     <row r="17" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -9157,14 +9351,14 @@
         <v>15</v>
       </c>
       <c r="B17" s="5" t="s">
-        <v>613</v>
+        <v>615</v>
       </c>
       <c r="C17" s="5" t="s">
-        <v>614</v>
+        <v>616</v>
       </c>
       <c r="D17" s="5"/>
       <c r="E17" s="5" t="s">
-        <v>615</v>
+        <v>617</v>
       </c>
     </row>
     <row r="18" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -9172,14 +9366,14 @@
         <v>16</v>
       </c>
       <c r="B18" s="5" t="s">
-        <v>616</v>
+        <v>618</v>
       </c>
       <c r="C18" s="5" t="s">
-        <v>617</v>
+        <v>619</v>
       </c>
       <c r="D18" s="5"/>
       <c r="E18" s="5" t="s">
-        <v>618</v>
+        <v>620</v>
       </c>
     </row>
     <row r="19" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -9187,14 +9381,14 @@
         <v>17</v>
       </c>
       <c r="B19" s="5" t="s">
-        <v>619</v>
+        <v>621</v>
       </c>
       <c r="C19" s="5" t="s">
-        <v>620</v>
+        <v>622</v>
       </c>
       <c r="D19" s="5"/>
       <c r="E19" s="5" t="s">
-        <v>621</v>
+        <v>623</v>
       </c>
     </row>
     <row r="20" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -9202,14 +9396,14 @@
         <v>18</v>
       </c>
       <c r="B20" s="5" t="s">
-        <v>622</v>
+        <v>624</v>
       </c>
       <c r="C20" s="5" t="s">
-        <v>623</v>
+        <v>625</v>
       </c>
       <c r="D20" s="5"/>
       <c r="E20" s="5" t="s">
-        <v>624</v>
+        <v>626</v>
       </c>
     </row>
     <row r="21" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -9217,14 +9411,14 @@
         <v>19</v>
       </c>
       <c r="B21" s="5" t="s">
-        <v>625</v>
+        <v>627</v>
       </c>
       <c r="C21" s="5" t="s">
-        <v>626</v>
+        <v>628</v>
       </c>
       <c r="D21" s="5"/>
       <c r="E21" s="5" t="s">
-        <v>627</v>
+        <v>629</v>
       </c>
     </row>
     <row r="22" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -9232,14 +9426,14 @@
         <v>20</v>
       </c>
       <c r="B22" s="5" t="s">
-        <v>628</v>
+        <v>630</v>
       </c>
       <c r="C22" s="5" t="s">
-        <v>629</v>
+        <v>631</v>
       </c>
       <c r="D22" s="5"/>
       <c r="E22" s="5" t="s">
-        <v>630</v>
+        <v>632</v>
       </c>
     </row>
     <row r="23" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -9247,14 +9441,14 @@
         <v>21</v>
       </c>
       <c r="B23" s="5" t="s">
-        <v>631</v>
+        <v>633</v>
       </c>
       <c r="C23" s="5" t="s">
-        <v>632</v>
+        <v>634</v>
       </c>
       <c r="D23" s="5"/>
       <c r="E23" s="5" t="s">
-        <v>633</v>
+        <v>635</v>
       </c>
     </row>
     <row r="24" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -9262,14 +9456,14 @@
         <v>22</v>
       </c>
       <c r="B24" s="5" t="s">
-        <v>634</v>
+        <v>636</v>
       </c>
       <c r="C24" s="5" t="s">
-        <v>635</v>
+        <v>637</v>
       </c>
       <c r="D24" s="5"/>
       <c r="E24" s="5" t="s">
-        <v>636</v>
+        <v>638</v>
       </c>
     </row>
     <row r="25" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -9277,14 +9471,14 @@
         <v>23</v>
       </c>
       <c r="B25" s="5" t="s">
-        <v>637</v>
+        <v>639</v>
       </c>
       <c r="C25" s="5" t="s">
-        <v>638</v>
+        <v>640</v>
       </c>
       <c r="D25" s="5"/>
       <c r="E25" s="5" t="s">
-        <v>639</v>
+        <v>641</v>
       </c>
     </row>
     <row r="26" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -9292,14 +9486,14 @@
         <v>24</v>
       </c>
       <c r="B26" s="5" t="s">
-        <v>640</v>
+        <v>642</v>
       </c>
       <c r="C26" s="5" t="s">
-        <v>641</v>
+        <v>643</v>
       </c>
       <c r="D26" s="5"/>
       <c r="E26" s="5" t="s">
-        <v>642</v>
+        <v>644</v>
       </c>
     </row>
     <row r="27" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -9307,14 +9501,14 @@
         <v>25</v>
       </c>
       <c r="B27" s="5" t="s">
-        <v>643</v>
+        <v>645</v>
       </c>
       <c r="C27" s="5" t="s">
-        <v>644</v>
+        <v>646</v>
       </c>
       <c r="D27" s="5"/>
       <c r="E27" s="5" t="s">
-        <v>645</v>
+        <v>647</v>
       </c>
     </row>
     <row r="28" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -9322,14 +9516,14 @@
         <v>26</v>
       </c>
       <c r="B28" s="5" t="s">
-        <v>646</v>
+        <v>648</v>
       </c>
       <c r="C28" s="5" t="s">
-        <v>647</v>
+        <v>649</v>
       </c>
       <c r="D28" s="5"/>
       <c r="E28" s="5" t="s">
-        <v>648</v>
+        <v>650</v>
       </c>
     </row>
     <row r="29" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -9337,14 +9531,14 @@
         <v>27</v>
       </c>
       <c r="B29" s="5" t="s">
-        <v>649</v>
+        <v>651</v>
       </c>
       <c r="C29" s="5" t="s">
-        <v>650</v>
+        <v>652</v>
       </c>
       <c r="D29" s="5"/>
       <c r="E29" s="5" t="s">
-        <v>651</v>
+        <v>653</v>
       </c>
     </row>
     <row r="30" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -9352,14 +9546,14 @@
         <v>28</v>
       </c>
       <c r="B30" s="5" t="s">
-        <v>652</v>
+        <v>654</v>
       </c>
       <c r="C30" s="5" t="s">
-        <v>653</v>
+        <v>655</v>
       </c>
       <c r="D30" s="5"/>
       <c r="E30" s="5" t="s">
-        <v>654</v>
+        <v>656</v>
       </c>
     </row>
     <row r="31" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -9367,14 +9561,14 @@
         <v>29</v>
       </c>
       <c r="B31" s="5" t="s">
-        <v>655</v>
+        <v>657</v>
       </c>
       <c r="C31" s="5" t="s">
-        <v>656</v>
+        <v>658</v>
       </c>
       <c r="D31" s="5"/>
       <c r="E31" s="5" t="s">
-        <v>657</v>
+        <v>659</v>
       </c>
     </row>
     <row r="32" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -9382,14 +9576,14 @@
         <v>30</v>
       </c>
       <c r="B32" s="5" t="s">
-        <v>601</v>
+        <v>603</v>
       </c>
       <c r="C32" s="5" t="s">
-        <v>658</v>
+        <v>660</v>
       </c>
       <c r="D32" s="5"/>
       <c r="E32" s="5" t="s">
-        <v>659</v>
+        <v>661</v>
       </c>
     </row>
     <row r="33" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -9397,14 +9591,14 @@
         <v>31</v>
       </c>
       <c r="B33" s="5" t="s">
-        <v>660</v>
+        <v>662</v>
       </c>
       <c r="C33" s="5" t="s">
-        <v>661</v>
+        <v>663</v>
       </c>
       <c r="D33" s="5"/>
       <c r="E33" s="5" t="s">
-        <v>662</v>
+        <v>664</v>
       </c>
     </row>
     <row r="34" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -9412,14 +9606,14 @@
         <v>32</v>
       </c>
       <c r="B34" s="5" t="s">
-        <v>619</v>
+        <v>621</v>
       </c>
       <c r="C34" s="5" t="s">
-        <v>663</v>
+        <v>665</v>
       </c>
       <c r="D34" s="5"/>
       <c r="E34" s="5" t="s">
-        <v>664</v>
+        <v>666</v>
       </c>
     </row>
     <row r="35" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -9427,14 +9621,14 @@
         <v>33</v>
       </c>
       <c r="B35" s="5" t="s">
-        <v>665</v>
+        <v>667</v>
       </c>
       <c r="C35" s="5" t="s">
-        <v>666</v>
+        <v>668</v>
       </c>
       <c r="D35" s="5"/>
       <c r="E35" s="5" t="s">
-        <v>667</v>
+        <v>669</v>
       </c>
     </row>
     <row r="36" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -9442,14 +9636,14 @@
         <v>34</v>
       </c>
       <c r="B36" s="5" t="s">
-        <v>668</v>
+        <v>670</v>
       </c>
       <c r="C36" s="5" t="s">
-        <v>669</v>
+        <v>671</v>
       </c>
       <c r="D36" s="5"/>
       <c r="E36" s="5" t="s">
-        <v>670</v>
+        <v>672</v>
       </c>
     </row>
     <row r="37" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -9457,14 +9651,14 @@
         <v>35</v>
       </c>
       <c r="B37" s="5" t="s">
-        <v>671</v>
+        <v>673</v>
       </c>
       <c r="C37" s="5" t="s">
-        <v>672</v>
+        <v>674</v>
       </c>
       <c r="D37" s="5"/>
       <c r="E37" s="5" t="s">
-        <v>673</v>
+        <v>675</v>
       </c>
     </row>
     <row r="38" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -9472,14 +9666,14 @@
         <v>36</v>
       </c>
       <c r="B38" s="5" t="s">
-        <v>619</v>
+        <v>621</v>
       </c>
       <c r="C38" s="5" t="s">
-        <v>674</v>
+        <v>676</v>
       </c>
       <c r="D38" s="5"/>
       <c r="E38" s="5" t="s">
-        <v>675</v>
+        <v>677</v>
       </c>
     </row>
     <row r="39" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -9487,14 +9681,14 @@
         <v>37</v>
       </c>
       <c r="B39" s="5" t="s">
-        <v>676</v>
+        <v>678</v>
       </c>
       <c r="C39" s="5" t="s">
-        <v>677</v>
+        <v>679</v>
       </c>
       <c r="D39" s="5"/>
       <c r="E39" s="5" t="s">
-        <v>678</v>
+        <v>680</v>
       </c>
     </row>
     <row r="40" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -9502,14 +9696,14 @@
         <v>38</v>
       </c>
       <c r="B40" s="5" t="s">
-        <v>679</v>
+        <v>681</v>
       </c>
       <c r="C40" s="5" t="s">
-        <v>680</v>
+        <v>682</v>
       </c>
       <c r="D40" s="5"/>
       <c r="E40" s="5" t="s">
-        <v>681</v>
+        <v>683</v>
       </c>
     </row>
     <row r="41" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -9517,10 +9711,10 @@
         <v>39</v>
       </c>
       <c r="B41" s="5" t="s">
-        <v>682</v>
+        <v>684</v>
       </c>
       <c r="C41" s="5" t="s">
-        <v>683</v>
+        <v>685</v>
       </c>
       <c r="D41" s="5"/>
       <c r="E41" s="5" t="s">
@@ -9532,14 +9726,14 @@
         <v>40</v>
       </c>
       <c r="B42" s="5" t="s">
-        <v>684</v>
+        <v>686</v>
       </c>
       <c r="C42" s="5" t="s">
-        <v>685</v>
+        <v>687</v>
       </c>
       <c r="D42" s="5"/>
       <c r="E42" s="5" t="s">
-        <v>686</v>
+        <v>688</v>
       </c>
     </row>
     <row r="43" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -9547,14 +9741,14 @@
         <v>41</v>
       </c>
       <c r="B43" s="5" t="s">
-        <v>687</v>
+        <v>689</v>
       </c>
       <c r="C43" s="5" t="s">
-        <v>688</v>
+        <v>690</v>
       </c>
       <c r="D43" s="5"/>
       <c r="E43" s="5" t="s">
-        <v>689</v>
+        <v>691</v>
       </c>
     </row>
     <row r="44" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -9562,14 +9756,14 @@
         <v>42</v>
       </c>
       <c r="B44" s="5" t="s">
-        <v>690</v>
+        <v>692</v>
       </c>
       <c r="C44" s="5" t="s">
-        <v>691</v>
+        <v>693</v>
       </c>
       <c r="D44" s="5"/>
       <c r="E44" s="5" t="s">
-        <v>692</v>
+        <v>694</v>
       </c>
     </row>
     <row r="45" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -9577,14 +9771,14 @@
         <v>43</v>
       </c>
       <c r="B45" s="5" t="s">
-        <v>693</v>
+        <v>695</v>
       </c>
       <c r="C45" s="5" t="s">
-        <v>694</v>
+        <v>696</v>
       </c>
       <c r="D45" s="5"/>
       <c r="E45" s="5" t="s">
-        <v>695</v>
+        <v>697</v>
       </c>
     </row>
     <row r="46" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -9592,14 +9786,14 @@
         <v>44</v>
       </c>
       <c r="B46" s="5" t="s">
-        <v>696</v>
+        <v>698</v>
       </c>
       <c r="C46" s="5" t="s">
-        <v>697</v>
+        <v>699</v>
       </c>
       <c r="D46" s="5"/>
       <c r="E46" s="5" t="s">
-        <v>698</v>
+        <v>700</v>
       </c>
     </row>
     <row r="47" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -9607,14 +9801,14 @@
         <v>45</v>
       </c>
       <c r="B47" s="5" t="s">
-        <v>699</v>
+        <v>701</v>
       </c>
       <c r="C47" s="5" t="s">
-        <v>700</v>
+        <v>702</v>
       </c>
       <c r="D47" s="5"/>
       <c r="E47" s="5" t="s">
-        <v>701</v>
+        <v>703</v>
       </c>
     </row>
     <row r="48" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -9622,14 +9816,14 @@
         <v>46</v>
       </c>
       <c r="B48" s="5" t="s">
-        <v>702</v>
+        <v>704</v>
       </c>
       <c r="C48" s="5" t="s">
-        <v>703</v>
+        <v>705</v>
       </c>
       <c r="D48" s="5"/>
       <c r="E48" s="5" t="s">
-        <v>704</v>
+        <v>706</v>
       </c>
     </row>
     <row r="49" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -9637,14 +9831,14 @@
         <v>47</v>
       </c>
       <c r="B49" s="5" t="s">
-        <v>705</v>
+        <v>707</v>
       </c>
       <c r="C49" s="5" t="s">
-        <v>706</v>
+        <v>708</v>
       </c>
       <c r="D49" s="5"/>
       <c r="E49" s="5" t="s">
-        <v>707</v>
+        <v>709</v>
       </c>
     </row>
     <row r="50" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -9652,14 +9846,14 @@
         <v>48</v>
       </c>
       <c r="B50" s="5" t="s">
-        <v>708</v>
+        <v>710</v>
       </c>
       <c r="C50" s="5" t="s">
-        <v>709</v>
+        <v>711</v>
       </c>
       <c r="D50" s="5"/>
       <c r="E50" s="5" t="s">
-        <v>710</v>
+        <v>712</v>
       </c>
     </row>
     <row r="51" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -9667,14 +9861,14 @@
         <v>49</v>
       </c>
       <c r="B51" s="5" t="s">
-        <v>711</v>
+        <v>713</v>
       </c>
       <c r="C51" s="5" t="s">
-        <v>712</v>
+        <v>714</v>
       </c>
       <c r="D51" s="5"/>
       <c r="E51" s="5" t="s">
-        <v>713</v>
+        <v>715</v>
       </c>
     </row>
     <row r="52" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -9682,14 +9876,14 @@
         <v>50</v>
       </c>
       <c r="B52" s="5" t="s">
-        <v>714</v>
+        <v>716</v>
       </c>
       <c r="C52" s="5" t="s">
-        <v>715</v>
+        <v>717</v>
       </c>
       <c r="D52" s="5"/>
       <c r="E52" s="5" t="s">
-        <v>716</v>
+        <v>718</v>
       </c>
     </row>
     <row r="53" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -9697,14 +9891,14 @@
         <v>51</v>
       </c>
       <c r="B53" s="5" t="s">
-        <v>717</v>
+        <v>719</v>
       </c>
       <c r="C53" s="5" t="s">
-        <v>718</v>
+        <v>720</v>
       </c>
       <c r="D53" s="5"/>
       <c r="E53" s="5" t="s">
-        <v>719</v>
+        <v>721</v>
       </c>
     </row>
     <row r="54" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -9712,14 +9906,14 @@
         <v>52</v>
       </c>
       <c r="B54" s="5" t="s">
-        <v>619</v>
+        <v>621</v>
       </c>
       <c r="C54" s="5" t="s">
-        <v>720</v>
+        <v>722</v>
       </c>
       <c r="D54" s="5"/>
       <c r="E54" s="5" t="s">
-        <v>721</v>
+        <v>723</v>
       </c>
     </row>
     <row r="55" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -9727,14 +9921,14 @@
         <v>53</v>
       </c>
       <c r="B55" s="5" t="s">
-        <v>722</v>
+        <v>724</v>
       </c>
       <c r="C55" s="5" t="s">
-        <v>723</v>
+        <v>725</v>
       </c>
       <c r="D55" s="5"/>
       <c r="E55" s="5" t="s">
-        <v>724</v>
+        <v>726</v>
       </c>
     </row>
     <row r="56" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -9742,14 +9936,14 @@
         <v>54</v>
       </c>
       <c r="B56" s="5" t="s">
-        <v>725</v>
+        <v>727</v>
       </c>
       <c r="C56" s="5" t="s">
-        <v>726</v>
+        <v>728</v>
       </c>
       <c r="D56" s="5"/>
       <c r="E56" s="5" t="s">
-        <v>727</v>
+        <v>729</v>
       </c>
     </row>
     <row r="57" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -9757,14 +9951,14 @@
         <v>55</v>
       </c>
       <c r="B57" s="5" t="s">
-        <v>728</v>
+        <v>730</v>
       </c>
       <c r="C57" s="5" t="s">
-        <v>729</v>
+        <v>731</v>
       </c>
       <c r="D57" s="5"/>
       <c r="E57" s="5" t="s">
-        <v>730</v>
+        <v>732</v>
       </c>
     </row>
     <row r="58" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -9772,14 +9966,14 @@
         <v>56</v>
       </c>
       <c r="B58" s="5" t="s">
-        <v>731</v>
+        <v>733</v>
       </c>
       <c r="C58" s="5" t="s">
-        <v>732</v>
+        <v>734</v>
       </c>
       <c r="D58" s="5"/>
       <c r="E58" s="5" t="s">
-        <v>733</v>
+        <v>735</v>
       </c>
     </row>
     <row r="59" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -9787,14 +9981,14 @@
         <v>57</v>
       </c>
       <c r="B59" s="5" t="s">
-        <v>734</v>
+        <v>736</v>
       </c>
       <c r="C59" s="5" t="s">
-        <v>735</v>
+        <v>737</v>
       </c>
       <c r="D59" s="5"/>
       <c r="E59" s="5" t="s">
-        <v>736</v>
+        <v>738</v>
       </c>
     </row>
     <row r="60" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -9802,14 +9996,14 @@
         <v>58</v>
       </c>
       <c r="B60" s="5" t="s">
-        <v>737</v>
+        <v>739</v>
       </c>
       <c r="C60" s="5" t="s">
-        <v>738</v>
+        <v>740</v>
       </c>
       <c r="D60" s="5"/>
       <c r="E60" s="5" t="s">
-        <v>739</v>
+        <v>741</v>
       </c>
     </row>
     <row r="61" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -9817,14 +10011,14 @@
         <v>59</v>
       </c>
       <c r="B61" s="5" t="s">
-        <v>740</v>
+        <v>742</v>
       </c>
       <c r="C61" s="5" t="s">
-        <v>741</v>
+        <v>743</v>
       </c>
       <c r="D61" s="5"/>
       <c r="E61" s="5" t="s">
-        <v>742</v>
+        <v>744</v>
       </c>
     </row>
     <row r="62" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -9832,14 +10026,14 @@
         <v>60</v>
       </c>
       <c r="B62" s="5" t="s">
-        <v>743</v>
+        <v>745</v>
       </c>
       <c r="C62" s="5" t="s">
-        <v>744</v>
+        <v>746</v>
       </c>
       <c r="D62" s="5"/>
       <c r="E62" s="5" t="s">
-        <v>745</v>
+        <v>747</v>
       </c>
     </row>
     <row r="63" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -9847,14 +10041,14 @@
         <v>61</v>
       </c>
       <c r="B63" s="5" t="s">
-        <v>746</v>
+        <v>748</v>
       </c>
       <c r="C63" s="5" t="s">
-        <v>747</v>
+        <v>749</v>
       </c>
       <c r="D63" s="5"/>
       <c r="E63" s="5" t="s">
-        <v>748</v>
+        <v>750</v>
       </c>
     </row>
     <row r="64" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -9862,14 +10056,14 @@
         <v>62</v>
       </c>
       <c r="B64" s="5" t="s">
-        <v>749</v>
+        <v>751</v>
       </c>
       <c r="C64" s="5" t="s">
-        <v>750</v>
+        <v>752</v>
       </c>
       <c r="D64" s="5"/>
       <c r="E64" s="5" t="s">
-        <v>751</v>
+        <v>753</v>
       </c>
     </row>
     <row r="65" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -9877,14 +10071,14 @@
         <v>63</v>
       </c>
       <c r="B65" s="5" t="s">
-        <v>752</v>
+        <v>754</v>
       </c>
       <c r="C65" s="5" t="s">
-        <v>753</v>
+        <v>755</v>
       </c>
       <c r="D65" s="5"/>
       <c r="E65" s="5" t="s">
-        <v>754</v>
+        <v>756</v>
       </c>
     </row>
     <row r="66" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -9892,14 +10086,14 @@
         <v>64</v>
       </c>
       <c r="B66" s="5" t="s">
-        <v>755</v>
+        <v>757</v>
       </c>
       <c r="C66" s="5" t="s">
-        <v>756</v>
+        <v>758</v>
       </c>
       <c r="D66" s="5"/>
       <c r="E66" s="5" t="s">
-        <v>757</v>
+        <v>759</v>
       </c>
     </row>
     <row r="67" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -9907,14 +10101,14 @@
         <v>65</v>
       </c>
       <c r="B67" s="5" t="s">
-        <v>758</v>
+        <v>760</v>
       </c>
       <c r="C67" s="5" t="s">
-        <v>759</v>
+        <v>761</v>
       </c>
       <c r="D67" s="5"/>
       <c r="E67" s="5" t="s">
-        <v>760</v>
+        <v>762</v>
       </c>
     </row>
     <row r="68" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -9922,14 +10116,14 @@
         <v>66</v>
       </c>
       <c r="B68" s="5" t="s">
-        <v>761</v>
+        <v>763</v>
       </c>
       <c r="C68" s="5" t="s">
-        <v>762</v>
+        <v>764</v>
       </c>
       <c r="D68" s="5"/>
       <c r="E68" s="5" t="s">
-        <v>763</v>
+        <v>765</v>
       </c>
     </row>
     <row r="69" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -9937,14 +10131,14 @@
         <v>67</v>
       </c>
       <c r="B69" s="5" t="s">
-        <v>764</v>
+        <v>766</v>
       </c>
       <c r="C69" s="5" t="s">
-        <v>765</v>
+        <v>767</v>
       </c>
       <c r="D69" s="5"/>
       <c r="E69" s="5" t="s">
-        <v>766</v>
+        <v>768</v>
       </c>
     </row>
     <row r="70" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -9952,14 +10146,14 @@
         <v>68</v>
       </c>
       <c r="B70" s="5" t="s">
-        <v>767</v>
+        <v>769</v>
       </c>
       <c r="C70" s="5" t="s">
-        <v>768</v>
+        <v>770</v>
       </c>
       <c r="D70" s="5"/>
       <c r="E70" s="5" t="s">
-        <v>769</v>
+        <v>771</v>
       </c>
     </row>
     <row r="71" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -9967,14 +10161,14 @@
         <v>69</v>
       </c>
       <c r="B71" s="5" t="s">
-        <v>770</v>
+        <v>772</v>
       </c>
       <c r="C71" s="5" t="s">
-        <v>771</v>
+        <v>773</v>
       </c>
       <c r="D71" s="5"/>
       <c r="E71" s="5" t="s">
-        <v>772</v>
+        <v>774</v>
       </c>
     </row>
     <row r="72" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -9982,14 +10176,14 @@
         <v>70</v>
       </c>
       <c r="B72" s="5" t="s">
-        <v>773</v>
+        <v>775</v>
       </c>
       <c r="C72" s="5" t="s">
-        <v>774</v>
+        <v>776</v>
       </c>
       <c r="D72" s="5"/>
       <c r="E72" s="5" t="s">
-        <v>775</v>
+        <v>777</v>
       </c>
     </row>
     <row r="73" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -9997,14 +10191,14 @@
         <v>71</v>
       </c>
       <c r="B73" s="5" t="s">
-        <v>776</v>
+        <v>778</v>
       </c>
       <c r="C73" s="5" t="s">
-        <v>777</v>
+        <v>779</v>
       </c>
       <c r="D73" s="5"/>
       <c r="E73" s="5" t="s">
-        <v>778</v>
+        <v>780</v>
       </c>
     </row>
     <row r="74" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -10012,14 +10206,14 @@
         <v>72</v>
       </c>
       <c r="B74" s="5" t="s">
-        <v>779</v>
+        <v>781</v>
       </c>
       <c r="C74" s="5" t="s">
-        <v>780</v>
+        <v>782</v>
       </c>
       <c r="D74" s="5"/>
       <c r="E74" s="5" t="s">
-        <v>781</v>
+        <v>783</v>
       </c>
     </row>
     <row r="75" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -10027,14 +10221,14 @@
         <v>73</v>
       </c>
       <c r="B75" s="5" t="s">
-        <v>619</v>
+        <v>621</v>
       </c>
       <c r="C75" s="5" t="s">
-        <v>782</v>
+        <v>784</v>
       </c>
       <c r="D75" s="5"/>
       <c r="E75" s="5" t="s">
-        <v>783</v>
+        <v>785</v>
       </c>
     </row>
     <row r="76" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -10042,14 +10236,14 @@
         <v>74</v>
       </c>
       <c r="B76" s="5" t="s">
-        <v>784</v>
+        <v>786</v>
       </c>
       <c r="C76" s="5" t="s">
-        <v>785</v>
+        <v>787</v>
       </c>
       <c r="D76" s="5"/>
       <c r="E76" s="5" t="s">
-        <v>786</v>
+        <v>788</v>
       </c>
     </row>
     <row r="77" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -10057,14 +10251,14 @@
         <v>75</v>
       </c>
       <c r="B77" s="5" t="s">
-        <v>619</v>
+        <v>621</v>
       </c>
       <c r="C77" s="5" t="s">
-        <v>787</v>
+        <v>789</v>
       </c>
       <c r="D77" s="5"/>
       <c r="E77" s="5" t="s">
-        <v>788</v>
+        <v>790</v>
       </c>
     </row>
     <row r="78" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -10072,14 +10266,14 @@
         <v>76</v>
       </c>
       <c r="B78" s="5" t="s">
-        <v>789</v>
+        <v>791</v>
       </c>
       <c r="C78" s="5" t="s">
-        <v>790</v>
+        <v>792</v>
       </c>
       <c r="D78" s="5"/>
       <c r="E78" s="5" t="s">
-        <v>791</v>
+        <v>793</v>
       </c>
     </row>
     <row r="79" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -10087,14 +10281,14 @@
         <v>77</v>
       </c>
       <c r="B79" s="5" t="s">
-        <v>792</v>
+        <v>794</v>
       </c>
       <c r="C79" s="5" t="s">
-        <v>793</v>
+        <v>795</v>
       </c>
       <c r="D79" s="5"/>
       <c r="E79" s="5" t="s">
-        <v>794</v>
+        <v>796</v>
       </c>
     </row>
     <row r="80" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -10102,14 +10296,14 @@
         <v>78</v>
       </c>
       <c r="B80" s="5" t="s">
-        <v>717</v>
+        <v>719</v>
       </c>
       <c r="C80" s="5" t="s">
-        <v>795</v>
+        <v>797</v>
       </c>
       <c r="D80" s="5"/>
       <c r="E80" s="5" t="s">
-        <v>796</v>
+        <v>798</v>
       </c>
     </row>
     <row r="81" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -10117,14 +10311,14 @@
         <v>79</v>
       </c>
       <c r="B81" s="5" t="s">
-        <v>589</v>
+        <v>591</v>
       </c>
       <c r="C81" s="5" t="s">
-        <v>797</v>
+        <v>799</v>
       </c>
       <c r="D81" s="5"/>
       <c r="E81" s="5" t="s">
-        <v>798</v>
+        <v>800</v>
       </c>
     </row>
     <row r="82" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -10132,16 +10326,16 @@
         <v>80</v>
       </c>
       <c r="B82" s="5" t="s">
-        <v>799</v>
+        <v>801</v>
       </c>
       <c r="C82" s="5" t="s">
-        <v>800</v>
+        <v>802</v>
       </c>
       <c r="D82" s="6" t="s">
-        <v>801</v>
+        <v>803</v>
       </c>
       <c r="E82" s="5" t="s">
-        <v>802</v>
+        <v>804</v>
       </c>
     </row>
     <row r="83" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -10149,16 +10343,16 @@
         <v>81</v>
       </c>
       <c r="B83" s="5" t="s">
-        <v>803</v>
+        <v>805</v>
       </c>
       <c r="C83" s="5" t="s">
-        <v>804</v>
+        <v>806</v>
       </c>
       <c r="D83" s="6" t="s">
-        <v>805</v>
+        <v>807</v>
       </c>
       <c r="E83" s="5" t="s">
-        <v>806</v>
+        <v>808</v>
       </c>
     </row>
     <row r="84" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -10166,13 +10360,13 @@
         <v>82</v>
       </c>
       <c r="B84" s="5" t="s">
-        <v>807</v>
+        <v>809</v>
       </c>
       <c r="C84" s="5" t="s">
-        <v>808</v>
+        <v>810</v>
       </c>
       <c r="D84" s="6" t="s">
-        <v>809</v>
+        <v>811</v>
       </c>
       <c r="E84" s="5" t="s">
         <v>297</v>
@@ -10183,13 +10377,13 @@
         <v>83</v>
       </c>
       <c r="B85" s="5" t="s">
-        <v>810</v>
+        <v>812</v>
       </c>
       <c r="C85" s="5" t="s">
-        <v>811</v>
+        <v>813</v>
       </c>
       <c r="D85" s="6" t="s">
-        <v>812</v>
+        <v>814</v>
       </c>
       <c r="E85" s="5" t="s">
         <v>300</v>
@@ -10200,16 +10394,16 @@
         <v>84</v>
       </c>
       <c r="B86" s="5" t="s">
-        <v>813</v>
+        <v>815</v>
       </c>
       <c r="C86" s="5" t="s">
-        <v>814</v>
+        <v>816</v>
       </c>
       <c r="D86" s="6" t="s">
-        <v>815</v>
+        <v>817</v>
       </c>
       <c r="E86" s="5" t="s">
-        <v>816</v>
+        <v>818</v>
       </c>
     </row>
     <row r="87" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -10217,16 +10411,16 @@
         <v>85</v>
       </c>
       <c r="B87" s="5" t="s">
-        <v>817</v>
+        <v>819</v>
       </c>
       <c r="C87" s="5" t="s">
-        <v>818</v>
+        <v>820</v>
       </c>
       <c r="D87" s="6" t="s">
-        <v>819</v>
+        <v>821</v>
       </c>
       <c r="E87" s="5" t="s">
-        <v>820</v>
+        <v>822</v>
       </c>
     </row>
     <row r="88" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -10234,16 +10428,16 @@
         <v>86</v>
       </c>
       <c r="B88" s="5" t="s">
-        <v>821</v>
+        <v>823</v>
       </c>
       <c r="C88" s="5" t="s">
+        <v>824</v>
+      </c>
+      <c r="D88" s="6" t="s">
+        <v>825</v>
+      </c>
+      <c r="E88" s="5" t="s">
         <v>822</v>
-      </c>
-      <c r="D88" s="6" t="s">
-        <v>823</v>
-      </c>
-      <c r="E88" s="5" t="s">
-        <v>820</v>
       </c>
     </row>
     <row r="89" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -10251,16 +10445,16 @@
         <v>87</v>
       </c>
       <c r="B89" s="5" t="s">
-        <v>824</v>
+        <v>826</v>
       </c>
       <c r="C89" s="5" t="s">
-        <v>825</v>
+        <v>827</v>
       </c>
       <c r="D89" s="6" t="s">
-        <v>826</v>
+        <v>828</v>
       </c>
       <c r="E89" s="5" t="s">
-        <v>820</v>
+        <v>822</v>
       </c>
     </row>
     <row r="90" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -10268,16 +10462,16 @@
         <v>88</v>
       </c>
       <c r="B90" s="5" t="s">
-        <v>827</v>
+        <v>829</v>
       </c>
       <c r="C90" s="5" t="s">
-        <v>828</v>
+        <v>830</v>
       </c>
       <c r="D90" s="6" t="s">
-        <v>829</v>
+        <v>831</v>
       </c>
       <c r="E90" s="5" t="s">
-        <v>830</v>
+        <v>832</v>
       </c>
     </row>
     <row r="91" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -10285,16 +10479,16 @@
         <v>89</v>
       </c>
       <c r="B91" s="5" t="s">
-        <v>831</v>
+        <v>833</v>
       </c>
       <c r="C91" s="5" t="s">
+        <v>834</v>
+      </c>
+      <c r="D91" s="6" t="s">
+        <v>835</v>
+      </c>
+      <c r="E91" s="5" t="s">
         <v>832</v>
-      </c>
-      <c r="D91" s="6" t="s">
-        <v>833</v>
-      </c>
-      <c r="E91" s="5" t="s">
-        <v>830</v>
       </c>
     </row>
     <row r="92" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -10302,16 +10496,16 @@
         <v>90</v>
       </c>
       <c r="B92" s="5" t="s">
-        <v>821</v>
+        <v>823</v>
       </c>
       <c r="C92" s="5" t="s">
-        <v>834</v>
+        <v>836</v>
       </c>
       <c r="D92" s="6" t="s">
-        <v>835</v>
+        <v>837</v>
       </c>
       <c r="E92" s="5" t="s">
-        <v>836</v>
+        <v>838</v>
       </c>
     </row>
     <row r="93" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -10319,16 +10513,16 @@
         <v>91</v>
       </c>
       <c r="B93" s="5" t="s">
-        <v>837</v>
+        <v>839</v>
       </c>
       <c r="C93" s="5" t="s">
+        <v>840</v>
+      </c>
+      <c r="D93" s="6" t="s">
+        <v>841</v>
+      </c>
+      <c r="E93" s="5" t="s">
         <v>838</v>
-      </c>
-      <c r="D93" s="6" t="s">
-        <v>839</v>
-      </c>
-      <c r="E93" s="5" t="s">
-        <v>836</v>
       </c>
     </row>
     <row r="94" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -10336,16 +10530,16 @@
         <v>92</v>
       </c>
       <c r="B94" s="5" t="s">
-        <v>840</v>
+        <v>842</v>
       </c>
       <c r="C94" s="5" t="s">
-        <v>841</v>
+        <v>843</v>
       </c>
       <c r="D94" s="6" t="s">
-        <v>842</v>
+        <v>844</v>
       </c>
       <c r="E94" s="5" t="s">
-        <v>843</v>
+        <v>845</v>
       </c>
     </row>
     <row r="95" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -10353,16 +10547,16 @@
         <v>93</v>
       </c>
       <c r="B95" s="5" t="s">
-        <v>682</v>
+        <v>684</v>
       </c>
       <c r="C95" s="5" t="s">
-        <v>844</v>
+        <v>846</v>
       </c>
       <c r="D95" s="6" t="s">
-        <v>845</v>
+        <v>847</v>
       </c>
       <c r="E95" s="5" t="s">
-        <v>846</v>
+        <v>848</v>
       </c>
     </row>
     <row r="96" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -10370,16 +10564,16 @@
         <v>94</v>
       </c>
       <c r="B96" s="5" t="s">
-        <v>827</v>
+        <v>829</v>
       </c>
       <c r="C96" s="5" t="s">
-        <v>847</v>
+        <v>849</v>
       </c>
       <c r="D96" s="6" t="s">
+        <v>850</v>
+      </c>
+      <c r="E96" s="5" t="s">
         <v>848</v>
-      </c>
-      <c r="E96" s="5" t="s">
-        <v>846</v>
       </c>
     </row>
     <row r="97" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -10387,16 +10581,16 @@
         <v>95</v>
       </c>
       <c r="B97" s="5" t="s">
-        <v>849</v>
+        <v>851</v>
       </c>
       <c r="C97" s="5" t="s">
-        <v>850</v>
+        <v>852</v>
       </c>
       <c r="D97" s="6" t="s">
-        <v>851</v>
+        <v>853</v>
       </c>
       <c r="E97" s="5" t="s">
-        <v>846</v>
+        <v>848</v>
       </c>
     </row>
     <row r="98" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -10404,16 +10598,16 @@
         <v>96</v>
       </c>
       <c r="B98" s="5" t="s">
-        <v>807</v>
+        <v>809</v>
       </c>
       <c r="C98" s="5" t="s">
-        <v>852</v>
+        <v>854</v>
       </c>
       <c r="D98" s="6" t="s">
-        <v>853</v>
+        <v>855</v>
       </c>
       <c r="E98" s="5" t="s">
-        <v>836</v>
+        <v>838</v>
       </c>
     </row>
     <row r="99" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -10421,16 +10615,16 @@
         <v>97</v>
       </c>
       <c r="B99" s="5" t="s">
-        <v>854</v>
+        <v>856</v>
       </c>
       <c r="C99" s="5" t="s">
-        <v>855</v>
+        <v>857</v>
       </c>
       <c r="D99" s="6" t="s">
-        <v>856</v>
+        <v>858</v>
       </c>
       <c r="E99" s="5" t="s">
-        <v>857</v>
+        <v>859</v>
       </c>
     </row>
     <row r="100" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -10438,16 +10632,16 @@
         <v>98</v>
       </c>
       <c r="B100" s="5" t="s">
-        <v>821</v>
+        <v>823</v>
       </c>
       <c r="C100" s="5" t="s">
-        <v>858</v>
+        <v>860</v>
       </c>
       <c r="D100" s="6" t="s">
-        <v>859</v>
+        <v>861</v>
       </c>
       <c r="E100" s="5" t="s">
-        <v>860</v>
+        <v>862</v>
       </c>
     </row>
     <row r="101" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -10455,16 +10649,16 @@
         <v>99</v>
       </c>
       <c r="B101" s="5" t="s">
-        <v>827</v>
+        <v>829</v>
       </c>
       <c r="C101" s="5" t="s">
-        <v>861</v>
+        <v>863</v>
       </c>
       <c r="D101" s="6" t="s">
-        <v>862</v>
+        <v>864</v>
       </c>
       <c r="E101" s="5" t="s">
-        <v>863</v>
+        <v>865</v>
       </c>
     </row>
     <row r="102" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -10472,16 +10666,16 @@
         <v>100</v>
       </c>
       <c r="B102" s="5" t="s">
-        <v>864</v>
+        <v>866</v>
       </c>
       <c r="C102" s="5" t="s">
-        <v>865</v>
+        <v>867</v>
       </c>
       <c r="D102" s="6" t="s">
-        <v>866</v>
+        <v>868</v>
       </c>
       <c r="E102" s="5" t="s">
-        <v>867</v>
+        <v>869</v>
       </c>
     </row>
     <row r="103" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -10489,16 +10683,16 @@
         <v>101</v>
       </c>
       <c r="B103" s="5" t="s">
-        <v>807</v>
+        <v>809</v>
       </c>
       <c r="C103" s="5" t="s">
-        <v>868</v>
+        <v>870</v>
       </c>
       <c r="D103" s="6" t="s">
-        <v>869</v>
+        <v>871</v>
       </c>
       <c r="E103" s="5" t="s">
-        <v>870</v>
+        <v>872</v>
       </c>
     </row>
     <row r="104" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -10506,13 +10700,13 @@
         <v>102</v>
       </c>
       <c r="B104" s="5" t="s">
-        <v>682</v>
+        <v>684</v>
       </c>
       <c r="C104" s="5" t="s">
-        <v>871</v>
+        <v>873</v>
       </c>
       <c r="D104" s="6" t="s">
-        <v>872</v>
+        <v>874</v>
       </c>
       <c r="E104" s="5" t="s">
         <v>352</v>
@@ -10523,16 +10717,16 @@
         <v>103</v>
       </c>
       <c r="B105" s="5" t="s">
-        <v>873</v>
+        <v>875</v>
       </c>
       <c r="C105" s="5" t="s">
-        <v>874</v>
+        <v>876</v>
       </c>
       <c r="D105" s="6" t="s">
-        <v>875</v>
+        <v>877</v>
       </c>
       <c r="E105" s="5" t="s">
-        <v>876</v>
+        <v>878</v>
       </c>
     </row>
     <row r="106" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -10540,16 +10734,16 @@
         <v>104</v>
       </c>
       <c r="B106" s="5" t="s">
-        <v>877</v>
+        <v>879</v>
       </c>
       <c r="C106" s="5" t="s">
-        <v>878</v>
+        <v>880</v>
       </c>
       <c r="D106" s="6" t="s">
-        <v>879</v>
+        <v>881</v>
       </c>
       <c r="E106" s="5" t="s">
-        <v>880</v>
+        <v>882</v>
       </c>
     </row>
     <row r="107" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -10557,16 +10751,16 @@
         <v>105</v>
       </c>
       <c r="B107" s="5" t="s">
-        <v>881</v>
+        <v>883</v>
       </c>
       <c r="C107" s="5" t="s">
-        <v>882</v>
+        <v>884</v>
       </c>
       <c r="D107" s="6" t="s">
-        <v>883</v>
+        <v>885</v>
       </c>
       <c r="E107" s="5" t="s">
-        <v>884</v>
+        <v>886</v>
       </c>
     </row>
     <row r="108" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -10574,16 +10768,16 @@
         <v>106</v>
       </c>
       <c r="B108" s="5" t="s">
-        <v>877</v>
+        <v>879</v>
       </c>
       <c r="C108" s="5" t="s">
-        <v>885</v>
+        <v>887</v>
       </c>
       <c r="D108" s="6" t="s">
-        <v>886</v>
+        <v>888</v>
       </c>
       <c r="E108" s="5" t="s">
-        <v>887</v>
+        <v>889</v>
       </c>
     </row>
     <row r="109" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -10591,13 +10785,13 @@
         <v>107</v>
       </c>
       <c r="B109" s="5" t="s">
-        <v>888</v>
+        <v>890</v>
       </c>
       <c r="C109" s="5" t="s">
-        <v>889</v>
+        <v>891</v>
       </c>
       <c r="D109" s="6" t="s">
-        <v>890</v>
+        <v>892</v>
       </c>
       <c r="E109" s="5" t="s">
         <v>368</v>
@@ -10608,13 +10802,13 @@
         <v>108</v>
       </c>
       <c r="B110" s="5" t="s">
-        <v>682</v>
+        <v>684</v>
       </c>
       <c r="C110" s="5" t="s">
-        <v>891</v>
+        <v>893</v>
       </c>
       <c r="D110" s="6" t="s">
-        <v>892</v>
+        <v>894</v>
       </c>
       <c r="E110" s="5" t="s">
         <v>368</v>
@@ -10625,16 +10819,16 @@
         <v>109</v>
       </c>
       <c r="B111" s="5" t="s">
-        <v>881</v>
+        <v>883</v>
       </c>
       <c r="C111" s="5" t="s">
-        <v>893</v>
+        <v>895</v>
       </c>
       <c r="D111" s="6" t="s">
-        <v>894</v>
+        <v>896</v>
       </c>
       <c r="E111" s="5" t="s">
-        <v>895</v>
+        <v>897</v>
       </c>
     </row>
     <row r="112" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -10642,16 +10836,16 @@
         <v>110</v>
       </c>
       <c r="B112" s="5" t="s">
-        <v>821</v>
+        <v>823</v>
       </c>
       <c r="C112" s="5" t="s">
-        <v>896</v>
+        <v>898</v>
       </c>
       <c r="D112" s="6" t="s">
-        <v>897</v>
+        <v>899</v>
       </c>
       <c r="E112" s="5" t="s">
-        <v>898</v>
+        <v>900</v>
       </c>
     </row>
     <row r="113" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -10659,13 +10853,13 @@
         <v>111</v>
       </c>
       <c r="B113" s="5" t="s">
-        <v>813</v>
+        <v>815</v>
       </c>
       <c r="C113" s="5" t="s">
-        <v>899</v>
+        <v>901</v>
       </c>
       <c r="D113" s="6" t="s">
-        <v>900</v>
+        <v>902</v>
       </c>
       <c r="E113" s="5" t="s">
         <v>382</v>
@@ -10676,16 +10870,16 @@
         <v>112</v>
       </c>
       <c r="B114" s="5" t="s">
-        <v>821</v>
+        <v>823</v>
       </c>
       <c r="C114" s="5" t="s">
-        <v>901</v>
+        <v>903</v>
       </c>
       <c r="D114" s="6" t="s">
-        <v>902</v>
+        <v>904</v>
       </c>
       <c r="E114" s="5" t="s">
-        <v>903</v>
+        <v>905</v>
       </c>
     </row>
     <row r="115" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -10693,16 +10887,16 @@
         <v>113</v>
       </c>
       <c r="B115" s="5" t="s">
-        <v>904</v>
+        <v>906</v>
       </c>
       <c r="C115" s="5" t="s">
-        <v>905</v>
+        <v>907</v>
       </c>
       <c r="D115" s="6" t="s">
-        <v>906</v>
+        <v>908</v>
       </c>
       <c r="E115" s="5" t="s">
-        <v>907</v>
+        <v>909</v>
       </c>
     </row>
     <row r="116" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -10710,16 +10904,16 @@
         <v>114</v>
       </c>
       <c r="B116" s="5" t="s">
-        <v>827</v>
+        <v>829</v>
       </c>
       <c r="C116" s="5" t="s">
-        <v>908</v>
+        <v>910</v>
       </c>
       <c r="D116" s="6" t="s">
+        <v>911</v>
+      </c>
+      <c r="E116" s="5" t="s">
         <v>909</v>
-      </c>
-      <c r="E116" s="5" t="s">
-        <v>907</v>
       </c>
     </row>
     <row r="117" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -10727,16 +10921,16 @@
         <v>115</v>
       </c>
       <c r="B117" s="5" t="s">
-        <v>910</v>
+        <v>912</v>
       </c>
       <c r="C117" s="5" t="s">
-        <v>911</v>
+        <v>913</v>
       </c>
       <c r="D117" s="6" t="s">
-        <v>912</v>
+        <v>914</v>
       </c>
       <c r="E117" s="5" t="s">
-        <v>913</v>
+        <v>915</v>
       </c>
     </row>
     <row r="118" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -10744,13 +10938,13 @@
         <v>116</v>
       </c>
       <c r="B118" s="5" t="s">
-        <v>827</v>
+        <v>829</v>
       </c>
       <c r="C118" s="5" t="s">
-        <v>914</v>
+        <v>916</v>
       </c>
       <c r="D118" s="6" t="s">
-        <v>915</v>
+        <v>917</v>
       </c>
       <c r="E118" s="5" t="s">
         <v>396</v>
@@ -10761,16 +10955,16 @@
         <v>117</v>
       </c>
       <c r="B119" s="5" t="s">
-        <v>916</v>
+        <v>918</v>
       </c>
       <c r="C119" s="5" t="s">
-        <v>917</v>
+        <v>919</v>
       </c>
       <c r="D119" s="6" t="s">
-        <v>918</v>
+        <v>920</v>
       </c>
       <c r="E119" s="5" t="s">
-        <v>919</v>
+        <v>921</v>
       </c>
     </row>
     <row r="120" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -10778,16 +10972,16 @@
         <v>118</v>
       </c>
       <c r="B120" s="5" t="s">
-        <v>904</v>
+        <v>906</v>
       </c>
       <c r="C120" s="5" t="s">
-        <v>920</v>
+        <v>922</v>
       </c>
       <c r="D120" s="6" t="s">
-        <v>921</v>
+        <v>923</v>
       </c>
       <c r="E120" s="5" t="s">
-        <v>922</v>
+        <v>924</v>
       </c>
     </row>
     <row r="121" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -10795,16 +10989,16 @@
         <v>119</v>
       </c>
       <c r="B121" s="5" t="s">
-        <v>923</v>
+        <v>925</v>
       </c>
       <c r="C121" s="5" t="s">
-        <v>924</v>
+        <v>926</v>
       </c>
       <c r="D121" s="6" t="s">
-        <v>925</v>
+        <v>927</v>
       </c>
       <c r="E121" s="5" t="s">
-        <v>919</v>
+        <v>921</v>
       </c>
     </row>
     <row r="122" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -10812,16 +11006,16 @@
         <v>120</v>
       </c>
       <c r="B122" s="5" t="s">
-        <v>926</v>
+        <v>928</v>
       </c>
       <c r="C122" s="5" t="s">
-        <v>927</v>
+        <v>929</v>
       </c>
       <c r="D122" s="6" t="s">
-        <v>928</v>
+        <v>930</v>
       </c>
       <c r="E122" s="5" t="s">
-        <v>929</v>
+        <v>931</v>
       </c>
     </row>
     <row r="123" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -10829,13 +11023,13 @@
         <v>121</v>
       </c>
       <c r="B123" s="5" t="s">
-        <v>827</v>
+        <v>829</v>
       </c>
       <c r="C123" s="5" t="s">
-        <v>930</v>
+        <v>932</v>
       </c>
       <c r="D123" s="6" t="s">
-        <v>931</v>
+        <v>933</v>
       </c>
       <c r="E123" s="5" t="s">
         <v>409</v>
@@ -10846,13 +11040,13 @@
         <v>122</v>
       </c>
       <c r="B124" s="5" t="s">
-        <v>888</v>
+        <v>890</v>
       </c>
       <c r="C124" s="5" t="s">
-        <v>932</v>
+        <v>934</v>
       </c>
       <c r="D124" s="6" t="s">
-        <v>933</v>
+        <v>935</v>
       </c>
       <c r="E124" s="5" t="s">
         <v>409</v>
@@ -10863,16 +11057,16 @@
         <v>123</v>
       </c>
       <c r="B125" s="5" t="s">
-        <v>854</v>
+        <v>856</v>
       </c>
       <c r="C125" s="5" t="s">
-        <v>934</v>
+        <v>936</v>
       </c>
       <c r="D125" s="6" t="s">
-        <v>935</v>
+        <v>937</v>
       </c>
       <c r="E125" s="5" t="s">
-        <v>936</v>
+        <v>938</v>
       </c>
     </row>
     <row r="126" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -10880,16 +11074,16 @@
         <v>124</v>
       </c>
       <c r="B126" s="5" t="s">
-        <v>937</v>
+        <v>939</v>
       </c>
       <c r="C126" s="5" t="s">
+        <v>940</v>
+      </c>
+      <c r="D126" s="6" t="s">
+        <v>941</v>
+      </c>
+      <c r="E126" s="5" t="s">
         <v>938</v>
-      </c>
-      <c r="D126" s="6" t="s">
-        <v>939</v>
-      </c>
-      <c r="E126" s="5" t="s">
-        <v>936</v>
       </c>
     </row>
     <row r="127" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -10897,16 +11091,16 @@
         <v>125</v>
       </c>
       <c r="B127" s="5" t="s">
-        <v>873</v>
+        <v>875</v>
       </c>
       <c r="C127" s="5" t="s">
-        <v>940</v>
+        <v>942</v>
       </c>
       <c r="D127" s="6" t="s">
-        <v>941</v>
+        <v>943</v>
       </c>
       <c r="E127" s="5" t="s">
-        <v>942</v>
+        <v>944</v>
       </c>
     </row>
     <row r="128" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -10914,16 +11108,16 @@
         <v>126</v>
       </c>
       <c r="B128" s="5" t="s">
-        <v>943</v>
+        <v>945</v>
       </c>
       <c r="C128" s="5" t="s">
-        <v>944</v>
+        <v>946</v>
       </c>
       <c r="D128" s="6" t="s">
-        <v>945</v>
+        <v>947</v>
       </c>
       <c r="E128" s="5" t="s">
-        <v>946</v>
+        <v>948</v>
       </c>
     </row>
     <row r="129" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -10931,16 +11125,16 @@
         <v>127</v>
       </c>
       <c r="B129" s="5" t="s">
-        <v>947</v>
+        <v>949</v>
       </c>
       <c r="C129" s="5" t="s">
-        <v>948</v>
+        <v>950</v>
       </c>
       <c r="D129" s="6" t="s">
-        <v>949</v>
+        <v>951</v>
       </c>
       <c r="E129" s="5" t="s">
-        <v>950</v>
+        <v>952</v>
       </c>
     </row>
     <row r="130" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -10948,16 +11142,16 @@
         <v>128</v>
       </c>
       <c r="B130" s="5" t="s">
+        <v>953</v>
+      </c>
+      <c r="C130" s="5" t="s">
+        <v>954</v>
+      </c>
+      <c r="D130" s="6" t="s">
         <v>951</v>
       </c>
-      <c r="C130" s="5" t="s">
-        <v>952</v>
-      </c>
-      <c r="D130" s="6" t="s">
-        <v>949</v>
-      </c>
       <c r="E130" s="5" t="s">
-        <v>953</v>
+        <v>955</v>
       </c>
     </row>
     <row r="131" customFormat="false" ht="34.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -10965,13 +11159,13 @@
         <v>129</v>
       </c>
       <c r="B131" s="5" t="s">
-        <v>954</v>
+        <v>956</v>
       </c>
       <c r="C131" s="5" t="s">
-        <v>955</v>
+        <v>957</v>
       </c>
       <c r="D131" s="6" t="s">
-        <v>949</v>
+        <v>951</v>
       </c>
       <c r="E131" s="5" t="s">
         <v>434</v>
@@ -10982,16 +11176,16 @@
         <v>130</v>
       </c>
       <c r="B132" s="5" t="s">
-        <v>956</v>
+        <v>958</v>
       </c>
       <c r="C132" s="5" t="s">
-        <v>957</v>
+        <v>959</v>
       </c>
       <c r="D132" s="6" t="s">
-        <v>958</v>
+        <v>960</v>
       </c>
       <c r="E132" s="5" t="s">
-        <v>959</v>
+        <v>961</v>
       </c>
     </row>
     <row r="133" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -10999,16 +11193,16 @@
         <v>131</v>
       </c>
       <c r="B133" s="5" t="s">
-        <v>960</v>
+        <v>962</v>
       </c>
       <c r="C133" s="5" t="s">
+        <v>963</v>
+      </c>
+      <c r="D133" s="6" t="s">
+        <v>964</v>
+      </c>
+      <c r="E133" s="5" t="s">
         <v>961</v>
-      </c>
-      <c r="D133" s="6" t="s">
-        <v>962</v>
-      </c>
-      <c r="E133" s="5" t="s">
-        <v>959</v>
       </c>
     </row>
     <row r="134" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -11016,16 +11210,16 @@
         <v>132</v>
       </c>
       <c r="B134" s="5" t="s">
-        <v>963</v>
+        <v>965</v>
       </c>
       <c r="C134" s="5" t="s">
-        <v>964</v>
+        <v>966</v>
       </c>
       <c r="D134" s="6" t="s">
-        <v>965</v>
+        <v>967</v>
       </c>
       <c r="E134" s="5" t="s">
-        <v>966</v>
+        <v>968</v>
       </c>
     </row>
     <row r="135" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -11033,16 +11227,16 @@
         <v>133</v>
       </c>
       <c r="B135" s="5" t="s">
-        <v>967</v>
+        <v>969</v>
       </c>
       <c r="C135" s="5" t="s">
-        <v>968</v>
+        <v>970</v>
       </c>
       <c r="D135" s="6" t="s">
-        <v>969</v>
+        <v>971</v>
       </c>
       <c r="E135" s="5" t="s">
-        <v>970</v>
+        <v>972</v>
       </c>
     </row>
     <row r="136" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -11050,13 +11244,13 @@
         <v>134</v>
       </c>
       <c r="B136" s="5" t="s">
-        <v>682</v>
+        <v>684</v>
       </c>
       <c r="C136" s="5" t="s">
-        <v>971</v>
+        <v>973</v>
       </c>
       <c r="D136" s="6" t="s">
-        <v>972</v>
+        <v>974</v>
       </c>
       <c r="E136" s="5" t="s">
         <v>451</v>
@@ -11067,13 +11261,13 @@
         <v>135</v>
       </c>
       <c r="B137" s="5" t="s">
-        <v>973</v>
+        <v>975</v>
       </c>
       <c r="C137" s="5" t="s">
-        <v>974</v>
+        <v>976</v>
       </c>
       <c r="D137" s="6" t="s">
-        <v>975</v>
+        <v>977</v>
       </c>
       <c r="E137" s="5" t="s">
         <v>451</v>
@@ -11084,16 +11278,16 @@
         <v>136</v>
       </c>
       <c r="B138" s="5" t="s">
-        <v>976</v>
+        <v>978</v>
       </c>
       <c r="C138" s="5" t="s">
-        <v>977</v>
+        <v>979</v>
       </c>
       <c r="D138" s="6" t="s">
-        <v>978</v>
+        <v>980</v>
       </c>
       <c r="E138" s="5" t="s">
-        <v>979</v>
+        <v>981</v>
       </c>
     </row>
     <row r="139" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -11101,16 +11295,16 @@
         <v>137</v>
       </c>
       <c r="B139" s="5" t="s">
-        <v>980</v>
+        <v>982</v>
       </c>
       <c r="C139" s="5" t="s">
-        <v>981</v>
+        <v>983</v>
       </c>
       <c r="D139" s="6" t="s">
-        <v>982</v>
+        <v>984</v>
       </c>
       <c r="E139" s="5" t="s">
-        <v>983</v>
+        <v>985</v>
       </c>
     </row>
     <row r="140" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -11118,13 +11312,13 @@
         <v>138</v>
       </c>
       <c r="B140" s="5" t="s">
-        <v>849</v>
+        <v>851</v>
       </c>
       <c r="C140" s="5" t="s">
-        <v>984</v>
+        <v>986</v>
       </c>
       <c r="D140" s="6" t="s">
-        <v>985</v>
+        <v>987</v>
       </c>
       <c r="E140" s="5" t="s">
         <v>463</v>
@@ -11135,16 +11329,16 @@
         <v>139</v>
       </c>
       <c r="B141" s="5" t="s">
-        <v>854</v>
+        <v>856</v>
       </c>
       <c r="C141" s="5" t="s">
-        <v>986</v>
+        <v>988</v>
       </c>
       <c r="D141" s="6" t="s">
-        <v>987</v>
+        <v>989</v>
       </c>
       <c r="E141" s="5" t="s">
-        <v>988</v>
+        <v>990</v>
       </c>
     </row>
     <row r="142" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -11152,16 +11346,16 @@
         <v>140</v>
       </c>
       <c r="B142" s="5" t="s">
-        <v>989</v>
+        <v>991</v>
       </c>
       <c r="C142" s="5" t="s">
-        <v>990</v>
+        <v>992</v>
       </c>
       <c r="D142" s="6" t="s">
-        <v>991</v>
+        <v>993</v>
       </c>
       <c r="E142" s="5" t="s">
-        <v>992</v>
+        <v>994</v>
       </c>
     </row>
     <row r="143" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -11169,13 +11363,13 @@
         <v>141</v>
       </c>
       <c r="B143" s="5" t="s">
-        <v>821</v>
+        <v>823</v>
       </c>
       <c r="C143" s="5" t="s">
-        <v>993</v>
+        <v>995</v>
       </c>
       <c r="D143" s="6" t="s">
-        <v>994</v>
+        <v>996</v>
       </c>
       <c r="E143" s="5" t="s">
         <v>472</v>
@@ -11186,16 +11380,16 @@
         <v>142</v>
       </c>
       <c r="B144" s="5" t="s">
-        <v>995</v>
+        <v>997</v>
       </c>
       <c r="C144" s="5" t="s">
-        <v>996</v>
+        <v>998</v>
       </c>
       <c r="D144" s="6" t="s">
-        <v>997</v>
+        <v>999</v>
       </c>
       <c r="E144" s="5" t="s">
-        <v>998</v>
+        <v>1000</v>
       </c>
     </row>
     <row r="145" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -11203,13 +11397,13 @@
         <v>143</v>
       </c>
       <c r="B145" s="5" t="s">
-        <v>881</v>
+        <v>883</v>
       </c>
       <c r="C145" s="5" t="s">
-        <v>999</v>
+        <v>1001</v>
       </c>
       <c r="D145" s="6" t="s">
-        <v>1000</v>
+        <v>1002</v>
       </c>
       <c r="E145" s="5" t="s">
         <v>479</v>
@@ -11220,16 +11414,16 @@
         <v>144</v>
       </c>
       <c r="B146" s="5" t="s">
-        <v>821</v>
+        <v>823</v>
       </c>
       <c r="C146" s="5" t="s">
-        <v>1001</v>
+        <v>1003</v>
       </c>
       <c r="D146" s="6" t="s">
-        <v>1002</v>
+        <v>1004</v>
       </c>
       <c r="E146" s="5" t="s">
-        <v>1003</v>
+        <v>1005</v>
       </c>
     </row>
     <row r="147" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -11237,16 +11431,16 @@
         <v>145</v>
       </c>
       <c r="B147" s="5" t="s">
-        <v>1004</v>
+        <v>1006</v>
       </c>
       <c r="C147" s="5" t="s">
-        <v>1005</v>
+        <v>1007</v>
       </c>
       <c r="D147" s="6" t="s">
-        <v>1006</v>
+        <v>1008</v>
       </c>
       <c r="E147" s="5" t="s">
-        <v>1007</v>
+        <v>1009</v>
       </c>
     </row>
     <row r="148" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -11254,16 +11448,16 @@
         <v>146</v>
       </c>
       <c r="B148" s="5" t="s">
-        <v>1008</v>
+        <v>1010</v>
       </c>
       <c r="C148" s="5" t="s">
-        <v>1009</v>
+        <v>1011</v>
       </c>
       <c r="D148" s="6" t="s">
-        <v>1010</v>
+        <v>1012</v>
       </c>
       <c r="E148" s="5" t="s">
-        <v>1011</v>
+        <v>1013</v>
       </c>
     </row>
     <row r="149" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -11271,13 +11465,13 @@
         <v>147</v>
       </c>
       <c r="B149" s="5" t="s">
-        <v>1012</v>
+        <v>1014</v>
       </c>
       <c r="C149" s="5" t="s">
-        <v>1013</v>
+        <v>1015</v>
       </c>
       <c r="D149" s="6" t="s">
-        <v>945</v>
+        <v>947</v>
       </c>
       <c r="E149" s="5" t="s">
         <v>492</v>
@@ -11288,13 +11482,13 @@
         <v>148</v>
       </c>
       <c r="B150" s="5" t="s">
-        <v>1014</v>
+        <v>1016</v>
       </c>
       <c r="C150" s="5" t="s">
-        <v>1015</v>
+        <v>1017</v>
       </c>
       <c r="D150" s="6" t="s">
-        <v>949</v>
+        <v>951</v>
       </c>
       <c r="E150" s="5" t="s">
         <v>492</v>
@@ -11305,16 +11499,16 @@
         <v>149</v>
       </c>
       <c r="B151" s="5" t="s">
-        <v>1016</v>
+        <v>1018</v>
       </c>
       <c r="C151" s="5" t="s">
-        <v>1017</v>
+        <v>1019</v>
       </c>
       <c r="D151" s="6" t="s">
-        <v>1018</v>
+        <v>1020</v>
       </c>
       <c r="E151" s="5" t="s">
-        <v>1019</v>
+        <v>1021</v>
       </c>
     </row>
     <row r="152" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -11322,16 +11516,16 @@
         <v>150</v>
       </c>
       <c r="B152" s="5" t="s">
-        <v>1016</v>
+        <v>1018</v>
       </c>
       <c r="C152" s="5" t="s">
+        <v>1022</v>
+      </c>
+      <c r="D152" s="6" t="s">
         <v>1020</v>
       </c>
-      <c r="D152" s="6" t="s">
-        <v>1018</v>
-      </c>
       <c r="E152" s="5" t="s">
-        <v>1019</v>
+        <v>1021</v>
       </c>
     </row>
     <row r="153" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -11339,16 +11533,16 @@
         <v>151</v>
       </c>
       <c r="B153" s="5" t="s">
-        <v>1021</v>
+        <v>1023</v>
       </c>
       <c r="C153" s="5" t="s">
-        <v>1022</v>
+        <v>1024</v>
       </c>
       <c r="D153" s="6" t="s">
-        <v>1023</v>
+        <v>1025</v>
       </c>
       <c r="E153" s="5" t="s">
-        <v>1024</v>
+        <v>1026</v>
       </c>
     </row>
     <row r="154" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -11356,16 +11550,16 @@
         <v>152</v>
       </c>
       <c r="B154" s="5" t="s">
-        <v>1021</v>
+        <v>1023</v>
       </c>
       <c r="C154" s="5" t="s">
+        <v>1027</v>
+      </c>
+      <c r="D154" s="6" t="s">
         <v>1025</v>
       </c>
-      <c r="D154" s="6" t="s">
-        <v>1023</v>
-      </c>
       <c r="E154" s="5" t="s">
-        <v>1024</v>
+        <v>1026</v>
       </c>
     </row>
     <row r="155" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -11373,16 +11567,16 @@
         <v>153</v>
       </c>
       <c r="B155" s="5" t="s">
-        <v>1026</v>
+        <v>1028</v>
       </c>
       <c r="C155" s="5" t="s">
-        <v>1027</v>
+        <v>1029</v>
       </c>
       <c r="D155" s="6" t="s">
-        <v>1028</v>
+        <v>1030</v>
       </c>
       <c r="E155" s="5" t="s">
-        <v>1029</v>
+        <v>1031</v>
       </c>
     </row>
     <row r="156" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -11390,16 +11584,16 @@
         <v>154</v>
       </c>
       <c r="B156" s="5" t="s">
-        <v>854</v>
+        <v>856</v>
       </c>
       <c r="C156" s="5" t="s">
-        <v>1030</v>
+        <v>1032</v>
       </c>
       <c r="D156" s="6" t="s">
+        <v>1033</v>
+      </c>
+      <c r="E156" s="5" t="s">
         <v>1031</v>
-      </c>
-      <c r="E156" s="5" t="s">
-        <v>1029</v>
       </c>
     </row>
     <row r="157" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -11407,14 +11601,14 @@
         <v>155</v>
       </c>
       <c r="B157" s="5" t="s">
-        <v>1032</v>
+        <v>1034</v>
       </c>
       <c r="C157" s="5" t="s">
-        <v>1033</v>
+        <v>1035</v>
       </c>
       <c r="D157" s="5"/>
       <c r="E157" s="5" t="s">
-        <v>1034</v>
+        <v>1036</v>
       </c>
     </row>
     <row r="158" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -11422,16 +11616,16 @@
         <v>156</v>
       </c>
       <c r="B158" s="5" t="s">
-        <v>1035</v>
+        <v>1037</v>
       </c>
       <c r="C158" s="5" t="s">
+        <v>1038</v>
+      </c>
+      <c r="D158" s="6" t="s">
+        <v>1039</v>
+      </c>
+      <c r="E158" s="5" t="s">
         <v>1036</v>
-      </c>
-      <c r="D158" s="6" t="s">
-        <v>1037</v>
-      </c>
-      <c r="E158" s="5" t="s">
-        <v>1034</v>
       </c>
     </row>
     <row r="159" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -11439,16 +11633,16 @@
         <v>157</v>
       </c>
       <c r="B159" s="5" t="s">
-        <v>682</v>
+        <v>684</v>
       </c>
       <c r="C159" s="5" t="s">
-        <v>1038</v>
+        <v>1040</v>
       </c>
       <c r="D159" s="6" t="s">
-        <v>1039</v>
+        <v>1041</v>
       </c>
       <c r="E159" s="5" t="s">
-        <v>1040</v>
+        <v>1042</v>
       </c>
     </row>
     <row r="160" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -11456,16 +11650,16 @@
         <v>158</v>
       </c>
       <c r="B160" s="5" t="s">
-        <v>821</v>
+        <v>823</v>
       </c>
       <c r="C160" s="5" t="s">
-        <v>1041</v>
+        <v>1043</v>
       </c>
       <c r="D160" s="6" t="s">
+        <v>1044</v>
+      </c>
+      <c r="E160" s="5" t="s">
         <v>1042</v>
-      </c>
-      <c r="E160" s="5" t="s">
-        <v>1040</v>
       </c>
     </row>
     <row r="161" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -11473,16 +11667,16 @@
         <v>159</v>
       </c>
       <c r="B161" s="5" t="s">
-        <v>877</v>
+        <v>879</v>
       </c>
       <c r="C161" s="5" t="s">
-        <v>1043</v>
+        <v>1045</v>
       </c>
       <c r="D161" s="6" t="s">
-        <v>1044</v>
+        <v>1046</v>
       </c>
       <c r="E161" s="5" t="s">
-        <v>1040</v>
+        <v>1042</v>
       </c>
     </row>
     <row r="162" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -11490,16 +11684,16 @@
         <v>160</v>
       </c>
       <c r="B162" s="5" t="s">
-        <v>1045</v>
+        <v>1047</v>
       </c>
       <c r="C162" s="5" t="s">
-        <v>1046</v>
+        <v>1048</v>
       </c>
       <c r="D162" s="6" t="s">
-        <v>1047</v>
+        <v>1049</v>
       </c>
       <c r="E162" s="5" t="s">
-        <v>1040</v>
+        <v>1042</v>
       </c>
     </row>
     <row r="163" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -11507,16 +11701,16 @@
         <v>161</v>
       </c>
       <c r="B163" s="5" t="s">
-        <v>1045</v>
+        <v>1047</v>
       </c>
       <c r="C163" s="5" t="s">
-        <v>1048</v>
+        <v>1050</v>
       </c>
       <c r="D163" s="6" t="s">
-        <v>1049</v>
+        <v>1051</v>
       </c>
       <c r="E163" s="5" t="s">
-        <v>1040</v>
+        <v>1042</v>
       </c>
     </row>
     <row r="164" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -11524,16 +11718,16 @@
         <v>162</v>
       </c>
       <c r="B164" s="5" t="s">
-        <v>888</v>
+        <v>890</v>
       </c>
       <c r="C164" s="5" t="s">
-        <v>1050</v>
+        <v>1052</v>
       </c>
       <c r="D164" s="6" t="s">
-        <v>1051</v>
+        <v>1053</v>
       </c>
       <c r="E164" s="5" t="s">
-        <v>1052</v>
+        <v>1054</v>
       </c>
     </row>
     <row r="165" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -11541,16 +11735,16 @@
         <v>163</v>
       </c>
       <c r="B165" s="5" t="s">
-        <v>682</v>
+        <v>684</v>
       </c>
       <c r="C165" s="5" t="s">
-        <v>1053</v>
+        <v>1055</v>
       </c>
       <c r="D165" s="6" t="s">
+        <v>1056</v>
+      </c>
+      <c r="E165" s="5" t="s">
         <v>1054</v>
-      </c>
-      <c r="E165" s="5" t="s">
-        <v>1052</v>
       </c>
     </row>
     <row r="166" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -11558,13 +11752,13 @@
         <v>157</v>
       </c>
       <c r="B166" s="5" t="s">
-        <v>1045</v>
+        <v>1047</v>
       </c>
       <c r="C166" s="5" t="s">
-        <v>1055</v>
+        <v>1057</v>
       </c>
       <c r="D166" s="6" t="s">
-        <v>1056</v>
+        <v>1058</v>
       </c>
       <c r="E166" s="5" t="s">
         <v>521</v>
@@ -11575,16 +11769,16 @@
         <v>158</v>
       </c>
       <c r="B167" s="5" t="s">
-        <v>904</v>
+        <v>906</v>
       </c>
       <c r="C167" s="5" t="s">
-        <v>1057</v>
+        <v>1059</v>
       </c>
       <c r="D167" s="6" t="s">
-        <v>1058</v>
+        <v>1060</v>
       </c>
       <c r="E167" s="5" t="s">
-        <v>1059</v>
+        <v>1061</v>
       </c>
     </row>
     <row r="168" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -11592,13 +11786,13 @@
         <v>159</v>
       </c>
       <c r="B168" s="5" t="s">
-        <v>682</v>
+        <v>684</v>
       </c>
       <c r="C168" s="5" t="s">
-        <v>1060</v>
+        <v>1062</v>
       </c>
       <c r="D168" s="6" t="s">
-        <v>1061</v>
+        <v>1063</v>
       </c>
       <c r="E168" s="5" t="s">
         <v>524</v>
@@ -11609,16 +11803,16 @@
         <v>160</v>
       </c>
       <c r="B169" s="5" t="s">
-        <v>877</v>
+        <v>879</v>
       </c>
       <c r="C169" s="5" t="s">
-        <v>1062</v>
+        <v>1064</v>
       </c>
       <c r="D169" s="6" t="s">
-        <v>1063</v>
+        <v>1065</v>
       </c>
       <c r="E169" s="5" t="s">
-        <v>1064</v>
+        <v>1066</v>
       </c>
     </row>
     <row r="170" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -11626,16 +11820,16 @@
         <v>161</v>
       </c>
       <c r="B170" s="5" t="s">
-        <v>877</v>
+        <v>879</v>
       </c>
       <c r="C170" s="5" t="s">
-        <v>1065</v>
+        <v>1067</v>
       </c>
       <c r="D170" s="6" t="s">
+        <v>1068</v>
+      </c>
+      <c r="E170" s="5" t="s">
         <v>1066</v>
-      </c>
-      <c r="E170" s="5" t="s">
-        <v>1064</v>
       </c>
     </row>
     <row r="171" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -11643,16 +11837,16 @@
         <v>162</v>
       </c>
       <c r="B171" s="5" t="s">
-        <v>877</v>
+        <v>879</v>
       </c>
       <c r="C171" s="5" t="s">
-        <v>1067</v>
+        <v>1069</v>
       </c>
       <c r="D171" s="6" t="s">
-        <v>1068</v>
+        <v>1070</v>
       </c>
       <c r="E171" s="5" t="s">
-        <v>1064</v>
+        <v>1066</v>
       </c>
     </row>
     <row r="172" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -11660,16 +11854,16 @@
         <v>163</v>
       </c>
       <c r="B172" s="5" t="s">
-        <v>827</v>
+        <v>829</v>
       </c>
       <c r="C172" s="5" t="s">
-        <v>1069</v>
+        <v>1071</v>
       </c>
       <c r="D172" s="6" t="s">
-        <v>1070</v>
+        <v>1072</v>
       </c>
       <c r="E172" s="5" t="s">
-        <v>1071</v>
+        <v>1073</v>
       </c>
     </row>
     <row r="173" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -11677,16 +11871,16 @@
         <v>164</v>
       </c>
       <c r="B173" s="5" t="s">
-        <v>821</v>
+        <v>823</v>
       </c>
       <c r="C173" s="5" t="s">
-        <v>1072</v>
+        <v>1074</v>
       </c>
       <c r="D173" s="6" t="s">
-        <v>1073</v>
+        <v>1075</v>
       </c>
       <c r="E173" s="5" t="s">
-        <v>1074</v>
+        <v>1076</v>
       </c>
     </row>
     <row r="174" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -11694,16 +11888,16 @@
         <v>165</v>
       </c>
       <c r="B174" s="5" t="s">
-        <v>821</v>
+        <v>823</v>
       </c>
       <c r="C174" s="5" t="s">
-        <v>1075</v>
+        <v>1077</v>
       </c>
       <c r="D174" s="6" t="s">
+        <v>1078</v>
+      </c>
+      <c r="E174" s="5" t="s">
         <v>1076</v>
-      </c>
-      <c r="E174" s="5" t="s">
-        <v>1074</v>
       </c>
     </row>
     <row r="175" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -11711,16 +11905,16 @@
         <v>166</v>
       </c>
       <c r="B175" s="5" t="s">
-        <v>821</v>
+        <v>823</v>
       </c>
       <c r="C175" s="5" t="s">
-        <v>1077</v>
+        <v>1079</v>
       </c>
       <c r="D175" s="6" t="s">
-        <v>1078</v>
+        <v>1080</v>
       </c>
       <c r="E175" s="5" t="s">
-        <v>1074</v>
+        <v>1076</v>
       </c>
     </row>
     <row r="176" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -11728,16 +11922,16 @@
         <v>167</v>
       </c>
       <c r="B176" s="5" t="s">
-        <v>888</v>
+        <v>890</v>
       </c>
       <c r="C176" s="5" t="s">
-        <v>1079</v>
+        <v>1081</v>
       </c>
       <c r="D176" s="6" t="s">
-        <v>1080</v>
+        <v>1082</v>
       </c>
       <c r="E176" s="5" t="s">
-        <v>1081</v>
+        <v>1083</v>
       </c>
     </row>
     <row r="177" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -11745,16 +11939,16 @@
         <v>168</v>
       </c>
       <c r="B177" s="5" t="s">
-        <v>682</v>
+        <v>684</v>
       </c>
       <c r="C177" s="5" t="s">
-        <v>1082</v>
+        <v>1084</v>
       </c>
       <c r="D177" s="6" t="s">
+        <v>1085</v>
+      </c>
+      <c r="E177" s="5" t="s">
         <v>1083</v>
-      </c>
-      <c r="E177" s="5" t="s">
-        <v>1081</v>
       </c>
     </row>
     <row r="178" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -11762,16 +11956,16 @@
         <v>169</v>
       </c>
       <c r="B178" s="5" t="s">
-        <v>682</v>
+        <v>684</v>
       </c>
       <c r="C178" s="5" t="s">
-        <v>1084</v>
+        <v>1086</v>
       </c>
       <c r="D178" s="6" t="s">
-        <v>1085</v>
+        <v>1087</v>
       </c>
       <c r="E178" s="5" t="s">
-        <v>1081</v>
+        <v>1083</v>
       </c>
     </row>
     <row r="179" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -11779,16 +11973,16 @@
         <v>170</v>
       </c>
       <c r="B179" s="5" t="s">
-        <v>904</v>
+        <v>906</v>
       </c>
       <c r="C179" s="5" t="s">
-        <v>1086</v>
+        <v>1088</v>
       </c>
       <c r="D179" s="6" t="s">
-        <v>1087</v>
+        <v>1089</v>
       </c>
       <c r="E179" s="5" t="s">
-        <v>1081</v>
+        <v>1083</v>
       </c>
     </row>
     <row r="180" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -11796,16 +11990,16 @@
         <v>171</v>
       </c>
       <c r="B180" s="5" t="s">
-        <v>904</v>
+        <v>906</v>
       </c>
       <c r="C180" s="5" t="s">
-        <v>1088</v>
+        <v>1090</v>
       </c>
       <c r="D180" s="6" t="s">
-        <v>1089</v>
+        <v>1091</v>
       </c>
       <c r="E180" s="5" t="s">
-        <v>1081</v>
+        <v>1083</v>
       </c>
     </row>
     <row r="181" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -11813,16 +12007,16 @@
         <v>172</v>
       </c>
       <c r="B181" s="5" t="s">
-        <v>877</v>
+        <v>879</v>
       </c>
       <c r="C181" s="5" t="s">
-        <v>1090</v>
+        <v>1092</v>
       </c>
       <c r="D181" s="6" t="s">
-        <v>1091</v>
+        <v>1093</v>
       </c>
       <c r="E181" s="5" t="s">
-        <v>1092</v>
+        <v>1094</v>
       </c>
     </row>
     <row r="182" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -11830,16 +12024,16 @@
         <v>173</v>
       </c>
       <c r="B182" s="5" t="s">
-        <v>682</v>
+        <v>684</v>
       </c>
       <c r="C182" s="5" t="s">
-        <v>1093</v>
+        <v>1095</v>
       </c>
       <c r="D182" s="6" t="s">
-        <v>1094</v>
+        <v>1096</v>
       </c>
       <c r="E182" s="5" t="s">
-        <v>1095</v>
+        <v>1097</v>
       </c>
     </row>
     <row r="183" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -11847,16 +12041,16 @@
         <v>174</v>
       </c>
       <c r="B183" s="5" t="s">
-        <v>682</v>
+        <v>684</v>
       </c>
       <c r="C183" s="5" t="s">
-        <v>1096</v>
+        <v>1098</v>
       </c>
       <c r="D183" s="6" t="s">
+        <v>1099</v>
+      </c>
+      <c r="E183" s="5" t="s">
         <v>1097</v>
-      </c>
-      <c r="E183" s="5" t="s">
-        <v>1095</v>
       </c>
     </row>
     <row r="184" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -11864,16 +12058,16 @@
         <v>175</v>
       </c>
       <c r="B184" s="5" t="s">
-        <v>682</v>
+        <v>684</v>
       </c>
       <c r="C184" s="5" t="s">
-        <v>1098</v>
+        <v>1100</v>
       </c>
       <c r="D184" s="6" t="s">
-        <v>1099</v>
+        <v>1101</v>
       </c>
       <c r="E184" s="5" t="s">
-        <v>1095</v>
+        <v>1097</v>
       </c>
     </row>
     <row r="185" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -11881,16 +12075,16 @@
         <v>176</v>
       </c>
       <c r="B185" s="5" t="s">
-        <v>1045</v>
+        <v>1047</v>
       </c>
       <c r="C185" s="5" t="s">
-        <v>1100</v>
+        <v>1102</v>
       </c>
       <c r="D185" s="6" t="s">
-        <v>1101</v>
+        <v>1103</v>
       </c>
       <c r="E185" s="5" t="s">
-        <v>1095</v>
+        <v>1097</v>
       </c>
     </row>
     <row r="186" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -11898,16 +12092,16 @@
         <v>177</v>
       </c>
       <c r="B186" s="5" t="s">
-        <v>1045</v>
+        <v>1047</v>
       </c>
       <c r="C186" s="5" t="s">
-        <v>1102</v>
+        <v>1104</v>
       </c>
       <c r="D186" s="6" t="s">
-        <v>1103</v>
+        <v>1105</v>
       </c>
       <c r="E186" s="5" t="s">
-        <v>1095</v>
+        <v>1097</v>
       </c>
     </row>
     <row r="187" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -11915,16 +12109,16 @@
         <v>178</v>
       </c>
       <c r="B187" s="5" t="s">
-        <v>1045</v>
+        <v>1047</v>
       </c>
       <c r="C187" s="5" t="s">
-        <v>1104</v>
+        <v>1106</v>
       </c>
       <c r="D187" s="6" t="s">
-        <v>1105</v>
+        <v>1107</v>
       </c>
       <c r="E187" s="5" t="s">
-        <v>1095</v>
+        <v>1097</v>
       </c>
     </row>
     <row r="188" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -11932,16 +12126,16 @@
         <v>179</v>
       </c>
       <c r="B188" s="5" t="s">
-        <v>682</v>
+        <v>684</v>
       </c>
       <c r="C188" s="5" t="s">
-        <v>1106</v>
+        <v>1108</v>
       </c>
       <c r="D188" s="6" t="s">
-        <v>1107</v>
+        <v>1109</v>
       </c>
       <c r="E188" s="5" t="s">
-        <v>1108</v>
+        <v>1110</v>
       </c>
     </row>
     <row r="189" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -11949,16 +12143,16 @@
         <v>180</v>
       </c>
       <c r="B189" s="5" t="s">
-        <v>682</v>
+        <v>684</v>
       </c>
       <c r="C189" s="5" t="s">
-        <v>1109</v>
+        <v>1111</v>
       </c>
       <c r="D189" s="6" t="s">
+        <v>1112</v>
+      </c>
+      <c r="E189" s="5" t="s">
         <v>1110</v>
-      </c>
-      <c r="E189" s="5" t="s">
-        <v>1108</v>
       </c>
     </row>
     <row r="190" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -11966,16 +12160,16 @@
         <v>181</v>
       </c>
       <c r="B190" s="5" t="s">
-        <v>877</v>
+        <v>879</v>
       </c>
       <c r="C190" s="5" t="s">
-        <v>1111</v>
+        <v>1113</v>
       </c>
       <c r="D190" s="6" t="s">
-        <v>1112</v>
+        <v>1114</v>
       </c>
       <c r="E190" s="5" t="s">
-        <v>1108</v>
+        <v>1110</v>
       </c>
     </row>
     <row r="191" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -11983,16 +12177,16 @@
         <v>182</v>
       </c>
       <c r="B191" s="5" t="s">
-        <v>1045</v>
+        <v>1047</v>
       </c>
       <c r="C191" s="5" t="s">
-        <v>1113</v>
+        <v>1115</v>
       </c>
       <c r="D191" s="6" t="s">
-        <v>1114</v>
+        <v>1116</v>
       </c>
       <c r="E191" s="5" t="s">
-        <v>1108</v>
+        <v>1110</v>
       </c>
     </row>
     <row r="192" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -12000,16 +12194,16 @@
         <v>183</v>
       </c>
       <c r="B192" s="5" t="s">
-        <v>1045</v>
+        <v>1047</v>
       </c>
       <c r="C192" s="5" t="s">
-        <v>1115</v>
+        <v>1117</v>
       </c>
       <c r="D192" s="6" t="s">
-        <v>1116</v>
+        <v>1118</v>
       </c>
       <c r="E192" s="5" t="s">
-        <v>1108</v>
+        <v>1110</v>
       </c>
     </row>
     <row r="193" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -12017,13 +12211,13 @@
         <v>184</v>
       </c>
       <c r="B193" s="5" t="s">
-        <v>877</v>
+        <v>879</v>
       </c>
       <c r="C193" s="5" t="s">
-        <v>1117</v>
+        <v>1119</v>
       </c>
       <c r="D193" s="6" t="s">
-        <v>1118</v>
+        <v>1120</v>
       </c>
       <c r="E193" s="5" t="s">
         <v>533</v>
@@ -12034,16 +12228,16 @@
         <v>185</v>
       </c>
       <c r="B194" s="5" t="s">
-        <v>877</v>
+        <v>879</v>
       </c>
       <c r="C194" s="5" t="s">
-        <v>1119</v>
+        <v>1121</v>
       </c>
       <c r="D194" s="6" t="s">
-        <v>1120</v>
+        <v>1122</v>
       </c>
       <c r="E194" s="5" t="s">
-        <v>1121</v>
+        <v>1123</v>
       </c>
     </row>
     <row r="195" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -12051,16 +12245,16 @@
         <v>186</v>
       </c>
       <c r="B195" s="5" t="s">
-        <v>682</v>
+        <v>684</v>
       </c>
       <c r="C195" s="5" t="s">
-        <v>1122</v>
+        <v>1124</v>
       </c>
       <c r="D195" s="6" t="s">
-        <v>1123</v>
+        <v>1125</v>
       </c>
       <c r="E195" s="5" t="s">
-        <v>1124</v>
+        <v>1126</v>
       </c>
     </row>
     <row r="196" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -12068,16 +12262,16 @@
         <v>187</v>
       </c>
       <c r="B196" s="5" t="s">
-        <v>821</v>
+        <v>823</v>
       </c>
       <c r="C196" s="5" t="s">
-        <v>1125</v>
+        <v>1127</v>
       </c>
       <c r="D196" s="6" t="s">
+        <v>1128</v>
+      </c>
+      <c r="E196" s="5" t="s">
         <v>1126</v>
-      </c>
-      <c r="E196" s="5" t="s">
-        <v>1124</v>
       </c>
     </row>
     <row r="197" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -12085,16 +12279,16 @@
         <v>188</v>
       </c>
       <c r="B197" s="5" t="s">
-        <v>1045</v>
+        <v>1047</v>
       </c>
       <c r="C197" s="5" t="s">
-        <v>1127</v>
+        <v>1129</v>
       </c>
       <c r="D197" s="6" t="s">
-        <v>1128</v>
+        <v>1130</v>
       </c>
       <c r="E197" s="5" t="s">
-        <v>1124</v>
+        <v>1126</v>
       </c>
     </row>
     <row r="198" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -12102,16 +12296,16 @@
         <v>189</v>
       </c>
       <c r="B198" s="5" t="s">
-        <v>1045</v>
+        <v>1047</v>
       </c>
       <c r="C198" s="5" t="s">
-        <v>1129</v>
+        <v>1131</v>
       </c>
       <c r="D198" s="6" t="s">
-        <v>1130</v>
+        <v>1132</v>
       </c>
       <c r="E198" s="5" t="s">
-        <v>1124</v>
+        <v>1126</v>
       </c>
     </row>
     <row r="199" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -12119,16 +12313,16 @@
         <v>190</v>
       </c>
       <c r="B199" s="5" t="s">
-        <v>888</v>
+        <v>890</v>
       </c>
       <c r="C199" s="5" t="s">
-        <v>1131</v>
+        <v>1133</v>
       </c>
       <c r="D199" s="6" t="s">
-        <v>1132</v>
+        <v>1134</v>
       </c>
       <c r="E199" s="5" t="s">
-        <v>1133</v>
+        <v>1135</v>
       </c>
     </row>
     <row r="200" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -12136,16 +12330,16 @@
         <v>191</v>
       </c>
       <c r="B200" s="5" t="s">
-        <v>888</v>
+        <v>890</v>
       </c>
       <c r="C200" s="5" t="s">
-        <v>1134</v>
+        <v>1136</v>
       </c>
       <c r="D200" s="6" t="s">
+        <v>1137</v>
+      </c>
+      <c r="E200" s="5" t="s">
         <v>1135</v>
-      </c>
-      <c r="E200" s="5" t="s">
-        <v>1133</v>
       </c>
     </row>
     <row r="201" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -12153,16 +12347,16 @@
         <v>192</v>
       </c>
       <c r="B201" s="5" t="s">
-        <v>682</v>
+        <v>684</v>
       </c>
       <c r="C201" s="5" t="s">
-        <v>1136</v>
+        <v>1138</v>
       </c>
       <c r="D201" s="6" t="s">
-        <v>1137</v>
+        <v>1139</v>
       </c>
       <c r="E201" s="5" t="s">
-        <v>1133</v>
+        <v>1135</v>
       </c>
     </row>
     <row r="202" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -12170,16 +12364,16 @@
         <v>193</v>
       </c>
       <c r="B202" s="5" t="s">
-        <v>682</v>
+        <v>684</v>
       </c>
       <c r="C202" s="5" t="s">
-        <v>1138</v>
+        <v>1140</v>
       </c>
       <c r="D202" s="6" t="s">
-        <v>1139</v>
+        <v>1141</v>
       </c>
       <c r="E202" s="5" t="s">
-        <v>1140</v>
+        <v>1142</v>
       </c>
     </row>
     <row r="203" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -12187,16 +12381,16 @@
         <v>194</v>
       </c>
       <c r="B203" s="5" t="s">
-        <v>682</v>
+        <v>684</v>
       </c>
       <c r="C203" s="5" t="s">
-        <v>1141</v>
+        <v>1143</v>
       </c>
       <c r="D203" s="6" t="s">
+        <v>1144</v>
+      </c>
+      <c r="E203" s="5" t="s">
         <v>1142</v>
-      </c>
-      <c r="E203" s="5" t="s">
-        <v>1140</v>
       </c>
     </row>
     <row r="204" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -12204,16 +12398,16 @@
         <v>195</v>
       </c>
       <c r="B204" s="5" t="s">
-        <v>682</v>
+        <v>684</v>
       </c>
       <c r="C204" s="5" t="s">
-        <v>1143</v>
+        <v>1145</v>
       </c>
       <c r="D204" s="6" t="s">
-        <v>1144</v>
+        <v>1146</v>
       </c>
       <c r="E204" s="5" t="s">
-        <v>1145</v>
+        <v>1147</v>
       </c>
     </row>
     <row r="205" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -12221,13 +12415,13 @@
         <v>196</v>
       </c>
       <c r="B205" s="5" t="s">
-        <v>877</v>
+        <v>879</v>
       </c>
       <c r="C205" s="5" t="s">
-        <v>1146</v>
+        <v>1148</v>
       </c>
       <c r="D205" s="6" t="s">
-        <v>1147</v>
+        <v>1149</v>
       </c>
       <c r="E205" s="5" t="s">
         <v>540</v>
@@ -12238,16 +12432,16 @@
         <v>197</v>
       </c>
       <c r="B206" s="5" t="s">
-        <v>682</v>
+        <v>684</v>
       </c>
       <c r="C206" s="5" t="s">
-        <v>1148</v>
+        <v>1150</v>
       </c>
       <c r="D206" s="6" t="s">
-        <v>1149</v>
+        <v>1151</v>
       </c>
       <c r="E206" s="5" t="s">
-        <v>1150</v>
+        <v>1152</v>
       </c>
     </row>
     <row r="207" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -12255,16 +12449,16 @@
         <v>198</v>
       </c>
       <c r="B207" s="5" t="s">
-        <v>904</v>
+        <v>906</v>
       </c>
       <c r="C207" s="5" t="s">
-        <v>1151</v>
+        <v>1153</v>
       </c>
       <c r="D207" s="6" t="s">
+        <v>1154</v>
+      </c>
+      <c r="E207" s="5" t="s">
         <v>1152</v>
-      </c>
-      <c r="E207" s="5" t="s">
-        <v>1150</v>
       </c>
     </row>
     <row r="208" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -12272,16 +12466,16 @@
         <v>199</v>
       </c>
       <c r="B208" s="5" t="s">
-        <v>1045</v>
+        <v>1047</v>
       </c>
       <c r="C208" s="5" t="s">
-        <v>1153</v>
+        <v>1155</v>
       </c>
       <c r="D208" s="6" t="s">
-        <v>1154</v>
+        <v>1156</v>
       </c>
       <c r="E208" s="5" t="s">
-        <v>1150</v>
+        <v>1152</v>
       </c>
     </row>
     <row r="209" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -12289,16 +12483,16 @@
         <v>200</v>
       </c>
       <c r="B209" s="5" t="s">
-        <v>1045</v>
+        <v>1047</v>
       </c>
       <c r="C209" s="5" t="s">
-        <v>1155</v>
+        <v>1157</v>
       </c>
       <c r="D209" s="6" t="s">
-        <v>1156</v>
+        <v>1158</v>
       </c>
       <c r="E209" s="5" t="s">
-        <v>1150</v>
+        <v>1152</v>
       </c>
     </row>
     <row r="210" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -12306,16 +12500,16 @@
         <v>201</v>
       </c>
       <c r="B210" s="5" t="s">
-        <v>821</v>
+        <v>823</v>
       </c>
       <c r="C210" s="5" t="s">
-        <v>1157</v>
+        <v>1159</v>
       </c>
       <c r="D210" s="6" t="s">
-        <v>1158</v>
+        <v>1160</v>
       </c>
       <c r="E210" s="5" t="s">
-        <v>1159</v>
+        <v>1161</v>
       </c>
     </row>
     <row r="211" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -12323,16 +12517,16 @@
         <v>202</v>
       </c>
       <c r="B211" s="5" t="s">
-        <v>904</v>
+        <v>906</v>
       </c>
       <c r="C211" s="5" t="s">
-        <v>1160</v>
+        <v>1162</v>
       </c>
       <c r="D211" s="6" t="s">
+        <v>1163</v>
+      </c>
+      <c r="E211" s="5" t="s">
         <v>1161</v>
-      </c>
-      <c r="E211" s="5" t="s">
-        <v>1159</v>
       </c>
     </row>
     <row r="212" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -12340,16 +12534,16 @@
         <v>203</v>
       </c>
       <c r="B212" s="5" t="s">
-        <v>904</v>
+        <v>906</v>
       </c>
       <c r="C212" s="5" t="s">
-        <v>1162</v>
+        <v>1164</v>
       </c>
       <c r="D212" s="6" t="s">
-        <v>1163</v>
+        <v>1165</v>
       </c>
       <c r="E212" s="5" t="s">
-        <v>1159</v>
+        <v>1161</v>
       </c>
     </row>
     <row r="213" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -12357,16 +12551,16 @@
         <v>204</v>
       </c>
       <c r="B213" s="5" t="s">
-        <v>877</v>
+        <v>879</v>
       </c>
       <c r="C213" s="5" t="s">
-        <v>1164</v>
+        <v>1166</v>
       </c>
       <c r="D213" s="6" t="s">
-        <v>1165</v>
+        <v>1167</v>
       </c>
       <c r="E213" s="5" t="s">
-        <v>1059</v>
+        <v>1061</v>
       </c>
     </row>
     <row r="214" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -12374,16 +12568,16 @@
         <v>205</v>
       </c>
       <c r="B214" s="5" t="s">
-        <v>682</v>
+        <v>684</v>
       </c>
       <c r="C214" s="5" t="s">
-        <v>1166</v>
+        <v>1168</v>
       </c>
       <c r="D214" s="6" t="s">
-        <v>1167</v>
+        <v>1169</v>
       </c>
       <c r="E214" s="5" t="s">
-        <v>1168</v>
+        <v>1170</v>
       </c>
     </row>
     <row r="215" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -12391,16 +12585,16 @@
         <v>206</v>
       </c>
       <c r="B215" s="5" t="s">
-        <v>821</v>
+        <v>823</v>
       </c>
       <c r="C215" s="5" t="s">
-        <v>1169</v>
+        <v>1171</v>
       </c>
       <c r="D215" s="6" t="s">
-        <v>1170</v>
+        <v>1172</v>
       </c>
       <c r="E215" s="5" t="s">
-        <v>1171</v>
+        <v>1173</v>
       </c>
     </row>
     <row r="216" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -12408,16 +12602,16 @@
         <v>207</v>
       </c>
       <c r="B216" s="5" t="s">
-        <v>904</v>
+        <v>906</v>
       </c>
       <c r="C216" s="5" t="s">
-        <v>1172</v>
+        <v>1174</v>
       </c>
       <c r="D216" s="6" t="s">
+        <v>1175</v>
+      </c>
+      <c r="E216" s="5" t="s">
         <v>1173</v>
-      </c>
-      <c r="E216" s="5" t="s">
-        <v>1171</v>
       </c>
     </row>
     <row r="217" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -12425,16 +12619,16 @@
         <v>208</v>
       </c>
       <c r="B217" s="5" t="s">
-        <v>682</v>
+        <v>684</v>
       </c>
       <c r="C217" s="5" t="s">
-        <v>1174</v>
+        <v>1176</v>
       </c>
       <c r="D217" s="6" t="s">
-        <v>1175</v>
+        <v>1177</v>
       </c>
       <c r="E217" s="5" t="s">
-        <v>1176</v>
+        <v>1178</v>
       </c>
     </row>
     <row r="218" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -12442,16 +12636,16 @@
         <v>209</v>
       </c>
       <c r="B218" s="5" t="s">
-        <v>821</v>
+        <v>823</v>
       </c>
       <c r="C218" s="5" t="s">
-        <v>1177</v>
+        <v>1179</v>
       </c>
       <c r="D218" s="6" t="s">
+        <v>1180</v>
+      </c>
+      <c r="E218" s="5" t="s">
         <v>1178</v>
-      </c>
-      <c r="E218" s="5" t="s">
-        <v>1176</v>
       </c>
     </row>
     <row r="219" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -12459,16 +12653,16 @@
         <v>210</v>
       </c>
       <c r="B219" s="5" t="s">
-        <v>904</v>
+        <v>906</v>
       </c>
       <c r="C219" s="5" t="s">
-        <v>1179</v>
+        <v>1181</v>
       </c>
       <c r="D219" s="6" t="s">
-        <v>1180</v>
+        <v>1182</v>
       </c>
       <c r="E219" s="5" t="s">
-        <v>1176</v>
+        <v>1178</v>
       </c>
     </row>
     <row r="220" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -12476,16 +12670,16 @@
         <v>211</v>
       </c>
       <c r="B220" s="5" t="s">
-        <v>1045</v>
+        <v>1047</v>
       </c>
       <c r="C220" s="5" t="s">
-        <v>1181</v>
+        <v>1183</v>
       </c>
       <c r="D220" s="6" t="s">
-        <v>1182</v>
+        <v>1184</v>
       </c>
       <c r="E220" s="5" t="s">
-        <v>1176</v>
+        <v>1178</v>
       </c>
     </row>
     <row r="221" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -12493,16 +12687,16 @@
         <v>212</v>
       </c>
       <c r="B221" s="5" t="s">
-        <v>877</v>
+        <v>879</v>
       </c>
       <c r="C221" s="5" t="s">
-        <v>1183</v>
+        <v>1185</v>
       </c>
       <c r="D221" s="6" t="s">
-        <v>1184</v>
+        <v>1186</v>
       </c>
       <c r="E221" s="5" t="s">
-        <v>1185</v>
+        <v>1187</v>
       </c>
     </row>
     <row r="222" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -12510,16 +12704,16 @@
         <v>213</v>
       </c>
       <c r="B222" s="5" t="s">
-        <v>682</v>
+        <v>684</v>
       </c>
       <c r="C222" s="5" t="s">
-        <v>1186</v>
+        <v>1188</v>
       </c>
       <c r="D222" s="6" t="s">
-        <v>1187</v>
+        <v>1189</v>
       </c>
       <c r="E222" s="5" t="s">
-        <v>1188</v>
+        <v>1190</v>
       </c>
     </row>
     <row r="223" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -12527,16 +12721,16 @@
         <v>214</v>
       </c>
       <c r="B223" s="5" t="s">
-        <v>877</v>
+        <v>879</v>
       </c>
       <c r="C223" s="5" t="s">
-        <v>1189</v>
+        <v>1191</v>
       </c>
       <c r="D223" s="6" t="s">
+        <v>1192</v>
+      </c>
+      <c r="E223" s="5" t="s">
         <v>1190</v>
-      </c>
-      <c r="E223" s="5" t="s">
-        <v>1188</v>
       </c>
     </row>
     <row r="224" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -12544,16 +12738,16 @@
         <v>215</v>
       </c>
       <c r="B224" s="5" t="s">
-        <v>877</v>
+        <v>879</v>
       </c>
       <c r="C224" s="5" t="s">
-        <v>1191</v>
+        <v>1193</v>
       </c>
       <c r="D224" s="6" t="s">
-        <v>1192</v>
+        <v>1194</v>
       </c>
       <c r="E224" s="5" t="s">
-        <v>1188</v>
+        <v>1190</v>
       </c>
     </row>
     <row r="225" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -12561,16 +12755,16 @@
         <v>216</v>
       </c>
       <c r="B225" s="5" t="s">
-        <v>1045</v>
+        <v>1047</v>
       </c>
       <c r="C225" s="5" t="s">
-        <v>1193</v>
+        <v>1195</v>
       </c>
       <c r="D225" s="6" t="s">
-        <v>1194</v>
+        <v>1196</v>
       </c>
       <c r="E225" s="5" t="s">
-        <v>1188</v>
+        <v>1190</v>
       </c>
     </row>
     <row r="226" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -12578,16 +12772,16 @@
         <v>217</v>
       </c>
       <c r="B226" s="5" t="s">
-        <v>888</v>
+        <v>890</v>
       </c>
       <c r="C226" s="5" t="s">
-        <v>1195</v>
+        <v>1197</v>
       </c>
       <c r="D226" s="6" t="s">
-        <v>1196</v>
+        <v>1198</v>
       </c>
       <c r="E226" s="5" t="s">
-        <v>1197</v>
+        <v>1199</v>
       </c>
     </row>
     <row r="227" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -12595,16 +12789,16 @@
         <v>218</v>
       </c>
       <c r="B227" s="5" t="s">
-        <v>682</v>
+        <v>684</v>
       </c>
       <c r="C227" s="5" t="s">
-        <v>1198</v>
+        <v>1200</v>
       </c>
       <c r="D227" s="6" t="s">
+        <v>1201</v>
+      </c>
+      <c r="E227" s="5" t="s">
         <v>1199</v>
-      </c>
-      <c r="E227" s="5" t="s">
-        <v>1197</v>
       </c>
     </row>
     <row r="228" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -12612,16 +12806,16 @@
         <v>219</v>
       </c>
       <c r="B228" s="5" t="s">
-        <v>821</v>
+        <v>823</v>
       </c>
       <c r="C228" s="5" t="s">
-        <v>1200</v>
+        <v>1202</v>
       </c>
       <c r="D228" s="6" t="s">
-        <v>1201</v>
+        <v>1203</v>
       </c>
       <c r="E228" s="5" t="s">
-        <v>1197</v>
+        <v>1199</v>
       </c>
     </row>
     <row r="229" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -12629,16 +12823,16 @@
         <v>220</v>
       </c>
       <c r="B229" s="5" t="s">
-        <v>1045</v>
+        <v>1047</v>
       </c>
       <c r="C229" s="5" t="s">
-        <v>1202</v>
+        <v>1204</v>
       </c>
       <c r="D229" s="6" t="s">
-        <v>1203</v>
+        <v>1205</v>
       </c>
       <c r="E229" s="5" t="s">
-        <v>1197</v>
+        <v>1199</v>
       </c>
     </row>
     <row r="230" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -12646,16 +12840,16 @@
         <v>221</v>
       </c>
       <c r="B230" s="5" t="s">
-        <v>682</v>
+        <v>684</v>
       </c>
       <c r="C230" s="5" t="s">
-        <v>1204</v>
+        <v>1206</v>
       </c>
       <c r="D230" s="6" t="s">
-        <v>1205</v>
+        <v>1207</v>
       </c>
       <c r="E230" s="5" t="s">
-        <v>1206</v>
+        <v>1208</v>
       </c>
     </row>
     <row r="231" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -12663,16 +12857,16 @@
         <v>222</v>
       </c>
       <c r="B231" s="5" t="s">
-        <v>877</v>
+        <v>879</v>
       </c>
       <c r="C231" s="5" t="s">
-        <v>1207</v>
+        <v>1209</v>
       </c>
       <c r="D231" s="6" t="s">
+        <v>1210</v>
+      </c>
+      <c r="E231" s="5" t="s">
         <v>1208</v>
-      </c>
-      <c r="E231" s="5" t="s">
-        <v>1206</v>
       </c>
     </row>
     <row r="232" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -12680,16 +12874,16 @@
         <v>223</v>
       </c>
       <c r="B232" s="5" t="s">
-        <v>682</v>
+        <v>684</v>
       </c>
       <c r="C232" s="5" t="s">
-        <v>1209</v>
+        <v>1211</v>
       </c>
       <c r="D232" s="6" t="s">
-        <v>1210</v>
+        <v>1212</v>
       </c>
       <c r="E232" s="5" t="s">
-        <v>1211</v>
+        <v>1213</v>
       </c>
     </row>
     <row r="233" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -12697,16 +12891,16 @@
         <v>224</v>
       </c>
       <c r="B233" s="5" t="s">
-        <v>904</v>
+        <v>906</v>
       </c>
       <c r="C233" s="5" t="s">
-        <v>1212</v>
+        <v>1214</v>
       </c>
       <c r="D233" s="6" t="s">
+        <v>1215</v>
+      </c>
+      <c r="E233" s="5" t="s">
         <v>1213</v>
-      </c>
-      <c r="E233" s="5" t="s">
-        <v>1211</v>
       </c>
     </row>
     <row r="234" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -12714,16 +12908,16 @@
         <v>225</v>
       </c>
       <c r="B234" s="5" t="s">
-        <v>682</v>
+        <v>684</v>
       </c>
       <c r="C234" s="5" t="s">
-        <v>1214</v>
+        <v>1216</v>
       </c>
       <c r="D234" s="6" t="s">
-        <v>1215</v>
+        <v>1217</v>
       </c>
       <c r="E234" s="5" t="s">
-        <v>1216</v>
+        <v>1218</v>
       </c>
     </row>
     <row r="235" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -12731,16 +12925,16 @@
         <v>226</v>
       </c>
       <c r="B235" s="5" t="s">
-        <v>821</v>
+        <v>823</v>
       </c>
       <c r="C235" s="5" t="s">
-        <v>1217</v>
+        <v>1219</v>
       </c>
       <c r="D235" s="6" t="s">
+        <v>1220</v>
+      </c>
+      <c r="E235" s="5" t="s">
         <v>1218</v>
-      </c>
-      <c r="E235" s="5" t="s">
-        <v>1216</v>
       </c>
     </row>
     <row r="236" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -12748,16 +12942,16 @@
         <v>227</v>
       </c>
       <c r="B236" s="5" t="s">
-        <v>904</v>
+        <v>906</v>
       </c>
       <c r="C236" s="5" t="s">
-        <v>1219</v>
+        <v>1221</v>
       </c>
       <c r="D236" s="6" t="s">
-        <v>1220</v>
+        <v>1222</v>
       </c>
       <c r="E236" s="5" t="s">
-        <v>1216</v>
+        <v>1218</v>
       </c>
     </row>
     <row r="237" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -12765,16 +12959,16 @@
         <v>228</v>
       </c>
       <c r="B237" s="5" t="s">
-        <v>904</v>
+        <v>906</v>
       </c>
       <c r="C237" s="5" t="s">
-        <v>1221</v>
+        <v>1223</v>
       </c>
       <c r="D237" s="6" t="s">
-        <v>1222</v>
+        <v>1224</v>
       </c>
       <c r="E237" s="5" t="s">
-        <v>1223</v>
+        <v>1225</v>
       </c>
     </row>
     <row r="238" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -12782,16 +12976,16 @@
         <v>229</v>
       </c>
       <c r="B238" s="5" t="s">
-        <v>877</v>
+        <v>879</v>
       </c>
       <c r="C238" s="5" t="s">
-        <v>1224</v>
+        <v>1226</v>
       </c>
       <c r="D238" s="6" t="s">
+        <v>1227</v>
+      </c>
+      <c r="E238" s="5" t="s">
         <v>1225</v>
-      </c>
-      <c r="E238" s="5" t="s">
-        <v>1223</v>
       </c>
     </row>
     <row r="239" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -12799,16 +12993,16 @@
         <v>230</v>
       </c>
       <c r="B239" s="5" t="s">
-        <v>877</v>
+        <v>879</v>
       </c>
       <c r="C239" s="5" t="s">
-        <v>1226</v>
+        <v>1228</v>
       </c>
       <c r="D239" s="6" t="s">
-        <v>1227</v>
+        <v>1229</v>
       </c>
       <c r="E239" s="5" t="s">
-        <v>1223</v>
+        <v>1225</v>
       </c>
     </row>
     <row r="240" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -12816,16 +13010,16 @@
         <v>231</v>
       </c>
       <c r="B240" s="5" t="s">
-        <v>1045</v>
+        <v>1047</v>
       </c>
       <c r="C240" s="5" t="s">
-        <v>1228</v>
+        <v>1230</v>
       </c>
       <c r="D240" s="6" t="s">
-        <v>1229</v>
+        <v>1231</v>
       </c>
       <c r="E240" s="5" t="s">
-        <v>1223</v>
+        <v>1225</v>
       </c>
     </row>
     <row r="241" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -12833,16 +13027,16 @@
         <v>232</v>
       </c>
       <c r="B241" s="5" t="s">
-        <v>1045</v>
+        <v>1047</v>
       </c>
       <c r="C241" s="5" t="s">
-        <v>1230</v>
+        <v>1232</v>
       </c>
       <c r="D241" s="6" t="s">
-        <v>1231</v>
+        <v>1233</v>
       </c>
       <c r="E241" s="5" t="s">
-        <v>1223</v>
+        <v>1225</v>
       </c>
     </row>
     <row r="242" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -12850,13 +13044,13 @@
         <v>233</v>
       </c>
       <c r="B242" s="5" t="s">
-        <v>877</v>
+        <v>879</v>
       </c>
       <c r="C242" s="5" t="s">
-        <v>1232</v>
+        <v>1234</v>
       </c>
       <c r="D242" s="6" t="s">
-        <v>1233</v>
+        <v>1235</v>
       </c>
       <c r="E242" s="5" t="s">
         <v>559</v>
@@ -12867,16 +13061,16 @@
         <v>234</v>
       </c>
       <c r="B243" s="5" t="s">
-        <v>888</v>
+        <v>890</v>
       </c>
       <c r="C243" s="5" t="s">
-        <v>1234</v>
+        <v>1236</v>
       </c>
       <c r="D243" s="6" t="s">
-        <v>1235</v>
+        <v>1237</v>
       </c>
       <c r="E243" s="5" t="s">
-        <v>1236</v>
+        <v>1238</v>
       </c>
     </row>
     <row r="244" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -12884,16 +13078,16 @@
         <v>235</v>
       </c>
       <c r="B244" s="5" t="s">
-        <v>682</v>
+        <v>684</v>
       </c>
       <c r="C244" s="5" t="s">
-        <v>1237</v>
+        <v>1239</v>
       </c>
       <c r="D244" s="6" t="s">
+        <v>1240</v>
+      </c>
+      <c r="E244" s="5" t="s">
         <v>1238</v>
-      </c>
-      <c r="E244" s="5" t="s">
-        <v>1236</v>
       </c>
     </row>
     <row r="245" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -12901,16 +13095,16 @@
         <v>236</v>
       </c>
       <c r="B245" s="5" t="s">
-        <v>682</v>
+        <v>684</v>
       </c>
       <c r="C245" s="5" t="s">
-        <v>1239</v>
+        <v>1241</v>
       </c>
       <c r="D245" s="6" t="s">
-        <v>1240</v>
+        <v>1242</v>
       </c>
       <c r="E245" s="5" t="s">
-        <v>1236</v>
+        <v>1238</v>
       </c>
     </row>
     <row r="246" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -12918,16 +13112,16 @@
         <v>237</v>
       </c>
       <c r="B246" s="5" t="s">
-        <v>877</v>
+        <v>879</v>
       </c>
       <c r="C246" s="5" t="s">
-        <v>1241</v>
+        <v>1243</v>
       </c>
       <c r="D246" s="6" t="s">
-        <v>1242</v>
+        <v>1244</v>
       </c>
       <c r="E246" s="5" t="s">
-        <v>1236</v>
+        <v>1238</v>
       </c>
     </row>
     <row r="247" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -12935,13 +13129,13 @@
         <v>238</v>
       </c>
       <c r="B247" s="5" t="s">
-        <v>821</v>
+        <v>823</v>
       </c>
       <c r="C247" s="5" t="s">
-        <v>1243</v>
+        <v>1245</v>
       </c>
       <c r="D247" s="6" t="s">
-        <v>1244</v>
+        <v>1246</v>
       </c>
       <c r="E247" s="5" t="s">
         <v>562</v>
@@ -12952,16 +13146,16 @@
         <v>239</v>
       </c>
       <c r="B248" s="5" t="s">
-        <v>682</v>
+        <v>684</v>
       </c>
       <c r="C248" s="5" t="s">
-        <v>1245</v>
+        <v>1247</v>
       </c>
       <c r="D248" s="6" t="s">
-        <v>1246</v>
+        <v>1248</v>
       </c>
       <c r="E248" s="5" t="s">
-        <v>1247</v>
+        <v>1249</v>
       </c>
     </row>
     <row r="249" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -12969,16 +13163,16 @@
         <v>240</v>
       </c>
       <c r="B249" s="5" t="s">
-        <v>821</v>
+        <v>823</v>
       </c>
       <c r="C249" s="5" t="s">
-        <v>1248</v>
+        <v>1250</v>
       </c>
       <c r="D249" s="6" t="s">
+        <v>1251</v>
+      </c>
+      <c r="E249" s="5" t="s">
         <v>1249</v>
-      </c>
-      <c r="E249" s="5" t="s">
-        <v>1247</v>
       </c>
     </row>
     <row r="250" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -12986,169 +13180,305 @@
         <v>241</v>
       </c>
       <c r="B250" s="5" t="s">
-        <v>807</v>
+        <v>809</v>
       </c>
       <c r="C250" s="5" t="s">
-        <v>1250</v>
+        <v>1252</v>
       </c>
       <c r="D250" s="6" t="s">
-        <v>1251</v>
+        <v>1253</v>
       </c>
       <c r="E250" s="5" t="s">
-        <v>1252</v>
-      </c>
-    </row>
-    <row r="251" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+        <v>1254</v>
+      </c>
+    </row>
+    <row r="251" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A251" s="5" t="n">
         <v>242</v>
       </c>
       <c r="B251" s="5" t="s">
-        <v>821</v>
+        <v>823</v>
       </c>
       <c r="C251" s="5" t="s">
-        <v>1253</v>
+        <v>1255</v>
       </c>
       <c r="D251" s="6" t="s">
-        <v>1254</v>
+        <v>1256</v>
       </c>
       <c r="E251" s="5" t="s">
-        <v>1255</v>
-      </c>
-    </row>
-    <row r="252" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+        <v>1257</v>
+      </c>
+    </row>
+    <row r="252" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A252" s="5" t="n">
         <v>243</v>
       </c>
       <c r="B252" s="5" t="s">
-        <v>1256</v>
+        <v>1258</v>
       </c>
       <c r="C252" s="5" t="s">
-        <v>1257</v>
+        <v>1259</v>
       </c>
       <c r="D252" s="6" t="s">
-        <v>1258</v>
+        <v>1260</v>
       </c>
       <c r="E252" s="5" t="s">
-        <v>1259</v>
-      </c>
-    </row>
-    <row r="253" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+        <v>1261</v>
+      </c>
+    </row>
+    <row r="253" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A253" s="5" t="n">
         <v>244</v>
       </c>
       <c r="B253" s="5" t="s">
-        <v>1260</v>
+        <v>1262</v>
       </c>
       <c r="C253" s="5" t="s">
-        <v>1261</v>
+        <v>1263</v>
       </c>
       <c r="D253" s="6" t="s">
-        <v>1262</v>
+        <v>1264</v>
       </c>
       <c r="E253" s="5" t="s">
-        <v>1247</v>
-      </c>
-    </row>
-    <row r="254" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+        <v>1249</v>
+      </c>
+    </row>
+    <row r="254" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A254" s="5" t="n">
         <v>245</v>
       </c>
       <c r="B254" s="5" t="s">
-        <v>821</v>
+        <v>823</v>
       </c>
       <c r="C254" s="5" t="s">
-        <v>1263</v>
+        <v>1265</v>
       </c>
       <c r="D254" s="6" t="s">
-        <v>1264</v>
+        <v>1266</v>
       </c>
       <c r="E254" s="5" t="s">
-        <v>1255</v>
-      </c>
-    </row>
-    <row r="255" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+        <v>1257</v>
+      </c>
+    </row>
+    <row r="255" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A255" s="5" t="n">
         <v>246</v>
       </c>
       <c r="B255" s="5" t="s">
-        <v>1256</v>
+        <v>1258</v>
       </c>
       <c r="C255" s="5" t="s">
-        <v>1265</v>
+        <v>1267</v>
       </c>
       <c r="D255" s="6" t="s">
-        <v>1266</v>
+        <v>1268</v>
       </c>
       <c r="E255" s="5" t="s">
-        <v>1252</v>
-      </c>
-    </row>
-    <row r="256" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+        <v>1254</v>
+      </c>
+    </row>
+    <row r="256" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A256" s="5" t="n">
         <v>247</v>
       </c>
       <c r="B256" s="5" t="s">
-        <v>1267</v>
+        <v>1269</v>
       </c>
       <c r="C256" s="5" t="s">
-        <v>1268</v>
+        <v>1270</v>
       </c>
       <c r="D256" s="6" t="s">
-        <v>1269</v>
+        <v>1271</v>
       </c>
       <c r="E256" s="5" t="s">
-        <v>1255</v>
-      </c>
-    </row>
-    <row r="257" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+        <v>1257</v>
+      </c>
+    </row>
+    <row r="257" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A257" s="5" t="n">
         <v>248</v>
       </c>
       <c r="B257" s="5" t="s">
-        <v>821</v>
+        <v>823</v>
       </c>
       <c r="C257" s="5" t="s">
-        <v>1270</v>
+        <v>1272</v>
       </c>
       <c r="D257" s="6" t="s">
-        <v>1271</v>
+        <v>1273</v>
       </c>
       <c r="E257" s="5" t="s">
-        <v>1255</v>
-      </c>
-    </row>
-    <row r="258" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+        <v>1257</v>
+      </c>
+    </row>
+    <row r="258" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A258" s="5" t="n">
         <v>249</v>
       </c>
       <c r="B258" s="5" t="s">
-        <v>888</v>
+        <v>890</v>
       </c>
       <c r="C258" s="5" t="s">
-        <v>1272</v>
+        <v>1274</v>
       </c>
       <c r="D258" s="6" t="s">
-        <v>1273</v>
+        <v>1275</v>
       </c>
       <c r="E258" s="5" t="s">
-        <v>1255</v>
-      </c>
-    </row>
-    <row r="259" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+        <v>1257</v>
+      </c>
+    </row>
+    <row r="259" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A259" s="5" t="n">
         <v>250</v>
       </c>
       <c r="B259" s="5" t="s">
-        <v>1260</v>
+        <v>1262</v>
       </c>
       <c r="C259" s="5" t="s">
-        <v>1274</v>
+        <v>1276</v>
       </c>
       <c r="D259" s="6" t="s">
-        <v>1275</v>
+        <v>1277</v>
       </c>
       <c r="E259" s="5" t="s">
-        <v>1259</v>
+        <v>1261</v>
+      </c>
+    </row>
+    <row r="260" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A260" s="5" t="n">
+        <v>251</v>
+      </c>
+      <c r="B260" s="5" t="s">
+        <v>1258</v>
+      </c>
+      <c r="C260" s="5" t="s">
+        <v>1278</v>
+      </c>
+      <c r="D260" s="6" t="s">
+        <v>1279</v>
+      </c>
+      <c r="E260" s="5" t="s">
+        <v>1280</v>
+      </c>
+    </row>
+    <row r="261" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A261" s="5" t="n">
+        <v>252</v>
+      </c>
+      <c r="B261" s="5" t="s">
+        <v>1258</v>
+      </c>
+      <c r="C261" s="5" t="s">
+        <v>1281</v>
+      </c>
+      <c r="D261" s="6" t="s">
+        <v>1282</v>
+      </c>
+      <c r="E261" s="5" t="s">
+        <v>1280</v>
+      </c>
+    </row>
+    <row r="262" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A262" s="5" t="n">
+        <v>253</v>
+      </c>
+      <c r="B262" s="5" t="s">
+        <v>684</v>
+      </c>
+      <c r="C262" s="5" t="s">
+        <v>1283</v>
+      </c>
+      <c r="D262" s="6" t="s">
+        <v>1284</v>
+      </c>
+      <c r="E262" s="5" t="s">
+        <v>1280</v>
+      </c>
+    </row>
+    <row r="263" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A263" s="5" t="n">
+        <v>254</v>
+      </c>
+      <c r="B263" s="5" t="s">
+        <v>823</v>
+      </c>
+      <c r="C263" s="5" t="s">
+        <v>1285</v>
+      </c>
+      <c r="D263" s="6" t="s">
+        <v>1286</v>
+      </c>
+      <c r="E263" s="5" t="s">
+        <v>1287</v>
+      </c>
+    </row>
+    <row r="264" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A264" s="5" t="n">
+        <v>255</v>
+      </c>
+      <c r="B264" s="5" t="s">
+        <v>684</v>
+      </c>
+      <c r="C264" s="5" t="s">
+        <v>1288</v>
+      </c>
+      <c r="D264" s="6" t="s">
+        <v>1289</v>
+      </c>
+      <c r="E264" s="5" t="s">
+        <v>1290</v>
+      </c>
+    </row>
+    <row r="265" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A265" s="5" t="n">
+        <v>256</v>
+      </c>
+      <c r="B265" s="5" t="s">
+        <v>815</v>
+      </c>
+      <c r="C265" s="5" t="s">
+        <v>1291</v>
+      </c>
+      <c r="D265" s="6" t="s">
+        <v>1292</v>
+      </c>
+      <c r="E265" s="5" t="s">
+        <v>1290</v>
+      </c>
+    </row>
+    <row r="266" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A266" s="5" t="n">
+        <v>257</v>
+      </c>
+      <c r="B266" s="5" t="s">
+        <v>1293</v>
+      </c>
+      <c r="C266" s="5" t="s">
+        <v>1294</v>
+      </c>
+      <c r="D266" s="6" t="s">
+        <v>1295</v>
+      </c>
+      <c r="E266" s="5" t="s">
+        <v>1280</v>
+      </c>
+    </row>
+    <row r="267" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A267" s="5" t="n">
+        <v>258</v>
+      </c>
+      <c r="B267" s="5" t="s">
+        <v>890</v>
+      </c>
+      <c r="C267" s="5" t="s">
+        <v>1296</v>
+      </c>
+      <c r="D267" s="6" t="s">
+        <v>1297</v>
+      </c>
+      <c r="E267" s="5" t="s">
+        <v>1280</v>
       </c>
     </row>
   </sheetData>
@@ -13333,6 +13663,14 @@
     <hyperlink ref="D257" r:id="rId175" display="https://www.theguardian.com/us-news/2026/sep/25/trump-cancels-congress-funding"/>
     <hyperlink ref="D258" r:id="rId176" display="https://www.npr.org/2026/09/26/nx-s1-5981103/cnn-is-getting-new-owners-with-close-ties-to-trump"/>
     <hyperlink ref="D259" r:id="rId177" display="https://www.latimes.com/politics/story/2026-09-22/trump-threatens-to-send-iran-into-hell-if-war-carries-on"/>
+    <hyperlink ref="D260" r:id="rId178" display="https://www.axios.com/2026/09/29/supreme-court-trump-third-country-deportations"/>
+    <hyperlink ref="D261" r:id="rId179" display="https://www.axios.com/2026/09/29/trump-supreme-court-shadow-docket-41-applications"/>
+    <hyperlink ref="D262" r:id="rId180" display="https://www.nbcnews.com/news/us-news/venezuelan-man-shot-wounded-ice-agent-texas-charged-assaulting-officer-rcna600533"/>
+    <hyperlink ref="D263" r:id="rId181" display="https://www.theguardian.com/us-news/2026/sep/30/trump-campaign-ads-violate-federal-law"/>
+    <hyperlink ref="D264" r:id="rId182" display="https://www.nbcnews.com/politics/trump-administration/trump-considering-preemptive-pardons-administration-officials-rcna600905"/>
+    <hyperlink ref="D265" r:id="rId183" display="https://thehill.com/homenews/6122096-white-house-blocks-cnn-pool-trump/"/>
+    <hyperlink ref="D266" r:id="rId184" display="https://www.washingtonpost.com/politics/2026/09/29/gop-senator-blocks-bill-stop-trump-demolishing-kennedy-center/"/>
+    <hyperlink ref="D267" r:id="rId185" display="https://www.npr.org/2026/09/29/nx-s1-5983673/trump-administration-says-its-scaling-back-fuel-efficiency-standards-for-new-cars"/>
   </hyperlinks>
   <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.511811023622047" footer="0.511811023622047"/>
@@ -13358,7 +13696,7 @@
   <sheetData>
     <row r="1" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A1" s="7" t="s">
-        <v>1276</v>
+        <v>1298</v>
       </c>
       <c r="B1" s="7"/>
     </row>
@@ -13367,7 +13705,7 @@
         <v>3</v>
       </c>
       <c r="B2" s="8" t="s">
-        <v>1277</v>
+        <v>1299</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -13394,7 +13732,7 @@
       </c>
       <c r="B5" s="9" t="n">
         <f aca="false">COUNTIF('Weekly Timeline'!C:C,A5)</f>
-        <v>9</v>
+        <v>11</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -13439,7 +13777,7 @@
       </c>
       <c r="B10" s="9" t="n">
         <f aca="false">COUNTIF('Weekly Timeline'!C:C,A10)</f>
-        <v>4</v>
+        <v>5</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -13448,7 +13786,7 @@
       </c>
       <c r="B11" s="9" t="n">
         <f aca="false">COUNTIF('Weekly Timeline'!C:C,A11)</f>
-        <v>33</v>
+        <v>36</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -13520,7 +13858,7 @@
       </c>
       <c r="B19" s="9" t="n">
         <f aca="false">COUNTIF('Weekly Timeline'!C:C,A19)</f>
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="20" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -13529,7 +13867,7 @@
       </c>
       <c r="B20" s="9" t="n">
         <f aca="false">COUNTIF('Weekly Timeline'!C:C,A20)</f>
-        <v>13</v>
+        <v>14</v>
       </c>
     </row>
     <row r="21" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -13550,13 +13888,13 @@
         <v>1</v>
       </c>
     </row>
-    <row r="23" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="23" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A23" s="10" t="s">
-        <v>1278</v>
+        <v>1300</v>
       </c>
       <c r="B23" s="10" t="n">
         <f aca="false">SUM(B3:B22)</f>
-        <v>194</v>
+        <v>202</v>
       </c>
     </row>
   </sheetData>

--- a/data/Trump_Second_Term_Weekly_Tracker.xlsx
+++ b/data/Trump_Second_Term_Weekly_Tracker.xlsx
@@ -13,7 +13,7 @@
     <sheet name="Summary" sheetId="3" state="visible" r:id="rId5"/>
   </sheets>
   <definedNames>
-    <definedName function="false" hidden="true" localSheetId="0" name="_xlnm._FilterDatabase" vbProcedure="false">'Weekly Timeline'!$A$2:$F$260</definedName>
+    <definedName function="false" hidden="true" localSheetId="0" name="_xlnm._FilterDatabase" vbProcedure="false">'Weekly Timeline'!$A$2:$F$268</definedName>
   </definedNames>
   <calcPr iterateCount="100" refMode="A1" iterate="false" iterateDelta="0.0001"/>
   <extLst>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2047" uniqueCount="1301">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2105" uniqueCount="1326">
   <si>
     <t xml:space="preserve">Documented actions and policies of the second Trump administration reported as harmful by major news outlets, courts, and government data — Jan 20, 2025 through Jul 8, 2026. One row per event; weeks with multiple events have multiple rows; quiet weeks are skipped. This compiles critical coverage as requested; the administration and its supporters dispute many of these characterizations. See the Sources tab (matching Ref #) and verify details independently before citing.</t>
   </si>
@@ -1737,6 +1737,24 @@
     <t xml:space="preserve">Sep 29</t>
   </si>
   <si>
+    <t xml:space="preserve">Oct 5, 2026</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Oct 9</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Oct 6</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Free Speech</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Dangerous Rhetoric</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Oct 7</t>
+  </si>
+  <si>
     <t xml:space="preserve">Ref # matches the Source Ref column on the Weekly Timeline tab. URLs are provided where verified via current web results (mostly 2026 items). For 2025 items, outlet names and dates are given; searching the description text will locate the original coverage. Per your request the mix emphasizes CNN, Politico, MSNBC/MS NOW, NBC and independent outlets, alongside AP, Reuters, Guardian, NPR, CBS, ABC and court documents.</t>
   </si>
   <si>
@@ -3919,6 +3937,63 @@
   </si>
   <si>
     <t xml:space="preserve">https://www.npr.org/2026/09/29/nx-s1-5983673/trump-administration-says-its-scaling-back-fuel-efficiency-standards-for-new-cars</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ICE officer shoots a man while making an arrest in New York</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://www.pbs.org/newshour/politics/ice-officer-shoots-a-man-while-making-an-arrest-in-new-york-officials-say</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Oct 9, 2026</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Trump has a new target: The words Americans use</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://www.axios.com/2026/10/06/trump-super-intelligence-war-words-ai-affordability</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Oct 6, 2026</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Trump targets US protesters with ‘antifa’ charges.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://www.theguardian.com/us-news/2026/oct/06/trump-protesters-antifa-defendants-union</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Trump remarks that Iran could "take out" Los Angeles, San Diego draw backlash</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://www.axios.com/2026/10/06/trump-iran-take-out-la-san-diego</t>
+  </si>
+  <si>
+    <t xml:space="preserve">‘Spit on our sacrifice’: Canadian veterans fume after Trump and allies take jibes at military</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://www.theguardian.com/us-news/2026/oct/06/canada-veterans-trump-allies-military</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Shock gloves purchased by ICE cause pain, compliance and fear, Army study found</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://www.pbs.org/newshour/nation/shock-gloves-purchased-by-ice-cause-pain-compliance-and-fear-army-study-found</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Oct 7, 2026</t>
+  </si>
+  <si>
+    <t xml:space="preserve">White House Blocked Politico From Air Force One for Trump’s Trip to Nebraska</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://www.nytimes.com/2026/10/05/us/politico-blocked-trump-nebraska.html</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Execution of a man Live Streamed in America</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://www.theguardian.com/commentisfree/2026/oct/09/nidal-hasan-execution-pete-hegseth-us-military-tv-democracy</t>
   </si>
   <si>
     <t xml:space="preserve">Entries by category (live COUNTIF formulas against the Weekly Timeline tab)</t>
@@ -4066,7 +4141,7 @@
     <xf numFmtId="42" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
     <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
   </cellStyleXfs>
-  <cellXfs count="11">
+  <cellXfs count="12">
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
@@ -4107,7 +4182,11 @@
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -4400,7 +4479,7 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:F260"/>
+  <dimension ref="A1:F268"/>
   <sheetFormatPr defaultColWidth="8.6875" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="13.01"/>
@@ -8952,7 +9031,7 @@
         <v>250</v>
       </c>
     </row>
-    <row r="253" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="253" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A253" s="4" t="s">
         <v>568</v>
       </c>
@@ -8968,7 +9047,7 @@
         <v>251</v>
       </c>
     </row>
-    <row r="254" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="254" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A254" s="4" t="s">
         <v>568</v>
       </c>
@@ -8984,7 +9063,7 @@
         <v>252</v>
       </c>
     </row>
-    <row r="255" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="255" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A255" s="4" t="s">
         <v>568</v>
       </c>
@@ -9000,7 +9079,7 @@
         <v>253</v>
       </c>
     </row>
-    <row r="256" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="256" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A256" s="4" t="s">
         <v>568</v>
       </c>
@@ -9016,7 +9095,7 @@
         <v>254</v>
       </c>
     </row>
-    <row r="257" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="257" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A257" s="4" t="s">
         <v>568</v>
       </c>
@@ -9032,7 +9111,7 @@
         <v>255</v>
       </c>
     </row>
-    <row r="258" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="258" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A258" s="4" t="s">
         <v>568</v>
       </c>
@@ -9048,7 +9127,7 @@
         <v>256</v>
       </c>
     </row>
-    <row r="259" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="259" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A259" s="4" t="s">
         <v>568</v>
       </c>
@@ -9064,7 +9143,7 @@
         <v>257</v>
       </c>
     </row>
-    <row r="260" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="260" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A260" s="4" t="s">
         <v>568</v>
       </c>
@@ -9080,8 +9159,136 @@
         <v>258</v>
       </c>
     </row>
+    <row r="261" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A261" s="5" t="s">
+        <v>570</v>
+      </c>
+      <c r="B261" s="5" t="s">
+        <v>571</v>
+      </c>
+      <c r="C261" s="5" t="s">
+        <v>566</v>
+      </c>
+      <c r="D261" s="5"/>
+      <c r="E261" s="5"/>
+      <c r="F261" s="5" t="n">
+        <v>259</v>
+      </c>
+    </row>
+    <row r="262" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A262" s="5" t="s">
+        <v>570</v>
+      </c>
+      <c r="B262" s="5" t="s">
+        <v>572</v>
+      </c>
+      <c r="C262" s="5" t="s">
+        <v>573</v>
+      </c>
+      <c r="D262" s="5"/>
+      <c r="E262" s="5"/>
+      <c r="F262" s="5" t="n">
+        <v>260</v>
+      </c>
+    </row>
+    <row r="263" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A263" s="5" t="s">
+        <v>570</v>
+      </c>
+      <c r="B263" s="5" t="s">
+        <v>572</v>
+      </c>
+      <c r="C263" s="5" t="s">
+        <v>24</v>
+      </c>
+      <c r="D263" s="5"/>
+      <c r="E263" s="5"/>
+      <c r="F263" s="5" t="n">
+        <v>261</v>
+      </c>
+    </row>
+    <row r="264" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A264" s="5" t="s">
+        <v>570</v>
+      </c>
+      <c r="B264" s="5" t="s">
+        <v>572</v>
+      </c>
+      <c r="C264" s="5" t="s">
+        <v>574</v>
+      </c>
+      <c r="D264" s="5"/>
+      <c r="E264" s="5"/>
+      <c r="F264" s="5" t="n">
+        <v>262</v>
+      </c>
+    </row>
+    <row r="265" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A265" s="5" t="s">
+        <v>570</v>
+      </c>
+      <c r="B265" s="5" t="s">
+        <v>572</v>
+      </c>
+      <c r="C265" s="5" t="s">
+        <v>48</v>
+      </c>
+      <c r="D265" s="5"/>
+      <c r="E265" s="5"/>
+      <c r="F265" s="5" t="n">
+        <v>263</v>
+      </c>
+    </row>
+    <row r="266" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A266" s="5" t="s">
+        <v>570</v>
+      </c>
+      <c r="B266" s="5" t="s">
+        <v>575</v>
+      </c>
+      <c r="C266" s="5" t="s">
+        <v>566</v>
+      </c>
+      <c r="D266" s="5"/>
+      <c r="E266" s="5"/>
+      <c r="F266" s="5" t="n">
+        <v>264</v>
+      </c>
+    </row>
+    <row r="267" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A267" s="5" t="s">
+        <v>570</v>
+      </c>
+      <c r="B267" s="5" t="s">
+        <v>572</v>
+      </c>
+      <c r="C267" s="5" t="s">
+        <v>68</v>
+      </c>
+      <c r="D267" s="5"/>
+      <c r="E267" s="5"/>
+      <c r="F267" s="5" t="n">
+        <v>265</v>
+      </c>
+    </row>
+    <row r="268" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A268" s="5" t="s">
+        <v>570</v>
+      </c>
+      <c r="B268" s="5" t="s">
+        <v>571</v>
+      </c>
+      <c r="C268" s="5" t="s">
+        <v>24</v>
+      </c>
+      <c r="D268" s="5"/>
+      <c r="E268" s="5"/>
+      <c r="F268" s="5" t="n">
+        <v>266</v>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A2:F260"/>
+  <autoFilter ref="A2:F268"/>
   <mergeCells count="1">
     <mergeCell ref="A1:F1"/>
   </mergeCells>
@@ -9101,7 +9308,7 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:E267"/>
+  <dimension ref="A1:E275"/>
   <sheetFormatPr defaultColWidth="8.6875" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="7"/>
@@ -9112,7 +9319,7 @@
   <sheetData>
     <row r="1" customFormat="false" ht="48" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A1" s="2" t="s">
-        <v>570</v>
+        <v>576</v>
       </c>
       <c r="B1" s="2"/>
       <c r="C1" s="2"/>
@@ -9121,19 +9328,19 @@
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A2" s="3" t="s">
-        <v>571</v>
+        <v>577</v>
       </c>
       <c r="B2" s="3" t="s">
-        <v>572</v>
+        <v>578</v>
       </c>
       <c r="C2" s="3" t="s">
-        <v>573</v>
+        <v>579</v>
       </c>
       <c r="D2" s="3" t="s">
-        <v>574</v>
+        <v>580</v>
       </c>
       <c r="E2" s="3" t="s">
-        <v>575</v>
+        <v>581</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -9141,14 +9348,14 @@
         <v>1</v>
       </c>
       <c r="B3" s="5" t="s">
-        <v>576</v>
+        <v>582</v>
       </c>
       <c r="C3" s="5" t="s">
-        <v>577</v>
+        <v>583</v>
       </c>
       <c r="D3" s="5"/>
       <c r="E3" s="5" t="s">
-        <v>578</v>
+        <v>584</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -9156,14 +9363,14 @@
         <v>2</v>
       </c>
       <c r="B4" s="5" t="s">
-        <v>579</v>
+        <v>585</v>
       </c>
       <c r="C4" s="5" t="s">
-        <v>580</v>
+        <v>586</v>
       </c>
       <c r="D4" s="5"/>
       <c r="E4" s="5" t="s">
-        <v>581</v>
+        <v>587</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -9171,14 +9378,14 @@
         <v>3</v>
       </c>
       <c r="B5" s="5" t="s">
-        <v>582</v>
+        <v>588</v>
       </c>
       <c r="C5" s="5" t="s">
-        <v>583</v>
+        <v>589</v>
       </c>
       <c r="D5" s="5"/>
       <c r="E5" s="5" t="s">
-        <v>578</v>
+        <v>584</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -9186,14 +9393,14 @@
         <v>4</v>
       </c>
       <c r="B6" s="5" t="s">
-        <v>584</v>
+        <v>590</v>
       </c>
       <c r="C6" s="5" t="s">
-        <v>585</v>
+        <v>591</v>
       </c>
       <c r="D6" s="5"/>
       <c r="E6" s="5" t="s">
-        <v>586</v>
+        <v>592</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -9201,14 +9408,14 @@
         <v>5</v>
       </c>
       <c r="B7" s="5" t="s">
-        <v>587</v>
+        <v>593</v>
       </c>
       <c r="C7" s="5" t="s">
-        <v>588</v>
+        <v>594</v>
       </c>
       <c r="D7" s="5"/>
       <c r="E7" s="5" t="s">
-        <v>578</v>
+        <v>584</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -9216,14 +9423,14 @@
         <v>6</v>
       </c>
       <c r="B8" s="5" t="s">
-        <v>589</v>
+        <v>595</v>
       </c>
       <c r="C8" s="5" t="s">
-        <v>590</v>
+        <v>596</v>
       </c>
       <c r="D8" s="5"/>
       <c r="E8" s="5" t="s">
-        <v>578</v>
+        <v>584</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -9231,14 +9438,14 @@
         <v>7</v>
       </c>
       <c r="B9" s="5" t="s">
-        <v>591</v>
+        <v>597</v>
       </c>
       <c r="C9" s="5" t="s">
-        <v>592</v>
+        <v>598</v>
       </c>
       <c r="D9" s="5"/>
       <c r="E9" s="5" t="s">
-        <v>593</v>
+        <v>599</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -9246,14 +9453,14 @@
         <v>8</v>
       </c>
       <c r="B10" s="5" t="s">
-        <v>594</v>
+        <v>600</v>
       </c>
       <c r="C10" s="5" t="s">
-        <v>595</v>
+        <v>601</v>
       </c>
       <c r="D10" s="5"/>
       <c r="E10" s="5" t="s">
-        <v>596</v>
+        <v>602</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -9261,14 +9468,14 @@
         <v>9</v>
       </c>
       <c r="B11" s="5" t="s">
-        <v>597</v>
+        <v>603</v>
       </c>
       <c r="C11" s="5" t="s">
-        <v>598</v>
+        <v>604</v>
       </c>
       <c r="D11" s="5"/>
       <c r="E11" s="5" t="s">
-        <v>599</v>
+        <v>605</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -9276,14 +9483,14 @@
         <v>10</v>
       </c>
       <c r="B12" s="5" t="s">
-        <v>600</v>
+        <v>606</v>
       </c>
       <c r="C12" s="5" t="s">
-        <v>601</v>
+        <v>607</v>
       </c>
       <c r="D12" s="5"/>
       <c r="E12" s="5" t="s">
-        <v>602</v>
+        <v>608</v>
       </c>
     </row>
     <row r="13" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -9291,14 +9498,14 @@
         <v>11</v>
       </c>
       <c r="B13" s="5" t="s">
-        <v>603</v>
+        <v>609</v>
       </c>
       <c r="C13" s="5" t="s">
-        <v>604</v>
+        <v>610</v>
       </c>
       <c r="D13" s="5"/>
       <c r="E13" s="5" t="s">
-        <v>605</v>
+        <v>611</v>
       </c>
     </row>
     <row r="14" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -9306,14 +9513,14 @@
         <v>12</v>
       </c>
       <c r="B14" s="5" t="s">
-        <v>606</v>
+        <v>612</v>
       </c>
       <c r="C14" s="5" t="s">
-        <v>607</v>
+        <v>613</v>
       </c>
       <c r="D14" s="5"/>
       <c r="E14" s="5" t="s">
-        <v>608</v>
+        <v>614</v>
       </c>
     </row>
     <row r="15" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -9321,14 +9528,14 @@
         <v>13</v>
       </c>
       <c r="B15" s="5" t="s">
-        <v>609</v>
+        <v>615</v>
       </c>
       <c r="C15" s="5" t="s">
-        <v>610</v>
+        <v>616</v>
       </c>
       <c r="D15" s="5"/>
       <c r="E15" s="5" t="s">
-        <v>611</v>
+        <v>617</v>
       </c>
     </row>
     <row r="16" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -9336,14 +9543,14 @@
         <v>14</v>
       </c>
       <c r="B16" s="5" t="s">
-        <v>612</v>
+        <v>618</v>
       </c>
       <c r="C16" s="5" t="s">
-        <v>613</v>
+        <v>619</v>
       </c>
       <c r="D16" s="5"/>
       <c r="E16" s="5" t="s">
-        <v>614</v>
+        <v>620</v>
       </c>
     </row>
     <row r="17" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -9351,14 +9558,14 @@
         <v>15</v>
       </c>
       <c r="B17" s="5" t="s">
-        <v>615</v>
+        <v>621</v>
       </c>
       <c r="C17" s="5" t="s">
-        <v>616</v>
+        <v>622</v>
       </c>
       <c r="D17" s="5"/>
       <c r="E17" s="5" t="s">
-        <v>617</v>
+        <v>623</v>
       </c>
     </row>
     <row r="18" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -9366,14 +9573,14 @@
         <v>16</v>
       </c>
       <c r="B18" s="5" t="s">
-        <v>618</v>
+        <v>624</v>
       </c>
       <c r="C18" s="5" t="s">
-        <v>619</v>
+        <v>625</v>
       </c>
       <c r="D18" s="5"/>
       <c r="E18" s="5" t="s">
-        <v>620</v>
+        <v>626</v>
       </c>
     </row>
     <row r="19" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -9381,14 +9588,14 @@
         <v>17</v>
       </c>
       <c r="B19" s="5" t="s">
-        <v>621</v>
+        <v>627</v>
       </c>
       <c r="C19" s="5" t="s">
-        <v>622</v>
+        <v>628</v>
       </c>
       <c r="D19" s="5"/>
       <c r="E19" s="5" t="s">
-        <v>623</v>
+        <v>629</v>
       </c>
     </row>
     <row r="20" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -9396,14 +9603,14 @@
         <v>18</v>
       </c>
       <c r="B20" s="5" t="s">
-        <v>624</v>
+        <v>630</v>
       </c>
       <c r="C20" s="5" t="s">
-        <v>625</v>
+        <v>631</v>
       </c>
       <c r="D20" s="5"/>
       <c r="E20" s="5" t="s">
-        <v>626</v>
+        <v>632</v>
       </c>
     </row>
     <row r="21" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -9411,14 +9618,14 @@
         <v>19</v>
       </c>
       <c r="B21" s="5" t="s">
-        <v>627</v>
+        <v>633</v>
       </c>
       <c r="C21" s="5" t="s">
-        <v>628</v>
+        <v>634</v>
       </c>
       <c r="D21" s="5"/>
       <c r="E21" s="5" t="s">
-        <v>629</v>
+        <v>635</v>
       </c>
     </row>
     <row r="22" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -9426,14 +9633,14 @@
         <v>20</v>
       </c>
       <c r="B22" s="5" t="s">
-        <v>630</v>
+        <v>636</v>
       </c>
       <c r="C22" s="5" t="s">
-        <v>631</v>
+        <v>637</v>
       </c>
       <c r="D22" s="5"/>
       <c r="E22" s="5" t="s">
-        <v>632</v>
+        <v>638</v>
       </c>
     </row>
     <row r="23" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -9441,14 +9648,14 @@
         <v>21</v>
       </c>
       <c r="B23" s="5" t="s">
-        <v>633</v>
+        <v>639</v>
       </c>
       <c r="C23" s="5" t="s">
-        <v>634</v>
+        <v>640</v>
       </c>
       <c r="D23" s="5"/>
       <c r="E23" s="5" t="s">
-        <v>635</v>
+        <v>641</v>
       </c>
     </row>
     <row r="24" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -9456,14 +9663,14 @@
         <v>22</v>
       </c>
       <c r="B24" s="5" t="s">
-        <v>636</v>
+        <v>642</v>
       </c>
       <c r="C24" s="5" t="s">
-        <v>637</v>
+        <v>643</v>
       </c>
       <c r="D24" s="5"/>
       <c r="E24" s="5" t="s">
-        <v>638</v>
+        <v>644</v>
       </c>
     </row>
     <row r="25" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -9471,14 +9678,14 @@
         <v>23</v>
       </c>
       <c r="B25" s="5" t="s">
-        <v>639</v>
+        <v>645</v>
       </c>
       <c r="C25" s="5" t="s">
-        <v>640</v>
+        <v>646</v>
       </c>
       <c r="D25" s="5"/>
       <c r="E25" s="5" t="s">
-        <v>641</v>
+        <v>647</v>
       </c>
     </row>
     <row r="26" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -9486,14 +9693,14 @@
         <v>24</v>
       </c>
       <c r="B26" s="5" t="s">
-        <v>642</v>
+        <v>648</v>
       </c>
       <c r="C26" s="5" t="s">
-        <v>643</v>
+        <v>649</v>
       </c>
       <c r="D26" s="5"/>
       <c r="E26" s="5" t="s">
-        <v>644</v>
+        <v>650</v>
       </c>
     </row>
     <row r="27" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -9501,14 +9708,14 @@
         <v>25</v>
       </c>
       <c r="B27" s="5" t="s">
-        <v>645</v>
+        <v>651</v>
       </c>
       <c r="C27" s="5" t="s">
-        <v>646</v>
+        <v>652</v>
       </c>
       <c r="D27" s="5"/>
       <c r="E27" s="5" t="s">
-        <v>647</v>
+        <v>653</v>
       </c>
     </row>
     <row r="28" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -9516,14 +9723,14 @@
         <v>26</v>
       </c>
       <c r="B28" s="5" t="s">
-        <v>648</v>
+        <v>654</v>
       </c>
       <c r="C28" s="5" t="s">
-        <v>649</v>
+        <v>655</v>
       </c>
       <c r="D28" s="5"/>
       <c r="E28" s="5" t="s">
-        <v>650</v>
+        <v>656</v>
       </c>
     </row>
     <row r="29" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -9531,14 +9738,14 @@
         <v>27</v>
       </c>
       <c r="B29" s="5" t="s">
-        <v>651</v>
+        <v>657</v>
       </c>
       <c r="C29" s="5" t="s">
-        <v>652</v>
+        <v>658</v>
       </c>
       <c r="D29" s="5"/>
       <c r="E29" s="5" t="s">
-        <v>653</v>
+        <v>659</v>
       </c>
     </row>
     <row r="30" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -9546,14 +9753,14 @@
         <v>28</v>
       </c>
       <c r="B30" s="5" t="s">
-        <v>654</v>
+        <v>660</v>
       </c>
       <c r="C30" s="5" t="s">
-        <v>655</v>
+        <v>661</v>
       </c>
       <c r="D30" s="5"/>
       <c r="E30" s="5" t="s">
-        <v>656</v>
+        <v>662</v>
       </c>
     </row>
     <row r="31" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -9561,14 +9768,14 @@
         <v>29</v>
       </c>
       <c r="B31" s="5" t="s">
-        <v>657</v>
+        <v>663</v>
       </c>
       <c r="C31" s="5" t="s">
-        <v>658</v>
+        <v>664</v>
       </c>
       <c r="D31" s="5"/>
       <c r="E31" s="5" t="s">
-        <v>659</v>
+        <v>665</v>
       </c>
     </row>
     <row r="32" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -9576,14 +9783,14 @@
         <v>30</v>
       </c>
       <c r="B32" s="5" t="s">
-        <v>603</v>
+        <v>609</v>
       </c>
       <c r="C32" s="5" t="s">
-        <v>660</v>
+        <v>666</v>
       </c>
       <c r="D32" s="5"/>
       <c r="E32" s="5" t="s">
-        <v>661</v>
+        <v>667</v>
       </c>
     </row>
     <row r="33" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -9591,14 +9798,14 @@
         <v>31</v>
       </c>
       <c r="B33" s="5" t="s">
-        <v>662</v>
+        <v>668</v>
       </c>
       <c r="C33" s="5" t="s">
-        <v>663</v>
+        <v>669</v>
       </c>
       <c r="D33" s="5"/>
       <c r="E33" s="5" t="s">
-        <v>664</v>
+        <v>670</v>
       </c>
     </row>
     <row r="34" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -9606,14 +9813,14 @@
         <v>32</v>
       </c>
       <c r="B34" s="5" t="s">
-        <v>621</v>
+        <v>627</v>
       </c>
       <c r="C34" s="5" t="s">
-        <v>665</v>
+        <v>671</v>
       </c>
       <c r="D34" s="5"/>
       <c r="E34" s="5" t="s">
-        <v>666</v>
+        <v>672</v>
       </c>
     </row>
     <row r="35" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -9621,14 +9828,14 @@
         <v>33</v>
       </c>
       <c r="B35" s="5" t="s">
-        <v>667</v>
+        <v>673</v>
       </c>
       <c r="C35" s="5" t="s">
-        <v>668</v>
+        <v>674</v>
       </c>
       <c r="D35" s="5"/>
       <c r="E35" s="5" t="s">
-        <v>669</v>
+        <v>675</v>
       </c>
     </row>
     <row r="36" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -9636,14 +9843,14 @@
         <v>34</v>
       </c>
       <c r="B36" s="5" t="s">
-        <v>670</v>
+        <v>676</v>
       </c>
       <c r="C36" s="5" t="s">
-        <v>671</v>
+        <v>677</v>
       </c>
       <c r="D36" s="5"/>
       <c r="E36" s="5" t="s">
-        <v>672</v>
+        <v>678</v>
       </c>
     </row>
     <row r="37" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -9651,14 +9858,14 @@
         <v>35</v>
       </c>
       <c r="B37" s="5" t="s">
-        <v>673</v>
+        <v>679</v>
       </c>
       <c r="C37" s="5" t="s">
-        <v>674</v>
+        <v>680</v>
       </c>
       <c r="D37" s="5"/>
       <c r="E37" s="5" t="s">
-        <v>675</v>
+        <v>681</v>
       </c>
     </row>
     <row r="38" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -9666,14 +9873,14 @@
         <v>36</v>
       </c>
       <c r="B38" s="5" t="s">
-        <v>621</v>
+        <v>627</v>
       </c>
       <c r="C38" s="5" t="s">
-        <v>676</v>
+        <v>682</v>
       </c>
       <c r="D38" s="5"/>
       <c r="E38" s="5" t="s">
-        <v>677</v>
+        <v>683</v>
       </c>
     </row>
     <row r="39" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -9681,14 +9888,14 @@
         <v>37</v>
       </c>
       <c r="B39" s="5" t="s">
-        <v>678</v>
+        <v>684</v>
       </c>
       <c r="C39" s="5" t="s">
-        <v>679</v>
+        <v>685</v>
       </c>
       <c r="D39" s="5"/>
       <c r="E39" s="5" t="s">
-        <v>680</v>
+        <v>686</v>
       </c>
     </row>
     <row r="40" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -9696,14 +9903,14 @@
         <v>38</v>
       </c>
       <c r="B40" s="5" t="s">
-        <v>681</v>
+        <v>687</v>
       </c>
       <c r="C40" s="5" t="s">
-        <v>682</v>
+        <v>688</v>
       </c>
       <c r="D40" s="5"/>
       <c r="E40" s="5" t="s">
-        <v>683</v>
+        <v>689</v>
       </c>
     </row>
     <row r="41" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -9711,10 +9918,10 @@
         <v>39</v>
       </c>
       <c r="B41" s="5" t="s">
-        <v>684</v>
+        <v>690</v>
       </c>
       <c r="C41" s="5" t="s">
-        <v>685</v>
+        <v>691</v>
       </c>
       <c r="D41" s="5"/>
       <c r="E41" s="5" t="s">
@@ -9726,14 +9933,14 @@
         <v>40</v>
       </c>
       <c r="B42" s="5" t="s">
-        <v>686</v>
+        <v>692</v>
       </c>
       <c r="C42" s="5" t="s">
-        <v>687</v>
+        <v>693</v>
       </c>
       <c r="D42" s="5"/>
       <c r="E42" s="5" t="s">
-        <v>688</v>
+        <v>694</v>
       </c>
     </row>
     <row r="43" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -9741,14 +9948,14 @@
         <v>41</v>
       </c>
       <c r="B43" s="5" t="s">
-        <v>689</v>
+        <v>695</v>
       </c>
       <c r="C43" s="5" t="s">
-        <v>690</v>
+        <v>696</v>
       </c>
       <c r="D43" s="5"/>
       <c r="E43" s="5" t="s">
-        <v>691</v>
+        <v>697</v>
       </c>
     </row>
     <row r="44" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -9756,14 +9963,14 @@
         <v>42</v>
       </c>
       <c r="B44" s="5" t="s">
-        <v>692</v>
+        <v>698</v>
       </c>
       <c r="C44" s="5" t="s">
-        <v>693</v>
+        <v>699</v>
       </c>
       <c r="D44" s="5"/>
       <c r="E44" s="5" t="s">
-        <v>694</v>
+        <v>700</v>
       </c>
     </row>
     <row r="45" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -9771,14 +9978,14 @@
         <v>43</v>
       </c>
       <c r="B45" s="5" t="s">
-        <v>695</v>
+        <v>701</v>
       </c>
       <c r="C45" s="5" t="s">
-        <v>696</v>
+        <v>702</v>
       </c>
       <c r="D45" s="5"/>
       <c r="E45" s="5" t="s">
-        <v>697</v>
+        <v>703</v>
       </c>
     </row>
     <row r="46" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -9786,14 +9993,14 @@
         <v>44</v>
       </c>
       <c r="B46" s="5" t="s">
-        <v>698</v>
+        <v>704</v>
       </c>
       <c r="C46" s="5" t="s">
-        <v>699</v>
+        <v>705</v>
       </c>
       <c r="D46" s="5"/>
       <c r="E46" s="5" t="s">
-        <v>700</v>
+        <v>706</v>
       </c>
     </row>
     <row r="47" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -9801,14 +10008,14 @@
         <v>45</v>
       </c>
       <c r="B47" s="5" t="s">
-        <v>701</v>
+        <v>707</v>
       </c>
       <c r="C47" s="5" t="s">
-        <v>702</v>
+        <v>708</v>
       </c>
       <c r="D47" s="5"/>
       <c r="E47" s="5" t="s">
-        <v>703</v>
+        <v>709</v>
       </c>
     </row>
     <row r="48" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -9816,14 +10023,14 @@
         <v>46</v>
       </c>
       <c r="B48" s="5" t="s">
-        <v>704</v>
+        <v>710</v>
       </c>
       <c r="C48" s="5" t="s">
-        <v>705</v>
+        <v>711</v>
       </c>
       <c r="D48" s="5"/>
       <c r="E48" s="5" t="s">
-        <v>706</v>
+        <v>712</v>
       </c>
     </row>
     <row r="49" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -9831,14 +10038,14 @@
         <v>47</v>
       </c>
       <c r="B49" s="5" t="s">
-        <v>707</v>
+        <v>713</v>
       </c>
       <c r="C49" s="5" t="s">
-        <v>708</v>
+        <v>714</v>
       </c>
       <c r="D49" s="5"/>
       <c r="E49" s="5" t="s">
-        <v>709</v>
+        <v>715</v>
       </c>
     </row>
     <row r="50" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -9846,14 +10053,14 @@
         <v>48</v>
       </c>
       <c r="B50" s="5" t="s">
-        <v>710</v>
+        <v>716</v>
       </c>
       <c r="C50" s="5" t="s">
-        <v>711</v>
+        <v>717</v>
       </c>
       <c r="D50" s="5"/>
       <c r="E50" s="5" t="s">
-        <v>712</v>
+        <v>718</v>
       </c>
     </row>
     <row r="51" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -9861,14 +10068,14 @@
         <v>49</v>
       </c>
       <c r="B51" s="5" t="s">
-        <v>713</v>
+        <v>719</v>
       </c>
       <c r="C51" s="5" t="s">
-        <v>714</v>
+        <v>720</v>
       </c>
       <c r="D51" s="5"/>
       <c r="E51" s="5" t="s">
-        <v>715</v>
+        <v>721</v>
       </c>
     </row>
     <row r="52" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -9876,14 +10083,14 @@
         <v>50</v>
       </c>
       <c r="B52" s="5" t="s">
-        <v>716</v>
+        <v>722</v>
       </c>
       <c r="C52" s="5" t="s">
-        <v>717</v>
+        <v>723</v>
       </c>
       <c r="D52" s="5"/>
       <c r="E52" s="5" t="s">
-        <v>718</v>
+        <v>724</v>
       </c>
     </row>
     <row r="53" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -9891,14 +10098,14 @@
         <v>51</v>
       </c>
       <c r="B53" s="5" t="s">
-        <v>719</v>
+        <v>725</v>
       </c>
       <c r="C53" s="5" t="s">
-        <v>720</v>
+        <v>726</v>
       </c>
       <c r="D53" s="5"/>
       <c r="E53" s="5" t="s">
-        <v>721</v>
+        <v>727</v>
       </c>
     </row>
     <row r="54" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -9906,14 +10113,14 @@
         <v>52</v>
       </c>
       <c r="B54" s="5" t="s">
-        <v>621</v>
+        <v>627</v>
       </c>
       <c r="C54" s="5" t="s">
-        <v>722</v>
+        <v>728</v>
       </c>
       <c r="D54" s="5"/>
       <c r="E54" s="5" t="s">
-        <v>723</v>
+        <v>729</v>
       </c>
     </row>
     <row r="55" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -9921,14 +10128,14 @@
         <v>53</v>
       </c>
       <c r="B55" s="5" t="s">
-        <v>724</v>
+        <v>730</v>
       </c>
       <c r="C55" s="5" t="s">
-        <v>725</v>
+        <v>731</v>
       </c>
       <c r="D55" s="5"/>
       <c r="E55" s="5" t="s">
-        <v>726</v>
+        <v>732</v>
       </c>
     </row>
     <row r="56" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -9936,14 +10143,14 @@
         <v>54</v>
       </c>
       <c r="B56" s="5" t="s">
-        <v>727</v>
+        <v>733</v>
       </c>
       <c r="C56" s="5" t="s">
-        <v>728</v>
+        <v>734</v>
       </c>
       <c r="D56" s="5"/>
       <c r="E56" s="5" t="s">
-        <v>729</v>
+        <v>735</v>
       </c>
     </row>
     <row r="57" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -9951,14 +10158,14 @@
         <v>55</v>
       </c>
       <c r="B57" s="5" t="s">
-        <v>730</v>
+        <v>736</v>
       </c>
       <c r="C57" s="5" t="s">
-        <v>731</v>
+        <v>737</v>
       </c>
       <c r="D57" s="5"/>
       <c r="E57" s="5" t="s">
-        <v>732</v>
+        <v>738</v>
       </c>
     </row>
     <row r="58" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -9966,14 +10173,14 @@
         <v>56</v>
       </c>
       <c r="B58" s="5" t="s">
-        <v>733</v>
+        <v>739</v>
       </c>
       <c r="C58" s="5" t="s">
-        <v>734</v>
+        <v>740</v>
       </c>
       <c r="D58" s="5"/>
       <c r="E58" s="5" t="s">
-        <v>735</v>
+        <v>741</v>
       </c>
     </row>
     <row r="59" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -9981,14 +10188,14 @@
         <v>57</v>
       </c>
       <c r="B59" s="5" t="s">
-        <v>736</v>
+        <v>742</v>
       </c>
       <c r="C59" s="5" t="s">
-        <v>737</v>
+        <v>743</v>
       </c>
       <c r="D59" s="5"/>
       <c r="E59" s="5" t="s">
-        <v>738</v>
+        <v>744</v>
       </c>
     </row>
     <row r="60" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -9996,14 +10203,14 @@
         <v>58</v>
       </c>
       <c r="B60" s="5" t="s">
-        <v>739</v>
+        <v>745</v>
       </c>
       <c r="C60" s="5" t="s">
-        <v>740</v>
+        <v>746</v>
       </c>
       <c r="D60" s="5"/>
       <c r="E60" s="5" t="s">
-        <v>741</v>
+        <v>747</v>
       </c>
     </row>
     <row r="61" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -10011,14 +10218,14 @@
         <v>59</v>
       </c>
       <c r="B61" s="5" t="s">
-        <v>742</v>
+        <v>748</v>
       </c>
       <c r="C61" s="5" t="s">
-        <v>743</v>
+        <v>749</v>
       </c>
       <c r="D61" s="5"/>
       <c r="E61" s="5" t="s">
-        <v>744</v>
+        <v>750</v>
       </c>
     </row>
     <row r="62" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -10026,14 +10233,14 @@
         <v>60</v>
       </c>
       <c r="B62" s="5" t="s">
-        <v>745</v>
+        <v>751</v>
       </c>
       <c r="C62" s="5" t="s">
-        <v>746</v>
+        <v>752</v>
       </c>
       <c r="D62" s="5"/>
       <c r="E62" s="5" t="s">
-        <v>747</v>
+        <v>753</v>
       </c>
     </row>
     <row r="63" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -10041,14 +10248,14 @@
         <v>61</v>
       </c>
       <c r="B63" s="5" t="s">
-        <v>748</v>
+        <v>754</v>
       </c>
       <c r="C63" s="5" t="s">
-        <v>749</v>
+        <v>755</v>
       </c>
       <c r="D63" s="5"/>
       <c r="E63" s="5" t="s">
-        <v>750</v>
+        <v>756</v>
       </c>
     </row>
     <row r="64" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -10056,14 +10263,14 @@
         <v>62</v>
       </c>
       <c r="B64" s="5" t="s">
-        <v>751</v>
+        <v>757</v>
       </c>
       <c r="C64" s="5" t="s">
-        <v>752</v>
+        <v>758</v>
       </c>
       <c r="D64" s="5"/>
       <c r="E64" s="5" t="s">
-        <v>753</v>
+        <v>759</v>
       </c>
     </row>
     <row r="65" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -10071,14 +10278,14 @@
         <v>63</v>
       </c>
       <c r="B65" s="5" t="s">
-        <v>754</v>
+        <v>760</v>
       </c>
       <c r="C65" s="5" t="s">
-        <v>755</v>
+        <v>761</v>
       </c>
       <c r="D65" s="5"/>
       <c r="E65" s="5" t="s">
-        <v>756</v>
+        <v>762</v>
       </c>
     </row>
     <row r="66" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -10086,14 +10293,14 @@
         <v>64</v>
       </c>
       <c r="B66" s="5" t="s">
-        <v>757</v>
+        <v>763</v>
       </c>
       <c r="C66" s="5" t="s">
-        <v>758</v>
+        <v>764</v>
       </c>
       <c r="D66" s="5"/>
       <c r="E66" s="5" t="s">
-        <v>759</v>
+        <v>765</v>
       </c>
     </row>
     <row r="67" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -10101,14 +10308,14 @@
         <v>65</v>
       </c>
       <c r="B67" s="5" t="s">
-        <v>760</v>
+        <v>766</v>
       </c>
       <c r="C67" s="5" t="s">
-        <v>761</v>
+        <v>767</v>
       </c>
       <c r="D67" s="5"/>
       <c r="E67" s="5" t="s">
-        <v>762</v>
+        <v>768</v>
       </c>
     </row>
     <row r="68" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -10116,14 +10323,14 @@
         <v>66</v>
       </c>
       <c r="B68" s="5" t="s">
-        <v>763</v>
+        <v>769</v>
       </c>
       <c r="C68" s="5" t="s">
-        <v>764</v>
+        <v>770</v>
       </c>
       <c r="D68" s="5"/>
       <c r="E68" s="5" t="s">
-        <v>765</v>
+        <v>771</v>
       </c>
     </row>
     <row r="69" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -10131,14 +10338,14 @@
         <v>67</v>
       </c>
       <c r="B69" s="5" t="s">
-        <v>766</v>
+        <v>772</v>
       </c>
       <c r="C69" s="5" t="s">
-        <v>767</v>
+        <v>773</v>
       </c>
       <c r="D69" s="5"/>
       <c r="E69" s="5" t="s">
-        <v>768</v>
+        <v>774</v>
       </c>
     </row>
     <row r="70" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -10146,14 +10353,14 @@
         <v>68</v>
       </c>
       <c r="B70" s="5" t="s">
-        <v>769</v>
+        <v>775</v>
       </c>
       <c r="C70" s="5" t="s">
-        <v>770</v>
+        <v>776</v>
       </c>
       <c r="D70" s="5"/>
       <c r="E70" s="5" t="s">
-        <v>771</v>
+        <v>777</v>
       </c>
     </row>
     <row r="71" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -10161,14 +10368,14 @@
         <v>69</v>
       </c>
       <c r="B71" s="5" t="s">
-        <v>772</v>
+        <v>778</v>
       </c>
       <c r="C71" s="5" t="s">
-        <v>773</v>
+        <v>779</v>
       </c>
       <c r="D71" s="5"/>
       <c r="E71" s="5" t="s">
-        <v>774</v>
+        <v>780</v>
       </c>
     </row>
     <row r="72" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -10176,14 +10383,14 @@
         <v>70</v>
       </c>
       <c r="B72" s="5" t="s">
-        <v>775</v>
+        <v>781</v>
       </c>
       <c r="C72" s="5" t="s">
-        <v>776</v>
+        <v>782</v>
       </c>
       <c r="D72" s="5"/>
       <c r="E72" s="5" t="s">
-        <v>777</v>
+        <v>783</v>
       </c>
     </row>
     <row r="73" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -10191,14 +10398,14 @@
         <v>71</v>
       </c>
       <c r="B73" s="5" t="s">
-        <v>778</v>
+        <v>784</v>
       </c>
       <c r="C73" s="5" t="s">
-        <v>779</v>
+        <v>785</v>
       </c>
       <c r="D73" s="5"/>
       <c r="E73" s="5" t="s">
-        <v>780</v>
+        <v>786</v>
       </c>
     </row>
     <row r="74" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -10206,14 +10413,14 @@
         <v>72</v>
       </c>
       <c r="B74" s="5" t="s">
-        <v>781</v>
+        <v>787</v>
       </c>
       <c r="C74" s="5" t="s">
-        <v>782</v>
+        <v>788</v>
       </c>
       <c r="D74" s="5"/>
       <c r="E74" s="5" t="s">
-        <v>783</v>
+        <v>789</v>
       </c>
     </row>
     <row r="75" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -10221,14 +10428,14 @@
         <v>73</v>
       </c>
       <c r="B75" s="5" t="s">
-        <v>621</v>
+        <v>627</v>
       </c>
       <c r="C75" s="5" t="s">
-        <v>784</v>
+        <v>790</v>
       </c>
       <c r="D75" s="5"/>
       <c r="E75" s="5" t="s">
-        <v>785</v>
+        <v>791</v>
       </c>
     </row>
     <row r="76" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -10236,14 +10443,14 @@
         <v>74</v>
       </c>
       <c r="B76" s="5" t="s">
-        <v>786</v>
+        <v>792</v>
       </c>
       <c r="C76" s="5" t="s">
-        <v>787</v>
+        <v>793</v>
       </c>
       <c r="D76" s="5"/>
       <c r="E76" s="5" t="s">
-        <v>788</v>
+        <v>794</v>
       </c>
     </row>
     <row r="77" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -10251,14 +10458,14 @@
         <v>75</v>
       </c>
       <c r="B77" s="5" t="s">
-        <v>621</v>
+        <v>627</v>
       </c>
       <c r="C77" s="5" t="s">
-        <v>789</v>
+        <v>795</v>
       </c>
       <c r="D77" s="5"/>
       <c r="E77" s="5" t="s">
-        <v>790</v>
+        <v>796</v>
       </c>
     </row>
     <row r="78" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -10266,14 +10473,14 @@
         <v>76</v>
       </c>
       <c r="B78" s="5" t="s">
-        <v>791</v>
+        <v>797</v>
       </c>
       <c r="C78" s="5" t="s">
-        <v>792</v>
+        <v>798</v>
       </c>
       <c r="D78" s="5"/>
       <c r="E78" s="5" t="s">
-        <v>793</v>
+        <v>799</v>
       </c>
     </row>
     <row r="79" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -10281,14 +10488,14 @@
         <v>77</v>
       </c>
       <c r="B79" s="5" t="s">
-        <v>794</v>
+        <v>800</v>
       </c>
       <c r="C79" s="5" t="s">
-        <v>795</v>
+        <v>801</v>
       </c>
       <c r="D79" s="5"/>
       <c r="E79" s="5" t="s">
-        <v>796</v>
+        <v>802</v>
       </c>
     </row>
     <row r="80" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -10296,14 +10503,14 @@
         <v>78</v>
       </c>
       <c r="B80" s="5" t="s">
-        <v>719</v>
+        <v>725</v>
       </c>
       <c r="C80" s="5" t="s">
-        <v>797</v>
+        <v>803</v>
       </c>
       <c r="D80" s="5"/>
       <c r="E80" s="5" t="s">
-        <v>798</v>
+        <v>804</v>
       </c>
     </row>
     <row r="81" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -10311,14 +10518,14 @@
         <v>79</v>
       </c>
       <c r="B81" s="5" t="s">
-        <v>591</v>
+        <v>597</v>
       </c>
       <c r="C81" s="5" t="s">
-        <v>799</v>
+        <v>805</v>
       </c>
       <c r="D81" s="5"/>
       <c r="E81" s="5" t="s">
-        <v>800</v>
+        <v>806</v>
       </c>
     </row>
     <row r="82" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -10326,16 +10533,16 @@
         <v>80</v>
       </c>
       <c r="B82" s="5" t="s">
-        <v>801</v>
+        <v>807</v>
       </c>
       <c r="C82" s="5" t="s">
-        <v>802</v>
+        <v>808</v>
       </c>
       <c r="D82" s="6" t="s">
-        <v>803</v>
+        <v>809</v>
       </c>
       <c r="E82" s="5" t="s">
-        <v>804</v>
+        <v>810</v>
       </c>
     </row>
     <row r="83" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -10343,16 +10550,16 @@
         <v>81</v>
       </c>
       <c r="B83" s="5" t="s">
-        <v>805</v>
+        <v>811</v>
       </c>
       <c r="C83" s="5" t="s">
-        <v>806</v>
+        <v>812</v>
       </c>
       <c r="D83" s="6" t="s">
-        <v>807</v>
+        <v>813</v>
       </c>
       <c r="E83" s="5" t="s">
-        <v>808</v>
+        <v>814</v>
       </c>
     </row>
     <row r="84" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -10360,13 +10567,13 @@
         <v>82</v>
       </c>
       <c r="B84" s="5" t="s">
-        <v>809</v>
+        <v>815</v>
       </c>
       <c r="C84" s="5" t="s">
-        <v>810</v>
+        <v>816</v>
       </c>
       <c r="D84" s="6" t="s">
-        <v>811</v>
+        <v>817</v>
       </c>
       <c r="E84" s="5" t="s">
         <v>297</v>
@@ -10377,13 +10584,13 @@
         <v>83</v>
       </c>
       <c r="B85" s="5" t="s">
-        <v>812</v>
+        <v>818</v>
       </c>
       <c r="C85" s="5" t="s">
-        <v>813</v>
+        <v>819</v>
       </c>
       <c r="D85" s="6" t="s">
-        <v>814</v>
+        <v>820</v>
       </c>
       <c r="E85" s="5" t="s">
         <v>300</v>
@@ -10394,16 +10601,16 @@
         <v>84</v>
       </c>
       <c r="B86" s="5" t="s">
-        <v>815</v>
+        <v>821</v>
       </c>
       <c r="C86" s="5" t="s">
-        <v>816</v>
+        <v>822</v>
       </c>
       <c r="D86" s="6" t="s">
-        <v>817</v>
+        <v>823</v>
       </c>
       <c r="E86" s="5" t="s">
-        <v>818</v>
+        <v>824</v>
       </c>
     </row>
     <row r="87" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -10411,16 +10618,16 @@
         <v>85</v>
       </c>
       <c r="B87" s="5" t="s">
-        <v>819</v>
+        <v>825</v>
       </c>
       <c r="C87" s="5" t="s">
-        <v>820</v>
+        <v>826</v>
       </c>
       <c r="D87" s="6" t="s">
-        <v>821</v>
+        <v>827</v>
       </c>
       <c r="E87" s="5" t="s">
-        <v>822</v>
+        <v>828</v>
       </c>
     </row>
     <row r="88" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -10428,16 +10635,16 @@
         <v>86</v>
       </c>
       <c r="B88" s="5" t="s">
-        <v>823</v>
+        <v>829</v>
       </c>
       <c r="C88" s="5" t="s">
-        <v>824</v>
+        <v>830</v>
       </c>
       <c r="D88" s="6" t="s">
-        <v>825</v>
+        <v>831</v>
       </c>
       <c r="E88" s="5" t="s">
-        <v>822</v>
+        <v>828</v>
       </c>
     </row>
     <row r="89" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -10445,16 +10652,16 @@
         <v>87</v>
       </c>
       <c r="B89" s="5" t="s">
-        <v>826</v>
+        <v>832</v>
       </c>
       <c r="C89" s="5" t="s">
-        <v>827</v>
+        <v>833</v>
       </c>
       <c r="D89" s="6" t="s">
+        <v>834</v>
+      </c>
+      <c r="E89" s="5" t="s">
         <v>828</v>
-      </c>
-      <c r="E89" s="5" t="s">
-        <v>822</v>
       </c>
     </row>
     <row r="90" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -10462,16 +10669,16 @@
         <v>88</v>
       </c>
       <c r="B90" s="5" t="s">
-        <v>829</v>
+        <v>835</v>
       </c>
       <c r="C90" s="5" t="s">
-        <v>830</v>
+        <v>836</v>
       </c>
       <c r="D90" s="6" t="s">
-        <v>831</v>
+        <v>837</v>
       </c>
       <c r="E90" s="5" t="s">
-        <v>832</v>
+        <v>838</v>
       </c>
     </row>
     <row r="91" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -10479,16 +10686,16 @@
         <v>89</v>
       </c>
       <c r="B91" s="5" t="s">
-        <v>833</v>
+        <v>839</v>
       </c>
       <c r="C91" s="5" t="s">
-        <v>834</v>
+        <v>840</v>
       </c>
       <c r="D91" s="6" t="s">
-        <v>835</v>
+        <v>841</v>
       </c>
       <c r="E91" s="5" t="s">
-        <v>832</v>
+        <v>838</v>
       </c>
     </row>
     <row r="92" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -10496,16 +10703,16 @@
         <v>90</v>
       </c>
       <c r="B92" s="5" t="s">
-        <v>823</v>
+        <v>829</v>
       </c>
       <c r="C92" s="5" t="s">
-        <v>836</v>
+        <v>842</v>
       </c>
       <c r="D92" s="6" t="s">
-        <v>837</v>
+        <v>843</v>
       </c>
       <c r="E92" s="5" t="s">
-        <v>838</v>
+        <v>844</v>
       </c>
     </row>
     <row r="93" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -10513,16 +10720,16 @@
         <v>91</v>
       </c>
       <c r="B93" s="5" t="s">
-        <v>839</v>
+        <v>845</v>
       </c>
       <c r="C93" s="5" t="s">
-        <v>840</v>
+        <v>846</v>
       </c>
       <c r="D93" s="6" t="s">
-        <v>841</v>
+        <v>847</v>
       </c>
       <c r="E93" s="5" t="s">
-        <v>838</v>
+        <v>844</v>
       </c>
     </row>
     <row r="94" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -10530,16 +10737,16 @@
         <v>92</v>
       </c>
       <c r="B94" s="5" t="s">
-        <v>842</v>
+        <v>848</v>
       </c>
       <c r="C94" s="5" t="s">
-        <v>843</v>
+        <v>849</v>
       </c>
       <c r="D94" s="6" t="s">
-        <v>844</v>
+        <v>850</v>
       </c>
       <c r="E94" s="5" t="s">
-        <v>845</v>
+        <v>851</v>
       </c>
     </row>
     <row r="95" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -10547,16 +10754,16 @@
         <v>93</v>
       </c>
       <c r="B95" s="5" t="s">
-        <v>684</v>
+        <v>690</v>
       </c>
       <c r="C95" s="5" t="s">
-        <v>846</v>
+        <v>852</v>
       </c>
       <c r="D95" s="6" t="s">
-        <v>847</v>
+        <v>853</v>
       </c>
       <c r="E95" s="5" t="s">
-        <v>848</v>
+        <v>854</v>
       </c>
     </row>
     <row r="96" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -10564,16 +10771,16 @@
         <v>94</v>
       </c>
       <c r="B96" s="5" t="s">
-        <v>829</v>
+        <v>835</v>
       </c>
       <c r="C96" s="5" t="s">
-        <v>849</v>
+        <v>855</v>
       </c>
       <c r="D96" s="6" t="s">
-        <v>850</v>
+        <v>856</v>
       </c>
       <c r="E96" s="5" t="s">
-        <v>848</v>
+        <v>854</v>
       </c>
     </row>
     <row r="97" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -10581,16 +10788,16 @@
         <v>95</v>
       </c>
       <c r="B97" s="5" t="s">
-        <v>851</v>
+        <v>857</v>
       </c>
       <c r="C97" s="5" t="s">
-        <v>852</v>
+        <v>858</v>
       </c>
       <c r="D97" s="6" t="s">
-        <v>853</v>
+        <v>859</v>
       </c>
       <c r="E97" s="5" t="s">
-        <v>848</v>
+        <v>854</v>
       </c>
     </row>
     <row r="98" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -10598,16 +10805,16 @@
         <v>96</v>
       </c>
       <c r="B98" s="5" t="s">
-        <v>809</v>
+        <v>815</v>
       </c>
       <c r="C98" s="5" t="s">
-        <v>854</v>
+        <v>860</v>
       </c>
       <c r="D98" s="6" t="s">
-        <v>855</v>
+        <v>861</v>
       </c>
       <c r="E98" s="5" t="s">
-        <v>838</v>
+        <v>844</v>
       </c>
     </row>
     <row r="99" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -10615,16 +10822,16 @@
         <v>97</v>
       </c>
       <c r="B99" s="5" t="s">
-        <v>856</v>
+        <v>862</v>
       </c>
       <c r="C99" s="5" t="s">
-        <v>857</v>
+        <v>863</v>
       </c>
       <c r="D99" s="6" t="s">
-        <v>858</v>
+        <v>864</v>
       </c>
       <c r="E99" s="5" t="s">
-        <v>859</v>
+        <v>865</v>
       </c>
     </row>
     <row r="100" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -10632,16 +10839,16 @@
         <v>98</v>
       </c>
       <c r="B100" s="5" t="s">
-        <v>823</v>
+        <v>829</v>
       </c>
       <c r="C100" s="5" t="s">
-        <v>860</v>
+        <v>866</v>
       </c>
       <c r="D100" s="6" t="s">
-        <v>861</v>
+        <v>867</v>
       </c>
       <c r="E100" s="5" t="s">
-        <v>862</v>
+        <v>868</v>
       </c>
     </row>
     <row r="101" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -10649,16 +10856,16 @@
         <v>99</v>
       </c>
       <c r="B101" s="5" t="s">
-        <v>829</v>
+        <v>835</v>
       </c>
       <c r="C101" s="5" t="s">
-        <v>863</v>
+        <v>869</v>
       </c>
       <c r="D101" s="6" t="s">
-        <v>864</v>
+        <v>870</v>
       </c>
       <c r="E101" s="5" t="s">
-        <v>865</v>
+        <v>871</v>
       </c>
     </row>
     <row r="102" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -10666,16 +10873,16 @@
         <v>100</v>
       </c>
       <c r="B102" s="5" t="s">
-        <v>866</v>
+        <v>872</v>
       </c>
       <c r="C102" s="5" t="s">
-        <v>867</v>
+        <v>873</v>
       </c>
       <c r="D102" s="6" t="s">
-        <v>868</v>
+        <v>874</v>
       </c>
       <c r="E102" s="5" t="s">
-        <v>869</v>
+        <v>875</v>
       </c>
     </row>
     <row r="103" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -10683,16 +10890,16 @@
         <v>101</v>
       </c>
       <c r="B103" s="5" t="s">
-        <v>809</v>
+        <v>815</v>
       </c>
       <c r="C103" s="5" t="s">
-        <v>870</v>
+        <v>876</v>
       </c>
       <c r="D103" s="6" t="s">
-        <v>871</v>
+        <v>877</v>
       </c>
       <c r="E103" s="5" t="s">
-        <v>872</v>
+        <v>878</v>
       </c>
     </row>
     <row r="104" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -10700,13 +10907,13 @@
         <v>102</v>
       </c>
       <c r="B104" s="5" t="s">
-        <v>684</v>
+        <v>690</v>
       </c>
       <c r="C104" s="5" t="s">
-        <v>873</v>
+        <v>879</v>
       </c>
       <c r="D104" s="6" t="s">
-        <v>874</v>
+        <v>880</v>
       </c>
       <c r="E104" s="5" t="s">
         <v>352</v>
@@ -10717,16 +10924,16 @@
         <v>103</v>
       </c>
       <c r="B105" s="5" t="s">
-        <v>875</v>
+        <v>881</v>
       </c>
       <c r="C105" s="5" t="s">
-        <v>876</v>
+        <v>882</v>
       </c>
       <c r="D105" s="6" t="s">
-        <v>877</v>
+        <v>883</v>
       </c>
       <c r="E105" s="5" t="s">
-        <v>878</v>
+        <v>884</v>
       </c>
     </row>
     <row r="106" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -10734,16 +10941,16 @@
         <v>104</v>
       </c>
       <c r="B106" s="5" t="s">
-        <v>879</v>
+        <v>885</v>
       </c>
       <c r="C106" s="5" t="s">
-        <v>880</v>
+        <v>886</v>
       </c>
       <c r="D106" s="6" t="s">
-        <v>881</v>
+        <v>887</v>
       </c>
       <c r="E106" s="5" t="s">
-        <v>882</v>
+        <v>888</v>
       </c>
     </row>
     <row r="107" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -10751,16 +10958,16 @@
         <v>105</v>
       </c>
       <c r="B107" s="5" t="s">
-        <v>883</v>
+        <v>889</v>
       </c>
       <c r="C107" s="5" t="s">
-        <v>884</v>
+        <v>890</v>
       </c>
       <c r="D107" s="6" t="s">
-        <v>885</v>
+        <v>891</v>
       </c>
       <c r="E107" s="5" t="s">
-        <v>886</v>
+        <v>892</v>
       </c>
     </row>
     <row r="108" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -10768,16 +10975,16 @@
         <v>106</v>
       </c>
       <c r="B108" s="5" t="s">
-        <v>879</v>
+        <v>885</v>
       </c>
       <c r="C108" s="5" t="s">
-        <v>887</v>
+        <v>893</v>
       </c>
       <c r="D108" s="6" t="s">
-        <v>888</v>
+        <v>894</v>
       </c>
       <c r="E108" s="5" t="s">
-        <v>889</v>
+        <v>895</v>
       </c>
     </row>
     <row r="109" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -10785,13 +10992,13 @@
         <v>107</v>
       </c>
       <c r="B109" s="5" t="s">
-        <v>890</v>
+        <v>896</v>
       </c>
       <c r="C109" s="5" t="s">
-        <v>891</v>
+        <v>897</v>
       </c>
       <c r="D109" s="6" t="s">
-        <v>892</v>
+        <v>898</v>
       </c>
       <c r="E109" s="5" t="s">
         <v>368</v>
@@ -10802,13 +11009,13 @@
         <v>108</v>
       </c>
       <c r="B110" s="5" t="s">
-        <v>684</v>
+        <v>690</v>
       </c>
       <c r="C110" s="5" t="s">
-        <v>893</v>
+        <v>899</v>
       </c>
       <c r="D110" s="6" t="s">
-        <v>894</v>
+        <v>900</v>
       </c>
       <c r="E110" s="5" t="s">
         <v>368</v>
@@ -10819,16 +11026,16 @@
         <v>109</v>
       </c>
       <c r="B111" s="5" t="s">
-        <v>883</v>
+        <v>889</v>
       </c>
       <c r="C111" s="5" t="s">
-        <v>895</v>
+        <v>901</v>
       </c>
       <c r="D111" s="6" t="s">
-        <v>896</v>
+        <v>902</v>
       </c>
       <c r="E111" s="5" t="s">
-        <v>897</v>
+        <v>903</v>
       </c>
     </row>
     <row r="112" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -10836,16 +11043,16 @@
         <v>110</v>
       </c>
       <c r="B112" s="5" t="s">
-        <v>823</v>
+        <v>829</v>
       </c>
       <c r="C112" s="5" t="s">
-        <v>898</v>
+        <v>904</v>
       </c>
       <c r="D112" s="6" t="s">
-        <v>899</v>
+        <v>905</v>
       </c>
       <c r="E112" s="5" t="s">
-        <v>900</v>
+        <v>906</v>
       </c>
     </row>
     <row r="113" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -10853,13 +11060,13 @@
         <v>111</v>
       </c>
       <c r="B113" s="5" t="s">
-        <v>815</v>
+        <v>821</v>
       </c>
       <c r="C113" s="5" t="s">
-        <v>901</v>
+        <v>907</v>
       </c>
       <c r="D113" s="6" t="s">
-        <v>902</v>
+        <v>908</v>
       </c>
       <c r="E113" s="5" t="s">
         <v>382</v>
@@ -10870,16 +11077,16 @@
         <v>112</v>
       </c>
       <c r="B114" s="5" t="s">
-        <v>823</v>
+        <v>829</v>
       </c>
       <c r="C114" s="5" t="s">
-        <v>903</v>
+        <v>909</v>
       </c>
       <c r="D114" s="6" t="s">
-        <v>904</v>
+        <v>910</v>
       </c>
       <c r="E114" s="5" t="s">
-        <v>905</v>
+        <v>911</v>
       </c>
     </row>
     <row r="115" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -10887,16 +11094,16 @@
         <v>113</v>
       </c>
       <c r="B115" s="5" t="s">
-        <v>906</v>
+        <v>912</v>
       </c>
       <c r="C115" s="5" t="s">
-        <v>907</v>
+        <v>913</v>
       </c>
       <c r="D115" s="6" t="s">
-        <v>908</v>
+        <v>914</v>
       </c>
       <c r="E115" s="5" t="s">
-        <v>909</v>
+        <v>915</v>
       </c>
     </row>
     <row r="116" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -10904,16 +11111,16 @@
         <v>114</v>
       </c>
       <c r="B116" s="5" t="s">
-        <v>829</v>
+        <v>835</v>
       </c>
       <c r="C116" s="5" t="s">
-        <v>910</v>
+        <v>916</v>
       </c>
       <c r="D116" s="6" t="s">
-        <v>911</v>
+        <v>917</v>
       </c>
       <c r="E116" s="5" t="s">
-        <v>909</v>
+        <v>915</v>
       </c>
     </row>
     <row r="117" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -10921,16 +11128,16 @@
         <v>115</v>
       </c>
       <c r="B117" s="5" t="s">
-        <v>912</v>
+        <v>918</v>
       </c>
       <c r="C117" s="5" t="s">
-        <v>913</v>
+        <v>919</v>
       </c>
       <c r="D117" s="6" t="s">
-        <v>914</v>
+        <v>920</v>
       </c>
       <c r="E117" s="5" t="s">
-        <v>915</v>
+        <v>921</v>
       </c>
     </row>
     <row r="118" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -10938,13 +11145,13 @@
         <v>116</v>
       </c>
       <c r="B118" s="5" t="s">
-        <v>829</v>
+        <v>835</v>
       </c>
       <c r="C118" s="5" t="s">
-        <v>916</v>
+        <v>922</v>
       </c>
       <c r="D118" s="6" t="s">
-        <v>917</v>
+        <v>923</v>
       </c>
       <c r="E118" s="5" t="s">
         <v>396</v>
@@ -10955,16 +11162,16 @@
         <v>117</v>
       </c>
       <c r="B119" s="5" t="s">
-        <v>918</v>
+        <v>924</v>
       </c>
       <c r="C119" s="5" t="s">
-        <v>919</v>
+        <v>925</v>
       </c>
       <c r="D119" s="6" t="s">
-        <v>920</v>
+        <v>926</v>
       </c>
       <c r="E119" s="5" t="s">
-        <v>921</v>
+        <v>927</v>
       </c>
     </row>
     <row r="120" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -10972,16 +11179,16 @@
         <v>118</v>
       </c>
       <c r="B120" s="5" t="s">
-        <v>906</v>
+        <v>912</v>
       </c>
       <c r="C120" s="5" t="s">
-        <v>922</v>
+        <v>928</v>
       </c>
       <c r="D120" s="6" t="s">
-        <v>923</v>
+        <v>929</v>
       </c>
       <c r="E120" s="5" t="s">
-        <v>924</v>
+        <v>930</v>
       </c>
     </row>
     <row r="121" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -10989,16 +11196,16 @@
         <v>119</v>
       </c>
       <c r="B121" s="5" t="s">
-        <v>925</v>
+        <v>931</v>
       </c>
       <c r="C121" s="5" t="s">
-        <v>926</v>
+        <v>932</v>
       </c>
       <c r="D121" s="6" t="s">
+        <v>933</v>
+      </c>
+      <c r="E121" s="5" t="s">
         <v>927</v>
-      </c>
-      <c r="E121" s="5" t="s">
-        <v>921</v>
       </c>
     </row>
     <row r="122" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -11006,16 +11213,16 @@
         <v>120</v>
       </c>
       <c r="B122" s="5" t="s">
-        <v>928</v>
+        <v>934</v>
       </c>
       <c r="C122" s="5" t="s">
-        <v>929</v>
+        <v>935</v>
       </c>
       <c r="D122" s="6" t="s">
-        <v>930</v>
+        <v>936</v>
       </c>
       <c r="E122" s="5" t="s">
-        <v>931</v>
+        <v>937</v>
       </c>
     </row>
     <row r="123" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -11023,13 +11230,13 @@
         <v>121</v>
       </c>
       <c r="B123" s="5" t="s">
-        <v>829</v>
+        <v>835</v>
       </c>
       <c r="C123" s="5" t="s">
-        <v>932</v>
+        <v>938</v>
       </c>
       <c r="D123" s="6" t="s">
-        <v>933</v>
+        <v>939</v>
       </c>
       <c r="E123" s="5" t="s">
         <v>409</v>
@@ -11040,13 +11247,13 @@
         <v>122</v>
       </c>
       <c r="B124" s="5" t="s">
-        <v>890</v>
+        <v>896</v>
       </c>
       <c r="C124" s="5" t="s">
-        <v>934</v>
+        <v>940</v>
       </c>
       <c r="D124" s="6" t="s">
-        <v>935</v>
+        <v>941</v>
       </c>
       <c r="E124" s="5" t="s">
         <v>409</v>
@@ -11057,16 +11264,16 @@
         <v>123</v>
       </c>
       <c r="B125" s="5" t="s">
-        <v>856</v>
+        <v>862</v>
       </c>
       <c r="C125" s="5" t="s">
-        <v>936</v>
+        <v>942</v>
       </c>
       <c r="D125" s="6" t="s">
-        <v>937</v>
+        <v>943</v>
       </c>
       <c r="E125" s="5" t="s">
-        <v>938</v>
+        <v>944</v>
       </c>
     </row>
     <row r="126" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -11074,16 +11281,16 @@
         <v>124</v>
       </c>
       <c r="B126" s="5" t="s">
-        <v>939</v>
+        <v>945</v>
       </c>
       <c r="C126" s="5" t="s">
-        <v>940</v>
+        <v>946</v>
       </c>
       <c r="D126" s="6" t="s">
-        <v>941</v>
+        <v>947</v>
       </c>
       <c r="E126" s="5" t="s">
-        <v>938</v>
+        <v>944</v>
       </c>
     </row>
     <row r="127" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -11091,16 +11298,16 @@
         <v>125</v>
       </c>
       <c r="B127" s="5" t="s">
-        <v>875</v>
+        <v>881</v>
       </c>
       <c r="C127" s="5" t="s">
-        <v>942</v>
+        <v>948</v>
       </c>
       <c r="D127" s="6" t="s">
-        <v>943</v>
+        <v>949</v>
       </c>
       <c r="E127" s="5" t="s">
-        <v>944</v>
+        <v>950</v>
       </c>
     </row>
     <row r="128" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -11108,16 +11315,16 @@
         <v>126</v>
       </c>
       <c r="B128" s="5" t="s">
-        <v>945</v>
+        <v>951</v>
       </c>
       <c r="C128" s="5" t="s">
-        <v>946</v>
+        <v>952</v>
       </c>
       <c r="D128" s="6" t="s">
-        <v>947</v>
+        <v>953</v>
       </c>
       <c r="E128" s="5" t="s">
-        <v>948</v>
+        <v>954</v>
       </c>
     </row>
     <row r="129" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -11125,16 +11332,16 @@
         <v>127</v>
       </c>
       <c r="B129" s="5" t="s">
-        <v>949</v>
+        <v>955</v>
       </c>
       <c r="C129" s="5" t="s">
-        <v>950</v>
+        <v>956</v>
       </c>
       <c r="D129" s="6" t="s">
-        <v>951</v>
+        <v>957</v>
       </c>
       <c r="E129" s="5" t="s">
-        <v>952</v>
+        <v>958</v>
       </c>
     </row>
     <row r="130" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -11142,16 +11349,16 @@
         <v>128</v>
       </c>
       <c r="B130" s="5" t="s">
-        <v>953</v>
+        <v>959</v>
       </c>
       <c r="C130" s="5" t="s">
-        <v>954</v>
+        <v>960</v>
       </c>
       <c r="D130" s="6" t="s">
-        <v>951</v>
+        <v>957</v>
       </c>
       <c r="E130" s="5" t="s">
-        <v>955</v>
+        <v>961</v>
       </c>
     </row>
     <row r="131" customFormat="false" ht="34.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -11159,13 +11366,13 @@
         <v>129</v>
       </c>
       <c r="B131" s="5" t="s">
-        <v>956</v>
+        <v>962</v>
       </c>
       <c r="C131" s="5" t="s">
+        <v>963</v>
+      </c>
+      <c r="D131" s="6" t="s">
         <v>957</v>
-      </c>
-      <c r="D131" s="6" t="s">
-        <v>951</v>
       </c>
       <c r="E131" s="5" t="s">
         <v>434</v>
@@ -11176,16 +11383,16 @@
         <v>130</v>
       </c>
       <c r="B132" s="5" t="s">
-        <v>958</v>
+        <v>964</v>
       </c>
       <c r="C132" s="5" t="s">
-        <v>959</v>
+        <v>965</v>
       </c>
       <c r="D132" s="6" t="s">
-        <v>960</v>
+        <v>966</v>
       </c>
       <c r="E132" s="5" t="s">
-        <v>961</v>
+        <v>967</v>
       </c>
     </row>
     <row r="133" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -11193,16 +11400,16 @@
         <v>131</v>
       </c>
       <c r="B133" s="5" t="s">
-        <v>962</v>
+        <v>968</v>
       </c>
       <c r="C133" s="5" t="s">
-        <v>963</v>
+        <v>969</v>
       </c>
       <c r="D133" s="6" t="s">
-        <v>964</v>
+        <v>970</v>
       </c>
       <c r="E133" s="5" t="s">
-        <v>961</v>
+        <v>967</v>
       </c>
     </row>
     <row r="134" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -11210,16 +11417,16 @@
         <v>132</v>
       </c>
       <c r="B134" s="5" t="s">
-        <v>965</v>
+        <v>971</v>
       </c>
       <c r="C134" s="5" t="s">
-        <v>966</v>
+        <v>972</v>
       </c>
       <c r="D134" s="6" t="s">
-        <v>967</v>
+        <v>973</v>
       </c>
       <c r="E134" s="5" t="s">
-        <v>968</v>
+        <v>974</v>
       </c>
     </row>
     <row r="135" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -11227,16 +11434,16 @@
         <v>133</v>
       </c>
       <c r="B135" s="5" t="s">
-        <v>969</v>
+        <v>975</v>
       </c>
       <c r="C135" s="5" t="s">
-        <v>970</v>
+        <v>976</v>
       </c>
       <c r="D135" s="6" t="s">
-        <v>971</v>
+        <v>977</v>
       </c>
       <c r="E135" s="5" t="s">
-        <v>972</v>
+        <v>978</v>
       </c>
     </row>
     <row r="136" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -11244,13 +11451,13 @@
         <v>134</v>
       </c>
       <c r="B136" s="5" t="s">
-        <v>684</v>
+        <v>690</v>
       </c>
       <c r="C136" s="5" t="s">
-        <v>973</v>
+        <v>979</v>
       </c>
       <c r="D136" s="6" t="s">
-        <v>974</v>
+        <v>980</v>
       </c>
       <c r="E136" s="5" t="s">
         <v>451</v>
@@ -11261,13 +11468,13 @@
         <v>135</v>
       </c>
       <c r="B137" s="5" t="s">
-        <v>975</v>
+        <v>981</v>
       </c>
       <c r="C137" s="5" t="s">
-        <v>976</v>
+        <v>982</v>
       </c>
       <c r="D137" s="6" t="s">
-        <v>977</v>
+        <v>983</v>
       </c>
       <c r="E137" s="5" t="s">
         <v>451</v>
@@ -11278,16 +11485,16 @@
         <v>136</v>
       </c>
       <c r="B138" s="5" t="s">
-        <v>978</v>
+        <v>984</v>
       </c>
       <c r="C138" s="5" t="s">
-        <v>979</v>
+        <v>985</v>
       </c>
       <c r="D138" s="6" t="s">
-        <v>980</v>
+        <v>986</v>
       </c>
       <c r="E138" s="5" t="s">
-        <v>981</v>
+        <v>987</v>
       </c>
     </row>
     <row r="139" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -11295,16 +11502,16 @@
         <v>137</v>
       </c>
       <c r="B139" s="5" t="s">
-        <v>982</v>
+        <v>988</v>
       </c>
       <c r="C139" s="5" t="s">
-        <v>983</v>
+        <v>989</v>
       </c>
       <c r="D139" s="6" t="s">
-        <v>984</v>
+        <v>990</v>
       </c>
       <c r="E139" s="5" t="s">
-        <v>985</v>
+        <v>991</v>
       </c>
     </row>
     <row r="140" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -11312,13 +11519,13 @@
         <v>138</v>
       </c>
       <c r="B140" s="5" t="s">
-        <v>851</v>
+        <v>857</v>
       </c>
       <c r="C140" s="5" t="s">
-        <v>986</v>
+        <v>992</v>
       </c>
       <c r="D140" s="6" t="s">
-        <v>987</v>
+        <v>993</v>
       </c>
       <c r="E140" s="5" t="s">
         <v>463</v>
@@ -11329,16 +11536,16 @@
         <v>139</v>
       </c>
       <c r="B141" s="5" t="s">
-        <v>856</v>
+        <v>862</v>
       </c>
       <c r="C141" s="5" t="s">
-        <v>988</v>
+        <v>994</v>
       </c>
       <c r="D141" s="6" t="s">
-        <v>989</v>
+        <v>995</v>
       </c>
       <c r="E141" s="5" t="s">
-        <v>990</v>
+        <v>996</v>
       </c>
     </row>
     <row r="142" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -11346,16 +11553,16 @@
         <v>140</v>
       </c>
       <c r="B142" s="5" t="s">
-        <v>991</v>
+        <v>997</v>
       </c>
       <c r="C142" s="5" t="s">
-        <v>992</v>
+        <v>998</v>
       </c>
       <c r="D142" s="6" t="s">
-        <v>993</v>
+        <v>999</v>
       </c>
       <c r="E142" s="5" t="s">
-        <v>994</v>
+        <v>1000</v>
       </c>
     </row>
     <row r="143" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -11363,13 +11570,13 @@
         <v>141</v>
       </c>
       <c r="B143" s="5" t="s">
-        <v>823</v>
+        <v>829</v>
       </c>
       <c r="C143" s="5" t="s">
-        <v>995</v>
+        <v>1001</v>
       </c>
       <c r="D143" s="6" t="s">
-        <v>996</v>
+        <v>1002</v>
       </c>
       <c r="E143" s="5" t="s">
         <v>472</v>
@@ -11380,16 +11587,16 @@
         <v>142</v>
       </c>
       <c r="B144" s="5" t="s">
-        <v>997</v>
+        <v>1003</v>
       </c>
       <c r="C144" s="5" t="s">
-        <v>998</v>
+        <v>1004</v>
       </c>
       <c r="D144" s="6" t="s">
-        <v>999</v>
+        <v>1005</v>
       </c>
       <c r="E144" s="5" t="s">
-        <v>1000</v>
+        <v>1006</v>
       </c>
     </row>
     <row r="145" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -11397,13 +11604,13 @@
         <v>143</v>
       </c>
       <c r="B145" s="5" t="s">
-        <v>883</v>
+        <v>889</v>
       </c>
       <c r="C145" s="5" t="s">
-        <v>1001</v>
+        <v>1007</v>
       </c>
       <c r="D145" s="6" t="s">
-        <v>1002</v>
+        <v>1008</v>
       </c>
       <c r="E145" s="5" t="s">
         <v>479</v>
@@ -11414,16 +11621,16 @@
         <v>144</v>
       </c>
       <c r="B146" s="5" t="s">
-        <v>823</v>
+        <v>829</v>
       </c>
       <c r="C146" s="5" t="s">
-        <v>1003</v>
+        <v>1009</v>
       </c>
       <c r="D146" s="6" t="s">
-        <v>1004</v>
+        <v>1010</v>
       </c>
       <c r="E146" s="5" t="s">
-        <v>1005</v>
+        <v>1011</v>
       </c>
     </row>
     <row r="147" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -11431,16 +11638,16 @@
         <v>145</v>
       </c>
       <c r="B147" s="5" t="s">
-        <v>1006</v>
+        <v>1012</v>
       </c>
       <c r="C147" s="5" t="s">
-        <v>1007</v>
+        <v>1013</v>
       </c>
       <c r="D147" s="6" t="s">
-        <v>1008</v>
+        <v>1014</v>
       </c>
       <c r="E147" s="5" t="s">
-        <v>1009</v>
+        <v>1015</v>
       </c>
     </row>
     <row r="148" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -11448,16 +11655,16 @@
         <v>146</v>
       </c>
       <c r="B148" s="5" t="s">
-        <v>1010</v>
+        <v>1016</v>
       </c>
       <c r="C148" s="5" t="s">
-        <v>1011</v>
+        <v>1017</v>
       </c>
       <c r="D148" s="6" t="s">
-        <v>1012</v>
+        <v>1018</v>
       </c>
       <c r="E148" s="5" t="s">
-        <v>1013</v>
+        <v>1019</v>
       </c>
     </row>
     <row r="149" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -11465,13 +11672,13 @@
         <v>147</v>
       </c>
       <c r="B149" s="5" t="s">
-        <v>1014</v>
+        <v>1020</v>
       </c>
       <c r="C149" s="5" t="s">
-        <v>1015</v>
+        <v>1021</v>
       </c>
       <c r="D149" s="6" t="s">
-        <v>947</v>
+        <v>953</v>
       </c>
       <c r="E149" s="5" t="s">
         <v>492</v>
@@ -11482,13 +11689,13 @@
         <v>148</v>
       </c>
       <c r="B150" s="5" t="s">
-        <v>1016</v>
+        <v>1022</v>
       </c>
       <c r="C150" s="5" t="s">
-        <v>1017</v>
+        <v>1023</v>
       </c>
       <c r="D150" s="6" t="s">
-        <v>951</v>
+        <v>957</v>
       </c>
       <c r="E150" s="5" t="s">
         <v>492</v>
@@ -11499,16 +11706,16 @@
         <v>149</v>
       </c>
       <c r="B151" s="5" t="s">
-        <v>1018</v>
+        <v>1024</v>
       </c>
       <c r="C151" s="5" t="s">
-        <v>1019</v>
+        <v>1025</v>
       </c>
       <c r="D151" s="6" t="s">
-        <v>1020</v>
+        <v>1026</v>
       </c>
       <c r="E151" s="5" t="s">
-        <v>1021</v>
+        <v>1027</v>
       </c>
     </row>
     <row r="152" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -11516,16 +11723,16 @@
         <v>150</v>
       </c>
       <c r="B152" s="5" t="s">
-        <v>1018</v>
+        <v>1024</v>
       </c>
       <c r="C152" s="5" t="s">
-        <v>1022</v>
+        <v>1028</v>
       </c>
       <c r="D152" s="6" t="s">
-        <v>1020</v>
+        <v>1026</v>
       </c>
       <c r="E152" s="5" t="s">
-        <v>1021</v>
+        <v>1027</v>
       </c>
     </row>
     <row r="153" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -11533,16 +11740,16 @@
         <v>151</v>
       </c>
       <c r="B153" s="5" t="s">
-        <v>1023</v>
+        <v>1029</v>
       </c>
       <c r="C153" s="5" t="s">
-        <v>1024</v>
+        <v>1030</v>
       </c>
       <c r="D153" s="6" t="s">
-        <v>1025</v>
+        <v>1031</v>
       </c>
       <c r="E153" s="5" t="s">
-        <v>1026</v>
+        <v>1032</v>
       </c>
     </row>
     <row r="154" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -11550,16 +11757,16 @@
         <v>152</v>
       </c>
       <c r="B154" s="5" t="s">
-        <v>1023</v>
+        <v>1029</v>
       </c>
       <c r="C154" s="5" t="s">
-        <v>1027</v>
+        <v>1033</v>
       </c>
       <c r="D154" s="6" t="s">
-        <v>1025</v>
+        <v>1031</v>
       </c>
       <c r="E154" s="5" t="s">
-        <v>1026</v>
+        <v>1032</v>
       </c>
     </row>
     <row r="155" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -11567,16 +11774,16 @@
         <v>153</v>
       </c>
       <c r="B155" s="5" t="s">
-        <v>1028</v>
+        <v>1034</v>
       </c>
       <c r="C155" s="5" t="s">
-        <v>1029</v>
+        <v>1035</v>
       </c>
       <c r="D155" s="6" t="s">
-        <v>1030</v>
+        <v>1036</v>
       </c>
       <c r="E155" s="5" t="s">
-        <v>1031</v>
+        <v>1037</v>
       </c>
     </row>
     <row r="156" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -11584,16 +11791,16 @@
         <v>154</v>
       </c>
       <c r="B156" s="5" t="s">
-        <v>856</v>
+        <v>862</v>
       </c>
       <c r="C156" s="5" t="s">
-        <v>1032</v>
+        <v>1038</v>
       </c>
       <c r="D156" s="6" t="s">
-        <v>1033</v>
+        <v>1039</v>
       </c>
       <c r="E156" s="5" t="s">
-        <v>1031</v>
+        <v>1037</v>
       </c>
     </row>
     <row r="157" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -11601,14 +11808,14 @@
         <v>155</v>
       </c>
       <c r="B157" s="5" t="s">
-        <v>1034</v>
+        <v>1040</v>
       </c>
       <c r="C157" s="5" t="s">
-        <v>1035</v>
+        <v>1041</v>
       </c>
       <c r="D157" s="5"/>
       <c r="E157" s="5" t="s">
-        <v>1036</v>
+        <v>1042</v>
       </c>
     </row>
     <row r="158" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -11616,16 +11823,16 @@
         <v>156</v>
       </c>
       <c r="B158" s="5" t="s">
-        <v>1037</v>
+        <v>1043</v>
       </c>
       <c r="C158" s="5" t="s">
-        <v>1038</v>
+        <v>1044</v>
       </c>
       <c r="D158" s="6" t="s">
-        <v>1039</v>
+        <v>1045</v>
       </c>
       <c r="E158" s="5" t="s">
-        <v>1036</v>
+        <v>1042</v>
       </c>
     </row>
     <row r="159" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -11633,16 +11840,16 @@
         <v>157</v>
       </c>
       <c r="B159" s="5" t="s">
-        <v>684</v>
+        <v>690</v>
       </c>
       <c r="C159" s="5" t="s">
-        <v>1040</v>
+        <v>1046</v>
       </c>
       <c r="D159" s="6" t="s">
-        <v>1041</v>
+        <v>1047</v>
       </c>
       <c r="E159" s="5" t="s">
-        <v>1042</v>
+        <v>1048</v>
       </c>
     </row>
     <row r="160" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -11650,16 +11857,16 @@
         <v>158</v>
       </c>
       <c r="B160" s="5" t="s">
-        <v>823</v>
+        <v>829</v>
       </c>
       <c r="C160" s="5" t="s">
-        <v>1043</v>
+        <v>1049</v>
       </c>
       <c r="D160" s="6" t="s">
-        <v>1044</v>
+        <v>1050</v>
       </c>
       <c r="E160" s="5" t="s">
-        <v>1042</v>
+        <v>1048</v>
       </c>
     </row>
     <row r="161" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -11667,16 +11874,16 @@
         <v>159</v>
       </c>
       <c r="B161" s="5" t="s">
-        <v>879</v>
+        <v>885</v>
       </c>
       <c r="C161" s="5" t="s">
-        <v>1045</v>
+        <v>1051</v>
       </c>
       <c r="D161" s="6" t="s">
-        <v>1046</v>
+        <v>1052</v>
       </c>
       <c r="E161" s="5" t="s">
-        <v>1042</v>
+        <v>1048</v>
       </c>
     </row>
     <row r="162" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -11684,16 +11891,16 @@
         <v>160</v>
       </c>
       <c r="B162" s="5" t="s">
-        <v>1047</v>
+        <v>1053</v>
       </c>
       <c r="C162" s="5" t="s">
+        <v>1054</v>
+      </c>
+      <c r="D162" s="6" t="s">
+        <v>1055</v>
+      </c>
+      <c r="E162" s="5" t="s">
         <v>1048</v>
-      </c>
-      <c r="D162" s="6" t="s">
-        <v>1049</v>
-      </c>
-      <c r="E162" s="5" t="s">
-        <v>1042</v>
       </c>
     </row>
     <row r="163" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -11701,16 +11908,16 @@
         <v>161</v>
       </c>
       <c r="B163" s="5" t="s">
-        <v>1047</v>
+        <v>1053</v>
       </c>
       <c r="C163" s="5" t="s">
-        <v>1050</v>
+        <v>1056</v>
       </c>
       <c r="D163" s="6" t="s">
-        <v>1051</v>
+        <v>1057</v>
       </c>
       <c r="E163" s="5" t="s">
-        <v>1042</v>
+        <v>1048</v>
       </c>
     </row>
     <row r="164" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -11718,16 +11925,16 @@
         <v>162</v>
       </c>
       <c r="B164" s="5" t="s">
-        <v>890</v>
+        <v>896</v>
       </c>
       <c r="C164" s="5" t="s">
-        <v>1052</v>
+        <v>1058</v>
       </c>
       <c r="D164" s="6" t="s">
-        <v>1053</v>
+        <v>1059</v>
       </c>
       <c r="E164" s="5" t="s">
-        <v>1054</v>
+        <v>1060</v>
       </c>
     </row>
     <row r="165" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -11735,16 +11942,16 @@
         <v>163</v>
       </c>
       <c r="B165" s="5" t="s">
-        <v>684</v>
+        <v>690</v>
       </c>
       <c r="C165" s="5" t="s">
-        <v>1055</v>
+        <v>1061</v>
       </c>
       <c r="D165" s="6" t="s">
-        <v>1056</v>
+        <v>1062</v>
       </c>
       <c r="E165" s="5" t="s">
-        <v>1054</v>
+        <v>1060</v>
       </c>
     </row>
     <row r="166" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -11752,13 +11959,13 @@
         <v>157</v>
       </c>
       <c r="B166" s="5" t="s">
-        <v>1047</v>
+        <v>1053</v>
       </c>
       <c r="C166" s="5" t="s">
-        <v>1057</v>
+        <v>1063</v>
       </c>
       <c r="D166" s="6" t="s">
-        <v>1058</v>
+        <v>1064</v>
       </c>
       <c r="E166" s="5" t="s">
         <v>521</v>
@@ -11769,16 +11976,16 @@
         <v>158</v>
       </c>
       <c r="B167" s="5" t="s">
-        <v>906</v>
+        <v>912</v>
       </c>
       <c r="C167" s="5" t="s">
-        <v>1059</v>
+        <v>1065</v>
       </c>
       <c r="D167" s="6" t="s">
-        <v>1060</v>
+        <v>1066</v>
       </c>
       <c r="E167" s="5" t="s">
-        <v>1061</v>
+        <v>1067</v>
       </c>
     </row>
     <row r="168" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -11786,13 +11993,13 @@
         <v>159</v>
       </c>
       <c r="B168" s="5" t="s">
-        <v>684</v>
+        <v>690</v>
       </c>
       <c r="C168" s="5" t="s">
-        <v>1062</v>
+        <v>1068</v>
       </c>
       <c r="D168" s="6" t="s">
-        <v>1063</v>
+        <v>1069</v>
       </c>
       <c r="E168" s="5" t="s">
         <v>524</v>
@@ -11803,16 +12010,16 @@
         <v>160</v>
       </c>
       <c r="B169" s="5" t="s">
-        <v>879</v>
+        <v>885</v>
       </c>
       <c r="C169" s="5" t="s">
-        <v>1064</v>
+        <v>1070</v>
       </c>
       <c r="D169" s="6" t="s">
-        <v>1065</v>
+        <v>1071</v>
       </c>
       <c r="E169" s="5" t="s">
-        <v>1066</v>
+        <v>1072</v>
       </c>
     </row>
     <row r="170" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -11820,16 +12027,16 @@
         <v>161</v>
       </c>
       <c r="B170" s="5" t="s">
-        <v>879</v>
+        <v>885</v>
       </c>
       <c r="C170" s="5" t="s">
-        <v>1067</v>
+        <v>1073</v>
       </c>
       <c r="D170" s="6" t="s">
-        <v>1068</v>
+        <v>1074</v>
       </c>
       <c r="E170" s="5" t="s">
-        <v>1066</v>
+        <v>1072</v>
       </c>
     </row>
     <row r="171" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -11837,16 +12044,16 @@
         <v>162</v>
       </c>
       <c r="B171" s="5" t="s">
-        <v>879</v>
+        <v>885</v>
       </c>
       <c r="C171" s="5" t="s">
-        <v>1069</v>
+        <v>1075</v>
       </c>
       <c r="D171" s="6" t="s">
-        <v>1070</v>
+        <v>1076</v>
       </c>
       <c r="E171" s="5" t="s">
-        <v>1066</v>
+        <v>1072</v>
       </c>
     </row>
     <row r="172" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -11854,16 +12061,16 @@
         <v>163</v>
       </c>
       <c r="B172" s="5" t="s">
-        <v>829</v>
+        <v>835</v>
       </c>
       <c r="C172" s="5" t="s">
-        <v>1071</v>
+        <v>1077</v>
       </c>
       <c r="D172" s="6" t="s">
-        <v>1072</v>
+        <v>1078</v>
       </c>
       <c r="E172" s="5" t="s">
-        <v>1073</v>
+        <v>1079</v>
       </c>
     </row>
     <row r="173" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -11871,16 +12078,16 @@
         <v>164</v>
       </c>
       <c r="B173" s="5" t="s">
-        <v>823</v>
+        <v>829</v>
       </c>
       <c r="C173" s="5" t="s">
-        <v>1074</v>
+        <v>1080</v>
       </c>
       <c r="D173" s="6" t="s">
-        <v>1075</v>
+        <v>1081</v>
       </c>
       <c r="E173" s="5" t="s">
-        <v>1076</v>
+        <v>1082</v>
       </c>
     </row>
     <row r="174" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -11888,16 +12095,16 @@
         <v>165</v>
       </c>
       <c r="B174" s="5" t="s">
-        <v>823</v>
+        <v>829</v>
       </c>
       <c r="C174" s="5" t="s">
-        <v>1077</v>
+        <v>1083</v>
       </c>
       <c r="D174" s="6" t="s">
-        <v>1078</v>
+        <v>1084</v>
       </c>
       <c r="E174" s="5" t="s">
-        <v>1076</v>
+        <v>1082</v>
       </c>
     </row>
     <row r="175" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -11905,16 +12112,16 @@
         <v>166</v>
       </c>
       <c r="B175" s="5" t="s">
-        <v>823</v>
+        <v>829</v>
       </c>
       <c r="C175" s="5" t="s">
-        <v>1079</v>
+        <v>1085</v>
       </c>
       <c r="D175" s="6" t="s">
-        <v>1080</v>
+        <v>1086</v>
       </c>
       <c r="E175" s="5" t="s">
-        <v>1076</v>
+        <v>1082</v>
       </c>
     </row>
     <row r="176" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -11922,16 +12129,16 @@
         <v>167</v>
       </c>
       <c r="B176" s="5" t="s">
-        <v>890</v>
+        <v>896</v>
       </c>
       <c r="C176" s="5" t="s">
-        <v>1081</v>
+        <v>1087</v>
       </c>
       <c r="D176" s="6" t="s">
-        <v>1082</v>
+        <v>1088</v>
       </c>
       <c r="E176" s="5" t="s">
-        <v>1083</v>
+        <v>1089</v>
       </c>
     </row>
     <row r="177" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -11939,16 +12146,16 @@
         <v>168</v>
       </c>
       <c r="B177" s="5" t="s">
-        <v>684</v>
+        <v>690</v>
       </c>
       <c r="C177" s="5" t="s">
-        <v>1084</v>
+        <v>1090</v>
       </c>
       <c r="D177" s="6" t="s">
-        <v>1085</v>
+        <v>1091</v>
       </c>
       <c r="E177" s="5" t="s">
-        <v>1083</v>
+        <v>1089</v>
       </c>
     </row>
     <row r="178" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -11956,16 +12163,16 @@
         <v>169</v>
       </c>
       <c r="B178" s="5" t="s">
-        <v>684</v>
+        <v>690</v>
       </c>
       <c r="C178" s="5" t="s">
-        <v>1086</v>
+        <v>1092</v>
       </c>
       <c r="D178" s="6" t="s">
-        <v>1087</v>
+        <v>1093</v>
       </c>
       <c r="E178" s="5" t="s">
-        <v>1083</v>
+        <v>1089</v>
       </c>
     </row>
     <row r="179" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -11973,16 +12180,16 @@
         <v>170</v>
       </c>
       <c r="B179" s="5" t="s">
-        <v>906</v>
+        <v>912</v>
       </c>
       <c r="C179" s="5" t="s">
-        <v>1088</v>
+        <v>1094</v>
       </c>
       <c r="D179" s="6" t="s">
+        <v>1095</v>
+      </c>
+      <c r="E179" s="5" t="s">
         <v>1089</v>
-      </c>
-      <c r="E179" s="5" t="s">
-        <v>1083</v>
       </c>
     </row>
     <row r="180" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -11990,16 +12197,16 @@
         <v>171</v>
       </c>
       <c r="B180" s="5" t="s">
-        <v>906</v>
+        <v>912</v>
       </c>
       <c r="C180" s="5" t="s">
-        <v>1090</v>
+        <v>1096</v>
       </c>
       <c r="D180" s="6" t="s">
-        <v>1091</v>
+        <v>1097</v>
       </c>
       <c r="E180" s="5" t="s">
-        <v>1083</v>
+        <v>1089</v>
       </c>
     </row>
     <row r="181" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -12007,16 +12214,16 @@
         <v>172</v>
       </c>
       <c r="B181" s="5" t="s">
-        <v>879</v>
+        <v>885</v>
       </c>
       <c r="C181" s="5" t="s">
-        <v>1092</v>
+        <v>1098</v>
       </c>
       <c r="D181" s="6" t="s">
-        <v>1093</v>
+        <v>1099</v>
       </c>
       <c r="E181" s="5" t="s">
-        <v>1094</v>
+        <v>1100</v>
       </c>
     </row>
     <row r="182" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -12024,16 +12231,16 @@
         <v>173</v>
       </c>
       <c r="B182" s="5" t="s">
-        <v>684</v>
+        <v>690</v>
       </c>
       <c r="C182" s="5" t="s">
-        <v>1095</v>
+        <v>1101</v>
       </c>
       <c r="D182" s="6" t="s">
-        <v>1096</v>
+        <v>1102</v>
       </c>
       <c r="E182" s="5" t="s">
-        <v>1097</v>
+        <v>1103</v>
       </c>
     </row>
     <row r="183" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -12041,16 +12248,16 @@
         <v>174</v>
       </c>
       <c r="B183" s="5" t="s">
-        <v>684</v>
+        <v>690</v>
       </c>
       <c r="C183" s="5" t="s">
-        <v>1098</v>
+        <v>1104</v>
       </c>
       <c r="D183" s="6" t="s">
-        <v>1099</v>
+        <v>1105</v>
       </c>
       <c r="E183" s="5" t="s">
-        <v>1097</v>
+        <v>1103</v>
       </c>
     </row>
     <row r="184" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -12058,16 +12265,16 @@
         <v>175</v>
       </c>
       <c r="B184" s="5" t="s">
-        <v>684</v>
+        <v>690</v>
       </c>
       <c r="C184" s="5" t="s">
-        <v>1100</v>
+        <v>1106</v>
       </c>
       <c r="D184" s="6" t="s">
-        <v>1101</v>
+        <v>1107</v>
       </c>
       <c r="E184" s="5" t="s">
-        <v>1097</v>
+        <v>1103</v>
       </c>
     </row>
     <row r="185" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -12075,16 +12282,16 @@
         <v>176</v>
       </c>
       <c r="B185" s="5" t="s">
-        <v>1047</v>
+        <v>1053</v>
       </c>
       <c r="C185" s="5" t="s">
-        <v>1102</v>
+        <v>1108</v>
       </c>
       <c r="D185" s="6" t="s">
+        <v>1109</v>
+      </c>
+      <c r="E185" s="5" t="s">
         <v>1103</v>
-      </c>
-      <c r="E185" s="5" t="s">
-        <v>1097</v>
       </c>
     </row>
     <row r="186" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -12092,16 +12299,16 @@
         <v>177</v>
       </c>
       <c r="B186" s="5" t="s">
-        <v>1047</v>
+        <v>1053</v>
       </c>
       <c r="C186" s="5" t="s">
-        <v>1104</v>
+        <v>1110</v>
       </c>
       <c r="D186" s="6" t="s">
-        <v>1105</v>
+        <v>1111</v>
       </c>
       <c r="E186" s="5" t="s">
-        <v>1097</v>
+        <v>1103</v>
       </c>
     </row>
     <row r="187" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -12109,16 +12316,16 @@
         <v>178</v>
       </c>
       <c r="B187" s="5" t="s">
-        <v>1047</v>
+        <v>1053</v>
       </c>
       <c r="C187" s="5" t="s">
-        <v>1106</v>
+        <v>1112</v>
       </c>
       <c r="D187" s="6" t="s">
-        <v>1107</v>
+        <v>1113</v>
       </c>
       <c r="E187" s="5" t="s">
-        <v>1097</v>
+        <v>1103</v>
       </c>
     </row>
     <row r="188" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -12126,16 +12333,16 @@
         <v>179</v>
       </c>
       <c r="B188" s="5" t="s">
-        <v>684</v>
+        <v>690</v>
       </c>
       <c r="C188" s="5" t="s">
-        <v>1108</v>
+        <v>1114</v>
       </c>
       <c r="D188" s="6" t="s">
-        <v>1109</v>
+        <v>1115</v>
       </c>
       <c r="E188" s="5" t="s">
-        <v>1110</v>
+        <v>1116</v>
       </c>
     </row>
     <row r="189" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -12143,16 +12350,16 @@
         <v>180</v>
       </c>
       <c r="B189" s="5" t="s">
-        <v>684</v>
+        <v>690</v>
       </c>
       <c r="C189" s="5" t="s">
-        <v>1111</v>
+        <v>1117</v>
       </c>
       <c r="D189" s="6" t="s">
-        <v>1112</v>
+        <v>1118</v>
       </c>
       <c r="E189" s="5" t="s">
-        <v>1110</v>
+        <v>1116</v>
       </c>
     </row>
     <row r="190" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -12160,16 +12367,16 @@
         <v>181</v>
       </c>
       <c r="B190" s="5" t="s">
-        <v>879</v>
+        <v>885</v>
       </c>
       <c r="C190" s="5" t="s">
-        <v>1113</v>
+        <v>1119</v>
       </c>
       <c r="D190" s="6" t="s">
-        <v>1114</v>
+        <v>1120</v>
       </c>
       <c r="E190" s="5" t="s">
-        <v>1110</v>
+        <v>1116</v>
       </c>
     </row>
     <row r="191" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -12177,16 +12384,16 @@
         <v>182</v>
       </c>
       <c r="B191" s="5" t="s">
-        <v>1047</v>
+        <v>1053</v>
       </c>
       <c r="C191" s="5" t="s">
-        <v>1115</v>
+        <v>1121</v>
       </c>
       <c r="D191" s="6" t="s">
+        <v>1122</v>
+      </c>
+      <c r="E191" s="5" t="s">
         <v>1116</v>
-      </c>
-      <c r="E191" s="5" t="s">
-        <v>1110</v>
       </c>
     </row>
     <row r="192" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -12194,16 +12401,16 @@
         <v>183</v>
       </c>
       <c r="B192" s="5" t="s">
-        <v>1047</v>
+        <v>1053</v>
       </c>
       <c r="C192" s="5" t="s">
-        <v>1117</v>
+        <v>1123</v>
       </c>
       <c r="D192" s="6" t="s">
-        <v>1118</v>
+        <v>1124</v>
       </c>
       <c r="E192" s="5" t="s">
-        <v>1110</v>
+        <v>1116</v>
       </c>
     </row>
     <row r="193" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -12211,13 +12418,13 @@
         <v>184</v>
       </c>
       <c r="B193" s="5" t="s">
-        <v>879</v>
+        <v>885</v>
       </c>
       <c r="C193" s="5" t="s">
-        <v>1119</v>
+        <v>1125</v>
       </c>
       <c r="D193" s="6" t="s">
-        <v>1120</v>
+        <v>1126</v>
       </c>
       <c r="E193" s="5" t="s">
         <v>533</v>
@@ -12228,16 +12435,16 @@
         <v>185</v>
       </c>
       <c r="B194" s="5" t="s">
-        <v>879</v>
+        <v>885</v>
       </c>
       <c r="C194" s="5" t="s">
-        <v>1121</v>
+        <v>1127</v>
       </c>
       <c r="D194" s="6" t="s">
-        <v>1122</v>
+        <v>1128</v>
       </c>
       <c r="E194" s="5" t="s">
-        <v>1123</v>
+        <v>1129</v>
       </c>
     </row>
     <row r="195" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -12245,16 +12452,16 @@
         <v>186</v>
       </c>
       <c r="B195" s="5" t="s">
-        <v>684</v>
+        <v>690</v>
       </c>
       <c r="C195" s="5" t="s">
-        <v>1124</v>
+        <v>1130</v>
       </c>
       <c r="D195" s="6" t="s">
-        <v>1125</v>
+        <v>1131</v>
       </c>
       <c r="E195" s="5" t="s">
-        <v>1126</v>
+        <v>1132</v>
       </c>
     </row>
     <row r="196" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -12262,16 +12469,16 @@
         <v>187</v>
       </c>
       <c r="B196" s="5" t="s">
-        <v>823</v>
+        <v>829</v>
       </c>
       <c r="C196" s="5" t="s">
-        <v>1127</v>
+        <v>1133</v>
       </c>
       <c r="D196" s="6" t="s">
-        <v>1128</v>
+        <v>1134</v>
       </c>
       <c r="E196" s="5" t="s">
-        <v>1126</v>
+        <v>1132</v>
       </c>
     </row>
     <row r="197" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -12279,16 +12486,16 @@
         <v>188</v>
       </c>
       <c r="B197" s="5" t="s">
-        <v>1047</v>
+        <v>1053</v>
       </c>
       <c r="C197" s="5" t="s">
-        <v>1129</v>
+        <v>1135</v>
       </c>
       <c r="D197" s="6" t="s">
-        <v>1130</v>
+        <v>1136</v>
       </c>
       <c r="E197" s="5" t="s">
-        <v>1126</v>
+        <v>1132</v>
       </c>
     </row>
     <row r="198" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -12296,16 +12503,16 @@
         <v>189</v>
       </c>
       <c r="B198" s="5" t="s">
-        <v>1047</v>
+        <v>1053</v>
       </c>
       <c r="C198" s="5" t="s">
-        <v>1131</v>
+        <v>1137</v>
       </c>
       <c r="D198" s="6" t="s">
+        <v>1138</v>
+      </c>
+      <c r="E198" s="5" t="s">
         <v>1132</v>
-      </c>
-      <c r="E198" s="5" t="s">
-        <v>1126</v>
       </c>
     </row>
     <row r="199" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -12313,16 +12520,16 @@
         <v>190</v>
       </c>
       <c r="B199" s="5" t="s">
-        <v>890</v>
+        <v>896</v>
       </c>
       <c r="C199" s="5" t="s">
-        <v>1133</v>
+        <v>1139</v>
       </c>
       <c r="D199" s="6" t="s">
-        <v>1134</v>
+        <v>1140</v>
       </c>
       <c r="E199" s="5" t="s">
-        <v>1135</v>
+        <v>1141</v>
       </c>
     </row>
     <row r="200" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -12330,16 +12537,16 @@
         <v>191</v>
       </c>
       <c r="B200" s="5" t="s">
-        <v>890</v>
+        <v>896</v>
       </c>
       <c r="C200" s="5" t="s">
-        <v>1136</v>
+        <v>1142</v>
       </c>
       <c r="D200" s="6" t="s">
-        <v>1137</v>
+        <v>1143</v>
       </c>
       <c r="E200" s="5" t="s">
-        <v>1135</v>
+        <v>1141</v>
       </c>
     </row>
     <row r="201" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -12347,16 +12554,16 @@
         <v>192</v>
       </c>
       <c r="B201" s="5" t="s">
-        <v>684</v>
+        <v>690</v>
       </c>
       <c r="C201" s="5" t="s">
-        <v>1138</v>
+        <v>1144</v>
       </c>
       <c r="D201" s="6" t="s">
-        <v>1139</v>
+        <v>1145</v>
       </c>
       <c r="E201" s="5" t="s">
-        <v>1135</v>
+        <v>1141</v>
       </c>
     </row>
     <row r="202" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -12364,16 +12571,16 @@
         <v>193</v>
       </c>
       <c r="B202" s="5" t="s">
-        <v>684</v>
+        <v>690</v>
       </c>
       <c r="C202" s="5" t="s">
-        <v>1140</v>
+        <v>1146</v>
       </c>
       <c r="D202" s="6" t="s">
-        <v>1141</v>
+        <v>1147</v>
       </c>
       <c r="E202" s="5" t="s">
-        <v>1142</v>
+        <v>1148</v>
       </c>
     </row>
     <row r="203" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -12381,16 +12588,16 @@
         <v>194</v>
       </c>
       <c r="B203" s="5" t="s">
-        <v>684</v>
+        <v>690</v>
       </c>
       <c r="C203" s="5" t="s">
-        <v>1143</v>
+        <v>1149</v>
       </c>
       <c r="D203" s="6" t="s">
-        <v>1144</v>
+        <v>1150</v>
       </c>
       <c r="E203" s="5" t="s">
-        <v>1142</v>
+        <v>1148</v>
       </c>
     </row>
     <row r="204" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -12398,16 +12605,16 @@
         <v>195</v>
       </c>
       <c r="B204" s="5" t="s">
-        <v>684</v>
+        <v>690</v>
       </c>
       <c r="C204" s="5" t="s">
-        <v>1145</v>
+        <v>1151</v>
       </c>
       <c r="D204" s="6" t="s">
-        <v>1146</v>
+        <v>1152</v>
       </c>
       <c r="E204" s="5" t="s">
-        <v>1147</v>
+        <v>1153</v>
       </c>
     </row>
     <row r="205" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -12415,13 +12622,13 @@
         <v>196</v>
       </c>
       <c r="B205" s="5" t="s">
-        <v>879</v>
+        <v>885</v>
       </c>
       <c r="C205" s="5" t="s">
-        <v>1148</v>
+        <v>1154</v>
       </c>
       <c r="D205" s="6" t="s">
-        <v>1149</v>
+        <v>1155</v>
       </c>
       <c r="E205" s="5" t="s">
         <v>540</v>
@@ -12432,16 +12639,16 @@
         <v>197</v>
       </c>
       <c r="B206" s="5" t="s">
-        <v>684</v>
+        <v>690</v>
       </c>
       <c r="C206" s="5" t="s">
-        <v>1150</v>
+        <v>1156</v>
       </c>
       <c r="D206" s="6" t="s">
-        <v>1151</v>
+        <v>1157</v>
       </c>
       <c r="E206" s="5" t="s">
-        <v>1152</v>
+        <v>1158</v>
       </c>
     </row>
     <row r="207" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -12449,16 +12656,16 @@
         <v>198</v>
       </c>
       <c r="B207" s="5" t="s">
-        <v>906</v>
+        <v>912</v>
       </c>
       <c r="C207" s="5" t="s">
-        <v>1153</v>
+        <v>1159</v>
       </c>
       <c r="D207" s="6" t="s">
-        <v>1154</v>
+        <v>1160</v>
       </c>
       <c r="E207" s="5" t="s">
-        <v>1152</v>
+        <v>1158</v>
       </c>
     </row>
     <row r="208" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -12466,16 +12673,16 @@
         <v>199</v>
       </c>
       <c r="B208" s="5" t="s">
-        <v>1047</v>
+        <v>1053</v>
       </c>
       <c r="C208" s="5" t="s">
-        <v>1155</v>
+        <v>1161</v>
       </c>
       <c r="D208" s="6" t="s">
-        <v>1156</v>
+        <v>1162</v>
       </c>
       <c r="E208" s="5" t="s">
-        <v>1152</v>
+        <v>1158</v>
       </c>
     </row>
     <row r="209" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -12483,16 +12690,16 @@
         <v>200</v>
       </c>
       <c r="B209" s="5" t="s">
-        <v>1047</v>
+        <v>1053</v>
       </c>
       <c r="C209" s="5" t="s">
-        <v>1157</v>
+        <v>1163</v>
       </c>
       <c r="D209" s="6" t="s">
+        <v>1164</v>
+      </c>
+      <c r="E209" s="5" t="s">
         <v>1158</v>
-      </c>
-      <c r="E209" s="5" t="s">
-        <v>1152</v>
       </c>
     </row>
     <row r="210" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -12500,16 +12707,16 @@
         <v>201</v>
       </c>
       <c r="B210" s="5" t="s">
-        <v>823</v>
+        <v>829</v>
       </c>
       <c r="C210" s="5" t="s">
-        <v>1159</v>
+        <v>1165</v>
       </c>
       <c r="D210" s="6" t="s">
-        <v>1160</v>
+        <v>1166</v>
       </c>
       <c r="E210" s="5" t="s">
-        <v>1161</v>
+        <v>1167</v>
       </c>
     </row>
     <row r="211" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -12517,16 +12724,16 @@
         <v>202</v>
       </c>
       <c r="B211" s="5" t="s">
-        <v>906</v>
+        <v>912</v>
       </c>
       <c r="C211" s="5" t="s">
-        <v>1162</v>
+        <v>1168</v>
       </c>
       <c r="D211" s="6" t="s">
-        <v>1163</v>
+        <v>1169</v>
       </c>
       <c r="E211" s="5" t="s">
-        <v>1161</v>
+        <v>1167</v>
       </c>
     </row>
     <row r="212" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -12534,16 +12741,16 @@
         <v>203</v>
       </c>
       <c r="B212" s="5" t="s">
-        <v>906</v>
+        <v>912</v>
       </c>
       <c r="C212" s="5" t="s">
-        <v>1164</v>
+        <v>1170</v>
       </c>
       <c r="D212" s="6" t="s">
-        <v>1165</v>
+        <v>1171</v>
       </c>
       <c r="E212" s="5" t="s">
-        <v>1161</v>
+        <v>1167</v>
       </c>
     </row>
     <row r="213" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -12551,16 +12758,16 @@
         <v>204</v>
       </c>
       <c r="B213" s="5" t="s">
-        <v>879</v>
+        <v>885</v>
       </c>
       <c r="C213" s="5" t="s">
-        <v>1166</v>
+        <v>1172</v>
       </c>
       <c r="D213" s="6" t="s">
-        <v>1167</v>
+        <v>1173</v>
       </c>
       <c r="E213" s="5" t="s">
-        <v>1061</v>
+        <v>1067</v>
       </c>
     </row>
     <row r="214" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -12568,16 +12775,16 @@
         <v>205</v>
       </c>
       <c r="B214" s="5" t="s">
-        <v>684</v>
+        <v>690</v>
       </c>
       <c r="C214" s="5" t="s">
-        <v>1168</v>
+        <v>1174</v>
       </c>
       <c r="D214" s="6" t="s">
-        <v>1169</v>
+        <v>1175</v>
       </c>
       <c r="E214" s="5" t="s">
-        <v>1170</v>
+        <v>1176</v>
       </c>
     </row>
     <row r="215" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -12585,16 +12792,16 @@
         <v>206</v>
       </c>
       <c r="B215" s="5" t="s">
-        <v>823</v>
+        <v>829</v>
       </c>
       <c r="C215" s="5" t="s">
-        <v>1171</v>
+        <v>1177</v>
       </c>
       <c r="D215" s="6" t="s">
-        <v>1172</v>
+        <v>1178</v>
       </c>
       <c r="E215" s="5" t="s">
-        <v>1173</v>
+        <v>1179</v>
       </c>
     </row>
     <row r="216" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -12602,16 +12809,16 @@
         <v>207</v>
       </c>
       <c r="B216" s="5" t="s">
-        <v>906</v>
+        <v>912</v>
       </c>
       <c r="C216" s="5" t="s">
-        <v>1174</v>
+        <v>1180</v>
       </c>
       <c r="D216" s="6" t="s">
-        <v>1175</v>
+        <v>1181</v>
       </c>
       <c r="E216" s="5" t="s">
-        <v>1173</v>
+        <v>1179</v>
       </c>
     </row>
     <row r="217" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -12619,16 +12826,16 @@
         <v>208</v>
       </c>
       <c r="B217" s="5" t="s">
-        <v>684</v>
+        <v>690</v>
       </c>
       <c r="C217" s="5" t="s">
-        <v>1176</v>
+        <v>1182</v>
       </c>
       <c r="D217" s="6" t="s">
-        <v>1177</v>
+        <v>1183</v>
       </c>
       <c r="E217" s="5" t="s">
-        <v>1178</v>
+        <v>1184</v>
       </c>
     </row>
     <row r="218" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -12636,16 +12843,16 @@
         <v>209</v>
       </c>
       <c r="B218" s="5" t="s">
-        <v>823</v>
+        <v>829</v>
       </c>
       <c r="C218" s="5" t="s">
-        <v>1179</v>
+        <v>1185</v>
       </c>
       <c r="D218" s="6" t="s">
-        <v>1180</v>
+        <v>1186</v>
       </c>
       <c r="E218" s="5" t="s">
-        <v>1178</v>
+        <v>1184</v>
       </c>
     </row>
     <row r="219" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -12653,16 +12860,16 @@
         <v>210</v>
       </c>
       <c r="B219" s="5" t="s">
-        <v>906</v>
+        <v>912</v>
       </c>
       <c r="C219" s="5" t="s">
-        <v>1181</v>
+        <v>1187</v>
       </c>
       <c r="D219" s="6" t="s">
-        <v>1182</v>
+        <v>1188</v>
       </c>
       <c r="E219" s="5" t="s">
-        <v>1178</v>
+        <v>1184</v>
       </c>
     </row>
     <row r="220" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -12670,16 +12877,16 @@
         <v>211</v>
       </c>
       <c r="B220" s="5" t="s">
-        <v>1047</v>
+        <v>1053</v>
       </c>
       <c r="C220" s="5" t="s">
-        <v>1183</v>
+        <v>1189</v>
       </c>
       <c r="D220" s="6" t="s">
+        <v>1190</v>
+      </c>
+      <c r="E220" s="5" t="s">
         <v>1184</v>
-      </c>
-      <c r="E220" s="5" t="s">
-        <v>1178</v>
       </c>
     </row>
     <row r="221" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -12687,16 +12894,16 @@
         <v>212</v>
       </c>
       <c r="B221" s="5" t="s">
-        <v>879</v>
+        <v>885</v>
       </c>
       <c r="C221" s="5" t="s">
-        <v>1185</v>
+        <v>1191</v>
       </c>
       <c r="D221" s="6" t="s">
-        <v>1186</v>
+        <v>1192</v>
       </c>
       <c r="E221" s="5" t="s">
-        <v>1187</v>
+        <v>1193</v>
       </c>
     </row>
     <row r="222" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -12704,16 +12911,16 @@
         <v>213</v>
       </c>
       <c r="B222" s="5" t="s">
-        <v>684</v>
+        <v>690</v>
       </c>
       <c r="C222" s="5" t="s">
-        <v>1188</v>
+        <v>1194</v>
       </c>
       <c r="D222" s="6" t="s">
-        <v>1189</v>
+        <v>1195</v>
       </c>
       <c r="E222" s="5" t="s">
-        <v>1190</v>
+        <v>1196</v>
       </c>
     </row>
     <row r="223" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -12721,16 +12928,16 @@
         <v>214</v>
       </c>
       <c r="B223" s="5" t="s">
-        <v>879</v>
+        <v>885</v>
       </c>
       <c r="C223" s="5" t="s">
-        <v>1191</v>
+        <v>1197</v>
       </c>
       <c r="D223" s="6" t="s">
-        <v>1192</v>
+        <v>1198</v>
       </c>
       <c r="E223" s="5" t="s">
-        <v>1190</v>
+        <v>1196</v>
       </c>
     </row>
     <row r="224" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -12738,16 +12945,16 @@
         <v>215</v>
       </c>
       <c r="B224" s="5" t="s">
-        <v>879</v>
+        <v>885</v>
       </c>
       <c r="C224" s="5" t="s">
-        <v>1193</v>
+        <v>1199</v>
       </c>
       <c r="D224" s="6" t="s">
-        <v>1194</v>
+        <v>1200</v>
       </c>
       <c r="E224" s="5" t="s">
-        <v>1190</v>
+        <v>1196</v>
       </c>
     </row>
     <row r="225" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -12755,16 +12962,16 @@
         <v>216</v>
       </c>
       <c r="B225" s="5" t="s">
-        <v>1047</v>
+        <v>1053</v>
       </c>
       <c r="C225" s="5" t="s">
-        <v>1195</v>
+        <v>1201</v>
       </c>
       <c r="D225" s="6" t="s">
+        <v>1202</v>
+      </c>
+      <c r="E225" s="5" t="s">
         <v>1196</v>
-      </c>
-      <c r="E225" s="5" t="s">
-        <v>1190</v>
       </c>
     </row>
     <row r="226" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -12772,16 +12979,16 @@
         <v>217</v>
       </c>
       <c r="B226" s="5" t="s">
-        <v>890</v>
+        <v>896</v>
       </c>
       <c r="C226" s="5" t="s">
-        <v>1197</v>
+        <v>1203</v>
       </c>
       <c r="D226" s="6" t="s">
-        <v>1198</v>
+        <v>1204</v>
       </c>
       <c r="E226" s="5" t="s">
-        <v>1199</v>
+        <v>1205</v>
       </c>
     </row>
     <row r="227" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -12789,16 +12996,16 @@
         <v>218</v>
       </c>
       <c r="B227" s="5" t="s">
-        <v>684</v>
+        <v>690</v>
       </c>
       <c r="C227" s="5" t="s">
-        <v>1200</v>
+        <v>1206</v>
       </c>
       <c r="D227" s="6" t="s">
-        <v>1201</v>
+        <v>1207</v>
       </c>
       <c r="E227" s="5" t="s">
-        <v>1199</v>
+        <v>1205</v>
       </c>
     </row>
     <row r="228" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -12806,16 +13013,16 @@
         <v>219</v>
       </c>
       <c r="B228" s="5" t="s">
-        <v>823</v>
+        <v>829</v>
       </c>
       <c r="C228" s="5" t="s">
-        <v>1202</v>
+        <v>1208</v>
       </c>
       <c r="D228" s="6" t="s">
-        <v>1203</v>
+        <v>1209</v>
       </c>
       <c r="E228" s="5" t="s">
-        <v>1199</v>
+        <v>1205</v>
       </c>
     </row>
     <row r="229" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -12823,16 +13030,16 @@
         <v>220</v>
       </c>
       <c r="B229" s="5" t="s">
-        <v>1047</v>
+        <v>1053</v>
       </c>
       <c r="C229" s="5" t="s">
-        <v>1204</v>
+        <v>1210</v>
       </c>
       <c r="D229" s="6" t="s">
+        <v>1211</v>
+      </c>
+      <c r="E229" s="5" t="s">
         <v>1205</v>
-      </c>
-      <c r="E229" s="5" t="s">
-        <v>1199</v>
       </c>
     </row>
     <row r="230" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -12840,16 +13047,16 @@
         <v>221</v>
       </c>
       <c r="B230" s="5" t="s">
-        <v>684</v>
+        <v>690</v>
       </c>
       <c r="C230" s="5" t="s">
-        <v>1206</v>
+        <v>1212</v>
       </c>
       <c r="D230" s="6" t="s">
-        <v>1207</v>
+        <v>1213</v>
       </c>
       <c r="E230" s="5" t="s">
-        <v>1208</v>
+        <v>1214</v>
       </c>
     </row>
     <row r="231" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -12857,16 +13064,16 @@
         <v>222</v>
       </c>
       <c r="B231" s="5" t="s">
-        <v>879</v>
+        <v>885</v>
       </c>
       <c r="C231" s="5" t="s">
-        <v>1209</v>
+        <v>1215</v>
       </c>
       <c r="D231" s="6" t="s">
-        <v>1210</v>
+        <v>1216</v>
       </c>
       <c r="E231" s="5" t="s">
-        <v>1208</v>
+        <v>1214</v>
       </c>
     </row>
     <row r="232" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -12874,16 +13081,16 @@
         <v>223</v>
       </c>
       <c r="B232" s="5" t="s">
-        <v>684</v>
+        <v>690</v>
       </c>
       <c r="C232" s="5" t="s">
-        <v>1211</v>
+        <v>1217</v>
       </c>
       <c r="D232" s="6" t="s">
-        <v>1212</v>
+        <v>1218</v>
       </c>
       <c r="E232" s="5" t="s">
-        <v>1213</v>
+        <v>1219</v>
       </c>
     </row>
     <row r="233" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -12891,16 +13098,16 @@
         <v>224</v>
       </c>
       <c r="B233" s="5" t="s">
-        <v>906</v>
+        <v>912</v>
       </c>
       <c r="C233" s="5" t="s">
-        <v>1214</v>
+        <v>1220</v>
       </c>
       <c r="D233" s="6" t="s">
-        <v>1215</v>
+        <v>1221</v>
       </c>
       <c r="E233" s="5" t="s">
-        <v>1213</v>
+        <v>1219</v>
       </c>
     </row>
     <row r="234" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -12908,16 +13115,16 @@
         <v>225</v>
       </c>
       <c r="B234" s="5" t="s">
-        <v>684</v>
+        <v>690</v>
       </c>
       <c r="C234" s="5" t="s">
-        <v>1216</v>
+        <v>1222</v>
       </c>
       <c r="D234" s="6" t="s">
-        <v>1217</v>
+        <v>1223</v>
       </c>
       <c r="E234" s="5" t="s">
-        <v>1218</v>
+        <v>1224</v>
       </c>
     </row>
     <row r="235" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -12925,16 +13132,16 @@
         <v>226</v>
       </c>
       <c r="B235" s="5" t="s">
-        <v>823</v>
+        <v>829</v>
       </c>
       <c r="C235" s="5" t="s">
-        <v>1219</v>
+        <v>1225</v>
       </c>
       <c r="D235" s="6" t="s">
-        <v>1220</v>
+        <v>1226</v>
       </c>
       <c r="E235" s="5" t="s">
-        <v>1218</v>
+        <v>1224</v>
       </c>
     </row>
     <row r="236" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -12942,16 +13149,16 @@
         <v>227</v>
       </c>
       <c r="B236" s="5" t="s">
-        <v>906</v>
+        <v>912</v>
       </c>
       <c r="C236" s="5" t="s">
-        <v>1221</v>
+        <v>1227</v>
       </c>
       <c r="D236" s="6" t="s">
-        <v>1222</v>
+        <v>1228</v>
       </c>
       <c r="E236" s="5" t="s">
-        <v>1218</v>
+        <v>1224</v>
       </c>
     </row>
     <row r="237" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -12959,16 +13166,16 @@
         <v>228</v>
       </c>
       <c r="B237" s="5" t="s">
-        <v>906</v>
+        <v>912</v>
       </c>
       <c r="C237" s="5" t="s">
-        <v>1223</v>
+        <v>1229</v>
       </c>
       <c r="D237" s="6" t="s">
-        <v>1224</v>
+        <v>1230</v>
       </c>
       <c r="E237" s="5" t="s">
-        <v>1225</v>
+        <v>1231</v>
       </c>
     </row>
     <row r="238" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -12976,16 +13183,16 @@
         <v>229</v>
       </c>
       <c r="B238" s="5" t="s">
-        <v>879</v>
+        <v>885</v>
       </c>
       <c r="C238" s="5" t="s">
-        <v>1226</v>
+        <v>1232</v>
       </c>
       <c r="D238" s="6" t="s">
-        <v>1227</v>
+        <v>1233</v>
       </c>
       <c r="E238" s="5" t="s">
-        <v>1225</v>
+        <v>1231</v>
       </c>
     </row>
     <row r="239" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -12993,16 +13200,16 @@
         <v>230</v>
       </c>
       <c r="B239" s="5" t="s">
-        <v>879</v>
+        <v>885</v>
       </c>
       <c r="C239" s="5" t="s">
-        <v>1228</v>
+        <v>1234</v>
       </c>
       <c r="D239" s="6" t="s">
-        <v>1229</v>
+        <v>1235</v>
       </c>
       <c r="E239" s="5" t="s">
-        <v>1225</v>
+        <v>1231</v>
       </c>
     </row>
     <row r="240" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -13010,16 +13217,16 @@
         <v>231</v>
       </c>
       <c r="B240" s="5" t="s">
-        <v>1047</v>
+        <v>1053</v>
       </c>
       <c r="C240" s="5" t="s">
-        <v>1230</v>
+        <v>1236</v>
       </c>
       <c r="D240" s="6" t="s">
+        <v>1237</v>
+      </c>
+      <c r="E240" s="5" t="s">
         <v>1231</v>
-      </c>
-      <c r="E240" s="5" t="s">
-        <v>1225</v>
       </c>
     </row>
     <row r="241" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -13027,16 +13234,16 @@
         <v>232</v>
       </c>
       <c r="B241" s="5" t="s">
-        <v>1047</v>
+        <v>1053</v>
       </c>
       <c r="C241" s="5" t="s">
-        <v>1232</v>
+        <v>1238</v>
       </c>
       <c r="D241" s="6" t="s">
-        <v>1233</v>
+        <v>1239</v>
       </c>
       <c r="E241" s="5" t="s">
-        <v>1225</v>
+        <v>1231</v>
       </c>
     </row>
     <row r="242" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -13044,13 +13251,13 @@
         <v>233</v>
       </c>
       <c r="B242" s="5" t="s">
-        <v>879</v>
+        <v>885</v>
       </c>
       <c r="C242" s="5" t="s">
-        <v>1234</v>
+        <v>1240</v>
       </c>
       <c r="D242" s="6" t="s">
-        <v>1235</v>
+        <v>1241</v>
       </c>
       <c r="E242" s="5" t="s">
         <v>559</v>
@@ -13061,16 +13268,16 @@
         <v>234</v>
       </c>
       <c r="B243" s="5" t="s">
-        <v>890</v>
+        <v>896</v>
       </c>
       <c r="C243" s="5" t="s">
-        <v>1236</v>
+        <v>1242</v>
       </c>
       <c r="D243" s="6" t="s">
-        <v>1237</v>
+        <v>1243</v>
       </c>
       <c r="E243" s="5" t="s">
-        <v>1238</v>
+        <v>1244</v>
       </c>
     </row>
     <row r="244" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -13078,16 +13285,16 @@
         <v>235</v>
       </c>
       <c r="B244" s="5" t="s">
-        <v>684</v>
+        <v>690</v>
       </c>
       <c r="C244" s="5" t="s">
-        <v>1239</v>
+        <v>1245</v>
       </c>
       <c r="D244" s="6" t="s">
-        <v>1240</v>
+        <v>1246</v>
       </c>
       <c r="E244" s="5" t="s">
-        <v>1238</v>
+        <v>1244</v>
       </c>
     </row>
     <row r="245" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -13095,16 +13302,16 @@
         <v>236</v>
       </c>
       <c r="B245" s="5" t="s">
-        <v>684</v>
+        <v>690</v>
       </c>
       <c r="C245" s="5" t="s">
-        <v>1241</v>
+        <v>1247</v>
       </c>
       <c r="D245" s="6" t="s">
-        <v>1242</v>
+        <v>1248</v>
       </c>
       <c r="E245" s="5" t="s">
-        <v>1238</v>
+        <v>1244</v>
       </c>
     </row>
     <row r="246" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -13112,16 +13319,16 @@
         <v>237</v>
       </c>
       <c r="B246" s="5" t="s">
-        <v>879</v>
+        <v>885</v>
       </c>
       <c r="C246" s="5" t="s">
-        <v>1243</v>
+        <v>1249</v>
       </c>
       <c r="D246" s="6" t="s">
+        <v>1250</v>
+      </c>
+      <c r="E246" s="5" t="s">
         <v>1244</v>
-      </c>
-      <c r="E246" s="5" t="s">
-        <v>1238</v>
       </c>
     </row>
     <row r="247" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -13129,13 +13336,13 @@
         <v>238</v>
       </c>
       <c r="B247" s="5" t="s">
-        <v>823</v>
+        <v>829</v>
       </c>
       <c r="C247" s="5" t="s">
-        <v>1245</v>
+        <v>1251</v>
       </c>
       <c r="D247" s="6" t="s">
-        <v>1246</v>
+        <v>1252</v>
       </c>
       <c r="E247" s="5" t="s">
         <v>562</v>
@@ -13146,16 +13353,16 @@
         <v>239</v>
       </c>
       <c r="B248" s="5" t="s">
-        <v>684</v>
+        <v>690</v>
       </c>
       <c r="C248" s="5" t="s">
-        <v>1247</v>
+        <v>1253</v>
       </c>
       <c r="D248" s="6" t="s">
-        <v>1248</v>
+        <v>1254</v>
       </c>
       <c r="E248" s="5" t="s">
-        <v>1249</v>
+        <v>1255</v>
       </c>
     </row>
     <row r="249" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -13163,16 +13370,16 @@
         <v>240</v>
       </c>
       <c r="B249" s="5" t="s">
-        <v>823</v>
+        <v>829</v>
       </c>
       <c r="C249" s="5" t="s">
-        <v>1250</v>
+        <v>1256</v>
       </c>
       <c r="D249" s="6" t="s">
-        <v>1251</v>
+        <v>1257</v>
       </c>
       <c r="E249" s="5" t="s">
-        <v>1249</v>
+        <v>1255</v>
       </c>
     </row>
     <row r="250" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -13180,16 +13387,16 @@
         <v>241</v>
       </c>
       <c r="B250" s="5" t="s">
-        <v>809</v>
+        <v>815</v>
       </c>
       <c r="C250" s="5" t="s">
-        <v>1252</v>
+        <v>1258</v>
       </c>
       <c r="D250" s="6" t="s">
-        <v>1253</v>
+        <v>1259</v>
       </c>
       <c r="E250" s="5" t="s">
-        <v>1254</v>
+        <v>1260</v>
       </c>
     </row>
     <row r="251" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -13197,16 +13404,16 @@
         <v>242</v>
       </c>
       <c r="B251" s="5" t="s">
-        <v>823</v>
+        <v>829</v>
       </c>
       <c r="C251" s="5" t="s">
-        <v>1255</v>
+        <v>1261</v>
       </c>
       <c r="D251" s="6" t="s">
-        <v>1256</v>
+        <v>1262</v>
       </c>
       <c r="E251" s="5" t="s">
-        <v>1257</v>
+        <v>1263</v>
       </c>
     </row>
     <row r="252" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -13214,16 +13421,16 @@
         <v>243</v>
       </c>
       <c r="B252" s="5" t="s">
-        <v>1258</v>
+        <v>1264</v>
       </c>
       <c r="C252" s="5" t="s">
-        <v>1259</v>
+        <v>1265</v>
       </c>
       <c r="D252" s="6" t="s">
-        <v>1260</v>
+        <v>1266</v>
       </c>
       <c r="E252" s="5" t="s">
-        <v>1261</v>
+        <v>1267</v>
       </c>
     </row>
     <row r="253" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -13231,16 +13438,16 @@
         <v>244</v>
       </c>
       <c r="B253" s="5" t="s">
-        <v>1262</v>
+        <v>1268</v>
       </c>
       <c r="C253" s="5" t="s">
-        <v>1263</v>
+        <v>1269</v>
       </c>
       <c r="D253" s="6" t="s">
-        <v>1264</v>
+        <v>1270</v>
       </c>
       <c r="E253" s="5" t="s">
-        <v>1249</v>
+        <v>1255</v>
       </c>
     </row>
     <row r="254" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -13248,16 +13455,16 @@
         <v>245</v>
       </c>
       <c r="B254" s="5" t="s">
-        <v>823</v>
+        <v>829</v>
       </c>
       <c r="C254" s="5" t="s">
-        <v>1265</v>
+        <v>1271</v>
       </c>
       <c r="D254" s="6" t="s">
-        <v>1266</v>
+        <v>1272</v>
       </c>
       <c r="E254" s="5" t="s">
-        <v>1257</v>
+        <v>1263</v>
       </c>
     </row>
     <row r="255" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -13265,16 +13472,16 @@
         <v>246</v>
       </c>
       <c r="B255" s="5" t="s">
-        <v>1258</v>
+        <v>1264</v>
       </c>
       <c r="C255" s="5" t="s">
-        <v>1267</v>
+        <v>1273</v>
       </c>
       <c r="D255" s="6" t="s">
-        <v>1268</v>
+        <v>1274</v>
       </c>
       <c r="E255" s="5" t="s">
-        <v>1254</v>
+        <v>1260</v>
       </c>
     </row>
     <row r="256" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -13282,16 +13489,16 @@
         <v>247</v>
       </c>
       <c r="B256" s="5" t="s">
-        <v>1269</v>
+        <v>1275</v>
       </c>
       <c r="C256" s="5" t="s">
-        <v>1270</v>
+        <v>1276</v>
       </c>
       <c r="D256" s="6" t="s">
-        <v>1271</v>
+        <v>1277</v>
       </c>
       <c r="E256" s="5" t="s">
-        <v>1257</v>
+        <v>1263</v>
       </c>
     </row>
     <row r="257" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -13299,16 +13506,16 @@
         <v>248</v>
       </c>
       <c r="B257" s="5" t="s">
-        <v>823</v>
+        <v>829</v>
       </c>
       <c r="C257" s="5" t="s">
-        <v>1272</v>
+        <v>1278</v>
       </c>
       <c r="D257" s="6" t="s">
-        <v>1273</v>
+        <v>1279</v>
       </c>
       <c r="E257" s="5" t="s">
-        <v>1257</v>
+        <v>1263</v>
       </c>
     </row>
     <row r="258" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -13316,16 +13523,16 @@
         <v>249</v>
       </c>
       <c r="B258" s="5" t="s">
-        <v>890</v>
+        <v>896</v>
       </c>
       <c r="C258" s="5" t="s">
-        <v>1274</v>
+        <v>1280</v>
       </c>
       <c r="D258" s="6" t="s">
-        <v>1275</v>
+        <v>1281</v>
       </c>
       <c r="E258" s="5" t="s">
-        <v>1257</v>
+        <v>1263</v>
       </c>
     </row>
     <row r="259" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -13333,152 +13540,288 @@
         <v>250</v>
       </c>
       <c r="B259" s="5" t="s">
-        <v>1262</v>
+        <v>1268</v>
       </c>
       <c r="C259" s="5" t="s">
-        <v>1276</v>
+        <v>1282</v>
       </c>
       <c r="D259" s="6" t="s">
-        <v>1277</v>
+        <v>1283</v>
       </c>
       <c r="E259" s="5" t="s">
-        <v>1261</v>
-      </c>
-    </row>
-    <row r="260" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+        <v>1267</v>
+      </c>
+    </row>
+    <row r="260" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A260" s="5" t="n">
         <v>251</v>
       </c>
       <c r="B260" s="5" t="s">
-        <v>1258</v>
+        <v>1264</v>
       </c>
       <c r="C260" s="5" t="s">
-        <v>1278</v>
+        <v>1284</v>
       </c>
       <c r="D260" s="6" t="s">
-        <v>1279</v>
+        <v>1285</v>
       </c>
       <c r="E260" s="5" t="s">
-        <v>1280</v>
-      </c>
-    </row>
-    <row r="261" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+        <v>1286</v>
+      </c>
+    </row>
+    <row r="261" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A261" s="5" t="n">
         <v>252</v>
       </c>
       <c r="B261" s="5" t="s">
-        <v>1258</v>
+        <v>1264</v>
       </c>
       <c r="C261" s="5" t="s">
-        <v>1281</v>
+        <v>1287</v>
       </c>
       <c r="D261" s="6" t="s">
-        <v>1282</v>
+        <v>1288</v>
       </c>
       <c r="E261" s="5" t="s">
-        <v>1280</v>
-      </c>
-    </row>
-    <row r="262" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+        <v>1286</v>
+      </c>
+    </row>
+    <row r="262" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A262" s="5" t="n">
         <v>253</v>
       </c>
       <c r="B262" s="5" t="s">
-        <v>684</v>
+        <v>690</v>
       </c>
       <c r="C262" s="5" t="s">
-        <v>1283</v>
+        <v>1289</v>
       </c>
       <c r="D262" s="6" t="s">
-        <v>1284</v>
+        <v>1290</v>
       </c>
       <c r="E262" s="5" t="s">
-        <v>1280</v>
-      </c>
-    </row>
-    <row r="263" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+        <v>1286</v>
+      </c>
+    </row>
+    <row r="263" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A263" s="5" t="n">
         <v>254</v>
       </c>
       <c r="B263" s="5" t="s">
-        <v>823</v>
+        <v>829</v>
       </c>
       <c r="C263" s="5" t="s">
-        <v>1285</v>
+        <v>1291</v>
       </c>
       <c r="D263" s="6" t="s">
-        <v>1286</v>
+        <v>1292</v>
       </c>
       <c r="E263" s="5" t="s">
-        <v>1287</v>
-      </c>
-    </row>
-    <row r="264" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+        <v>1293</v>
+      </c>
+    </row>
+    <row r="264" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A264" s="5" t="n">
         <v>255</v>
       </c>
       <c r="B264" s="5" t="s">
-        <v>684</v>
+        <v>690</v>
       </c>
       <c r="C264" s="5" t="s">
-        <v>1288</v>
+        <v>1294</v>
       </c>
       <c r="D264" s="6" t="s">
-        <v>1289</v>
+        <v>1295</v>
       </c>
       <c r="E264" s="5" t="s">
-        <v>1290</v>
-      </c>
-    </row>
-    <row r="265" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+        <v>1296</v>
+      </c>
+    </row>
+    <row r="265" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A265" s="5" t="n">
         <v>256</v>
       </c>
       <c r="B265" s="5" t="s">
-        <v>815</v>
+        <v>821</v>
       </c>
       <c r="C265" s="5" t="s">
-        <v>1291</v>
+        <v>1297</v>
       </c>
       <c r="D265" s="6" t="s">
-        <v>1292</v>
+        <v>1298</v>
       </c>
       <c r="E265" s="5" t="s">
-        <v>1290</v>
-      </c>
-    </row>
-    <row r="266" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+        <v>1296</v>
+      </c>
+    </row>
+    <row r="266" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A266" s="5" t="n">
         <v>257</v>
       </c>
       <c r="B266" s="5" t="s">
-        <v>1293</v>
+        <v>1299</v>
       </c>
       <c r="C266" s="5" t="s">
-        <v>1294</v>
+        <v>1300</v>
       </c>
       <c r="D266" s="6" t="s">
-        <v>1295</v>
+        <v>1301</v>
       </c>
       <c r="E266" s="5" t="s">
-        <v>1280</v>
-      </c>
-    </row>
-    <row r="267" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+        <v>1286</v>
+      </c>
+    </row>
+    <row r="267" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A267" s="5" t="n">
         <v>258</v>
       </c>
       <c r="B267" s="5" t="s">
-        <v>890</v>
+        <v>896</v>
       </c>
       <c r="C267" s="5" t="s">
-        <v>1296</v>
+        <v>1302</v>
       </c>
       <c r="D267" s="6" t="s">
-        <v>1297</v>
+        <v>1303</v>
       </c>
       <c r="E267" s="5" t="s">
-        <v>1280</v>
+        <v>1286</v>
+      </c>
+    </row>
+    <row r="268" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A268" s="5" t="n">
+        <v>259</v>
+      </c>
+      <c r="B268" s="5" t="s">
+        <v>1053</v>
+      </c>
+      <c r="C268" s="5" t="s">
+        <v>1304</v>
+      </c>
+      <c r="D268" s="6" t="s">
+        <v>1305</v>
+      </c>
+      <c r="E268" s="5" t="s">
+        <v>1306</v>
+      </c>
+    </row>
+    <row r="269" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A269" s="5" t="n">
+        <v>260</v>
+      </c>
+      <c r="B269" s="5" t="s">
+        <v>1264</v>
+      </c>
+      <c r="C269" s="5" t="s">
+        <v>1307</v>
+      </c>
+      <c r="D269" s="6" t="s">
+        <v>1308</v>
+      </c>
+      <c r="E269" s="5" t="s">
+        <v>1309</v>
+      </c>
+    </row>
+    <row r="270" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A270" s="5" t="n">
+        <v>261</v>
+      </c>
+      <c r="B270" s="5" t="s">
+        <v>829</v>
+      </c>
+      <c r="C270" s="5" t="s">
+        <v>1310</v>
+      </c>
+      <c r="D270" s="6" t="s">
+        <v>1311</v>
+      </c>
+      <c r="E270" s="5" t="s">
+        <v>1309</v>
+      </c>
+    </row>
+    <row r="271" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A271" s="5" t="n">
+        <v>262</v>
+      </c>
+      <c r="B271" s="5" t="s">
+        <v>1264</v>
+      </c>
+      <c r="C271" s="5" t="s">
+        <v>1312</v>
+      </c>
+      <c r="D271" s="6" t="s">
+        <v>1313</v>
+      </c>
+      <c r="E271" s="5" t="s">
+        <v>1309</v>
+      </c>
+    </row>
+    <row r="272" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A272" s="5" t="n">
+        <v>263</v>
+      </c>
+      <c r="B272" s="5" t="s">
+        <v>829</v>
+      </c>
+      <c r="C272" s="5" t="s">
+        <v>1314</v>
+      </c>
+      <c r="D272" s="6" t="s">
+        <v>1315</v>
+      </c>
+      <c r="E272" s="5" t="s">
+        <v>1309</v>
+      </c>
+    </row>
+    <row r="273" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A273" s="5" t="n">
+        <v>264</v>
+      </c>
+      <c r="B273" s="5" t="s">
+        <v>1053</v>
+      </c>
+      <c r="C273" s="5" t="s">
+        <v>1316</v>
+      </c>
+      <c r="D273" s="6" t="s">
+        <v>1317</v>
+      </c>
+      <c r="E273" s="5" t="s">
+        <v>1318</v>
+      </c>
+    </row>
+    <row r="274" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A274" s="5" t="n">
+        <v>265</v>
+      </c>
+      <c r="B274" s="5" t="s">
+        <v>1275</v>
+      </c>
+      <c r="C274" s="5" t="s">
+        <v>1319</v>
+      </c>
+      <c r="D274" s="6" t="s">
+        <v>1320</v>
+      </c>
+      <c r="E274" s="5" t="s">
+        <v>1309</v>
+      </c>
+    </row>
+    <row r="275" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A275" s="5" t="n">
+        <v>266</v>
+      </c>
+      <c r="B275" s="5" t="s">
+        <v>829</v>
+      </c>
+      <c r="C275" s="5" t="s">
+        <v>1321</v>
+      </c>
+      <c r="D275" s="6" t="s">
+        <v>1322</v>
+      </c>
+      <c r="E275" s="5" t="s">
+        <v>1306</v>
       </c>
     </row>
   </sheetData>
@@ -13671,6 +14014,14 @@
     <hyperlink ref="D265" r:id="rId183" display="https://thehill.com/homenews/6122096-white-house-blocks-cnn-pool-trump/"/>
     <hyperlink ref="D266" r:id="rId184" display="https://www.washingtonpost.com/politics/2026/09/29/gop-senator-blocks-bill-stop-trump-demolishing-kennedy-center/"/>
     <hyperlink ref="D267" r:id="rId185" display="https://www.npr.org/2026/09/29/nx-s1-5983673/trump-administration-says-its-scaling-back-fuel-efficiency-standards-for-new-cars"/>
+    <hyperlink ref="D268" r:id="rId186" display="https://www.pbs.org/newshour/politics/ice-officer-shoots-a-man-while-making-an-arrest-in-new-york-officials-say"/>
+    <hyperlink ref="D269" r:id="rId187" display="https://www.axios.com/2026/10/06/trump-super-intelligence-war-words-ai-affordability"/>
+    <hyperlink ref="D270" r:id="rId188" display="https://www.theguardian.com/us-news/2026/oct/06/trump-protesters-antifa-defendants-union"/>
+    <hyperlink ref="D271" r:id="rId189" display="https://www.axios.com/2026/10/06/trump-iran-take-out-la-san-diego"/>
+    <hyperlink ref="D272" r:id="rId190" display="https://www.theguardian.com/us-news/2026/oct/06/canada-veterans-trump-allies-military"/>
+    <hyperlink ref="D273" r:id="rId191" display="https://www.pbs.org/newshour/nation/shock-gloves-purchased-by-ice-cause-pain-compliance-and-fear-army-study-found"/>
+    <hyperlink ref="D274" r:id="rId192" display="https://www.nytimes.com/2026/10/05/us/politico-blocked-trump-nebraska.html"/>
+    <hyperlink ref="D275" r:id="rId193" display="https://www.theguardian.com/commentisfree/2026/oct/09/nidal-hasan-execution-pete-hegseth-us-military-tv-democracy"/>
   </hyperlinks>
   <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.511811023622047" footer="0.511811023622047"/>
@@ -13687,7 +14038,7 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:B23"/>
+  <dimension ref="A1:B25"/>
   <sheetFormatPr defaultColWidth="8.6875" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="30.01"/>
@@ -13696,7 +14047,7 @@
   <sheetData>
     <row r="1" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A1" s="7" t="s">
-        <v>1298</v>
+        <v>1323</v>
       </c>
       <c r="B1" s="7"/>
     </row>
@@ -13705,7 +14056,7 @@
         <v>3</v>
       </c>
       <c r="B2" s="8" t="s">
-        <v>1299</v>
+        <v>1324</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -13737,124 +14088,124 @@
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A6" s="9" t="s">
-        <v>9</v>
+        <v>574</v>
       </c>
       <c r="B6" s="9" t="n">
         <f aca="false">COUNTIF('Weekly Timeline'!C:C,A6)</f>
-        <v>37</v>
+        <v>1</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A7" s="9" t="s">
-        <v>100</v>
+        <v>9</v>
       </c>
       <c r="B7" s="9" t="n">
         <f aca="false">COUNTIF('Weekly Timeline'!C:C,A7)</f>
-        <v>14</v>
+        <v>37</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A8" s="9" t="s">
-        <v>107</v>
+        <v>100</v>
       </c>
       <c r="B8" s="9" t="n">
         <f aca="false">COUNTIF('Weekly Timeline'!C:C,A8)</f>
-        <v>5</v>
+        <v>14</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A9" s="9" t="s">
-        <v>558</v>
+        <v>107</v>
       </c>
       <c r="B9" s="9" t="n">
         <f aca="false">COUNTIF('Weekly Timeline'!C:C,A9)</f>
-        <v>4</v>
+        <v>5</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A10" s="9" t="s">
-        <v>21</v>
+        <v>558</v>
       </c>
       <c r="B10" s="9" t="n">
         <f aca="false">COUNTIF('Weekly Timeline'!C:C,A10)</f>
-        <v>5</v>
+        <v>4</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A11" s="9" t="s">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="B11" s="9" t="n">
         <f aca="false">COUNTIF('Weekly Timeline'!C:C,A11)</f>
-        <v>36</v>
+        <v>5</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A12" s="9" t="s">
-        <v>38</v>
+        <v>24</v>
       </c>
       <c r="B12" s="9" t="n">
         <f aca="false">COUNTIF('Weekly Timeline'!C:C,A12)</f>
-        <v>3</v>
+        <v>38</v>
       </c>
     </row>
     <row r="13" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A13" s="9" t="s">
-        <v>48</v>
+        <v>38</v>
       </c>
       <c r="B13" s="9" t="n">
         <f aca="false">COUNTIF('Weekly Timeline'!C:C,A13)</f>
-        <v>17</v>
+        <v>3</v>
       </c>
     </row>
     <row r="14" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A14" s="9" t="s">
-        <v>171</v>
+        <v>48</v>
       </c>
       <c r="B14" s="9" t="n">
         <f aca="false">COUNTIF('Weekly Timeline'!C:C,A14)</f>
-        <v>4</v>
+        <v>18</v>
       </c>
     </row>
     <row r="15" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A15" s="9" t="s">
-        <v>12</v>
+        <v>573</v>
       </c>
       <c r="B15" s="9" t="n">
         <f aca="false">COUNTIF('Weekly Timeline'!C:C,A15)</f>
-        <v>19</v>
+        <v>1</v>
       </c>
     </row>
     <row r="16" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A16" s="9" t="s">
-        <v>112</v>
+        <v>171</v>
       </c>
       <c r="B16" s="9" t="n">
         <f aca="false">COUNTIF('Weekly Timeline'!C:C,A16)</f>
-        <v>1</v>
+        <v>4</v>
       </c>
     </row>
     <row r="17" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A17" s="9" t="s">
-        <v>553</v>
+        <v>12</v>
       </c>
       <c r="B17" s="9" t="n">
         <f aca="false">COUNTIF('Weekly Timeline'!C:C,A17)</f>
-        <v>2</v>
+        <v>19</v>
       </c>
     </row>
     <row r="18" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A18" s="9" t="s">
-        <v>15</v>
+        <v>112</v>
       </c>
       <c r="B18" s="9" t="n">
         <f aca="false">COUNTIF('Weekly Timeline'!C:C,A18)</f>
-        <v>4</v>
+        <v>1</v>
       </c>
     </row>
     <row r="19" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A19" s="9" t="s">
-        <v>566</v>
+        <v>553</v>
       </c>
       <c r="B19" s="9" t="n">
         <f aca="false">COUNTIF('Weekly Timeline'!C:C,A19)</f>
@@ -13863,16 +14214,16 @@
     </row>
     <row r="20" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A20" s="9" t="s">
-        <v>68</v>
+        <v>15</v>
       </c>
       <c r="B20" s="9" t="n">
         <f aca="false">COUNTIF('Weekly Timeline'!C:C,A20)</f>
-        <v>14</v>
+        <v>4</v>
       </c>
     </row>
     <row r="21" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A21" s="9" t="s">
-        <v>72</v>
+        <v>566</v>
       </c>
       <c r="B21" s="9" t="n">
         <f aca="false">COUNTIF('Weekly Timeline'!C:C,A21)</f>
@@ -13881,20 +14232,38 @@
     </row>
     <row r="22" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A22" s="9" t="s">
-        <v>346</v>
+        <v>68</v>
       </c>
       <c r="B22" s="9" t="n">
         <f aca="false">COUNTIF('Weekly Timeline'!C:C,A22)</f>
+        <v>15</v>
+      </c>
+    </row>
+    <row r="23" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A23" s="9" t="s">
+        <v>72</v>
+      </c>
+      <c r="B23" s="9" t="n">
+        <f aca="false">COUNTIF('Weekly Timeline'!C:C,A23)</f>
+        <v>4</v>
+      </c>
+    </row>
+    <row r="24" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A24" s="10" t="s">
+        <v>346</v>
+      </c>
+      <c r="B24" s="10" t="n">
+        <f aca="false">COUNTIF('Weekly Timeline'!C:C,A24)</f>
         <v>1</v>
       </c>
     </row>
-    <row r="23" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A23" s="10" t="s">
-        <v>1300</v>
-      </c>
-      <c r="B23" s="10" t="n">
-        <f aca="false">SUM(B3:B22)</f>
-        <v>202</v>
+    <row r="25" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A25" s="11" t="s">
+        <v>1325</v>
+      </c>
+      <c r="B25" s="11" t="n">
+        <f aca="false">SUM(B3:B24)</f>
+        <v>210</v>
       </c>
     </row>
   </sheetData>

--- a/data/Trump_Second_Term_Weekly_Tracker.xlsx
+++ b/data/Trump_Second_Term_Weekly_Tracker.xlsx
@@ -13,7 +13,7 @@
     <sheet name="Summary" sheetId="3" state="visible" r:id="rId5"/>
   </sheets>
   <definedNames>
-    <definedName function="false" hidden="true" localSheetId="0" name="_xlnm._FilterDatabase" vbProcedure="false">'Weekly Timeline'!$A$2:$F$268</definedName>
+    <definedName function="false" hidden="true" localSheetId="0" name="_xlnm._FilterDatabase" vbProcedure="false">'Weekly Timeline'!$A$2:$F$281</definedName>
   </definedNames>
   <calcPr iterateCount="100" refMode="A1" iterate="false" iterateDelta="0.0001"/>
   <extLst>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2105" uniqueCount="1326">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2196" uniqueCount="1366">
   <si>
     <t xml:space="preserve">Documented actions and policies of the second Trump administration reported as harmful by major news outlets, courts, and government data — Jan 20, 2025 through Jul 8, 2026. One row per event; weeks with multiple events have multiple rows; quiet weeks are skipped. This compiles critical coverage as requested; the administration and its supporters dispute many of these characterizations. See the Sources tab (matching Ref #) and verify details independently before citing.</t>
   </si>
@@ -1755,6 +1755,30 @@
     <t xml:space="preserve">Oct 7</t>
   </si>
   <si>
+    <t xml:space="preserve">Oct 12, 2026</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Oct 12</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Oct 14</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Oct 11</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Oct 15</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Oct 13</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Oct 17</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Oct 16</t>
+  </si>
+  <si>
     <t xml:space="preserve">Ref # matches the Source Ref column on the Weekly Timeline tab. URLs are provided where verified via current web results (mostly 2026 items). For 2025 items, outlet names and dates are given; searching the description text will locate the original coverage. Per your request the mix emphasizes CNN, Politico, MSNBC/MS NOW, NBC and independent outlets, alongside AP, Reuters, Guardian, NPR, CBS, ABC and court documents.</t>
   </si>
   <si>
@@ -3994,6 +4018,102 @@
   </si>
   <si>
     <t xml:space="preserve">https://www.theguardian.com/commentisfree/2026/oct/09/nidal-hasan-execution-pete-hegseth-us-military-tv-democracy</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Feds search Rep. Ilhan Omar's home in immigration probe</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://www.axios.com/2026/10/12/ilhan-omar-search-immigration</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ICE says no to automatic body-cams</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://www.axios.com/2026/10/14/ice-body-cam-automatic-gao-report</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Oct 14, 2026</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ICE agent strikes man with vehicle during pursuit in Texas</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://www.theguardian.com/us-news/2026/oct/11/ice-agent-strikes-man-with-car-texas</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Oct 11, 2026</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Trump sues California to prevent counting 20,000 voters' ballots</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://www.axios.com/2026/10/15/trump-doj-california-voters-ballots-lawsuit</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Oct 15, 2026</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Federal judge admonishes Trump administration over East Potomac Park tree removal</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://thehill.com/regulation/court-battles/6143318-trump-administration-east-potomac-park-golf-trees/</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Hegseth wants a livestream execution. Here's how firing squads work</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://www.axios.com/2026/10/13/execution-nidal-hasan-firing-squad-hegseth-stream</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Oct 13, 2026</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Trump Revives 2020 Election Conspiracy Theories as Midterms Loom</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://www.nytimes.com/2026/10/17/us/politics/election-fraud-conspiracies-trump.html</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Oct 17, 2026</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Trump Administration Sues California Over Voter Rolls</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://www.nytimes.com/2026/10/15/us/politics/trump-administration-california-voter-rolls.html</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Trump Waives Russia Energy Tariffs, Sanctions</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://www.bloomberg.com/news/articles/2026-10-17/trump-waives-russia-energy-tariffs-sanctions-in-graham-law</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Mullin says livestreaming Hasan execution is part of 'restoring American values'</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://thehill.com/homenews/administration/6141440-mullin-backs-hasan-execution-livestream/</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Russian diesel deal "a betrayal,"</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://www.axios.com/2026/10/13/trump-russian-diesel-deal-betrayal-bipartisan-letter</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Trump Pardons Two Alaska Mechanics Over Clean Air Act Violations</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://www.bloomberg.com/news/articles/2026-10-14/trump-pardons-two-alaska-mechanics-over-clean-air-act-violations</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Of course Trump is helping Russia in Ukraine</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://www.theguardian.com/commentisfree/2026/oct/16/donald-trump-russia-ukraine-protect-world</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Oct 16, 2026</t>
   </si>
   <si>
     <t xml:space="preserve">Entries by category (live COUNTIF formulas against the Weekly Timeline tab)</t>
@@ -4141,7 +4261,7 @@
     <xf numFmtId="42" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
     <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
   </cellStyleXfs>
-  <cellXfs count="12">
+  <cellXfs count="11">
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
@@ -4182,11 +4302,7 @@
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="164" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -4479,7 +4595,7 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:F268"/>
+  <dimension ref="A1:F281"/>
   <sheetFormatPr defaultColWidth="8.6875" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="13.01"/>
@@ -9159,7 +9275,7 @@
         <v>258</v>
       </c>
     </row>
-    <row r="261" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="261" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A261" s="5" t="s">
         <v>570</v>
       </c>
@@ -9175,7 +9291,7 @@
         <v>259</v>
       </c>
     </row>
-    <row r="262" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="262" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A262" s="5" t="s">
         <v>570</v>
       </c>
@@ -9191,7 +9307,7 @@
         <v>260</v>
       </c>
     </row>
-    <row r="263" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="263" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A263" s="5" t="s">
         <v>570</v>
       </c>
@@ -9207,7 +9323,7 @@
         <v>261</v>
       </c>
     </row>
-    <row r="264" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="264" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A264" s="5" t="s">
         <v>570</v>
       </c>
@@ -9223,7 +9339,7 @@
         <v>262</v>
       </c>
     </row>
-    <row r="265" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="265" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A265" s="5" t="s">
         <v>570</v>
       </c>
@@ -9239,7 +9355,7 @@
         <v>263</v>
       </c>
     </row>
-    <row r="266" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="266" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A266" s="5" t="s">
         <v>570</v>
       </c>
@@ -9255,7 +9371,7 @@
         <v>264</v>
       </c>
     </row>
-    <row r="267" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="267" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A267" s="5" t="s">
         <v>570</v>
       </c>
@@ -9271,7 +9387,7 @@
         <v>265</v>
       </c>
     </row>
-    <row r="268" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="268" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A268" s="5" t="s">
         <v>570</v>
       </c>
@@ -9287,8 +9403,216 @@
         <v>266</v>
       </c>
     </row>
+    <row r="269" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A269" s="4" t="s">
+        <v>576</v>
+      </c>
+      <c r="B269" s="4" t="s">
+        <v>577</v>
+      </c>
+      <c r="C269" s="4" t="s">
+        <v>566</v>
+      </c>
+      <c r="D269" s="4"/>
+      <c r="E269" s="4"/>
+      <c r="F269" s="4" t="n">
+        <v>267</v>
+      </c>
+    </row>
+    <row r="270" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A270" s="4" t="s">
+        <v>576</v>
+      </c>
+      <c r="B270" s="4" t="s">
+        <v>578</v>
+      </c>
+      <c r="C270" s="4" t="s">
+        <v>566</v>
+      </c>
+      <c r="D270" s="4"/>
+      <c r="E270" s="4"/>
+      <c r="F270" s="4" t="n">
+        <v>268</v>
+      </c>
+    </row>
+    <row r="271" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A271" s="5" t="s">
+        <v>570</v>
+      </c>
+      <c r="B271" s="5" t="s">
+        <v>579</v>
+      </c>
+      <c r="C271" s="5" t="s">
+        <v>566</v>
+      </c>
+      <c r="D271" s="5"/>
+      <c r="E271" s="5"/>
+      <c r="F271" s="5" t="n">
+        <v>269</v>
+      </c>
+    </row>
+    <row r="272" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A272" s="4" t="s">
+        <v>576</v>
+      </c>
+      <c r="B272" s="4" t="s">
+        <v>580</v>
+      </c>
+      <c r="C272" s="4" t="s">
+        <v>558</v>
+      </c>
+      <c r="D272" s="4"/>
+      <c r="E272" s="4"/>
+      <c r="F272" s="4" t="n">
+        <v>270</v>
+      </c>
+    </row>
+    <row r="273" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A273" s="4" t="s">
+        <v>576</v>
+      </c>
+      <c r="B273" s="4" t="s">
+        <v>577</v>
+      </c>
+      <c r="C273" s="4" t="s">
+        <v>21</v>
+      </c>
+      <c r="D273" s="4"/>
+      <c r="E273" s="4"/>
+      <c r="F273" s="4" t="n">
+        <v>271</v>
+      </c>
+    </row>
+    <row r="274" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A274" s="4" t="s">
+        <v>576</v>
+      </c>
+      <c r="B274" s="4" t="s">
+        <v>581</v>
+      </c>
+      <c r="C274" s="4" t="s">
+        <v>574</v>
+      </c>
+      <c r="D274" s="4"/>
+      <c r="E274" s="4"/>
+      <c r="F274" s="4" t="n">
+        <v>272</v>
+      </c>
+    </row>
+    <row r="275" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A275" s="4" t="s">
+        <v>576</v>
+      </c>
+      <c r="B275" s="4" t="s">
+        <v>582</v>
+      </c>
+      <c r="C275" s="4" t="s">
+        <v>558</v>
+      </c>
+      <c r="D275" s="4"/>
+      <c r="E275" s="4"/>
+      <c r="F275" s="4" t="n">
+        <v>273</v>
+      </c>
+    </row>
+    <row r="276" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A276" s="4" t="s">
+        <v>576</v>
+      </c>
+      <c r="B276" s="4" t="s">
+        <v>580</v>
+      </c>
+      <c r="C276" s="4" t="s">
+        <v>558</v>
+      </c>
+      <c r="D276" s="4"/>
+      <c r="E276" s="4"/>
+      <c r="F276" s="4" t="n">
+        <v>274</v>
+      </c>
+    </row>
+    <row r="277" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A277" s="4" t="s">
+        <v>576</v>
+      </c>
+      <c r="B277" s="4" t="s">
+        <v>582</v>
+      </c>
+      <c r="C277" s="4" t="s">
+        <v>48</v>
+      </c>
+      <c r="D277" s="4"/>
+      <c r="E277" s="4"/>
+      <c r="F277" s="4" t="n">
+        <v>275</v>
+      </c>
+    </row>
+    <row r="278" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A278" s="5" t="s">
+        <v>570</v>
+      </c>
+      <c r="B278" s="5" t="s">
+        <v>579</v>
+      </c>
+      <c r="C278" s="5" t="s">
+        <v>574</v>
+      </c>
+      <c r="D278" s="5"/>
+      <c r="E278" s="5"/>
+      <c r="F278" s="5" t="n">
+        <v>276</v>
+      </c>
+    </row>
+    <row r="279" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A279" s="4" t="s">
+        <v>576</v>
+      </c>
+      <c r="B279" s="4" t="s">
+        <v>581</v>
+      </c>
+      <c r="C279" s="4" t="s">
+        <v>48</v>
+      </c>
+      <c r="D279" s="4"/>
+      <c r="E279" s="4"/>
+      <c r="F279" s="4" t="n">
+        <v>277</v>
+      </c>
+    </row>
+    <row r="280" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A280" s="4" t="s">
+        <v>576</v>
+      </c>
+      <c r="B280" s="4" t="s">
+        <v>578</v>
+      </c>
+      <c r="C280" s="4" t="s">
+        <v>21</v>
+      </c>
+      <c r="D280" s="4"/>
+      <c r="E280" s="4"/>
+      <c r="F280" s="4" t="n">
+        <v>278</v>
+      </c>
+    </row>
+    <row r="281" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A281" s="4" t="s">
+        <v>576</v>
+      </c>
+      <c r="B281" s="4" t="s">
+        <v>583</v>
+      </c>
+      <c r="C281" s="4" t="s">
+        <v>48</v>
+      </c>
+      <c r="D281" s="4"/>
+      <c r="E281" s="4"/>
+      <c r="F281" s="4" t="n">
+        <v>279</v>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A2:F268"/>
+  <autoFilter ref="A2:F281"/>
   <mergeCells count="1">
     <mergeCell ref="A1:F1"/>
   </mergeCells>
@@ -9308,7 +9632,7 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:E275"/>
+  <dimension ref="A1:E288"/>
   <sheetFormatPr defaultColWidth="8.6875" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="7"/>
@@ -9319,7 +9643,7 @@
   <sheetData>
     <row r="1" customFormat="false" ht="48" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A1" s="2" t="s">
-        <v>576</v>
+        <v>584</v>
       </c>
       <c r="B1" s="2"/>
       <c r="C1" s="2"/>
@@ -9328,19 +9652,19 @@
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A2" s="3" t="s">
-        <v>577</v>
+        <v>585</v>
       </c>
       <c r="B2" s="3" t="s">
-        <v>578</v>
+        <v>586</v>
       </c>
       <c r="C2" s="3" t="s">
-        <v>579</v>
+        <v>587</v>
       </c>
       <c r="D2" s="3" t="s">
-        <v>580</v>
+        <v>588</v>
       </c>
       <c r="E2" s="3" t="s">
-        <v>581</v>
+        <v>589</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -9348,14 +9672,14 @@
         <v>1</v>
       </c>
       <c r="B3" s="5" t="s">
-        <v>582</v>
+        <v>590</v>
       </c>
       <c r="C3" s="5" t="s">
-        <v>583</v>
+        <v>591</v>
       </c>
       <c r="D3" s="5"/>
       <c r="E3" s="5" t="s">
-        <v>584</v>
+        <v>592</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -9363,14 +9687,14 @@
         <v>2</v>
       </c>
       <c r="B4" s="5" t="s">
-        <v>585</v>
+        <v>593</v>
       </c>
       <c r="C4" s="5" t="s">
-        <v>586</v>
+        <v>594</v>
       </c>
       <c r="D4" s="5"/>
       <c r="E4" s="5" t="s">
-        <v>587</v>
+        <v>595</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -9378,14 +9702,14 @@
         <v>3</v>
       </c>
       <c r="B5" s="5" t="s">
-        <v>588</v>
+        <v>596</v>
       </c>
       <c r="C5" s="5" t="s">
-        <v>589</v>
+        <v>597</v>
       </c>
       <c r="D5" s="5"/>
       <c r="E5" s="5" t="s">
-        <v>584</v>
+        <v>592</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -9393,14 +9717,14 @@
         <v>4</v>
       </c>
       <c r="B6" s="5" t="s">
-        <v>590</v>
+        <v>598</v>
       </c>
       <c r="C6" s="5" t="s">
-        <v>591</v>
+        <v>599</v>
       </c>
       <c r="D6" s="5"/>
       <c r="E6" s="5" t="s">
-        <v>592</v>
+        <v>600</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -9408,14 +9732,14 @@
         <v>5</v>
       </c>
       <c r="B7" s="5" t="s">
-        <v>593</v>
+        <v>601</v>
       </c>
       <c r="C7" s="5" t="s">
-        <v>594</v>
+        <v>602</v>
       </c>
       <c r="D7" s="5"/>
       <c r="E7" s="5" t="s">
-        <v>584</v>
+        <v>592</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -9423,14 +9747,14 @@
         <v>6</v>
       </c>
       <c r="B8" s="5" t="s">
-        <v>595</v>
+        <v>603</v>
       </c>
       <c r="C8" s="5" t="s">
-        <v>596</v>
+        <v>604</v>
       </c>
       <c r="D8" s="5"/>
       <c r="E8" s="5" t="s">
-        <v>584</v>
+        <v>592</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -9438,14 +9762,14 @@
         <v>7</v>
       </c>
       <c r="B9" s="5" t="s">
-        <v>597</v>
+        <v>605</v>
       </c>
       <c r="C9" s="5" t="s">
-        <v>598</v>
+        <v>606</v>
       </c>
       <c r="D9" s="5"/>
       <c r="E9" s="5" t="s">
-        <v>599</v>
+        <v>607</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -9453,14 +9777,14 @@
         <v>8</v>
       </c>
       <c r="B10" s="5" t="s">
-        <v>600</v>
+        <v>608</v>
       </c>
       <c r="C10" s="5" t="s">
-        <v>601</v>
+        <v>609</v>
       </c>
       <c r="D10" s="5"/>
       <c r="E10" s="5" t="s">
-        <v>602</v>
+        <v>610</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -9468,14 +9792,14 @@
         <v>9</v>
       </c>
       <c r="B11" s="5" t="s">
-        <v>603</v>
+        <v>611</v>
       </c>
       <c r="C11" s="5" t="s">
-        <v>604</v>
+        <v>612</v>
       </c>
       <c r="D11" s="5"/>
       <c r="E11" s="5" t="s">
-        <v>605</v>
+        <v>613</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -9483,14 +9807,14 @@
         <v>10</v>
       </c>
       <c r="B12" s="5" t="s">
-        <v>606</v>
+        <v>614</v>
       </c>
       <c r="C12" s="5" t="s">
-        <v>607</v>
+        <v>615</v>
       </c>
       <c r="D12" s="5"/>
       <c r="E12" s="5" t="s">
-        <v>608</v>
+        <v>616</v>
       </c>
     </row>
     <row r="13" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -9498,14 +9822,14 @@
         <v>11</v>
       </c>
       <c r="B13" s="5" t="s">
-        <v>609</v>
+        <v>617</v>
       </c>
       <c r="C13" s="5" t="s">
-        <v>610</v>
+        <v>618</v>
       </c>
       <c r="D13" s="5"/>
       <c r="E13" s="5" t="s">
-        <v>611</v>
+        <v>619</v>
       </c>
     </row>
     <row r="14" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -9513,14 +9837,14 @@
         <v>12</v>
       </c>
       <c r="B14" s="5" t="s">
-        <v>612</v>
+        <v>620</v>
       </c>
       <c r="C14" s="5" t="s">
-        <v>613</v>
+        <v>621</v>
       </c>
       <c r="D14" s="5"/>
       <c r="E14" s="5" t="s">
-        <v>614</v>
+        <v>622</v>
       </c>
     </row>
     <row r="15" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -9528,14 +9852,14 @@
         <v>13</v>
       </c>
       <c r="B15" s="5" t="s">
-        <v>615</v>
+        <v>623</v>
       </c>
       <c r="C15" s="5" t="s">
-        <v>616</v>
+        <v>624</v>
       </c>
       <c r="D15" s="5"/>
       <c r="E15" s="5" t="s">
-        <v>617</v>
+        <v>625</v>
       </c>
     </row>
     <row r="16" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -9543,14 +9867,14 @@
         <v>14</v>
       </c>
       <c r="B16" s="5" t="s">
-        <v>618</v>
+        <v>626</v>
       </c>
       <c r="C16" s="5" t="s">
-        <v>619</v>
+        <v>627</v>
       </c>
       <c r="D16" s="5"/>
       <c r="E16" s="5" t="s">
-        <v>620</v>
+        <v>628</v>
       </c>
     </row>
     <row r="17" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -9558,14 +9882,14 @@
         <v>15</v>
       </c>
       <c r="B17" s="5" t="s">
-        <v>621</v>
+        <v>629</v>
       </c>
       <c r="C17" s="5" t="s">
-        <v>622</v>
+        <v>630</v>
       </c>
       <c r="D17" s="5"/>
       <c r="E17" s="5" t="s">
-        <v>623</v>
+        <v>631</v>
       </c>
     </row>
     <row r="18" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -9573,14 +9897,14 @@
         <v>16</v>
       </c>
       <c r="B18" s="5" t="s">
-        <v>624</v>
+        <v>632</v>
       </c>
       <c r="C18" s="5" t="s">
-        <v>625</v>
+        <v>633</v>
       </c>
       <c r="D18" s="5"/>
       <c r="E18" s="5" t="s">
-        <v>626</v>
+        <v>634</v>
       </c>
     </row>
     <row r="19" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -9588,14 +9912,14 @@
         <v>17</v>
       </c>
       <c r="B19" s="5" t="s">
-        <v>627</v>
+        <v>635</v>
       </c>
       <c r="C19" s="5" t="s">
-        <v>628</v>
+        <v>636</v>
       </c>
       <c r="D19" s="5"/>
       <c r="E19" s="5" t="s">
-        <v>629</v>
+        <v>637</v>
       </c>
     </row>
     <row r="20" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -9603,14 +9927,14 @@
         <v>18</v>
       </c>
       <c r="B20" s="5" t="s">
-        <v>630</v>
+        <v>638</v>
       </c>
       <c r="C20" s="5" t="s">
-        <v>631</v>
+        <v>639</v>
       </c>
       <c r="D20" s="5"/>
       <c r="E20" s="5" t="s">
-        <v>632</v>
+        <v>640</v>
       </c>
     </row>
     <row r="21" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -9618,14 +9942,14 @@
         <v>19</v>
       </c>
       <c r="B21" s="5" t="s">
-        <v>633</v>
+        <v>641</v>
       </c>
       <c r="C21" s="5" t="s">
-        <v>634</v>
+        <v>642</v>
       </c>
       <c r="D21" s="5"/>
       <c r="E21" s="5" t="s">
-        <v>635</v>
+        <v>643</v>
       </c>
     </row>
     <row r="22" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -9633,14 +9957,14 @@
         <v>20</v>
       </c>
       <c r="B22" s="5" t="s">
-        <v>636</v>
+        <v>644</v>
       </c>
       <c r="C22" s="5" t="s">
-        <v>637</v>
+        <v>645</v>
       </c>
       <c r="D22" s="5"/>
       <c r="E22" s="5" t="s">
-        <v>638</v>
+        <v>646</v>
       </c>
     </row>
     <row r="23" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -9648,14 +9972,14 @@
         <v>21</v>
       </c>
       <c r="B23" s="5" t="s">
-        <v>639</v>
+        <v>647</v>
       </c>
       <c r="C23" s="5" t="s">
-        <v>640</v>
+        <v>648</v>
       </c>
       <c r="D23" s="5"/>
       <c r="E23" s="5" t="s">
-        <v>641</v>
+        <v>649</v>
       </c>
     </row>
     <row r="24" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -9663,14 +9987,14 @@
         <v>22</v>
       </c>
       <c r="B24" s="5" t="s">
-        <v>642</v>
+        <v>650</v>
       </c>
       <c r="C24" s="5" t="s">
-        <v>643</v>
+        <v>651</v>
       </c>
       <c r="D24" s="5"/>
       <c r="E24" s="5" t="s">
-        <v>644</v>
+        <v>652</v>
       </c>
     </row>
     <row r="25" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -9678,14 +10002,14 @@
         <v>23</v>
       </c>
       <c r="B25" s="5" t="s">
-        <v>645</v>
+        <v>653</v>
       </c>
       <c r="C25" s="5" t="s">
-        <v>646</v>
+        <v>654</v>
       </c>
       <c r="D25" s="5"/>
       <c r="E25" s="5" t="s">
-        <v>647</v>
+        <v>655</v>
       </c>
     </row>
     <row r="26" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -9693,14 +10017,14 @@
         <v>24</v>
       </c>
       <c r="B26" s="5" t="s">
-        <v>648</v>
+        <v>656</v>
       </c>
       <c r="C26" s="5" t="s">
-        <v>649</v>
+        <v>657</v>
       </c>
       <c r="D26" s="5"/>
       <c r="E26" s="5" t="s">
-        <v>650</v>
+        <v>658</v>
       </c>
     </row>
     <row r="27" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -9708,14 +10032,14 @@
         <v>25</v>
       </c>
       <c r="B27" s="5" t="s">
-        <v>651</v>
+        <v>659</v>
       </c>
       <c r="C27" s="5" t="s">
-        <v>652</v>
+        <v>660</v>
       </c>
       <c r="D27" s="5"/>
       <c r="E27" s="5" t="s">
-        <v>653</v>
+        <v>661</v>
       </c>
     </row>
     <row r="28" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -9723,14 +10047,14 @@
         <v>26</v>
       </c>
       <c r="B28" s="5" t="s">
-        <v>654</v>
+        <v>662</v>
       </c>
       <c r="C28" s="5" t="s">
-        <v>655</v>
+        <v>663</v>
       </c>
       <c r="D28" s="5"/>
       <c r="E28" s="5" t="s">
-        <v>656</v>
+        <v>664</v>
       </c>
     </row>
     <row r="29" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -9738,14 +10062,14 @@
         <v>27</v>
       </c>
       <c r="B29" s="5" t="s">
-        <v>657</v>
+        <v>665</v>
       </c>
       <c r="C29" s="5" t="s">
-        <v>658</v>
+        <v>666</v>
       </c>
       <c r="D29" s="5"/>
       <c r="E29" s="5" t="s">
-        <v>659</v>
+        <v>667</v>
       </c>
     </row>
     <row r="30" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -9753,14 +10077,14 @@
         <v>28</v>
       </c>
       <c r="B30" s="5" t="s">
-        <v>660</v>
+        <v>668</v>
       </c>
       <c r="C30" s="5" t="s">
-        <v>661</v>
+        <v>669</v>
       </c>
       <c r="D30" s="5"/>
       <c r="E30" s="5" t="s">
-        <v>662</v>
+        <v>670</v>
       </c>
     </row>
     <row r="31" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -9768,14 +10092,14 @@
         <v>29</v>
       </c>
       <c r="B31" s="5" t="s">
-        <v>663</v>
+        <v>671</v>
       </c>
       <c r="C31" s="5" t="s">
-        <v>664</v>
+        <v>672</v>
       </c>
       <c r="D31" s="5"/>
       <c r="E31" s="5" t="s">
-        <v>665</v>
+        <v>673</v>
       </c>
     </row>
     <row r="32" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -9783,14 +10107,14 @@
         <v>30</v>
       </c>
       <c r="B32" s="5" t="s">
-        <v>609</v>
+        <v>617</v>
       </c>
       <c r="C32" s="5" t="s">
-        <v>666</v>
+        <v>674</v>
       </c>
       <c r="D32" s="5"/>
       <c r="E32" s="5" t="s">
-        <v>667</v>
+        <v>675</v>
       </c>
     </row>
     <row r="33" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -9798,14 +10122,14 @@
         <v>31</v>
       </c>
       <c r="B33" s="5" t="s">
-        <v>668</v>
+        <v>676</v>
       </c>
       <c r="C33" s="5" t="s">
-        <v>669</v>
+        <v>677</v>
       </c>
       <c r="D33" s="5"/>
       <c r="E33" s="5" t="s">
-        <v>670</v>
+        <v>678</v>
       </c>
     </row>
     <row r="34" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -9813,14 +10137,14 @@
         <v>32</v>
       </c>
       <c r="B34" s="5" t="s">
-        <v>627</v>
+        <v>635</v>
       </c>
       <c r="C34" s="5" t="s">
-        <v>671</v>
+        <v>679</v>
       </c>
       <c r="D34" s="5"/>
       <c r="E34" s="5" t="s">
-        <v>672</v>
+        <v>680</v>
       </c>
     </row>
     <row r="35" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -9828,14 +10152,14 @@
         <v>33</v>
       </c>
       <c r="B35" s="5" t="s">
-        <v>673</v>
+        <v>681</v>
       </c>
       <c r="C35" s="5" t="s">
-        <v>674</v>
+        <v>682</v>
       </c>
       <c r="D35" s="5"/>
       <c r="E35" s="5" t="s">
-        <v>675</v>
+        <v>683</v>
       </c>
     </row>
     <row r="36" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -9843,14 +10167,14 @@
         <v>34</v>
       </c>
       <c r="B36" s="5" t="s">
-        <v>676</v>
+        <v>684</v>
       </c>
       <c r="C36" s="5" t="s">
-        <v>677</v>
+        <v>685</v>
       </c>
       <c r="D36" s="5"/>
       <c r="E36" s="5" t="s">
-        <v>678</v>
+        <v>686</v>
       </c>
     </row>
     <row r="37" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -9858,14 +10182,14 @@
         <v>35</v>
       </c>
       <c r="B37" s="5" t="s">
-        <v>679</v>
+        <v>687</v>
       </c>
       <c r="C37" s="5" t="s">
-        <v>680</v>
+        <v>688</v>
       </c>
       <c r="D37" s="5"/>
       <c r="E37" s="5" t="s">
-        <v>681</v>
+        <v>689</v>
       </c>
     </row>
     <row r="38" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -9873,14 +10197,14 @@
         <v>36</v>
       </c>
       <c r="B38" s="5" t="s">
-        <v>627</v>
+        <v>635</v>
       </c>
       <c r="C38" s="5" t="s">
-        <v>682</v>
+        <v>690</v>
       </c>
       <c r="D38" s="5"/>
       <c r="E38" s="5" t="s">
-        <v>683</v>
+        <v>691</v>
       </c>
     </row>
     <row r="39" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -9888,14 +10212,14 @@
         <v>37</v>
       </c>
       <c r="B39" s="5" t="s">
-        <v>684</v>
+        <v>692</v>
       </c>
       <c r="C39" s="5" t="s">
-        <v>685</v>
+        <v>693</v>
       </c>
       <c r="D39" s="5"/>
       <c r="E39" s="5" t="s">
-        <v>686</v>
+        <v>694</v>
       </c>
     </row>
     <row r="40" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -9903,14 +10227,14 @@
         <v>38</v>
       </c>
       <c r="B40" s="5" t="s">
-        <v>687</v>
+        <v>695</v>
       </c>
       <c r="C40" s="5" t="s">
-        <v>688</v>
+        <v>696</v>
       </c>
       <c r="D40" s="5"/>
       <c r="E40" s="5" t="s">
-        <v>689</v>
+        <v>697</v>
       </c>
     </row>
     <row r="41" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -9918,10 +10242,10 @@
         <v>39</v>
       </c>
       <c r="B41" s="5" t="s">
-        <v>690</v>
+        <v>698</v>
       </c>
       <c r="C41" s="5" t="s">
-        <v>691</v>
+        <v>699</v>
       </c>
       <c r="D41" s="5"/>
       <c r="E41" s="5" t="s">
@@ -9933,14 +10257,14 @@
         <v>40</v>
       </c>
       <c r="B42" s="5" t="s">
-        <v>692</v>
+        <v>700</v>
       </c>
       <c r="C42" s="5" t="s">
-        <v>693</v>
+        <v>701</v>
       </c>
       <c r="D42" s="5"/>
       <c r="E42" s="5" t="s">
-        <v>694</v>
+        <v>702</v>
       </c>
     </row>
     <row r="43" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -9948,14 +10272,14 @@
         <v>41</v>
       </c>
       <c r="B43" s="5" t="s">
-        <v>695</v>
+        <v>703</v>
       </c>
       <c r="C43" s="5" t="s">
-        <v>696</v>
+        <v>704</v>
       </c>
       <c r="D43" s="5"/>
       <c r="E43" s="5" t="s">
-        <v>697</v>
+        <v>705</v>
       </c>
     </row>
     <row r="44" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -9963,14 +10287,14 @@
         <v>42</v>
       </c>
       <c r="B44" s="5" t="s">
-        <v>698</v>
+        <v>706</v>
       </c>
       <c r="C44" s="5" t="s">
-        <v>699</v>
+        <v>707</v>
       </c>
       <c r="D44" s="5"/>
       <c r="E44" s="5" t="s">
-        <v>700</v>
+        <v>708</v>
       </c>
     </row>
     <row r="45" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -9978,14 +10302,14 @@
         <v>43</v>
       </c>
       <c r="B45" s="5" t="s">
-        <v>701</v>
+        <v>709</v>
       </c>
       <c r="C45" s="5" t="s">
-        <v>702</v>
+        <v>710</v>
       </c>
       <c r="D45" s="5"/>
       <c r="E45" s="5" t="s">
-        <v>703</v>
+        <v>711</v>
       </c>
     </row>
     <row r="46" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -9993,14 +10317,14 @@
         <v>44</v>
       </c>
       <c r="B46" s="5" t="s">
-        <v>704</v>
+        <v>712</v>
       </c>
       <c r="C46" s="5" t="s">
-        <v>705</v>
+        <v>713</v>
       </c>
       <c r="D46" s="5"/>
       <c r="E46" s="5" t="s">
-        <v>706</v>
+        <v>714</v>
       </c>
     </row>
     <row r="47" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -10008,14 +10332,14 @@
         <v>45</v>
       </c>
       <c r="B47" s="5" t="s">
-        <v>707</v>
+        <v>715</v>
       </c>
       <c r="C47" s="5" t="s">
-        <v>708</v>
+        <v>716</v>
       </c>
       <c r="D47" s="5"/>
       <c r="E47" s="5" t="s">
-        <v>709</v>
+        <v>717</v>
       </c>
     </row>
     <row r="48" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -10023,14 +10347,14 @@
         <v>46</v>
       </c>
       <c r="B48" s="5" t="s">
-        <v>710</v>
+        <v>718</v>
       </c>
       <c r="C48" s="5" t="s">
-        <v>711</v>
+        <v>719</v>
       </c>
       <c r="D48" s="5"/>
       <c r="E48" s="5" t="s">
-        <v>712</v>
+        <v>720</v>
       </c>
     </row>
     <row r="49" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -10038,14 +10362,14 @@
         <v>47</v>
       </c>
       <c r="B49" s="5" t="s">
-        <v>713</v>
+        <v>721</v>
       </c>
       <c r="C49" s="5" t="s">
-        <v>714</v>
+        <v>722</v>
       </c>
       <c r="D49" s="5"/>
       <c r="E49" s="5" t="s">
-        <v>715</v>
+        <v>723</v>
       </c>
     </row>
     <row r="50" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -10053,14 +10377,14 @@
         <v>48</v>
       </c>
       <c r="B50" s="5" t="s">
-        <v>716</v>
+        <v>724</v>
       </c>
       <c r="C50" s="5" t="s">
-        <v>717</v>
+        <v>725</v>
       </c>
       <c r="D50" s="5"/>
       <c r="E50" s="5" t="s">
-        <v>718</v>
+        <v>726</v>
       </c>
     </row>
     <row r="51" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -10068,14 +10392,14 @@
         <v>49</v>
       </c>
       <c r="B51" s="5" t="s">
-        <v>719</v>
+        <v>727</v>
       </c>
       <c r="C51" s="5" t="s">
-        <v>720</v>
+        <v>728</v>
       </c>
       <c r="D51" s="5"/>
       <c r="E51" s="5" t="s">
-        <v>721</v>
+        <v>729</v>
       </c>
     </row>
     <row r="52" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -10083,14 +10407,14 @@
         <v>50</v>
       </c>
       <c r="B52" s="5" t="s">
-        <v>722</v>
+        <v>730</v>
       </c>
       <c r="C52" s="5" t="s">
-        <v>723</v>
+        <v>731</v>
       </c>
       <c r="D52" s="5"/>
       <c r="E52" s="5" t="s">
-        <v>724</v>
+        <v>732</v>
       </c>
     </row>
     <row r="53" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -10098,14 +10422,14 @@
         <v>51</v>
       </c>
       <c r="B53" s="5" t="s">
-        <v>725</v>
+        <v>733</v>
       </c>
       <c r="C53" s="5" t="s">
-        <v>726</v>
+        <v>734</v>
       </c>
       <c r="D53" s="5"/>
       <c r="E53" s="5" t="s">
-        <v>727</v>
+        <v>735</v>
       </c>
     </row>
     <row r="54" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -10113,14 +10437,14 @@
         <v>52</v>
       </c>
       <c r="B54" s="5" t="s">
-        <v>627</v>
+        <v>635</v>
       </c>
       <c r="C54" s="5" t="s">
-        <v>728</v>
+        <v>736</v>
       </c>
       <c r="D54" s="5"/>
       <c r="E54" s="5" t="s">
-        <v>729</v>
+        <v>737</v>
       </c>
     </row>
     <row r="55" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -10128,14 +10452,14 @@
         <v>53</v>
       </c>
       <c r="B55" s="5" t="s">
-        <v>730</v>
+        <v>738</v>
       </c>
       <c r="C55" s="5" t="s">
-        <v>731</v>
+        <v>739</v>
       </c>
       <c r="D55" s="5"/>
       <c r="E55" s="5" t="s">
-        <v>732</v>
+        <v>740</v>
       </c>
     </row>
     <row r="56" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -10143,14 +10467,14 @@
         <v>54</v>
       </c>
       <c r="B56" s="5" t="s">
-        <v>733</v>
+        <v>741</v>
       </c>
       <c r="C56" s="5" t="s">
-        <v>734</v>
+        <v>742</v>
       </c>
       <c r="D56" s="5"/>
       <c r="E56" s="5" t="s">
-        <v>735</v>
+        <v>743</v>
       </c>
     </row>
     <row r="57" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -10158,14 +10482,14 @@
         <v>55</v>
       </c>
       <c r="B57" s="5" t="s">
-        <v>736</v>
+        <v>744</v>
       </c>
       <c r="C57" s="5" t="s">
-        <v>737</v>
+        <v>745</v>
       </c>
       <c r="D57" s="5"/>
       <c r="E57" s="5" t="s">
-        <v>738</v>
+        <v>746</v>
       </c>
     </row>
     <row r="58" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -10173,14 +10497,14 @@
         <v>56</v>
       </c>
       <c r="B58" s="5" t="s">
-        <v>739</v>
+        <v>747</v>
       </c>
       <c r="C58" s="5" t="s">
-        <v>740</v>
+        <v>748</v>
       </c>
       <c r="D58" s="5"/>
       <c r="E58" s="5" t="s">
-        <v>741</v>
+        <v>749</v>
       </c>
     </row>
     <row r="59" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -10188,14 +10512,14 @@
         <v>57</v>
       </c>
       <c r="B59" s="5" t="s">
-        <v>742</v>
+        <v>750</v>
       </c>
       <c r="C59" s="5" t="s">
-        <v>743</v>
+        <v>751</v>
       </c>
       <c r="D59" s="5"/>
       <c r="E59" s="5" t="s">
-        <v>744</v>
+        <v>752</v>
       </c>
     </row>
     <row r="60" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -10203,14 +10527,14 @@
         <v>58</v>
       </c>
       <c r="B60" s="5" t="s">
-        <v>745</v>
+        <v>753</v>
       </c>
       <c r="C60" s="5" t="s">
-        <v>746</v>
+        <v>754</v>
       </c>
       <c r="D60" s="5"/>
       <c r="E60" s="5" t="s">
-        <v>747</v>
+        <v>755</v>
       </c>
     </row>
     <row r="61" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -10218,14 +10542,14 @@
         <v>59</v>
       </c>
       <c r="B61" s="5" t="s">
-        <v>748</v>
+        <v>756</v>
       </c>
       <c r="C61" s="5" t="s">
-        <v>749</v>
+        <v>757</v>
       </c>
       <c r="D61" s="5"/>
       <c r="E61" s="5" t="s">
-        <v>750</v>
+        <v>758</v>
       </c>
     </row>
     <row r="62" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -10233,14 +10557,14 @@
         <v>60</v>
       </c>
       <c r="B62" s="5" t="s">
-        <v>751</v>
+        <v>759</v>
       </c>
       <c r="C62" s="5" t="s">
-        <v>752</v>
+        <v>760</v>
       </c>
       <c r="D62" s="5"/>
       <c r="E62" s="5" t="s">
-        <v>753</v>
+        <v>761</v>
       </c>
     </row>
     <row r="63" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -10248,14 +10572,14 @@
         <v>61</v>
       </c>
       <c r="B63" s="5" t="s">
-        <v>754</v>
+        <v>762</v>
       </c>
       <c r="C63" s="5" t="s">
-        <v>755</v>
+        <v>763</v>
       </c>
       <c r="D63" s="5"/>
       <c r="E63" s="5" t="s">
-        <v>756</v>
+        <v>764</v>
       </c>
     </row>
     <row r="64" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -10263,14 +10587,14 @@
         <v>62</v>
       </c>
       <c r="B64" s="5" t="s">
-        <v>757</v>
+        <v>765</v>
       </c>
       <c r="C64" s="5" t="s">
-        <v>758</v>
+        <v>766</v>
       </c>
       <c r="D64" s="5"/>
       <c r="E64" s="5" t="s">
-        <v>759</v>
+        <v>767</v>
       </c>
     </row>
     <row r="65" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -10278,14 +10602,14 @@
         <v>63</v>
       </c>
       <c r="B65" s="5" t="s">
-        <v>760</v>
+        <v>768</v>
       </c>
       <c r="C65" s="5" t="s">
-        <v>761</v>
+        <v>769</v>
       </c>
       <c r="D65" s="5"/>
       <c r="E65" s="5" t="s">
-        <v>762</v>
+        <v>770</v>
       </c>
     </row>
     <row r="66" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -10293,14 +10617,14 @@
         <v>64</v>
       </c>
       <c r="B66" s="5" t="s">
-        <v>763</v>
+        <v>771</v>
       </c>
       <c r="C66" s="5" t="s">
-        <v>764</v>
+        <v>772</v>
       </c>
       <c r="D66" s="5"/>
       <c r="E66" s="5" t="s">
-        <v>765</v>
+        <v>773</v>
       </c>
     </row>
     <row r="67" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -10308,14 +10632,14 @@
         <v>65</v>
       </c>
       <c r="B67" s="5" t="s">
-        <v>766</v>
+        <v>774</v>
       </c>
       <c r="C67" s="5" t="s">
-        <v>767</v>
+        <v>775</v>
       </c>
       <c r="D67" s="5"/>
       <c r="E67" s="5" t="s">
-        <v>768</v>
+        <v>776</v>
       </c>
     </row>
     <row r="68" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -10323,14 +10647,14 @@
         <v>66</v>
       </c>
       <c r="B68" s="5" t="s">
-        <v>769</v>
+        <v>777</v>
       </c>
       <c r="C68" s="5" t="s">
-        <v>770</v>
+        <v>778</v>
       </c>
       <c r="D68" s="5"/>
       <c r="E68" s="5" t="s">
-        <v>771</v>
+        <v>779</v>
       </c>
     </row>
     <row r="69" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -10338,14 +10662,14 @@
         <v>67</v>
       </c>
       <c r="B69" s="5" t="s">
-        <v>772</v>
+        <v>780</v>
       </c>
       <c r="C69" s="5" t="s">
-        <v>773</v>
+        <v>781</v>
       </c>
       <c r="D69" s="5"/>
       <c r="E69" s="5" t="s">
-        <v>774</v>
+        <v>782</v>
       </c>
     </row>
     <row r="70" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -10353,14 +10677,14 @@
         <v>68</v>
       </c>
       <c r="B70" s="5" t="s">
-        <v>775</v>
+        <v>783</v>
       </c>
       <c r="C70" s="5" t="s">
-        <v>776</v>
+        <v>784</v>
       </c>
       <c r="D70" s="5"/>
       <c r="E70" s="5" t="s">
-        <v>777</v>
+        <v>785</v>
       </c>
     </row>
     <row r="71" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -10368,14 +10692,14 @@
         <v>69</v>
       </c>
       <c r="B71" s="5" t="s">
-        <v>778</v>
+        <v>786</v>
       </c>
       <c r="C71" s="5" t="s">
-        <v>779</v>
+        <v>787</v>
       </c>
       <c r="D71" s="5"/>
       <c r="E71" s="5" t="s">
-        <v>780</v>
+        <v>788</v>
       </c>
     </row>
     <row r="72" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -10383,14 +10707,14 @@
         <v>70</v>
       </c>
       <c r="B72" s="5" t="s">
-        <v>781</v>
+        <v>789</v>
       </c>
       <c r="C72" s="5" t="s">
-        <v>782</v>
+        <v>790</v>
       </c>
       <c r="D72" s="5"/>
       <c r="E72" s="5" t="s">
-        <v>783</v>
+        <v>791</v>
       </c>
     </row>
     <row r="73" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -10398,14 +10722,14 @@
         <v>71</v>
       </c>
       <c r="B73" s="5" t="s">
-        <v>784</v>
+        <v>792</v>
       </c>
       <c r="C73" s="5" t="s">
-        <v>785</v>
+        <v>793</v>
       </c>
       <c r="D73" s="5"/>
       <c r="E73" s="5" t="s">
-        <v>786</v>
+        <v>794</v>
       </c>
     </row>
     <row r="74" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -10413,14 +10737,14 @@
         <v>72</v>
       </c>
       <c r="B74" s="5" t="s">
-        <v>787</v>
+        <v>795</v>
       </c>
       <c r="C74" s="5" t="s">
-        <v>788</v>
+        <v>796</v>
       </c>
       <c r="D74" s="5"/>
       <c r="E74" s="5" t="s">
-        <v>789</v>
+        <v>797</v>
       </c>
     </row>
     <row r="75" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -10428,14 +10752,14 @@
         <v>73</v>
       </c>
       <c r="B75" s="5" t="s">
-        <v>627</v>
+        <v>635</v>
       </c>
       <c r="C75" s="5" t="s">
-        <v>790</v>
+        <v>798</v>
       </c>
       <c r="D75" s="5"/>
       <c r="E75" s="5" t="s">
-        <v>791</v>
+        <v>799</v>
       </c>
     </row>
     <row r="76" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -10443,14 +10767,14 @@
         <v>74</v>
       </c>
       <c r="B76" s="5" t="s">
-        <v>792</v>
+        <v>800</v>
       </c>
       <c r="C76" s="5" t="s">
-        <v>793</v>
+        <v>801</v>
       </c>
       <c r="D76" s="5"/>
       <c r="E76" s="5" t="s">
-        <v>794</v>
+        <v>802</v>
       </c>
     </row>
     <row r="77" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -10458,14 +10782,14 @@
         <v>75</v>
       </c>
       <c r="B77" s="5" t="s">
-        <v>627</v>
+        <v>635</v>
       </c>
       <c r="C77" s="5" t="s">
-        <v>795</v>
+        <v>803</v>
       </c>
       <c r="D77" s="5"/>
       <c r="E77" s="5" t="s">
-        <v>796</v>
+        <v>804</v>
       </c>
     </row>
     <row r="78" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -10473,14 +10797,14 @@
         <v>76</v>
       </c>
       <c r="B78" s="5" t="s">
-        <v>797</v>
+        <v>805</v>
       </c>
       <c r="C78" s="5" t="s">
-        <v>798</v>
+        <v>806</v>
       </c>
       <c r="D78" s="5"/>
       <c r="E78" s="5" t="s">
-        <v>799</v>
+        <v>807</v>
       </c>
     </row>
     <row r="79" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -10488,14 +10812,14 @@
         <v>77</v>
       </c>
       <c r="B79" s="5" t="s">
-        <v>800</v>
+        <v>808</v>
       </c>
       <c r="C79" s="5" t="s">
-        <v>801</v>
+        <v>809</v>
       </c>
       <c r="D79" s="5"/>
       <c r="E79" s="5" t="s">
-        <v>802</v>
+        <v>810</v>
       </c>
     </row>
     <row r="80" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -10503,14 +10827,14 @@
         <v>78</v>
       </c>
       <c r="B80" s="5" t="s">
-        <v>725</v>
+        <v>733</v>
       </c>
       <c r="C80" s="5" t="s">
-        <v>803</v>
+        <v>811</v>
       </c>
       <c r="D80" s="5"/>
       <c r="E80" s="5" t="s">
-        <v>804</v>
+        <v>812</v>
       </c>
     </row>
     <row r="81" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -10518,14 +10842,14 @@
         <v>79</v>
       </c>
       <c r="B81" s="5" t="s">
-        <v>597</v>
+        <v>605</v>
       </c>
       <c r="C81" s="5" t="s">
-        <v>805</v>
+        <v>813</v>
       </c>
       <c r="D81" s="5"/>
       <c r="E81" s="5" t="s">
-        <v>806</v>
+        <v>814</v>
       </c>
     </row>
     <row r="82" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -10533,16 +10857,16 @@
         <v>80</v>
       </c>
       <c r="B82" s="5" t="s">
-        <v>807</v>
+        <v>815</v>
       </c>
       <c r="C82" s="5" t="s">
-        <v>808</v>
+        <v>816</v>
       </c>
       <c r="D82" s="6" t="s">
-        <v>809</v>
+        <v>817</v>
       </c>
       <c r="E82" s="5" t="s">
-        <v>810</v>
+        <v>818</v>
       </c>
     </row>
     <row r="83" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -10550,16 +10874,16 @@
         <v>81</v>
       </c>
       <c r="B83" s="5" t="s">
-        <v>811</v>
+        <v>819</v>
       </c>
       <c r="C83" s="5" t="s">
-        <v>812</v>
+        <v>820</v>
       </c>
       <c r="D83" s="6" t="s">
-        <v>813</v>
+        <v>821</v>
       </c>
       <c r="E83" s="5" t="s">
-        <v>814</v>
+        <v>822</v>
       </c>
     </row>
     <row r="84" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -10567,13 +10891,13 @@
         <v>82</v>
       </c>
       <c r="B84" s="5" t="s">
-        <v>815</v>
+        <v>823</v>
       </c>
       <c r="C84" s="5" t="s">
-        <v>816</v>
+        <v>824</v>
       </c>
       <c r="D84" s="6" t="s">
-        <v>817</v>
+        <v>825</v>
       </c>
       <c r="E84" s="5" t="s">
         <v>297</v>
@@ -10584,13 +10908,13 @@
         <v>83</v>
       </c>
       <c r="B85" s="5" t="s">
-        <v>818</v>
+        <v>826</v>
       </c>
       <c r="C85" s="5" t="s">
-        <v>819</v>
+        <v>827</v>
       </c>
       <c r="D85" s="6" t="s">
-        <v>820</v>
+        <v>828</v>
       </c>
       <c r="E85" s="5" t="s">
         <v>300</v>
@@ -10601,16 +10925,16 @@
         <v>84</v>
       </c>
       <c r="B86" s="5" t="s">
-        <v>821</v>
+        <v>829</v>
       </c>
       <c r="C86" s="5" t="s">
-        <v>822</v>
+        <v>830</v>
       </c>
       <c r="D86" s="6" t="s">
-        <v>823</v>
+        <v>831</v>
       </c>
       <c r="E86" s="5" t="s">
-        <v>824</v>
+        <v>832</v>
       </c>
     </row>
     <row r="87" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -10618,16 +10942,16 @@
         <v>85</v>
       </c>
       <c r="B87" s="5" t="s">
-        <v>825</v>
+        <v>833</v>
       </c>
       <c r="C87" s="5" t="s">
-        <v>826</v>
+        <v>834</v>
       </c>
       <c r="D87" s="6" t="s">
-        <v>827</v>
+        <v>835</v>
       </c>
       <c r="E87" s="5" t="s">
-        <v>828</v>
+        <v>836</v>
       </c>
     </row>
     <row r="88" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -10635,16 +10959,16 @@
         <v>86</v>
       </c>
       <c r="B88" s="5" t="s">
-        <v>829</v>
+        <v>837</v>
       </c>
       <c r="C88" s="5" t="s">
-        <v>830</v>
+        <v>838</v>
       </c>
       <c r="D88" s="6" t="s">
-        <v>831</v>
+        <v>839</v>
       </c>
       <c r="E88" s="5" t="s">
-        <v>828</v>
+        <v>836</v>
       </c>
     </row>
     <row r="89" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -10652,16 +10976,16 @@
         <v>87</v>
       </c>
       <c r="B89" s="5" t="s">
-        <v>832</v>
+        <v>840</v>
       </c>
       <c r="C89" s="5" t="s">
-        <v>833</v>
+        <v>841</v>
       </c>
       <c r="D89" s="6" t="s">
-        <v>834</v>
+        <v>842</v>
       </c>
       <c r="E89" s="5" t="s">
-        <v>828</v>
+        <v>836</v>
       </c>
     </row>
     <row r="90" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -10669,16 +10993,16 @@
         <v>88</v>
       </c>
       <c r="B90" s="5" t="s">
-        <v>835</v>
+        <v>843</v>
       </c>
       <c r="C90" s="5" t="s">
-        <v>836</v>
+        <v>844</v>
       </c>
       <c r="D90" s="6" t="s">
-        <v>837</v>
+        <v>845</v>
       </c>
       <c r="E90" s="5" t="s">
-        <v>838</v>
+        <v>846</v>
       </c>
     </row>
     <row r="91" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -10686,16 +11010,16 @@
         <v>89</v>
       </c>
       <c r="B91" s="5" t="s">
-        <v>839</v>
+        <v>847</v>
       </c>
       <c r="C91" s="5" t="s">
-        <v>840</v>
+        <v>848</v>
       </c>
       <c r="D91" s="6" t="s">
-        <v>841</v>
+        <v>849</v>
       </c>
       <c r="E91" s="5" t="s">
-        <v>838</v>
+        <v>846</v>
       </c>
     </row>
     <row r="92" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -10703,16 +11027,16 @@
         <v>90</v>
       </c>
       <c r="B92" s="5" t="s">
-        <v>829</v>
+        <v>837</v>
       </c>
       <c r="C92" s="5" t="s">
-        <v>842</v>
+        <v>850</v>
       </c>
       <c r="D92" s="6" t="s">
-        <v>843</v>
+        <v>851</v>
       </c>
       <c r="E92" s="5" t="s">
-        <v>844</v>
+        <v>852</v>
       </c>
     </row>
     <row r="93" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -10720,16 +11044,16 @@
         <v>91</v>
       </c>
       <c r="B93" s="5" t="s">
-        <v>845</v>
+        <v>853</v>
       </c>
       <c r="C93" s="5" t="s">
-        <v>846</v>
+        <v>854</v>
       </c>
       <c r="D93" s="6" t="s">
-        <v>847</v>
+        <v>855</v>
       </c>
       <c r="E93" s="5" t="s">
-        <v>844</v>
+        <v>852</v>
       </c>
     </row>
     <row r="94" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -10737,16 +11061,16 @@
         <v>92</v>
       </c>
       <c r="B94" s="5" t="s">
-        <v>848</v>
+        <v>856</v>
       </c>
       <c r="C94" s="5" t="s">
-        <v>849</v>
+        <v>857</v>
       </c>
       <c r="D94" s="6" t="s">
-        <v>850</v>
+        <v>858</v>
       </c>
       <c r="E94" s="5" t="s">
-        <v>851</v>
+        <v>859</v>
       </c>
     </row>
     <row r="95" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -10754,16 +11078,16 @@
         <v>93</v>
       </c>
       <c r="B95" s="5" t="s">
-        <v>690</v>
+        <v>698</v>
       </c>
       <c r="C95" s="5" t="s">
-        <v>852</v>
+        <v>860</v>
       </c>
       <c r="D95" s="6" t="s">
-        <v>853</v>
+        <v>861</v>
       </c>
       <c r="E95" s="5" t="s">
-        <v>854</v>
+        <v>862</v>
       </c>
     </row>
     <row r="96" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -10771,16 +11095,16 @@
         <v>94</v>
       </c>
       <c r="B96" s="5" t="s">
-        <v>835</v>
+        <v>843</v>
       </c>
       <c r="C96" s="5" t="s">
-        <v>855</v>
+        <v>863</v>
       </c>
       <c r="D96" s="6" t="s">
-        <v>856</v>
+        <v>864</v>
       </c>
       <c r="E96" s="5" t="s">
-        <v>854</v>
+        <v>862</v>
       </c>
     </row>
     <row r="97" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -10788,16 +11112,16 @@
         <v>95</v>
       </c>
       <c r="B97" s="5" t="s">
-        <v>857</v>
+        <v>865</v>
       </c>
       <c r="C97" s="5" t="s">
-        <v>858</v>
+        <v>866</v>
       </c>
       <c r="D97" s="6" t="s">
-        <v>859</v>
+        <v>867</v>
       </c>
       <c r="E97" s="5" t="s">
-        <v>854</v>
+        <v>862</v>
       </c>
     </row>
     <row r="98" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -10805,16 +11129,16 @@
         <v>96</v>
       </c>
       <c r="B98" s="5" t="s">
-        <v>815</v>
+        <v>823</v>
       </c>
       <c r="C98" s="5" t="s">
-        <v>860</v>
+        <v>868</v>
       </c>
       <c r="D98" s="6" t="s">
-        <v>861</v>
+        <v>869</v>
       </c>
       <c r="E98" s="5" t="s">
-        <v>844</v>
+        <v>852</v>
       </c>
     </row>
     <row r="99" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -10822,16 +11146,16 @@
         <v>97</v>
       </c>
       <c r="B99" s="5" t="s">
-        <v>862</v>
+        <v>870</v>
       </c>
       <c r="C99" s="5" t="s">
-        <v>863</v>
+        <v>871</v>
       </c>
       <c r="D99" s="6" t="s">
-        <v>864</v>
+        <v>872</v>
       </c>
       <c r="E99" s="5" t="s">
-        <v>865</v>
+        <v>873</v>
       </c>
     </row>
     <row r="100" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -10839,16 +11163,16 @@
         <v>98</v>
       </c>
       <c r="B100" s="5" t="s">
-        <v>829</v>
+        <v>837</v>
       </c>
       <c r="C100" s="5" t="s">
-        <v>866</v>
+        <v>874</v>
       </c>
       <c r="D100" s="6" t="s">
-        <v>867</v>
+        <v>875</v>
       </c>
       <c r="E100" s="5" t="s">
-        <v>868</v>
+        <v>876</v>
       </c>
     </row>
     <row r="101" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -10856,16 +11180,16 @@
         <v>99</v>
       </c>
       <c r="B101" s="5" t="s">
-        <v>835</v>
+        <v>843</v>
       </c>
       <c r="C101" s="5" t="s">
-        <v>869</v>
+        <v>877</v>
       </c>
       <c r="D101" s="6" t="s">
-        <v>870</v>
+        <v>878</v>
       </c>
       <c r="E101" s="5" t="s">
-        <v>871</v>
+        <v>879</v>
       </c>
     </row>
     <row r="102" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -10873,16 +11197,16 @@
         <v>100</v>
       </c>
       <c r="B102" s="5" t="s">
-        <v>872</v>
+        <v>880</v>
       </c>
       <c r="C102" s="5" t="s">
-        <v>873</v>
+        <v>881</v>
       </c>
       <c r="D102" s="6" t="s">
-        <v>874</v>
+        <v>882</v>
       </c>
       <c r="E102" s="5" t="s">
-        <v>875</v>
+        <v>883</v>
       </c>
     </row>
     <row r="103" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -10890,16 +11214,16 @@
         <v>101</v>
       </c>
       <c r="B103" s="5" t="s">
-        <v>815</v>
+        <v>823</v>
       </c>
       <c r="C103" s="5" t="s">
-        <v>876</v>
+        <v>884</v>
       </c>
       <c r="D103" s="6" t="s">
-        <v>877</v>
+        <v>885</v>
       </c>
       <c r="E103" s="5" t="s">
-        <v>878</v>
+        <v>886</v>
       </c>
     </row>
     <row r="104" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -10907,13 +11231,13 @@
         <v>102</v>
       </c>
       <c r="B104" s="5" t="s">
-        <v>690</v>
+        <v>698</v>
       </c>
       <c r="C104" s="5" t="s">
-        <v>879</v>
+        <v>887</v>
       </c>
       <c r="D104" s="6" t="s">
-        <v>880</v>
+        <v>888</v>
       </c>
       <c r="E104" s="5" t="s">
         <v>352</v>
@@ -10924,16 +11248,16 @@
         <v>103</v>
       </c>
       <c r="B105" s="5" t="s">
-        <v>881</v>
+        <v>889</v>
       </c>
       <c r="C105" s="5" t="s">
-        <v>882</v>
+        <v>890</v>
       </c>
       <c r="D105" s="6" t="s">
-        <v>883</v>
+        <v>891</v>
       </c>
       <c r="E105" s="5" t="s">
-        <v>884</v>
+        <v>892</v>
       </c>
     </row>
     <row r="106" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -10941,16 +11265,16 @@
         <v>104</v>
       </c>
       <c r="B106" s="5" t="s">
-        <v>885</v>
+        <v>893</v>
       </c>
       <c r="C106" s="5" t="s">
-        <v>886</v>
+        <v>894</v>
       </c>
       <c r="D106" s="6" t="s">
-        <v>887</v>
+        <v>895</v>
       </c>
       <c r="E106" s="5" t="s">
-        <v>888</v>
+        <v>896</v>
       </c>
     </row>
     <row r="107" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -10958,16 +11282,16 @@
         <v>105</v>
       </c>
       <c r="B107" s="5" t="s">
-        <v>889</v>
+        <v>897</v>
       </c>
       <c r="C107" s="5" t="s">
-        <v>890</v>
+        <v>898</v>
       </c>
       <c r="D107" s="6" t="s">
-        <v>891</v>
+        <v>899</v>
       </c>
       <c r="E107" s="5" t="s">
-        <v>892</v>
+        <v>900</v>
       </c>
     </row>
     <row r="108" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -10975,16 +11299,16 @@
         <v>106</v>
       </c>
       <c r="B108" s="5" t="s">
-        <v>885</v>
+        <v>893</v>
       </c>
       <c r="C108" s="5" t="s">
-        <v>893</v>
+        <v>901</v>
       </c>
       <c r="D108" s="6" t="s">
-        <v>894</v>
+        <v>902</v>
       </c>
       <c r="E108" s="5" t="s">
-        <v>895</v>
+        <v>903</v>
       </c>
     </row>
     <row r="109" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -10992,13 +11316,13 @@
         <v>107</v>
       </c>
       <c r="B109" s="5" t="s">
-        <v>896</v>
+        <v>904</v>
       </c>
       <c r="C109" s="5" t="s">
-        <v>897</v>
+        <v>905</v>
       </c>
       <c r="D109" s="6" t="s">
-        <v>898</v>
+        <v>906</v>
       </c>
       <c r="E109" s="5" t="s">
         <v>368</v>
@@ -11009,13 +11333,13 @@
         <v>108</v>
       </c>
       <c r="B110" s="5" t="s">
-        <v>690</v>
+        <v>698</v>
       </c>
       <c r="C110" s="5" t="s">
-        <v>899</v>
+        <v>907</v>
       </c>
       <c r="D110" s="6" t="s">
-        <v>900</v>
+        <v>908</v>
       </c>
       <c r="E110" s="5" t="s">
         <v>368</v>
@@ -11026,16 +11350,16 @@
         <v>109</v>
       </c>
       <c r="B111" s="5" t="s">
-        <v>889</v>
+        <v>897</v>
       </c>
       <c r="C111" s="5" t="s">
-        <v>901</v>
+        <v>909</v>
       </c>
       <c r="D111" s="6" t="s">
-        <v>902</v>
+        <v>910</v>
       </c>
       <c r="E111" s="5" t="s">
-        <v>903</v>
+        <v>911</v>
       </c>
     </row>
     <row r="112" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -11043,16 +11367,16 @@
         <v>110</v>
       </c>
       <c r="B112" s="5" t="s">
-        <v>829</v>
+        <v>837</v>
       </c>
       <c r="C112" s="5" t="s">
-        <v>904</v>
+        <v>912</v>
       </c>
       <c r="D112" s="6" t="s">
-        <v>905</v>
+        <v>913</v>
       </c>
       <c r="E112" s="5" t="s">
-        <v>906</v>
+        <v>914</v>
       </c>
     </row>
     <row r="113" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -11060,13 +11384,13 @@
         <v>111</v>
       </c>
       <c r="B113" s="5" t="s">
-        <v>821</v>
+        <v>829</v>
       </c>
       <c r="C113" s="5" t="s">
-        <v>907</v>
+        <v>915</v>
       </c>
       <c r="D113" s="6" t="s">
-        <v>908</v>
+        <v>916</v>
       </c>
       <c r="E113" s="5" t="s">
         <v>382</v>
@@ -11077,16 +11401,16 @@
         <v>112</v>
       </c>
       <c r="B114" s="5" t="s">
-        <v>829</v>
+        <v>837</v>
       </c>
       <c r="C114" s="5" t="s">
-        <v>909</v>
+        <v>917</v>
       </c>
       <c r="D114" s="6" t="s">
-        <v>910</v>
+        <v>918</v>
       </c>
       <c r="E114" s="5" t="s">
-        <v>911</v>
+        <v>919</v>
       </c>
     </row>
     <row r="115" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -11094,16 +11418,16 @@
         <v>113</v>
       </c>
       <c r="B115" s="5" t="s">
-        <v>912</v>
+        <v>920</v>
       </c>
       <c r="C115" s="5" t="s">
-        <v>913</v>
+        <v>921</v>
       </c>
       <c r="D115" s="6" t="s">
-        <v>914</v>
+        <v>922</v>
       </c>
       <c r="E115" s="5" t="s">
-        <v>915</v>
+        <v>923</v>
       </c>
     </row>
     <row r="116" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -11111,16 +11435,16 @@
         <v>114</v>
       </c>
       <c r="B116" s="5" t="s">
-        <v>835</v>
+        <v>843</v>
       </c>
       <c r="C116" s="5" t="s">
-        <v>916</v>
+        <v>924</v>
       </c>
       <c r="D116" s="6" t="s">
-        <v>917</v>
+        <v>925</v>
       </c>
       <c r="E116" s="5" t="s">
-        <v>915</v>
+        <v>923</v>
       </c>
     </row>
     <row r="117" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -11128,16 +11452,16 @@
         <v>115</v>
       </c>
       <c r="B117" s="5" t="s">
-        <v>918</v>
+        <v>926</v>
       </c>
       <c r="C117" s="5" t="s">
-        <v>919</v>
+        <v>927</v>
       </c>
       <c r="D117" s="6" t="s">
-        <v>920</v>
+        <v>928</v>
       </c>
       <c r="E117" s="5" t="s">
-        <v>921</v>
+        <v>929</v>
       </c>
     </row>
     <row r="118" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -11145,13 +11469,13 @@
         <v>116</v>
       </c>
       <c r="B118" s="5" t="s">
-        <v>835</v>
+        <v>843</v>
       </c>
       <c r="C118" s="5" t="s">
-        <v>922</v>
+        <v>930</v>
       </c>
       <c r="D118" s="6" t="s">
-        <v>923</v>
+        <v>931</v>
       </c>
       <c r="E118" s="5" t="s">
         <v>396</v>
@@ -11162,16 +11486,16 @@
         <v>117</v>
       </c>
       <c r="B119" s="5" t="s">
-        <v>924</v>
+        <v>932</v>
       </c>
       <c r="C119" s="5" t="s">
-        <v>925</v>
+        <v>933</v>
       </c>
       <c r="D119" s="6" t="s">
-        <v>926</v>
+        <v>934</v>
       </c>
       <c r="E119" s="5" t="s">
-        <v>927</v>
+        <v>935</v>
       </c>
     </row>
     <row r="120" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -11179,16 +11503,16 @@
         <v>118</v>
       </c>
       <c r="B120" s="5" t="s">
-        <v>912</v>
+        <v>920</v>
       </c>
       <c r="C120" s="5" t="s">
-        <v>928</v>
+        <v>936</v>
       </c>
       <c r="D120" s="6" t="s">
-        <v>929</v>
+        <v>937</v>
       </c>
       <c r="E120" s="5" t="s">
-        <v>930</v>
+        <v>938</v>
       </c>
     </row>
     <row r="121" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -11196,16 +11520,16 @@
         <v>119</v>
       </c>
       <c r="B121" s="5" t="s">
-        <v>931</v>
+        <v>939</v>
       </c>
       <c r="C121" s="5" t="s">
-        <v>932</v>
+        <v>940</v>
       </c>
       <c r="D121" s="6" t="s">
-        <v>933</v>
+        <v>941</v>
       </c>
       <c r="E121" s="5" t="s">
-        <v>927</v>
+        <v>935</v>
       </c>
     </row>
     <row r="122" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -11213,16 +11537,16 @@
         <v>120</v>
       </c>
       <c r="B122" s="5" t="s">
-        <v>934</v>
+        <v>942</v>
       </c>
       <c r="C122" s="5" t="s">
-        <v>935</v>
+        <v>943</v>
       </c>
       <c r="D122" s="6" t="s">
-        <v>936</v>
+        <v>944</v>
       </c>
       <c r="E122" s="5" t="s">
-        <v>937</v>
+        <v>945</v>
       </c>
     </row>
     <row r="123" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -11230,13 +11554,13 @@
         <v>121</v>
       </c>
       <c r="B123" s="5" t="s">
-        <v>835</v>
+        <v>843</v>
       </c>
       <c r="C123" s="5" t="s">
-        <v>938</v>
+        <v>946</v>
       </c>
       <c r="D123" s="6" t="s">
-        <v>939</v>
+        <v>947</v>
       </c>
       <c r="E123" s="5" t="s">
         <v>409</v>
@@ -11247,13 +11571,13 @@
         <v>122</v>
       </c>
       <c r="B124" s="5" t="s">
-        <v>896</v>
+        <v>904</v>
       </c>
       <c r="C124" s="5" t="s">
-        <v>940</v>
+        <v>948</v>
       </c>
       <c r="D124" s="6" t="s">
-        <v>941</v>
+        <v>949</v>
       </c>
       <c r="E124" s="5" t="s">
         <v>409</v>
@@ -11264,16 +11588,16 @@
         <v>123</v>
       </c>
       <c r="B125" s="5" t="s">
-        <v>862</v>
+        <v>870</v>
       </c>
       <c r="C125" s="5" t="s">
-        <v>942</v>
+        <v>950</v>
       </c>
       <c r="D125" s="6" t="s">
-        <v>943</v>
+        <v>951</v>
       </c>
       <c r="E125" s="5" t="s">
-        <v>944</v>
+        <v>952</v>
       </c>
     </row>
     <row r="126" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -11281,16 +11605,16 @@
         <v>124</v>
       </c>
       <c r="B126" s="5" t="s">
-        <v>945</v>
+        <v>953</v>
       </c>
       <c r="C126" s="5" t="s">
-        <v>946</v>
+        <v>954</v>
       </c>
       <c r="D126" s="6" t="s">
-        <v>947</v>
+        <v>955</v>
       </c>
       <c r="E126" s="5" t="s">
-        <v>944</v>
+        <v>952</v>
       </c>
     </row>
     <row r="127" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -11298,16 +11622,16 @@
         <v>125</v>
       </c>
       <c r="B127" s="5" t="s">
-        <v>881</v>
+        <v>889</v>
       </c>
       <c r="C127" s="5" t="s">
-        <v>948</v>
+        <v>956</v>
       </c>
       <c r="D127" s="6" t="s">
-        <v>949</v>
+        <v>957</v>
       </c>
       <c r="E127" s="5" t="s">
-        <v>950</v>
+        <v>958</v>
       </c>
     </row>
     <row r="128" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -11315,16 +11639,16 @@
         <v>126</v>
       </c>
       <c r="B128" s="5" t="s">
-        <v>951</v>
+        <v>959</v>
       </c>
       <c r="C128" s="5" t="s">
-        <v>952</v>
+        <v>960</v>
       </c>
       <c r="D128" s="6" t="s">
-        <v>953</v>
+        <v>961</v>
       </c>
       <c r="E128" s="5" t="s">
-        <v>954</v>
+        <v>962</v>
       </c>
     </row>
     <row r="129" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -11332,16 +11656,16 @@
         <v>127</v>
       </c>
       <c r="B129" s="5" t="s">
-        <v>955</v>
+        <v>963</v>
       </c>
       <c r="C129" s="5" t="s">
-        <v>956</v>
+        <v>964</v>
       </c>
       <c r="D129" s="6" t="s">
-        <v>957</v>
+        <v>965</v>
       </c>
       <c r="E129" s="5" t="s">
-        <v>958</v>
+        <v>966</v>
       </c>
     </row>
     <row r="130" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -11349,16 +11673,16 @@
         <v>128</v>
       </c>
       <c r="B130" s="5" t="s">
-        <v>959</v>
+        <v>967</v>
       </c>
       <c r="C130" s="5" t="s">
-        <v>960</v>
+        <v>968</v>
       </c>
       <c r="D130" s="6" t="s">
-        <v>957</v>
+        <v>965</v>
       </c>
       <c r="E130" s="5" t="s">
-        <v>961</v>
+        <v>969</v>
       </c>
     </row>
     <row r="131" customFormat="false" ht="34.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -11366,13 +11690,13 @@
         <v>129</v>
       </c>
       <c r="B131" s="5" t="s">
-        <v>962</v>
+        <v>970</v>
       </c>
       <c r="C131" s="5" t="s">
-        <v>963</v>
+        <v>971</v>
       </c>
       <c r="D131" s="6" t="s">
-        <v>957</v>
+        <v>965</v>
       </c>
       <c r="E131" s="5" t="s">
         <v>434</v>
@@ -11383,16 +11707,16 @@
         <v>130</v>
       </c>
       <c r="B132" s="5" t="s">
-        <v>964</v>
+        <v>972</v>
       </c>
       <c r="C132" s="5" t="s">
-        <v>965</v>
+        <v>973</v>
       </c>
       <c r="D132" s="6" t="s">
-        <v>966</v>
+        <v>974</v>
       </c>
       <c r="E132" s="5" t="s">
-        <v>967</v>
+        <v>975</v>
       </c>
     </row>
     <row r="133" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -11400,16 +11724,16 @@
         <v>131</v>
       </c>
       <c r="B133" s="5" t="s">
-        <v>968</v>
+        <v>976</v>
       </c>
       <c r="C133" s="5" t="s">
-        <v>969</v>
+        <v>977</v>
       </c>
       <c r="D133" s="6" t="s">
-        <v>970</v>
+        <v>978</v>
       </c>
       <c r="E133" s="5" t="s">
-        <v>967</v>
+        <v>975</v>
       </c>
     </row>
     <row r="134" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -11417,16 +11741,16 @@
         <v>132</v>
       </c>
       <c r="B134" s="5" t="s">
-        <v>971</v>
+        <v>979</v>
       </c>
       <c r="C134" s="5" t="s">
-        <v>972</v>
+        <v>980</v>
       </c>
       <c r="D134" s="6" t="s">
-        <v>973</v>
+        <v>981</v>
       </c>
       <c r="E134" s="5" t="s">
-        <v>974</v>
+        <v>982</v>
       </c>
     </row>
     <row r="135" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -11434,16 +11758,16 @@
         <v>133</v>
       </c>
       <c r="B135" s="5" t="s">
-        <v>975</v>
+        <v>983</v>
       </c>
       <c r="C135" s="5" t="s">
-        <v>976</v>
+        <v>984</v>
       </c>
       <c r="D135" s="6" t="s">
-        <v>977</v>
+        <v>985</v>
       </c>
       <c r="E135" s="5" t="s">
-        <v>978</v>
+        <v>986</v>
       </c>
     </row>
     <row r="136" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -11451,13 +11775,13 @@
         <v>134</v>
       </c>
       <c r="B136" s="5" t="s">
-        <v>690</v>
+        <v>698</v>
       </c>
       <c r="C136" s="5" t="s">
-        <v>979</v>
+        <v>987</v>
       </c>
       <c r="D136" s="6" t="s">
-        <v>980</v>
+        <v>988</v>
       </c>
       <c r="E136" s="5" t="s">
         <v>451</v>
@@ -11468,13 +11792,13 @@
         <v>135</v>
       </c>
       <c r="B137" s="5" t="s">
-        <v>981</v>
+        <v>989</v>
       </c>
       <c r="C137" s="5" t="s">
-        <v>982</v>
+        <v>990</v>
       </c>
       <c r="D137" s="6" t="s">
-        <v>983</v>
+        <v>991</v>
       </c>
       <c r="E137" s="5" t="s">
         <v>451</v>
@@ -11485,16 +11809,16 @@
         <v>136</v>
       </c>
       <c r="B138" s="5" t="s">
-        <v>984</v>
+        <v>992</v>
       </c>
       <c r="C138" s="5" t="s">
-        <v>985</v>
+        <v>993</v>
       </c>
       <c r="D138" s="6" t="s">
-        <v>986</v>
+        <v>994</v>
       </c>
       <c r="E138" s="5" t="s">
-        <v>987</v>
+        <v>995</v>
       </c>
     </row>
     <row r="139" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -11502,16 +11826,16 @@
         <v>137</v>
       </c>
       <c r="B139" s="5" t="s">
-        <v>988</v>
+        <v>996</v>
       </c>
       <c r="C139" s="5" t="s">
-        <v>989</v>
+        <v>997</v>
       </c>
       <c r="D139" s="6" t="s">
-        <v>990</v>
+        <v>998</v>
       </c>
       <c r="E139" s="5" t="s">
-        <v>991</v>
+        <v>999</v>
       </c>
     </row>
     <row r="140" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -11519,13 +11843,13 @@
         <v>138</v>
       </c>
       <c r="B140" s="5" t="s">
-        <v>857</v>
+        <v>865</v>
       </c>
       <c r="C140" s="5" t="s">
-        <v>992</v>
+        <v>1000</v>
       </c>
       <c r="D140" s="6" t="s">
-        <v>993</v>
+        <v>1001</v>
       </c>
       <c r="E140" s="5" t="s">
         <v>463</v>
@@ -11536,16 +11860,16 @@
         <v>139</v>
       </c>
       <c r="B141" s="5" t="s">
-        <v>862</v>
+        <v>870</v>
       </c>
       <c r="C141" s="5" t="s">
-        <v>994</v>
+        <v>1002</v>
       </c>
       <c r="D141" s="6" t="s">
-        <v>995</v>
+        <v>1003</v>
       </c>
       <c r="E141" s="5" t="s">
-        <v>996</v>
+        <v>1004</v>
       </c>
     </row>
     <row r="142" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -11553,16 +11877,16 @@
         <v>140</v>
       </c>
       <c r="B142" s="5" t="s">
-        <v>997</v>
+        <v>1005</v>
       </c>
       <c r="C142" s="5" t="s">
-        <v>998</v>
+        <v>1006</v>
       </c>
       <c r="D142" s="6" t="s">
-        <v>999</v>
+        <v>1007</v>
       </c>
       <c r="E142" s="5" t="s">
-        <v>1000</v>
+        <v>1008</v>
       </c>
     </row>
     <row r="143" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -11570,13 +11894,13 @@
         <v>141</v>
       </c>
       <c r="B143" s="5" t="s">
-        <v>829</v>
+        <v>837</v>
       </c>
       <c r="C143" s="5" t="s">
-        <v>1001</v>
+        <v>1009</v>
       </c>
       <c r="D143" s="6" t="s">
-        <v>1002</v>
+        <v>1010</v>
       </c>
       <c r="E143" s="5" t="s">
         <v>472</v>
@@ -11587,16 +11911,16 @@
         <v>142</v>
       </c>
       <c r="B144" s="5" t="s">
-        <v>1003</v>
+        <v>1011</v>
       </c>
       <c r="C144" s="5" t="s">
-        <v>1004</v>
+        <v>1012</v>
       </c>
       <c r="D144" s="6" t="s">
-        <v>1005</v>
+        <v>1013</v>
       </c>
       <c r="E144" s="5" t="s">
-        <v>1006</v>
+        <v>1014</v>
       </c>
     </row>
     <row r="145" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -11604,13 +11928,13 @@
         <v>143</v>
       </c>
       <c r="B145" s="5" t="s">
-        <v>889</v>
+        <v>897</v>
       </c>
       <c r="C145" s="5" t="s">
-        <v>1007</v>
+        <v>1015</v>
       </c>
       <c r="D145" s="6" t="s">
-        <v>1008</v>
+        <v>1016</v>
       </c>
       <c r="E145" s="5" t="s">
         <v>479</v>
@@ -11621,16 +11945,16 @@
         <v>144</v>
       </c>
       <c r="B146" s="5" t="s">
-        <v>829</v>
+        <v>837</v>
       </c>
       <c r="C146" s="5" t="s">
-        <v>1009</v>
+        <v>1017</v>
       </c>
       <c r="D146" s="6" t="s">
-        <v>1010</v>
+        <v>1018</v>
       </c>
       <c r="E146" s="5" t="s">
-        <v>1011</v>
+        <v>1019</v>
       </c>
     </row>
     <row r="147" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -11638,16 +11962,16 @@
         <v>145</v>
       </c>
       <c r="B147" s="5" t="s">
-        <v>1012</v>
+        <v>1020</v>
       </c>
       <c r="C147" s="5" t="s">
-        <v>1013</v>
+        <v>1021</v>
       </c>
       <c r="D147" s="6" t="s">
-        <v>1014</v>
+        <v>1022</v>
       </c>
       <c r="E147" s="5" t="s">
-        <v>1015</v>
+        <v>1023</v>
       </c>
     </row>
     <row r="148" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -11655,16 +11979,16 @@
         <v>146</v>
       </c>
       <c r="B148" s="5" t="s">
-        <v>1016</v>
+        <v>1024</v>
       </c>
       <c r="C148" s="5" t="s">
-        <v>1017</v>
+        <v>1025</v>
       </c>
       <c r="D148" s="6" t="s">
-        <v>1018</v>
+        <v>1026</v>
       </c>
       <c r="E148" s="5" t="s">
-        <v>1019</v>
+        <v>1027</v>
       </c>
     </row>
     <row r="149" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -11672,13 +11996,13 @@
         <v>147</v>
       </c>
       <c r="B149" s="5" t="s">
-        <v>1020</v>
+        <v>1028</v>
       </c>
       <c r="C149" s="5" t="s">
-        <v>1021</v>
+        <v>1029</v>
       </c>
       <c r="D149" s="6" t="s">
-        <v>953</v>
+        <v>961</v>
       </c>
       <c r="E149" s="5" t="s">
         <v>492</v>
@@ -11689,13 +12013,13 @@
         <v>148</v>
       </c>
       <c r="B150" s="5" t="s">
-        <v>1022</v>
+        <v>1030</v>
       </c>
       <c r="C150" s="5" t="s">
-        <v>1023</v>
+        <v>1031</v>
       </c>
       <c r="D150" s="6" t="s">
-        <v>957</v>
+        <v>965</v>
       </c>
       <c r="E150" s="5" t="s">
         <v>492</v>
@@ -11706,16 +12030,16 @@
         <v>149</v>
       </c>
       <c r="B151" s="5" t="s">
-        <v>1024</v>
+        <v>1032</v>
       </c>
       <c r="C151" s="5" t="s">
-        <v>1025</v>
+        <v>1033</v>
       </c>
       <c r="D151" s="6" t="s">
-        <v>1026</v>
+        <v>1034</v>
       </c>
       <c r="E151" s="5" t="s">
-        <v>1027</v>
+        <v>1035</v>
       </c>
     </row>
     <row r="152" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -11723,16 +12047,16 @@
         <v>150</v>
       </c>
       <c r="B152" s="5" t="s">
-        <v>1024</v>
+        <v>1032</v>
       </c>
       <c r="C152" s="5" t="s">
-        <v>1028</v>
+        <v>1036</v>
       </c>
       <c r="D152" s="6" t="s">
-        <v>1026</v>
+        <v>1034</v>
       </c>
       <c r="E152" s="5" t="s">
-        <v>1027</v>
+        <v>1035</v>
       </c>
     </row>
     <row r="153" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -11740,16 +12064,16 @@
         <v>151</v>
       </c>
       <c r="B153" s="5" t="s">
-        <v>1029</v>
+        <v>1037</v>
       </c>
       <c r="C153" s="5" t="s">
-        <v>1030</v>
+        <v>1038</v>
       </c>
       <c r="D153" s="6" t="s">
-        <v>1031</v>
+        <v>1039</v>
       </c>
       <c r="E153" s="5" t="s">
-        <v>1032</v>
+        <v>1040</v>
       </c>
     </row>
     <row r="154" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -11757,16 +12081,16 @@
         <v>152</v>
       </c>
       <c r="B154" s="5" t="s">
-        <v>1029</v>
+        <v>1037</v>
       </c>
       <c r="C154" s="5" t="s">
-        <v>1033</v>
+        <v>1041</v>
       </c>
       <c r="D154" s="6" t="s">
-        <v>1031</v>
+        <v>1039</v>
       </c>
       <c r="E154" s="5" t="s">
-        <v>1032</v>
+        <v>1040</v>
       </c>
     </row>
     <row r="155" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -11774,16 +12098,16 @@
         <v>153</v>
       </c>
       <c r="B155" s="5" t="s">
-        <v>1034</v>
+        <v>1042</v>
       </c>
       <c r="C155" s="5" t="s">
-        <v>1035</v>
+        <v>1043</v>
       </c>
       <c r="D155" s="6" t="s">
-        <v>1036</v>
+        <v>1044</v>
       </c>
       <c r="E155" s="5" t="s">
-        <v>1037</v>
+        <v>1045</v>
       </c>
     </row>
     <row r="156" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -11791,16 +12115,16 @@
         <v>154</v>
       </c>
       <c r="B156" s="5" t="s">
-        <v>862</v>
+        <v>870</v>
       </c>
       <c r="C156" s="5" t="s">
-        <v>1038</v>
+        <v>1046</v>
       </c>
       <c r="D156" s="6" t="s">
-        <v>1039</v>
+        <v>1047</v>
       </c>
       <c r="E156" s="5" t="s">
-        <v>1037</v>
+        <v>1045</v>
       </c>
     </row>
     <row r="157" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -11808,14 +12132,14 @@
         <v>155</v>
       </c>
       <c r="B157" s="5" t="s">
-        <v>1040</v>
+        <v>1048</v>
       </c>
       <c r="C157" s="5" t="s">
-        <v>1041</v>
+        <v>1049</v>
       </c>
       <c r="D157" s="5"/>
       <c r="E157" s="5" t="s">
-        <v>1042</v>
+        <v>1050</v>
       </c>
     </row>
     <row r="158" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -11823,16 +12147,16 @@
         <v>156</v>
       </c>
       <c r="B158" s="5" t="s">
-        <v>1043</v>
+        <v>1051</v>
       </c>
       <c r="C158" s="5" t="s">
-        <v>1044</v>
+        <v>1052</v>
       </c>
       <c r="D158" s="6" t="s">
-        <v>1045</v>
+        <v>1053</v>
       </c>
       <c r="E158" s="5" t="s">
-        <v>1042</v>
+        <v>1050</v>
       </c>
     </row>
     <row r="159" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -11840,16 +12164,16 @@
         <v>157</v>
       </c>
       <c r="B159" s="5" t="s">
-        <v>690</v>
+        <v>698</v>
       </c>
       <c r="C159" s="5" t="s">
-        <v>1046</v>
+        <v>1054</v>
       </c>
       <c r="D159" s="6" t="s">
-        <v>1047</v>
+        <v>1055</v>
       </c>
       <c r="E159" s="5" t="s">
-        <v>1048</v>
+        <v>1056</v>
       </c>
     </row>
     <row r="160" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -11857,16 +12181,16 @@
         <v>158</v>
       </c>
       <c r="B160" s="5" t="s">
-        <v>829</v>
+        <v>837</v>
       </c>
       <c r="C160" s="5" t="s">
-        <v>1049</v>
+        <v>1057</v>
       </c>
       <c r="D160" s="6" t="s">
-        <v>1050</v>
+        <v>1058</v>
       </c>
       <c r="E160" s="5" t="s">
-        <v>1048</v>
+        <v>1056</v>
       </c>
     </row>
     <row r="161" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -11874,16 +12198,16 @@
         <v>159</v>
       </c>
       <c r="B161" s="5" t="s">
-        <v>885</v>
+        <v>893</v>
       </c>
       <c r="C161" s="5" t="s">
-        <v>1051</v>
+        <v>1059</v>
       </c>
       <c r="D161" s="6" t="s">
-        <v>1052</v>
+        <v>1060</v>
       </c>
       <c r="E161" s="5" t="s">
-        <v>1048</v>
+        <v>1056</v>
       </c>
     </row>
     <row r="162" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -11891,16 +12215,16 @@
         <v>160</v>
       </c>
       <c r="B162" s="5" t="s">
-        <v>1053</v>
+        <v>1061</v>
       </c>
       <c r="C162" s="5" t="s">
-        <v>1054</v>
+        <v>1062</v>
       </c>
       <c r="D162" s="6" t="s">
-        <v>1055</v>
+        <v>1063</v>
       </c>
       <c r="E162" s="5" t="s">
-        <v>1048</v>
+        <v>1056</v>
       </c>
     </row>
     <row r="163" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -11908,16 +12232,16 @@
         <v>161</v>
       </c>
       <c r="B163" s="5" t="s">
-        <v>1053</v>
+        <v>1061</v>
       </c>
       <c r="C163" s="5" t="s">
+        <v>1064</v>
+      </c>
+      <c r="D163" s="6" t="s">
+        <v>1065</v>
+      </c>
+      <c r="E163" s="5" t="s">
         <v>1056</v>
-      </c>
-      <c r="D163" s="6" t="s">
-        <v>1057</v>
-      </c>
-      <c r="E163" s="5" t="s">
-        <v>1048</v>
       </c>
     </row>
     <row r="164" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -11925,16 +12249,16 @@
         <v>162</v>
       </c>
       <c r="B164" s="5" t="s">
-        <v>896</v>
+        <v>904</v>
       </c>
       <c r="C164" s="5" t="s">
-        <v>1058</v>
+        <v>1066</v>
       </c>
       <c r="D164" s="6" t="s">
-        <v>1059</v>
+        <v>1067</v>
       </c>
       <c r="E164" s="5" t="s">
-        <v>1060</v>
+        <v>1068</v>
       </c>
     </row>
     <row r="165" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -11942,16 +12266,16 @@
         <v>163</v>
       </c>
       <c r="B165" s="5" t="s">
-        <v>690</v>
+        <v>698</v>
       </c>
       <c r="C165" s="5" t="s">
-        <v>1061</v>
+        <v>1069</v>
       </c>
       <c r="D165" s="6" t="s">
-        <v>1062</v>
+        <v>1070</v>
       </c>
       <c r="E165" s="5" t="s">
-        <v>1060</v>
+        <v>1068</v>
       </c>
     </row>
     <row r="166" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -11959,13 +12283,13 @@
         <v>157</v>
       </c>
       <c r="B166" s="5" t="s">
-        <v>1053</v>
+        <v>1061</v>
       </c>
       <c r="C166" s="5" t="s">
-        <v>1063</v>
+        <v>1071</v>
       </c>
       <c r="D166" s="6" t="s">
-        <v>1064</v>
+        <v>1072</v>
       </c>
       <c r="E166" s="5" t="s">
         <v>521</v>
@@ -11976,16 +12300,16 @@
         <v>158</v>
       </c>
       <c r="B167" s="5" t="s">
-        <v>912</v>
+        <v>920</v>
       </c>
       <c r="C167" s="5" t="s">
-        <v>1065</v>
+        <v>1073</v>
       </c>
       <c r="D167" s="6" t="s">
-        <v>1066</v>
+        <v>1074</v>
       </c>
       <c r="E167" s="5" t="s">
-        <v>1067</v>
+        <v>1075</v>
       </c>
     </row>
     <row r="168" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -11993,13 +12317,13 @@
         <v>159</v>
       </c>
       <c r="B168" s="5" t="s">
-        <v>690</v>
+        <v>698</v>
       </c>
       <c r="C168" s="5" t="s">
-        <v>1068</v>
+        <v>1076</v>
       </c>
       <c r="D168" s="6" t="s">
-        <v>1069</v>
+        <v>1077</v>
       </c>
       <c r="E168" s="5" t="s">
         <v>524</v>
@@ -12010,16 +12334,16 @@
         <v>160</v>
       </c>
       <c r="B169" s="5" t="s">
-        <v>885</v>
+        <v>893</v>
       </c>
       <c r="C169" s="5" t="s">
-        <v>1070</v>
+        <v>1078</v>
       </c>
       <c r="D169" s="6" t="s">
-        <v>1071</v>
+        <v>1079</v>
       </c>
       <c r="E169" s="5" t="s">
-        <v>1072</v>
+        <v>1080</v>
       </c>
     </row>
     <row r="170" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -12027,16 +12351,16 @@
         <v>161</v>
       </c>
       <c r="B170" s="5" t="s">
-        <v>885</v>
+        <v>893</v>
       </c>
       <c r="C170" s="5" t="s">
-        <v>1073</v>
+        <v>1081</v>
       </c>
       <c r="D170" s="6" t="s">
-        <v>1074</v>
+        <v>1082</v>
       </c>
       <c r="E170" s="5" t="s">
-        <v>1072</v>
+        <v>1080</v>
       </c>
     </row>
     <row r="171" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -12044,16 +12368,16 @@
         <v>162</v>
       </c>
       <c r="B171" s="5" t="s">
-        <v>885</v>
+        <v>893</v>
       </c>
       <c r="C171" s="5" t="s">
-        <v>1075</v>
+        <v>1083</v>
       </c>
       <c r="D171" s="6" t="s">
-        <v>1076</v>
+        <v>1084</v>
       </c>
       <c r="E171" s="5" t="s">
-        <v>1072</v>
+        <v>1080</v>
       </c>
     </row>
     <row r="172" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -12061,16 +12385,16 @@
         <v>163</v>
       </c>
       <c r="B172" s="5" t="s">
-        <v>835</v>
+        <v>843</v>
       </c>
       <c r="C172" s="5" t="s">
-        <v>1077</v>
+        <v>1085</v>
       </c>
       <c r="D172" s="6" t="s">
-        <v>1078</v>
+        <v>1086</v>
       </c>
       <c r="E172" s="5" t="s">
-        <v>1079</v>
+        <v>1087</v>
       </c>
     </row>
     <row r="173" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -12078,16 +12402,16 @@
         <v>164</v>
       </c>
       <c r="B173" s="5" t="s">
-        <v>829</v>
+        <v>837</v>
       </c>
       <c r="C173" s="5" t="s">
-        <v>1080</v>
+        <v>1088</v>
       </c>
       <c r="D173" s="6" t="s">
-        <v>1081</v>
+        <v>1089</v>
       </c>
       <c r="E173" s="5" t="s">
-        <v>1082</v>
+        <v>1090</v>
       </c>
     </row>
     <row r="174" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -12095,16 +12419,16 @@
         <v>165</v>
       </c>
       <c r="B174" s="5" t="s">
-        <v>829</v>
+        <v>837</v>
       </c>
       <c r="C174" s="5" t="s">
-        <v>1083</v>
+        <v>1091</v>
       </c>
       <c r="D174" s="6" t="s">
-        <v>1084</v>
+        <v>1092</v>
       </c>
       <c r="E174" s="5" t="s">
-        <v>1082</v>
+        <v>1090</v>
       </c>
     </row>
     <row r="175" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -12112,16 +12436,16 @@
         <v>166</v>
       </c>
       <c r="B175" s="5" t="s">
-        <v>829</v>
+        <v>837</v>
       </c>
       <c r="C175" s="5" t="s">
-        <v>1085</v>
+        <v>1093</v>
       </c>
       <c r="D175" s="6" t="s">
-        <v>1086</v>
+        <v>1094</v>
       </c>
       <c r="E175" s="5" t="s">
-        <v>1082</v>
+        <v>1090</v>
       </c>
     </row>
     <row r="176" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -12129,16 +12453,16 @@
         <v>167</v>
       </c>
       <c r="B176" s="5" t="s">
-        <v>896</v>
+        <v>904</v>
       </c>
       <c r="C176" s="5" t="s">
-        <v>1087</v>
+        <v>1095</v>
       </c>
       <c r="D176" s="6" t="s">
-        <v>1088</v>
+        <v>1096</v>
       </c>
       <c r="E176" s="5" t="s">
-        <v>1089</v>
+        <v>1097</v>
       </c>
     </row>
     <row r="177" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -12146,16 +12470,16 @@
         <v>168</v>
       </c>
       <c r="B177" s="5" t="s">
-        <v>690</v>
+        <v>698</v>
       </c>
       <c r="C177" s="5" t="s">
-        <v>1090</v>
+        <v>1098</v>
       </c>
       <c r="D177" s="6" t="s">
-        <v>1091</v>
+        <v>1099</v>
       </c>
       <c r="E177" s="5" t="s">
-        <v>1089</v>
+        <v>1097</v>
       </c>
     </row>
     <row r="178" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -12163,16 +12487,16 @@
         <v>169</v>
       </c>
       <c r="B178" s="5" t="s">
-        <v>690</v>
+        <v>698</v>
       </c>
       <c r="C178" s="5" t="s">
-        <v>1092</v>
+        <v>1100</v>
       </c>
       <c r="D178" s="6" t="s">
-        <v>1093</v>
+        <v>1101</v>
       </c>
       <c r="E178" s="5" t="s">
-        <v>1089</v>
+        <v>1097</v>
       </c>
     </row>
     <row r="179" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -12180,16 +12504,16 @@
         <v>170</v>
       </c>
       <c r="B179" s="5" t="s">
-        <v>912</v>
+        <v>920</v>
       </c>
       <c r="C179" s="5" t="s">
-        <v>1094</v>
+        <v>1102</v>
       </c>
       <c r="D179" s="6" t="s">
-        <v>1095</v>
+        <v>1103</v>
       </c>
       <c r="E179" s="5" t="s">
-        <v>1089</v>
+        <v>1097</v>
       </c>
     </row>
     <row r="180" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -12197,16 +12521,16 @@
         <v>171</v>
       </c>
       <c r="B180" s="5" t="s">
-        <v>912</v>
+        <v>920</v>
       </c>
       <c r="C180" s="5" t="s">
-        <v>1096</v>
+        <v>1104</v>
       </c>
       <c r="D180" s="6" t="s">
+        <v>1105</v>
+      </c>
+      <c r="E180" s="5" t="s">
         <v>1097</v>
-      </c>
-      <c r="E180" s="5" t="s">
-        <v>1089</v>
       </c>
     </row>
     <row r="181" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -12214,16 +12538,16 @@
         <v>172</v>
       </c>
       <c r="B181" s="5" t="s">
-        <v>885</v>
+        <v>893</v>
       </c>
       <c r="C181" s="5" t="s">
-        <v>1098</v>
+        <v>1106</v>
       </c>
       <c r="D181" s="6" t="s">
-        <v>1099</v>
+        <v>1107</v>
       </c>
       <c r="E181" s="5" t="s">
-        <v>1100</v>
+        <v>1108</v>
       </c>
     </row>
     <row r="182" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -12231,16 +12555,16 @@
         <v>173</v>
       </c>
       <c r="B182" s="5" t="s">
-        <v>690</v>
+        <v>698</v>
       </c>
       <c r="C182" s="5" t="s">
-        <v>1101</v>
+        <v>1109</v>
       </c>
       <c r="D182" s="6" t="s">
-        <v>1102</v>
+        <v>1110</v>
       </c>
       <c r="E182" s="5" t="s">
-        <v>1103</v>
+        <v>1111</v>
       </c>
     </row>
     <row r="183" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -12248,16 +12572,16 @@
         <v>174</v>
       </c>
       <c r="B183" s="5" t="s">
-        <v>690</v>
+        <v>698</v>
       </c>
       <c r="C183" s="5" t="s">
-        <v>1104</v>
+        <v>1112</v>
       </c>
       <c r="D183" s="6" t="s">
-        <v>1105</v>
+        <v>1113</v>
       </c>
       <c r="E183" s="5" t="s">
-        <v>1103</v>
+        <v>1111</v>
       </c>
     </row>
     <row r="184" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -12265,16 +12589,16 @@
         <v>175</v>
       </c>
       <c r="B184" s="5" t="s">
-        <v>690</v>
+        <v>698</v>
       </c>
       <c r="C184" s="5" t="s">
-        <v>1106</v>
+        <v>1114</v>
       </c>
       <c r="D184" s="6" t="s">
-        <v>1107</v>
+        <v>1115</v>
       </c>
       <c r="E184" s="5" t="s">
-        <v>1103</v>
+        <v>1111</v>
       </c>
     </row>
     <row r="185" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -12282,16 +12606,16 @@
         <v>176</v>
       </c>
       <c r="B185" s="5" t="s">
-        <v>1053</v>
+        <v>1061</v>
       </c>
       <c r="C185" s="5" t="s">
-        <v>1108</v>
+        <v>1116</v>
       </c>
       <c r="D185" s="6" t="s">
-        <v>1109</v>
+        <v>1117</v>
       </c>
       <c r="E185" s="5" t="s">
-        <v>1103</v>
+        <v>1111</v>
       </c>
     </row>
     <row r="186" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -12299,16 +12623,16 @@
         <v>177</v>
       </c>
       <c r="B186" s="5" t="s">
-        <v>1053</v>
+        <v>1061</v>
       </c>
       <c r="C186" s="5" t="s">
-        <v>1110</v>
+        <v>1118</v>
       </c>
       <c r="D186" s="6" t="s">
+        <v>1119</v>
+      </c>
+      <c r="E186" s="5" t="s">
         <v>1111</v>
-      </c>
-      <c r="E186" s="5" t="s">
-        <v>1103</v>
       </c>
     </row>
     <row r="187" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -12316,16 +12640,16 @@
         <v>178</v>
       </c>
       <c r="B187" s="5" t="s">
-        <v>1053</v>
+        <v>1061</v>
       </c>
       <c r="C187" s="5" t="s">
-        <v>1112</v>
+        <v>1120</v>
       </c>
       <c r="D187" s="6" t="s">
-        <v>1113</v>
+        <v>1121</v>
       </c>
       <c r="E187" s="5" t="s">
-        <v>1103</v>
+        <v>1111</v>
       </c>
     </row>
     <row r="188" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -12333,16 +12657,16 @@
         <v>179</v>
       </c>
       <c r="B188" s="5" t="s">
-        <v>690</v>
+        <v>698</v>
       </c>
       <c r="C188" s="5" t="s">
-        <v>1114</v>
+        <v>1122</v>
       </c>
       <c r="D188" s="6" t="s">
-        <v>1115</v>
+        <v>1123</v>
       </c>
       <c r="E188" s="5" t="s">
-        <v>1116</v>
+        <v>1124</v>
       </c>
     </row>
     <row r="189" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -12350,16 +12674,16 @@
         <v>180</v>
       </c>
       <c r="B189" s="5" t="s">
-        <v>690</v>
+        <v>698</v>
       </c>
       <c r="C189" s="5" t="s">
-        <v>1117</v>
+        <v>1125</v>
       </c>
       <c r="D189" s="6" t="s">
-        <v>1118</v>
+        <v>1126</v>
       </c>
       <c r="E189" s="5" t="s">
-        <v>1116</v>
+        <v>1124</v>
       </c>
     </row>
     <row r="190" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -12367,16 +12691,16 @@
         <v>181</v>
       </c>
       <c r="B190" s="5" t="s">
-        <v>885</v>
+        <v>893</v>
       </c>
       <c r="C190" s="5" t="s">
-        <v>1119</v>
+        <v>1127</v>
       </c>
       <c r="D190" s="6" t="s">
-        <v>1120</v>
+        <v>1128</v>
       </c>
       <c r="E190" s="5" t="s">
-        <v>1116</v>
+        <v>1124</v>
       </c>
     </row>
     <row r="191" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -12384,16 +12708,16 @@
         <v>182</v>
       </c>
       <c r="B191" s="5" t="s">
-        <v>1053</v>
+        <v>1061</v>
       </c>
       <c r="C191" s="5" t="s">
-        <v>1121</v>
+        <v>1129</v>
       </c>
       <c r="D191" s="6" t="s">
-        <v>1122</v>
+        <v>1130</v>
       </c>
       <c r="E191" s="5" t="s">
-        <v>1116</v>
+        <v>1124</v>
       </c>
     </row>
     <row r="192" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -12401,16 +12725,16 @@
         <v>183</v>
       </c>
       <c r="B192" s="5" t="s">
-        <v>1053</v>
+        <v>1061</v>
       </c>
       <c r="C192" s="5" t="s">
-        <v>1123</v>
+        <v>1131</v>
       </c>
       <c r="D192" s="6" t="s">
+        <v>1132</v>
+      </c>
+      <c r="E192" s="5" t="s">
         <v>1124</v>
-      </c>
-      <c r="E192" s="5" t="s">
-        <v>1116</v>
       </c>
     </row>
     <row r="193" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -12418,13 +12742,13 @@
         <v>184</v>
       </c>
       <c r="B193" s="5" t="s">
-        <v>885</v>
+        <v>893</v>
       </c>
       <c r="C193" s="5" t="s">
-        <v>1125</v>
+        <v>1133</v>
       </c>
       <c r="D193" s="6" t="s">
-        <v>1126</v>
+        <v>1134</v>
       </c>
       <c r="E193" s="5" t="s">
         <v>533</v>
@@ -12435,16 +12759,16 @@
         <v>185</v>
       </c>
       <c r="B194" s="5" t="s">
-        <v>885</v>
+        <v>893</v>
       </c>
       <c r="C194" s="5" t="s">
-        <v>1127</v>
+        <v>1135</v>
       </c>
       <c r="D194" s="6" t="s">
-        <v>1128</v>
+        <v>1136</v>
       </c>
       <c r="E194" s="5" t="s">
-        <v>1129</v>
+        <v>1137</v>
       </c>
     </row>
     <row r="195" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -12452,16 +12776,16 @@
         <v>186</v>
       </c>
       <c r="B195" s="5" t="s">
-        <v>690</v>
+        <v>698</v>
       </c>
       <c r="C195" s="5" t="s">
-        <v>1130</v>
+        <v>1138</v>
       </c>
       <c r="D195" s="6" t="s">
-        <v>1131</v>
+        <v>1139</v>
       </c>
       <c r="E195" s="5" t="s">
-        <v>1132</v>
+        <v>1140</v>
       </c>
     </row>
     <row r="196" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -12469,16 +12793,16 @@
         <v>187</v>
       </c>
       <c r="B196" s="5" t="s">
-        <v>829</v>
+        <v>837</v>
       </c>
       <c r="C196" s="5" t="s">
-        <v>1133</v>
+        <v>1141</v>
       </c>
       <c r="D196" s="6" t="s">
-        <v>1134</v>
+        <v>1142</v>
       </c>
       <c r="E196" s="5" t="s">
-        <v>1132</v>
+        <v>1140</v>
       </c>
     </row>
     <row r="197" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -12486,16 +12810,16 @@
         <v>188</v>
       </c>
       <c r="B197" s="5" t="s">
-        <v>1053</v>
+        <v>1061</v>
       </c>
       <c r="C197" s="5" t="s">
-        <v>1135</v>
+        <v>1143</v>
       </c>
       <c r="D197" s="6" t="s">
-        <v>1136</v>
+        <v>1144</v>
       </c>
       <c r="E197" s="5" t="s">
-        <v>1132</v>
+        <v>1140</v>
       </c>
     </row>
     <row r="198" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -12503,16 +12827,16 @@
         <v>189</v>
       </c>
       <c r="B198" s="5" t="s">
-        <v>1053</v>
+        <v>1061</v>
       </c>
       <c r="C198" s="5" t="s">
-        <v>1137</v>
+        <v>1145</v>
       </c>
       <c r="D198" s="6" t="s">
-        <v>1138</v>
+        <v>1146</v>
       </c>
       <c r="E198" s="5" t="s">
-        <v>1132</v>
+        <v>1140</v>
       </c>
     </row>
     <row r="199" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -12520,16 +12844,16 @@
         <v>190</v>
       </c>
       <c r="B199" s="5" t="s">
-        <v>896</v>
+        <v>904</v>
       </c>
       <c r="C199" s="5" t="s">
-        <v>1139</v>
+        <v>1147</v>
       </c>
       <c r="D199" s="6" t="s">
-        <v>1140</v>
+        <v>1148</v>
       </c>
       <c r="E199" s="5" t="s">
-        <v>1141</v>
+        <v>1149</v>
       </c>
     </row>
     <row r="200" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -12537,16 +12861,16 @@
         <v>191</v>
       </c>
       <c r="B200" s="5" t="s">
-        <v>896</v>
+        <v>904</v>
       </c>
       <c r="C200" s="5" t="s">
-        <v>1142</v>
+        <v>1150</v>
       </c>
       <c r="D200" s="6" t="s">
-        <v>1143</v>
+        <v>1151</v>
       </c>
       <c r="E200" s="5" t="s">
-        <v>1141</v>
+        <v>1149</v>
       </c>
     </row>
     <row r="201" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -12554,16 +12878,16 @@
         <v>192</v>
       </c>
       <c r="B201" s="5" t="s">
-        <v>690</v>
+        <v>698</v>
       </c>
       <c r="C201" s="5" t="s">
-        <v>1144</v>
+        <v>1152</v>
       </c>
       <c r="D201" s="6" t="s">
-        <v>1145</v>
+        <v>1153</v>
       </c>
       <c r="E201" s="5" t="s">
-        <v>1141</v>
+        <v>1149</v>
       </c>
     </row>
     <row r="202" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -12571,16 +12895,16 @@
         <v>193</v>
       </c>
       <c r="B202" s="5" t="s">
-        <v>690</v>
+        <v>698</v>
       </c>
       <c r="C202" s="5" t="s">
-        <v>1146</v>
+        <v>1154</v>
       </c>
       <c r="D202" s="6" t="s">
-        <v>1147</v>
+        <v>1155</v>
       </c>
       <c r="E202" s="5" t="s">
-        <v>1148</v>
+        <v>1156</v>
       </c>
     </row>
     <row r="203" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -12588,16 +12912,16 @@
         <v>194</v>
       </c>
       <c r="B203" s="5" t="s">
-        <v>690</v>
+        <v>698</v>
       </c>
       <c r="C203" s="5" t="s">
-        <v>1149</v>
+        <v>1157</v>
       </c>
       <c r="D203" s="6" t="s">
-        <v>1150</v>
+        <v>1158</v>
       </c>
       <c r="E203" s="5" t="s">
-        <v>1148</v>
+        <v>1156</v>
       </c>
     </row>
     <row r="204" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -12605,16 +12929,16 @@
         <v>195</v>
       </c>
       <c r="B204" s="5" t="s">
-        <v>690</v>
+        <v>698</v>
       </c>
       <c r="C204" s="5" t="s">
-        <v>1151</v>
+        <v>1159</v>
       </c>
       <c r="D204" s="6" t="s">
-        <v>1152</v>
+        <v>1160</v>
       </c>
       <c r="E204" s="5" t="s">
-        <v>1153</v>
+        <v>1161</v>
       </c>
     </row>
     <row r="205" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -12622,13 +12946,13 @@
         <v>196</v>
       </c>
       <c r="B205" s="5" t="s">
-        <v>885</v>
+        <v>893</v>
       </c>
       <c r="C205" s="5" t="s">
-        <v>1154</v>
+        <v>1162</v>
       </c>
       <c r="D205" s="6" t="s">
-        <v>1155</v>
+        <v>1163</v>
       </c>
       <c r="E205" s="5" t="s">
         <v>540</v>
@@ -12639,16 +12963,16 @@
         <v>197</v>
       </c>
       <c r="B206" s="5" t="s">
-        <v>690</v>
+        <v>698</v>
       </c>
       <c r="C206" s="5" t="s">
-        <v>1156</v>
+        <v>1164</v>
       </c>
       <c r="D206" s="6" t="s">
-        <v>1157</v>
+        <v>1165</v>
       </c>
       <c r="E206" s="5" t="s">
-        <v>1158</v>
+        <v>1166</v>
       </c>
     </row>
     <row r="207" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -12656,16 +12980,16 @@
         <v>198</v>
       </c>
       <c r="B207" s="5" t="s">
-        <v>912</v>
+        <v>920</v>
       </c>
       <c r="C207" s="5" t="s">
-        <v>1159</v>
+        <v>1167</v>
       </c>
       <c r="D207" s="6" t="s">
-        <v>1160</v>
+        <v>1168</v>
       </c>
       <c r="E207" s="5" t="s">
-        <v>1158</v>
+        <v>1166</v>
       </c>
     </row>
     <row r="208" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -12673,16 +12997,16 @@
         <v>199</v>
       </c>
       <c r="B208" s="5" t="s">
-        <v>1053</v>
+        <v>1061</v>
       </c>
       <c r="C208" s="5" t="s">
-        <v>1161</v>
+        <v>1169</v>
       </c>
       <c r="D208" s="6" t="s">
-        <v>1162</v>
+        <v>1170</v>
       </c>
       <c r="E208" s="5" t="s">
-        <v>1158</v>
+        <v>1166</v>
       </c>
     </row>
     <row r="209" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -12690,16 +13014,16 @@
         <v>200</v>
       </c>
       <c r="B209" s="5" t="s">
-        <v>1053</v>
+        <v>1061</v>
       </c>
       <c r="C209" s="5" t="s">
-        <v>1163</v>
+        <v>1171</v>
       </c>
       <c r="D209" s="6" t="s">
-        <v>1164</v>
+        <v>1172</v>
       </c>
       <c r="E209" s="5" t="s">
-        <v>1158</v>
+        <v>1166</v>
       </c>
     </row>
     <row r="210" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -12707,16 +13031,16 @@
         <v>201</v>
       </c>
       <c r="B210" s="5" t="s">
-        <v>829</v>
+        <v>837</v>
       </c>
       <c r="C210" s="5" t="s">
-        <v>1165</v>
+        <v>1173</v>
       </c>
       <c r="D210" s="6" t="s">
-        <v>1166</v>
+        <v>1174</v>
       </c>
       <c r="E210" s="5" t="s">
-        <v>1167</v>
+        <v>1175</v>
       </c>
     </row>
     <row r="211" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -12724,16 +13048,16 @@
         <v>202</v>
       </c>
       <c r="B211" s="5" t="s">
-        <v>912</v>
+        <v>920</v>
       </c>
       <c r="C211" s="5" t="s">
-        <v>1168</v>
+        <v>1176</v>
       </c>
       <c r="D211" s="6" t="s">
-        <v>1169</v>
+        <v>1177</v>
       </c>
       <c r="E211" s="5" t="s">
-        <v>1167</v>
+        <v>1175</v>
       </c>
     </row>
     <row r="212" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -12741,16 +13065,16 @@
         <v>203</v>
       </c>
       <c r="B212" s="5" t="s">
-        <v>912</v>
+        <v>920</v>
       </c>
       <c r="C212" s="5" t="s">
-        <v>1170</v>
+        <v>1178</v>
       </c>
       <c r="D212" s="6" t="s">
-        <v>1171</v>
+        <v>1179</v>
       </c>
       <c r="E212" s="5" t="s">
-        <v>1167</v>
+        <v>1175</v>
       </c>
     </row>
     <row r="213" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -12758,16 +13082,16 @@
         <v>204</v>
       </c>
       <c r="B213" s="5" t="s">
-        <v>885</v>
+        <v>893</v>
       </c>
       <c r="C213" s="5" t="s">
-        <v>1172</v>
+        <v>1180</v>
       </c>
       <c r="D213" s="6" t="s">
-        <v>1173</v>
+        <v>1181</v>
       </c>
       <c r="E213" s="5" t="s">
-        <v>1067</v>
+        <v>1075</v>
       </c>
     </row>
     <row r="214" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -12775,16 +13099,16 @@
         <v>205</v>
       </c>
       <c r="B214" s="5" t="s">
-        <v>690</v>
+        <v>698</v>
       </c>
       <c r="C214" s="5" t="s">
-        <v>1174</v>
+        <v>1182</v>
       </c>
       <c r="D214" s="6" t="s">
-        <v>1175</v>
+        <v>1183</v>
       </c>
       <c r="E214" s="5" t="s">
-        <v>1176</v>
+        <v>1184</v>
       </c>
     </row>
     <row r="215" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -12792,16 +13116,16 @@
         <v>206</v>
       </c>
       <c r="B215" s="5" t="s">
-        <v>829</v>
+        <v>837</v>
       </c>
       <c r="C215" s="5" t="s">
-        <v>1177</v>
+        <v>1185</v>
       </c>
       <c r="D215" s="6" t="s">
-        <v>1178</v>
+        <v>1186</v>
       </c>
       <c r="E215" s="5" t="s">
-        <v>1179</v>
+        <v>1187</v>
       </c>
     </row>
     <row r="216" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -12809,16 +13133,16 @@
         <v>207</v>
       </c>
       <c r="B216" s="5" t="s">
-        <v>912</v>
+        <v>920</v>
       </c>
       <c r="C216" s="5" t="s">
-        <v>1180</v>
+        <v>1188</v>
       </c>
       <c r="D216" s="6" t="s">
-        <v>1181</v>
+        <v>1189</v>
       </c>
       <c r="E216" s="5" t="s">
-        <v>1179</v>
+        <v>1187</v>
       </c>
     </row>
     <row r="217" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -12826,16 +13150,16 @@
         <v>208</v>
       </c>
       <c r="B217" s="5" t="s">
-        <v>690</v>
+        <v>698</v>
       </c>
       <c r="C217" s="5" t="s">
-        <v>1182</v>
+        <v>1190</v>
       </c>
       <c r="D217" s="6" t="s">
-        <v>1183</v>
+        <v>1191</v>
       </c>
       <c r="E217" s="5" t="s">
-        <v>1184</v>
+        <v>1192</v>
       </c>
     </row>
     <row r="218" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -12843,16 +13167,16 @@
         <v>209</v>
       </c>
       <c r="B218" s="5" t="s">
-        <v>829</v>
+        <v>837</v>
       </c>
       <c r="C218" s="5" t="s">
-        <v>1185</v>
+        <v>1193</v>
       </c>
       <c r="D218" s="6" t="s">
-        <v>1186</v>
+        <v>1194</v>
       </c>
       <c r="E218" s="5" t="s">
-        <v>1184</v>
+        <v>1192</v>
       </c>
     </row>
     <row r="219" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -12860,16 +13184,16 @@
         <v>210</v>
       </c>
       <c r="B219" s="5" t="s">
-        <v>912</v>
+        <v>920</v>
       </c>
       <c r="C219" s="5" t="s">
-        <v>1187</v>
+        <v>1195</v>
       </c>
       <c r="D219" s="6" t="s">
-        <v>1188</v>
+        <v>1196</v>
       </c>
       <c r="E219" s="5" t="s">
-        <v>1184</v>
+        <v>1192</v>
       </c>
     </row>
     <row r="220" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -12877,16 +13201,16 @@
         <v>211</v>
       </c>
       <c r="B220" s="5" t="s">
-        <v>1053</v>
+        <v>1061</v>
       </c>
       <c r="C220" s="5" t="s">
-        <v>1189</v>
+        <v>1197</v>
       </c>
       <c r="D220" s="6" t="s">
-        <v>1190</v>
+        <v>1198</v>
       </c>
       <c r="E220" s="5" t="s">
-        <v>1184</v>
+        <v>1192</v>
       </c>
     </row>
     <row r="221" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -12894,16 +13218,16 @@
         <v>212</v>
       </c>
       <c r="B221" s="5" t="s">
-        <v>885</v>
+        <v>893</v>
       </c>
       <c r="C221" s="5" t="s">
-        <v>1191</v>
+        <v>1199</v>
       </c>
       <c r="D221" s="6" t="s">
-        <v>1192</v>
+        <v>1200</v>
       </c>
       <c r="E221" s="5" t="s">
-        <v>1193</v>
+        <v>1201</v>
       </c>
     </row>
     <row r="222" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -12911,16 +13235,16 @@
         <v>213</v>
       </c>
       <c r="B222" s="5" t="s">
-        <v>690</v>
+        <v>698</v>
       </c>
       <c r="C222" s="5" t="s">
-        <v>1194</v>
+        <v>1202</v>
       </c>
       <c r="D222" s="6" t="s">
-        <v>1195</v>
+        <v>1203</v>
       </c>
       <c r="E222" s="5" t="s">
-        <v>1196</v>
+        <v>1204</v>
       </c>
     </row>
     <row r="223" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -12928,16 +13252,16 @@
         <v>214</v>
       </c>
       <c r="B223" s="5" t="s">
-        <v>885</v>
+        <v>893</v>
       </c>
       <c r="C223" s="5" t="s">
-        <v>1197</v>
+        <v>1205</v>
       </c>
       <c r="D223" s="6" t="s">
-        <v>1198</v>
+        <v>1206</v>
       </c>
       <c r="E223" s="5" t="s">
-        <v>1196</v>
+        <v>1204</v>
       </c>
     </row>
     <row r="224" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -12945,16 +13269,16 @@
         <v>215</v>
       </c>
       <c r="B224" s="5" t="s">
-        <v>885</v>
+        <v>893</v>
       </c>
       <c r="C224" s="5" t="s">
-        <v>1199</v>
+        <v>1207</v>
       </c>
       <c r="D224" s="6" t="s">
-        <v>1200</v>
+        <v>1208</v>
       </c>
       <c r="E224" s="5" t="s">
-        <v>1196</v>
+        <v>1204</v>
       </c>
     </row>
     <row r="225" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -12962,16 +13286,16 @@
         <v>216</v>
       </c>
       <c r="B225" s="5" t="s">
-        <v>1053</v>
+        <v>1061</v>
       </c>
       <c r="C225" s="5" t="s">
-        <v>1201</v>
+        <v>1209</v>
       </c>
       <c r="D225" s="6" t="s">
-        <v>1202</v>
+        <v>1210</v>
       </c>
       <c r="E225" s="5" t="s">
-        <v>1196</v>
+        <v>1204</v>
       </c>
     </row>
     <row r="226" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -12979,16 +13303,16 @@
         <v>217</v>
       </c>
       <c r="B226" s="5" t="s">
-        <v>896</v>
+        <v>904</v>
       </c>
       <c r="C226" s="5" t="s">
-        <v>1203</v>
+        <v>1211</v>
       </c>
       <c r="D226" s="6" t="s">
-        <v>1204</v>
+        <v>1212</v>
       </c>
       <c r="E226" s="5" t="s">
-        <v>1205</v>
+        <v>1213</v>
       </c>
     </row>
     <row r="227" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -12996,16 +13320,16 @@
         <v>218</v>
       </c>
       <c r="B227" s="5" t="s">
-        <v>690</v>
+        <v>698</v>
       </c>
       <c r="C227" s="5" t="s">
-        <v>1206</v>
+        <v>1214</v>
       </c>
       <c r="D227" s="6" t="s">
-        <v>1207</v>
+        <v>1215</v>
       </c>
       <c r="E227" s="5" t="s">
-        <v>1205</v>
+        <v>1213</v>
       </c>
     </row>
     <row r="228" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -13013,16 +13337,16 @@
         <v>219</v>
       </c>
       <c r="B228" s="5" t="s">
-        <v>829</v>
+        <v>837</v>
       </c>
       <c r="C228" s="5" t="s">
-        <v>1208</v>
+        <v>1216</v>
       </c>
       <c r="D228" s="6" t="s">
-        <v>1209</v>
+        <v>1217</v>
       </c>
       <c r="E228" s="5" t="s">
-        <v>1205</v>
+        <v>1213</v>
       </c>
     </row>
     <row r="229" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -13030,16 +13354,16 @@
         <v>220</v>
       </c>
       <c r="B229" s="5" t="s">
-        <v>1053</v>
+        <v>1061</v>
       </c>
       <c r="C229" s="5" t="s">
-        <v>1210</v>
+        <v>1218</v>
       </c>
       <c r="D229" s="6" t="s">
-        <v>1211</v>
+        <v>1219</v>
       </c>
       <c r="E229" s="5" t="s">
-        <v>1205</v>
+        <v>1213</v>
       </c>
     </row>
     <row r="230" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -13047,16 +13371,16 @@
         <v>221</v>
       </c>
       <c r="B230" s="5" t="s">
-        <v>690</v>
+        <v>698</v>
       </c>
       <c r="C230" s="5" t="s">
-        <v>1212</v>
+        <v>1220</v>
       </c>
       <c r="D230" s="6" t="s">
-        <v>1213</v>
+        <v>1221</v>
       </c>
       <c r="E230" s="5" t="s">
-        <v>1214</v>
+        <v>1222</v>
       </c>
     </row>
     <row r="231" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -13064,16 +13388,16 @@
         <v>222</v>
       </c>
       <c r="B231" s="5" t="s">
-        <v>885</v>
+        <v>893</v>
       </c>
       <c r="C231" s="5" t="s">
-        <v>1215</v>
+        <v>1223</v>
       </c>
       <c r="D231" s="6" t="s">
-        <v>1216</v>
+        <v>1224</v>
       </c>
       <c r="E231" s="5" t="s">
-        <v>1214</v>
+        <v>1222</v>
       </c>
     </row>
     <row r="232" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -13081,16 +13405,16 @@
         <v>223</v>
       </c>
       <c r="B232" s="5" t="s">
-        <v>690</v>
+        <v>698</v>
       </c>
       <c r="C232" s="5" t="s">
-        <v>1217</v>
+        <v>1225</v>
       </c>
       <c r="D232" s="6" t="s">
-        <v>1218</v>
+        <v>1226</v>
       </c>
       <c r="E232" s="5" t="s">
-        <v>1219</v>
+        <v>1227</v>
       </c>
     </row>
     <row r="233" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -13098,16 +13422,16 @@
         <v>224</v>
       </c>
       <c r="B233" s="5" t="s">
-        <v>912</v>
+        <v>920</v>
       </c>
       <c r="C233" s="5" t="s">
-        <v>1220</v>
+        <v>1228</v>
       </c>
       <c r="D233" s="6" t="s">
-        <v>1221</v>
+        <v>1229</v>
       </c>
       <c r="E233" s="5" t="s">
-        <v>1219</v>
+        <v>1227</v>
       </c>
     </row>
     <row r="234" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -13115,16 +13439,16 @@
         <v>225</v>
       </c>
       <c r="B234" s="5" t="s">
-        <v>690</v>
+        <v>698</v>
       </c>
       <c r="C234" s="5" t="s">
-        <v>1222</v>
+        <v>1230</v>
       </c>
       <c r="D234" s="6" t="s">
-        <v>1223</v>
+        <v>1231</v>
       </c>
       <c r="E234" s="5" t="s">
-        <v>1224</v>
+        <v>1232</v>
       </c>
     </row>
     <row r="235" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -13132,16 +13456,16 @@
         <v>226</v>
       </c>
       <c r="B235" s="5" t="s">
-        <v>829</v>
+        <v>837</v>
       </c>
       <c r="C235" s="5" t="s">
-        <v>1225</v>
+        <v>1233</v>
       </c>
       <c r="D235" s="6" t="s">
-        <v>1226</v>
+        <v>1234</v>
       </c>
       <c r="E235" s="5" t="s">
-        <v>1224</v>
+        <v>1232</v>
       </c>
     </row>
     <row r="236" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -13149,16 +13473,16 @@
         <v>227</v>
       </c>
       <c r="B236" s="5" t="s">
-        <v>912</v>
+        <v>920</v>
       </c>
       <c r="C236" s="5" t="s">
-        <v>1227</v>
+        <v>1235</v>
       </c>
       <c r="D236" s="6" t="s">
-        <v>1228</v>
+        <v>1236</v>
       </c>
       <c r="E236" s="5" t="s">
-        <v>1224</v>
+        <v>1232</v>
       </c>
     </row>
     <row r="237" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -13166,16 +13490,16 @@
         <v>228</v>
       </c>
       <c r="B237" s="5" t="s">
-        <v>912</v>
+        <v>920</v>
       </c>
       <c r="C237" s="5" t="s">
-        <v>1229</v>
+        <v>1237</v>
       </c>
       <c r="D237" s="6" t="s">
-        <v>1230</v>
+        <v>1238</v>
       </c>
       <c r="E237" s="5" t="s">
-        <v>1231</v>
+        <v>1239</v>
       </c>
     </row>
     <row r="238" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -13183,16 +13507,16 @@
         <v>229</v>
       </c>
       <c r="B238" s="5" t="s">
-        <v>885</v>
+        <v>893</v>
       </c>
       <c r="C238" s="5" t="s">
-        <v>1232</v>
+        <v>1240</v>
       </c>
       <c r="D238" s="6" t="s">
-        <v>1233</v>
+        <v>1241</v>
       </c>
       <c r="E238" s="5" t="s">
-        <v>1231</v>
+        <v>1239</v>
       </c>
     </row>
     <row r="239" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -13200,16 +13524,16 @@
         <v>230</v>
       </c>
       <c r="B239" s="5" t="s">
-        <v>885</v>
+        <v>893</v>
       </c>
       <c r="C239" s="5" t="s">
-        <v>1234</v>
+        <v>1242</v>
       </c>
       <c r="D239" s="6" t="s">
-        <v>1235</v>
+        <v>1243</v>
       </c>
       <c r="E239" s="5" t="s">
-        <v>1231</v>
+        <v>1239</v>
       </c>
     </row>
     <row r="240" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -13217,16 +13541,16 @@
         <v>231</v>
       </c>
       <c r="B240" s="5" t="s">
-        <v>1053</v>
+        <v>1061</v>
       </c>
       <c r="C240" s="5" t="s">
-        <v>1236</v>
+        <v>1244</v>
       </c>
       <c r="D240" s="6" t="s">
-        <v>1237</v>
+        <v>1245</v>
       </c>
       <c r="E240" s="5" t="s">
-        <v>1231</v>
+        <v>1239</v>
       </c>
     </row>
     <row r="241" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -13234,16 +13558,16 @@
         <v>232</v>
       </c>
       <c r="B241" s="5" t="s">
-        <v>1053</v>
+        <v>1061</v>
       </c>
       <c r="C241" s="5" t="s">
-        <v>1238</v>
+        <v>1246</v>
       </c>
       <c r="D241" s="6" t="s">
+        <v>1247</v>
+      </c>
+      <c r="E241" s="5" t="s">
         <v>1239</v>
-      </c>
-      <c r="E241" s="5" t="s">
-        <v>1231</v>
       </c>
     </row>
     <row r="242" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -13251,13 +13575,13 @@
         <v>233</v>
       </c>
       <c r="B242" s="5" t="s">
-        <v>885</v>
+        <v>893</v>
       </c>
       <c r="C242" s="5" t="s">
-        <v>1240</v>
+        <v>1248</v>
       </c>
       <c r="D242" s="6" t="s">
-        <v>1241</v>
+        <v>1249</v>
       </c>
       <c r="E242" s="5" t="s">
         <v>559</v>
@@ -13268,16 +13592,16 @@
         <v>234</v>
       </c>
       <c r="B243" s="5" t="s">
-        <v>896</v>
+        <v>904</v>
       </c>
       <c r="C243" s="5" t="s">
-        <v>1242</v>
+        <v>1250</v>
       </c>
       <c r="D243" s="6" t="s">
-        <v>1243</v>
+        <v>1251</v>
       </c>
       <c r="E243" s="5" t="s">
-        <v>1244</v>
+        <v>1252</v>
       </c>
     </row>
     <row r="244" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -13285,16 +13609,16 @@
         <v>235</v>
       </c>
       <c r="B244" s="5" t="s">
-        <v>690</v>
+        <v>698</v>
       </c>
       <c r="C244" s="5" t="s">
-        <v>1245</v>
+        <v>1253</v>
       </c>
       <c r="D244" s="6" t="s">
-        <v>1246</v>
+        <v>1254</v>
       </c>
       <c r="E244" s="5" t="s">
-        <v>1244</v>
+        <v>1252</v>
       </c>
     </row>
     <row r="245" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -13302,16 +13626,16 @@
         <v>236</v>
       </c>
       <c r="B245" s="5" t="s">
-        <v>690</v>
+        <v>698</v>
       </c>
       <c r="C245" s="5" t="s">
-        <v>1247</v>
+        <v>1255</v>
       </c>
       <c r="D245" s="6" t="s">
-        <v>1248</v>
+        <v>1256</v>
       </c>
       <c r="E245" s="5" t="s">
-        <v>1244</v>
+        <v>1252</v>
       </c>
     </row>
     <row r="246" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -13319,16 +13643,16 @@
         <v>237</v>
       </c>
       <c r="B246" s="5" t="s">
-        <v>885</v>
+        <v>893</v>
       </c>
       <c r="C246" s="5" t="s">
-        <v>1249</v>
+        <v>1257</v>
       </c>
       <c r="D246" s="6" t="s">
-        <v>1250</v>
+        <v>1258</v>
       </c>
       <c r="E246" s="5" t="s">
-        <v>1244</v>
+        <v>1252</v>
       </c>
     </row>
     <row r="247" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -13336,13 +13660,13 @@
         <v>238</v>
       </c>
       <c r="B247" s="5" t="s">
-        <v>829</v>
+        <v>837</v>
       </c>
       <c r="C247" s="5" t="s">
-        <v>1251</v>
+        <v>1259</v>
       </c>
       <c r="D247" s="6" t="s">
-        <v>1252</v>
+        <v>1260</v>
       </c>
       <c r="E247" s="5" t="s">
         <v>562</v>
@@ -13353,16 +13677,16 @@
         <v>239</v>
       </c>
       <c r="B248" s="5" t="s">
-        <v>690</v>
+        <v>698</v>
       </c>
       <c r="C248" s="5" t="s">
-        <v>1253</v>
+        <v>1261</v>
       </c>
       <c r="D248" s="6" t="s">
-        <v>1254</v>
+        <v>1262</v>
       </c>
       <c r="E248" s="5" t="s">
-        <v>1255</v>
+        <v>1263</v>
       </c>
     </row>
     <row r="249" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -13370,16 +13694,16 @@
         <v>240</v>
       </c>
       <c r="B249" s="5" t="s">
-        <v>829</v>
+        <v>837</v>
       </c>
       <c r="C249" s="5" t="s">
-        <v>1256</v>
+        <v>1264</v>
       </c>
       <c r="D249" s="6" t="s">
-        <v>1257</v>
+        <v>1265</v>
       </c>
       <c r="E249" s="5" t="s">
-        <v>1255</v>
+        <v>1263</v>
       </c>
     </row>
     <row r="250" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -13387,16 +13711,16 @@
         <v>241</v>
       </c>
       <c r="B250" s="5" t="s">
-        <v>815</v>
+        <v>823</v>
       </c>
       <c r="C250" s="5" t="s">
-        <v>1258</v>
+        <v>1266</v>
       </c>
       <c r="D250" s="6" t="s">
-        <v>1259</v>
+        <v>1267</v>
       </c>
       <c r="E250" s="5" t="s">
-        <v>1260</v>
+        <v>1268</v>
       </c>
     </row>
     <row r="251" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -13404,16 +13728,16 @@
         <v>242</v>
       </c>
       <c r="B251" s="5" t="s">
-        <v>829</v>
+        <v>837</v>
       </c>
       <c r="C251" s="5" t="s">
-        <v>1261</v>
+        <v>1269</v>
       </c>
       <c r="D251" s="6" t="s">
-        <v>1262</v>
+        <v>1270</v>
       </c>
       <c r="E251" s="5" t="s">
-        <v>1263</v>
+        <v>1271</v>
       </c>
     </row>
     <row r="252" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -13421,16 +13745,16 @@
         <v>243</v>
       </c>
       <c r="B252" s="5" t="s">
-        <v>1264</v>
+        <v>1272</v>
       </c>
       <c r="C252" s="5" t="s">
-        <v>1265</v>
+        <v>1273</v>
       </c>
       <c r="D252" s="6" t="s">
-        <v>1266</v>
+        <v>1274</v>
       </c>
       <c r="E252" s="5" t="s">
-        <v>1267</v>
+        <v>1275</v>
       </c>
     </row>
     <row r="253" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -13438,16 +13762,16 @@
         <v>244</v>
       </c>
       <c r="B253" s="5" t="s">
-        <v>1268</v>
+        <v>1276</v>
       </c>
       <c r="C253" s="5" t="s">
-        <v>1269</v>
+        <v>1277</v>
       </c>
       <c r="D253" s="6" t="s">
-        <v>1270</v>
+        <v>1278</v>
       </c>
       <c r="E253" s="5" t="s">
-        <v>1255</v>
+        <v>1263</v>
       </c>
     </row>
     <row r="254" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -13455,16 +13779,16 @@
         <v>245</v>
       </c>
       <c r="B254" s="5" t="s">
-        <v>829</v>
+        <v>837</v>
       </c>
       <c r="C254" s="5" t="s">
+        <v>1279</v>
+      </c>
+      <c r="D254" s="6" t="s">
+        <v>1280</v>
+      </c>
+      <c r="E254" s="5" t="s">
         <v>1271</v>
-      </c>
-      <c r="D254" s="6" t="s">
-        <v>1272</v>
-      </c>
-      <c r="E254" s="5" t="s">
-        <v>1263</v>
       </c>
     </row>
     <row r="255" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -13472,16 +13796,16 @@
         <v>246</v>
       </c>
       <c r="B255" s="5" t="s">
-        <v>1264</v>
+        <v>1272</v>
       </c>
       <c r="C255" s="5" t="s">
-        <v>1273</v>
+        <v>1281</v>
       </c>
       <c r="D255" s="6" t="s">
-        <v>1274</v>
+        <v>1282</v>
       </c>
       <c r="E255" s="5" t="s">
-        <v>1260</v>
+        <v>1268</v>
       </c>
     </row>
     <row r="256" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -13489,16 +13813,16 @@
         <v>247</v>
       </c>
       <c r="B256" s="5" t="s">
-        <v>1275</v>
+        <v>1283</v>
       </c>
       <c r="C256" s="5" t="s">
-        <v>1276</v>
+        <v>1284</v>
       </c>
       <c r="D256" s="6" t="s">
-        <v>1277</v>
+        <v>1285</v>
       </c>
       <c r="E256" s="5" t="s">
-        <v>1263</v>
+        <v>1271</v>
       </c>
     </row>
     <row r="257" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -13506,16 +13830,16 @@
         <v>248</v>
       </c>
       <c r="B257" s="5" t="s">
-        <v>829</v>
+        <v>837</v>
       </c>
       <c r="C257" s="5" t="s">
-        <v>1278</v>
+        <v>1286</v>
       </c>
       <c r="D257" s="6" t="s">
-        <v>1279</v>
+        <v>1287</v>
       </c>
       <c r="E257" s="5" t="s">
-        <v>1263</v>
+        <v>1271</v>
       </c>
     </row>
     <row r="258" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -13523,16 +13847,16 @@
         <v>249</v>
       </c>
       <c r="B258" s="5" t="s">
-        <v>896</v>
+        <v>904</v>
       </c>
       <c r="C258" s="5" t="s">
-        <v>1280</v>
+        <v>1288</v>
       </c>
       <c r="D258" s="6" t="s">
-        <v>1281</v>
+        <v>1289</v>
       </c>
       <c r="E258" s="5" t="s">
-        <v>1263</v>
+        <v>1271</v>
       </c>
     </row>
     <row r="259" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -13540,16 +13864,16 @@
         <v>250</v>
       </c>
       <c r="B259" s="5" t="s">
-        <v>1268</v>
+        <v>1276</v>
       </c>
       <c r="C259" s="5" t="s">
-        <v>1282</v>
+        <v>1290</v>
       </c>
       <c r="D259" s="6" t="s">
-        <v>1283</v>
+        <v>1291</v>
       </c>
       <c r="E259" s="5" t="s">
-        <v>1267</v>
+        <v>1275</v>
       </c>
     </row>
     <row r="260" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -13557,16 +13881,16 @@
         <v>251</v>
       </c>
       <c r="B260" s="5" t="s">
-        <v>1264</v>
+        <v>1272</v>
       </c>
       <c r="C260" s="5" t="s">
-        <v>1284</v>
+        <v>1292</v>
       </c>
       <c r="D260" s="6" t="s">
-        <v>1285</v>
+        <v>1293</v>
       </c>
       <c r="E260" s="5" t="s">
-        <v>1286</v>
+        <v>1294</v>
       </c>
     </row>
     <row r="261" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -13574,16 +13898,16 @@
         <v>252</v>
       </c>
       <c r="B261" s="5" t="s">
-        <v>1264</v>
+        <v>1272</v>
       </c>
       <c r="C261" s="5" t="s">
-        <v>1287</v>
+        <v>1295</v>
       </c>
       <c r="D261" s="6" t="s">
-        <v>1288</v>
+        <v>1296</v>
       </c>
       <c r="E261" s="5" t="s">
-        <v>1286</v>
+        <v>1294</v>
       </c>
     </row>
     <row r="262" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -13591,16 +13915,16 @@
         <v>253</v>
       </c>
       <c r="B262" s="5" t="s">
-        <v>690</v>
+        <v>698</v>
       </c>
       <c r="C262" s="5" t="s">
-        <v>1289</v>
+        <v>1297</v>
       </c>
       <c r="D262" s="6" t="s">
-        <v>1290</v>
+        <v>1298</v>
       </c>
       <c r="E262" s="5" t="s">
-        <v>1286</v>
+        <v>1294</v>
       </c>
     </row>
     <row r="263" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -13608,16 +13932,16 @@
         <v>254</v>
       </c>
       <c r="B263" s="5" t="s">
-        <v>829</v>
+        <v>837</v>
       </c>
       <c r="C263" s="5" t="s">
-        <v>1291</v>
+        <v>1299</v>
       </c>
       <c r="D263" s="6" t="s">
-        <v>1292</v>
+        <v>1300</v>
       </c>
       <c r="E263" s="5" t="s">
-        <v>1293</v>
+        <v>1301</v>
       </c>
     </row>
     <row r="264" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -13625,16 +13949,16 @@
         <v>255</v>
       </c>
       <c r="B264" s="5" t="s">
-        <v>690</v>
+        <v>698</v>
       </c>
       <c r="C264" s="5" t="s">
-        <v>1294</v>
+        <v>1302</v>
       </c>
       <c r="D264" s="6" t="s">
-        <v>1295</v>
+        <v>1303</v>
       </c>
       <c r="E264" s="5" t="s">
-        <v>1296</v>
+        <v>1304</v>
       </c>
     </row>
     <row r="265" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -13642,16 +13966,16 @@
         <v>256</v>
       </c>
       <c r="B265" s="5" t="s">
-        <v>821</v>
+        <v>829</v>
       </c>
       <c r="C265" s="5" t="s">
-        <v>1297</v>
+        <v>1305</v>
       </c>
       <c r="D265" s="6" t="s">
-        <v>1298</v>
+        <v>1306</v>
       </c>
       <c r="E265" s="5" t="s">
-        <v>1296</v>
+        <v>1304</v>
       </c>
     </row>
     <row r="266" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -13659,16 +13983,16 @@
         <v>257</v>
       </c>
       <c r="B266" s="5" t="s">
-        <v>1299</v>
+        <v>1307</v>
       </c>
       <c r="C266" s="5" t="s">
-        <v>1300</v>
+        <v>1308</v>
       </c>
       <c r="D266" s="6" t="s">
-        <v>1301</v>
+        <v>1309</v>
       </c>
       <c r="E266" s="5" t="s">
-        <v>1286</v>
+        <v>1294</v>
       </c>
     </row>
     <row r="267" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -13676,152 +14000,373 @@
         <v>258</v>
       </c>
       <c r="B267" s="5" t="s">
-        <v>896</v>
+        <v>904</v>
       </c>
       <c r="C267" s="5" t="s">
-        <v>1302</v>
+        <v>1310</v>
       </c>
       <c r="D267" s="6" t="s">
-        <v>1303</v>
+        <v>1311</v>
       </c>
       <c r="E267" s="5" t="s">
-        <v>1286</v>
-      </c>
-    </row>
-    <row r="268" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+        <v>1294</v>
+      </c>
+    </row>
+    <row r="268" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A268" s="5" t="n">
         <v>259</v>
       </c>
       <c r="B268" s="5" t="s">
-        <v>1053</v>
+        <v>1061</v>
       </c>
       <c r="C268" s="5" t="s">
-        <v>1304</v>
+        <v>1312</v>
       </c>
       <c r="D268" s="6" t="s">
-        <v>1305</v>
+        <v>1313</v>
       </c>
       <c r="E268" s="5" t="s">
-        <v>1306</v>
-      </c>
-    </row>
-    <row r="269" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+        <v>1314</v>
+      </c>
+    </row>
+    <row r="269" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A269" s="5" t="n">
         <v>260</v>
       </c>
       <c r="B269" s="5" t="s">
-        <v>1264</v>
+        <v>1272</v>
       </c>
       <c r="C269" s="5" t="s">
-        <v>1307</v>
+        <v>1315</v>
       </c>
       <c r="D269" s="6" t="s">
-        <v>1308</v>
+        <v>1316</v>
       </c>
       <c r="E269" s="5" t="s">
-        <v>1309</v>
-      </c>
-    </row>
-    <row r="270" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+        <v>1317</v>
+      </c>
+    </row>
+    <row r="270" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A270" s="5" t="n">
         <v>261</v>
       </c>
       <c r="B270" s="5" t="s">
-        <v>829</v>
+        <v>837</v>
       </c>
       <c r="C270" s="5" t="s">
-        <v>1310</v>
+        <v>1318</v>
       </c>
       <c r="D270" s="6" t="s">
-        <v>1311</v>
+        <v>1319</v>
       </c>
       <c r="E270" s="5" t="s">
-        <v>1309</v>
-      </c>
-    </row>
-    <row r="271" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+        <v>1317</v>
+      </c>
+    </row>
+    <row r="271" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A271" s="5" t="n">
         <v>262</v>
       </c>
       <c r="B271" s="5" t="s">
-        <v>1264</v>
+        <v>1272</v>
       </c>
       <c r="C271" s="5" t="s">
-        <v>1312</v>
+        <v>1320</v>
       </c>
       <c r="D271" s="6" t="s">
-        <v>1313</v>
+        <v>1321</v>
       </c>
       <c r="E271" s="5" t="s">
-        <v>1309</v>
-      </c>
-    </row>
-    <row r="272" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+        <v>1317</v>
+      </c>
+    </row>
+    <row r="272" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A272" s="5" t="n">
         <v>263</v>
       </c>
       <c r="B272" s="5" t="s">
-        <v>829</v>
+        <v>837</v>
       </c>
       <c r="C272" s="5" t="s">
-        <v>1314</v>
+        <v>1322</v>
       </c>
       <c r="D272" s="6" t="s">
-        <v>1315</v>
+        <v>1323</v>
       </c>
       <c r="E272" s="5" t="s">
-        <v>1309</v>
-      </c>
-    </row>
-    <row r="273" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+        <v>1317</v>
+      </c>
+    </row>
+    <row r="273" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A273" s="5" t="n">
         <v>264</v>
       </c>
       <c r="B273" s="5" t="s">
-        <v>1053</v>
+        <v>1061</v>
       </c>
       <c r="C273" s="5" t="s">
-        <v>1316</v>
+        <v>1324</v>
       </c>
       <c r="D273" s="6" t="s">
-        <v>1317</v>
+        <v>1325</v>
       </c>
       <c r="E273" s="5" t="s">
-        <v>1318</v>
-      </c>
-    </row>
-    <row r="274" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+        <v>1326</v>
+      </c>
+    </row>
+    <row r="274" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A274" s="5" t="n">
         <v>265</v>
       </c>
       <c r="B274" s="5" t="s">
-        <v>1275</v>
+        <v>1283</v>
       </c>
       <c r="C274" s="5" t="s">
-        <v>1319</v>
+        <v>1327</v>
       </c>
       <c r="D274" s="6" t="s">
-        <v>1320</v>
+        <v>1328</v>
       </c>
       <c r="E274" s="5" t="s">
-        <v>1309</v>
-      </c>
-    </row>
-    <row r="275" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+        <v>1317</v>
+      </c>
+    </row>
+    <row r="275" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A275" s="5" t="n">
         <v>266</v>
       </c>
       <c r="B275" s="5" t="s">
+        <v>837</v>
+      </c>
+      <c r="C275" s="5" t="s">
+        <v>1329</v>
+      </c>
+      <c r="D275" s="6" t="s">
+        <v>1330</v>
+      </c>
+      <c r="E275" s="5" t="s">
+        <v>1314</v>
+      </c>
+    </row>
+    <row r="276" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A276" s="5" t="n">
+        <v>267</v>
+      </c>
+      <c r="B276" s="5" t="s">
+        <v>1272</v>
+      </c>
+      <c r="C276" s="5" t="s">
+        <v>1331</v>
+      </c>
+      <c r="D276" s="6" t="s">
+        <v>1332</v>
+      </c>
+      <c r="E276" s="5" t="s">
+        <v>576</v>
+      </c>
+    </row>
+    <row r="277" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A277" s="5" t="n">
+        <v>268</v>
+      </c>
+      <c r="B277" s="5" t="s">
+        <v>1272</v>
+      </c>
+      <c r="C277" s="5" t="s">
+        <v>1333</v>
+      </c>
+      <c r="D277" s="6" t="s">
+        <v>1334</v>
+      </c>
+      <c r="E277" s="5" t="s">
+        <v>1335</v>
+      </c>
+    </row>
+    <row r="278" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A278" s="5" t="n">
+        <v>269</v>
+      </c>
+      <c r="B278" s="5" t="s">
+        <v>837</v>
+      </c>
+      <c r="C278" s="5" t="s">
+        <v>1336</v>
+      </c>
+      <c r="D278" s="6" t="s">
+        <v>1337</v>
+      </c>
+      <c r="E278" s="5" t="s">
+        <v>1338</v>
+      </c>
+    </row>
+    <row r="279" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A279" s="5" t="n">
+        <v>270</v>
+      </c>
+      <c r="B279" s="5" t="s">
+        <v>1272</v>
+      </c>
+      <c r="C279" s="5" t="s">
+        <v>1339</v>
+      </c>
+      <c r="D279" s="6" t="s">
+        <v>1340</v>
+      </c>
+      <c r="E279" s="5" t="s">
+        <v>1341</v>
+      </c>
+    </row>
+    <row r="280" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A280" s="5" t="n">
+        <v>271</v>
+      </c>
+      <c r="B280" s="5" t="s">
         <v>829</v>
       </c>
-      <c r="C275" s="5" t="s">
-        <v>1321</v>
-      </c>
-      <c r="D275" s="6" t="s">
-        <v>1322</v>
-      </c>
-      <c r="E275" s="5" t="s">
-        <v>1306</v>
+      <c r="C280" s="5" t="s">
+        <v>1342</v>
+      </c>
+      <c r="D280" s="6" t="s">
+        <v>1343</v>
+      </c>
+      <c r="E280" s="5" t="s">
+        <v>576</v>
+      </c>
+    </row>
+    <row r="281" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A281" s="5" t="n">
+        <v>272</v>
+      </c>
+      <c r="B281" s="5" t="s">
+        <v>1272</v>
+      </c>
+      <c r="C281" s="5" t="s">
+        <v>1344</v>
+      </c>
+      <c r="D281" s="6" t="s">
+        <v>1345</v>
+      </c>
+      <c r="E281" s="5" t="s">
+        <v>1346</v>
+      </c>
+    </row>
+    <row r="282" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A282" s="5" t="n">
+        <v>273</v>
+      </c>
+      <c r="B282" s="5" t="s">
+        <v>1283</v>
+      </c>
+      <c r="C282" s="5" t="s">
+        <v>1347</v>
+      </c>
+      <c r="D282" s="6" t="s">
+        <v>1348</v>
+      </c>
+      <c r="E282" s="5" t="s">
+        <v>1349</v>
+      </c>
+    </row>
+    <row r="283" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A283" s="5" t="n">
+        <v>274</v>
+      </c>
+      <c r="B283" s="5" t="s">
+        <v>1283</v>
+      </c>
+      <c r="C283" s="5" t="s">
+        <v>1350</v>
+      </c>
+      <c r="D283" s="6" t="s">
+        <v>1351</v>
+      </c>
+      <c r="E283" s="5" t="s">
+        <v>1341</v>
+      </c>
+    </row>
+    <row r="284" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A284" s="5" t="n">
+        <v>275</v>
+      </c>
+      <c r="B284" s="5" t="s">
+        <v>847</v>
+      </c>
+      <c r="C284" s="5" t="s">
+        <v>1352</v>
+      </c>
+      <c r="D284" s="6" t="s">
+        <v>1353</v>
+      </c>
+      <c r="E284" s="5" t="s">
+        <v>1349</v>
+      </c>
+    </row>
+    <row r="285" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A285" s="5" t="n">
+        <v>276</v>
+      </c>
+      <c r="B285" s="5" t="s">
+        <v>829</v>
+      </c>
+      <c r="C285" s="5" t="s">
+        <v>1354</v>
+      </c>
+      <c r="D285" s="6" t="s">
+        <v>1355</v>
+      </c>
+      <c r="E285" s="5" t="s">
+        <v>1338</v>
+      </c>
+    </row>
+    <row r="286" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A286" s="5" t="n">
+        <v>277</v>
+      </c>
+      <c r="B286" s="5" t="s">
+        <v>1272</v>
+      </c>
+      <c r="C286" s="5" t="s">
+        <v>1356</v>
+      </c>
+      <c r="D286" s="6" t="s">
+        <v>1357</v>
+      </c>
+      <c r="E286" s="5" t="s">
+        <v>1346</v>
+      </c>
+    </row>
+    <row r="287" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A287" s="5" t="n">
+        <v>278</v>
+      </c>
+      <c r="B287" s="5" t="s">
+        <v>847</v>
+      </c>
+      <c r="C287" s="5" t="s">
+        <v>1358</v>
+      </c>
+      <c r="D287" s="6" t="s">
+        <v>1359</v>
+      </c>
+      <c r="E287" s="5" t="s">
+        <v>1335</v>
+      </c>
+    </row>
+    <row r="288" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A288" s="5" t="n">
+        <v>279</v>
+      </c>
+      <c r="B288" s="5" t="s">
+        <v>837</v>
+      </c>
+      <c r="C288" s="5" t="s">
+        <v>1360</v>
+      </c>
+      <c r="D288" s="6" t="s">
+        <v>1361</v>
+      </c>
+      <c r="E288" s="5" t="s">
+        <v>1362</v>
       </c>
     </row>
   </sheetData>
@@ -14022,6 +14567,19 @@
     <hyperlink ref="D273" r:id="rId191" display="https://www.pbs.org/newshour/nation/shock-gloves-purchased-by-ice-cause-pain-compliance-and-fear-army-study-found"/>
     <hyperlink ref="D274" r:id="rId192" display="https://www.nytimes.com/2026/10/05/us/politico-blocked-trump-nebraska.html"/>
     <hyperlink ref="D275" r:id="rId193" display="https://www.theguardian.com/commentisfree/2026/oct/09/nidal-hasan-execution-pete-hegseth-us-military-tv-democracy"/>
+    <hyperlink ref="D276" r:id="rId194" display="https://www.axios.com/2026/10/12/ilhan-omar-search-immigration"/>
+    <hyperlink ref="D277" r:id="rId195" display="https://www.axios.com/2026/10/14/ice-body-cam-automatic-gao-report"/>
+    <hyperlink ref="D278" r:id="rId196" display="https://www.theguardian.com/us-news/2026/oct/11/ice-agent-strikes-man-with-car-texas"/>
+    <hyperlink ref="D279" r:id="rId197" display="https://www.axios.com/2026/10/15/trump-doj-california-voters-ballots-lawsuit"/>
+    <hyperlink ref="D280" r:id="rId198" display="https://thehill.com/regulation/court-battles/6143318-trump-administration-east-potomac-park-golf-trees/"/>
+    <hyperlink ref="D281" r:id="rId199" display="https://www.axios.com/2026/10/13/execution-nidal-hasan-firing-squad-hegseth-stream"/>
+    <hyperlink ref="D282" r:id="rId200" display="https://www.nytimes.com/2026/10/17/us/politics/election-fraud-conspiracies-trump.html"/>
+    <hyperlink ref="D283" r:id="rId201" display="https://www.nytimes.com/2026/10/15/us/politics/trump-administration-california-voter-rolls.html"/>
+    <hyperlink ref="D284" r:id="rId202" display="https://www.bloomberg.com/news/articles/2026-10-17/trump-waives-russia-energy-tariffs-sanctions-in-graham-law"/>
+    <hyperlink ref="D285" r:id="rId203" display="https://thehill.com/homenews/administration/6141440-mullin-backs-hasan-execution-livestream/"/>
+    <hyperlink ref="D286" r:id="rId204" display="https://www.axios.com/2026/10/13/trump-russian-diesel-deal-betrayal-bipartisan-letter"/>
+    <hyperlink ref="D287" r:id="rId205" display="https://www.bloomberg.com/news/articles/2026-10-14/trump-pardons-two-alaska-mechanics-over-clean-air-act-violations"/>
+    <hyperlink ref="D288" r:id="rId206" display="https://www.theguardian.com/commentisfree/2026/oct/16/donald-trump-russia-ukraine-protect-world"/>
   </hyperlinks>
   <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.511811023622047" footer="0.511811023622047"/>
@@ -14047,7 +14605,7 @@
   <sheetData>
     <row r="1" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A1" s="7" t="s">
-        <v>1323</v>
+        <v>1363</v>
       </c>
       <c r="B1" s="7"/>
     </row>
@@ -14056,7 +14614,7 @@
         <v>3</v>
       </c>
       <c r="B2" s="8" t="s">
-        <v>1324</v>
+        <v>1364</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -14092,7 +14650,7 @@
       </c>
       <c r="B6" s="9" t="n">
         <f aca="false">COUNTIF('Weekly Timeline'!C:C,A6)</f>
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -14128,7 +14686,7 @@
       </c>
       <c r="B10" s="9" t="n">
         <f aca="false">COUNTIF('Weekly Timeline'!C:C,A10)</f>
-        <v>4</v>
+        <v>7</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -14137,7 +14695,7 @@
       </c>
       <c r="B11" s="9" t="n">
         <f aca="false">COUNTIF('Weekly Timeline'!C:C,A11)</f>
-        <v>5</v>
+        <v>7</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -14164,7 +14722,7 @@
       </c>
       <c r="B14" s="9" t="n">
         <f aca="false">COUNTIF('Weekly Timeline'!C:C,A14)</f>
-        <v>18</v>
+        <v>21</v>
       </c>
     </row>
     <row r="15" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -14227,7 +14785,7 @@
       </c>
       <c r="B21" s="9" t="n">
         <f aca="false">COUNTIF('Weekly Timeline'!C:C,A21)</f>
-        <v>4</v>
+        <v>7</v>
       </c>
     </row>
     <row r="22" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -14248,22 +14806,22 @@
         <v>4</v>
       </c>
     </row>
-    <row r="24" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A24" s="10" t="s">
+    <row r="24" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A24" s="9" t="s">
         <v>346</v>
       </c>
-      <c r="B24" s="10" t="n">
+      <c r="B24" s="9" t="n">
         <f aca="false">COUNTIF('Weekly Timeline'!C:C,A24)</f>
         <v>1</v>
       </c>
     </row>
-    <row r="25" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A25" s="11" t="s">
-        <v>1325</v>
-      </c>
-      <c r="B25" s="11" t="n">
+    <row r="25" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A25" s="10" t="s">
+        <v>1365</v>
+      </c>
+      <c r="B25" s="10" t="n">
         <f aca="false">SUM(B3:B24)</f>
-        <v>210</v>
+        <v>223</v>
       </c>
     </row>
   </sheetData>

--- a/data/Trump_Second_Term_Weekly_Tracker.xlsx
+++ b/data/Trump_Second_Term_Weekly_Tracker.xlsx
@@ -1,8 +1,8 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2">
   <fileVersion appName="Calc"/>
-  <workbookPr backupFile="false" showObjects="all" dateCompatibility="false"/>
+  <workbookPr backupFile="false" showObjects="all" date1904="false"/>
   <workbookProtection/>
   <bookViews>
     <workbookView showHorizontalScroll="true" showVerticalScroll="true" showSheetTabs="true" xWindow="0" yWindow="0" windowWidth="16384" windowHeight="8192" tabRatio="500" firstSheet="0" activeTab="0"/>
@@ -13,7 +13,7 @@
     <sheet name="Summary" sheetId="3" state="visible" r:id="rId5"/>
   </sheets>
   <definedNames>
-    <definedName function="false" hidden="true" localSheetId="0" name="_xlnm._FilterDatabase" vbProcedure="false">'Weekly Timeline'!$A$2:$F$281</definedName>
+    <definedName function="false" hidden="true" localSheetId="0" name="_xlnm._FilterDatabase" vbProcedure="false">'Weekly Timeline'!$A$2:$F$291</definedName>
   </definedNames>
   <calcPr iterateCount="100" refMode="A1" iterate="false" iterateDelta="0.0001"/>
   <extLst>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2196" uniqueCount="1366">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2266" uniqueCount="1394">
   <si>
     <t xml:space="preserve">Documented actions and policies of the second Trump administration reported as harmful by major news outlets, courts, and government data — Jan 20, 2025 through Jul 8, 2026. One row per event; weeks with multiple events have multiple rows; quiet weeks are skipped. This compiles critical coverage as requested; the administration and its supporters dispute many of these characterizations. See the Sources tab (matching Ref #) and verify details independently before citing.</t>
   </si>
@@ -1779,6 +1779,21 @@
     <t xml:space="preserve">Oct 16</t>
   </si>
   <si>
+    <t xml:space="preserve">Oct 19, 2026</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Oct 19</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Oct 21</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Oct 23</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Oct 22</t>
+  </si>
+  <si>
     <t xml:space="preserve">Ref # matches the Source Ref column on the Weekly Timeline tab. URLs are provided where verified via current web results (mostly 2026 items). For 2025 items, outlet names and dates are given; searching the description text will locate the original coverage. Per your request the mix emphasizes CNN, Politico, MSNBC/MS NOW, NBC and independent outlets, alongside AP, Reuters, Guardian, NPR, CBS, ABC and court documents.</t>
   </si>
   <si>
@@ -4114,6 +4129,75 @@
   </si>
   <si>
     <t xml:space="preserve">Oct 16, 2026</t>
+  </si>
+  <si>
+    <t xml:space="preserve">US citizen injured by ICE agents in California</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://www.theguardian.com/us-news/video/2026/oct/19/us-citizen-injured-by-ice-agents-in-california-video</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Severely ill ICE detainees targeted for imminent deportation in Florida, advocates say</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://www.theguardian.com/us-news/2026/oct/21/ice-detention-illness-deportation-florida</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Oct 21, 2026</t>
+  </si>
+  <si>
+    <t xml:space="preserve">DOJ sues to delay Alaska election results if GOP incumbent loses</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://www.axios.com/2026/10/23/trump-administration-sues-alaska-dan-sullivan</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Oct 23, 2026</t>
+  </si>
+  <si>
+    <t xml:space="preserve">DOJ monitoring plans and DHS voter checks raise concerns of election interference</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://www.pbs.org/newshour/show/doj-monitoring-plans-and-dhs-voter-checks-raise-concerns-of-election-interference</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Oct 22, 2026</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Trump administration asks Supreme Court to allow Big Bend border wall construction</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://thehill.com/regulation/court-battles/6164069-trump-asks-scotus-big-bend-wall/</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Investigation finds hundreds of U.S. citizens detained by ICE</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://www.pbs.org/newshour/show/investigation-finds-hundreds-of-u-s-citizens-detained-by-ice</t>
+  </si>
+  <si>
+    <t xml:space="preserve">DHS knocks on doors over citizenship, voting</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://www.cbsnews.com/video/dhs-knocks-on-doors-over-citizenship-voting/</t>
+  </si>
+  <si>
+    <t xml:space="preserve">White House to Politico: Retract stories or face "consequences"</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://www.axios.com/2026/10/21/white-house-politico-retract-stories-or-face-consequences</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Appeals court rules Trump unlawfully deployed National Guard to California</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://thehill.com/regulation/court-battles/6168756-trump-los-angeles-deployment-unlawful-appeals-court-ruling/</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Musk Ordered Starlink Slowdown Helped the Russians</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://www.bloomberg.com/news/videos/2026-10-22/farkas-says-starlink-slowdown-helped-the-russians-video</t>
   </si>
   <si>
     <t xml:space="preserve">Entries by category (live COUNTIF formulas against the Weekly Timeline tab)</t>
@@ -4423,34 +4507,34 @@
         <a:srgbClr val="000000"/>
       </a:dk1>
       <a:lt1>
-        <a:srgbClr val="ffffff"/>
+        <a:srgbClr val="FFFFFF"/>
       </a:lt1>
       <a:dk2>
-        <a:srgbClr val="1f497d"/>
+        <a:srgbClr val="1F497D"/>
       </a:dk2>
       <a:lt2>
-        <a:srgbClr val="eeece1"/>
+        <a:srgbClr val="EEECE1"/>
       </a:lt2>
       <a:accent1>
-        <a:srgbClr val="4f81bd"/>
+        <a:srgbClr val="4F81BD"/>
       </a:accent1>
       <a:accent2>
-        <a:srgbClr val="c0504d"/>
+        <a:srgbClr val="C0504D"/>
       </a:accent2>
       <a:accent3>
-        <a:srgbClr val="9bbb59"/>
+        <a:srgbClr val="9BBB59"/>
       </a:accent3>
       <a:accent4>
-        <a:srgbClr val="8064a2"/>
+        <a:srgbClr val="8064A2"/>
       </a:accent4>
       <a:accent5>
-        <a:srgbClr val="4bacc6"/>
+        <a:srgbClr val="4BACC6"/>
       </a:accent5>
       <a:accent6>
-        <a:srgbClr val="f79646"/>
+        <a:srgbClr val="F79646"/>
       </a:accent6>
       <a:hlink>
-        <a:srgbClr val="0000ff"/>
+        <a:srgbClr val="0000FF"/>
       </a:hlink>
       <a:folHlink>
         <a:srgbClr val="800080"/>
@@ -4595,8 +4679,8 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:F281"/>
-  <sheetFormatPr defaultColWidth="8.6875" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <dimension ref="A1:F291"/>
+  <sheetFormatPr defaultColWidth="8.6875" defaultRowHeight="15" customHeight="false" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="13.01"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="1" width="11.99"/>
@@ -9403,7 +9487,7 @@
         <v>266</v>
       </c>
     </row>
-    <row r="269" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="269" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A269" s="4" t="s">
         <v>576</v>
       </c>
@@ -9419,7 +9503,7 @@
         <v>267</v>
       </c>
     </row>
-    <row r="270" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="270" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A270" s="4" t="s">
         <v>576</v>
       </c>
@@ -9435,7 +9519,7 @@
         <v>268</v>
       </c>
     </row>
-    <row r="271" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="271" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A271" s="5" t="s">
         <v>570</v>
       </c>
@@ -9451,7 +9535,7 @@
         <v>269</v>
       </c>
     </row>
-    <row r="272" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="272" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A272" s="4" t="s">
         <v>576</v>
       </c>
@@ -9467,7 +9551,7 @@
         <v>270</v>
       </c>
     </row>
-    <row r="273" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="273" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A273" s="4" t="s">
         <v>576</v>
       </c>
@@ -9483,7 +9567,7 @@
         <v>271</v>
       </c>
     </row>
-    <row r="274" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="274" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A274" s="4" t="s">
         <v>576</v>
       </c>
@@ -9499,7 +9583,7 @@
         <v>272</v>
       </c>
     </row>
-    <row r="275" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="275" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A275" s="4" t="s">
         <v>576</v>
       </c>
@@ -9515,7 +9599,7 @@
         <v>273</v>
       </c>
     </row>
-    <row r="276" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="276" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A276" s="4" t="s">
         <v>576</v>
       </c>
@@ -9531,7 +9615,7 @@
         <v>274</v>
       </c>
     </row>
-    <row r="277" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="277" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A277" s="4" t="s">
         <v>576</v>
       </c>
@@ -9547,7 +9631,7 @@
         <v>275</v>
       </c>
     </row>
-    <row r="278" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="278" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A278" s="5" t="s">
         <v>570</v>
       </c>
@@ -9563,7 +9647,7 @@
         <v>276</v>
       </c>
     </row>
-    <row r="279" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="279" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A279" s="4" t="s">
         <v>576</v>
       </c>
@@ -9579,7 +9663,7 @@
         <v>277</v>
       </c>
     </row>
-    <row r="280" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="280" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A280" s="4" t="s">
         <v>576</v>
       </c>
@@ -9595,7 +9679,7 @@
         <v>278</v>
       </c>
     </row>
-    <row r="281" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="281" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A281" s="4" t="s">
         <v>576</v>
       </c>
@@ -9611,8 +9695,168 @@
         <v>279</v>
       </c>
     </row>
+    <row r="282" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A282" s="5" t="s">
+        <v>584</v>
+      </c>
+      <c r="B282" s="5" t="s">
+        <v>585</v>
+      </c>
+      <c r="C282" s="5" t="s">
+        <v>566</v>
+      </c>
+      <c r="D282" s="5"/>
+      <c r="E282" s="5"/>
+      <c r="F282" s="5" t="n">
+        <v>280</v>
+      </c>
+    </row>
+    <row r="283" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A283" s="5" t="s">
+        <v>584</v>
+      </c>
+      <c r="B283" s="5" t="s">
+        <v>586</v>
+      </c>
+      <c r="C283" s="5" t="s">
+        <v>566</v>
+      </c>
+      <c r="D283" s="5"/>
+      <c r="E283" s="5"/>
+      <c r="F283" s="5" t="n">
+        <v>281</v>
+      </c>
+    </row>
+    <row r="284" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A284" s="5" t="s">
+        <v>584</v>
+      </c>
+      <c r="B284" s="5" t="s">
+        <v>587</v>
+      </c>
+      <c r="C284" s="5" t="s">
+        <v>558</v>
+      </c>
+      <c r="D284" s="5"/>
+      <c r="E284" s="5"/>
+      <c r="F284" s="5" t="n">
+        <v>282</v>
+      </c>
+    </row>
+    <row r="285" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A285" s="5" t="s">
+        <v>584</v>
+      </c>
+      <c r="B285" s="5" t="s">
+        <v>588</v>
+      </c>
+      <c r="C285" s="5" t="s">
+        <v>558</v>
+      </c>
+      <c r="D285" s="5"/>
+      <c r="E285" s="5"/>
+      <c r="F285" s="5" t="n">
+        <v>283</v>
+      </c>
+    </row>
+    <row r="286" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A286" s="5" t="s">
+        <v>584</v>
+      </c>
+      <c r="B286" s="5" t="s">
+        <v>586</v>
+      </c>
+      <c r="C286" s="5" t="s">
+        <v>194</v>
+      </c>
+      <c r="D286" s="5"/>
+      <c r="E286" s="5"/>
+      <c r="F286" s="5" t="n">
+        <v>284</v>
+      </c>
+    </row>
+    <row r="287" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A287" s="5" t="s">
+        <v>584</v>
+      </c>
+      <c r="B287" s="5" t="s">
+        <v>586</v>
+      </c>
+      <c r="C287" s="5" t="s">
+        <v>566</v>
+      </c>
+      <c r="D287" s="5"/>
+      <c r="E287" s="5"/>
+      <c r="F287" s="5" t="n">
+        <v>285</v>
+      </c>
+    </row>
+    <row r="288" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A288" s="5" t="s">
+        <v>584</v>
+      </c>
+      <c r="B288" s="5" t="s">
+        <v>588</v>
+      </c>
+      <c r="C288" s="5" t="s">
+        <v>558</v>
+      </c>
+      <c r="D288" s="5"/>
+      <c r="E288" s="5"/>
+      <c r="F288" s="5" t="n">
+        <v>286</v>
+      </c>
+    </row>
+    <row r="289" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A289" s="5" t="s">
+        <v>584</v>
+      </c>
+      <c r="B289" s="5" t="s">
+        <v>586</v>
+      </c>
+      <c r="C289" s="5" t="s">
+        <v>68</v>
+      </c>
+      <c r="D289" s="5"/>
+      <c r="E289" s="5"/>
+      <c r="F289" s="5" t="n">
+        <v>287</v>
+      </c>
+    </row>
+    <row r="290" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A290" s="5" t="s">
+        <v>584</v>
+      </c>
+      <c r="B290" s="5" t="s">
+        <v>587</v>
+      </c>
+      <c r="C290" s="5" t="s">
+        <v>24</v>
+      </c>
+      <c r="D290" s="5"/>
+      <c r="E290" s="5"/>
+      <c r="F290" s="5" t="n">
+        <v>288</v>
+      </c>
+    </row>
+    <row r="291" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A291" s="5" t="s">
+        <v>584</v>
+      </c>
+      <c r="B291" s="5" t="s">
+        <v>588</v>
+      </c>
+      <c r="C291" s="5" t="s">
+        <v>48</v>
+      </c>
+      <c r="D291" s="5"/>
+      <c r="E291" s="5"/>
+      <c r="F291" s="5" t="n">
+        <v>289</v>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A2:F281"/>
+  <autoFilter ref="A2:F291"/>
   <mergeCells count="1">
     <mergeCell ref="A1:F1"/>
   </mergeCells>
@@ -9632,8 +9876,8 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:E288"/>
-  <sheetFormatPr defaultColWidth="8.6875" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <dimension ref="A1:E298"/>
+  <sheetFormatPr defaultColWidth="8.6875" defaultRowHeight="15" customHeight="false" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="7"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="1" width="26"/>
@@ -9643,7 +9887,7 @@
   <sheetData>
     <row r="1" customFormat="false" ht="48" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A1" s="2" t="s">
-        <v>584</v>
+        <v>589</v>
       </c>
       <c r="B1" s="2"/>
       <c r="C1" s="2"/>
@@ -9652,19 +9896,19 @@
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A2" s="3" t="s">
-        <v>585</v>
+        <v>590</v>
       </c>
       <c r="B2" s="3" t="s">
-        <v>586</v>
+        <v>591</v>
       </c>
       <c r="C2" s="3" t="s">
-        <v>587</v>
+        <v>592</v>
       </c>
       <c r="D2" s="3" t="s">
-        <v>588</v>
+        <v>593</v>
       </c>
       <c r="E2" s="3" t="s">
-        <v>589</v>
+        <v>594</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -9672,14 +9916,14 @@
         <v>1</v>
       </c>
       <c r="B3" s="5" t="s">
-        <v>590</v>
+        <v>595</v>
       </c>
       <c r="C3" s="5" t="s">
-        <v>591</v>
+        <v>596</v>
       </c>
       <c r="D3" s="5"/>
       <c r="E3" s="5" t="s">
-        <v>592</v>
+        <v>597</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -9687,14 +9931,14 @@
         <v>2</v>
       </c>
       <c r="B4" s="5" t="s">
-        <v>593</v>
+        <v>598</v>
       </c>
       <c r="C4" s="5" t="s">
-        <v>594</v>
+        <v>599</v>
       </c>
       <c r="D4" s="5"/>
       <c r="E4" s="5" t="s">
-        <v>595</v>
+        <v>600</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -9702,14 +9946,14 @@
         <v>3</v>
       </c>
       <c r="B5" s="5" t="s">
-        <v>596</v>
+        <v>601</v>
       </c>
       <c r="C5" s="5" t="s">
-        <v>597</v>
+        <v>602</v>
       </c>
       <c r="D5" s="5"/>
       <c r="E5" s="5" t="s">
-        <v>592</v>
+        <v>597</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -9717,14 +9961,14 @@
         <v>4</v>
       </c>
       <c r="B6" s="5" t="s">
-        <v>598</v>
+        <v>603</v>
       </c>
       <c r="C6" s="5" t="s">
-        <v>599</v>
+        <v>604</v>
       </c>
       <c r="D6" s="5"/>
       <c r="E6" s="5" t="s">
-        <v>600</v>
+        <v>605</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -9732,14 +9976,14 @@
         <v>5</v>
       </c>
       <c r="B7" s="5" t="s">
-        <v>601</v>
+        <v>606</v>
       </c>
       <c r="C7" s="5" t="s">
-        <v>602</v>
+        <v>607</v>
       </c>
       <c r="D7" s="5"/>
       <c r="E7" s="5" t="s">
-        <v>592</v>
+        <v>597</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -9747,14 +9991,14 @@
         <v>6</v>
       </c>
       <c r="B8" s="5" t="s">
-        <v>603</v>
+        <v>608</v>
       </c>
       <c r="C8" s="5" t="s">
-        <v>604</v>
+        <v>609</v>
       </c>
       <c r="D8" s="5"/>
       <c r="E8" s="5" t="s">
-        <v>592</v>
+        <v>597</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -9762,14 +10006,14 @@
         <v>7</v>
       </c>
       <c r="B9" s="5" t="s">
-        <v>605</v>
+        <v>610</v>
       </c>
       <c r="C9" s="5" t="s">
-        <v>606</v>
+        <v>611</v>
       </c>
       <c r="D9" s="5"/>
       <c r="E9" s="5" t="s">
-        <v>607</v>
+        <v>612</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -9777,14 +10021,14 @@
         <v>8</v>
       </c>
       <c r="B10" s="5" t="s">
-        <v>608</v>
+        <v>613</v>
       </c>
       <c r="C10" s="5" t="s">
-        <v>609</v>
+        <v>614</v>
       </c>
       <c r="D10" s="5"/>
       <c r="E10" s="5" t="s">
-        <v>610</v>
+        <v>615</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -9792,14 +10036,14 @@
         <v>9</v>
       </c>
       <c r="B11" s="5" t="s">
-        <v>611</v>
+        <v>616</v>
       </c>
       <c r="C11" s="5" t="s">
-        <v>612</v>
+        <v>617</v>
       </c>
       <c r="D11" s="5"/>
       <c r="E11" s="5" t="s">
-        <v>613</v>
+        <v>618</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -9807,14 +10051,14 @@
         <v>10</v>
       </c>
       <c r="B12" s="5" t="s">
-        <v>614</v>
+        <v>619</v>
       </c>
       <c r="C12" s="5" t="s">
-        <v>615</v>
+        <v>620</v>
       </c>
       <c r="D12" s="5"/>
       <c r="E12" s="5" t="s">
-        <v>616</v>
+        <v>621</v>
       </c>
     </row>
     <row r="13" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -9822,14 +10066,14 @@
         <v>11</v>
       </c>
       <c r="B13" s="5" t="s">
-        <v>617</v>
+        <v>622</v>
       </c>
       <c r="C13" s="5" t="s">
-        <v>618</v>
+        <v>623</v>
       </c>
       <c r="D13" s="5"/>
       <c r="E13" s="5" t="s">
-        <v>619</v>
+        <v>624</v>
       </c>
     </row>
     <row r="14" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -9837,14 +10081,14 @@
         <v>12</v>
       </c>
       <c r="B14" s="5" t="s">
-        <v>620</v>
+        <v>625</v>
       </c>
       <c r="C14" s="5" t="s">
-        <v>621</v>
+        <v>626</v>
       </c>
       <c r="D14" s="5"/>
       <c r="E14" s="5" t="s">
-        <v>622</v>
+        <v>627</v>
       </c>
     </row>
     <row r="15" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -9852,14 +10096,14 @@
         <v>13</v>
       </c>
       <c r="B15" s="5" t="s">
-        <v>623</v>
+        <v>628</v>
       </c>
       <c r="C15" s="5" t="s">
-        <v>624</v>
+        <v>629</v>
       </c>
       <c r="D15" s="5"/>
       <c r="E15" s="5" t="s">
-        <v>625</v>
+        <v>630</v>
       </c>
     </row>
     <row r="16" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -9867,14 +10111,14 @@
         <v>14</v>
       </c>
       <c r="B16" s="5" t="s">
-        <v>626</v>
+        <v>631</v>
       </c>
       <c r="C16" s="5" t="s">
-        <v>627</v>
+        <v>632</v>
       </c>
       <c r="D16" s="5"/>
       <c r="E16" s="5" t="s">
-        <v>628</v>
+        <v>633</v>
       </c>
     </row>
     <row r="17" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -9882,14 +10126,14 @@
         <v>15</v>
       </c>
       <c r="B17" s="5" t="s">
-        <v>629</v>
+        <v>634</v>
       </c>
       <c r="C17" s="5" t="s">
-        <v>630</v>
+        <v>635</v>
       </c>
       <c r="D17" s="5"/>
       <c r="E17" s="5" t="s">
-        <v>631</v>
+        <v>636</v>
       </c>
     </row>
     <row r="18" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -9897,14 +10141,14 @@
         <v>16</v>
       </c>
       <c r="B18" s="5" t="s">
-        <v>632</v>
+        <v>637</v>
       </c>
       <c r="C18" s="5" t="s">
-        <v>633</v>
+        <v>638</v>
       </c>
       <c r="D18" s="5"/>
       <c r="E18" s="5" t="s">
-        <v>634</v>
+        <v>639</v>
       </c>
     </row>
     <row r="19" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -9912,14 +10156,14 @@
         <v>17</v>
       </c>
       <c r="B19" s="5" t="s">
-        <v>635</v>
+        <v>640</v>
       </c>
       <c r="C19" s="5" t="s">
-        <v>636</v>
+        <v>641</v>
       </c>
       <c r="D19" s="5"/>
       <c r="E19" s="5" t="s">
-        <v>637</v>
+        <v>642</v>
       </c>
     </row>
     <row r="20" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -9927,14 +10171,14 @@
         <v>18</v>
       </c>
       <c r="B20" s="5" t="s">
-        <v>638</v>
+        <v>643</v>
       </c>
       <c r="C20" s="5" t="s">
-        <v>639</v>
+        <v>644</v>
       </c>
       <c r="D20" s="5"/>
       <c r="E20" s="5" t="s">
-        <v>640</v>
+        <v>645</v>
       </c>
     </row>
     <row r="21" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -9942,14 +10186,14 @@
         <v>19</v>
       </c>
       <c r="B21" s="5" t="s">
-        <v>641</v>
+        <v>646</v>
       </c>
       <c r="C21" s="5" t="s">
-        <v>642</v>
+        <v>647</v>
       </c>
       <c r="D21" s="5"/>
       <c r="E21" s="5" t="s">
-        <v>643</v>
+        <v>648</v>
       </c>
     </row>
     <row r="22" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -9957,14 +10201,14 @@
         <v>20</v>
       </c>
       <c r="B22" s="5" t="s">
-        <v>644</v>
+        <v>649</v>
       </c>
       <c r="C22" s="5" t="s">
-        <v>645</v>
+        <v>650</v>
       </c>
       <c r="D22" s="5"/>
       <c r="E22" s="5" t="s">
-        <v>646</v>
+        <v>651</v>
       </c>
     </row>
     <row r="23" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -9972,14 +10216,14 @@
         <v>21</v>
       </c>
       <c r="B23" s="5" t="s">
-        <v>647</v>
+        <v>652</v>
       </c>
       <c r="C23" s="5" t="s">
-        <v>648</v>
+        <v>653</v>
       </c>
       <c r="D23" s="5"/>
       <c r="E23" s="5" t="s">
-        <v>649</v>
+        <v>654</v>
       </c>
     </row>
     <row r="24" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -9987,14 +10231,14 @@
         <v>22</v>
       </c>
       <c r="B24" s="5" t="s">
-        <v>650</v>
+        <v>655</v>
       </c>
       <c r="C24" s="5" t="s">
-        <v>651</v>
+        <v>656</v>
       </c>
       <c r="D24" s="5"/>
       <c r="E24" s="5" t="s">
-        <v>652</v>
+        <v>657</v>
       </c>
     </row>
     <row r="25" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -10002,14 +10246,14 @@
         <v>23</v>
       </c>
       <c r="B25" s="5" t="s">
-        <v>653</v>
+        <v>658</v>
       </c>
       <c r="C25" s="5" t="s">
-        <v>654</v>
+        <v>659</v>
       </c>
       <c r="D25" s="5"/>
       <c r="E25" s="5" t="s">
-        <v>655</v>
+        <v>660</v>
       </c>
     </row>
     <row r="26" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -10017,14 +10261,14 @@
         <v>24</v>
       </c>
       <c r="B26" s="5" t="s">
-        <v>656</v>
+        <v>661</v>
       </c>
       <c r="C26" s="5" t="s">
-        <v>657</v>
+        <v>662</v>
       </c>
       <c r="D26" s="5"/>
       <c r="E26" s="5" t="s">
-        <v>658</v>
+        <v>663</v>
       </c>
     </row>
     <row r="27" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -10032,14 +10276,14 @@
         <v>25</v>
       </c>
       <c r="B27" s="5" t="s">
-        <v>659</v>
+        <v>664</v>
       </c>
       <c r="C27" s="5" t="s">
-        <v>660</v>
+        <v>665</v>
       </c>
       <c r="D27" s="5"/>
       <c r="E27" s="5" t="s">
-        <v>661</v>
+        <v>666</v>
       </c>
     </row>
     <row r="28" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -10047,14 +10291,14 @@
         <v>26</v>
       </c>
       <c r="B28" s="5" t="s">
-        <v>662</v>
+        <v>667</v>
       </c>
       <c r="C28" s="5" t="s">
-        <v>663</v>
+        <v>668</v>
       </c>
       <c r="D28" s="5"/>
       <c r="E28" s="5" t="s">
-        <v>664</v>
+        <v>669</v>
       </c>
     </row>
     <row r="29" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -10062,14 +10306,14 @@
         <v>27</v>
       </c>
       <c r="B29" s="5" t="s">
-        <v>665</v>
+        <v>670</v>
       </c>
       <c r="C29" s="5" t="s">
-        <v>666</v>
+        <v>671</v>
       </c>
       <c r="D29" s="5"/>
       <c r="E29" s="5" t="s">
-        <v>667</v>
+        <v>672</v>
       </c>
     </row>
     <row r="30" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -10077,14 +10321,14 @@
         <v>28</v>
       </c>
       <c r="B30" s="5" t="s">
-        <v>668</v>
+        <v>673</v>
       </c>
       <c r="C30" s="5" t="s">
-        <v>669</v>
+        <v>674</v>
       </c>
       <c r="D30" s="5"/>
       <c r="E30" s="5" t="s">
-        <v>670</v>
+        <v>675</v>
       </c>
     </row>
     <row r="31" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -10092,14 +10336,14 @@
         <v>29</v>
       </c>
       <c r="B31" s="5" t="s">
-        <v>671</v>
+        <v>676</v>
       </c>
       <c r="C31" s="5" t="s">
-        <v>672</v>
+        <v>677</v>
       </c>
       <c r="D31" s="5"/>
       <c r="E31" s="5" t="s">
-        <v>673</v>
+        <v>678</v>
       </c>
     </row>
     <row r="32" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -10107,14 +10351,14 @@
         <v>30</v>
       </c>
       <c r="B32" s="5" t="s">
-        <v>617</v>
+        <v>622</v>
       </c>
       <c r="C32" s="5" t="s">
-        <v>674</v>
+        <v>679</v>
       </c>
       <c r="D32" s="5"/>
       <c r="E32" s="5" t="s">
-        <v>675</v>
+        <v>680</v>
       </c>
     </row>
     <row r="33" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -10122,14 +10366,14 @@
         <v>31</v>
       </c>
       <c r="B33" s="5" t="s">
-        <v>676</v>
+        <v>681</v>
       </c>
       <c r="C33" s="5" t="s">
-        <v>677</v>
+        <v>682</v>
       </c>
       <c r="D33" s="5"/>
       <c r="E33" s="5" t="s">
-        <v>678</v>
+        <v>683</v>
       </c>
     </row>
     <row r="34" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -10137,14 +10381,14 @@
         <v>32</v>
       </c>
       <c r="B34" s="5" t="s">
-        <v>635</v>
+        <v>640</v>
       </c>
       <c r="C34" s="5" t="s">
-        <v>679</v>
+        <v>684</v>
       </c>
       <c r="D34" s="5"/>
       <c r="E34" s="5" t="s">
-        <v>680</v>
+        <v>685</v>
       </c>
     </row>
     <row r="35" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -10152,14 +10396,14 @@
         <v>33</v>
       </c>
       <c r="B35" s="5" t="s">
-        <v>681</v>
+        <v>686</v>
       </c>
       <c r="C35" s="5" t="s">
-        <v>682</v>
+        <v>687</v>
       </c>
       <c r="D35" s="5"/>
       <c r="E35" s="5" t="s">
-        <v>683</v>
+        <v>688</v>
       </c>
     </row>
     <row r="36" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -10167,14 +10411,14 @@
         <v>34</v>
       </c>
       <c r="B36" s="5" t="s">
-        <v>684</v>
+        <v>689</v>
       </c>
       <c r="C36" s="5" t="s">
-        <v>685</v>
+        <v>690</v>
       </c>
       <c r="D36" s="5"/>
       <c r="E36" s="5" t="s">
-        <v>686</v>
+        <v>691</v>
       </c>
     </row>
     <row r="37" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -10182,14 +10426,14 @@
         <v>35</v>
       </c>
       <c r="B37" s="5" t="s">
-        <v>687</v>
+        <v>692</v>
       </c>
       <c r="C37" s="5" t="s">
-        <v>688</v>
+        <v>693</v>
       </c>
       <c r="D37" s="5"/>
       <c r="E37" s="5" t="s">
-        <v>689</v>
+        <v>694</v>
       </c>
     </row>
     <row r="38" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -10197,14 +10441,14 @@
         <v>36</v>
       </c>
       <c r="B38" s="5" t="s">
-        <v>635</v>
+        <v>640</v>
       </c>
       <c r="C38" s="5" t="s">
-        <v>690</v>
+        <v>695</v>
       </c>
       <c r="D38" s="5"/>
       <c r="E38" s="5" t="s">
-        <v>691</v>
+        <v>696</v>
       </c>
     </row>
     <row r="39" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -10212,14 +10456,14 @@
         <v>37</v>
       </c>
       <c r="B39" s="5" t="s">
-        <v>692</v>
+        <v>697</v>
       </c>
       <c r="C39" s="5" t="s">
-        <v>693</v>
+        <v>698</v>
       </c>
       <c r="D39" s="5"/>
       <c r="E39" s="5" t="s">
-        <v>694</v>
+        <v>699</v>
       </c>
     </row>
     <row r="40" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -10227,14 +10471,14 @@
         <v>38</v>
       </c>
       <c r="B40" s="5" t="s">
-        <v>695</v>
+        <v>700</v>
       </c>
       <c r="C40" s="5" t="s">
-        <v>696</v>
+        <v>701</v>
       </c>
       <c r="D40" s="5"/>
       <c r="E40" s="5" t="s">
-        <v>697</v>
+        <v>702</v>
       </c>
     </row>
     <row r="41" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -10242,10 +10486,10 @@
         <v>39</v>
       </c>
       <c r="B41" s="5" t="s">
-        <v>698</v>
+        <v>703</v>
       </c>
       <c r="C41" s="5" t="s">
-        <v>699</v>
+        <v>704</v>
       </c>
       <c r="D41" s="5"/>
       <c r="E41" s="5" t="s">
@@ -10257,14 +10501,14 @@
         <v>40</v>
       </c>
       <c r="B42" s="5" t="s">
-        <v>700</v>
+        <v>705</v>
       </c>
       <c r="C42" s="5" t="s">
-        <v>701</v>
+        <v>706</v>
       </c>
       <c r="D42" s="5"/>
       <c r="E42" s="5" t="s">
-        <v>702</v>
+        <v>707</v>
       </c>
     </row>
     <row r="43" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -10272,14 +10516,14 @@
         <v>41</v>
       </c>
       <c r="B43" s="5" t="s">
-        <v>703</v>
+        <v>708</v>
       </c>
       <c r="C43" s="5" t="s">
-        <v>704</v>
+        <v>709</v>
       </c>
       <c r="D43" s="5"/>
       <c r="E43" s="5" t="s">
-        <v>705</v>
+        <v>710</v>
       </c>
     </row>
     <row r="44" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -10287,14 +10531,14 @@
         <v>42</v>
       </c>
       <c r="B44" s="5" t="s">
-        <v>706</v>
+        <v>711</v>
       </c>
       <c r="C44" s="5" t="s">
-        <v>707</v>
+        <v>712</v>
       </c>
       <c r="D44" s="5"/>
       <c r="E44" s="5" t="s">
-        <v>708</v>
+        <v>713</v>
       </c>
     </row>
     <row r="45" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -10302,14 +10546,14 @@
         <v>43</v>
       </c>
       <c r="B45" s="5" t="s">
-        <v>709</v>
+        <v>714</v>
       </c>
       <c r="C45" s="5" t="s">
-        <v>710</v>
+        <v>715</v>
       </c>
       <c r="D45" s="5"/>
       <c r="E45" s="5" t="s">
-        <v>711</v>
+        <v>716</v>
       </c>
     </row>
     <row r="46" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -10317,14 +10561,14 @@
         <v>44</v>
       </c>
       <c r="B46" s="5" t="s">
-        <v>712</v>
+        <v>717</v>
       </c>
       <c r="C46" s="5" t="s">
-        <v>713</v>
+        <v>718</v>
       </c>
       <c r="D46" s="5"/>
       <c r="E46" s="5" t="s">
-        <v>714</v>
+        <v>719</v>
       </c>
     </row>
     <row r="47" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -10332,14 +10576,14 @@
         <v>45</v>
       </c>
       <c r="B47" s="5" t="s">
-        <v>715</v>
+        <v>720</v>
       </c>
       <c r="C47" s="5" t="s">
-        <v>716</v>
+        <v>721</v>
       </c>
       <c r="D47" s="5"/>
       <c r="E47" s="5" t="s">
-        <v>717</v>
+        <v>722</v>
       </c>
     </row>
     <row r="48" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -10347,14 +10591,14 @@
         <v>46</v>
       </c>
       <c r="B48" s="5" t="s">
-        <v>718</v>
+        <v>723</v>
       </c>
       <c r="C48" s="5" t="s">
-        <v>719</v>
+        <v>724</v>
       </c>
       <c r="D48" s="5"/>
       <c r="E48" s="5" t="s">
-        <v>720</v>
+        <v>725</v>
       </c>
     </row>
     <row r="49" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -10362,14 +10606,14 @@
         <v>47</v>
       </c>
       <c r="B49" s="5" t="s">
-        <v>721</v>
+        <v>726</v>
       </c>
       <c r="C49" s="5" t="s">
-        <v>722</v>
+        <v>727</v>
       </c>
       <c r="D49" s="5"/>
       <c r="E49" s="5" t="s">
-        <v>723</v>
+        <v>728</v>
       </c>
     </row>
     <row r="50" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -10377,14 +10621,14 @@
         <v>48</v>
       </c>
       <c r="B50" s="5" t="s">
-        <v>724</v>
+        <v>729</v>
       </c>
       <c r="C50" s="5" t="s">
-        <v>725</v>
+        <v>730</v>
       </c>
       <c r="D50" s="5"/>
       <c r="E50" s="5" t="s">
-        <v>726</v>
+        <v>731</v>
       </c>
     </row>
     <row r="51" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -10392,14 +10636,14 @@
         <v>49</v>
       </c>
       <c r="B51" s="5" t="s">
-        <v>727</v>
+        <v>732</v>
       </c>
       <c r="C51" s="5" t="s">
-        <v>728</v>
+        <v>733</v>
       </c>
       <c r="D51" s="5"/>
       <c r="E51" s="5" t="s">
-        <v>729</v>
+        <v>734</v>
       </c>
     </row>
     <row r="52" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -10407,14 +10651,14 @@
         <v>50</v>
       </c>
       <c r="B52" s="5" t="s">
-        <v>730</v>
+        <v>735</v>
       </c>
       <c r="C52" s="5" t="s">
-        <v>731</v>
+        <v>736</v>
       </c>
       <c r="D52" s="5"/>
       <c r="E52" s="5" t="s">
-        <v>732</v>
+        <v>737</v>
       </c>
     </row>
     <row r="53" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -10422,14 +10666,14 @@
         <v>51</v>
       </c>
       <c r="B53" s="5" t="s">
-        <v>733</v>
+        <v>738</v>
       </c>
       <c r="C53" s="5" t="s">
-        <v>734</v>
+        <v>739</v>
       </c>
       <c r="D53" s="5"/>
       <c r="E53" s="5" t="s">
-        <v>735</v>
+        <v>740</v>
       </c>
     </row>
     <row r="54" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -10437,14 +10681,14 @@
         <v>52</v>
       </c>
       <c r="B54" s="5" t="s">
-        <v>635</v>
+        <v>640</v>
       </c>
       <c r="C54" s="5" t="s">
-        <v>736</v>
+        <v>741</v>
       </c>
       <c r="D54" s="5"/>
       <c r="E54" s="5" t="s">
-        <v>737</v>
+        <v>742</v>
       </c>
     </row>
     <row r="55" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -10452,14 +10696,14 @@
         <v>53</v>
       </c>
       <c r="B55" s="5" t="s">
-        <v>738</v>
+        <v>743</v>
       </c>
       <c r="C55" s="5" t="s">
-        <v>739</v>
+        <v>744</v>
       </c>
       <c r="D55" s="5"/>
       <c r="E55" s="5" t="s">
-        <v>740</v>
+        <v>745</v>
       </c>
     </row>
     <row r="56" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -10467,14 +10711,14 @@
         <v>54</v>
       </c>
       <c r="B56" s="5" t="s">
-        <v>741</v>
+        <v>746</v>
       </c>
       <c r="C56" s="5" t="s">
-        <v>742</v>
+        <v>747</v>
       </c>
       <c r="D56" s="5"/>
       <c r="E56" s="5" t="s">
-        <v>743</v>
+        <v>748</v>
       </c>
     </row>
     <row r="57" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -10482,14 +10726,14 @@
         <v>55</v>
       </c>
       <c r="B57" s="5" t="s">
-        <v>744</v>
+        <v>749</v>
       </c>
       <c r="C57" s="5" t="s">
-        <v>745</v>
+        <v>750</v>
       </c>
       <c r="D57" s="5"/>
       <c r="E57" s="5" t="s">
-        <v>746</v>
+        <v>751</v>
       </c>
     </row>
     <row r="58" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -10497,14 +10741,14 @@
         <v>56</v>
       </c>
       <c r="B58" s="5" t="s">
-        <v>747</v>
+        <v>752</v>
       </c>
       <c r="C58" s="5" t="s">
-        <v>748</v>
+        <v>753</v>
       </c>
       <c r="D58" s="5"/>
       <c r="E58" s="5" t="s">
-        <v>749</v>
+        <v>754</v>
       </c>
     </row>
     <row r="59" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -10512,14 +10756,14 @@
         <v>57</v>
       </c>
       <c r="B59" s="5" t="s">
-        <v>750</v>
+        <v>755</v>
       </c>
       <c r="C59" s="5" t="s">
-        <v>751</v>
+        <v>756</v>
       </c>
       <c r="D59" s="5"/>
       <c r="E59" s="5" t="s">
-        <v>752</v>
+        <v>757</v>
       </c>
     </row>
     <row r="60" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -10527,14 +10771,14 @@
         <v>58</v>
       </c>
       <c r="B60" s="5" t="s">
-        <v>753</v>
+        <v>758</v>
       </c>
       <c r="C60" s="5" t="s">
-        <v>754</v>
+        <v>759</v>
       </c>
       <c r="D60" s="5"/>
       <c r="E60" s="5" t="s">
-        <v>755</v>
+        <v>760</v>
       </c>
     </row>
     <row r="61" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -10542,14 +10786,14 @@
         <v>59</v>
       </c>
       <c r="B61" s="5" t="s">
-        <v>756</v>
+        <v>761</v>
       </c>
       <c r="C61" s="5" t="s">
-        <v>757</v>
+        <v>762</v>
       </c>
       <c r="D61" s="5"/>
       <c r="E61" s="5" t="s">
-        <v>758</v>
+        <v>763</v>
       </c>
     </row>
     <row r="62" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -10557,14 +10801,14 @@
         <v>60</v>
       </c>
       <c r="B62" s="5" t="s">
-        <v>759</v>
+        <v>764</v>
       </c>
       <c r="C62" s="5" t="s">
-        <v>760</v>
+        <v>765</v>
       </c>
       <c r="D62" s="5"/>
       <c r="E62" s="5" t="s">
-        <v>761</v>
+        <v>766</v>
       </c>
     </row>
     <row r="63" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -10572,14 +10816,14 @@
         <v>61</v>
       </c>
       <c r="B63" s="5" t="s">
-        <v>762</v>
+        <v>767</v>
       </c>
       <c r="C63" s="5" t="s">
-        <v>763</v>
+        <v>768</v>
       </c>
       <c r="D63" s="5"/>
       <c r="E63" s="5" t="s">
-        <v>764</v>
+        <v>769</v>
       </c>
     </row>
     <row r="64" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -10587,14 +10831,14 @@
         <v>62</v>
       </c>
       <c r="B64" s="5" t="s">
-        <v>765</v>
+        <v>770</v>
       </c>
       <c r="C64" s="5" t="s">
-        <v>766</v>
+        <v>771</v>
       </c>
       <c r="D64" s="5"/>
       <c r="E64" s="5" t="s">
-        <v>767</v>
+        <v>772</v>
       </c>
     </row>
     <row r="65" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -10602,14 +10846,14 @@
         <v>63</v>
       </c>
       <c r="B65" s="5" t="s">
-        <v>768</v>
+        <v>773</v>
       </c>
       <c r="C65" s="5" t="s">
-        <v>769</v>
+        <v>774</v>
       </c>
       <c r="D65" s="5"/>
       <c r="E65" s="5" t="s">
-        <v>770</v>
+        <v>775</v>
       </c>
     </row>
     <row r="66" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -10617,14 +10861,14 @@
         <v>64</v>
       </c>
       <c r="B66" s="5" t="s">
-        <v>771</v>
+        <v>776</v>
       </c>
       <c r="C66" s="5" t="s">
-        <v>772</v>
+        <v>777</v>
       </c>
       <c r="D66" s="5"/>
       <c r="E66" s="5" t="s">
-        <v>773</v>
+        <v>778</v>
       </c>
     </row>
     <row r="67" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -10632,14 +10876,14 @@
         <v>65</v>
       </c>
       <c r="B67" s="5" t="s">
-        <v>774</v>
+        <v>779</v>
       </c>
       <c r="C67" s="5" t="s">
-        <v>775</v>
+        <v>780</v>
       </c>
       <c r="D67" s="5"/>
       <c r="E67" s="5" t="s">
-        <v>776</v>
+        <v>781</v>
       </c>
     </row>
     <row r="68" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -10647,14 +10891,14 @@
         <v>66</v>
       </c>
       <c r="B68" s="5" t="s">
-        <v>777</v>
+        <v>782</v>
       </c>
       <c r="C68" s="5" t="s">
-        <v>778</v>
+        <v>783</v>
       </c>
       <c r="D68" s="5"/>
       <c r="E68" s="5" t="s">
-        <v>779</v>
+        <v>784</v>
       </c>
     </row>
     <row r="69" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -10662,14 +10906,14 @@
         <v>67</v>
       </c>
       <c r="B69" s="5" t="s">
-        <v>780</v>
+        <v>785</v>
       </c>
       <c r="C69" s="5" t="s">
-        <v>781</v>
+        <v>786</v>
       </c>
       <c r="D69" s="5"/>
       <c r="E69" s="5" t="s">
-        <v>782</v>
+        <v>787</v>
       </c>
     </row>
     <row r="70" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -10677,14 +10921,14 @@
         <v>68</v>
       </c>
       <c r="B70" s="5" t="s">
-        <v>783</v>
+        <v>788</v>
       </c>
       <c r="C70" s="5" t="s">
-        <v>784</v>
+        <v>789</v>
       </c>
       <c r="D70" s="5"/>
       <c r="E70" s="5" t="s">
-        <v>785</v>
+        <v>790</v>
       </c>
     </row>
     <row r="71" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -10692,14 +10936,14 @@
         <v>69</v>
       </c>
       <c r="B71" s="5" t="s">
-        <v>786</v>
+        <v>791</v>
       </c>
       <c r="C71" s="5" t="s">
-        <v>787</v>
+        <v>792</v>
       </c>
       <c r="D71" s="5"/>
       <c r="E71" s="5" t="s">
-        <v>788</v>
+        <v>793</v>
       </c>
     </row>
     <row r="72" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -10707,14 +10951,14 @@
         <v>70</v>
       </c>
       <c r="B72" s="5" t="s">
-        <v>789</v>
+        <v>794</v>
       </c>
       <c r="C72" s="5" t="s">
-        <v>790</v>
+        <v>795</v>
       </c>
       <c r="D72" s="5"/>
       <c r="E72" s="5" t="s">
-        <v>791</v>
+        <v>796</v>
       </c>
     </row>
     <row r="73" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -10722,14 +10966,14 @@
         <v>71</v>
       </c>
       <c r="B73" s="5" t="s">
-        <v>792</v>
+        <v>797</v>
       </c>
       <c r="C73" s="5" t="s">
-        <v>793</v>
+        <v>798</v>
       </c>
       <c r="D73" s="5"/>
       <c r="E73" s="5" t="s">
-        <v>794</v>
+        <v>799</v>
       </c>
     </row>
     <row r="74" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -10737,14 +10981,14 @@
         <v>72</v>
       </c>
       <c r="B74" s="5" t="s">
-        <v>795</v>
+        <v>800</v>
       </c>
       <c r="C74" s="5" t="s">
-        <v>796</v>
+        <v>801</v>
       </c>
       <c r="D74" s="5"/>
       <c r="E74" s="5" t="s">
-        <v>797</v>
+        <v>802</v>
       </c>
     </row>
     <row r="75" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -10752,14 +10996,14 @@
         <v>73</v>
       </c>
       <c r="B75" s="5" t="s">
-        <v>635</v>
+        <v>640</v>
       </c>
       <c r="C75" s="5" t="s">
-        <v>798</v>
+        <v>803</v>
       </c>
       <c r="D75" s="5"/>
       <c r="E75" s="5" t="s">
-        <v>799</v>
+        <v>804</v>
       </c>
     </row>
     <row r="76" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -10767,14 +11011,14 @@
         <v>74</v>
       </c>
       <c r="B76" s="5" t="s">
-        <v>800</v>
+        <v>805</v>
       </c>
       <c r="C76" s="5" t="s">
-        <v>801</v>
+        <v>806</v>
       </c>
       <c r="D76" s="5"/>
       <c r="E76" s="5" t="s">
-        <v>802</v>
+        <v>807</v>
       </c>
     </row>
     <row r="77" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -10782,14 +11026,14 @@
         <v>75</v>
       </c>
       <c r="B77" s="5" t="s">
-        <v>635</v>
+        <v>640</v>
       </c>
       <c r="C77" s="5" t="s">
-        <v>803</v>
+        <v>808</v>
       </c>
       <c r="D77" s="5"/>
       <c r="E77" s="5" t="s">
-        <v>804</v>
+        <v>809</v>
       </c>
     </row>
     <row r="78" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -10797,14 +11041,14 @@
         <v>76</v>
       </c>
       <c r="B78" s="5" t="s">
-        <v>805</v>
+        <v>810</v>
       </c>
       <c r="C78" s="5" t="s">
-        <v>806</v>
+        <v>811</v>
       </c>
       <c r="D78" s="5"/>
       <c r="E78" s="5" t="s">
-        <v>807</v>
+        <v>812</v>
       </c>
     </row>
     <row r="79" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -10812,14 +11056,14 @@
         <v>77</v>
       </c>
       <c r="B79" s="5" t="s">
-        <v>808</v>
+        <v>813</v>
       </c>
       <c r="C79" s="5" t="s">
-        <v>809</v>
+        <v>814</v>
       </c>
       <c r="D79" s="5"/>
       <c r="E79" s="5" t="s">
-        <v>810</v>
+        <v>815</v>
       </c>
     </row>
     <row r="80" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -10827,14 +11071,14 @@
         <v>78</v>
       </c>
       <c r="B80" s="5" t="s">
-        <v>733</v>
+        <v>738</v>
       </c>
       <c r="C80" s="5" t="s">
-        <v>811</v>
+        <v>816</v>
       </c>
       <c r="D80" s="5"/>
       <c r="E80" s="5" t="s">
-        <v>812</v>
+        <v>817</v>
       </c>
     </row>
     <row r="81" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -10842,14 +11086,14 @@
         <v>79</v>
       </c>
       <c r="B81" s="5" t="s">
-        <v>605</v>
+        <v>610</v>
       </c>
       <c r="C81" s="5" t="s">
-        <v>813</v>
+        <v>818</v>
       </c>
       <c r="D81" s="5"/>
       <c r="E81" s="5" t="s">
-        <v>814</v>
+        <v>819</v>
       </c>
     </row>
     <row r="82" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -10857,16 +11101,16 @@
         <v>80</v>
       </c>
       <c r="B82" s="5" t="s">
-        <v>815</v>
+        <v>820</v>
       </c>
       <c r="C82" s="5" t="s">
-        <v>816</v>
+        <v>821</v>
       </c>
       <c r="D82" s="6" t="s">
-        <v>817</v>
+        <v>822</v>
       </c>
       <c r="E82" s="5" t="s">
-        <v>818</v>
+        <v>823</v>
       </c>
     </row>
     <row r="83" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -10874,16 +11118,16 @@
         <v>81</v>
       </c>
       <c r="B83" s="5" t="s">
-        <v>819</v>
+        <v>824</v>
       </c>
       <c r="C83" s="5" t="s">
-        <v>820</v>
+        <v>825</v>
       </c>
       <c r="D83" s="6" t="s">
-        <v>821</v>
+        <v>826</v>
       </c>
       <c r="E83" s="5" t="s">
-        <v>822</v>
+        <v>827</v>
       </c>
     </row>
     <row r="84" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -10891,13 +11135,13 @@
         <v>82</v>
       </c>
       <c r="B84" s="5" t="s">
-        <v>823</v>
+        <v>828</v>
       </c>
       <c r="C84" s="5" t="s">
-        <v>824</v>
+        <v>829</v>
       </c>
       <c r="D84" s="6" t="s">
-        <v>825</v>
+        <v>830</v>
       </c>
       <c r="E84" s="5" t="s">
         <v>297</v>
@@ -10908,13 +11152,13 @@
         <v>83</v>
       </c>
       <c r="B85" s="5" t="s">
-        <v>826</v>
+        <v>831</v>
       </c>
       <c r="C85" s="5" t="s">
-        <v>827</v>
+        <v>832</v>
       </c>
       <c r="D85" s="6" t="s">
-        <v>828</v>
+        <v>833</v>
       </c>
       <c r="E85" s="5" t="s">
         <v>300</v>
@@ -10925,16 +11169,16 @@
         <v>84</v>
       </c>
       <c r="B86" s="5" t="s">
-        <v>829</v>
+        <v>834</v>
       </c>
       <c r="C86" s="5" t="s">
-        <v>830</v>
+        <v>835</v>
       </c>
       <c r="D86" s="6" t="s">
-        <v>831</v>
+        <v>836</v>
       </c>
       <c r="E86" s="5" t="s">
-        <v>832</v>
+        <v>837</v>
       </c>
     </row>
     <row r="87" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -10942,16 +11186,16 @@
         <v>85</v>
       </c>
       <c r="B87" s="5" t="s">
-        <v>833</v>
+        <v>838</v>
       </c>
       <c r="C87" s="5" t="s">
-        <v>834</v>
+        <v>839</v>
       </c>
       <c r="D87" s="6" t="s">
-        <v>835</v>
+        <v>840</v>
       </c>
       <c r="E87" s="5" t="s">
-        <v>836</v>
+        <v>841</v>
       </c>
     </row>
     <row r="88" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -10959,16 +11203,16 @@
         <v>86</v>
       </c>
       <c r="B88" s="5" t="s">
-        <v>837</v>
+        <v>842</v>
       </c>
       <c r="C88" s="5" t="s">
-        <v>838</v>
+        <v>843</v>
       </c>
       <c r="D88" s="6" t="s">
-        <v>839</v>
+        <v>844</v>
       </c>
       <c r="E88" s="5" t="s">
-        <v>836</v>
+        <v>841</v>
       </c>
     </row>
     <row r="89" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -10976,16 +11220,16 @@
         <v>87</v>
       </c>
       <c r="B89" s="5" t="s">
-        <v>840</v>
+        <v>845</v>
       </c>
       <c r="C89" s="5" t="s">
+        <v>846</v>
+      </c>
+      <c r="D89" s="6" t="s">
+        <v>847</v>
+      </c>
+      <c r="E89" s="5" t="s">
         <v>841</v>
-      </c>
-      <c r="D89" s="6" t="s">
-        <v>842</v>
-      </c>
-      <c r="E89" s="5" t="s">
-        <v>836</v>
       </c>
     </row>
     <row r="90" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -10993,16 +11237,16 @@
         <v>88</v>
       </c>
       <c r="B90" s="5" t="s">
-        <v>843</v>
+        <v>848</v>
       </c>
       <c r="C90" s="5" t="s">
-        <v>844</v>
+        <v>849</v>
       </c>
       <c r="D90" s="6" t="s">
-        <v>845</v>
+        <v>850</v>
       </c>
       <c r="E90" s="5" t="s">
-        <v>846</v>
+        <v>851</v>
       </c>
     </row>
     <row r="91" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -11010,16 +11254,16 @@
         <v>89</v>
       </c>
       <c r="B91" s="5" t="s">
-        <v>847</v>
+        <v>852</v>
       </c>
       <c r="C91" s="5" t="s">
-        <v>848</v>
+        <v>853</v>
       </c>
       <c r="D91" s="6" t="s">
-        <v>849</v>
+        <v>854</v>
       </c>
       <c r="E91" s="5" t="s">
-        <v>846</v>
+        <v>851</v>
       </c>
     </row>
     <row r="92" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -11027,16 +11271,16 @@
         <v>90</v>
       </c>
       <c r="B92" s="5" t="s">
-        <v>837</v>
+        <v>842</v>
       </c>
       <c r="C92" s="5" t="s">
-        <v>850</v>
+        <v>855</v>
       </c>
       <c r="D92" s="6" t="s">
-        <v>851</v>
+        <v>856</v>
       </c>
       <c r="E92" s="5" t="s">
-        <v>852</v>
+        <v>857</v>
       </c>
     </row>
     <row r="93" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -11044,16 +11288,16 @@
         <v>91</v>
       </c>
       <c r="B93" s="5" t="s">
-        <v>853</v>
+        <v>858</v>
       </c>
       <c r="C93" s="5" t="s">
-        <v>854</v>
+        <v>859</v>
       </c>
       <c r="D93" s="6" t="s">
-        <v>855</v>
+        <v>860</v>
       </c>
       <c r="E93" s="5" t="s">
-        <v>852</v>
+        <v>857</v>
       </c>
     </row>
     <row r="94" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -11061,16 +11305,16 @@
         <v>92</v>
       </c>
       <c r="B94" s="5" t="s">
-        <v>856</v>
+        <v>861</v>
       </c>
       <c r="C94" s="5" t="s">
-        <v>857</v>
+        <v>862</v>
       </c>
       <c r="D94" s="6" t="s">
-        <v>858</v>
+        <v>863</v>
       </c>
       <c r="E94" s="5" t="s">
-        <v>859</v>
+        <v>864</v>
       </c>
     </row>
     <row r="95" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -11078,16 +11322,16 @@
         <v>93</v>
       </c>
       <c r="B95" s="5" t="s">
-        <v>698</v>
+        <v>703</v>
       </c>
       <c r="C95" s="5" t="s">
-        <v>860</v>
+        <v>865</v>
       </c>
       <c r="D95" s="6" t="s">
-        <v>861</v>
+        <v>866</v>
       </c>
       <c r="E95" s="5" t="s">
-        <v>862</v>
+        <v>867</v>
       </c>
     </row>
     <row r="96" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -11095,16 +11339,16 @@
         <v>94</v>
       </c>
       <c r="B96" s="5" t="s">
-        <v>843</v>
+        <v>848</v>
       </c>
       <c r="C96" s="5" t="s">
-        <v>863</v>
+        <v>868</v>
       </c>
       <c r="D96" s="6" t="s">
-        <v>864</v>
+        <v>869</v>
       </c>
       <c r="E96" s="5" t="s">
-        <v>862</v>
+        <v>867</v>
       </c>
     </row>
     <row r="97" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -11112,16 +11356,16 @@
         <v>95</v>
       </c>
       <c r="B97" s="5" t="s">
-        <v>865</v>
+        <v>870</v>
       </c>
       <c r="C97" s="5" t="s">
-        <v>866</v>
+        <v>871</v>
       </c>
       <c r="D97" s="6" t="s">
+        <v>872</v>
+      </c>
+      <c r="E97" s="5" t="s">
         <v>867</v>
-      </c>
-      <c r="E97" s="5" t="s">
-        <v>862</v>
       </c>
     </row>
     <row r="98" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -11129,16 +11373,16 @@
         <v>96</v>
       </c>
       <c r="B98" s="5" t="s">
-        <v>823</v>
+        <v>828</v>
       </c>
       <c r="C98" s="5" t="s">
-        <v>868</v>
+        <v>873</v>
       </c>
       <c r="D98" s="6" t="s">
-        <v>869</v>
+        <v>874</v>
       </c>
       <c r="E98" s="5" t="s">
-        <v>852</v>
+        <v>857</v>
       </c>
     </row>
     <row r="99" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -11146,16 +11390,16 @@
         <v>97</v>
       </c>
       <c r="B99" s="5" t="s">
-        <v>870</v>
+        <v>875</v>
       </c>
       <c r="C99" s="5" t="s">
-        <v>871</v>
+        <v>876</v>
       </c>
       <c r="D99" s="6" t="s">
-        <v>872</v>
+        <v>877</v>
       </c>
       <c r="E99" s="5" t="s">
-        <v>873</v>
+        <v>878</v>
       </c>
     </row>
     <row r="100" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -11163,16 +11407,16 @@
         <v>98</v>
       </c>
       <c r="B100" s="5" t="s">
-        <v>837</v>
+        <v>842</v>
       </c>
       <c r="C100" s="5" t="s">
-        <v>874</v>
+        <v>879</v>
       </c>
       <c r="D100" s="6" t="s">
-        <v>875</v>
+        <v>880</v>
       </c>
       <c r="E100" s="5" t="s">
-        <v>876</v>
+        <v>881</v>
       </c>
     </row>
     <row r="101" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -11180,16 +11424,16 @@
         <v>99</v>
       </c>
       <c r="B101" s="5" t="s">
-        <v>843</v>
+        <v>848</v>
       </c>
       <c r="C101" s="5" t="s">
-        <v>877</v>
+        <v>882</v>
       </c>
       <c r="D101" s="6" t="s">
-        <v>878</v>
+        <v>883</v>
       </c>
       <c r="E101" s="5" t="s">
-        <v>879</v>
+        <v>884</v>
       </c>
     </row>
     <row r="102" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -11197,16 +11441,16 @@
         <v>100</v>
       </c>
       <c r="B102" s="5" t="s">
-        <v>880</v>
+        <v>885</v>
       </c>
       <c r="C102" s="5" t="s">
-        <v>881</v>
+        <v>886</v>
       </c>
       <c r="D102" s="6" t="s">
-        <v>882</v>
+        <v>887</v>
       </c>
       <c r="E102" s="5" t="s">
-        <v>883</v>
+        <v>888</v>
       </c>
     </row>
     <row r="103" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -11214,16 +11458,16 @@
         <v>101</v>
       </c>
       <c r="B103" s="5" t="s">
-        <v>823</v>
+        <v>828</v>
       </c>
       <c r="C103" s="5" t="s">
-        <v>884</v>
+        <v>889</v>
       </c>
       <c r="D103" s="6" t="s">
-        <v>885</v>
+        <v>890</v>
       </c>
       <c r="E103" s="5" t="s">
-        <v>886</v>
+        <v>891</v>
       </c>
     </row>
     <row r="104" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -11231,13 +11475,13 @@
         <v>102</v>
       </c>
       <c r="B104" s="5" t="s">
-        <v>698</v>
+        <v>703</v>
       </c>
       <c r="C104" s="5" t="s">
-        <v>887</v>
+        <v>892</v>
       </c>
       <c r="D104" s="6" t="s">
-        <v>888</v>
+        <v>893</v>
       </c>
       <c r="E104" s="5" t="s">
         <v>352</v>
@@ -11248,16 +11492,16 @@
         <v>103</v>
       </c>
       <c r="B105" s="5" t="s">
-        <v>889</v>
+        <v>894</v>
       </c>
       <c r="C105" s="5" t="s">
-        <v>890</v>
+        <v>895</v>
       </c>
       <c r="D105" s="6" t="s">
-        <v>891</v>
+        <v>896</v>
       </c>
       <c r="E105" s="5" t="s">
-        <v>892</v>
+        <v>897</v>
       </c>
     </row>
     <row r="106" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -11265,16 +11509,16 @@
         <v>104</v>
       </c>
       <c r="B106" s="5" t="s">
-        <v>893</v>
+        <v>898</v>
       </c>
       <c r="C106" s="5" t="s">
-        <v>894</v>
+        <v>899</v>
       </c>
       <c r="D106" s="6" t="s">
-        <v>895</v>
+        <v>900</v>
       </c>
       <c r="E106" s="5" t="s">
-        <v>896</v>
+        <v>901</v>
       </c>
     </row>
     <row r="107" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -11282,16 +11526,16 @@
         <v>105</v>
       </c>
       <c r="B107" s="5" t="s">
-        <v>897</v>
+        <v>902</v>
       </c>
       <c r="C107" s="5" t="s">
-        <v>898</v>
+        <v>903</v>
       </c>
       <c r="D107" s="6" t="s">
-        <v>899</v>
+        <v>904</v>
       </c>
       <c r="E107" s="5" t="s">
-        <v>900</v>
+        <v>905</v>
       </c>
     </row>
     <row r="108" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -11299,16 +11543,16 @@
         <v>106</v>
       </c>
       <c r="B108" s="5" t="s">
-        <v>893</v>
+        <v>898</v>
       </c>
       <c r="C108" s="5" t="s">
-        <v>901</v>
+        <v>906</v>
       </c>
       <c r="D108" s="6" t="s">
-        <v>902</v>
+        <v>907</v>
       </c>
       <c r="E108" s="5" t="s">
-        <v>903</v>
+        <v>908</v>
       </c>
     </row>
     <row r="109" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -11316,13 +11560,13 @@
         <v>107</v>
       </c>
       <c r="B109" s="5" t="s">
-        <v>904</v>
+        <v>909</v>
       </c>
       <c r="C109" s="5" t="s">
-        <v>905</v>
+        <v>910</v>
       </c>
       <c r="D109" s="6" t="s">
-        <v>906</v>
+        <v>911</v>
       </c>
       <c r="E109" s="5" t="s">
         <v>368</v>
@@ -11333,13 +11577,13 @@
         <v>108</v>
       </c>
       <c r="B110" s="5" t="s">
-        <v>698</v>
+        <v>703</v>
       </c>
       <c r="C110" s="5" t="s">
-        <v>907</v>
+        <v>912</v>
       </c>
       <c r="D110" s="6" t="s">
-        <v>908</v>
+        <v>913</v>
       </c>
       <c r="E110" s="5" t="s">
         <v>368</v>
@@ -11350,16 +11594,16 @@
         <v>109</v>
       </c>
       <c r="B111" s="5" t="s">
-        <v>897</v>
+        <v>902</v>
       </c>
       <c r="C111" s="5" t="s">
-        <v>909</v>
+        <v>914</v>
       </c>
       <c r="D111" s="6" t="s">
-        <v>910</v>
+        <v>915</v>
       </c>
       <c r="E111" s="5" t="s">
-        <v>911</v>
+        <v>916</v>
       </c>
     </row>
     <row r="112" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -11367,16 +11611,16 @@
         <v>110</v>
       </c>
       <c r="B112" s="5" t="s">
-        <v>837</v>
+        <v>842</v>
       </c>
       <c r="C112" s="5" t="s">
-        <v>912</v>
+        <v>917</v>
       </c>
       <c r="D112" s="6" t="s">
-        <v>913</v>
+        <v>918</v>
       </c>
       <c r="E112" s="5" t="s">
-        <v>914</v>
+        <v>919</v>
       </c>
     </row>
     <row r="113" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -11384,13 +11628,13 @@
         <v>111</v>
       </c>
       <c r="B113" s="5" t="s">
-        <v>829</v>
+        <v>834</v>
       </c>
       <c r="C113" s="5" t="s">
-        <v>915</v>
+        <v>920</v>
       </c>
       <c r="D113" s="6" t="s">
-        <v>916</v>
+        <v>921</v>
       </c>
       <c r="E113" s="5" t="s">
         <v>382</v>
@@ -11401,16 +11645,16 @@
         <v>112</v>
       </c>
       <c r="B114" s="5" t="s">
-        <v>837</v>
+        <v>842</v>
       </c>
       <c r="C114" s="5" t="s">
-        <v>917</v>
+        <v>922</v>
       </c>
       <c r="D114" s="6" t="s">
-        <v>918</v>
+        <v>923</v>
       </c>
       <c r="E114" s="5" t="s">
-        <v>919</v>
+        <v>924</v>
       </c>
     </row>
     <row r="115" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -11418,16 +11662,16 @@
         <v>113</v>
       </c>
       <c r="B115" s="5" t="s">
-        <v>920</v>
+        <v>925</v>
       </c>
       <c r="C115" s="5" t="s">
-        <v>921</v>
+        <v>926</v>
       </c>
       <c r="D115" s="6" t="s">
-        <v>922</v>
+        <v>927</v>
       </c>
       <c r="E115" s="5" t="s">
-        <v>923</v>
+        <v>928</v>
       </c>
     </row>
     <row r="116" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -11435,16 +11679,16 @@
         <v>114</v>
       </c>
       <c r="B116" s="5" t="s">
-        <v>843</v>
+        <v>848</v>
       </c>
       <c r="C116" s="5" t="s">
-        <v>924</v>
+        <v>929</v>
       </c>
       <c r="D116" s="6" t="s">
-        <v>925</v>
+        <v>930</v>
       </c>
       <c r="E116" s="5" t="s">
-        <v>923</v>
+        <v>928</v>
       </c>
     </row>
     <row r="117" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -11452,16 +11696,16 @@
         <v>115</v>
       </c>
       <c r="B117" s="5" t="s">
-        <v>926</v>
+        <v>931</v>
       </c>
       <c r="C117" s="5" t="s">
-        <v>927</v>
+        <v>932</v>
       </c>
       <c r="D117" s="6" t="s">
-        <v>928</v>
+        <v>933</v>
       </c>
       <c r="E117" s="5" t="s">
-        <v>929</v>
+        <v>934</v>
       </c>
     </row>
     <row r="118" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -11469,13 +11713,13 @@
         <v>116</v>
       </c>
       <c r="B118" s="5" t="s">
-        <v>843</v>
+        <v>848</v>
       </c>
       <c r="C118" s="5" t="s">
-        <v>930</v>
+        <v>935</v>
       </c>
       <c r="D118" s="6" t="s">
-        <v>931</v>
+        <v>936</v>
       </c>
       <c r="E118" s="5" t="s">
         <v>396</v>
@@ -11486,16 +11730,16 @@
         <v>117</v>
       </c>
       <c r="B119" s="5" t="s">
-        <v>932</v>
+        <v>937</v>
       </c>
       <c r="C119" s="5" t="s">
-        <v>933</v>
+        <v>938</v>
       </c>
       <c r="D119" s="6" t="s">
-        <v>934</v>
+        <v>939</v>
       </c>
       <c r="E119" s="5" t="s">
-        <v>935</v>
+        <v>940</v>
       </c>
     </row>
     <row r="120" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -11503,16 +11747,16 @@
         <v>118</v>
       </c>
       <c r="B120" s="5" t="s">
-        <v>920</v>
+        <v>925</v>
       </c>
       <c r="C120" s="5" t="s">
-        <v>936</v>
+        <v>941</v>
       </c>
       <c r="D120" s="6" t="s">
-        <v>937</v>
+        <v>942</v>
       </c>
       <c r="E120" s="5" t="s">
-        <v>938</v>
+        <v>943</v>
       </c>
     </row>
     <row r="121" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -11520,16 +11764,16 @@
         <v>119</v>
       </c>
       <c r="B121" s="5" t="s">
-        <v>939</v>
+        <v>944</v>
       </c>
       <c r="C121" s="5" t="s">
+        <v>945</v>
+      </c>
+      <c r="D121" s="6" t="s">
+        <v>946</v>
+      </c>
+      <c r="E121" s="5" t="s">
         <v>940</v>
-      </c>
-      <c r="D121" s="6" t="s">
-        <v>941</v>
-      </c>
-      <c r="E121" s="5" t="s">
-        <v>935</v>
       </c>
     </row>
     <row r="122" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -11537,16 +11781,16 @@
         <v>120</v>
       </c>
       <c r="B122" s="5" t="s">
-        <v>942</v>
+        <v>947</v>
       </c>
       <c r="C122" s="5" t="s">
-        <v>943</v>
+        <v>948</v>
       </c>
       <c r="D122" s="6" t="s">
-        <v>944</v>
+        <v>949</v>
       </c>
       <c r="E122" s="5" t="s">
-        <v>945</v>
+        <v>950</v>
       </c>
     </row>
     <row r="123" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -11554,13 +11798,13 @@
         <v>121</v>
       </c>
       <c r="B123" s="5" t="s">
-        <v>843</v>
+        <v>848</v>
       </c>
       <c r="C123" s="5" t="s">
-        <v>946</v>
+        <v>951</v>
       </c>
       <c r="D123" s="6" t="s">
-        <v>947</v>
+        <v>952</v>
       </c>
       <c r="E123" s="5" t="s">
         <v>409</v>
@@ -11571,13 +11815,13 @@
         <v>122</v>
       </c>
       <c r="B124" s="5" t="s">
-        <v>904</v>
+        <v>909</v>
       </c>
       <c r="C124" s="5" t="s">
-        <v>948</v>
+        <v>953</v>
       </c>
       <c r="D124" s="6" t="s">
-        <v>949</v>
+        <v>954</v>
       </c>
       <c r="E124" s="5" t="s">
         <v>409</v>
@@ -11588,16 +11832,16 @@
         <v>123</v>
       </c>
       <c r="B125" s="5" t="s">
-        <v>870</v>
+        <v>875</v>
       </c>
       <c r="C125" s="5" t="s">
-        <v>950</v>
+        <v>955</v>
       </c>
       <c r="D125" s="6" t="s">
-        <v>951</v>
+        <v>956</v>
       </c>
       <c r="E125" s="5" t="s">
-        <v>952</v>
+        <v>957</v>
       </c>
     </row>
     <row r="126" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -11605,16 +11849,16 @@
         <v>124</v>
       </c>
       <c r="B126" s="5" t="s">
-        <v>953</v>
+        <v>958</v>
       </c>
       <c r="C126" s="5" t="s">
-        <v>954</v>
+        <v>959</v>
       </c>
       <c r="D126" s="6" t="s">
-        <v>955</v>
+        <v>960</v>
       </c>
       <c r="E126" s="5" t="s">
-        <v>952</v>
+        <v>957</v>
       </c>
     </row>
     <row r="127" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -11622,16 +11866,16 @@
         <v>125</v>
       </c>
       <c r="B127" s="5" t="s">
-        <v>889</v>
+        <v>894</v>
       </c>
       <c r="C127" s="5" t="s">
-        <v>956</v>
+        <v>961</v>
       </c>
       <c r="D127" s="6" t="s">
-        <v>957</v>
+        <v>962</v>
       </c>
       <c r="E127" s="5" t="s">
-        <v>958</v>
+        <v>963</v>
       </c>
     </row>
     <row r="128" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -11639,16 +11883,16 @@
         <v>126</v>
       </c>
       <c r="B128" s="5" t="s">
-        <v>959</v>
+        <v>964</v>
       </c>
       <c r="C128" s="5" t="s">
-        <v>960</v>
+        <v>965</v>
       </c>
       <c r="D128" s="6" t="s">
-        <v>961</v>
+        <v>966</v>
       </c>
       <c r="E128" s="5" t="s">
-        <v>962</v>
+        <v>967</v>
       </c>
     </row>
     <row r="129" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -11656,16 +11900,16 @@
         <v>127</v>
       </c>
       <c r="B129" s="5" t="s">
-        <v>963</v>
+        <v>968</v>
       </c>
       <c r="C129" s="5" t="s">
-        <v>964</v>
+        <v>969</v>
       </c>
       <c r="D129" s="6" t="s">
-        <v>965</v>
+        <v>970</v>
       </c>
       <c r="E129" s="5" t="s">
-        <v>966</v>
+        <v>971</v>
       </c>
     </row>
     <row r="130" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -11673,16 +11917,16 @@
         <v>128</v>
       </c>
       <c r="B130" s="5" t="s">
-        <v>967</v>
+        <v>972</v>
       </c>
       <c r="C130" s="5" t="s">
-        <v>968</v>
+        <v>973</v>
       </c>
       <c r="D130" s="6" t="s">
-        <v>965</v>
+        <v>970</v>
       </c>
       <c r="E130" s="5" t="s">
-        <v>969</v>
+        <v>974</v>
       </c>
     </row>
     <row r="131" customFormat="false" ht="34.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -11690,13 +11934,13 @@
         <v>129</v>
       </c>
       <c r="B131" s="5" t="s">
+        <v>975</v>
+      </c>
+      <c r="C131" s="5" t="s">
+        <v>976</v>
+      </c>
+      <c r="D131" s="6" t="s">
         <v>970</v>
-      </c>
-      <c r="C131" s="5" t="s">
-        <v>971</v>
-      </c>
-      <c r="D131" s="6" t="s">
-        <v>965</v>
       </c>
       <c r="E131" s="5" t="s">
         <v>434</v>
@@ -11707,16 +11951,16 @@
         <v>130</v>
       </c>
       <c r="B132" s="5" t="s">
-        <v>972</v>
+        <v>977</v>
       </c>
       <c r="C132" s="5" t="s">
-        <v>973</v>
+        <v>978</v>
       </c>
       <c r="D132" s="6" t="s">
-        <v>974</v>
+        <v>979</v>
       </c>
       <c r="E132" s="5" t="s">
-        <v>975</v>
+        <v>980</v>
       </c>
     </row>
     <row r="133" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -11724,16 +11968,16 @@
         <v>131</v>
       </c>
       <c r="B133" s="5" t="s">
-        <v>976</v>
+        <v>981</v>
       </c>
       <c r="C133" s="5" t="s">
-        <v>977</v>
+        <v>982</v>
       </c>
       <c r="D133" s="6" t="s">
-        <v>978</v>
+        <v>983</v>
       </c>
       <c r="E133" s="5" t="s">
-        <v>975</v>
+        <v>980</v>
       </c>
     </row>
     <row r="134" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -11741,16 +11985,16 @@
         <v>132</v>
       </c>
       <c r="B134" s="5" t="s">
-        <v>979</v>
+        <v>984</v>
       </c>
       <c r="C134" s="5" t="s">
-        <v>980</v>
+        <v>985</v>
       </c>
       <c r="D134" s="6" t="s">
-        <v>981</v>
+        <v>986</v>
       </c>
       <c r="E134" s="5" t="s">
-        <v>982</v>
+        <v>987</v>
       </c>
     </row>
     <row r="135" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -11758,16 +12002,16 @@
         <v>133</v>
       </c>
       <c r="B135" s="5" t="s">
-        <v>983</v>
+        <v>988</v>
       </c>
       <c r="C135" s="5" t="s">
-        <v>984</v>
+        <v>989</v>
       </c>
       <c r="D135" s="6" t="s">
-        <v>985</v>
+        <v>990</v>
       </c>
       <c r="E135" s="5" t="s">
-        <v>986</v>
+        <v>991</v>
       </c>
     </row>
     <row r="136" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -11775,13 +12019,13 @@
         <v>134</v>
       </c>
       <c r="B136" s="5" t="s">
-        <v>698</v>
+        <v>703</v>
       </c>
       <c r="C136" s="5" t="s">
-        <v>987</v>
+        <v>992</v>
       </c>
       <c r="D136" s="6" t="s">
-        <v>988</v>
+        <v>993</v>
       </c>
       <c r="E136" s="5" t="s">
         <v>451</v>
@@ -11792,13 +12036,13 @@
         <v>135</v>
       </c>
       <c r="B137" s="5" t="s">
-        <v>989</v>
+        <v>994</v>
       </c>
       <c r="C137" s="5" t="s">
-        <v>990</v>
+        <v>995</v>
       </c>
       <c r="D137" s="6" t="s">
-        <v>991</v>
+        <v>996</v>
       </c>
       <c r="E137" s="5" t="s">
         <v>451</v>
@@ -11809,16 +12053,16 @@
         <v>136</v>
       </c>
       <c r="B138" s="5" t="s">
-        <v>992</v>
+        <v>997</v>
       </c>
       <c r="C138" s="5" t="s">
-        <v>993</v>
+        <v>998</v>
       </c>
       <c r="D138" s="6" t="s">
-        <v>994</v>
+        <v>999</v>
       </c>
       <c r="E138" s="5" t="s">
-        <v>995</v>
+        <v>1000</v>
       </c>
     </row>
     <row r="139" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -11826,16 +12070,16 @@
         <v>137</v>
       </c>
       <c r="B139" s="5" t="s">
-        <v>996</v>
+        <v>1001</v>
       </c>
       <c r="C139" s="5" t="s">
-        <v>997</v>
+        <v>1002</v>
       </c>
       <c r="D139" s="6" t="s">
-        <v>998</v>
+        <v>1003</v>
       </c>
       <c r="E139" s="5" t="s">
-        <v>999</v>
+        <v>1004</v>
       </c>
     </row>
     <row r="140" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -11843,13 +12087,13 @@
         <v>138</v>
       </c>
       <c r="B140" s="5" t="s">
-        <v>865</v>
+        <v>870</v>
       </c>
       <c r="C140" s="5" t="s">
-        <v>1000</v>
+        <v>1005</v>
       </c>
       <c r="D140" s="6" t="s">
-        <v>1001</v>
+        <v>1006</v>
       </c>
       <c r="E140" s="5" t="s">
         <v>463</v>
@@ -11860,16 +12104,16 @@
         <v>139</v>
       </c>
       <c r="B141" s="5" t="s">
-        <v>870</v>
+        <v>875</v>
       </c>
       <c r="C141" s="5" t="s">
-        <v>1002</v>
+        <v>1007</v>
       </c>
       <c r="D141" s="6" t="s">
-        <v>1003</v>
+        <v>1008</v>
       </c>
       <c r="E141" s="5" t="s">
-        <v>1004</v>
+        <v>1009</v>
       </c>
     </row>
     <row r="142" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -11877,16 +12121,16 @@
         <v>140</v>
       </c>
       <c r="B142" s="5" t="s">
-        <v>1005</v>
+        <v>1010</v>
       </c>
       <c r="C142" s="5" t="s">
-        <v>1006</v>
+        <v>1011</v>
       </c>
       <c r="D142" s="6" t="s">
-        <v>1007</v>
+        <v>1012</v>
       </c>
       <c r="E142" s="5" t="s">
-        <v>1008</v>
+        <v>1013</v>
       </c>
     </row>
     <row r="143" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -11894,13 +12138,13 @@
         <v>141</v>
       </c>
       <c r="B143" s="5" t="s">
-        <v>837</v>
+        <v>842</v>
       </c>
       <c r="C143" s="5" t="s">
-        <v>1009</v>
+        <v>1014</v>
       </c>
       <c r="D143" s="6" t="s">
-        <v>1010</v>
+        <v>1015</v>
       </c>
       <c r="E143" s="5" t="s">
         <v>472</v>
@@ -11911,16 +12155,16 @@
         <v>142</v>
       </c>
       <c r="B144" s="5" t="s">
-        <v>1011</v>
+        <v>1016</v>
       </c>
       <c r="C144" s="5" t="s">
-        <v>1012</v>
+        <v>1017</v>
       </c>
       <c r="D144" s="6" t="s">
-        <v>1013</v>
+        <v>1018</v>
       </c>
       <c r="E144" s="5" t="s">
-        <v>1014</v>
+        <v>1019</v>
       </c>
     </row>
     <row r="145" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -11928,13 +12172,13 @@
         <v>143</v>
       </c>
       <c r="B145" s="5" t="s">
-        <v>897</v>
+        <v>902</v>
       </c>
       <c r="C145" s="5" t="s">
-        <v>1015</v>
+        <v>1020</v>
       </c>
       <c r="D145" s="6" t="s">
-        <v>1016</v>
+        <v>1021</v>
       </c>
       <c r="E145" s="5" t="s">
         <v>479</v>
@@ -11945,16 +12189,16 @@
         <v>144</v>
       </c>
       <c r="B146" s="5" t="s">
-        <v>837</v>
+        <v>842</v>
       </c>
       <c r="C146" s="5" t="s">
-        <v>1017</v>
+        <v>1022</v>
       </c>
       <c r="D146" s="6" t="s">
-        <v>1018</v>
+        <v>1023</v>
       </c>
       <c r="E146" s="5" t="s">
-        <v>1019</v>
+        <v>1024</v>
       </c>
     </row>
     <row r="147" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -11962,16 +12206,16 @@
         <v>145</v>
       </c>
       <c r="B147" s="5" t="s">
-        <v>1020</v>
+        <v>1025</v>
       </c>
       <c r="C147" s="5" t="s">
-        <v>1021</v>
+        <v>1026</v>
       </c>
       <c r="D147" s="6" t="s">
-        <v>1022</v>
+        <v>1027</v>
       </c>
       <c r="E147" s="5" t="s">
-        <v>1023</v>
+        <v>1028</v>
       </c>
     </row>
     <row r="148" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -11979,16 +12223,16 @@
         <v>146</v>
       </c>
       <c r="B148" s="5" t="s">
-        <v>1024</v>
+        <v>1029</v>
       </c>
       <c r="C148" s="5" t="s">
-        <v>1025</v>
+        <v>1030</v>
       </c>
       <c r="D148" s="6" t="s">
-        <v>1026</v>
+        <v>1031</v>
       </c>
       <c r="E148" s="5" t="s">
-        <v>1027</v>
+        <v>1032</v>
       </c>
     </row>
     <row r="149" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -11996,13 +12240,13 @@
         <v>147</v>
       </c>
       <c r="B149" s="5" t="s">
-        <v>1028</v>
+        <v>1033</v>
       </c>
       <c r="C149" s="5" t="s">
-        <v>1029</v>
+        <v>1034</v>
       </c>
       <c r="D149" s="6" t="s">
-        <v>961</v>
+        <v>966</v>
       </c>
       <c r="E149" s="5" t="s">
         <v>492</v>
@@ -12013,13 +12257,13 @@
         <v>148</v>
       </c>
       <c r="B150" s="5" t="s">
-        <v>1030</v>
+        <v>1035</v>
       </c>
       <c r="C150" s="5" t="s">
-        <v>1031</v>
+        <v>1036</v>
       </c>
       <c r="D150" s="6" t="s">
-        <v>965</v>
+        <v>970</v>
       </c>
       <c r="E150" s="5" t="s">
         <v>492</v>
@@ -12030,16 +12274,16 @@
         <v>149</v>
       </c>
       <c r="B151" s="5" t="s">
-        <v>1032</v>
+        <v>1037</v>
       </c>
       <c r="C151" s="5" t="s">
-        <v>1033</v>
+        <v>1038</v>
       </c>
       <c r="D151" s="6" t="s">
-        <v>1034</v>
+        <v>1039</v>
       </c>
       <c r="E151" s="5" t="s">
-        <v>1035</v>
+        <v>1040</v>
       </c>
     </row>
     <row r="152" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -12047,16 +12291,16 @@
         <v>150</v>
       </c>
       <c r="B152" s="5" t="s">
-        <v>1032</v>
+        <v>1037</v>
       </c>
       <c r="C152" s="5" t="s">
-        <v>1036</v>
+        <v>1041</v>
       </c>
       <c r="D152" s="6" t="s">
-        <v>1034</v>
+        <v>1039</v>
       </c>
       <c r="E152" s="5" t="s">
-        <v>1035</v>
+        <v>1040</v>
       </c>
     </row>
     <row r="153" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -12064,16 +12308,16 @@
         <v>151</v>
       </c>
       <c r="B153" s="5" t="s">
-        <v>1037</v>
+        <v>1042</v>
       </c>
       <c r="C153" s="5" t="s">
-        <v>1038</v>
+        <v>1043</v>
       </c>
       <c r="D153" s="6" t="s">
-        <v>1039</v>
+        <v>1044</v>
       </c>
       <c r="E153" s="5" t="s">
-        <v>1040</v>
+        <v>1045</v>
       </c>
     </row>
     <row r="154" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -12081,16 +12325,16 @@
         <v>152</v>
       </c>
       <c r="B154" s="5" t="s">
-        <v>1037</v>
+        <v>1042</v>
       </c>
       <c r="C154" s="5" t="s">
-        <v>1041</v>
+        <v>1046</v>
       </c>
       <c r="D154" s="6" t="s">
-        <v>1039</v>
+        <v>1044</v>
       </c>
       <c r="E154" s="5" t="s">
-        <v>1040</v>
+        <v>1045</v>
       </c>
     </row>
     <row r="155" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -12098,16 +12342,16 @@
         <v>153</v>
       </c>
       <c r="B155" s="5" t="s">
-        <v>1042</v>
+        <v>1047</v>
       </c>
       <c r="C155" s="5" t="s">
-        <v>1043</v>
+        <v>1048</v>
       </c>
       <c r="D155" s="6" t="s">
-        <v>1044</v>
+        <v>1049</v>
       </c>
       <c r="E155" s="5" t="s">
-        <v>1045</v>
+        <v>1050</v>
       </c>
     </row>
     <row r="156" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -12115,16 +12359,16 @@
         <v>154</v>
       </c>
       <c r="B156" s="5" t="s">
-        <v>870</v>
+        <v>875</v>
       </c>
       <c r="C156" s="5" t="s">
-        <v>1046</v>
+        <v>1051</v>
       </c>
       <c r="D156" s="6" t="s">
-        <v>1047</v>
+        <v>1052</v>
       </c>
       <c r="E156" s="5" t="s">
-        <v>1045</v>
+        <v>1050</v>
       </c>
     </row>
     <row r="157" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -12132,14 +12376,14 @@
         <v>155</v>
       </c>
       <c r="B157" s="5" t="s">
-        <v>1048</v>
+        <v>1053</v>
       </c>
       <c r="C157" s="5" t="s">
-        <v>1049</v>
+        <v>1054</v>
       </c>
       <c r="D157" s="5"/>
       <c r="E157" s="5" t="s">
-        <v>1050</v>
+        <v>1055</v>
       </c>
     </row>
     <row r="158" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -12147,16 +12391,16 @@
         <v>156</v>
       </c>
       <c r="B158" s="5" t="s">
-        <v>1051</v>
+        <v>1056</v>
       </c>
       <c r="C158" s="5" t="s">
-        <v>1052</v>
+        <v>1057</v>
       </c>
       <c r="D158" s="6" t="s">
-        <v>1053</v>
+        <v>1058</v>
       </c>
       <c r="E158" s="5" t="s">
-        <v>1050</v>
+        <v>1055</v>
       </c>
     </row>
     <row r="159" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -12164,16 +12408,16 @@
         <v>157</v>
       </c>
       <c r="B159" s="5" t="s">
-        <v>698</v>
+        <v>703</v>
       </c>
       <c r="C159" s="5" t="s">
-        <v>1054</v>
+        <v>1059</v>
       </c>
       <c r="D159" s="6" t="s">
-        <v>1055</v>
+        <v>1060</v>
       </c>
       <c r="E159" s="5" t="s">
-        <v>1056</v>
+        <v>1061</v>
       </c>
     </row>
     <row r="160" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -12181,16 +12425,16 @@
         <v>158</v>
       </c>
       <c r="B160" s="5" t="s">
-        <v>837</v>
+        <v>842</v>
       </c>
       <c r="C160" s="5" t="s">
-        <v>1057</v>
+        <v>1062</v>
       </c>
       <c r="D160" s="6" t="s">
-        <v>1058</v>
+        <v>1063</v>
       </c>
       <c r="E160" s="5" t="s">
-        <v>1056</v>
+        <v>1061</v>
       </c>
     </row>
     <row r="161" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -12198,16 +12442,16 @@
         <v>159</v>
       </c>
       <c r="B161" s="5" t="s">
-        <v>893</v>
+        <v>898</v>
       </c>
       <c r="C161" s="5" t="s">
-        <v>1059</v>
+        <v>1064</v>
       </c>
       <c r="D161" s="6" t="s">
-        <v>1060</v>
+        <v>1065</v>
       </c>
       <c r="E161" s="5" t="s">
-        <v>1056</v>
+        <v>1061</v>
       </c>
     </row>
     <row r="162" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -12215,16 +12459,16 @@
         <v>160</v>
       </c>
       <c r="B162" s="5" t="s">
+        <v>1066</v>
+      </c>
+      <c r="C162" s="5" t="s">
+        <v>1067</v>
+      </c>
+      <c r="D162" s="6" t="s">
+        <v>1068</v>
+      </c>
+      <c r="E162" s="5" t="s">
         <v>1061</v>
-      </c>
-      <c r="C162" s="5" t="s">
-        <v>1062</v>
-      </c>
-      <c r="D162" s="6" t="s">
-        <v>1063</v>
-      </c>
-      <c r="E162" s="5" t="s">
-        <v>1056</v>
       </c>
     </row>
     <row r="163" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -12232,16 +12476,16 @@
         <v>161</v>
       </c>
       <c r="B163" s="5" t="s">
+        <v>1066</v>
+      </c>
+      <c r="C163" s="5" t="s">
+        <v>1069</v>
+      </c>
+      <c r="D163" s="6" t="s">
+        <v>1070</v>
+      </c>
+      <c r="E163" s="5" t="s">
         <v>1061</v>
-      </c>
-      <c r="C163" s="5" t="s">
-        <v>1064</v>
-      </c>
-      <c r="D163" s="6" t="s">
-        <v>1065</v>
-      </c>
-      <c r="E163" s="5" t="s">
-        <v>1056</v>
       </c>
     </row>
     <row r="164" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -12249,16 +12493,16 @@
         <v>162</v>
       </c>
       <c r="B164" s="5" t="s">
-        <v>904</v>
+        <v>909</v>
       </c>
       <c r="C164" s="5" t="s">
-        <v>1066</v>
+        <v>1071</v>
       </c>
       <c r="D164" s="6" t="s">
-        <v>1067</v>
+        <v>1072</v>
       </c>
       <c r="E164" s="5" t="s">
-        <v>1068</v>
+        <v>1073</v>
       </c>
     </row>
     <row r="165" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -12266,16 +12510,16 @@
         <v>163</v>
       </c>
       <c r="B165" s="5" t="s">
-        <v>698</v>
+        <v>703</v>
       </c>
       <c r="C165" s="5" t="s">
-        <v>1069</v>
+        <v>1074</v>
       </c>
       <c r="D165" s="6" t="s">
-        <v>1070</v>
+        <v>1075</v>
       </c>
       <c r="E165" s="5" t="s">
-        <v>1068</v>
+        <v>1073</v>
       </c>
     </row>
     <row r="166" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -12283,13 +12527,13 @@
         <v>157</v>
       </c>
       <c r="B166" s="5" t="s">
-        <v>1061</v>
+        <v>1066</v>
       </c>
       <c r="C166" s="5" t="s">
-        <v>1071</v>
+        <v>1076</v>
       </c>
       <c r="D166" s="6" t="s">
-        <v>1072</v>
+        <v>1077</v>
       </c>
       <c r="E166" s="5" t="s">
         <v>521</v>
@@ -12300,16 +12544,16 @@
         <v>158</v>
       </c>
       <c r="B167" s="5" t="s">
-        <v>920</v>
+        <v>925</v>
       </c>
       <c r="C167" s="5" t="s">
-        <v>1073</v>
+        <v>1078</v>
       </c>
       <c r="D167" s="6" t="s">
-        <v>1074</v>
+        <v>1079</v>
       </c>
       <c r="E167" s="5" t="s">
-        <v>1075</v>
+        <v>1080</v>
       </c>
     </row>
     <row r="168" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -12317,13 +12561,13 @@
         <v>159</v>
       </c>
       <c r="B168" s="5" t="s">
-        <v>698</v>
+        <v>703</v>
       </c>
       <c r="C168" s="5" t="s">
-        <v>1076</v>
+        <v>1081</v>
       </c>
       <c r="D168" s="6" t="s">
-        <v>1077</v>
+        <v>1082</v>
       </c>
       <c r="E168" s="5" t="s">
         <v>524</v>
@@ -12334,16 +12578,16 @@
         <v>160</v>
       </c>
       <c r="B169" s="5" t="s">
-        <v>893</v>
+        <v>898</v>
       </c>
       <c r="C169" s="5" t="s">
-        <v>1078</v>
+        <v>1083</v>
       </c>
       <c r="D169" s="6" t="s">
-        <v>1079</v>
+        <v>1084</v>
       </c>
       <c r="E169" s="5" t="s">
-        <v>1080</v>
+        <v>1085</v>
       </c>
     </row>
     <row r="170" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -12351,16 +12595,16 @@
         <v>161</v>
       </c>
       <c r="B170" s="5" t="s">
-        <v>893</v>
+        <v>898</v>
       </c>
       <c r="C170" s="5" t="s">
-        <v>1081</v>
+        <v>1086</v>
       </c>
       <c r="D170" s="6" t="s">
-        <v>1082</v>
+        <v>1087</v>
       </c>
       <c r="E170" s="5" t="s">
-        <v>1080</v>
+        <v>1085</v>
       </c>
     </row>
     <row r="171" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -12368,16 +12612,16 @@
         <v>162</v>
       </c>
       <c r="B171" s="5" t="s">
-        <v>893</v>
+        <v>898</v>
       </c>
       <c r="C171" s="5" t="s">
-        <v>1083</v>
+        <v>1088</v>
       </c>
       <c r="D171" s="6" t="s">
-        <v>1084</v>
+        <v>1089</v>
       </c>
       <c r="E171" s="5" t="s">
-        <v>1080</v>
+        <v>1085</v>
       </c>
     </row>
     <row r="172" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -12385,16 +12629,16 @@
         <v>163</v>
       </c>
       <c r="B172" s="5" t="s">
-        <v>843</v>
+        <v>848</v>
       </c>
       <c r="C172" s="5" t="s">
-        <v>1085</v>
+        <v>1090</v>
       </c>
       <c r="D172" s="6" t="s">
-        <v>1086</v>
+        <v>1091</v>
       </c>
       <c r="E172" s="5" t="s">
-        <v>1087</v>
+        <v>1092</v>
       </c>
     </row>
     <row r="173" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -12402,16 +12646,16 @@
         <v>164</v>
       </c>
       <c r="B173" s="5" t="s">
-        <v>837</v>
+        <v>842</v>
       </c>
       <c r="C173" s="5" t="s">
-        <v>1088</v>
+        <v>1093</v>
       </c>
       <c r="D173" s="6" t="s">
-        <v>1089</v>
+        <v>1094</v>
       </c>
       <c r="E173" s="5" t="s">
-        <v>1090</v>
+        <v>1095</v>
       </c>
     </row>
     <row r="174" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -12419,16 +12663,16 @@
         <v>165</v>
       </c>
       <c r="B174" s="5" t="s">
-        <v>837</v>
+        <v>842</v>
       </c>
       <c r="C174" s="5" t="s">
-        <v>1091</v>
+        <v>1096</v>
       </c>
       <c r="D174" s="6" t="s">
-        <v>1092</v>
+        <v>1097</v>
       </c>
       <c r="E174" s="5" t="s">
-        <v>1090</v>
+        <v>1095</v>
       </c>
     </row>
     <row r="175" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -12436,16 +12680,16 @@
         <v>166</v>
       </c>
       <c r="B175" s="5" t="s">
-        <v>837</v>
+        <v>842</v>
       </c>
       <c r="C175" s="5" t="s">
-        <v>1093</v>
+        <v>1098</v>
       </c>
       <c r="D175" s="6" t="s">
-        <v>1094</v>
+        <v>1099</v>
       </c>
       <c r="E175" s="5" t="s">
-        <v>1090</v>
+        <v>1095</v>
       </c>
     </row>
     <row r="176" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -12453,16 +12697,16 @@
         <v>167</v>
       </c>
       <c r="B176" s="5" t="s">
-        <v>904</v>
+        <v>909</v>
       </c>
       <c r="C176" s="5" t="s">
-        <v>1095</v>
+        <v>1100</v>
       </c>
       <c r="D176" s="6" t="s">
-        <v>1096</v>
+        <v>1101</v>
       </c>
       <c r="E176" s="5" t="s">
-        <v>1097</v>
+        <v>1102</v>
       </c>
     </row>
     <row r="177" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -12470,16 +12714,16 @@
         <v>168</v>
       </c>
       <c r="B177" s="5" t="s">
-        <v>698</v>
+        <v>703</v>
       </c>
       <c r="C177" s="5" t="s">
-        <v>1098</v>
+        <v>1103</v>
       </c>
       <c r="D177" s="6" t="s">
-        <v>1099</v>
+        <v>1104</v>
       </c>
       <c r="E177" s="5" t="s">
-        <v>1097</v>
+        <v>1102</v>
       </c>
     </row>
     <row r="178" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -12487,16 +12731,16 @@
         <v>169</v>
       </c>
       <c r="B178" s="5" t="s">
-        <v>698</v>
+        <v>703</v>
       </c>
       <c r="C178" s="5" t="s">
-        <v>1100</v>
+        <v>1105</v>
       </c>
       <c r="D178" s="6" t="s">
-        <v>1101</v>
+        <v>1106</v>
       </c>
       <c r="E178" s="5" t="s">
-        <v>1097</v>
+        <v>1102</v>
       </c>
     </row>
     <row r="179" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -12504,16 +12748,16 @@
         <v>170</v>
       </c>
       <c r="B179" s="5" t="s">
-        <v>920</v>
+        <v>925</v>
       </c>
       <c r="C179" s="5" t="s">
+        <v>1107</v>
+      </c>
+      <c r="D179" s="6" t="s">
+        <v>1108</v>
+      </c>
+      <c r="E179" s="5" t="s">
         <v>1102</v>
-      </c>
-      <c r="D179" s="6" t="s">
-        <v>1103</v>
-      </c>
-      <c r="E179" s="5" t="s">
-        <v>1097</v>
       </c>
     </row>
     <row r="180" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -12521,16 +12765,16 @@
         <v>171</v>
       </c>
       <c r="B180" s="5" t="s">
-        <v>920</v>
+        <v>925</v>
       </c>
       <c r="C180" s="5" t="s">
-        <v>1104</v>
+        <v>1109</v>
       </c>
       <c r="D180" s="6" t="s">
-        <v>1105</v>
+        <v>1110</v>
       </c>
       <c r="E180" s="5" t="s">
-        <v>1097</v>
+        <v>1102</v>
       </c>
     </row>
     <row r="181" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -12538,16 +12782,16 @@
         <v>172</v>
       </c>
       <c r="B181" s="5" t="s">
-        <v>893</v>
+        <v>898</v>
       </c>
       <c r="C181" s="5" t="s">
-        <v>1106</v>
+        <v>1111</v>
       </c>
       <c r="D181" s="6" t="s">
-        <v>1107</v>
+        <v>1112</v>
       </c>
       <c r="E181" s="5" t="s">
-        <v>1108</v>
+        <v>1113</v>
       </c>
     </row>
     <row r="182" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -12555,16 +12799,16 @@
         <v>173</v>
       </c>
       <c r="B182" s="5" t="s">
-        <v>698</v>
+        <v>703</v>
       </c>
       <c r="C182" s="5" t="s">
-        <v>1109</v>
+        <v>1114</v>
       </c>
       <c r="D182" s="6" t="s">
-        <v>1110</v>
+        <v>1115</v>
       </c>
       <c r="E182" s="5" t="s">
-        <v>1111</v>
+        <v>1116</v>
       </c>
     </row>
     <row r="183" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -12572,16 +12816,16 @@
         <v>174</v>
       </c>
       <c r="B183" s="5" t="s">
-        <v>698</v>
+        <v>703</v>
       </c>
       <c r="C183" s="5" t="s">
-        <v>1112</v>
+        <v>1117</v>
       </c>
       <c r="D183" s="6" t="s">
-        <v>1113</v>
+        <v>1118</v>
       </c>
       <c r="E183" s="5" t="s">
-        <v>1111</v>
+        <v>1116</v>
       </c>
     </row>
     <row r="184" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -12589,16 +12833,16 @@
         <v>175</v>
       </c>
       <c r="B184" s="5" t="s">
-        <v>698</v>
+        <v>703</v>
       </c>
       <c r="C184" s="5" t="s">
-        <v>1114</v>
+        <v>1119</v>
       </c>
       <c r="D184" s="6" t="s">
-        <v>1115</v>
+        <v>1120</v>
       </c>
       <c r="E184" s="5" t="s">
-        <v>1111</v>
+        <v>1116</v>
       </c>
     </row>
     <row r="185" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -12606,16 +12850,16 @@
         <v>176</v>
       </c>
       <c r="B185" s="5" t="s">
-        <v>1061</v>
+        <v>1066</v>
       </c>
       <c r="C185" s="5" t="s">
+        <v>1121</v>
+      </c>
+      <c r="D185" s="6" t="s">
+        <v>1122</v>
+      </c>
+      <c r="E185" s="5" t="s">
         <v>1116</v>
-      </c>
-      <c r="D185" s="6" t="s">
-        <v>1117</v>
-      </c>
-      <c r="E185" s="5" t="s">
-        <v>1111</v>
       </c>
     </row>
     <row r="186" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -12623,16 +12867,16 @@
         <v>177</v>
       </c>
       <c r="B186" s="5" t="s">
-        <v>1061</v>
+        <v>1066</v>
       </c>
       <c r="C186" s="5" t="s">
-        <v>1118</v>
+        <v>1123</v>
       </c>
       <c r="D186" s="6" t="s">
-        <v>1119</v>
+        <v>1124</v>
       </c>
       <c r="E186" s="5" t="s">
-        <v>1111</v>
+        <v>1116</v>
       </c>
     </row>
     <row r="187" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -12640,16 +12884,16 @@
         <v>178</v>
       </c>
       <c r="B187" s="5" t="s">
-        <v>1061</v>
+        <v>1066</v>
       </c>
       <c r="C187" s="5" t="s">
-        <v>1120</v>
+        <v>1125</v>
       </c>
       <c r="D187" s="6" t="s">
-        <v>1121</v>
+        <v>1126</v>
       </c>
       <c r="E187" s="5" t="s">
-        <v>1111</v>
+        <v>1116</v>
       </c>
     </row>
     <row r="188" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -12657,16 +12901,16 @@
         <v>179</v>
       </c>
       <c r="B188" s="5" t="s">
-        <v>698</v>
+        <v>703</v>
       </c>
       <c r="C188" s="5" t="s">
-        <v>1122</v>
+        <v>1127</v>
       </c>
       <c r="D188" s="6" t="s">
-        <v>1123</v>
+        <v>1128</v>
       </c>
       <c r="E188" s="5" t="s">
-        <v>1124</v>
+        <v>1129</v>
       </c>
     </row>
     <row r="189" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -12674,16 +12918,16 @@
         <v>180</v>
       </c>
       <c r="B189" s="5" t="s">
-        <v>698</v>
+        <v>703</v>
       </c>
       <c r="C189" s="5" t="s">
-        <v>1125</v>
+        <v>1130</v>
       </c>
       <c r="D189" s="6" t="s">
-        <v>1126</v>
+        <v>1131</v>
       </c>
       <c r="E189" s="5" t="s">
-        <v>1124</v>
+        <v>1129</v>
       </c>
     </row>
     <row r="190" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -12691,16 +12935,16 @@
         <v>181</v>
       </c>
       <c r="B190" s="5" t="s">
-        <v>893</v>
+        <v>898</v>
       </c>
       <c r="C190" s="5" t="s">
-        <v>1127</v>
+        <v>1132</v>
       </c>
       <c r="D190" s="6" t="s">
-        <v>1128</v>
+        <v>1133</v>
       </c>
       <c r="E190" s="5" t="s">
-        <v>1124</v>
+        <v>1129</v>
       </c>
     </row>
     <row r="191" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -12708,16 +12952,16 @@
         <v>182</v>
       </c>
       <c r="B191" s="5" t="s">
-        <v>1061</v>
+        <v>1066</v>
       </c>
       <c r="C191" s="5" t="s">
+        <v>1134</v>
+      </c>
+      <c r="D191" s="6" t="s">
+        <v>1135</v>
+      </c>
+      <c r="E191" s="5" t="s">
         <v>1129</v>
-      </c>
-      <c r="D191" s="6" t="s">
-        <v>1130</v>
-      </c>
-      <c r="E191" s="5" t="s">
-        <v>1124</v>
       </c>
     </row>
     <row r="192" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -12725,16 +12969,16 @@
         <v>183</v>
       </c>
       <c r="B192" s="5" t="s">
-        <v>1061</v>
+        <v>1066</v>
       </c>
       <c r="C192" s="5" t="s">
-        <v>1131</v>
+        <v>1136</v>
       </c>
       <c r="D192" s="6" t="s">
-        <v>1132</v>
+        <v>1137</v>
       </c>
       <c r="E192" s="5" t="s">
-        <v>1124</v>
+        <v>1129</v>
       </c>
     </row>
     <row r="193" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -12742,13 +12986,13 @@
         <v>184</v>
       </c>
       <c r="B193" s="5" t="s">
-        <v>893</v>
+        <v>898</v>
       </c>
       <c r="C193" s="5" t="s">
-        <v>1133</v>
+        <v>1138</v>
       </c>
       <c r="D193" s="6" t="s">
-        <v>1134</v>
+        <v>1139</v>
       </c>
       <c r="E193" s="5" t="s">
         <v>533</v>
@@ -12759,16 +13003,16 @@
         <v>185</v>
       </c>
       <c r="B194" s="5" t="s">
-        <v>893</v>
+        <v>898</v>
       </c>
       <c r="C194" s="5" t="s">
-        <v>1135</v>
+        <v>1140</v>
       </c>
       <c r="D194" s="6" t="s">
-        <v>1136</v>
+        <v>1141</v>
       </c>
       <c r="E194" s="5" t="s">
-        <v>1137</v>
+        <v>1142</v>
       </c>
     </row>
     <row r="195" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -12776,16 +13020,16 @@
         <v>186</v>
       </c>
       <c r="B195" s="5" t="s">
-        <v>698</v>
+        <v>703</v>
       </c>
       <c r="C195" s="5" t="s">
-        <v>1138</v>
+        <v>1143</v>
       </c>
       <c r="D195" s="6" t="s">
-        <v>1139</v>
+        <v>1144</v>
       </c>
       <c r="E195" s="5" t="s">
-        <v>1140</v>
+        <v>1145</v>
       </c>
     </row>
     <row r="196" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -12793,16 +13037,16 @@
         <v>187</v>
       </c>
       <c r="B196" s="5" t="s">
-        <v>837</v>
+        <v>842</v>
       </c>
       <c r="C196" s="5" t="s">
-        <v>1141</v>
+        <v>1146</v>
       </c>
       <c r="D196" s="6" t="s">
-        <v>1142</v>
+        <v>1147</v>
       </c>
       <c r="E196" s="5" t="s">
-        <v>1140</v>
+        <v>1145</v>
       </c>
     </row>
     <row r="197" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -12810,16 +13054,16 @@
         <v>188</v>
       </c>
       <c r="B197" s="5" t="s">
-        <v>1061</v>
+        <v>1066</v>
       </c>
       <c r="C197" s="5" t="s">
-        <v>1143</v>
+        <v>1148</v>
       </c>
       <c r="D197" s="6" t="s">
-        <v>1144</v>
+        <v>1149</v>
       </c>
       <c r="E197" s="5" t="s">
-        <v>1140</v>
+        <v>1145</v>
       </c>
     </row>
     <row r="198" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -12827,16 +13071,16 @@
         <v>189</v>
       </c>
       <c r="B198" s="5" t="s">
-        <v>1061</v>
+        <v>1066</v>
       </c>
       <c r="C198" s="5" t="s">
+        <v>1150</v>
+      </c>
+      <c r="D198" s="6" t="s">
+        <v>1151</v>
+      </c>
+      <c r="E198" s="5" t="s">
         <v>1145</v>
-      </c>
-      <c r="D198" s="6" t="s">
-        <v>1146</v>
-      </c>
-      <c r="E198" s="5" t="s">
-        <v>1140</v>
       </c>
     </row>
     <row r="199" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -12844,16 +13088,16 @@
         <v>190</v>
       </c>
       <c r="B199" s="5" t="s">
-        <v>904</v>
+        <v>909</v>
       </c>
       <c r="C199" s="5" t="s">
-        <v>1147</v>
+        <v>1152</v>
       </c>
       <c r="D199" s="6" t="s">
-        <v>1148</v>
+        <v>1153</v>
       </c>
       <c r="E199" s="5" t="s">
-        <v>1149</v>
+        <v>1154</v>
       </c>
     </row>
     <row r="200" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -12861,16 +13105,16 @@
         <v>191</v>
       </c>
       <c r="B200" s="5" t="s">
-        <v>904</v>
+        <v>909</v>
       </c>
       <c r="C200" s="5" t="s">
-        <v>1150</v>
+        <v>1155</v>
       </c>
       <c r="D200" s="6" t="s">
-        <v>1151</v>
+        <v>1156</v>
       </c>
       <c r="E200" s="5" t="s">
-        <v>1149</v>
+        <v>1154</v>
       </c>
     </row>
     <row r="201" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -12878,16 +13122,16 @@
         <v>192</v>
       </c>
       <c r="B201" s="5" t="s">
-        <v>698</v>
+        <v>703</v>
       </c>
       <c r="C201" s="5" t="s">
-        <v>1152</v>
+        <v>1157</v>
       </c>
       <c r="D201" s="6" t="s">
-        <v>1153</v>
+        <v>1158</v>
       </c>
       <c r="E201" s="5" t="s">
-        <v>1149</v>
+        <v>1154</v>
       </c>
     </row>
     <row r="202" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -12895,16 +13139,16 @@
         <v>193</v>
       </c>
       <c r="B202" s="5" t="s">
-        <v>698</v>
+        <v>703</v>
       </c>
       <c r="C202" s="5" t="s">
-        <v>1154</v>
+        <v>1159</v>
       </c>
       <c r="D202" s="6" t="s">
-        <v>1155</v>
+        <v>1160</v>
       </c>
       <c r="E202" s="5" t="s">
-        <v>1156</v>
+        <v>1161</v>
       </c>
     </row>
     <row r="203" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -12912,16 +13156,16 @@
         <v>194</v>
       </c>
       <c r="B203" s="5" t="s">
-        <v>698</v>
+        <v>703</v>
       </c>
       <c r="C203" s="5" t="s">
-        <v>1157</v>
+        <v>1162</v>
       </c>
       <c r="D203" s="6" t="s">
-        <v>1158</v>
+        <v>1163</v>
       </c>
       <c r="E203" s="5" t="s">
-        <v>1156</v>
+        <v>1161</v>
       </c>
     </row>
     <row r="204" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -12929,16 +13173,16 @@
         <v>195</v>
       </c>
       <c r="B204" s="5" t="s">
-        <v>698</v>
+        <v>703</v>
       </c>
       <c r="C204" s="5" t="s">
-        <v>1159</v>
+        <v>1164</v>
       </c>
       <c r="D204" s="6" t="s">
-        <v>1160</v>
+        <v>1165</v>
       </c>
       <c r="E204" s="5" t="s">
-        <v>1161</v>
+        <v>1166</v>
       </c>
     </row>
     <row r="205" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -12946,13 +13190,13 @@
         <v>196</v>
       </c>
       <c r="B205" s="5" t="s">
-        <v>893</v>
+        <v>898</v>
       </c>
       <c r="C205" s="5" t="s">
-        <v>1162</v>
+        <v>1167</v>
       </c>
       <c r="D205" s="6" t="s">
-        <v>1163</v>
+        <v>1168</v>
       </c>
       <c r="E205" s="5" t="s">
         <v>540</v>
@@ -12963,16 +13207,16 @@
         <v>197</v>
       </c>
       <c r="B206" s="5" t="s">
-        <v>698</v>
+        <v>703</v>
       </c>
       <c r="C206" s="5" t="s">
-        <v>1164</v>
+        <v>1169</v>
       </c>
       <c r="D206" s="6" t="s">
-        <v>1165</v>
+        <v>1170</v>
       </c>
       <c r="E206" s="5" t="s">
-        <v>1166</v>
+        <v>1171</v>
       </c>
     </row>
     <row r="207" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -12980,16 +13224,16 @@
         <v>198</v>
       </c>
       <c r="B207" s="5" t="s">
-        <v>920</v>
+        <v>925</v>
       </c>
       <c r="C207" s="5" t="s">
-        <v>1167</v>
+        <v>1172</v>
       </c>
       <c r="D207" s="6" t="s">
-        <v>1168</v>
+        <v>1173</v>
       </c>
       <c r="E207" s="5" t="s">
-        <v>1166</v>
+        <v>1171</v>
       </c>
     </row>
     <row r="208" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -12997,16 +13241,16 @@
         <v>199</v>
       </c>
       <c r="B208" s="5" t="s">
-        <v>1061</v>
+        <v>1066</v>
       </c>
       <c r="C208" s="5" t="s">
-        <v>1169</v>
+        <v>1174</v>
       </c>
       <c r="D208" s="6" t="s">
-        <v>1170</v>
+        <v>1175</v>
       </c>
       <c r="E208" s="5" t="s">
-        <v>1166</v>
+        <v>1171</v>
       </c>
     </row>
     <row r="209" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -13014,16 +13258,16 @@
         <v>200</v>
       </c>
       <c r="B209" s="5" t="s">
-        <v>1061</v>
+        <v>1066</v>
       </c>
       <c r="C209" s="5" t="s">
+        <v>1176</v>
+      </c>
+      <c r="D209" s="6" t="s">
+        <v>1177</v>
+      </c>
+      <c r="E209" s="5" t="s">
         <v>1171</v>
-      </c>
-      <c r="D209" s="6" t="s">
-        <v>1172</v>
-      </c>
-      <c r="E209" s="5" t="s">
-        <v>1166</v>
       </c>
     </row>
     <row r="210" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -13031,16 +13275,16 @@
         <v>201</v>
       </c>
       <c r="B210" s="5" t="s">
-        <v>837</v>
+        <v>842</v>
       </c>
       <c r="C210" s="5" t="s">
-        <v>1173</v>
+        <v>1178</v>
       </c>
       <c r="D210" s="6" t="s">
-        <v>1174</v>
+        <v>1179</v>
       </c>
       <c r="E210" s="5" t="s">
-        <v>1175</v>
+        <v>1180</v>
       </c>
     </row>
     <row r="211" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -13048,16 +13292,16 @@
         <v>202</v>
       </c>
       <c r="B211" s="5" t="s">
-        <v>920</v>
+        <v>925</v>
       </c>
       <c r="C211" s="5" t="s">
-        <v>1176</v>
+        <v>1181</v>
       </c>
       <c r="D211" s="6" t="s">
-        <v>1177</v>
+        <v>1182</v>
       </c>
       <c r="E211" s="5" t="s">
-        <v>1175</v>
+        <v>1180</v>
       </c>
     </row>
     <row r="212" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -13065,16 +13309,16 @@
         <v>203</v>
       </c>
       <c r="B212" s="5" t="s">
-        <v>920</v>
+        <v>925</v>
       </c>
       <c r="C212" s="5" t="s">
-        <v>1178</v>
+        <v>1183</v>
       </c>
       <c r="D212" s="6" t="s">
-        <v>1179</v>
+        <v>1184</v>
       </c>
       <c r="E212" s="5" t="s">
-        <v>1175</v>
+        <v>1180</v>
       </c>
     </row>
     <row r="213" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -13082,16 +13326,16 @@
         <v>204</v>
       </c>
       <c r="B213" s="5" t="s">
-        <v>893</v>
+        <v>898</v>
       </c>
       <c r="C213" s="5" t="s">
-        <v>1180</v>
+        <v>1185</v>
       </c>
       <c r="D213" s="6" t="s">
-        <v>1181</v>
+        <v>1186</v>
       </c>
       <c r="E213" s="5" t="s">
-        <v>1075</v>
+        <v>1080</v>
       </c>
     </row>
     <row r="214" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -13099,16 +13343,16 @@
         <v>205</v>
       </c>
       <c r="B214" s="5" t="s">
-        <v>698</v>
+        <v>703</v>
       </c>
       <c r="C214" s="5" t="s">
-        <v>1182</v>
+        <v>1187</v>
       </c>
       <c r="D214" s="6" t="s">
-        <v>1183</v>
+        <v>1188</v>
       </c>
       <c r="E214" s="5" t="s">
-        <v>1184</v>
+        <v>1189</v>
       </c>
     </row>
     <row r="215" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -13116,16 +13360,16 @@
         <v>206</v>
       </c>
       <c r="B215" s="5" t="s">
-        <v>837</v>
+        <v>842</v>
       </c>
       <c r="C215" s="5" t="s">
-        <v>1185</v>
+        <v>1190</v>
       </c>
       <c r="D215" s="6" t="s">
-        <v>1186</v>
+        <v>1191</v>
       </c>
       <c r="E215" s="5" t="s">
-        <v>1187</v>
+        <v>1192</v>
       </c>
     </row>
     <row r="216" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -13133,16 +13377,16 @@
         <v>207</v>
       </c>
       <c r="B216" s="5" t="s">
-        <v>920</v>
+        <v>925</v>
       </c>
       <c r="C216" s="5" t="s">
-        <v>1188</v>
+        <v>1193</v>
       </c>
       <c r="D216" s="6" t="s">
-        <v>1189</v>
+        <v>1194</v>
       </c>
       <c r="E216" s="5" t="s">
-        <v>1187</v>
+        <v>1192</v>
       </c>
     </row>
     <row r="217" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -13150,16 +13394,16 @@
         <v>208</v>
       </c>
       <c r="B217" s="5" t="s">
-        <v>698</v>
+        <v>703</v>
       </c>
       <c r="C217" s="5" t="s">
-        <v>1190</v>
+        <v>1195</v>
       </c>
       <c r="D217" s="6" t="s">
-        <v>1191</v>
+        <v>1196</v>
       </c>
       <c r="E217" s="5" t="s">
-        <v>1192</v>
+        <v>1197</v>
       </c>
     </row>
     <row r="218" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -13167,16 +13411,16 @@
         <v>209</v>
       </c>
       <c r="B218" s="5" t="s">
-        <v>837</v>
+        <v>842</v>
       </c>
       <c r="C218" s="5" t="s">
-        <v>1193</v>
+        <v>1198</v>
       </c>
       <c r="D218" s="6" t="s">
-        <v>1194</v>
+        <v>1199</v>
       </c>
       <c r="E218" s="5" t="s">
-        <v>1192</v>
+        <v>1197</v>
       </c>
     </row>
     <row r="219" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -13184,16 +13428,16 @@
         <v>210</v>
       </c>
       <c r="B219" s="5" t="s">
-        <v>920</v>
+        <v>925</v>
       </c>
       <c r="C219" s="5" t="s">
-        <v>1195</v>
+        <v>1200</v>
       </c>
       <c r="D219" s="6" t="s">
-        <v>1196</v>
+        <v>1201</v>
       </c>
       <c r="E219" s="5" t="s">
-        <v>1192</v>
+        <v>1197</v>
       </c>
     </row>
     <row r="220" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -13201,16 +13445,16 @@
         <v>211</v>
       </c>
       <c r="B220" s="5" t="s">
-        <v>1061</v>
+        <v>1066</v>
       </c>
       <c r="C220" s="5" t="s">
+        <v>1202</v>
+      </c>
+      <c r="D220" s="6" t="s">
+        <v>1203</v>
+      </c>
+      <c r="E220" s="5" t="s">
         <v>1197</v>
-      </c>
-      <c r="D220" s="6" t="s">
-        <v>1198</v>
-      </c>
-      <c r="E220" s="5" t="s">
-        <v>1192</v>
       </c>
     </row>
     <row r="221" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -13218,16 +13462,16 @@
         <v>212</v>
       </c>
       <c r="B221" s="5" t="s">
-        <v>893</v>
+        <v>898</v>
       </c>
       <c r="C221" s="5" t="s">
-        <v>1199</v>
+        <v>1204</v>
       </c>
       <c r="D221" s="6" t="s">
-        <v>1200</v>
+        <v>1205</v>
       </c>
       <c r="E221" s="5" t="s">
-        <v>1201</v>
+        <v>1206</v>
       </c>
     </row>
     <row r="222" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -13235,16 +13479,16 @@
         <v>213</v>
       </c>
       <c r="B222" s="5" t="s">
-        <v>698</v>
+        <v>703</v>
       </c>
       <c r="C222" s="5" t="s">
-        <v>1202</v>
+        <v>1207</v>
       </c>
       <c r="D222" s="6" t="s">
-        <v>1203</v>
+        <v>1208</v>
       </c>
       <c r="E222" s="5" t="s">
-        <v>1204</v>
+        <v>1209</v>
       </c>
     </row>
     <row r="223" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -13252,16 +13496,16 @@
         <v>214</v>
       </c>
       <c r="B223" s="5" t="s">
-        <v>893</v>
+        <v>898</v>
       </c>
       <c r="C223" s="5" t="s">
-        <v>1205</v>
+        <v>1210</v>
       </c>
       <c r="D223" s="6" t="s">
-        <v>1206</v>
+        <v>1211</v>
       </c>
       <c r="E223" s="5" t="s">
-        <v>1204</v>
+        <v>1209</v>
       </c>
     </row>
     <row r="224" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -13269,16 +13513,16 @@
         <v>215</v>
       </c>
       <c r="B224" s="5" t="s">
-        <v>893</v>
+        <v>898</v>
       </c>
       <c r="C224" s="5" t="s">
-        <v>1207</v>
+        <v>1212</v>
       </c>
       <c r="D224" s="6" t="s">
-        <v>1208</v>
+        <v>1213</v>
       </c>
       <c r="E224" s="5" t="s">
-        <v>1204</v>
+        <v>1209</v>
       </c>
     </row>
     <row r="225" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -13286,16 +13530,16 @@
         <v>216</v>
       </c>
       <c r="B225" s="5" t="s">
-        <v>1061</v>
+        <v>1066</v>
       </c>
       <c r="C225" s="5" t="s">
+        <v>1214</v>
+      </c>
+      <c r="D225" s="6" t="s">
+        <v>1215</v>
+      </c>
+      <c r="E225" s="5" t="s">
         <v>1209</v>
-      </c>
-      <c r="D225" s="6" t="s">
-        <v>1210</v>
-      </c>
-      <c r="E225" s="5" t="s">
-        <v>1204</v>
       </c>
     </row>
     <row r="226" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -13303,16 +13547,16 @@
         <v>217</v>
       </c>
       <c r="B226" s="5" t="s">
-        <v>904</v>
+        <v>909</v>
       </c>
       <c r="C226" s="5" t="s">
-        <v>1211</v>
+        <v>1216</v>
       </c>
       <c r="D226" s="6" t="s">
-        <v>1212</v>
+        <v>1217</v>
       </c>
       <c r="E226" s="5" t="s">
-        <v>1213</v>
+        <v>1218</v>
       </c>
     </row>
     <row r="227" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -13320,16 +13564,16 @@
         <v>218</v>
       </c>
       <c r="B227" s="5" t="s">
-        <v>698</v>
+        <v>703</v>
       </c>
       <c r="C227" s="5" t="s">
-        <v>1214</v>
+        <v>1219</v>
       </c>
       <c r="D227" s="6" t="s">
-        <v>1215</v>
+        <v>1220</v>
       </c>
       <c r="E227" s="5" t="s">
-        <v>1213</v>
+        <v>1218</v>
       </c>
     </row>
     <row r="228" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -13337,16 +13581,16 @@
         <v>219</v>
       </c>
       <c r="B228" s="5" t="s">
-        <v>837</v>
+        <v>842</v>
       </c>
       <c r="C228" s="5" t="s">
-        <v>1216</v>
+        <v>1221</v>
       </c>
       <c r="D228" s="6" t="s">
-        <v>1217</v>
+        <v>1222</v>
       </c>
       <c r="E228" s="5" t="s">
-        <v>1213</v>
+        <v>1218</v>
       </c>
     </row>
     <row r="229" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -13354,16 +13598,16 @@
         <v>220</v>
       </c>
       <c r="B229" s="5" t="s">
-        <v>1061</v>
+        <v>1066</v>
       </c>
       <c r="C229" s="5" t="s">
+        <v>1223</v>
+      </c>
+      <c r="D229" s="6" t="s">
+        <v>1224</v>
+      </c>
+      <c r="E229" s="5" t="s">
         <v>1218</v>
-      </c>
-      <c r="D229" s="6" t="s">
-        <v>1219</v>
-      </c>
-      <c r="E229" s="5" t="s">
-        <v>1213</v>
       </c>
     </row>
     <row r="230" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -13371,16 +13615,16 @@
         <v>221</v>
       </c>
       <c r="B230" s="5" t="s">
-        <v>698</v>
+        <v>703</v>
       </c>
       <c r="C230" s="5" t="s">
-        <v>1220</v>
+        <v>1225</v>
       </c>
       <c r="D230" s="6" t="s">
-        <v>1221</v>
+        <v>1226</v>
       </c>
       <c r="E230" s="5" t="s">
-        <v>1222</v>
+        <v>1227</v>
       </c>
     </row>
     <row r="231" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -13388,16 +13632,16 @@
         <v>222</v>
       </c>
       <c r="B231" s="5" t="s">
-        <v>893</v>
+        <v>898</v>
       </c>
       <c r="C231" s="5" t="s">
-        <v>1223</v>
+        <v>1228</v>
       </c>
       <c r="D231" s="6" t="s">
-        <v>1224</v>
+        <v>1229</v>
       </c>
       <c r="E231" s="5" t="s">
-        <v>1222</v>
+        <v>1227</v>
       </c>
     </row>
     <row r="232" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -13405,16 +13649,16 @@
         <v>223</v>
       </c>
       <c r="B232" s="5" t="s">
-        <v>698</v>
+        <v>703</v>
       </c>
       <c r="C232" s="5" t="s">
-        <v>1225</v>
+        <v>1230</v>
       </c>
       <c r="D232" s="6" t="s">
-        <v>1226</v>
+        <v>1231</v>
       </c>
       <c r="E232" s="5" t="s">
-        <v>1227</v>
+        <v>1232</v>
       </c>
     </row>
     <row r="233" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -13422,16 +13666,16 @@
         <v>224</v>
       </c>
       <c r="B233" s="5" t="s">
-        <v>920</v>
+        <v>925</v>
       </c>
       <c r="C233" s="5" t="s">
-        <v>1228</v>
+        <v>1233</v>
       </c>
       <c r="D233" s="6" t="s">
-        <v>1229</v>
+        <v>1234</v>
       </c>
       <c r="E233" s="5" t="s">
-        <v>1227</v>
+        <v>1232</v>
       </c>
     </row>
     <row r="234" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -13439,16 +13683,16 @@
         <v>225</v>
       </c>
       <c r="B234" s="5" t="s">
-        <v>698</v>
+        <v>703</v>
       </c>
       <c r="C234" s="5" t="s">
-        <v>1230</v>
+        <v>1235</v>
       </c>
       <c r="D234" s="6" t="s">
-        <v>1231</v>
+        <v>1236</v>
       </c>
       <c r="E234" s="5" t="s">
-        <v>1232</v>
+        <v>1237</v>
       </c>
     </row>
     <row r="235" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -13456,16 +13700,16 @@
         <v>226</v>
       </c>
       <c r="B235" s="5" t="s">
-        <v>837</v>
+        <v>842</v>
       </c>
       <c r="C235" s="5" t="s">
-        <v>1233</v>
+        <v>1238</v>
       </c>
       <c r="D235" s="6" t="s">
-        <v>1234</v>
+        <v>1239</v>
       </c>
       <c r="E235" s="5" t="s">
-        <v>1232</v>
+        <v>1237</v>
       </c>
     </row>
     <row r="236" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -13473,16 +13717,16 @@
         <v>227</v>
       </c>
       <c r="B236" s="5" t="s">
-        <v>920</v>
+        <v>925</v>
       </c>
       <c r="C236" s="5" t="s">
-        <v>1235</v>
+        <v>1240</v>
       </c>
       <c r="D236" s="6" t="s">
-        <v>1236</v>
+        <v>1241</v>
       </c>
       <c r="E236" s="5" t="s">
-        <v>1232</v>
+        <v>1237</v>
       </c>
     </row>
     <row r="237" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -13490,16 +13734,16 @@
         <v>228</v>
       </c>
       <c r="B237" s="5" t="s">
-        <v>920</v>
+        <v>925</v>
       </c>
       <c r="C237" s="5" t="s">
-        <v>1237</v>
+        <v>1242</v>
       </c>
       <c r="D237" s="6" t="s">
-        <v>1238</v>
+        <v>1243</v>
       </c>
       <c r="E237" s="5" t="s">
-        <v>1239</v>
+        <v>1244</v>
       </c>
     </row>
     <row r="238" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -13507,16 +13751,16 @@
         <v>229</v>
       </c>
       <c r="B238" s="5" t="s">
-        <v>893</v>
+        <v>898</v>
       </c>
       <c r="C238" s="5" t="s">
-        <v>1240</v>
+        <v>1245</v>
       </c>
       <c r="D238" s="6" t="s">
-        <v>1241</v>
+        <v>1246</v>
       </c>
       <c r="E238" s="5" t="s">
-        <v>1239</v>
+        <v>1244</v>
       </c>
     </row>
     <row r="239" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -13524,16 +13768,16 @@
         <v>230</v>
       </c>
       <c r="B239" s="5" t="s">
-        <v>893</v>
+        <v>898</v>
       </c>
       <c r="C239" s="5" t="s">
-        <v>1242</v>
+        <v>1247</v>
       </c>
       <c r="D239" s="6" t="s">
-        <v>1243</v>
+        <v>1248</v>
       </c>
       <c r="E239" s="5" t="s">
-        <v>1239</v>
+        <v>1244</v>
       </c>
     </row>
     <row r="240" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -13541,16 +13785,16 @@
         <v>231</v>
       </c>
       <c r="B240" s="5" t="s">
-        <v>1061</v>
+        <v>1066</v>
       </c>
       <c r="C240" s="5" t="s">
+        <v>1249</v>
+      </c>
+      <c r="D240" s="6" t="s">
+        <v>1250</v>
+      </c>
+      <c r="E240" s="5" t="s">
         <v>1244</v>
-      </c>
-      <c r="D240" s="6" t="s">
-        <v>1245</v>
-      </c>
-      <c r="E240" s="5" t="s">
-        <v>1239</v>
       </c>
     </row>
     <row r="241" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -13558,16 +13802,16 @@
         <v>232</v>
       </c>
       <c r="B241" s="5" t="s">
-        <v>1061</v>
+        <v>1066</v>
       </c>
       <c r="C241" s="5" t="s">
-        <v>1246</v>
+        <v>1251</v>
       </c>
       <c r="D241" s="6" t="s">
-        <v>1247</v>
+        <v>1252</v>
       </c>
       <c r="E241" s="5" t="s">
-        <v>1239</v>
+        <v>1244</v>
       </c>
     </row>
     <row r="242" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -13575,13 +13819,13 @@
         <v>233</v>
       </c>
       <c r="B242" s="5" t="s">
-        <v>893</v>
+        <v>898</v>
       </c>
       <c r="C242" s="5" t="s">
-        <v>1248</v>
+        <v>1253</v>
       </c>
       <c r="D242" s="6" t="s">
-        <v>1249</v>
+        <v>1254</v>
       </c>
       <c r="E242" s="5" t="s">
         <v>559</v>
@@ -13592,16 +13836,16 @@
         <v>234</v>
       </c>
       <c r="B243" s="5" t="s">
-        <v>904</v>
+        <v>909</v>
       </c>
       <c r="C243" s="5" t="s">
-        <v>1250</v>
+        <v>1255</v>
       </c>
       <c r="D243" s="6" t="s">
-        <v>1251</v>
+        <v>1256</v>
       </c>
       <c r="E243" s="5" t="s">
-        <v>1252</v>
+        <v>1257</v>
       </c>
     </row>
     <row r="244" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -13609,16 +13853,16 @@
         <v>235</v>
       </c>
       <c r="B244" s="5" t="s">
-        <v>698</v>
+        <v>703</v>
       </c>
       <c r="C244" s="5" t="s">
-        <v>1253</v>
+        <v>1258</v>
       </c>
       <c r="D244" s="6" t="s">
-        <v>1254</v>
+        <v>1259</v>
       </c>
       <c r="E244" s="5" t="s">
-        <v>1252</v>
+        <v>1257</v>
       </c>
     </row>
     <row r="245" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -13626,16 +13870,16 @@
         <v>236</v>
       </c>
       <c r="B245" s="5" t="s">
-        <v>698</v>
+        <v>703</v>
       </c>
       <c r="C245" s="5" t="s">
-        <v>1255</v>
+        <v>1260</v>
       </c>
       <c r="D245" s="6" t="s">
-        <v>1256</v>
+        <v>1261</v>
       </c>
       <c r="E245" s="5" t="s">
-        <v>1252</v>
+        <v>1257</v>
       </c>
     </row>
     <row r="246" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -13643,16 +13887,16 @@
         <v>237</v>
       </c>
       <c r="B246" s="5" t="s">
-        <v>893</v>
+        <v>898</v>
       </c>
       <c r="C246" s="5" t="s">
+        <v>1262</v>
+      </c>
+      <c r="D246" s="6" t="s">
+        <v>1263</v>
+      </c>
+      <c r="E246" s="5" t="s">
         <v>1257</v>
-      </c>
-      <c r="D246" s="6" t="s">
-        <v>1258</v>
-      </c>
-      <c r="E246" s="5" t="s">
-        <v>1252</v>
       </c>
     </row>
     <row r="247" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -13660,13 +13904,13 @@
         <v>238</v>
       </c>
       <c r="B247" s="5" t="s">
-        <v>837</v>
+        <v>842</v>
       </c>
       <c r="C247" s="5" t="s">
-        <v>1259</v>
+        <v>1264</v>
       </c>
       <c r="D247" s="6" t="s">
-        <v>1260</v>
+        <v>1265</v>
       </c>
       <c r="E247" s="5" t="s">
         <v>562</v>
@@ -13677,16 +13921,16 @@
         <v>239</v>
       </c>
       <c r="B248" s="5" t="s">
-        <v>698</v>
+        <v>703</v>
       </c>
       <c r="C248" s="5" t="s">
-        <v>1261</v>
+        <v>1266</v>
       </c>
       <c r="D248" s="6" t="s">
-        <v>1262</v>
+        <v>1267</v>
       </c>
       <c r="E248" s="5" t="s">
-        <v>1263</v>
+        <v>1268</v>
       </c>
     </row>
     <row r="249" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -13694,16 +13938,16 @@
         <v>240</v>
       </c>
       <c r="B249" s="5" t="s">
-        <v>837</v>
+        <v>842</v>
       </c>
       <c r="C249" s="5" t="s">
-        <v>1264</v>
+        <v>1269</v>
       </c>
       <c r="D249" s="6" t="s">
-        <v>1265</v>
+        <v>1270</v>
       </c>
       <c r="E249" s="5" t="s">
-        <v>1263</v>
+        <v>1268</v>
       </c>
     </row>
     <row r="250" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -13711,16 +13955,16 @@
         <v>241</v>
       </c>
       <c r="B250" s="5" t="s">
-        <v>823</v>
+        <v>828</v>
       </c>
       <c r="C250" s="5" t="s">
-        <v>1266</v>
+        <v>1271</v>
       </c>
       <c r="D250" s="6" t="s">
-        <v>1267</v>
+        <v>1272</v>
       </c>
       <c r="E250" s="5" t="s">
-        <v>1268</v>
+        <v>1273</v>
       </c>
     </row>
     <row r="251" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -13728,16 +13972,16 @@
         <v>242</v>
       </c>
       <c r="B251" s="5" t="s">
-        <v>837</v>
+        <v>842</v>
       </c>
       <c r="C251" s="5" t="s">
-        <v>1269</v>
+        <v>1274</v>
       </c>
       <c r="D251" s="6" t="s">
-        <v>1270</v>
+        <v>1275</v>
       </c>
       <c r="E251" s="5" t="s">
-        <v>1271</v>
+        <v>1276</v>
       </c>
     </row>
     <row r="252" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -13745,16 +13989,16 @@
         <v>243</v>
       </c>
       <c r="B252" s="5" t="s">
-        <v>1272</v>
+        <v>1277</v>
       </c>
       <c r="C252" s="5" t="s">
-        <v>1273</v>
+        <v>1278</v>
       </c>
       <c r="D252" s="6" t="s">
-        <v>1274</v>
+        <v>1279</v>
       </c>
       <c r="E252" s="5" t="s">
-        <v>1275</v>
+        <v>1280</v>
       </c>
     </row>
     <row r="253" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -13762,16 +14006,16 @@
         <v>244</v>
       </c>
       <c r="B253" s="5" t="s">
-        <v>1276</v>
+        <v>1281</v>
       </c>
       <c r="C253" s="5" t="s">
-        <v>1277</v>
+        <v>1282</v>
       </c>
       <c r="D253" s="6" t="s">
-        <v>1278</v>
+        <v>1283</v>
       </c>
       <c r="E253" s="5" t="s">
-        <v>1263</v>
+        <v>1268</v>
       </c>
     </row>
     <row r="254" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -13779,16 +14023,16 @@
         <v>245</v>
       </c>
       <c r="B254" s="5" t="s">
-        <v>837</v>
+        <v>842</v>
       </c>
       <c r="C254" s="5" t="s">
-        <v>1279</v>
+        <v>1284</v>
       </c>
       <c r="D254" s="6" t="s">
-        <v>1280</v>
+        <v>1285</v>
       </c>
       <c r="E254" s="5" t="s">
-        <v>1271</v>
+        <v>1276</v>
       </c>
     </row>
     <row r="255" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -13796,16 +14040,16 @@
         <v>246</v>
       </c>
       <c r="B255" s="5" t="s">
-        <v>1272</v>
+        <v>1277</v>
       </c>
       <c r="C255" s="5" t="s">
-        <v>1281</v>
+        <v>1286</v>
       </c>
       <c r="D255" s="6" t="s">
-        <v>1282</v>
+        <v>1287</v>
       </c>
       <c r="E255" s="5" t="s">
-        <v>1268</v>
+        <v>1273</v>
       </c>
     </row>
     <row r="256" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -13813,16 +14057,16 @@
         <v>247</v>
       </c>
       <c r="B256" s="5" t="s">
-        <v>1283</v>
+        <v>1288</v>
       </c>
       <c r="C256" s="5" t="s">
-        <v>1284</v>
+        <v>1289</v>
       </c>
       <c r="D256" s="6" t="s">
-        <v>1285</v>
+        <v>1290</v>
       </c>
       <c r="E256" s="5" t="s">
-        <v>1271</v>
+        <v>1276</v>
       </c>
     </row>
     <row r="257" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -13830,16 +14074,16 @@
         <v>248</v>
       </c>
       <c r="B257" s="5" t="s">
-        <v>837</v>
+        <v>842</v>
       </c>
       <c r="C257" s="5" t="s">
-        <v>1286</v>
+        <v>1291</v>
       </c>
       <c r="D257" s="6" t="s">
-        <v>1287</v>
+        <v>1292</v>
       </c>
       <c r="E257" s="5" t="s">
-        <v>1271</v>
+        <v>1276</v>
       </c>
     </row>
     <row r="258" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -13847,16 +14091,16 @@
         <v>249</v>
       </c>
       <c r="B258" s="5" t="s">
-        <v>904</v>
+        <v>909</v>
       </c>
       <c r="C258" s="5" t="s">
-        <v>1288</v>
+        <v>1293</v>
       </c>
       <c r="D258" s="6" t="s">
-        <v>1289</v>
+        <v>1294</v>
       </c>
       <c r="E258" s="5" t="s">
-        <v>1271</v>
+        <v>1276</v>
       </c>
     </row>
     <row r="259" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -13864,16 +14108,16 @@
         <v>250</v>
       </c>
       <c r="B259" s="5" t="s">
-        <v>1276</v>
+        <v>1281</v>
       </c>
       <c r="C259" s="5" t="s">
-        <v>1290</v>
+        <v>1295</v>
       </c>
       <c r="D259" s="6" t="s">
-        <v>1291</v>
+        <v>1296</v>
       </c>
       <c r="E259" s="5" t="s">
-        <v>1275</v>
+        <v>1280</v>
       </c>
     </row>
     <row r="260" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -13881,16 +14125,16 @@
         <v>251</v>
       </c>
       <c r="B260" s="5" t="s">
-        <v>1272</v>
+        <v>1277</v>
       </c>
       <c r="C260" s="5" t="s">
-        <v>1292</v>
+        <v>1297</v>
       </c>
       <c r="D260" s="6" t="s">
-        <v>1293</v>
+        <v>1298</v>
       </c>
       <c r="E260" s="5" t="s">
-        <v>1294</v>
+        <v>1299</v>
       </c>
     </row>
     <row r="261" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -13898,16 +14142,16 @@
         <v>252</v>
       </c>
       <c r="B261" s="5" t="s">
-        <v>1272</v>
+        <v>1277</v>
       </c>
       <c r="C261" s="5" t="s">
-        <v>1295</v>
+        <v>1300</v>
       </c>
       <c r="D261" s="6" t="s">
-        <v>1296</v>
+        <v>1301</v>
       </c>
       <c r="E261" s="5" t="s">
-        <v>1294</v>
+        <v>1299</v>
       </c>
     </row>
     <row r="262" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -13915,16 +14159,16 @@
         <v>253</v>
       </c>
       <c r="B262" s="5" t="s">
-        <v>698</v>
+        <v>703</v>
       </c>
       <c r="C262" s="5" t="s">
-        <v>1297</v>
+        <v>1302</v>
       </c>
       <c r="D262" s="6" t="s">
-        <v>1298</v>
+        <v>1303</v>
       </c>
       <c r="E262" s="5" t="s">
-        <v>1294</v>
+        <v>1299</v>
       </c>
     </row>
     <row r="263" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -13932,16 +14176,16 @@
         <v>254</v>
       </c>
       <c r="B263" s="5" t="s">
-        <v>837</v>
+        <v>842</v>
       </c>
       <c r="C263" s="5" t="s">
-        <v>1299</v>
+        <v>1304</v>
       </c>
       <c r="D263" s="6" t="s">
-        <v>1300</v>
+        <v>1305</v>
       </c>
       <c r="E263" s="5" t="s">
-        <v>1301</v>
+        <v>1306</v>
       </c>
     </row>
     <row r="264" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -13949,16 +14193,16 @@
         <v>255</v>
       </c>
       <c r="B264" s="5" t="s">
-        <v>698</v>
+        <v>703</v>
       </c>
       <c r="C264" s="5" t="s">
-        <v>1302</v>
+        <v>1307</v>
       </c>
       <c r="D264" s="6" t="s">
-        <v>1303</v>
+        <v>1308</v>
       </c>
       <c r="E264" s="5" t="s">
-        <v>1304</v>
+        <v>1309</v>
       </c>
     </row>
     <row r="265" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -13966,16 +14210,16 @@
         <v>256</v>
       </c>
       <c r="B265" s="5" t="s">
-        <v>829</v>
+        <v>834</v>
       </c>
       <c r="C265" s="5" t="s">
-        <v>1305</v>
+        <v>1310</v>
       </c>
       <c r="D265" s="6" t="s">
-        <v>1306</v>
+        <v>1311</v>
       </c>
       <c r="E265" s="5" t="s">
-        <v>1304</v>
+        <v>1309</v>
       </c>
     </row>
     <row r="266" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -13983,16 +14227,16 @@
         <v>257</v>
       </c>
       <c r="B266" s="5" t="s">
-        <v>1307</v>
+        <v>1312</v>
       </c>
       <c r="C266" s="5" t="s">
-        <v>1308</v>
+        <v>1313</v>
       </c>
       <c r="D266" s="6" t="s">
-        <v>1309</v>
+        <v>1314</v>
       </c>
       <c r="E266" s="5" t="s">
-        <v>1294</v>
+        <v>1299</v>
       </c>
     </row>
     <row r="267" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -14000,16 +14244,16 @@
         <v>258</v>
       </c>
       <c r="B267" s="5" t="s">
-        <v>904</v>
+        <v>909</v>
       </c>
       <c r="C267" s="5" t="s">
-        <v>1310</v>
+        <v>1315</v>
       </c>
       <c r="D267" s="6" t="s">
-        <v>1311</v>
+        <v>1316</v>
       </c>
       <c r="E267" s="5" t="s">
-        <v>1294</v>
+        <v>1299</v>
       </c>
     </row>
     <row r="268" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -14017,16 +14261,16 @@
         <v>259</v>
       </c>
       <c r="B268" s="5" t="s">
-        <v>1061</v>
+        <v>1066</v>
       </c>
       <c r="C268" s="5" t="s">
-        <v>1312</v>
+        <v>1317</v>
       </c>
       <c r="D268" s="6" t="s">
-        <v>1313</v>
+        <v>1318</v>
       </c>
       <c r="E268" s="5" t="s">
-        <v>1314</v>
+        <v>1319</v>
       </c>
     </row>
     <row r="269" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -14034,16 +14278,16 @@
         <v>260</v>
       </c>
       <c r="B269" s="5" t="s">
-        <v>1272</v>
+        <v>1277</v>
       </c>
       <c r="C269" s="5" t="s">
-        <v>1315</v>
+        <v>1320</v>
       </c>
       <c r="D269" s="6" t="s">
-        <v>1316</v>
+        <v>1321</v>
       </c>
       <c r="E269" s="5" t="s">
-        <v>1317</v>
+        <v>1322</v>
       </c>
     </row>
     <row r="270" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -14051,16 +14295,16 @@
         <v>261</v>
       </c>
       <c r="B270" s="5" t="s">
-        <v>837</v>
+        <v>842</v>
       </c>
       <c r="C270" s="5" t="s">
-        <v>1318</v>
+        <v>1323</v>
       </c>
       <c r="D270" s="6" t="s">
-        <v>1319</v>
+        <v>1324</v>
       </c>
       <c r="E270" s="5" t="s">
-        <v>1317</v>
+        <v>1322</v>
       </c>
     </row>
     <row r="271" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -14068,16 +14312,16 @@
         <v>262</v>
       </c>
       <c r="B271" s="5" t="s">
-        <v>1272</v>
+        <v>1277</v>
       </c>
       <c r="C271" s="5" t="s">
-        <v>1320</v>
+        <v>1325</v>
       </c>
       <c r="D271" s="6" t="s">
-        <v>1321</v>
+        <v>1326</v>
       </c>
       <c r="E271" s="5" t="s">
-        <v>1317</v>
+        <v>1322</v>
       </c>
     </row>
     <row r="272" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -14085,16 +14329,16 @@
         <v>263</v>
       </c>
       <c r="B272" s="5" t="s">
-        <v>837</v>
+        <v>842</v>
       </c>
       <c r="C272" s="5" t="s">
+        <v>1327</v>
+      </c>
+      <c r="D272" s="6" t="s">
+        <v>1328</v>
+      </c>
+      <c r="E272" s="5" t="s">
         <v>1322</v>
-      </c>
-      <c r="D272" s="6" t="s">
-        <v>1323</v>
-      </c>
-      <c r="E272" s="5" t="s">
-        <v>1317</v>
       </c>
     </row>
     <row r="273" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -14102,16 +14346,16 @@
         <v>264</v>
       </c>
       <c r="B273" s="5" t="s">
-        <v>1061</v>
+        <v>1066</v>
       </c>
       <c r="C273" s="5" t="s">
-        <v>1324</v>
+        <v>1329</v>
       </c>
       <c r="D273" s="6" t="s">
-        <v>1325</v>
+        <v>1330</v>
       </c>
       <c r="E273" s="5" t="s">
-        <v>1326</v>
+        <v>1331</v>
       </c>
     </row>
     <row r="274" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -14119,16 +14363,16 @@
         <v>265</v>
       </c>
       <c r="B274" s="5" t="s">
-        <v>1283</v>
+        <v>1288</v>
       </c>
       <c r="C274" s="5" t="s">
-        <v>1327</v>
+        <v>1332</v>
       </c>
       <c r="D274" s="6" t="s">
-        <v>1328</v>
+        <v>1333</v>
       </c>
       <c r="E274" s="5" t="s">
-        <v>1317</v>
+        <v>1322</v>
       </c>
     </row>
     <row r="275" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -14136,237 +14380,407 @@
         <v>266</v>
       </c>
       <c r="B275" s="5" t="s">
-        <v>837</v>
+        <v>842</v>
       </c>
       <c r="C275" s="5" t="s">
-        <v>1329</v>
+        <v>1334</v>
       </c>
       <c r="D275" s="6" t="s">
-        <v>1330</v>
+        <v>1335</v>
       </c>
       <c r="E275" s="5" t="s">
-        <v>1314</v>
-      </c>
-    </row>
-    <row r="276" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+        <v>1319</v>
+      </c>
+    </row>
+    <row r="276" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A276" s="5" t="n">
         <v>267</v>
       </c>
       <c r="B276" s="5" t="s">
-        <v>1272</v>
+        <v>1277</v>
       </c>
       <c r="C276" s="5" t="s">
-        <v>1331</v>
+        <v>1336</v>
       </c>
       <c r="D276" s="6" t="s">
-        <v>1332</v>
+        <v>1337</v>
       </c>
       <c r="E276" s="5" t="s">
         <v>576</v>
       </c>
     </row>
-    <row r="277" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="277" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A277" s="5" t="n">
         <v>268</v>
       </c>
       <c r="B277" s="5" t="s">
-        <v>1272</v>
+        <v>1277</v>
       </c>
       <c r="C277" s="5" t="s">
-        <v>1333</v>
+        <v>1338</v>
       </c>
       <c r="D277" s="6" t="s">
-        <v>1334</v>
+        <v>1339</v>
       </c>
       <c r="E277" s="5" t="s">
-        <v>1335</v>
-      </c>
-    </row>
-    <row r="278" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+        <v>1340</v>
+      </c>
+    </row>
+    <row r="278" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A278" s="5" t="n">
         <v>269</v>
       </c>
       <c r="B278" s="5" t="s">
-        <v>837</v>
+        <v>842</v>
       </c>
       <c r="C278" s="5" t="s">
-        <v>1336</v>
+        <v>1341</v>
       </c>
       <c r="D278" s="6" t="s">
-        <v>1337</v>
+        <v>1342</v>
       </c>
       <c r="E278" s="5" t="s">
-        <v>1338</v>
-      </c>
-    </row>
-    <row r="279" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+        <v>1343</v>
+      </c>
+    </row>
+    <row r="279" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A279" s="5" t="n">
         <v>270</v>
       </c>
       <c r="B279" s="5" t="s">
-        <v>1272</v>
+        <v>1277</v>
       </c>
       <c r="C279" s="5" t="s">
-        <v>1339</v>
+        <v>1344</v>
       </c>
       <c r="D279" s="6" t="s">
-        <v>1340</v>
+        <v>1345</v>
       </c>
       <c r="E279" s="5" t="s">
-        <v>1341</v>
-      </c>
-    </row>
-    <row r="280" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+        <v>1346</v>
+      </c>
+    </row>
+    <row r="280" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A280" s="5" t="n">
         <v>271</v>
       </c>
       <c r="B280" s="5" t="s">
-        <v>829</v>
+        <v>834</v>
       </c>
       <c r="C280" s="5" t="s">
-        <v>1342</v>
+        <v>1347</v>
       </c>
       <c r="D280" s="6" t="s">
-        <v>1343</v>
+        <v>1348</v>
       </c>
       <c r="E280" s="5" t="s">
         <v>576</v>
       </c>
     </row>
-    <row r="281" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="281" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A281" s="5" t="n">
         <v>272</v>
       </c>
       <c r="B281" s="5" t="s">
-        <v>1272</v>
+        <v>1277</v>
       </c>
       <c r="C281" s="5" t="s">
-        <v>1344</v>
+        <v>1349</v>
       </c>
       <c r="D281" s="6" t="s">
-        <v>1345</v>
+        <v>1350</v>
       </c>
       <c r="E281" s="5" t="s">
-        <v>1346</v>
-      </c>
-    </row>
-    <row r="282" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+        <v>1351</v>
+      </c>
+    </row>
+    <row r="282" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A282" s="5" t="n">
         <v>273</v>
       </c>
       <c r="B282" s="5" t="s">
-        <v>1283</v>
+        <v>1288</v>
       </c>
       <c r="C282" s="5" t="s">
-        <v>1347</v>
+        <v>1352</v>
       </c>
       <c r="D282" s="6" t="s">
-        <v>1348</v>
+        <v>1353</v>
       </c>
       <c r="E282" s="5" t="s">
-        <v>1349</v>
-      </c>
-    </row>
-    <row r="283" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+        <v>1354</v>
+      </c>
+    </row>
+    <row r="283" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A283" s="5" t="n">
         <v>274</v>
       </c>
       <c r="B283" s="5" t="s">
-        <v>1283</v>
+        <v>1288</v>
       </c>
       <c r="C283" s="5" t="s">
-        <v>1350</v>
+        <v>1355</v>
       </c>
       <c r="D283" s="6" t="s">
-        <v>1351</v>
+        <v>1356</v>
       </c>
       <c r="E283" s="5" t="s">
-        <v>1341</v>
-      </c>
-    </row>
-    <row r="284" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+        <v>1346</v>
+      </c>
+    </row>
+    <row r="284" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A284" s="5" t="n">
         <v>275</v>
       </c>
       <c r="B284" s="5" t="s">
-        <v>847</v>
+        <v>852</v>
       </c>
       <c r="C284" s="5" t="s">
-        <v>1352</v>
+        <v>1357</v>
       </c>
       <c r="D284" s="6" t="s">
-        <v>1353</v>
+        <v>1358</v>
       </c>
       <c r="E284" s="5" t="s">
-        <v>1349</v>
-      </c>
-    </row>
-    <row r="285" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+        <v>1354</v>
+      </c>
+    </row>
+    <row r="285" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A285" s="5" t="n">
         <v>276</v>
       </c>
       <c r="B285" s="5" t="s">
-        <v>829</v>
+        <v>834</v>
       </c>
       <c r="C285" s="5" t="s">
-        <v>1354</v>
+        <v>1359</v>
       </c>
       <c r="D285" s="6" t="s">
-        <v>1355</v>
+        <v>1360</v>
       </c>
       <c r="E285" s="5" t="s">
-        <v>1338</v>
-      </c>
-    </row>
-    <row r="286" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+        <v>1343</v>
+      </c>
+    </row>
+    <row r="286" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A286" s="5" t="n">
         <v>277</v>
       </c>
       <c r="B286" s="5" t="s">
-        <v>1272</v>
+        <v>1277</v>
       </c>
       <c r="C286" s="5" t="s">
-        <v>1356</v>
+        <v>1361</v>
       </c>
       <c r="D286" s="6" t="s">
-        <v>1357</v>
+        <v>1362</v>
       </c>
       <c r="E286" s="5" t="s">
-        <v>1346</v>
-      </c>
-    </row>
-    <row r="287" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+        <v>1351</v>
+      </c>
+    </row>
+    <row r="287" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A287" s="5" t="n">
         <v>278</v>
       </c>
       <c r="B287" s="5" t="s">
-        <v>847</v>
+        <v>852</v>
       </c>
       <c r="C287" s="5" t="s">
-        <v>1358</v>
+        <v>1363</v>
       </c>
       <c r="D287" s="6" t="s">
-        <v>1359</v>
+        <v>1364</v>
       </c>
       <c r="E287" s="5" t="s">
-        <v>1335</v>
-      </c>
-    </row>
-    <row r="288" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+        <v>1340</v>
+      </c>
+    </row>
+    <row r="288" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A288" s="5" t="n">
         <v>279</v>
       </c>
       <c r="B288" s="5" t="s">
-        <v>837</v>
+        <v>842</v>
       </c>
       <c r="C288" s="5" t="s">
-        <v>1360</v>
+        <v>1365</v>
       </c>
       <c r="D288" s="6" t="s">
-        <v>1361</v>
+        <v>1366</v>
       </c>
       <c r="E288" s="5" t="s">
-        <v>1362</v>
+        <v>1367</v>
+      </c>
+    </row>
+    <row r="289" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A289" s="5" t="n">
+        <v>280</v>
+      </c>
+      <c r="B289" s="5" t="s">
+        <v>842</v>
+      </c>
+      <c r="C289" s="5" t="s">
+        <v>1368</v>
+      </c>
+      <c r="D289" s="6" t="s">
+        <v>1369</v>
+      </c>
+      <c r="E289" s="5" t="s">
+        <v>584</v>
+      </c>
+    </row>
+    <row r="290" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A290" s="5" t="n">
+        <v>281</v>
+      </c>
+      <c r="B290" s="5" t="s">
+        <v>842</v>
+      </c>
+      <c r="C290" s="5" t="s">
+        <v>1370</v>
+      </c>
+      <c r="D290" s="6" t="s">
+        <v>1371</v>
+      </c>
+      <c r="E290" s="5" t="s">
+        <v>1372</v>
+      </c>
+    </row>
+    <row r="291" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A291" s="5" t="n">
+        <v>282</v>
+      </c>
+      <c r="B291" s="5" t="s">
+        <v>1277</v>
+      </c>
+      <c r="C291" s="5" t="s">
+        <v>1373</v>
+      </c>
+      <c r="D291" s="6" t="s">
+        <v>1374</v>
+      </c>
+      <c r="E291" s="5" t="s">
+        <v>1375</v>
+      </c>
+    </row>
+    <row r="292" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A292" s="5" t="n">
+        <v>283</v>
+      </c>
+      <c r="B292" s="5" t="s">
+        <v>1066</v>
+      </c>
+      <c r="C292" s="5" t="s">
+        <v>1376</v>
+      </c>
+      <c r="D292" s="6" t="s">
+        <v>1377</v>
+      </c>
+      <c r="E292" s="5" t="s">
+        <v>1378</v>
+      </c>
+    </row>
+    <row r="293" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A293" s="5" t="n">
+        <v>284</v>
+      </c>
+      <c r="B293" s="5" t="s">
+        <v>834</v>
+      </c>
+      <c r="C293" s="5" t="s">
+        <v>1379</v>
+      </c>
+      <c r="D293" s="6" t="s">
+        <v>1380</v>
+      </c>
+      <c r="E293" s="5" t="s">
+        <v>1372</v>
+      </c>
+    </row>
+    <row r="294" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A294" s="5" t="n">
+        <v>285</v>
+      </c>
+      <c r="B294" s="5" t="s">
+        <v>1066</v>
+      </c>
+      <c r="C294" s="5" t="s">
+        <v>1381</v>
+      </c>
+      <c r="D294" s="6" t="s">
+        <v>1382</v>
+      </c>
+      <c r="E294" s="5" t="s">
+        <v>1372</v>
+      </c>
+    </row>
+    <row r="295" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A295" s="5" t="n">
+        <v>286</v>
+      </c>
+      <c r="B295" s="5" t="s">
+        <v>925</v>
+      </c>
+      <c r="C295" s="5" t="s">
+        <v>1383</v>
+      </c>
+      <c r="D295" s="6" t="s">
+        <v>1384</v>
+      </c>
+      <c r="E295" s="5" t="s">
+        <v>1378</v>
+      </c>
+    </row>
+    <row r="296" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A296" s="5" t="n">
+        <v>287</v>
+      </c>
+      <c r="B296" s="5" t="s">
+        <v>1277</v>
+      </c>
+      <c r="C296" s="5" t="s">
+        <v>1385</v>
+      </c>
+      <c r="D296" s="6" t="s">
+        <v>1386</v>
+      </c>
+      <c r="E296" s="5" t="s">
+        <v>1372</v>
+      </c>
+    </row>
+    <row r="297" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A297" s="5" t="n">
+        <v>288</v>
+      </c>
+      <c r="B297" s="5" t="s">
+        <v>834</v>
+      </c>
+      <c r="C297" s="5" t="s">
+        <v>1387</v>
+      </c>
+      <c r="D297" s="6" t="s">
+        <v>1388</v>
+      </c>
+      <c r="E297" s="5" t="s">
+        <v>1375</v>
+      </c>
+    </row>
+    <row r="298" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A298" s="5" t="n">
+        <v>289</v>
+      </c>
+      <c r="B298" s="5" t="s">
+        <v>852</v>
+      </c>
+      <c r="C298" s="5" t="s">
+        <v>1389</v>
+      </c>
+      <c r="D298" s="6" t="s">
+        <v>1390</v>
+      </c>
+      <c r="E298" s="5" t="s">
+        <v>1378</v>
       </c>
     </row>
   </sheetData>
@@ -14580,6 +14994,16 @@
     <hyperlink ref="D286" r:id="rId204" display="https://www.axios.com/2026/10/13/trump-russian-diesel-deal-betrayal-bipartisan-letter"/>
     <hyperlink ref="D287" r:id="rId205" display="https://www.bloomberg.com/news/articles/2026-10-14/trump-pardons-two-alaska-mechanics-over-clean-air-act-violations"/>
     <hyperlink ref="D288" r:id="rId206" display="https://www.theguardian.com/commentisfree/2026/oct/16/donald-trump-russia-ukraine-protect-world"/>
+    <hyperlink ref="D289" r:id="rId207" display="https://www.theguardian.com/us-news/video/2026/oct/19/us-citizen-injured-by-ice-agents-in-california-video"/>
+    <hyperlink ref="D290" r:id="rId208" display="https://www.theguardian.com/us-news/2026/oct/21/ice-detention-illness-deportation-florida"/>
+    <hyperlink ref="D291" r:id="rId209" display="https://www.axios.com/2026/10/23/trump-administration-sues-alaska-dan-sullivan"/>
+    <hyperlink ref="D292" r:id="rId210" display="https://www.pbs.org/newshour/show/doj-monitoring-plans-and-dhs-voter-checks-raise-concerns-of-election-interference"/>
+    <hyperlink ref="D293" r:id="rId211" display="https://thehill.com/regulation/court-battles/6164069-trump-asks-scotus-big-bend-wall/"/>
+    <hyperlink ref="D294" r:id="rId212" display="https://www.pbs.org/newshour/show/investigation-finds-hundreds-of-u-s-citizens-detained-by-ice"/>
+    <hyperlink ref="D295" r:id="rId213" display="https://www.cbsnews.com/video/dhs-knocks-on-doors-over-citizenship-voting/"/>
+    <hyperlink ref="D296" r:id="rId214" display="https://www.axios.com/2026/10/21/white-house-politico-retract-stories-or-face-consequences"/>
+    <hyperlink ref="D297" r:id="rId215" display="https://thehill.com/regulation/court-battles/6168756-trump-los-angeles-deployment-unlawful-appeals-court-ruling/"/>
+    <hyperlink ref="D298" r:id="rId216" display="https://www.bloomberg.com/news/videos/2026-10-22/farkas-says-starlink-slowdown-helped-the-russians-video"/>
   </hyperlinks>
   <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.511811023622047" footer="0.511811023622047"/>
@@ -14597,7 +15021,7 @@
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
   <dimension ref="A1:B25"/>
-  <sheetFormatPr defaultColWidth="8.6875" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <sheetFormatPr defaultColWidth="8.6875" defaultRowHeight="15" customHeight="false" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="30.01"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="1" width="10"/>
@@ -14605,7 +15029,7 @@
   <sheetData>
     <row r="1" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A1" s="7" t="s">
-        <v>1363</v>
+        <v>1391</v>
       </c>
       <c r="B1" s="7"/>
     </row>
@@ -14614,7 +15038,7 @@
         <v>3</v>
       </c>
       <c r="B2" s="8" t="s">
-        <v>1364</v>
+        <v>1392</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -14641,7 +15065,7 @@
       </c>
       <c r="B5" s="9" t="n">
         <f aca="false">COUNTIF('Weekly Timeline'!C:C,A5)</f>
-        <v>11</v>
+        <v>12</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -14686,7 +15110,7 @@
       </c>
       <c r="B10" s="9" t="n">
         <f aca="false">COUNTIF('Weekly Timeline'!C:C,A10)</f>
-        <v>7</v>
+        <v>10</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -14704,7 +15128,7 @@
       </c>
       <c r="B12" s="9" t="n">
         <f aca="false">COUNTIF('Weekly Timeline'!C:C,A12)</f>
-        <v>38</v>
+        <v>39</v>
       </c>
     </row>
     <row r="13" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -14722,7 +15146,7 @@
       </c>
       <c r="B14" s="9" t="n">
         <f aca="false">COUNTIF('Weekly Timeline'!C:C,A14)</f>
-        <v>21</v>
+        <v>22</v>
       </c>
     </row>
     <row r="15" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -14785,7 +15209,7 @@
       </c>
       <c r="B21" s="9" t="n">
         <f aca="false">COUNTIF('Weekly Timeline'!C:C,A21)</f>
-        <v>7</v>
+        <v>10</v>
       </c>
     </row>
     <row r="22" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -14794,7 +15218,7 @@
       </c>
       <c r="B22" s="9" t="n">
         <f aca="false">COUNTIF('Weekly Timeline'!C:C,A22)</f>
-        <v>15</v>
+        <v>16</v>
       </c>
     </row>
     <row r="23" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -14817,11 +15241,11 @@
     </row>
     <row r="25" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A25" s="10" t="s">
-        <v>1365</v>
+        <v>1393</v>
       </c>
       <c r="B25" s="10" t="n">
         <f aca="false">SUM(B3:B24)</f>
-        <v>223</v>
+        <v>233</v>
       </c>
     </row>
   </sheetData>
